--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,7 +892,7 @@
         <v>226.549723637419</v>
       </c>
       <c r="AB3" t="n">
-        <v>490.6936524638191</v>
+        <v>490.6936524638192</v>
       </c>
       <c r="AC3" t="n">
         <v>124</v>
@@ -922,7 +922,7 @@
         <v>1.745635268477249</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="AM3" t="n">
         <v>214.728675813495</v>
@@ -1019,7 +1019,7 @@
         <v>34.92747542249608</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.00881231720520243</v>
+        <v>-0.0088123172052024</v>
       </c>
       <c r="U4" t="n">
         <v>0.4603174603174603</v>
@@ -1070,7 +1070,7 @@
         <v>34.70906596802268</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.02194268614028044</v>
+        <v>-0.0219426861402804</v>
       </c>
       <c r="AL4" t="n">
         <v>0.4274193548387097</v>
@@ -1152,7 +1152,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N5" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O5" t="n">
         <v>74.91719886917585</v>
@@ -1161,7 +1161,7 @@
         <v>78.39571411846676</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.711013572373497</v>
+        <v>9.711013572373496</v>
       </c>
       <c r="R5" t="n">
         <v>61.29707440530581</v>
@@ -1173,7 +1173,7 @@
         <v>-1.116510525741735</v>
       </c>
       <c r="U5" t="n">
-        <v>0.253968253968254</v>
+        <v>0.2539682539682539</v>
       </c>
       <c r="V5" t="n">
         <v>344.3134935761985</v>
@@ -1203,7 +1203,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE5" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF5" t="n">
         <v>72.7265189141975</v>
@@ -1324,7 +1324,7 @@
         <v>-0.6813979368487536</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.238095238095238</v>
       </c>
       <c r="V6" t="n">
         <v>330.7495644540284</v>
@@ -1366,7 +1366,7 @@
         <v>1.920880039883152</v>
       </c>
       <c r="AI6" t="n">
-        <v>27.64653123825595</v>
+        <v>27.64653123825596</v>
       </c>
       <c r="AJ6" t="n">
         <v>32.6446195792587</v>
@@ -1375,7 +1375,7 @@
         <v>-1.014415354377868</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1370967741935484</v>
+        <v>0.1370967741935483</v>
       </c>
       <c r="AM6" t="n">
         <v>330.7495644540284</v>
@@ -1460,7 +1460,7 @@
         <v>24.81354057111685</v>
       </c>
       <c r="P7" t="n">
-        <v>24.45551391965331</v>
+        <v>24.4555139196533</v>
       </c>
       <c r="Q7" t="n">
         <v>2.599953635337401</v>
@@ -1623,7 +1623,7 @@
         <v>26.50944369222463</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03203632796460248</v>
+        <v>0.0320363279646024</v>
       </c>
       <c r="U8" t="n">
         <v>0.5238095238095238</v>
@@ -1641,7 +1641,7 @@
         <v>396.1754903124479</v>
       </c>
       <c r="Z8" t="n">
-        <v>435.8921394113643</v>
+        <v>435.8921394113642</v>
       </c>
       <c r="AA8" t="n">
         <v>389.6339176600243</v>
@@ -1662,7 +1662,7 @@
         <v>27.43189715615672</v>
       </c>
       <c r="AG8" t="n">
-        <v>25.35834965517999</v>
+        <v>25.35834965518</v>
       </c>
       <c r="AH8" t="n">
         <v>4.118216138579381</v>
@@ -1759,13 +1759,13 @@
         <v>42.60474344487245</v>
       </c>
       <c r="O9" t="n">
-        <v>38.41600789652239</v>
+        <v>38.4160078965224</v>
       </c>
       <c r="P9" t="n">
         <v>37.71936770955563</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.917248392190739</v>
+        <v>1.917248392190738</v>
       </c>
       <c r="R9" t="n">
         <v>36.41976247191899</v>
@@ -1789,7 +1789,7 @@
         <v>119.0896244792194</v>
       </c>
       <c r="Y9" t="n">
-        <v>113.1461544634281</v>
+        <v>113.1461544634282</v>
       </c>
       <c r="Z9" t="n">
         <v>125.0330944950107</v>
@@ -1804,13 +1804,13 @@
         <v>89</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE9" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF9" t="n">
-        <v>24.66089290957747</v>
+        <v>24.66089290957746</v>
       </c>
       <c r="AG9" t="n">
         <v>32.4901173708467</v>
@@ -1825,10 +1825,10 @@
         <v>39.10988125405291</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.1186763619131203</v>
+        <v>0.1186763619131202</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.348314606741573</v>
       </c>
       <c r="AM9" t="n">
         <v>10.81762752038992</v>
@@ -1928,7 +1928,7 @@
         <v>-1.672769915643793</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01587301587301587</v>
+        <v>0.0158730158730158</v>
       </c>
       <c r="V10" t="n">
         <v>204.7859172733417</v>
@@ -1961,7 +1961,7 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF10" t="n">
-        <v>38.32041307606467</v>
+        <v>38.32041307606468</v>
       </c>
       <c r="AG10" t="n">
         <v>37.37551007952008</v>
@@ -1979,7 +1979,7 @@
         <v>-1.731914848513478</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.0140845070422535</v>
       </c>
       <c r="AM10" t="n">
         <v>204.7859172733417</v>
@@ -2001,6 +2001,1365 @@
       </c>
       <c r="AS10" t="n">
         <v>288.2239191794881</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>301.54</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.506054</v>
+      </c>
+      <c r="K11" t="n">
+        <v>67</v>
+      </c>
+      <c r="L11" t="n">
+        <v>62</v>
+      </c>
+      <c r="M11" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N11" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O11" t="n">
+        <v>34.29914316528635</v>
+      </c>
+      <c r="P11" t="n">
+        <v>34.20253319076345</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.086475296404038</v>
+      </c>
+      <c r="R11" t="n">
+        <v>31.83607656744462</v>
+      </c>
+      <c r="S11" t="n">
+        <v>37.38147763305368</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.057722005392147</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.7903225806451613</v>
+      </c>
+      <c r="V11" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="W11" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X11" t="n">
+        <v>283.3109225452652</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>266.0766365969678</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>300.5452084935625</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>262.9659924470926</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>308.7710052490234</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>34.49176155124631</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.777300376160677</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>36.91245386750294</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.133343848778651</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.8114754098360656</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>284.9019504132945</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>270.2214493062074</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>299.5824515203817</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>265.4011122227922</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>304.8968689455743</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>490.33</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J12" t="n">
+        <v>163.98996</v>
+      </c>
+      <c r="K12" t="n">
+        <v>63</v>
+      </c>
+      <c r="L12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M12" t="n">
+        <v>72.9773582602447</v>
+      </c>
+      <c r="N12" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="O12" t="n">
+        <v>117.0632143411623</v>
+      </c>
+      <c r="P12" t="n">
+        <v>118.5924486844045</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>34.08285792004858</v>
+      </c>
+      <c r="R12" t="n">
+        <v>75.99849139519458</v>
+      </c>
+      <c r="S12" t="n">
+        <v>164.9360701764216</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.3768430384834</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="V12" t="n">
+        <v>218.2023011981317</v>
+      </c>
+      <c r="W12" t="n">
+        <v>531.8474945568648</v>
+      </c>
+      <c r="X12" t="n">
+        <v>350.0190108800753</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>248.11126569913</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>451.9267560610205</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>227.2354892716318</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>493.1588498275007</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>107.2228551603934</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>105.0953815714424</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>29.0980349864215</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>149.0626240714652</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.950891352838665</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.9426229508196722</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>531.8474945568648</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>320.5963369295761</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>233.5932123201758</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>407.5994615389765</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>225.7991528435473</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>445.6972459736809</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>245.22</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>31.64129</v>
+      </c>
+      <c r="K13" t="n">
+        <v>67</v>
+      </c>
+      <c r="L13" t="n">
+        <v>62</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O13" t="n">
+        <v>31.70656586892432</v>
+      </c>
+      <c r="P13" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.364655164592175</v>
+      </c>
+      <c r="R13" t="n">
+        <v>29.05425429510439</v>
+      </c>
+      <c r="S13" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.02760481523976249</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="V13" t="n">
+        <v>215.4651285381663</v>
+      </c>
+      <c r="W13" t="n">
+        <v>285.3448290538921</v>
+      </c>
+      <c r="X13" t="n">
+        <v>245.7258854841635</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>227.3998079585741</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>264.0519630097529</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>225.170470787059</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>270.758191884146</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>31.6787340441008</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>31.95592771818937</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.268451172495901</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>28.94741893645942</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.01650643600126667</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>214.8706343050948</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>285.3448290538921</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>245.5101888417812</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>227.929692254938</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>263.0906854286245</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>224.3424967575606</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>269.1076750070314</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>396.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J14" t="n">
+        <v>65.77114</v>
+      </c>
+      <c r="K14" t="n">
+        <v>33</v>
+      </c>
+      <c r="L14" t="n">
+        <v>62</v>
+      </c>
+      <c r="M14" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N14" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O14" t="n">
+        <v>75.04499179120712</v>
+      </c>
+      <c r="P14" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9.781241462981987</v>
+      </c>
+      <c r="R14" t="n">
+        <v>61.29473531920079</v>
+      </c>
+      <c r="S14" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.9481262502622875</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="V14" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="W14" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X14" t="n">
+        <v>452.521300500979</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>393.5404144791976</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>511.5021865227603</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>369.6072539747808</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>503.467376494826</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>117</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>72.76569347655681</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>71.85744439530923</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>7.673032529667959</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>62.51890781097711</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>82.39649127566095</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.9115761531717999</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.1709401709401709</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>438.7771316636375</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>392.5087455097398</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>485.0455178175354</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>376.989014100192</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>496.8508423922356</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="I15" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J15" t="n">
+        <v>27.5492</v>
+      </c>
+      <c r="K15" t="n">
+        <v>37</v>
+      </c>
+      <c r="L15" t="n">
+        <v>62</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N15" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O15" t="n">
+        <v>29.0332733400003</v>
+      </c>
+      <c r="P15" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.623880269917904</v>
+      </c>
+      <c r="R15" t="n">
+        <v>27.14135001944186</v>
+      </c>
+      <c r="S15" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.9139056416242591</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.1774193548387097</v>
+      </c>
+      <c r="V15" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W15" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X15" t="n">
+        <v>380.6262134874038</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>359.3371431487801</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>401.9152838260276</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>355.8230987548828</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>29.83504690282757</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>29.46390610450698</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.933208796634226</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>27.59935151416874</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>32.65449124757065</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-1.182410770532027</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.09016393442622951</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>391.1374648960694</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>365.7930975721947</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>416.4818322199441</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>361.8274983507521</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>428.1003802556511</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>585.39</v>
+      </c>
+      <c r="I16" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21.279171</v>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>62</v>
+      </c>
+      <c r="M16" t="n">
+        <v>21.28690962357955</v>
+      </c>
+      <c r="N16" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O16" t="n">
+        <v>24.6634695409604</v>
+      </c>
+      <c r="P16" t="n">
+        <v>24.37526659033764</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.603320992855815</v>
+      </c>
+      <c r="R16" t="n">
+        <v>21.93440007990057</v>
+      </c>
+      <c r="S16" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.299992797756324</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>585.6028837446734</v>
+      </c>
+      <c r="W16" t="n">
+        <v>806.3861287434895</v>
+      </c>
+      <c r="X16" t="n">
+        <v>678.4920470718207</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>606.8746865583573</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>750.1094075852842</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>603.4153461980646</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>786.1805475110751</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>21.28690962357955</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>26.56178868730787</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>27.52679771768262</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.759774229104261</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>22.19181840376421</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>29.31080928832899</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-1.914148495046441</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>585.6028837446734</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>730.7148067878396</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>654.7934177451815</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>806.6361958304979</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>610.4969242875534</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>806.3403635219306</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>411.74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.508333</v>
+      </c>
+      <c r="K17" t="n">
+        <v>67</v>
+      </c>
+      <c r="L17" t="n">
+        <v>62</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N17" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24.76636544625846</v>
+      </c>
+      <c r="P17" t="n">
+        <v>24.72342929518021</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.186495357009306</v>
+      </c>
+      <c r="R17" t="n">
+        <v>23.21232073451669</v>
+      </c>
+      <c r="S17" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.2174744677542248</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3870967741935484</v>
+      </c>
+      <c r="V17" t="n">
+        <v>374.8427651926008</v>
+      </c>
+      <c r="W17" t="n">
+        <v>460.5199890136719</v>
+      </c>
+      <c r="X17" t="n">
+        <v>416.0749394971421</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>396.1418174993858</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>436.0080614948985</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>389.9669883398803</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>445.5025934788345</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>27.23040246766649</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>25.30487804878049</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3.996590461513518</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>23.45741009548204</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>34.08285908814344</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.6810979243131255</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.2131147540983606</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>374.8427651926008</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>583.1248801870332</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>457.4707614567971</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>390.32804170337</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>524.6134812102242</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>394.0844896040983</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>572.5920326808099</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>26.658066</v>
+      </c>
+      <c r="K18" t="n">
+        <v>67</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26</v>
+      </c>
+      <c r="M18" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="N18" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="O18" t="n">
+        <v>38.40270594790844</v>
+      </c>
+      <c r="P18" t="n">
+        <v>37.65019654285294</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.990322096160243</v>
+      </c>
+      <c r="R18" t="n">
+        <v>36.38339890792905</v>
+      </c>
+      <c r="S18" t="n">
+        <v>41.39130483031742</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-5.900874019620422</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>111.4039503255851</v>
+      </c>
+      <c r="W18" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="X18" t="n">
+        <v>119.0483884385162</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>112.8783899404194</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>125.2183869366129</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>112.7885366145801</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>128.313044973984</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>86</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>25.3821414425773</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>32.59090830686063</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>15.350467123509</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.777151179492922</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>39.12055275656958</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.08311959155097284</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>78.68463847198962</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>31.09819038911171</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>126.2710865548675</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>11.70916865642806</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>121.2737135453657</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-09 03:47:43</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>208.64</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.950994</v>
+      </c>
+      <c r="K19" t="n">
+        <v>65</v>
+      </c>
+      <c r="L19" t="n">
+        <v>62</v>
+      </c>
+      <c r="M19" t="n">
+        <v>31.4088830173837</v>
+      </c>
+      <c r="N19" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O19" t="n">
+        <v>38.36880050331563</v>
+      </c>
+      <c r="P19" t="n">
+        <v>37.38367353166852</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.287242152477702</v>
+      </c>
+      <c r="R19" t="n">
+        <v>32.91071986713963</v>
+      </c>
+      <c r="S19" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.496954516461501</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="V19" t="n">
+        <v>205.1000061035156</v>
+      </c>
+      <c r="W19" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X19" t="n">
+        <v>250.5482672866511</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>222.5525760309716</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>278.5439585423305</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>214.9070007324218</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>31.4088830173837</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>38.23194894045754</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>37.36530537507971</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4.00582481027654</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>33.02649341717613</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>44.17734698860012</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1.567955474324383</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>205.1000061035156</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>249.6546265811877</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>223.4965905700819</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>275.8126625922935</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>215.6630020141602</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>288.4780758355588</v>
       </c>
     </row>
   </sheetData>
@@ -2247,12 +3606,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2281,19 +3640,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>365.76</v>
+        <v>361.17</v>
       </c>
       <c r="I2" t="n">
-        <v>13.09</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.94194</v>
+        <v>27.5492</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -2302,49 +3661,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>29.03515793312945</v>
+        <v>29.0332733400003</v>
       </c>
       <c r="P2" t="n">
-        <v>29.20629058470889</v>
+        <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.604375173463596</v>
+        <v>1.623880269917904</v>
       </c>
       <c r="R2" t="n">
-        <v>27.15226581494923</v>
+        <v>27.14135001944186</v>
       </c>
       <c r="S2" t="n">
-        <v>31.19926064462159</v>
+        <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6813979368487536</v>
+        <v>-0.9139056416242591</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="V2" t="n">
-        <v>330.7495644540284</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="W2" t="n">
-        <v>422.0283678250661</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>380.0702173446646</v>
+        <v>380.6262134874038</v>
       </c>
       <c r="Y2" t="n">
-        <v>359.0689463240261</v>
+        <v>359.3371431487801</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.071488365303</v>
+        <v>401.9152838260276</v>
       </c>
       <c r="AA2" t="n">
-        <v>355.4231595176854</v>
+        <v>355.8230987548828</v>
       </c>
       <c r="AB2" t="n">
-        <v>408.3983218380966</v>
+        <v>409.3048835916722</v>
       </c>
       <c r="AC2" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -2353,57 +3712,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.89051020637544</v>
+        <v>29.83504690282757</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.51552249913338</v>
+        <v>29.46390610450698</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.920880039883152</v>
+        <v>1.933208796634226</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.64653123825595</v>
+        <v>27.59935151416874</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.6446195792587</v>
+        <v>32.65449124757065</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.014415354377868</v>
+        <v>-1.182410770532027</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1370967741935484</v>
+        <v>0.09016393442622951</v>
       </c>
       <c r="AM2" t="n">
-        <v>330.7495644540284</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>445.6802487764048</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>391.2667786014545</v>
+        <v>391.1374648960694</v>
       </c>
       <c r="AP2" t="n">
-        <v>366.1224588793841</v>
+        <v>365.7930975721947</v>
       </c>
       <c r="AQ2" t="n">
-        <v>416.4110983235249</v>
+        <v>416.4818322199441</v>
       </c>
       <c r="AR2" t="n">
-        <v>361.8930939087704</v>
+        <v>361.8274983507521</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.3180702924964</v>
+        <v>428.1003802556511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2432,19 +3791,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>416.67</v>
+        <v>411.74</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.8</v>
       </c>
       <c r="J3" t="n">
-        <v>24.831347</v>
+        <v>24.508333</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
         <v>22.31206935670243</v>
@@ -2453,108 +3812,108 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.79343354361776</v>
+        <v>24.76636544625846</v>
       </c>
       <c r="P3" t="n">
-        <v>24.76369040352958</v>
+        <v>24.72342929518021</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.183451999371762</v>
+        <v>1.186495357009306</v>
       </c>
       <c r="R3" t="n">
-        <v>23.22013812038286</v>
+        <v>23.21232073451669</v>
       </c>
       <c r="S3" t="n">
-        <v>26.50944369222463</v>
+        <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>0.03203632796460248</v>
+        <v>-0.2174744677542248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="V3" t="n">
-        <v>374.3965238054668</v>
+        <v>374.8427651926008</v>
       </c>
       <c r="W3" t="n">
-        <v>459.9717509315128</v>
+        <v>460.5199890136719</v>
       </c>
       <c r="X3" t="n">
-        <v>416.0338148619061</v>
+        <v>416.0749394971421</v>
       </c>
       <c r="Y3" t="n">
-        <v>396.1754903124479</v>
+        <v>396.1418174993858</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.8921394113643</v>
+        <v>436.0080614948985</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.6339176600243</v>
+        <v>389.9669883398803</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.8284651555294</v>
+        <v>445.5025934788345</v>
       </c>
       <c r="AC3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD3" t="n">
         <v>22.31206935670243</v>
       </c>
       <c r="AE3" t="n">
-        <v>34.99430931818434</v>
+        <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>27.43189715615672</v>
+        <v>27.23040246766649</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.35834965517999</v>
+        <v>25.30487804878049</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.118216138579381</v>
+        <v>3.996590461513518</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.55171914544979</v>
+        <v>23.45741009548204</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34.32453746985575</v>
+        <v>34.08285908814344</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.6314749077385238</v>
+        <v>-0.6810979243131255</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.2131147540983606</v>
       </c>
       <c r="AM3" t="n">
-        <v>374.3965238054668</v>
+        <v>374.8427651926008</v>
       </c>
       <c r="AN3" t="n">
-        <v>587.2045103591333</v>
+        <v>583.1248801870332</v>
       </c>
       <c r="AO3" t="n">
-        <v>460.3072342803097</v>
+        <v>457.4707614567971</v>
       </c>
       <c r="AP3" t="n">
-        <v>391.2035674749477</v>
+        <v>390.32804170337</v>
       </c>
       <c r="AQ3" t="n">
-        <v>529.4109010856718</v>
+        <v>524.6134812102242</v>
       </c>
       <c r="AR3" t="n">
-        <v>395.1978472606475</v>
+        <v>394.0844896040983</v>
       </c>
       <c r="AS3" t="n">
-        <v>575.9657387441795</v>
+        <v>572.5920326808099</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2583,129 +3942,129 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>593</v>
+        <v>585.39</v>
       </c>
       <c r="I4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="J4" t="n">
-        <v>21.547964</v>
+        <v>21.279171</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
-        <v>21.56363636363636</v>
+        <v>21.28690962357955</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.81354057111685</v>
+        <v>24.6634695409604</v>
       </c>
       <c r="P4" t="n">
-        <v>24.45551391965331</v>
+        <v>24.37526659033764</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.599953635337401</v>
+        <v>2.603320992855815</v>
       </c>
       <c r="R4" t="n">
-        <v>21.99927334872159</v>
+        <v>21.93440007990057</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57616075407753</v>
+        <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.256013386828365</v>
+        <v>-1.299992797756324</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>593.4312727272727</v>
+        <v>585.6028837446734</v>
       </c>
       <c r="W4" t="n">
-        <v>806.6792534722222</v>
+        <v>806.3861287434895</v>
       </c>
       <c r="X4" t="n">
-        <v>682.8686365171357</v>
+        <v>678.4920470718207</v>
       </c>
       <c r="Y4" t="n">
-        <v>611.3179124726504</v>
+        <v>606.8746865583573</v>
       </c>
       <c r="Z4" t="n">
-        <v>754.4193605616209</v>
+        <v>750.1094075852842</v>
       </c>
       <c r="AA4" t="n">
-        <v>605.4200025568182</v>
+        <v>603.4153461980646</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.4159439522136</v>
+        <v>786.1805475110751</v>
       </c>
       <c r="AC4" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD4" t="n">
-        <v>21.56363636363636</v>
+        <v>21.28690962357955</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.66668497656942</v>
+        <v>26.56178868730787</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.62856513908844</v>
+        <v>27.52679771768262</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.723870427428682</v>
+        <v>2.759774229104261</v>
       </c>
       <c r="AI4" t="n">
-        <v>22.2054541015625</v>
+        <v>22.19181840376421</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.35631868302171</v>
+        <v>29.31080928832899</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.879208689600359</v>
+        <v>-1.914148495046441</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>593.4312727272727</v>
+        <v>585.6028837446734</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.9762082934226</v>
+        <v>864.6619000781998</v>
       </c>
       <c r="AO4" t="n">
-        <v>733.8671705551906</v>
+        <v>730.7148067878396</v>
       </c>
       <c r="AP4" t="n">
-        <v>658.9062563923532</v>
+        <v>654.7934177451815</v>
       </c>
       <c r="AQ4" t="n">
-        <v>808.8280847180279</v>
+        <v>806.6361958304979</v>
       </c>
       <c r="AR4" t="n">
-        <v>611.094096875</v>
+        <v>610.4969242875534</v>
       </c>
       <c r="AS4" t="n">
-        <v>807.8858901567575</v>
+        <v>806.3403635219306</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2734,19 +4093,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>246.03</v>
+        <v>245.22</v>
       </c>
       <c r="I5" t="n">
-        <v>7.77</v>
+        <v>7.75</v>
       </c>
       <c r="J5" t="n">
-        <v>31.664093</v>
+        <v>31.64129</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -2755,49 +4114,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.68480333699108</v>
+        <v>31.70656586892432</v>
       </c>
       <c r="P5" t="n">
-        <v>31.70574133476002</v>
+        <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.350157910663178</v>
+        <v>2.364655164592175</v>
       </c>
       <c r="R5" t="n">
-        <v>29.0610881895866</v>
+        <v>29.05425429510439</v>
       </c>
       <c r="S5" t="n">
-        <v>34.92747542249608</v>
+        <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.00881231720520243</v>
+        <v>-0.02760481523976249</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4603174603174603</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="V5" t="n">
-        <v>216.0211675795551</v>
+        <v>215.4651285381663</v>
       </c>
       <c r="W5" t="n">
-        <v>286.0812028062892</v>
+        <v>285.3448290538921</v>
       </c>
       <c r="X5" t="n">
-        <v>246.1909219284207</v>
+        <v>245.7258854841635</v>
       </c>
       <c r="Y5" t="n">
-        <v>227.9301949625678</v>
+        <v>227.3998079585741</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.4516488942736</v>
+        <v>264.0519630097529</v>
       </c>
       <c r="AA5" t="n">
-        <v>225.8046552330879</v>
+        <v>225.170470787059</v>
       </c>
       <c r="AB5" t="n">
-        <v>271.3864840327946</v>
+        <v>270.758191884146</v>
       </c>
       <c r="AC5" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -2806,57 +4165,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.71329843171316</v>
+        <v>31.6787340441008</v>
       </c>
       <c r="AG5" t="n">
-        <v>32.0098866177144</v>
+        <v>31.95592771818937</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.242452514636653</v>
+        <v>2.268451172495901</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.95104529302323</v>
+        <v>28.94741893645942</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.70906596802268</v>
+        <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02194268614028044</v>
+        <v>-0.01650643600126667</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4274193548387097</v>
+        <v>0.4426229508196721</v>
       </c>
       <c r="AM5" t="n">
-        <v>215.4251391678176</v>
+        <v>214.8706343050948</v>
       </c>
       <c r="AN5" t="n">
-        <v>286.0812028062892</v>
+        <v>285.3448290538921</v>
       </c>
       <c r="AO5" t="n">
-        <v>246.4123288144112</v>
+        <v>245.5101888417812</v>
       </c>
       <c r="AP5" t="n">
-        <v>228.9884727756844</v>
+        <v>227.929692254938</v>
       </c>
       <c r="AQ5" t="n">
-        <v>263.836184853138</v>
+        <v>263.0906854286245</v>
       </c>
       <c r="AR5" t="n">
-        <v>224.9496219267905</v>
+        <v>224.3424967575606</v>
       </c>
       <c r="AS5" t="n">
-        <v>269.6894425715362</v>
+        <v>269.1076750070314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2885,19 +4244,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>307.34</v>
+        <v>301.54</v>
       </c>
       <c r="I6" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>37.16324</v>
+        <v>36.506054</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -2906,49 +4265,49 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.22148379509058</v>
+        <v>34.29914316528635</v>
       </c>
       <c r="P6" t="n">
-        <v>33.91525601070672</v>
+        <v>34.20253319076345</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.063192221013672</v>
+        <v>2.086475296404038</v>
       </c>
       <c r="R6" t="n">
-        <v>31.83797522436215</v>
+        <v>31.83607656744462</v>
       </c>
       <c r="S6" t="n">
-        <v>37.37554517842955</v>
+        <v>37.38147763305368</v>
       </c>
       <c r="T6" t="n">
-        <v>1.425827499225494</v>
+        <v>1.057722005392147</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7903225806451613</v>
       </c>
       <c r="V6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="W6" t="n">
-        <v>315.5816102847638</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>283.0116709853991</v>
+        <v>283.3109225452652</v>
       </c>
       <c r="Y6" t="n">
-        <v>265.9490713176161</v>
+        <v>266.0766365969678</v>
       </c>
       <c r="Z6" t="n">
-        <v>300.0742706531822</v>
+        <v>300.5452084935625</v>
       </c>
       <c r="AA6" t="n">
-        <v>263.3000551054749</v>
+        <v>262.9659924470926</v>
       </c>
       <c r="AB6" t="n">
-        <v>309.0957586256124</v>
+        <v>308.7710052490234</v>
       </c>
       <c r="AC6" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -2957,57 +4316,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.54245963852536</v>
+        <v>34.49176155124631</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.49936878832081</v>
+        <v>34.42623029342849</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.805208059622547</v>
+        <v>1.777300376160677</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.14202455931072</v>
+        <v>32.13088525699663</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.19241090054221</v>
+        <v>36.91245386750294</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.451788533462799</v>
+        <v>1.133343848778651</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.8951612903225806</v>
+        <v>0.8114754098360656</v>
       </c>
       <c r="AM6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.5816102847638</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="AO6" t="n">
-        <v>285.6661412106047</v>
+        <v>284.9019504132945</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.7370705575262</v>
+        <v>270.2214493062074</v>
       </c>
       <c r="AQ6" t="n">
-        <v>300.5952118636832</v>
+        <v>299.5824515203817</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.8145431054996</v>
+        <v>265.4011122227922</v>
       </c>
       <c r="AS6" t="n">
-        <v>307.5812381474841</v>
+        <v>304.8968689455743</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3036,19 +4395,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>205.1</v>
+        <v>208.64</v>
       </c>
       <c r="I7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.457056</v>
+        <v>31.950994</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
         <v>31.4088830173837</v>
@@ -3057,49 +4416,49 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>38.44283030141145</v>
+        <v>38.36880050331563</v>
       </c>
       <c r="P7" t="n">
-        <v>37.39183698381696</v>
+        <v>37.38367353166852</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.176171651630198</v>
+        <v>4.287242152477702</v>
       </c>
       <c r="R7" t="n">
-        <v>33.07748885103608</v>
+        <v>32.91071986713963</v>
       </c>
       <c r="S7" t="n">
-        <v>44.66816368881537</v>
+        <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.672769915643793</v>
+        <v>-1.496954516461501</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01587301587301587</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="V7" t="n">
-        <v>204.7859172733417</v>
+        <v>205.1000061035156</v>
       </c>
       <c r="W7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>250.6472535652026</v>
+        <v>250.5482672866511</v>
       </c>
       <c r="Y7" t="n">
-        <v>223.4186143965737</v>
+        <v>222.5525760309716</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.8758927338315</v>
+        <v>278.5439585423305</v>
       </c>
       <c r="AA7" t="n">
-        <v>215.6652273087552</v>
+        <v>214.9070007324218</v>
       </c>
       <c r="AB7" t="n">
-        <v>291.2364272510762</v>
+        <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD7" t="n">
         <v>31.4088830173837</v>
@@ -3108,57 +4467,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>38.32041307606467</v>
+        <v>38.23194894045754</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.37551007952008</v>
+        <v>37.36530537507971</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.962872125009824</v>
+        <v>4.00582481027654</v>
       </c>
       <c r="AI7" t="n">
-        <v>33.48545232191567</v>
+        <v>33.02649341717613</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.20612257354113</v>
+        <v>44.17734698860012</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.731914848513478</v>
+        <v>-1.567955474324383</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.01388888888888889</v>
       </c>
       <c r="AM7" t="n">
-        <v>204.7859172733417</v>
+        <v>205.1000061035156</v>
       </c>
       <c r="AN7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>249.8490932559417</v>
+        <v>249.6546265811877</v>
       </c>
       <c r="AP7" t="n">
-        <v>224.0111670008776</v>
+        <v>223.4965905700819</v>
       </c>
       <c r="AQ7" t="n">
-        <v>275.6870195110057</v>
+        <v>275.8126625922935</v>
       </c>
       <c r="AR7" t="n">
-        <v>218.3251491388902</v>
+        <v>215.6630020141602</v>
       </c>
       <c r="AS7" t="n">
-        <v>288.2239191794881</v>
+        <v>288.4780758355588</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3187,19 +4546,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>466.38</v>
+        <v>490.33</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>156.50336</v>
+        <v>163.98996</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
         <v>72.9773582602447</v>
@@ -3208,49 +4567,49 @@
         <v>177.8754162397541</v>
       </c>
       <c r="O8" t="n">
-        <v>115.0845863437765</v>
+        <v>117.0632143411623</v>
       </c>
       <c r="P8" t="n">
-        <v>114.513204322671</v>
+        <v>118.5924486844045</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.07307640454155</v>
+        <v>34.08285792004858</v>
       </c>
       <c r="R8" t="n">
-        <v>76.02339719376475</v>
+        <v>75.99849139519458</v>
       </c>
       <c r="S8" t="n">
-        <v>164.6622994845031</v>
+        <v>164.9360701764216</v>
       </c>
       <c r="T8" t="n">
-        <v>1.215586557681737</v>
+        <v>1.3768430384834</v>
       </c>
       <c r="U8" t="n">
-        <v>0.873015873015873</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="V8" t="n">
-        <v>217.4725276155292</v>
+        <v>218.2023011981317</v>
       </c>
       <c r="W8" t="n">
-        <v>530.0687403944672</v>
+        <v>531.8474945568648</v>
       </c>
       <c r="X8" t="n">
-        <v>342.952067304454</v>
+        <v>350.0190108800753</v>
       </c>
       <c r="Y8" t="n">
-        <v>241.4142996189202</v>
+        <v>248.11126569913</v>
       </c>
       <c r="Z8" t="n">
-        <v>444.4898349899879</v>
+        <v>451.9267560610205</v>
       </c>
       <c r="AA8" t="n">
-        <v>226.549723637419</v>
+        <v>227.2354892716318</v>
       </c>
       <c r="AB8" t="n">
-        <v>490.6936524638191</v>
+        <v>493.1588498275007</v>
       </c>
       <c r="AC8" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -3259,57 +4618,57 @@
         <v>177.8754162397541</v>
       </c>
       <c r="AF8" t="n">
-        <v>106.8354184211481</v>
+        <v>107.2228551603934</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.3177330881504</v>
+        <v>105.0953815714424</v>
       </c>
       <c r="AH8" t="n">
-        <v>28.45264556448733</v>
+        <v>29.0980349864215</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.52037537772701</v>
+        <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>147.4318057200948</v>
+        <v>149.0626240714652</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.745635268477249</v>
+        <v>1.950891352838665</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9426229508196722</v>
       </c>
       <c r="AM8" t="n">
-        <v>214.728675813495</v>
+        <v>215.4492418397148</v>
       </c>
       <c r="AN8" t="n">
-        <v>530.0687403944672</v>
+        <v>531.8474945568648</v>
       </c>
       <c r="AO8" t="n">
-        <v>318.3695468950214</v>
+        <v>320.5963369295761</v>
       </c>
       <c r="AP8" t="n">
-        <v>233.5806631128492</v>
+        <v>233.5932123201758</v>
       </c>
       <c r="AQ8" t="n">
-        <v>403.1584306771937</v>
+        <v>407.5994615389765</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.0507186256265</v>
+        <v>225.7991528435473</v>
       </c>
       <c r="AS8" t="n">
-        <v>439.3467810458824</v>
+        <v>445.6972459736809</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3338,19 +4697,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>385.73</v>
+        <v>396.6</v>
       </c>
       <c r="I9" t="n">
-        <v>6.02</v>
+        <v>6.03</v>
       </c>
       <c r="J9" t="n">
-        <v>64.07474999999999</v>
+        <v>65.77114</v>
       </c>
       <c r="K9" t="n">
         <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -3359,49 +4718,49 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>74.91719886917585</v>
+        <v>75.04499179120712</v>
       </c>
       <c r="P9" t="n">
-        <v>78.39571411846676</v>
+        <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.711013572373497</v>
+        <v>9.781241462981987</v>
       </c>
       <c r="R9" t="n">
-        <v>61.29707440530581</v>
+        <v>61.29473531920079</v>
       </c>
       <c r="S9" t="n">
-        <v>83.47290277016327</v>
+        <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.116510525741735</v>
+        <v>-0.9481262502622875</v>
       </c>
       <c r="U9" t="n">
-        <v>0.253968253968254</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="V9" t="n">
-        <v>344.3134935761985</v>
+        <v>344.885442901076</v>
       </c>
       <c r="W9" t="n">
-        <v>565.1172405637031</v>
+        <v>566.0559735214503</v>
       </c>
       <c r="X9" t="n">
-        <v>451.0015371924386</v>
+        <v>452.521300500979</v>
       </c>
       <c r="Y9" t="n">
-        <v>392.5412354867501</v>
+        <v>393.5404144791976</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.461838898127</v>
+        <v>511.5021865227603</v>
       </c>
       <c r="AA9" t="n">
-        <v>369.008387919941</v>
+        <v>369.6072539747808</v>
       </c>
       <c r="AB9" t="n">
-        <v>502.5068746763829</v>
+        <v>503.467376494826</v>
       </c>
       <c r="AC9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -3410,57 +4769,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.7265189141975</v>
+        <v>72.76569347655681</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.83857403961119</v>
+        <v>71.85744439530923</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.694561292849456</v>
+        <v>7.673032529667959</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.49025281642149</v>
+        <v>62.51890781097711</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.3986358345136</v>
+        <v>82.39649127566095</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.124400545387504</v>
+        <v>-0.9115761531717999</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.1709401709401709</v>
       </c>
       <c r="AM9" t="n">
-        <v>344.3134935761985</v>
+        <v>344.885442901076</v>
       </c>
       <c r="AN9" t="n">
-        <v>565.1172405637031</v>
+        <v>566.0559735214503</v>
       </c>
       <c r="AO9" t="n">
-        <v>437.8136438634689</v>
+        <v>438.7771316636375</v>
       </c>
       <c r="AP9" t="n">
-        <v>391.4923848805152</v>
+        <v>392.5087455097398</v>
       </c>
       <c r="AQ9" t="n">
-        <v>484.1349028464226</v>
+        <v>485.0455178175354</v>
       </c>
       <c r="AR9" t="n">
-        <v>376.1913219548574</v>
+        <v>376.989014100192</v>
       </c>
       <c r="AS9" t="n">
-        <v>496.0397877237718</v>
+        <v>496.8508423922356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-06 01:09:28</t>
+          <t>2026-06-09 03:47:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3489,19 +4848,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>82.18000000000001</v>
+        <v>82.64</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>26.509678</v>
+        <v>26.658066</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M10" t="n">
         <v>35.93675816954359</v>
@@ -3510,22 +4869,22 @@
         <v>42.60474344487245</v>
       </c>
       <c r="O10" t="n">
-        <v>38.41600789652239</v>
+        <v>38.40270594790844</v>
       </c>
       <c r="P10" t="n">
-        <v>37.71936770955563</v>
+        <v>37.65019654285294</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.917248392190739</v>
+        <v>1.990322096160243</v>
       </c>
       <c r="R10" t="n">
-        <v>36.41976247191899</v>
+        <v>36.38339890792905</v>
       </c>
       <c r="S10" t="n">
-        <v>41.14466490010498</v>
+        <v>41.39130483031742</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.210113381770872</v>
+        <v>-5.900874019620422</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -3537,22 +4896,22 @@
         <v>132.0747046791046</v>
       </c>
       <c r="X10" t="n">
-        <v>119.0896244792194</v>
+        <v>119.0483884385162</v>
       </c>
       <c r="Y10" t="n">
-        <v>113.1461544634281</v>
+        <v>112.8783899404194</v>
       </c>
       <c r="Z10" t="n">
-        <v>125.0330944950107</v>
+        <v>125.2183869366129</v>
       </c>
       <c r="AA10" t="n">
-        <v>112.9012636629489</v>
+        <v>112.7885366145801</v>
       </c>
       <c r="AB10" t="n">
-        <v>127.5484611903254</v>
+        <v>128.313044973984</v>
       </c>
       <c r="AC10" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -3561,25 +4920,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>24.66089290957747</v>
+        <v>25.3821414425773</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.4901173708467</v>
+        <v>32.59090830686063</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.57837686140042</v>
+        <v>15.350467123509</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.779782746967516</v>
+        <v>3.777151179492922</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.10988125405291</v>
+        <v>39.12055275656958</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1186763619131203</v>
+        <v>0.08311959155097284</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -3588,19 +4947,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>76.44876801969015</v>
+        <v>78.68463847198962</v>
       </c>
       <c r="AP10" t="n">
-        <v>28.15579974934885</v>
+        <v>31.09819038911171</v>
       </c>
       <c r="AQ10" t="n">
-        <v>124.7417362900314</v>
+        <v>126.2710865548675</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.7173265155993</v>
+        <v>11.70916865642806</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.240631887564</v>
+        <v>121.2737135453657</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS19"/>
+  <dimension ref="A1:AS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,7 +1034,7 @@
         <v>246.1909219284207</v>
       </c>
       <c r="Y4" t="n">
-        <v>227.9301949625678</v>
+        <v>227.9301949625677</v>
       </c>
       <c r="Z4" t="n">
         <v>264.4516488942736</v>
@@ -2227,7 +2227,7 @@
         <v>164.9360701764216</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3768430384834</v>
+        <v>1.376843038483401</v>
       </c>
       <c r="U12" t="n">
         <v>0.8870967741935484</v>
@@ -2366,7 +2366,7 @@
         <v>31.70656586892432</v>
       </c>
       <c r="P13" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q13" t="n">
         <v>2.364655164592175</v>
@@ -2378,7 +2378,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.02760481523976249</v>
+        <v>-0.0276048152397624</v>
       </c>
       <c r="U13" t="n">
         <v>0.4516129032258064</v>
@@ -2390,7 +2390,7 @@
         <v>285.3448290538921</v>
       </c>
       <c r="X13" t="n">
-        <v>245.7258854841635</v>
+        <v>245.7258854841634</v>
       </c>
       <c r="Y13" t="n">
         <v>227.3998079585741</v>
@@ -2429,7 +2429,7 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.01650643600126667</v>
+        <v>-0.0165064360012666</v>
       </c>
       <c r="AL13" t="n">
         <v>0.4426229508196721</v>
@@ -2450,7 +2450,7 @@
         <v>263.0906854286245</v>
       </c>
       <c r="AR13" t="n">
-        <v>224.3424967575606</v>
+        <v>224.3424967575605</v>
       </c>
       <c r="AS13" t="n">
         <v>269.1076750070314</v>
@@ -2511,7 +2511,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N14" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O14" t="n">
         <v>75.04499179120712</v>
@@ -2520,7 +2520,7 @@
         <v>78.71540210865163</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.781241462981987</v>
+        <v>9.781241462981988</v>
       </c>
       <c r="R14" t="n">
         <v>61.29473531920079</v>
@@ -2529,7 +2529,7 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9481262502622875</v>
+        <v>-0.9481262502622876</v>
       </c>
       <c r="U14" t="n">
         <v>0.2903225806451613</v>
@@ -2562,7 +2562,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE14" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF14" t="n">
         <v>72.76569347655681</v>
@@ -2580,7 +2580,7 @@
         <v>82.39649127566095</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.9115761531717999</v>
+        <v>-0.9115761531718</v>
       </c>
       <c r="AL14" t="n">
         <v>0.1709401709401709</v>
@@ -2680,7 +2680,7 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9139056416242591</v>
+        <v>-0.9139056416242592</v>
       </c>
       <c r="U15" t="n">
         <v>0.1774193548387097</v>
@@ -2692,7 +2692,7 @@
         <v>422.673178165517</v>
       </c>
       <c r="X15" t="n">
-        <v>380.6262134874038</v>
+        <v>380.6262134874039</v>
       </c>
       <c r="Y15" t="n">
         <v>359.3371431487801</v>
@@ -2719,13 +2719,13 @@
         <v>29.83504690282757</v>
       </c>
       <c r="AG15" t="n">
-        <v>29.46390610450698</v>
+        <v>29.46390610450697</v>
       </c>
       <c r="AH15" t="n">
         <v>1.933208796634226</v>
       </c>
       <c r="AI15" t="n">
-        <v>27.59935151416874</v>
+        <v>27.59935151416873</v>
       </c>
       <c r="AJ15" t="n">
         <v>32.65449124757065</v>
@@ -2734,7 +2734,7 @@
         <v>-1.182410770532027</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.09016393442622951</v>
+        <v>0.0901639344262295</v>
       </c>
       <c r="AM15" t="n">
         <v>331.2549113821476</v>
@@ -2755,7 +2755,7 @@
         <v>361.8274983507521</v>
       </c>
       <c r="AS15" t="n">
-        <v>428.1003802556511</v>
+        <v>428.1003802556512</v>
       </c>
     </row>
     <row r="16">
@@ -2879,7 +2879,7 @@
         <v>22.19181840376421</v>
       </c>
       <c r="AJ16" t="n">
-        <v>29.31080928832899</v>
+        <v>29.310809288329</v>
       </c>
       <c r="AK16" t="n">
         <v>-1.914148495046441</v>
@@ -2967,7 +2967,7 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O17" t="n">
-        <v>24.76636544625846</v>
+        <v>24.76636544625845</v>
       </c>
       <c r="P17" t="n">
         <v>24.72342929518021</v>
@@ -2982,7 +2982,7 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2174744677542248</v>
+        <v>-0.2174744677542247</v>
       </c>
       <c r="U17" t="n">
         <v>0.3870967741935484</v>
@@ -3048,7 +3048,7 @@
         <v>457.4707614567971</v>
       </c>
       <c r="AP17" t="n">
-        <v>390.32804170337</v>
+        <v>390.3280417033701</v>
       </c>
       <c r="AQ17" t="n">
         <v>524.6134812102242</v>
@@ -3154,7 +3154,7 @@
         <v>125.2183869366129</v>
       </c>
       <c r="AA18" t="n">
-        <v>112.7885366145801</v>
+        <v>112.78853661458</v>
       </c>
       <c r="AB18" t="n">
         <v>128.313044973984</v>
@@ -3163,7 +3163,7 @@
         <v>86</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE18" t="n">
         <v>42.60474344487245</v>
@@ -3184,7 +3184,7 @@
         <v>39.12055275656958</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.08311959155097284</v>
+        <v>0.0831195915509728</v>
       </c>
       <c r="AL18" t="n">
         <v>0.3255813953488372</v>
@@ -3199,7 +3199,7 @@
         <v>78.68463847198962</v>
       </c>
       <c r="AP18" t="n">
-        <v>31.09819038911171</v>
+        <v>31.09819038911172</v>
       </c>
       <c r="AQ18" t="n">
         <v>126.2710865548675</v>
@@ -3275,7 +3275,7 @@
         <v>37.38367353166852</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.287242152477702</v>
+        <v>4.287242152477703</v>
       </c>
       <c r="R19" t="n">
         <v>32.91071986713963</v>
@@ -3287,7 +3287,7 @@
         <v>-1.496954516461501</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="V19" t="n">
         <v>205.1000061035156</v>
@@ -3338,7 +3338,7 @@
         <v>-1.567955474324383</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.0138888888888888</v>
       </c>
       <c r="AM19" t="n">
         <v>205.1000061035156</v>
@@ -3360,6 +3360,1365 @@
       </c>
       <c r="AS19" t="n">
         <v>288.4780758355588</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>35.21818</v>
+      </c>
+      <c r="K20" t="n">
+        <v>67</v>
+      </c>
+      <c r="L20" t="n">
+        <v>61</v>
+      </c>
+      <c r="M20" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N20" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O20" t="n">
+        <v>34.32021233616655</v>
+      </c>
+      <c r="P20" t="n">
+        <v>34.2063305045985</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.097130028706181</v>
+      </c>
+      <c r="R20" t="n">
+        <v>31.8341779105271</v>
+      </c>
+      <c r="S20" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.4281888349991569</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.6557377049180327</v>
+      </c>
+      <c r="V20" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="W20" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X20" t="n">
+        <v>283.141751773374</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>265.840429036548</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>300.4430745102</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>262.6319677618486</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>308.446133223342</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>34.46880555717656</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>34.40435746680161</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.766435081379112</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>32.1253156058396</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36.81098999350704</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.4242298235145881</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.7024793388429752</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>284.3676458467066</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>269.7945564253289</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>298.9407352680843</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>265.0338537481767</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>303.6906674464331</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>475.505</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>158.50166</v>
+      </c>
+      <c r="K21" t="n">
+        <v>63</v>
+      </c>
+      <c r="L21" t="n">
+        <v>61</v>
+      </c>
+      <c r="M21" t="n">
+        <v>72.9773582602447</v>
+      </c>
+      <c r="N21" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="O21" t="n">
+        <v>117.7151630957124</v>
+      </c>
+      <c r="P21" t="n">
+        <v>121.9660345113502</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>33.97367187361893</v>
+      </c>
+      <c r="R21" t="n">
+        <v>75.97358559662442</v>
+      </c>
+      <c r="S21" t="n">
+        <v>165.2098408683402</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.200532490453554</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.8524590163934426</v>
+      </c>
+      <c r="V21" t="n">
+        <v>218.9320747807341</v>
+      </c>
+      <c r="W21" t="n">
+        <v>533.6262487192623</v>
+      </c>
+      <c r="X21" t="n">
+        <v>353.1454892871371</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>251.2244736662804</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>455.0665049079939</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>227.9207567898733</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>495.6295226050205</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>107.2075166565454</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>105.0528357163915</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>29.21852999343573</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>75.51697928950472</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>149.2426237512807</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.755534701950387</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.9256198347107438</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>216.1698078659346</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>533.6262487192623</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>321.6225499696361</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>233.9669599893288</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>409.2781399499432</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>226.5509378685142</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>447.7278712538422</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>244.19</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="J22" t="n">
+        <v>31.63083</v>
+      </c>
+      <c r="K22" t="n">
+        <v>67</v>
+      </c>
+      <c r="L22" t="n">
+        <v>61</v>
+      </c>
+      <c r="M22" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N22" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O22" t="n">
+        <v>31.74014403702845</v>
+      </c>
+      <c r="P22" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.369328515831107</v>
+      </c>
+      <c r="R22" t="n">
+        <v>29.04742040062217</v>
+      </c>
+      <c r="S22" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.04613713813768135</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V22" t="n">
+        <v>214.6310699760831</v>
+      </c>
+      <c r="W22" t="n">
+        <v>284.2402684252964</v>
+      </c>
+      <c r="X22" t="n">
+        <v>245.0339119658596</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>226.7426958236435</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>263.3251281080758</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>224.2460854928031</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>269.7800810533255</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>31.67173661011488</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>31.94774045782574</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>2.276560910630987</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>28.94560575817752</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>34.73082346896248</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-0.01796859900556732</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.4462809917355372</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>214.0388770110105</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>284.2402684252964</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>244.5058066300869</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>226.9307564000156</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>262.0808568601581</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>223.4600764531305</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>268.1219571803903</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>392.16</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="K23" t="n">
+        <v>34</v>
+      </c>
+      <c r="L23" t="n">
+        <v>61</v>
+      </c>
+      <c r="M23" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N23" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O23" t="n">
+        <v>75.18371546923311</v>
+      </c>
+      <c r="P23" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.800724438389427</v>
+      </c>
+      <c r="R23" t="n">
+        <v>61.29239623309577</v>
+      </c>
+      <c r="S23" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.002345850144875</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2786885245901639</v>
+      </c>
+      <c r="V23" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="W23" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="X23" t="n">
+        <v>451.1022928153986</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>392.2979461850621</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>509.9066394457352</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>367.7543773985747</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>501.087710731908</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>117</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>72.76569347655681</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>71.85744439530923</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>7.673032529667959</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>62.51890781097711</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>82.39649127566095</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-0.9651586185673682</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.1623931623931624</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>436.5941608593408</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>390.5559656813331</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>482.6323560373486</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>375.1134468658627</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>494.3789476539657</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="I24" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J24" t="n">
+        <v>27.634632</v>
+      </c>
+      <c r="K24" t="n">
+        <v>37</v>
+      </c>
+      <c r="L24" t="n">
+        <v>61</v>
+      </c>
+      <c r="M24" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N24" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O24" t="n">
+        <v>29.04150747563317</v>
+      </c>
+      <c r="P24" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.636051097663735</v>
+      </c>
+      <c r="R24" t="n">
+        <v>27.1304342239345</v>
+      </c>
+      <c r="S24" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.8599214765615648</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1967213114754098</v>
+      </c>
+      <c r="V24" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W24" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X24" t="n">
+        <v>380.7341630055508</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>359.2855331151792</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>402.1827928959224</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>355.6799926757812</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>409.5874601323553</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>29.8256884086393</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>29.45232609589531</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.938470121839614</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>27.59481848223578</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>32.65942708172662</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>-1.130301872571541</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.1074380165289256</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>391.0147750372612</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>365.6014317399438</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>416.4281183345785</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>361.768070302111</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>428.165089041436</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>584.59</v>
+      </c>
+      <c r="I25" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="J25" t="n">
+        <v>21.27329</v>
+      </c>
+      <c r="K25" t="n">
+        <v>55</v>
+      </c>
+      <c r="L25" t="n">
+        <v>61</v>
+      </c>
+      <c r="M25" t="n">
+        <v>21.28690962357955</v>
+      </c>
+      <c r="N25" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O25" t="n">
+        <v>24.61076829673761</v>
+      </c>
+      <c r="P25" t="n">
+        <v>24.35632204694817</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.591363492259886</v>
+      </c>
+      <c r="R25" t="n">
+        <v>21.92727272727273</v>
+      </c>
+      <c r="S25" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-1.287923638156625</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>584.964276455966</v>
+      </c>
+      <c r="W25" t="n">
+        <v>805.5067545572916</v>
+      </c>
+      <c r="X25" t="n">
+        <v>676.3039127943495</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>605.0932440270478</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>747.5145815616511</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>602.5614545454545</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>785.3735180071639</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>21.28690962357955</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>26.54241044963202</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>27.49335641244326</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.76290221909011</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>22.19127308238636</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-1.90709624583358</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>584.964276455966</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>863.718975432531</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>729.3854391558878</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>653.4608861752916</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>805.309992136484</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>609.8161843039773</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>805.5067545572916</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>403.41</v>
+      </c>
+      <c r="I26" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J26" t="n">
+        <v>24.04112</v>
+      </c>
+      <c r="K26" t="n">
+        <v>67</v>
+      </c>
+      <c r="L26" t="n">
+        <v>61</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N26" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O26" t="n">
+        <v>24.75727593191328</v>
+      </c>
+      <c r="P26" t="n">
+        <v>24.70952351888021</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.194163438572818</v>
+      </c>
+      <c r="R26" t="n">
+        <v>23.20450334865052</v>
+      </c>
+      <c r="S26" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.5997134971484183</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2622950819672131</v>
+      </c>
+      <c r="V26" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="W26" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X26" t="n">
+        <v>415.4270901375049</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>395.389027638253</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>435.4651526367568</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>389.3715661903558</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>445.1160013414757</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>27.1712636279093</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>25.28893027624687</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>3.95924268811864</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>23.41025557049816</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>34.03485055329281</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-0.790591503092904</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.1322314049586777</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>582.4306839010962</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>455.9338036763182</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>389.4977113696874</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>522.3698959829489</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>392.8240884729592</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>571.1047922842533</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>81.41</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>26.261292</v>
+      </c>
+      <c r="K27" t="n">
+        <v>67</v>
+      </c>
+      <c r="L27" t="n">
+        <v>25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="N27" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="O27" t="n">
+        <v>38.4385770413244</v>
+      </c>
+      <c r="P27" t="n">
+        <v>37.67193579391056</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.02276804145474</v>
+      </c>
+      <c r="R27" t="n">
+        <v>36.36521712593409</v>
+      </c>
+      <c r="S27" t="n">
+        <v>41.51462479542365</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-6.020109469678346</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>111.4039503255851</v>
+      </c>
+      <c r="W27" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="X27" t="n">
+        <v>119.1595888281056</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>112.889007899596</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>125.4301697566153</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>112.7321730903957</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>128.6953368658133</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>85</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>25.63451672873259</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>32.68774582934472</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>15.26103564931867</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3.776273990334723</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>39.12410992407514</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.04107029730288267</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.3176470588235294</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>79.46700185907103</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>32.15779134618315</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>126.7762123719589</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>11.70644937003764</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>121.2847407646329</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-10 04:50:29</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>208.19</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J28" t="n">
+        <v>31.833334</v>
+      </c>
+      <c r="K28" t="n">
+        <v>65</v>
+      </c>
+      <c r="L28" t="n">
+        <v>61</v>
+      </c>
+      <c r="M28" t="n">
+        <v>31.4088830173837</v>
+      </c>
+      <c r="N28" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O28" t="n">
+        <v>38.37541516938103</v>
+      </c>
+      <c r="P28" t="n">
+        <v>37.37551007952008</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.322502525185715</v>
+      </c>
+      <c r="R28" t="n">
+        <v>32.90352229867558</v>
+      </c>
+      <c r="S28" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-1.513493891851445</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V28" t="n">
+        <v>205.4140949336894</v>
+      </c>
+      <c r="W28" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="X28" t="n">
+        <v>250.9752152077519</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>222.7060486930374</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>279.2443817224665</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>215.1890358333383</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>292.8852277483259</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>31.4088830173837</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>38.23194894045754</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>37.36530537507971</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>4.00582481027654</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>33.02649341717613</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>44.17734698860012</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-1.597327702410383</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.01388888888888889</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>205.4140949336894</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>250.0369460705923</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>223.8388518113837</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>276.2350403298009</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>215.9932669483319</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>288.9198493054448</v>
       </c>
     </row>
   </sheetData>
@@ -3606,12 +4965,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3640,19 +4999,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>361.17</v>
+        <v>362.29</v>
       </c>
       <c r="I2" t="n">
         <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.5492</v>
+        <v>27.634632</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -3661,25 +5020,25 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>29.0332733400003</v>
+        <v>29.04150747563317</v>
       </c>
       <c r="P2" t="n">
-        <v>29.21870597964289</v>
+        <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.623880269917904</v>
+        <v>1.636051097663735</v>
       </c>
       <c r="R2" t="n">
-        <v>27.14135001944186</v>
+        <v>27.1304342239345</v>
       </c>
       <c r="S2" t="n">
-        <v>31.22081491927324</v>
+        <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9139056416242591</v>
+        <v>-0.8599214765615648</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.1967213114754098</v>
       </c>
       <c r="V2" t="n">
         <v>331.2549113821476</v>
@@ -3688,22 +5047,22 @@
         <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>380.6262134874038</v>
+        <v>380.7341630055508</v>
       </c>
       <c r="Y2" t="n">
-        <v>359.3371431487801</v>
+        <v>359.2855331151792</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.9152838260276</v>
+        <v>402.1827928959224</v>
       </c>
       <c r="AA2" t="n">
-        <v>355.8230987548828</v>
+        <v>355.6799926757812</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.3048835916722</v>
+        <v>409.5874601323553</v>
       </c>
       <c r="AC2" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -3712,25 +5071,25 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.83504690282757</v>
+        <v>29.8256884086393</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.46390610450698</v>
+        <v>29.45232609589531</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.933208796634226</v>
+        <v>1.938470121839614</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.59935151416874</v>
+        <v>27.59481848223578</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65449124757065</v>
+        <v>32.65942708172662</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.182410770532027</v>
+        <v>-1.130301872571541</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.09016393442622951</v>
+        <v>0.1074380165289256</v>
       </c>
       <c r="AM2" t="n">
         <v>331.2549113821476</v>
@@ -3739,30 +5098,30 @@
         <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>391.1374648960694</v>
+        <v>391.0147750372612</v>
       </c>
       <c r="AP2" t="n">
-        <v>365.7930975721947</v>
+        <v>365.6014317399438</v>
       </c>
       <c r="AQ2" t="n">
-        <v>416.4818322199441</v>
+        <v>416.4281183345785</v>
       </c>
       <c r="AR2" t="n">
-        <v>361.8274983507521</v>
+        <v>361.768070302111</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.1003802556511</v>
+        <v>428.165089041436</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3791,19 +5150,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>411.74</v>
+        <v>403.41</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8</v>
+        <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>24.508333</v>
+        <v>24.04112</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M3" t="n">
         <v>22.31206935670243</v>
@@ -3812,49 +5171,49 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.76636544625846</v>
+        <v>24.75727593191328</v>
       </c>
       <c r="P3" t="n">
-        <v>24.72342929518021</v>
+        <v>24.70952351888021</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.186495357009306</v>
+        <v>1.194163438572818</v>
       </c>
       <c r="R3" t="n">
-        <v>23.21232073451669</v>
+        <v>23.20450334865052</v>
       </c>
       <c r="S3" t="n">
-        <v>26.51801151659729</v>
+        <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2174744677542248</v>
+        <v>-0.5997134971484183</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.2622950819672131</v>
       </c>
       <c r="V3" t="n">
-        <v>374.8427651926008</v>
+        <v>374.3965238054668</v>
       </c>
       <c r="W3" t="n">
-        <v>460.5199890136719</v>
+        <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>416.0749394971421</v>
+        <v>415.4270901375049</v>
       </c>
       <c r="Y3" t="n">
-        <v>396.1418174993858</v>
+        <v>395.389027638253</v>
       </c>
       <c r="Z3" t="n">
-        <v>436.0080614948985</v>
+        <v>435.4651526367568</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.9669883398803</v>
+        <v>389.3715661903558</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.5025934788345</v>
+        <v>445.1160013414757</v>
       </c>
       <c r="AC3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD3" t="n">
         <v>22.31206935670243</v>
@@ -3863,57 +5222,57 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>27.23040246766649</v>
+        <v>27.1712636279093</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.30487804878049</v>
+        <v>25.28893027624687</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.996590461513518</v>
+        <v>3.95924268811864</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.45741009548204</v>
+        <v>23.41025557049816</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34.08285908814344</v>
+        <v>34.03485055329281</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.6810979243131255</v>
+        <v>-0.790591503092904</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2131147540983606</v>
+        <v>0.1322314049586777</v>
       </c>
       <c r="AM3" t="n">
-        <v>374.8427651926008</v>
+        <v>374.3965238054668</v>
       </c>
       <c r="AN3" t="n">
-        <v>583.1248801870332</v>
+        <v>582.4306839010962</v>
       </c>
       <c r="AO3" t="n">
-        <v>457.4707614567971</v>
+        <v>455.9338036763182</v>
       </c>
       <c r="AP3" t="n">
-        <v>390.32804170337</v>
+        <v>389.4977113696874</v>
       </c>
       <c r="AQ3" t="n">
-        <v>524.6134812102242</v>
+        <v>522.3698959829489</v>
       </c>
       <c r="AR3" t="n">
-        <v>394.0844896040983</v>
+        <v>392.8240884729592</v>
       </c>
       <c r="AS3" t="n">
-        <v>572.5920326808099</v>
+        <v>571.1047922842533</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3942,19 +5301,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>585.39</v>
+        <v>584.59</v>
       </c>
       <c r="I4" t="n">
-        <v>27.51</v>
+        <v>27.48</v>
       </c>
       <c r="J4" t="n">
-        <v>21.279171</v>
+        <v>21.27329</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M4" t="n">
         <v>21.28690962357955</v>
@@ -3963,49 +5322,49 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.6634695409604</v>
+        <v>24.61076829673761</v>
       </c>
       <c r="P4" t="n">
-        <v>24.37526659033764</v>
+        <v>24.35632204694817</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.603320992855815</v>
+        <v>2.591363492259886</v>
       </c>
       <c r="R4" t="n">
-        <v>21.93440007990057</v>
+        <v>21.92727272727273</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57799154893039</v>
+        <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.299992797756324</v>
+        <v>-1.287923638156625</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>585.6028837446734</v>
+        <v>584.964276455966</v>
       </c>
       <c r="W4" t="n">
-        <v>806.3861287434895</v>
+        <v>805.5067545572916</v>
       </c>
       <c r="X4" t="n">
-        <v>678.4920470718207</v>
+        <v>676.3039127943495</v>
       </c>
       <c r="Y4" t="n">
-        <v>606.8746865583573</v>
+        <v>605.0932440270478</v>
       </c>
       <c r="Z4" t="n">
-        <v>750.1094075852842</v>
+        <v>747.5145815616511</v>
       </c>
       <c r="AA4" t="n">
-        <v>603.4153461980646</v>
+        <v>602.5614545454545</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.1805475110751</v>
+        <v>785.3735180071639</v>
       </c>
       <c r="AC4" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD4" t="n">
         <v>21.28690962357955</v>
@@ -4014,57 +5373,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.56178868730787</v>
+        <v>26.54241044963202</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.52679771768262</v>
+        <v>27.49335641244326</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.759774229104261</v>
+        <v>2.76290221909011</v>
       </c>
       <c r="AI4" t="n">
-        <v>22.19181840376421</v>
+        <v>22.19127308238636</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.31080928832899</v>
+        <v>29.31247287326389</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.914148495046441</v>
+        <v>-1.90709624583358</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>585.6028837446734</v>
+        <v>584.964276455966</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.6619000781998</v>
+        <v>863.718975432531</v>
       </c>
       <c r="AO4" t="n">
-        <v>730.7148067878396</v>
+        <v>729.3854391558878</v>
       </c>
       <c r="AP4" t="n">
-        <v>654.7934177451815</v>
+        <v>653.4608861752916</v>
       </c>
       <c r="AQ4" t="n">
-        <v>806.6361958304979</v>
+        <v>805.309992136484</v>
       </c>
       <c r="AR4" t="n">
-        <v>610.4969242875534</v>
+        <v>609.8161843039773</v>
       </c>
       <c r="AS4" t="n">
-        <v>806.3403635219306</v>
+        <v>805.5067545572916</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4093,19 +5452,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>245.22</v>
+        <v>244.19</v>
       </c>
       <c r="I5" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="J5" t="n">
-        <v>31.64129</v>
+        <v>31.63083</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -4114,49 +5473,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.70656586892432</v>
+        <v>31.74014403702845</v>
       </c>
       <c r="P5" t="n">
-        <v>31.71949797269831</v>
+        <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.364655164592175</v>
+        <v>2.369328515831107</v>
       </c>
       <c r="R5" t="n">
-        <v>29.05425429510439</v>
+        <v>29.04742040062217</v>
       </c>
       <c r="S5" t="n">
-        <v>34.93654088827689</v>
+        <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.02760481523976249</v>
+        <v>-0.04613713813768135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>215.4651285381663</v>
+        <v>214.6310699760831</v>
       </c>
       <c r="W5" t="n">
-        <v>285.3448290538921</v>
+        <v>284.2402684252964</v>
       </c>
       <c r="X5" t="n">
-        <v>245.7258854841635</v>
+        <v>245.0339119658596</v>
       </c>
       <c r="Y5" t="n">
-        <v>227.3998079585741</v>
+        <v>226.7426958236435</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.0519630097529</v>
+        <v>263.3251281080758</v>
       </c>
       <c r="AA5" t="n">
-        <v>225.170470787059</v>
+        <v>224.2460854928031</v>
       </c>
       <c r="AB5" t="n">
-        <v>270.758191884146</v>
+        <v>269.7800810533255</v>
       </c>
       <c r="AC5" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -4165,57 +5524,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.6787340441008</v>
+        <v>31.67173661011488</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.95592771818937</v>
+        <v>31.94774045782574</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.268451172495901</v>
+        <v>2.276560910630987</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.94741893645942</v>
+        <v>28.94560575817752</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.72357096864921</v>
+        <v>34.73082346896248</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01650643600126667</v>
+        <v>-0.01796859900556732</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4426229508196721</v>
+        <v>0.4462809917355372</v>
       </c>
       <c r="AM5" t="n">
-        <v>214.8706343050948</v>
+        <v>214.0388770110105</v>
       </c>
       <c r="AN5" t="n">
-        <v>285.3448290538921</v>
+        <v>284.2402684252964</v>
       </c>
       <c r="AO5" t="n">
-        <v>245.5101888417812</v>
+        <v>244.5058066300869</v>
       </c>
       <c r="AP5" t="n">
-        <v>227.929692254938</v>
+        <v>226.9307564000156</v>
       </c>
       <c r="AQ5" t="n">
-        <v>263.0906854286245</v>
+        <v>262.0808568601581</v>
       </c>
       <c r="AR5" t="n">
-        <v>224.3424967575606</v>
+        <v>223.4600764531305</v>
       </c>
       <c r="AS5" t="n">
-        <v>269.1076750070314</v>
+        <v>268.1219571803903</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4244,19 +5603,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>301.54</v>
+        <v>290.55</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>36.506054</v>
+        <v>35.21818</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -4265,49 +5624,49 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.29914316528635</v>
+        <v>34.32021233616655</v>
       </c>
       <c r="P6" t="n">
-        <v>34.20253319076345</v>
+        <v>34.2063305045985</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.086475296404038</v>
+        <v>2.097130028706181</v>
       </c>
       <c r="R6" t="n">
-        <v>31.83607656744462</v>
+        <v>31.8341779105271</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38147763305368</v>
+        <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>1.057722005392147</v>
+        <v>0.4281888349991569</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="V6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="W6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>283.3109225452652</v>
+        <v>283.141751773374</v>
       </c>
       <c r="Y6" t="n">
-        <v>266.0766365969678</v>
+        <v>265.840429036548</v>
       </c>
       <c r="Z6" t="n">
-        <v>300.5452084935625</v>
+        <v>300.4430745102</v>
       </c>
       <c r="AA6" t="n">
-        <v>262.9659924470926</v>
+        <v>262.6319677618486</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.7710052490234</v>
+        <v>308.446133223342</v>
       </c>
       <c r="AC6" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -4316,57 +5675,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.49176155124631</v>
+        <v>34.46880555717656</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.42623029342849</v>
+        <v>34.40435746680161</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.777300376160677</v>
+        <v>1.766435081379112</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13088525699663</v>
+        <v>32.1253156058396</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.91245386750294</v>
+        <v>36.81098999350704</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.133343848778651</v>
+        <v>0.4242298235145881</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.8114754098360656</v>
+        <v>0.7024793388429752</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.9019504132945</v>
+        <v>284.3676458467066</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.2214493062074</v>
+        <v>269.7945564253289</v>
       </c>
       <c r="AQ6" t="n">
-        <v>299.5824515203817</v>
+        <v>298.9407352680843</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.4011122227922</v>
+        <v>265.0338537481767</v>
       </c>
       <c r="AS6" t="n">
-        <v>304.8968689455743</v>
+        <v>303.6906674464331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4395,19 +5754,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>208.64</v>
+        <v>208.19</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="J7" t="n">
-        <v>31.950994</v>
+        <v>31.833334</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M7" t="n">
         <v>31.4088830173837</v>
@@ -4416,46 +5775,46 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>38.36880050331563</v>
+        <v>38.37541516938103</v>
       </c>
       <c r="P7" t="n">
-        <v>37.38367353166852</v>
+        <v>37.37551007952008</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.287242152477702</v>
+        <v>4.322502525185715</v>
       </c>
       <c r="R7" t="n">
-        <v>32.91071986713963</v>
+        <v>32.90352229867558</v>
       </c>
       <c r="S7" t="n">
-        <v>44.72591882822464</v>
+        <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.496954516461501</v>
+        <v>-1.513493891851445</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="V7" t="n">
-        <v>205.1000061035156</v>
+        <v>205.4140949336894</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="X7" t="n">
-        <v>250.5482672866511</v>
+        <v>250.9752152077519</v>
       </c>
       <c r="Y7" t="n">
-        <v>222.5525760309716</v>
+        <v>222.7060486930374</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.5439585423305</v>
+        <v>279.2443817224665</v>
       </c>
       <c r="AA7" t="n">
-        <v>214.9070007324218</v>
+        <v>215.1890358333383</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.0602499483069</v>
+        <v>292.8852277483259</v>
       </c>
       <c r="AC7" t="n">
         <v>72</v>
@@ -4482,42 +5841,42 @@
         <v>44.17734698860012</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.567955474324383</v>
+        <v>-1.597327702410383</v>
       </c>
       <c r="AL7" t="n">
         <v>0.01388888888888889</v>
       </c>
       <c r="AM7" t="n">
-        <v>205.1000061035156</v>
+        <v>205.4140949336894</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="AO7" t="n">
-        <v>249.6546265811877</v>
+        <v>250.0369460705923</v>
       </c>
       <c r="AP7" t="n">
-        <v>223.4965905700819</v>
+        <v>223.8388518113837</v>
       </c>
       <c r="AQ7" t="n">
-        <v>275.8126625922935</v>
+        <v>276.2350403298009</v>
       </c>
       <c r="AR7" t="n">
-        <v>215.6630020141602</v>
+        <v>215.9932669483319</v>
       </c>
       <c r="AS7" t="n">
-        <v>288.4780758355588</v>
+        <v>288.9198493054448</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4546,19 +5905,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>490.33</v>
+        <v>475.505</v>
       </c>
       <c r="I8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>163.98996</v>
+        <v>158.50166</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
         <v>72.9773582602447</v>
@@ -4567,49 +5926,49 @@
         <v>177.8754162397541</v>
       </c>
       <c r="O8" t="n">
-        <v>117.0632143411623</v>
+        <v>117.7151630957124</v>
       </c>
       <c r="P8" t="n">
-        <v>118.5924486844045</v>
+        <v>121.9660345113502</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.08285792004858</v>
+        <v>33.97367187361893</v>
       </c>
       <c r="R8" t="n">
-        <v>75.99849139519458</v>
+        <v>75.97358559662442</v>
       </c>
       <c r="S8" t="n">
-        <v>164.9360701764216</v>
+        <v>165.2098408683402</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3768430384834</v>
+        <v>1.200532490453554</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8870967741935484</v>
+        <v>0.8524590163934426</v>
       </c>
       <c r="V8" t="n">
-        <v>218.2023011981317</v>
+        <v>218.9320747807341</v>
       </c>
       <c r="W8" t="n">
-        <v>531.8474945568648</v>
+        <v>533.6262487192623</v>
       </c>
       <c r="X8" t="n">
-        <v>350.0190108800753</v>
+        <v>353.1454892871371</v>
       </c>
       <c r="Y8" t="n">
-        <v>248.11126569913</v>
+        <v>251.2244736662804</v>
       </c>
       <c r="Z8" t="n">
-        <v>451.9267560610205</v>
+        <v>455.0665049079939</v>
       </c>
       <c r="AA8" t="n">
-        <v>227.2354892716318</v>
+        <v>227.9207567898733</v>
       </c>
       <c r="AB8" t="n">
-        <v>493.1588498275007</v>
+        <v>495.6295226050205</v>
       </c>
       <c r="AC8" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -4618,57 +5977,57 @@
         <v>177.8754162397541</v>
       </c>
       <c r="AF8" t="n">
-        <v>107.2228551603934</v>
+        <v>107.2075166565454</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.0953815714424</v>
+        <v>105.0528357163915</v>
       </c>
       <c r="AH8" t="n">
-        <v>29.0980349864215</v>
+        <v>29.21852999343573</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51811131891215</v>
+        <v>75.51697928950472</v>
       </c>
       <c r="AJ8" t="n">
-        <v>149.0626240714652</v>
+        <v>149.2426237512807</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.950891352838665</v>
+        <v>1.755534701950387</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9426229508196722</v>
+        <v>0.9256198347107438</v>
       </c>
       <c r="AM8" t="n">
-        <v>215.4492418397148</v>
+        <v>216.1698078659346</v>
       </c>
       <c r="AN8" t="n">
-        <v>531.8474945568648</v>
+        <v>533.6262487192623</v>
       </c>
       <c r="AO8" t="n">
-        <v>320.5963369295761</v>
+        <v>321.6225499696361</v>
       </c>
       <c r="AP8" t="n">
-        <v>233.5932123201758</v>
+        <v>233.9669599893288</v>
       </c>
       <c r="AQ8" t="n">
-        <v>407.5994615389765</v>
+        <v>409.2781399499432</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.7991528435473</v>
+        <v>226.5509378685142</v>
       </c>
       <c r="AS8" t="n">
-        <v>445.6972459736809</v>
+        <v>447.7278712538422</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4697,19 +6056,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>396.6</v>
+        <v>392.16</v>
       </c>
       <c r="I9" t="n">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>65.77114</v>
+        <v>65.36</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -4718,46 +6077,46 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.04499179120712</v>
+        <v>75.18371546923311</v>
       </c>
       <c r="P9" t="n">
-        <v>78.71540210865163</v>
+        <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.781241462981987</v>
+        <v>9.800724438389427</v>
       </c>
       <c r="R9" t="n">
-        <v>61.29473531920079</v>
+        <v>61.29239623309577</v>
       </c>
       <c r="S9" t="n">
-        <v>83.49376061274063</v>
+        <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9481262502622875</v>
+        <v>-1.002345850144875</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2786885245901639</v>
       </c>
       <c r="V9" t="n">
-        <v>344.885442901076</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="W9" t="n">
-        <v>566.0559735214503</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="X9" t="n">
-        <v>452.521300500979</v>
+        <v>451.1022928153986</v>
       </c>
       <c r="Y9" t="n">
-        <v>393.5404144791976</v>
+        <v>392.2979461850621</v>
       </c>
       <c r="Z9" t="n">
-        <v>511.5021865227603</v>
+        <v>509.9066394457352</v>
       </c>
       <c r="AA9" t="n">
-        <v>369.6072539747808</v>
+        <v>367.7543773985747</v>
       </c>
       <c r="AB9" t="n">
-        <v>503.467376494826</v>
+        <v>501.087710731908</v>
       </c>
       <c r="AC9" t="n">
         <v>117</v>
@@ -4784,42 +6143,42 @@
         <v>82.39649127566095</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.9115761531717999</v>
+        <v>-0.9651586185673682</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1709401709401709</v>
+        <v>0.1623931623931624</v>
       </c>
       <c r="AM9" t="n">
-        <v>344.885442901076</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="AN9" t="n">
-        <v>566.0559735214503</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="AO9" t="n">
-        <v>438.7771316636375</v>
+        <v>436.5941608593408</v>
       </c>
       <c r="AP9" t="n">
-        <v>392.5087455097398</v>
+        <v>390.5559656813331</v>
       </c>
       <c r="AQ9" t="n">
-        <v>485.0455178175354</v>
+        <v>482.6323560373486</v>
       </c>
       <c r="AR9" t="n">
-        <v>376.989014100192</v>
+        <v>375.1134468658627</v>
       </c>
       <c r="AS9" t="n">
-        <v>496.8508423922356</v>
+        <v>494.3789476539657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-09 03:47:43</t>
+          <t>2026-06-10 04:50:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4848,19 +6207,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>82.64</v>
+        <v>81.41</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>26.658066</v>
+        <v>26.261292</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M10" t="n">
         <v>35.93675816954359</v>
@@ -4869,22 +6228,22 @@
         <v>42.60474344487245</v>
       </c>
       <c r="O10" t="n">
-        <v>38.40270594790844</v>
+        <v>38.4385770413244</v>
       </c>
       <c r="P10" t="n">
-        <v>37.65019654285294</v>
+        <v>37.67193579391056</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.990322096160243</v>
+        <v>2.02276804145474</v>
       </c>
       <c r="R10" t="n">
-        <v>36.38339890792905</v>
+        <v>36.36521712593409</v>
       </c>
       <c r="S10" t="n">
-        <v>41.39130483031742</v>
+        <v>41.51462479542365</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.900874019620422</v>
+        <v>-6.020109469678346</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4896,22 +6255,22 @@
         <v>132.0747046791046</v>
       </c>
       <c r="X10" t="n">
-        <v>119.0483884385162</v>
+        <v>119.1595888281056</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.8783899404194</v>
+        <v>112.889007899596</v>
       </c>
       <c r="Z10" t="n">
-        <v>125.2183869366129</v>
+        <v>125.4301697566153</v>
       </c>
       <c r="AA10" t="n">
-        <v>112.7885366145801</v>
+        <v>112.7321730903957</v>
       </c>
       <c r="AB10" t="n">
-        <v>128.313044973984</v>
+        <v>128.6953368658133</v>
       </c>
       <c r="AC10" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -4920,25 +6279,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>25.3821414425773</v>
+        <v>25.63451672873259</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.59090830686063</v>
+        <v>32.68774582934472</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.350467123509</v>
+        <v>15.26103564931867</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.777151179492922</v>
+        <v>3.776273990334723</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.12055275656958</v>
+        <v>39.12410992407514</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.08311959155097284</v>
+        <v>0.04107029730288267</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.3255813953488372</v>
+        <v>0.3176470588235294</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -4947,19 +6306,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>78.68463847198962</v>
+        <v>79.46700185907103</v>
       </c>
       <c r="AP10" t="n">
-        <v>31.09819038911171</v>
+        <v>32.15779134618315</v>
       </c>
       <c r="AQ10" t="n">
-        <v>126.2710865548675</v>
+        <v>126.7762123719589</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.70916865642806</v>
+        <v>11.70644937003764</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.2737135453657</v>
+        <v>121.2847407646329</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS28"/>
+  <dimension ref="A1:AS37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3658,7 +3658,7 @@
         <v>409.2781399499432</v>
       </c>
       <c r="AR21" t="n">
-        <v>226.5509378685142</v>
+        <v>226.5509378685141</v>
       </c>
       <c r="AS21" t="n">
         <v>447.7278712538422</v>
@@ -3737,7 +3737,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.04613713813768135</v>
+        <v>-0.0461371381376813</v>
       </c>
       <c r="U22" t="n">
         <v>0.4426229508196721</v>
@@ -3752,13 +3752,13 @@
         <v>245.0339119658596</v>
       </c>
       <c r="Y22" t="n">
-        <v>226.7426958236435</v>
+        <v>226.7426958236434</v>
       </c>
       <c r="Z22" t="n">
         <v>263.3251281080758</v>
       </c>
       <c r="AA22" t="n">
-        <v>224.2460854928031</v>
+        <v>224.2460854928032</v>
       </c>
       <c r="AB22" t="n">
         <v>269.7800810533255</v>
@@ -3788,7 +3788,7 @@
         <v>34.73082346896248</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.01796859900556732</v>
+        <v>-0.0179685990055673</v>
       </c>
       <c r="AL22" t="n">
         <v>0.4462809917355372</v>
@@ -3809,7 +3809,7 @@
         <v>262.0808568601581</v>
       </c>
       <c r="AR22" t="n">
-        <v>223.4600764531305</v>
+        <v>223.4600764531304</v>
       </c>
       <c r="AS22" t="n">
         <v>268.1219571803903</v>
@@ -3870,7 +3870,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N23" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O23" t="n">
         <v>75.18371546923311</v>
@@ -3879,7 +3879,7 @@
         <v>79.03509009883652</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.800724438389427</v>
+        <v>9.800724438389429</v>
       </c>
       <c r="R23" t="n">
         <v>61.29239623309577</v>
@@ -3921,7 +3921,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE23" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF23" t="n">
         <v>72.76569347655681</v>
@@ -3960,7 +3960,7 @@
         <v>482.6323560373486</v>
       </c>
       <c r="AR23" t="n">
-        <v>375.1134468658627</v>
+        <v>375.1134468658626</v>
       </c>
       <c r="AS23" t="n">
         <v>494.3789476539657</v>
@@ -4051,7 +4051,7 @@
         <v>422.673178165517</v>
       </c>
       <c r="X24" t="n">
-        <v>380.7341630055508</v>
+        <v>380.7341630055509</v>
       </c>
       <c r="Y24" t="n">
         <v>359.2855331151792</v>
@@ -4075,7 +4075,7 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF24" t="n">
-        <v>29.8256884086393</v>
+        <v>29.82568840863929</v>
       </c>
       <c r="AG24" t="n">
         <v>29.45232609589531</v>
@@ -4105,7 +4105,7 @@
         <v>391.0147750372612</v>
       </c>
       <c r="AP24" t="n">
-        <v>365.6014317399438</v>
+        <v>365.6014317399439</v>
       </c>
       <c r="AQ24" t="n">
         <v>416.4281183345785</v>
@@ -4226,7 +4226,7 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF25" t="n">
-        <v>26.54241044963202</v>
+        <v>26.54241044963201</v>
       </c>
       <c r="AG25" t="n">
         <v>27.49335641244326</v>
@@ -4241,7 +4241,7 @@
         <v>29.31247287326389</v>
       </c>
       <c r="AK25" t="n">
-        <v>-1.90709624583358</v>
+        <v>-1.907096245833581</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
         <v>23.20450334865052</v>
       </c>
       <c r="S26" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T26" t="n">
         <v>-0.5997134971484183</v>
@@ -4380,7 +4380,7 @@
         <v>27.1712636279093</v>
       </c>
       <c r="AG26" t="n">
-        <v>25.28893027624687</v>
+        <v>25.28893027624688</v>
       </c>
       <c r="AH26" t="n">
         <v>3.95924268811864</v>
@@ -4522,7 +4522,7 @@
         <v>85</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE27" t="n">
         <v>42.60474344487245</v>
@@ -4543,7 +4543,7 @@
         <v>39.12410992407514</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.04107029730288267</v>
+        <v>0.0410702973028826</v>
       </c>
       <c r="AL27" t="n">
         <v>0.3176470588235294</v>
@@ -4646,7 +4646,7 @@
         <v>-1.513493891851445</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V28" t="n">
         <v>205.4140949336894</v>
@@ -4697,7 +4697,7 @@
         <v>-1.597327702410383</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.0138888888888888</v>
       </c>
       <c r="AM28" t="n">
         <v>205.4140949336894</v>
@@ -4719,6 +4719,1365 @@
       </c>
       <c r="AS28" t="n">
         <v>288.9198493054448</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>291.58</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35.34303</v>
+      </c>
+      <c r="K29" t="n">
+        <v>67</v>
+      </c>
+      <c r="L29" t="n">
+        <v>62</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N29" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O29" t="n">
+        <v>34.38119441094596</v>
+      </c>
+      <c r="P29" t="n">
+        <v>34.28923981099189</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.070691878973815</v>
+      </c>
+      <c r="R29" t="n">
+        <v>31.83607656744462</v>
+      </c>
+      <c r="S29" t="n">
+        <v>37.38147763305368</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.4644996190986669</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.6612903225806451</v>
+      </c>
+      <c r="V29" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="W29" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X29" t="n">
+        <v>283.6448538903041</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>266.5616458887702</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>300.7280618918381</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>262.6476316814181</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>308.3971904726929</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>34.45818284706386</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.742942735158953</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>36.73994458073265</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.5076742540571434</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.7131147540983607</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>284.2800084882768</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>269.9007309232155</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>298.6592860533382</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>265.0798033702222</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>303.1045427910444</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>452.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J30" t="n">
+        <v>151.30435</v>
+      </c>
+      <c r="K30" t="n">
+        <v>63</v>
+      </c>
+      <c r="L30" t="n">
+        <v>62</v>
+      </c>
+      <c r="M30" t="n">
+        <v>72.9773582602447</v>
+      </c>
+      <c r="N30" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="O30" t="n">
+        <v>119.5199817246286</v>
+      </c>
+      <c r="P30" t="n">
+        <v>126.7433943838443</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>33.77577234707775</v>
+      </c>
+      <c r="R30" t="n">
+        <v>76.24868083450029</v>
+      </c>
+      <c r="S30" t="n">
+        <v>164.9360701764216</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.9410404578985555</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="V30" t="n">
+        <v>218.2023011981317</v>
+      </c>
+      <c r="W30" t="n">
+        <v>531.8474945568648</v>
+      </c>
+      <c r="X30" t="n">
+        <v>357.3647453566395</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>256.375186038877</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>458.354304674402</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>227.9835556951559</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>493.1588498275007</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>107.9713917361802</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>105.3177330881504</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>29.65733244873455</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>150.3049206342854</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.461121236669711</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.9016393442622951</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>531.8474945568648</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>322.8344612911789</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>234.1590372694626</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>411.5098853128952</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>225.7991528435473</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>449.4117126965133</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>238</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="J31" t="n">
+        <v>31.648935</v>
+      </c>
+      <c r="K31" t="n">
+        <v>67</v>
+      </c>
+      <c r="L31" t="n">
+        <v>62</v>
+      </c>
+      <c r="M31" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N31" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O31" t="n">
+        <v>31.68715910264157</v>
+      </c>
+      <c r="P31" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.386505114862865</v>
+      </c>
+      <c r="R31" t="n">
+        <v>28.97210582695912</v>
+      </c>
+      <c r="S31" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T31" t="n">
+        <v>-0.01601676962832227</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="V31" t="n">
+        <v>209.0706795621949</v>
+      </c>
+      <c r="W31" t="n">
+        <v>276.8765309013249</v>
+      </c>
+      <c r="X31" t="n">
+        <v>238.2874364518646</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>220.3409179880959</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>256.2339549156334</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>217.8702358187326</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>262.7227874798422</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>31.62303786330475</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>31.82655590002617</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>2.2960326000314</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>28.90795038667516</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.01127908057354901</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.459016393442623</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>208.4938283837822</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>276.8765309013249</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>237.8052447320517</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>220.5390795798156</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>255.0714098842879</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>217.3877869077972</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>261.121253684242</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J32" t="n">
+        <v>61.708126</v>
+      </c>
+      <c r="K32" t="n">
+        <v>34</v>
+      </c>
+      <c r="L32" t="n">
+        <v>62</v>
+      </c>
+      <c r="M32" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N32" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O32" t="n">
+        <v>74.9658087483477</v>
+      </c>
+      <c r="P32" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>9.868908608061547</v>
+      </c>
+      <c r="R32" t="n">
+        <v>61.29473531920079</v>
+      </c>
+      <c r="S32" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-1.343378814706824</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.1451612903225807</v>
+      </c>
+      <c r="V32" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="W32" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X32" t="n">
+        <v>452.0438267525366</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>392.5343078459255</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>511.5533456591477</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>369.6072539747808</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>503.467376494826</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>119</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>72.61135179697153</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>71.81970368391313</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>7.702603776047882</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>62.30682194581507</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>82.39220215795567</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-1.415524686713907</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.07563025210084033</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>437.8464513357384</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>391.3997505661696</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>484.2931521053071</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>375.7101363332649</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>496.8249790124727</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>353.32</v>
+      </c>
+      <c r="I33" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J33" t="n">
+        <v>26.95042</v>
+      </c>
+      <c r="K33" t="n">
+        <v>37</v>
+      </c>
+      <c r="L33" t="n">
+        <v>62</v>
+      </c>
+      <c r="M33" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N33" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O33" t="n">
+        <v>29.0010964341592</v>
+      </c>
+      <c r="P33" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.648971241107393</v>
+      </c>
+      <c r="R33" t="n">
+        <v>26.96842149957094</v>
+      </c>
+      <c r="S33" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T33" t="n">
+        <v>-1.243609580954265</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="V33" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W33" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X33" t="n">
+        <v>380.2043742518271</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>358.5863612809092</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>401.822387222745</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>353.556005859375</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>29.77737577769321</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>29.39138079928343</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.956168105159117</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>27.55376194623738</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>32.65449124757065</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>-1.445149713993145</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>390.381396445558</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>364.736032586922</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>416.0267603041941</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>361.229819115172</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>428.1003802556511</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>570.98</v>
+      </c>
+      <c r="I34" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="J34" t="n">
+        <v>20.747818</v>
+      </c>
+      <c r="K34" t="n">
+        <v>55</v>
+      </c>
+      <c r="L34" t="n">
+        <v>62</v>
+      </c>
+      <c r="M34" t="n">
+        <v>20.76290838068182</v>
+      </c>
+      <c r="N34" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O34" t="n">
+        <v>24.45337802079756</v>
+      </c>
+      <c r="P34" t="n">
+        <v>23.2054731062458</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.626729250262965</v>
+      </c>
+      <c r="R34" t="n">
+        <v>21.84305353338068</v>
+      </c>
+      <c r="S34" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-1.410712588831375</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>571.3952386363636</v>
+      </c>
+      <c r="W34" t="n">
+        <v>806.6792534722222</v>
+      </c>
+      <c r="X34" t="n">
+        <v>672.9569631323488</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>600.6693741651121</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>745.2445520995857</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>601.1208332386362</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>786.4663274265644</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>20.76290838068182</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>26.43542124527686</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>27.46076574171008</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>2.834285376876971</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>22.13956365411932</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>29.31080928832899</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>-2.006715093574623</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>571.3952386363636</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>864.9762082934226</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>727.5027926700191</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>649.5032590983649</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>805.5023262416732</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>609.2807917613636</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>806.6334716148139</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>397.36</v>
+      </c>
+      <c r="I35" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="J35" t="n">
+        <v>23.63831</v>
+      </c>
+      <c r="K35" t="n">
+        <v>67</v>
+      </c>
+      <c r="L35" t="n">
+        <v>62</v>
+      </c>
+      <c r="M35" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N35" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O35" t="n">
+        <v>24.72139928367455</v>
+      </c>
+      <c r="P35" t="n">
+        <v>24.65476172310965</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.195050427058125</v>
+      </c>
+      <c r="R35" t="n">
+        <v>23.21232073451669</v>
+      </c>
+      <c r="S35" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T35" t="n">
+        <v>-0.9063126200798165</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="V35" t="n">
+        <v>375.0658858861678</v>
+      </c>
+      <c r="W35" t="n">
+        <v>460.7941080547514</v>
+      </c>
+      <c r="X35" t="n">
+        <v>415.5667219585692</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>395.4779242797222</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>435.6555196374163</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>390.1991115472255</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>445.7677735940003</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>27.06026990755874</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>25.26344430358227</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>3.915239171210909</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>23.43446802149336</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>34.03058373571968</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-0.8740104391886724</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.1065573770491803</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>375.0658858861678</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>583.4719783300017</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>454.8831371460624</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>389.067966678007</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>520.6983076141178</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>393.9334074413034</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>572.0541125974478</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>82</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>26.451614</v>
+      </c>
+      <c r="K36" t="n">
+        <v>67</v>
+      </c>
+      <c r="L36" t="n">
+        <v>24</v>
+      </c>
+      <c r="M36" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="N36" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="O36" t="n">
+        <v>38.48698946484148</v>
+      </c>
+      <c r="P36" t="n">
+        <v>37.71936770955563</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.051424908164389</v>
+      </c>
+      <c r="R36" t="n">
+        <v>36.34703534393912</v>
+      </c>
+      <c r="S36" t="n">
+        <v>41.63794476052987</v>
+      </c>
+      <c r="T36" t="n">
+        <v>-5.866836956567282</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>111.4039503255851</v>
+      </c>
+      <c r="W36" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="X36" t="n">
+        <v>119.3096673410086</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>112.950250125699</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>125.6690845563182</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>112.6758095662113</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>129.0776287576426</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>25.89235394481071</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>32.69960456214874</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>15.16530049649943</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>3.775396801176525</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>39.1276670915807</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.03687761118339752</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.3095238095238095</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>80.2662972289132</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>33.25386568976496</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>127.2787287680614</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>11.70373008364723</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>121.2957679839002</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:54:25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>200.42</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J37" t="n">
+        <v>30.692188</v>
+      </c>
+      <c r="K37" t="n">
+        <v>65</v>
+      </c>
+      <c r="L37" t="n">
+        <v>62</v>
+      </c>
+      <c r="M37" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N37" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O37" t="n">
+        <v>38.16288851506849</v>
+      </c>
+      <c r="P37" t="n">
+        <v>37.14387699049346</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4.469269939765504</v>
+      </c>
+      <c r="R37" t="n">
+        <v>32.8177641653905</v>
+      </c>
+      <c r="S37" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T37" t="n">
+        <v>-1.671570662715545</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="W37" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X37" t="n">
+        <v>249.2036620033972</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>220.0193292967285</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>278.387994710066</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>38.04425130262792</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>37.31530481455277</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>4.11124854985372</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>32.89173050277265</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>44.11979581871811</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>-1.788279938192866</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>248.4289610061603</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>221.5825079756155</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>275.2754140367051</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>214.7830001831054</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>288.1022666962293</v>
       </c>
     </row>
   </sheetData>
@@ -4965,12 +6324,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4999,19 +6358,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>362.29</v>
+        <v>353.32</v>
       </c>
       <c r="I2" t="n">
         <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.634632</v>
+        <v>26.95042</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -5020,25 +6379,25 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>29.04150747563317</v>
+        <v>29.0010964341592</v>
       </c>
       <c r="P2" t="n">
-        <v>29.2311213745769</v>
+        <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.636051097663735</v>
+        <v>1.648971241107393</v>
       </c>
       <c r="R2" t="n">
-        <v>27.1304342239345</v>
+        <v>26.96842149957094</v>
       </c>
       <c r="S2" t="n">
-        <v>31.24236919392489</v>
+        <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8599214765615648</v>
+        <v>-1.243609580954265</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1967213114754098</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="V2" t="n">
         <v>331.2549113821476</v>
@@ -5047,22 +6406,22 @@
         <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>380.7341630055508</v>
+        <v>380.2043742518271</v>
       </c>
       <c r="Y2" t="n">
-        <v>359.2855331151792</v>
+        <v>358.5863612809092</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.1827928959224</v>
+        <v>401.822387222745</v>
       </c>
       <c r="AA2" t="n">
-        <v>355.6799926757812</v>
+        <v>353.556005859375</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.5874601323553</v>
+        <v>409.3048835916722</v>
       </c>
       <c r="AC2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -5071,25 +6430,25 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.8256884086393</v>
+        <v>29.77737577769321</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.45232609589531</v>
+        <v>29.39138079928343</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.938470121839614</v>
+        <v>1.956168105159117</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.59481848223578</v>
+        <v>27.55376194623738</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65942708172662</v>
+        <v>32.65449124757065</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.130301872571541</v>
+        <v>-1.445149713993145</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1074380165289256</v>
+        <v>0.04918032786885246</v>
       </c>
       <c r="AM2" t="n">
         <v>331.2549113821476</v>
@@ -5098,30 +6457,30 @@
         <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>391.0147750372612</v>
+        <v>390.381396445558</v>
       </c>
       <c r="AP2" t="n">
-        <v>365.6014317399438</v>
+        <v>364.736032586922</v>
       </c>
       <c r="AQ2" t="n">
-        <v>416.4281183345785</v>
+        <v>416.0267603041941</v>
       </c>
       <c r="AR2" t="n">
-        <v>361.768070302111</v>
+        <v>361.229819115172</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.165089041436</v>
+        <v>428.1003802556511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5150,19 +6509,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>403.41</v>
+        <v>397.36</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.81</v>
       </c>
       <c r="J3" t="n">
-        <v>24.04112</v>
+        <v>23.63831</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
         <v>22.31206935670243</v>
@@ -5171,49 +6530,49 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.75727593191328</v>
+        <v>24.72139928367455</v>
       </c>
       <c r="P3" t="n">
-        <v>24.70952351888021</v>
+        <v>24.65476172310965</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.194163438572818</v>
+        <v>1.195050427058125</v>
       </c>
       <c r="R3" t="n">
-        <v>23.20450334865052</v>
+        <v>23.21232073451669</v>
       </c>
       <c r="S3" t="n">
-        <v>26.52657934096994</v>
+        <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5997134971484183</v>
+        <v>-0.9063126200798165</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2622950819672131</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="V3" t="n">
-        <v>374.3965238054668</v>
+        <v>375.0658858861678</v>
       </c>
       <c r="W3" t="n">
-        <v>459.9717509315128</v>
+        <v>460.7941080547514</v>
       </c>
       <c r="X3" t="n">
-        <v>415.4270901375049</v>
+        <v>415.5667219585692</v>
       </c>
       <c r="Y3" t="n">
-        <v>395.389027638253</v>
+        <v>395.4779242797222</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.4651526367568</v>
+        <v>435.6555196374163</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.3715661903558</v>
+        <v>390.1991115472255</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.1160013414757</v>
+        <v>445.7677735940003</v>
       </c>
       <c r="AC3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD3" t="n">
         <v>22.31206935670243</v>
@@ -5222,57 +6581,57 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>27.1712636279093</v>
+        <v>27.06026990755874</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.28893027624687</v>
+        <v>25.26344430358227</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.95924268811864</v>
+        <v>3.915239171210909</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.41025557049816</v>
+        <v>23.43446802149336</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34.03485055329281</v>
+        <v>34.03058373571968</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.790591503092904</v>
+        <v>-0.8740104391886724</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1322314049586777</v>
+        <v>0.1065573770491803</v>
       </c>
       <c r="AM3" t="n">
-        <v>374.3965238054668</v>
+        <v>375.0658858861678</v>
       </c>
       <c r="AN3" t="n">
-        <v>582.4306839010962</v>
+        <v>583.4719783300017</v>
       </c>
       <c r="AO3" t="n">
-        <v>455.9338036763182</v>
+        <v>454.8831371460624</v>
       </c>
       <c r="AP3" t="n">
-        <v>389.4977113696874</v>
+        <v>389.067966678007</v>
       </c>
       <c r="AQ3" t="n">
-        <v>522.3698959829489</v>
+        <v>520.6983076141178</v>
       </c>
       <c r="AR3" t="n">
-        <v>392.8240884729592</v>
+        <v>393.9334074413034</v>
       </c>
       <c r="AS3" t="n">
-        <v>571.1047922842533</v>
+        <v>572.0541125974478</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5301,129 +6660,129 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>584.59</v>
+        <v>570.98</v>
       </c>
       <c r="I4" t="n">
-        <v>27.48</v>
+        <v>27.52</v>
       </c>
       <c r="J4" t="n">
-        <v>21.27329</v>
+        <v>20.747818</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
-        <v>21.28690962357955</v>
+        <v>20.76290838068182</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.61076829673761</v>
+        <v>24.45337802079756</v>
       </c>
       <c r="P4" t="n">
-        <v>24.35632204694817</v>
+        <v>23.2054731062458</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.591363492259886</v>
+        <v>2.626729250262965</v>
       </c>
       <c r="R4" t="n">
-        <v>21.92727272727273</v>
+        <v>21.84305353338068</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57982234378326</v>
+        <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.287923638156625</v>
+        <v>-1.410712588831375</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>584.964276455966</v>
+        <v>571.3952386363636</v>
       </c>
       <c r="W4" t="n">
-        <v>805.5067545572916</v>
+        <v>806.6792534722222</v>
       </c>
       <c r="X4" t="n">
-        <v>676.3039127943495</v>
+        <v>672.9569631323488</v>
       </c>
       <c r="Y4" t="n">
-        <v>605.0932440270478</v>
+        <v>600.6693741651121</v>
       </c>
       <c r="Z4" t="n">
-        <v>747.5145815616511</v>
+        <v>745.2445520995857</v>
       </c>
       <c r="AA4" t="n">
-        <v>602.5614545454545</v>
+        <v>601.1208332386362</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.3735180071639</v>
+        <v>786.4663274265644</v>
       </c>
       <c r="AC4" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD4" t="n">
-        <v>21.28690962357955</v>
+        <v>20.76290838068182</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.54241044963202</v>
+        <v>26.43542124527686</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.49335641244326</v>
+        <v>27.46076574171008</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.76290221909011</v>
+        <v>2.834285376876971</v>
       </c>
       <c r="AI4" t="n">
-        <v>22.19127308238636</v>
+        <v>22.13956365411932</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.31247287326389</v>
+        <v>29.31080928832899</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.90709624583358</v>
+        <v>-2.006715093574623</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>584.964276455966</v>
+        <v>571.3952386363636</v>
       </c>
       <c r="AN4" t="n">
-        <v>863.718975432531</v>
+        <v>864.9762082934226</v>
       </c>
       <c r="AO4" t="n">
-        <v>729.3854391558878</v>
+        <v>727.5027926700191</v>
       </c>
       <c r="AP4" t="n">
-        <v>653.4608861752916</v>
+        <v>649.5032590983649</v>
       </c>
       <c r="AQ4" t="n">
-        <v>805.309992136484</v>
+        <v>805.5023262416732</v>
       </c>
       <c r="AR4" t="n">
-        <v>609.8161843039773</v>
+        <v>609.2807917613636</v>
       </c>
       <c r="AS4" t="n">
-        <v>805.5067545572916</v>
+        <v>806.6334716148139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5452,19 +6811,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>244.19</v>
+        <v>238</v>
       </c>
       <c r="I5" t="n">
-        <v>7.72</v>
+        <v>7.52</v>
       </c>
       <c r="J5" t="n">
-        <v>31.63083</v>
+        <v>31.648935</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -5473,49 +6832,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.74014403702845</v>
+        <v>31.68715910264157</v>
       </c>
       <c r="P5" t="n">
-        <v>31.73325461063659</v>
+        <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.369328515831107</v>
+        <v>2.386505114862865</v>
       </c>
       <c r="R5" t="n">
-        <v>29.04742040062217</v>
+        <v>28.97210582695912</v>
       </c>
       <c r="S5" t="n">
-        <v>34.94560635405771</v>
+        <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.04613713813768135</v>
+        <v>-0.01601676962832227</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4426229508196721</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="V5" t="n">
-        <v>214.6310699760831</v>
+        <v>209.0706795621949</v>
       </c>
       <c r="W5" t="n">
-        <v>284.2402684252964</v>
+        <v>276.8765309013249</v>
       </c>
       <c r="X5" t="n">
-        <v>245.0339119658596</v>
+        <v>238.2874364518646</v>
       </c>
       <c r="Y5" t="n">
-        <v>226.7426958236435</v>
+        <v>220.3409179880959</v>
       </c>
       <c r="Z5" t="n">
-        <v>263.3251281080758</v>
+        <v>256.2339549156334</v>
       </c>
       <c r="AA5" t="n">
-        <v>224.2460854928031</v>
+        <v>217.8702358187326</v>
       </c>
       <c r="AB5" t="n">
-        <v>269.7800810533255</v>
+        <v>262.7227874798422</v>
       </c>
       <c r="AC5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -5524,57 +6883,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.67173661011488</v>
+        <v>31.62303786330475</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.94774045782574</v>
+        <v>31.82655590002617</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.276560910630987</v>
+        <v>2.2960326000314</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.94560575817752</v>
+        <v>28.90795038667516</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.73082346896248</v>
+        <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01796859900556732</v>
+        <v>0.01127908057354901</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4462809917355372</v>
+        <v>0.459016393442623</v>
       </c>
       <c r="AM5" t="n">
-        <v>214.0388770110105</v>
+        <v>208.4938283837822</v>
       </c>
       <c r="AN5" t="n">
-        <v>284.2402684252964</v>
+        <v>276.8765309013249</v>
       </c>
       <c r="AO5" t="n">
-        <v>244.5058066300869</v>
+        <v>237.8052447320517</v>
       </c>
       <c r="AP5" t="n">
-        <v>226.9307564000156</v>
+        <v>220.5390795798156</v>
       </c>
       <c r="AQ5" t="n">
-        <v>262.0808568601581</v>
+        <v>255.0714098842879</v>
       </c>
       <c r="AR5" t="n">
-        <v>223.4600764531305</v>
+        <v>217.3877869077972</v>
       </c>
       <c r="AS5" t="n">
-        <v>268.1219571803903</v>
+        <v>261.121253684242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5603,19 +6962,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>290.55</v>
+        <v>291.58</v>
       </c>
       <c r="I6" t="n">
         <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>35.21818</v>
+        <v>35.34303</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -5624,25 +6983,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.32021233616655</v>
+        <v>34.38119441094596</v>
       </c>
       <c r="P6" t="n">
-        <v>34.2063305045985</v>
+        <v>34.28923981099189</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.097130028706181</v>
+        <v>2.070691878973815</v>
       </c>
       <c r="R6" t="n">
-        <v>31.8341779105271</v>
+        <v>31.83607656744462</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38741008767781</v>
+        <v>37.38147763305368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4281888349991569</v>
+        <v>0.4644996190986669</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6557377049180327</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="V6" t="n">
         <v>257.5566506687599</v>
@@ -5651,22 +7010,22 @@
         <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>283.141751773374</v>
+        <v>283.6448538903041</v>
       </c>
       <c r="Y6" t="n">
-        <v>265.840429036548</v>
+        <v>266.5616458887702</v>
       </c>
       <c r="Z6" t="n">
-        <v>300.4430745102</v>
+        <v>300.7280618918381</v>
       </c>
       <c r="AA6" t="n">
-        <v>262.6319677618486</v>
+        <v>262.6476316814181</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.446133223342</v>
+        <v>308.3971904726929</v>
       </c>
       <c r="AC6" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -5675,25 +7034,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.46880555717656</v>
+        <v>34.45818284706386</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.40435746680161</v>
+        <v>34.42623029342849</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.766435081379112</v>
+        <v>1.742942735158953</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.1253156058396</v>
+        <v>32.13088525699663</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.81098999350704</v>
+        <v>36.73994458073265</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.4242298235145881</v>
+        <v>0.5076742540571434</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7024793388429752</v>
+        <v>0.7131147540983607</v>
       </c>
       <c r="AM6" t="n">
         <v>257.5566506687599</v>
@@ -5702,30 +7061,30 @@
         <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.3676458467066</v>
+        <v>284.2800084882768</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.7945564253289</v>
+        <v>269.9007309232155</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.9407352680843</v>
+        <v>298.6592860533382</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.0338537481767</v>
+        <v>265.0798033702222</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.6906674464331</v>
+        <v>303.1045427910444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5754,129 +7113,129 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>208.19</v>
+        <v>200.42</v>
       </c>
       <c r="I7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.833334</v>
+        <v>30.692188</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
-        <v>31.4088830173837</v>
+        <v>30.69218961239591</v>
       </c>
       <c r="N7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>38.37541516938103</v>
+        <v>38.16288851506849</v>
       </c>
       <c r="P7" t="n">
-        <v>37.37551007952008</v>
+        <v>37.14387699049346</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.322502525185715</v>
+        <v>4.469269939765504</v>
       </c>
       <c r="R7" t="n">
-        <v>32.90352229867558</v>
+        <v>32.8177641653905</v>
       </c>
       <c r="S7" t="n">
-        <v>44.78367396763392</v>
+        <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.513493891851445</v>
+        <v>-1.671570662715545</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01639344262295082</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>205.4140949336894</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="W7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>250.9752152077519</v>
+        <v>249.2036620033972</v>
       </c>
       <c r="Y7" t="n">
-        <v>222.7060486930374</v>
+        <v>220.0193292967285</v>
       </c>
       <c r="Z7" t="n">
-        <v>279.2443817224665</v>
+        <v>278.387994710066</v>
       </c>
       <c r="AA7" t="n">
-        <v>215.1890358333383</v>
+        <v>214.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.8852277483259</v>
+        <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AD7" t="n">
-        <v>31.4088830173837</v>
+        <v>30.69218961239591</v>
       </c>
       <c r="AE7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>38.23194894045754</v>
+        <v>38.04425130262792</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.36530537507971</v>
+        <v>37.31530481455277</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.00582481027654</v>
+        <v>4.11124854985372</v>
       </c>
       <c r="AI7" t="n">
-        <v>33.02649341717613</v>
+        <v>32.89173050277265</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.17734698860012</v>
+        <v>44.11979581871811</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.597327702410383</v>
+        <v>-1.788279938192866</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01388888888888889</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>205.4140949336894</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>250.0369460705923</v>
+        <v>248.4289610061603</v>
       </c>
       <c r="AP7" t="n">
-        <v>223.8388518113837</v>
+        <v>221.5825079756155</v>
       </c>
       <c r="AQ7" t="n">
-        <v>276.2350403298009</v>
+        <v>275.2754140367051</v>
       </c>
       <c r="AR7" t="n">
-        <v>215.9932669483319</v>
+        <v>214.7830001831054</v>
       </c>
       <c r="AS7" t="n">
-        <v>288.9198493054448</v>
+        <v>288.1022666962293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5905,19 +7264,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>475.505</v>
+        <v>452.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>158.50166</v>
+        <v>151.30435</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
         <v>72.9773582602447</v>
@@ -5926,49 +7285,49 @@
         <v>177.8754162397541</v>
       </c>
       <c r="O8" t="n">
-        <v>117.7151630957124</v>
+        <v>119.5199817246286</v>
       </c>
       <c r="P8" t="n">
-        <v>121.9660345113502</v>
+        <v>126.7433943838443</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.97367187361893</v>
+        <v>33.77577234707775</v>
       </c>
       <c r="R8" t="n">
-        <v>75.97358559662442</v>
+        <v>76.24868083450029</v>
       </c>
       <c r="S8" t="n">
-        <v>165.2098408683402</v>
+        <v>164.9360701764216</v>
       </c>
       <c r="T8" t="n">
-        <v>1.200532490453554</v>
+        <v>0.9410404578985555</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8524590163934426</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="V8" t="n">
-        <v>218.9320747807341</v>
+        <v>218.2023011981317</v>
       </c>
       <c r="W8" t="n">
-        <v>533.6262487192623</v>
+        <v>531.8474945568648</v>
       </c>
       <c r="X8" t="n">
-        <v>353.1454892871371</v>
+        <v>357.3647453566395</v>
       </c>
       <c r="Y8" t="n">
-        <v>251.2244736662804</v>
+        <v>256.375186038877</v>
       </c>
       <c r="Z8" t="n">
-        <v>455.0665049079939</v>
+        <v>458.354304674402</v>
       </c>
       <c r="AA8" t="n">
-        <v>227.9207567898733</v>
+        <v>227.9835556951559</v>
       </c>
       <c r="AB8" t="n">
-        <v>495.6295226050205</v>
+        <v>493.1588498275007</v>
       </c>
       <c r="AC8" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -5977,57 +7336,57 @@
         <v>177.8754162397541</v>
       </c>
       <c r="AF8" t="n">
-        <v>107.2075166565454</v>
+        <v>107.9713917361802</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.0528357163915</v>
+        <v>105.3177330881504</v>
       </c>
       <c r="AH8" t="n">
-        <v>29.21852999343573</v>
+        <v>29.65733244873455</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51697928950472</v>
+        <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>149.2426237512807</v>
+        <v>150.3049206342854</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.755534701950387</v>
+        <v>1.461121236669711</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9256198347107438</v>
+        <v>0.9016393442622951</v>
       </c>
       <c r="AM8" t="n">
-        <v>216.1698078659346</v>
+        <v>215.4492418397148</v>
       </c>
       <c r="AN8" t="n">
-        <v>533.6262487192623</v>
+        <v>531.8474945568648</v>
       </c>
       <c r="AO8" t="n">
-        <v>321.6225499696361</v>
+        <v>322.8344612911789</v>
       </c>
       <c r="AP8" t="n">
-        <v>233.9669599893288</v>
+        <v>234.1590372694626</v>
       </c>
       <c r="AQ8" t="n">
-        <v>409.2781399499432</v>
+        <v>411.5098853128952</v>
       </c>
       <c r="AR8" t="n">
-        <v>226.5509378685142</v>
+        <v>225.7991528435473</v>
       </c>
       <c r="AS8" t="n">
-        <v>447.7278712538422</v>
+        <v>449.4117126965133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6056,19 +7415,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>392.16</v>
+        <v>372.1</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="J9" t="n">
-        <v>65.36</v>
+        <v>61.708126</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -6077,49 +7436,49 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.18371546923311</v>
+        <v>74.9658087483477</v>
       </c>
       <c r="P9" t="n">
-        <v>79.03509009883652</v>
+        <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.800724438389427</v>
+        <v>9.868908608061547</v>
       </c>
       <c r="R9" t="n">
-        <v>61.29239623309577</v>
+        <v>61.29473531920079</v>
       </c>
       <c r="S9" t="n">
-        <v>83.514618455318</v>
+        <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.002345850144875</v>
+        <v>-1.343378814706824</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2786885245901639</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="V9" t="n">
-        <v>343.1695949264438</v>
+        <v>344.885442901076</v>
       </c>
       <c r="W9" t="n">
-        <v>563.2397746482092</v>
+        <v>566.0559735214503</v>
       </c>
       <c r="X9" t="n">
-        <v>451.1022928153986</v>
+        <v>452.0438267525366</v>
       </c>
       <c r="Y9" t="n">
-        <v>392.2979461850621</v>
+        <v>392.5343078459255</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.9066394457352</v>
+        <v>511.5533456591477</v>
       </c>
       <c r="AA9" t="n">
-        <v>367.7543773985747</v>
+        <v>369.6072539747808</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.087710731908</v>
+        <v>503.467376494826</v>
       </c>
       <c r="AC9" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -6128,57 +7487,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.76569347655681</v>
+        <v>72.61135179697153</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.85744439530923</v>
+        <v>71.81970368391313</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.673032529667959</v>
+        <v>7.702603776047882</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.51890781097711</v>
+        <v>62.30682194581507</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.39649127566095</v>
+        <v>82.39220215795567</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.9651586185673682</v>
+        <v>-1.415524686713907</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1623931623931624</v>
+        <v>0.07563025210084033</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.1695949264438</v>
+        <v>344.885442901076</v>
       </c>
       <c r="AN9" t="n">
-        <v>563.2397746482092</v>
+        <v>566.0559735214503</v>
       </c>
       <c r="AO9" t="n">
-        <v>436.5941608593408</v>
+        <v>437.8464513357384</v>
       </c>
       <c r="AP9" t="n">
-        <v>390.5559656813331</v>
+        <v>391.3997505661696</v>
       </c>
       <c r="AQ9" t="n">
-        <v>482.6323560373486</v>
+        <v>484.2931521053071</v>
       </c>
       <c r="AR9" t="n">
-        <v>375.1134468658627</v>
+        <v>375.7101363332649</v>
       </c>
       <c r="AS9" t="n">
-        <v>494.3789476539657</v>
+        <v>496.8249790124727</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-10 04:50:29</t>
+          <t>2026-06-11 05:54:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6207,19 +7566,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>81.41</v>
+        <v>82</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>26.261292</v>
+        <v>26.451614</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
         <v>35.93675816954359</v>
@@ -6228,22 +7587,22 @@
         <v>42.60474344487245</v>
       </c>
       <c r="O10" t="n">
-        <v>38.4385770413244</v>
+        <v>38.48698946484148</v>
       </c>
       <c r="P10" t="n">
-        <v>37.67193579391056</v>
+        <v>37.71936770955563</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.02276804145474</v>
+        <v>2.051424908164389</v>
       </c>
       <c r="R10" t="n">
-        <v>36.36521712593409</v>
+        <v>36.34703534393912</v>
       </c>
       <c r="S10" t="n">
-        <v>41.51462479542365</v>
+        <v>41.63794476052987</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.020109469678346</v>
+        <v>-5.866836956567282</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -6255,22 +7614,22 @@
         <v>132.0747046791046</v>
       </c>
       <c r="X10" t="n">
-        <v>119.1595888281056</v>
+        <v>119.3096673410086</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.889007899596</v>
+        <v>112.950250125699</v>
       </c>
       <c r="Z10" t="n">
-        <v>125.4301697566153</v>
+        <v>125.6690845563182</v>
       </c>
       <c r="AA10" t="n">
-        <v>112.7321730903957</v>
+        <v>112.6758095662113</v>
       </c>
       <c r="AB10" t="n">
-        <v>128.6953368658133</v>
+        <v>129.0776287576426</v>
       </c>
       <c r="AC10" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -6279,25 +7638,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>25.63451672873259</v>
+        <v>25.89235394481071</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.68774582934472</v>
+        <v>32.69960456214874</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.26103564931867</v>
+        <v>15.16530049649943</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.776273990334723</v>
+        <v>3.775396801176525</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.12410992407514</v>
+        <v>39.1276670915807</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.04107029730288267</v>
+        <v>0.03687761118339752</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.3176470588235294</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -6306,19 +7665,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>79.46700185907103</v>
+        <v>80.2662972289132</v>
       </c>
       <c r="AP10" t="n">
-        <v>32.15779134618315</v>
+        <v>33.25386568976496</v>
       </c>
       <c r="AQ10" t="n">
-        <v>126.7762123719589</v>
+        <v>127.2787287680614</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.70644937003764</v>
+        <v>11.70373008364723</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.2847407646329</v>
+        <v>121.2957679839002</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS37"/>
+  <dimension ref="A1:AS46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4836,7 +4836,7 @@
         <v>34.42623029342849</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.742942735158953</v>
+        <v>1.742942735158954</v>
       </c>
       <c r="AI29" t="n">
         <v>32.13088525699663</v>
@@ -4945,7 +4945,7 @@
         <v>164.9360701764216</v>
       </c>
       <c r="T30" t="n">
-        <v>0.9410404578985555</v>
+        <v>0.9410404578985556</v>
       </c>
       <c r="U30" t="n">
         <v>0.8064516129032258</v>
@@ -4999,7 +4999,7 @@
         <v>1.461121236669711</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.9016393442622951</v>
+        <v>0.9016393442622952</v>
       </c>
       <c r="AM30" t="n">
         <v>215.4492418397148</v>
@@ -5084,7 +5084,7 @@
         <v>31.68715910264157</v>
       </c>
       <c r="P31" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q31" t="n">
         <v>2.386505114862865</v>
@@ -5096,7 +5096,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.01601676962832227</v>
+        <v>-0.0160167696283222</v>
       </c>
       <c r="U31" t="n">
         <v>0.4516129032258064</v>
@@ -5147,10 +5147,10 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.01127908057354901</v>
+        <v>0.011279080573549</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.459016393442623</v>
+        <v>0.4590163934426229</v>
       </c>
       <c r="AM31" t="n">
         <v>208.4938283837822</v>
@@ -5229,7 +5229,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N32" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O32" t="n">
         <v>74.9658087483477</v>
@@ -5250,7 +5250,7 @@
         <v>-1.343378814706824</v>
       </c>
       <c r="U32" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.1451612903225806</v>
       </c>
       <c r="V32" t="n">
         <v>344.885442901076</v>
@@ -5280,7 +5280,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE32" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF32" t="n">
         <v>72.61135179697153</v>
@@ -5301,7 +5301,7 @@
         <v>-1.415524686713907</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.07563025210084033</v>
+        <v>0.0756302521008403</v>
       </c>
       <c r="AM32" t="n">
         <v>344.885442901076</v>
@@ -5452,7 +5452,7 @@
         <v>-1.445149713993145</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="AM33" t="n">
         <v>331.2549113821476</v>
@@ -5473,7 +5473,7 @@
         <v>361.229819115172</v>
       </c>
       <c r="AS33" t="n">
-        <v>428.1003802556511</v>
+        <v>428.1003802556512</v>
       </c>
     </row>
     <row r="34">
@@ -5528,7 +5528,7 @@
         <v>62</v>
       </c>
       <c r="M34" t="n">
-        <v>20.76290838068182</v>
+        <v>20.76290838068181</v>
       </c>
       <c r="N34" t="n">
         <v>29.31247287326389</v>
@@ -5549,7 +5549,7 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T34" t="n">
-        <v>-1.410712588831375</v>
+        <v>-1.410712588831374</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
         <v>122</v>
       </c>
       <c r="AD34" t="n">
-        <v>20.76290838068182</v>
+        <v>20.76290838068181</v>
       </c>
       <c r="AE34" t="n">
         <v>31.43082152229007</v>
@@ -5591,13 +5591,13 @@
         <v>27.46076574171008</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.834285376876971</v>
+        <v>2.834285376876972</v>
       </c>
       <c r="AI34" t="n">
         <v>22.13956365411932</v>
       </c>
       <c r="AJ34" t="n">
-        <v>29.31080928832899</v>
+        <v>29.310809288329</v>
       </c>
       <c r="AK34" t="n">
         <v>-2.006715093574623</v>
@@ -5685,13 +5685,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O35" t="n">
-        <v>24.72139928367455</v>
+        <v>24.72139928367456</v>
       </c>
       <c r="P35" t="n">
         <v>24.65476172310965</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.195050427058125</v>
+        <v>1.195050427058126</v>
       </c>
       <c r="R35" t="n">
         <v>23.21232073451669</v>
@@ -5700,19 +5700,19 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.9063126200798165</v>
+        <v>-0.9063126200798164</v>
       </c>
       <c r="U35" t="n">
         <v>0.2096774193548387</v>
       </c>
       <c r="V35" t="n">
-        <v>375.0658858861678</v>
+        <v>375.0658858861679</v>
       </c>
       <c r="W35" t="n">
         <v>460.7941080547514</v>
       </c>
       <c r="X35" t="n">
-        <v>415.5667219585692</v>
+        <v>415.5667219585693</v>
       </c>
       <c r="Y35" t="n">
         <v>395.4779242797222</v>
@@ -5724,7 +5724,7 @@
         <v>390.1991115472255</v>
       </c>
       <c r="AB35" t="n">
-        <v>445.7677735940003</v>
+        <v>445.7677735940004</v>
       </c>
       <c r="AC35" t="n">
         <v>122</v>
@@ -5757,7 +5757,7 @@
         <v>0.1065573770491803</v>
       </c>
       <c r="AM35" t="n">
-        <v>375.0658858861678</v>
+        <v>375.0658858861679</v>
       </c>
       <c r="AN35" t="n">
         <v>583.4719783300017</v>
@@ -5881,7 +5881,7 @@
         <v>84</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE36" t="n">
         <v>42.60474344487245</v>
@@ -5899,10 +5899,10 @@
         <v>3.775396801176525</v>
       </c>
       <c r="AJ36" t="n">
-        <v>39.1276670915807</v>
+        <v>39.12766709158071</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.03687761118339752</v>
+        <v>0.0368776111833975</v>
       </c>
       <c r="AL36" t="n">
         <v>0.3095238095238095</v>
@@ -6065,10 +6065,10 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO37" t="n">
-        <v>248.4289610061603</v>
+        <v>248.4289610061604</v>
       </c>
       <c r="AP37" t="n">
-        <v>221.5825079756155</v>
+        <v>221.5825079756156</v>
       </c>
       <c r="AQ37" t="n">
         <v>275.2754140367051</v>
@@ -6078,6 +6078,1365 @@
       </c>
       <c r="AS37" t="n">
         <v>288.1022666962293</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>295.63</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J38" t="n">
+        <v>35.83394</v>
+      </c>
+      <c r="K38" t="n">
+        <v>67</v>
+      </c>
+      <c r="L38" t="n">
+        <v>62</v>
+      </c>
+      <c r="M38" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N38" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O38" t="n">
+        <v>34.44780406604713</v>
+      </c>
+      <c r="P38" t="n">
+        <v>34.32974706722212</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.04804627672053</v>
+      </c>
+      <c r="R38" t="n">
+        <v>31.86556948891169</v>
+      </c>
+      <c r="S38" t="n">
+        <v>37.38147763305368</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.6768088932894814</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="V38" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="W38" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X38" t="n">
+        <v>284.1943835448889</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>267.2980017619445</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>301.0907653278332</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>262.8909482835215</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>308.3971904726929</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>34.46901516124925</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>34.44810312005538</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.739937261532854</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>36.7359232966446</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.7844678477362328</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.7479674796747967</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>284.3693750803063</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>270.0148926726603</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>298.7238574879523</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>303.071367197318</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>488.45</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J39" t="n">
+        <v>163.9094</v>
+      </c>
+      <c r="K39" t="n">
+        <v>63</v>
+      </c>
+      <c r="L39" t="n">
+        <v>62</v>
+      </c>
+      <c r="M39" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N39" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="O39" t="n">
+        <v>120.9259524782684</v>
+      </c>
+      <c r="P39" t="n">
+        <v>128.047168659714</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>33.62054285667178</v>
+      </c>
+      <c r="R39" t="n">
+        <v>76.51131799086085</v>
+      </c>
+      <c r="S39" t="n">
+        <v>164.9360701764216</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.278487611130344</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="V39" t="n">
+        <v>220.4525207519531</v>
+      </c>
+      <c r="W39" t="n">
+        <v>530.0687403944672</v>
+      </c>
+      <c r="X39" t="n">
+        <v>360.3593383852397</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>260.1701206723578</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>460.5485560981215</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>228.0037276127653</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>491.5094891257364</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>108.3955881040642</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>105.4975387498076</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>29.90787214180765</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>152.4137723328637</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.856160533010106</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.943089430894309</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>214.728675813495</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>530.0687403944672</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>323.0188525501114</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>233.8933935675246</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>412.1443115326982</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>225.0473451779923</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>454.193041551934</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>241.51</v>
+      </c>
+      <c r="I40" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="J40" t="n">
+        <v>31.652685</v>
+      </c>
+      <c r="K40" t="n">
+        <v>67</v>
+      </c>
+      <c r="L40" t="n">
+        <v>62</v>
+      </c>
+      <c r="M40" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N40" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O40" t="n">
+        <v>31.68594971204137</v>
+      </c>
+      <c r="P40" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.38792644284783</v>
+      </c>
+      <c r="R40" t="n">
+        <v>28.95578722242199</v>
+      </c>
+      <c r="S40" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-0.0139303755109381</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="V40" t="n">
+        <v>212.1288942898334</v>
+      </c>
+      <c r="W40" t="n">
+        <v>280.9265865395092</v>
+      </c>
+      <c r="X40" t="n">
+        <v>241.7637963028756</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>223.5439175439467</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>259.9836750618046</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>220.9326565070797</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>266.5658069775527</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>31.60080792395906</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>31.79665159380607</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.299855960956872</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>28.89175755032901</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.02255666307874404</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.4634146341463415</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>211.5436051287578</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>280.9265865395092</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>241.1141644598076</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>223.5662634777067</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>258.6620654419085</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>220.4441101090104</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>264.8855099134033</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>385.57</v>
+      </c>
+      <c r="I41" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="J41" t="n">
+        <v>64.15474</v>
+      </c>
+      <c r="K41" t="n">
+        <v>34</v>
+      </c>
+      <c r="L41" t="n">
+        <v>62</v>
+      </c>
+      <c r="M41" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N41" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O41" t="n">
+        <v>74.98767201170918</v>
+      </c>
+      <c r="P41" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>9.842980710970602</v>
+      </c>
+      <c r="R41" t="n">
+        <v>61.29473531920079</v>
+      </c>
+      <c r="S41" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T41" t="n">
+        <v>-1.1005743412293</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="V41" t="n">
+        <v>343.7415442513212</v>
+      </c>
+      <c r="W41" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="X41" t="n">
+        <v>450.6759087903721</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>391.5195947174388</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>509.8322228633055</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>368.3813592683967</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>501.7975012825711</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>120</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>72.54088005962326</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>71.70125773367891</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>7.708922396303556</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>62.32689989472924</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>82.39005759910303</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>-1.087848551133999</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.1416666666666667</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>343.7415442513212</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>435.9706891583358</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>389.6400655565515</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>482.3013127601201</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>374.5846683673227</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>495.1642461706092</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>356.56</v>
+      </c>
+      <c r="I42" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J42" t="n">
+        <v>27.176828</v>
+      </c>
+      <c r="K42" t="n">
+        <v>37</v>
+      </c>
+      <c r="L42" t="n">
+        <v>62</v>
+      </c>
+      <c r="M42" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N42" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O42" t="n">
+        <v>28.9899741468012</v>
+      </c>
+      <c r="P42" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.658903726109226</v>
+      </c>
+      <c r="R42" t="n">
+        <v>26.96842149957094</v>
+      </c>
+      <c r="S42" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-1.092978524470333</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="V42" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="W42" t="n">
+        <v>422.9955833357424</v>
+      </c>
+      <c r="X42" t="n">
+        <v>380.3484608060317</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>358.5836439194787</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>402.1132776925847</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>353.8256900743707</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>409.6170917408649</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>29.75640165697176</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>29.35926726899195</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.961972865230032</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>27.53833242970753</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>-1.314785592954324</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0.06504065040650407</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>446.7016702785662</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>390.4039897394695</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>364.6629057476515</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>416.1450737312875</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>361.3029214777628</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>428.3621670240005</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>568.4299999999999</v>
+      </c>
+      <c r="I43" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J43" t="n">
+        <v>20.662668</v>
+      </c>
+      <c r="K43" t="n">
+        <v>55</v>
+      </c>
+      <c r="L43" t="n">
+        <v>62</v>
+      </c>
+      <c r="M43" t="n">
+        <v>20.67018155184659</v>
+      </c>
+      <c r="N43" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O43" t="n">
+        <v>24.36537388910131</v>
+      </c>
+      <c r="P43" t="n">
+        <v>23.10090886896307</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.660935905533687</v>
+      </c>
+      <c r="R43" t="n">
+        <v>21.78258123224432</v>
+      </c>
+      <c r="S43" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T43" t="n">
+        <v>-1.391505102171443</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>568.6366944912997</v>
+      </c>
+      <c r="W43" t="n">
+        <v>806.3861287434895</v>
+      </c>
+      <c r="X43" t="n">
+        <v>670.2914356891772</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>597.0890889279455</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>743.493782450409</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>599.2388096990412</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>786.1805475110751</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>20.67018155184659</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>26.3885493778506</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>27.45253236915975</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>2.870114189878805</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>22.09650923295455</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>29.3091457033941</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>-1.995001243519298</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>568.6366944912997</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>725.94899338467</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>646.9921520211041</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>804.905834748236</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>607.8749689985796</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>806.2945983003717</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>390.34</v>
+      </c>
+      <c r="I44" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J44" t="n">
+        <v>23.262217</v>
+      </c>
+      <c r="K44" t="n">
+        <v>67</v>
+      </c>
+      <c r="L44" t="n">
+        <v>62</v>
+      </c>
+      <c r="M44" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N44" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O44" t="n">
+        <v>24.69716038883682</v>
+      </c>
+      <c r="P44" t="n">
+        <v>24.63035674322219</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.209870578371996</v>
+      </c>
+      <c r="R44" t="n">
+        <v>23.20750537293958</v>
+      </c>
+      <c r="S44" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T44" t="n">
+        <v>-1.186030484985995</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="V44" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="W44" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X44" t="n">
+        <v>414.418351324682</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>394.1167230195999</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>434.719979629764</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>389.4219401579262</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>444.9722332485025</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>27.02916627897323</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>25.26141292531465</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>3.91438935440781</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>23.36672861028866</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>34.02773861186433</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>-0.962333824746239</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0.06504065040650407</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>582.4306839010962</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>453.5494101611708</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>387.8659567942078</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>519.2328635281339</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>392.0937060806437</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>570.9854539070835</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>81.27</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>26.21613</v>
+      </c>
+      <c r="K45" t="n">
+        <v>67</v>
+      </c>
+      <c r="L45" t="n">
+        <v>23</v>
+      </c>
+      <c r="M45" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="N45" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="O45" t="n">
+        <v>38.52242658096891</v>
+      </c>
+      <c r="P45" t="n">
+        <v>37.7667996252007</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.090005653539248</v>
+      </c>
+      <c r="R45" t="n">
+        <v>36.32885356194415</v>
+      </c>
+      <c r="S45" t="n">
+        <v>41.7612647256361</v>
+      </c>
+      <c r="T45" t="n">
+        <v>-5.888164254546028</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>111.4039503255851</v>
+      </c>
+      <c r="W45" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="X45" t="n">
+        <v>119.4195224010036</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>112.9405048750319</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>125.8985399269753</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>112.6194460420269</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>129.4599206494719</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>25.89235394481071</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>32.69960456214874</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>15.16530049649943</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>3.775396801176525</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>39.1276670915807</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0.02134979489948309</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0.3095238095238095</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>80.2662972289132</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>33.25386568976496</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>127.2787287680614</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>11.70373008364723</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>121.2957679839002</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:00:20</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>204.87</v>
+      </c>
+      <c r="I46" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J46" t="n">
+        <v>31.325687</v>
+      </c>
+      <c r="K46" t="n">
+        <v>65</v>
+      </c>
+      <c r="L46" t="n">
+        <v>62</v>
+      </c>
+      <c r="M46" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N46" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O46" t="n">
+        <v>38.0755973053453</v>
+      </c>
+      <c r="P46" t="n">
+        <v>37.14387699049346</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4.548754831143522</v>
+      </c>
+      <c r="R46" t="n">
+        <v>32.58269609389954</v>
+      </c>
+      <c r="S46" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T46" t="n">
+        <v>-1.483902860433661</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="V46" t="n">
+        <v>200.7269200650692</v>
+      </c>
+      <c r="W46" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="X46" t="n">
+        <v>249.0144063769583</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>219.2655497812797</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>278.7632629726369</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>213.090832454103</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>292.5075091365892</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>37.95531007569792</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>37.2755089584662</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>4.155387460190137</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>32.8407350689127</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>44.0910202337771</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>-1.595428378030136</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>200.7269200650692</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>248.2277278950644</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>221.0514939054209</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>275.4039618847078</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>214.7784073506891</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>288.3552723289022</v>
       </c>
     </row>
   </sheetData>
@@ -6324,12 +7683,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6358,13 +7717,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>353.32</v>
+        <v>356.56</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.12</v>
       </c>
       <c r="J2" t="n">
-        <v>26.95042</v>
+        <v>27.176828</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -6379,13 +7738,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>29.0010964341592</v>
+        <v>28.9899741468012</v>
       </c>
       <c r="P2" t="n">
         <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.648971241107393</v>
+        <v>1.658903726109226</v>
       </c>
       <c r="R2" t="n">
         <v>26.96842149957094</v>
@@ -6394,34 +7753,34 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.243609580954265</v>
+        <v>-1.092978524470333</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="V2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="W2" t="n">
-        <v>422.673178165517</v>
+        <v>422.9955833357424</v>
       </c>
       <c r="X2" t="n">
-        <v>380.2043742518271</v>
+        <v>380.3484608060317</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.5863612809092</v>
+        <v>358.5836439194787</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.822387222745</v>
+        <v>402.1132776925847</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.556005859375</v>
+        <v>353.8256900743707</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.3048835916722</v>
+        <v>409.6170917408649</v>
       </c>
       <c r="AC2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -6430,57 +7789,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.77737577769321</v>
+        <v>29.75640165697176</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.39138079928343</v>
+        <v>29.35926726899195</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.956168105159117</v>
+        <v>1.961972865230032</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.55376194623738</v>
+        <v>27.53833242970753</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65449124757065</v>
+        <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.445149713993145</v>
+        <v>-1.314785592954324</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.06504065040650407</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.3611964445124</v>
+        <v>446.7016702785662</v>
       </c>
       <c r="AO2" t="n">
-        <v>390.381396445558</v>
+        <v>390.4039897394695</v>
       </c>
       <c r="AP2" t="n">
-        <v>364.736032586922</v>
+        <v>364.6629057476515</v>
       </c>
       <c r="AQ2" t="n">
-        <v>416.0267603041941</v>
+        <v>416.1450737312875</v>
       </c>
       <c r="AR2" t="n">
-        <v>361.229819115172</v>
+        <v>361.3029214777628</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.1003802556511</v>
+        <v>428.3621670240005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6509,13 +7868,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>397.36</v>
+        <v>390.34</v>
       </c>
       <c r="I3" t="n">
-        <v>16.81</v>
+        <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>23.63831</v>
+        <v>23.262217</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -6530,49 +7889,49 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.72139928367455</v>
+        <v>24.69716038883682</v>
       </c>
       <c r="P3" t="n">
-        <v>24.65476172310965</v>
+        <v>24.63035674322219</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.195050427058125</v>
+        <v>1.209870578371996</v>
       </c>
       <c r="R3" t="n">
-        <v>23.21232073451669</v>
+        <v>23.20750537293958</v>
       </c>
       <c r="S3" t="n">
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9063126200798165</v>
+        <v>-1.186030484985995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="V3" t="n">
-        <v>375.0658858861678</v>
+        <v>374.3965238054668</v>
       </c>
       <c r="W3" t="n">
-        <v>460.7941080547514</v>
+        <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>415.5667219585692</v>
+        <v>414.418351324682</v>
       </c>
       <c r="Y3" t="n">
-        <v>395.4779242797222</v>
+        <v>394.1167230195999</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.6555196374163</v>
+        <v>434.719979629764</v>
       </c>
       <c r="AA3" t="n">
-        <v>390.1991115472255</v>
+        <v>389.4219401579262</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.7677735940003</v>
+        <v>444.9722332485025</v>
       </c>
       <c r="AC3" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD3" t="n">
         <v>22.31206935670243</v>
@@ -6581,57 +7940,57 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>27.06026990755874</v>
+        <v>27.02916627897323</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.26344430358227</v>
+        <v>25.26141292531465</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.915239171210909</v>
+        <v>3.91438935440781</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.43446802149336</v>
+        <v>23.36672861028866</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34.03058373571968</v>
+        <v>34.02773861186433</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8740104391886724</v>
+        <v>-0.962333824746239</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1065573770491803</v>
+        <v>0.06504065040650407</v>
       </c>
       <c r="AM3" t="n">
-        <v>375.0658858861678</v>
+        <v>374.3965238054668</v>
       </c>
       <c r="AN3" t="n">
-        <v>583.4719783300017</v>
+        <v>582.4306839010962</v>
       </c>
       <c r="AO3" t="n">
-        <v>454.8831371460624</v>
+        <v>453.5494101611708</v>
       </c>
       <c r="AP3" t="n">
-        <v>389.067966678007</v>
+        <v>387.8659567942078</v>
       </c>
       <c r="AQ3" t="n">
-        <v>520.6983076141178</v>
+        <v>519.2328635281339</v>
       </c>
       <c r="AR3" t="n">
-        <v>393.9334074413034</v>
+        <v>392.0937060806437</v>
       </c>
       <c r="AS3" t="n">
-        <v>572.0541125974478</v>
+        <v>570.9854539070835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6660,13 +8019,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>570.98</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="J4" t="n">
-        <v>20.747818</v>
+        <v>20.662668</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -6675,114 +8034,114 @@
         <v>62</v>
       </c>
       <c r="M4" t="n">
-        <v>20.76290838068182</v>
+        <v>20.67018155184659</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.45337802079756</v>
+        <v>24.36537388910131</v>
       </c>
       <c r="P4" t="n">
-        <v>23.2054731062458</v>
+        <v>23.10090886896307</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.626729250262965</v>
+        <v>2.660935905533687</v>
       </c>
       <c r="R4" t="n">
-        <v>21.84305353338068</v>
+        <v>21.78258123224432</v>
       </c>
       <c r="S4" t="n">
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.410712588831375</v>
+        <v>-1.391505102171443</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>571.3952386363636</v>
+        <v>568.6366944912997</v>
       </c>
       <c r="W4" t="n">
-        <v>806.6792534722222</v>
+        <v>806.3861287434895</v>
       </c>
       <c r="X4" t="n">
-        <v>672.9569631323488</v>
+        <v>670.2914356891772</v>
       </c>
       <c r="Y4" t="n">
-        <v>600.6693741651121</v>
+        <v>597.0890889279455</v>
       </c>
       <c r="Z4" t="n">
-        <v>745.2445520995857</v>
+        <v>743.493782450409</v>
       </c>
       <c r="AA4" t="n">
-        <v>601.1208332386362</v>
+        <v>599.2388096990412</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.4663274265644</v>
+        <v>786.1805475110751</v>
       </c>
       <c r="AC4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.76290838068182</v>
+        <v>20.67018155184659</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.43542124527686</v>
+        <v>26.3885493778506</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.46076574171008</v>
+        <v>27.45253236915975</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.834285376876971</v>
+        <v>2.870114189878805</v>
       </c>
       <c r="AI4" t="n">
-        <v>22.13956365411932</v>
+        <v>22.09650923295455</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.31080928832899</v>
+        <v>29.3091457033941</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2.006715093574623</v>
+        <v>-1.995001243519298</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>571.3952386363636</v>
+        <v>568.6366944912997</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.9762082934226</v>
+        <v>864.6619000781998</v>
       </c>
       <c r="AO4" t="n">
-        <v>727.5027926700191</v>
+        <v>725.94899338467</v>
       </c>
       <c r="AP4" t="n">
-        <v>649.5032590983649</v>
+        <v>646.9921520211041</v>
       </c>
       <c r="AQ4" t="n">
-        <v>805.5023262416732</v>
+        <v>804.905834748236</v>
       </c>
       <c r="AR4" t="n">
-        <v>609.2807917613636</v>
+        <v>607.8749689985796</v>
       </c>
       <c r="AS4" t="n">
-        <v>806.6334716148139</v>
+        <v>806.2945983003717</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6811,13 +8170,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>238</v>
+        <v>241.51</v>
       </c>
       <c r="I5" t="n">
-        <v>7.52</v>
+        <v>7.63</v>
       </c>
       <c r="J5" t="n">
-        <v>31.648935</v>
+        <v>31.652685</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -6832,49 +8191,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.68715910264157</v>
+        <v>31.68594971204137</v>
       </c>
       <c r="P5" t="n">
         <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.386505114862865</v>
+        <v>2.38792644284783</v>
       </c>
       <c r="R5" t="n">
-        <v>28.97210582695912</v>
+        <v>28.95578722242199</v>
       </c>
       <c r="S5" t="n">
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01601676962832227</v>
+        <v>-0.0139303755109381</v>
       </c>
       <c r="U5" t="n">
         <v>0.4516129032258064</v>
       </c>
       <c r="V5" t="n">
-        <v>209.0706795621949</v>
+        <v>212.1288942898334</v>
       </c>
       <c r="W5" t="n">
-        <v>276.8765309013249</v>
+        <v>280.9265865395092</v>
       </c>
       <c r="X5" t="n">
-        <v>238.2874364518646</v>
+        <v>241.7637963028756</v>
       </c>
       <c r="Y5" t="n">
-        <v>220.3409179880959</v>
+        <v>223.5439175439467</v>
       </c>
       <c r="Z5" t="n">
-        <v>256.2339549156334</v>
+        <v>259.9836750618046</v>
       </c>
       <c r="AA5" t="n">
-        <v>217.8702358187326</v>
+        <v>220.9326565070797</v>
       </c>
       <c r="AB5" t="n">
-        <v>262.7227874798422</v>
+        <v>266.5658069775527</v>
       </c>
       <c r="AC5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -6883,57 +8242,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.62303786330475</v>
+        <v>31.60080792395906</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.82655590002617</v>
+        <v>31.79665159380607</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.2960326000314</v>
+        <v>2.299855960956872</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.90795038667516</v>
+        <v>28.89175755032901</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.72357096864921</v>
+        <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01127908057354901</v>
+        <v>0.02255666307874404</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.459016393442623</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="AM5" t="n">
-        <v>208.4938283837822</v>
+        <v>211.5436051287578</v>
       </c>
       <c r="AN5" t="n">
-        <v>276.8765309013249</v>
+        <v>280.9265865395092</v>
       </c>
       <c r="AO5" t="n">
-        <v>237.8052447320517</v>
+        <v>241.1141644598076</v>
       </c>
       <c r="AP5" t="n">
-        <v>220.5390795798156</v>
+        <v>223.5662634777067</v>
       </c>
       <c r="AQ5" t="n">
-        <v>255.0714098842879</v>
+        <v>258.6620654419085</v>
       </c>
       <c r="AR5" t="n">
-        <v>217.3877869077972</v>
+        <v>220.4441101090104</v>
       </c>
       <c r="AS5" t="n">
-        <v>261.121253684242</v>
+        <v>264.8855099134033</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6962,13 +8321,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>291.58</v>
+        <v>295.63</v>
       </c>
       <c r="I6" t="n">
         <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>35.34303</v>
+        <v>35.83394</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -6983,25 +8342,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.38119441094596</v>
+        <v>34.44780406604713</v>
       </c>
       <c r="P6" t="n">
-        <v>34.28923981099189</v>
+        <v>34.32974706722212</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.070691878973815</v>
+        <v>2.04804627672053</v>
       </c>
       <c r="R6" t="n">
-        <v>31.83607656744462</v>
+        <v>31.86556948891169</v>
       </c>
       <c r="S6" t="n">
         <v>37.38147763305368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4644996190986669</v>
+        <v>0.6768088932894814</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="V6" t="n">
         <v>257.5566506687599</v>
@@ -7010,22 +8369,22 @@
         <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>283.6448538903041</v>
+        <v>284.1943835448889</v>
       </c>
       <c r="Y6" t="n">
-        <v>266.5616458887702</v>
+        <v>267.2980017619445</v>
       </c>
       <c r="Z6" t="n">
-        <v>300.7280618918381</v>
+        <v>301.0907653278332</v>
       </c>
       <c r="AA6" t="n">
-        <v>262.6476316814181</v>
+        <v>262.8909482835215</v>
       </c>
       <c r="AB6" t="n">
         <v>308.3971904726929</v>
       </c>
       <c r="AC6" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -7034,25 +8393,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.45818284706386</v>
+        <v>34.46901516124925</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.42623029342849</v>
+        <v>34.44810312005538</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.742942735158953</v>
+        <v>1.739937261532854</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13088525699663</v>
+        <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.73994458073265</v>
+        <v>36.7359232966446</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.5076742540571434</v>
+        <v>0.7844678477362328</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7131147540983607</v>
+        <v>0.7479674796747967</v>
       </c>
       <c r="AM6" t="n">
         <v>257.5566506687599</v>
@@ -7061,30 +8420,30 @@
         <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.2800084882768</v>
+        <v>284.3693750803063</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.9007309232155</v>
+        <v>270.0148926726603</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.6592860533382</v>
+        <v>298.7238574879523</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.0798033702222</v>
+        <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.1045427910444</v>
+        <v>303.071367197318</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7113,13 +8472,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>200.42</v>
+        <v>204.87</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="J7" t="n">
-        <v>30.692188</v>
+        <v>31.325687</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -7134,49 +8493,49 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>38.16288851506849</v>
+        <v>38.0755973053453</v>
       </c>
       <c r="P7" t="n">
         <v>37.14387699049346</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.469269939765504</v>
+        <v>4.548754831143522</v>
       </c>
       <c r="R7" t="n">
-        <v>32.8177641653905</v>
+        <v>32.58269609389954</v>
       </c>
       <c r="S7" t="n">
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.671570662715545</v>
+        <v>-1.483902860433661</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="V7" t="n">
-        <v>200.4199981689453</v>
+        <v>200.7269200650692</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="X7" t="n">
-        <v>249.2036620033972</v>
+        <v>249.0144063769583</v>
       </c>
       <c r="Y7" t="n">
-        <v>220.0193292967285</v>
+        <v>219.2655497812797</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.387994710066</v>
+        <v>278.7632629726369</v>
       </c>
       <c r="AA7" t="n">
-        <v>214.3</v>
+        <v>213.090832454103</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.0602499483069</v>
+        <v>292.5075091365892</v>
       </c>
       <c r="AC7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD7" t="n">
         <v>30.69218961239591</v>
@@ -7185,57 +8544,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>38.04425130262792</v>
+        <v>37.95531007569792</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.31530481455277</v>
+        <v>37.2755089584662</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.11124854985372</v>
+        <v>4.155387460190137</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.89173050277265</v>
+        <v>32.8407350689127</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.11979581871811</v>
+        <v>44.0910202337771</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.788279938192866</v>
+        <v>-1.595428378030136</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>0.01333333333333333</v>
       </c>
       <c r="AM7" t="n">
-        <v>200.4199981689453</v>
+        <v>200.7269200650692</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="AO7" t="n">
-        <v>248.4289610061603</v>
+        <v>248.2277278950644</v>
       </c>
       <c r="AP7" t="n">
-        <v>221.5825079756155</v>
+        <v>221.0514939054209</v>
       </c>
       <c r="AQ7" t="n">
-        <v>275.2754140367051</v>
+        <v>275.4039618847078</v>
       </c>
       <c r="AR7" t="n">
-        <v>214.7830001831054</v>
+        <v>214.7784073506891</v>
       </c>
       <c r="AS7" t="n">
-        <v>288.1022666962293</v>
+        <v>288.3552723289022</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7264,13 +8623,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>452.4</v>
+        <v>488.45</v>
       </c>
       <c r="I8" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="n">
-        <v>151.30435</v>
+        <v>163.9094</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -7279,55 +8638,55 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>72.9773582602447</v>
+        <v>73.97735595703125</v>
       </c>
       <c r="N8" t="n">
         <v>177.8754162397541</v>
       </c>
       <c r="O8" t="n">
-        <v>119.5199817246286</v>
+        <v>120.9259524782684</v>
       </c>
       <c r="P8" t="n">
-        <v>126.7433943838443</v>
+        <v>128.047168659714</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.77577234707775</v>
+        <v>33.62054285667178</v>
       </c>
       <c r="R8" t="n">
-        <v>76.24868083450029</v>
+        <v>76.51131799086085</v>
       </c>
       <c r="S8" t="n">
         <v>164.9360701764216</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9410404578985555</v>
+        <v>1.278487611130344</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="V8" t="n">
-        <v>218.2023011981317</v>
+        <v>220.4525207519531</v>
       </c>
       <c r="W8" t="n">
-        <v>531.8474945568648</v>
+        <v>530.0687403944672</v>
       </c>
       <c r="X8" t="n">
-        <v>357.3647453566395</v>
+        <v>360.3593383852397</v>
       </c>
       <c r="Y8" t="n">
-        <v>256.375186038877</v>
+        <v>260.1701206723578</v>
       </c>
       <c r="Z8" t="n">
-        <v>458.354304674402</v>
+        <v>460.5485560981215</v>
       </c>
       <c r="AA8" t="n">
-        <v>227.9835556951559</v>
+        <v>228.0037276127653</v>
       </c>
       <c r="AB8" t="n">
-        <v>493.1588498275007</v>
+        <v>491.5094891257364</v>
       </c>
       <c r="AC8" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -7336,57 +8695,57 @@
         <v>177.8754162397541</v>
       </c>
       <c r="AF8" t="n">
-        <v>107.9713917361802</v>
+        <v>108.3955881040642</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.3177330881504</v>
+        <v>105.4975387498076</v>
       </c>
       <c r="AH8" t="n">
-        <v>29.65733244873455</v>
+        <v>29.90787214180765</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51811131891215</v>
+        <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>150.3049206342854</v>
+        <v>152.4137723328637</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.461121236669711</v>
+        <v>1.856160533010106</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9016393442622951</v>
+        <v>0.943089430894309</v>
       </c>
       <c r="AM8" t="n">
-        <v>215.4492418397148</v>
+        <v>214.728675813495</v>
       </c>
       <c r="AN8" t="n">
-        <v>531.8474945568648</v>
+        <v>530.0687403944672</v>
       </c>
       <c r="AO8" t="n">
-        <v>322.8344612911789</v>
+        <v>323.0188525501114</v>
       </c>
       <c r="AP8" t="n">
-        <v>234.1590372694626</v>
+        <v>233.8933935675246</v>
       </c>
       <c r="AQ8" t="n">
-        <v>411.5098853128952</v>
+        <v>412.1443115326982</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.7991528435473</v>
+        <v>225.0473451779923</v>
       </c>
       <c r="AS8" t="n">
-        <v>449.4117126965133</v>
+        <v>454.193041551934</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7415,13 +8774,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>372.1</v>
+        <v>385.57</v>
       </c>
       <c r="I9" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="J9" t="n">
-        <v>61.708126</v>
+        <v>64.15474</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -7436,13 +8795,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>74.9658087483477</v>
+        <v>74.98767201170918</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.868908608061547</v>
+        <v>9.842980710970602</v>
       </c>
       <c r="R9" t="n">
         <v>61.29473531920079</v>
@@ -7451,34 +8810,34 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.343378814706824</v>
+        <v>-1.1005743412293</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="V9" t="n">
-        <v>344.885442901076</v>
+        <v>343.7415442513212</v>
       </c>
       <c r="W9" t="n">
-        <v>566.0559735214503</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="X9" t="n">
-        <v>452.0438267525366</v>
+        <v>450.6759087903721</v>
       </c>
       <c r="Y9" t="n">
-        <v>392.5343078459255</v>
+        <v>391.5195947174388</v>
       </c>
       <c r="Z9" t="n">
-        <v>511.5533456591477</v>
+        <v>509.8322228633055</v>
       </c>
       <c r="AA9" t="n">
-        <v>369.6072539747808</v>
+        <v>368.3813592683967</v>
       </c>
       <c r="AB9" t="n">
-        <v>503.467376494826</v>
+        <v>501.7975012825711</v>
       </c>
       <c r="AC9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -7487,57 +8846,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.61135179697153</v>
+        <v>72.54088005962326</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.81970368391313</v>
+        <v>71.70125773367891</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.702603776047882</v>
+        <v>7.708922396303556</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.30682194581507</v>
+        <v>62.32689989472924</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.39220215795567</v>
+        <v>82.39005759910303</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.415524686713907</v>
+        <v>-1.087848551133999</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.07563025210084033</v>
+        <v>0.1416666666666667</v>
       </c>
       <c r="AM9" t="n">
-        <v>344.885442901076</v>
+        <v>343.7415442513212</v>
       </c>
       <c r="AN9" t="n">
-        <v>566.0559735214503</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="AO9" t="n">
-        <v>437.8464513357384</v>
+        <v>435.9706891583358</v>
       </c>
       <c r="AP9" t="n">
-        <v>391.3997505661696</v>
+        <v>389.6400655565515</v>
       </c>
       <c r="AQ9" t="n">
-        <v>484.2931521053071</v>
+        <v>482.3013127601201</v>
       </c>
       <c r="AR9" t="n">
-        <v>375.7101363332649</v>
+        <v>374.5846683673227</v>
       </c>
       <c r="AS9" t="n">
-        <v>496.8249790124727</v>
+        <v>495.1642461706092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-11 05:54:25</t>
+          <t>2026-06-12 05:00:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7566,19 +8925,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>82</v>
+        <v>81.27</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>26.451614</v>
+        <v>26.21613</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M10" t="n">
         <v>35.93675816954359</v>
@@ -7587,22 +8946,22 @@
         <v>42.60474344487245</v>
       </c>
       <c r="O10" t="n">
-        <v>38.48698946484148</v>
+        <v>38.52242658096891</v>
       </c>
       <c r="P10" t="n">
-        <v>37.71936770955563</v>
+        <v>37.7667996252007</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.051424908164389</v>
+        <v>2.090005653539248</v>
       </c>
       <c r="R10" t="n">
-        <v>36.34703534393912</v>
+        <v>36.32885356194415</v>
       </c>
       <c r="S10" t="n">
-        <v>41.63794476052987</v>
+        <v>41.7612647256361</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.866836956567282</v>
+        <v>-5.888164254546028</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -7614,19 +8973,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="X10" t="n">
-        <v>119.3096673410086</v>
+        <v>119.4195224010036</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.950250125699</v>
+        <v>112.9405048750319</v>
       </c>
       <c r="Z10" t="n">
-        <v>125.6690845563182</v>
+        <v>125.8985399269753</v>
       </c>
       <c r="AA10" t="n">
-        <v>112.6758095662113</v>
+        <v>112.6194460420269</v>
       </c>
       <c r="AB10" t="n">
-        <v>129.0776287576426</v>
+        <v>129.4599206494719</v>
       </c>
       <c r="AC10" t="n">
         <v>84</v>
@@ -7653,7 +9012,7 @@
         <v>39.1276670915807</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.03687761118339752</v>
+        <v>0.02134979489948309</v>
       </c>
       <c r="AL10" t="n">
         <v>0.3095238095238095</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS46"/>
+  <dimension ref="A1:AS55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6222,7 +6222,7 @@
         <v>270.0148926726603</v>
       </c>
       <c r="AQ38" t="n">
-        <v>298.7238574879523</v>
+        <v>298.7238574879524</v>
       </c>
       <c r="AR38" t="n">
         <v>265.1257529922678</v>
@@ -6310,7 +6310,7 @@
         <v>0.8870967741935484</v>
       </c>
       <c r="V39" t="n">
-        <v>220.4525207519531</v>
+        <v>220.4525207519532</v>
       </c>
       <c r="W39" t="n">
         <v>530.0687403944672</v>
@@ -6322,7 +6322,7 @@
         <v>260.1701206723578</v>
       </c>
       <c r="Z39" t="n">
-        <v>460.5485560981215</v>
+        <v>460.5485560981216</v>
       </c>
       <c r="AA39" t="n">
         <v>228.0037276127653</v>
@@ -6376,7 +6376,7 @@
         <v>412.1443115326982</v>
       </c>
       <c r="AR39" t="n">
-        <v>225.0473451779923</v>
+        <v>225.0473451779924</v>
       </c>
       <c r="AS39" t="n">
         <v>454.193041551934</v>
@@ -6443,7 +6443,7 @@
         <v>31.68594971204137</v>
       </c>
       <c r="P40" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q40" t="n">
         <v>2.38792644284783</v>
@@ -6506,7 +6506,7 @@
         <v>34.71631846833595</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.02255666307874404</v>
+        <v>0.022556663078744</v>
       </c>
       <c r="AL40" t="n">
         <v>0.4634146341463415</v>
@@ -6521,7 +6521,7 @@
         <v>241.1141644598076</v>
       </c>
       <c r="AP40" t="n">
-        <v>223.5662634777067</v>
+        <v>223.5662634777066</v>
       </c>
       <c r="AQ40" t="n">
         <v>258.6620654419085</v>
@@ -6588,7 +6588,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N41" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O41" t="n">
         <v>74.98767201170918</v>
@@ -6609,7 +6609,7 @@
         <v>-1.1005743412293</v>
       </c>
       <c r="U41" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2580645161290322</v>
       </c>
       <c r="V41" t="n">
         <v>343.7415442513212</v>
@@ -6627,10 +6627,10 @@
         <v>509.8322228633055</v>
       </c>
       <c r="AA41" t="n">
-        <v>368.3813592683967</v>
+        <v>368.3813592683968</v>
       </c>
       <c r="AB41" t="n">
-        <v>501.7975012825711</v>
+        <v>501.7975012825712</v>
       </c>
       <c r="AC41" t="n">
         <v>120</v>
@@ -6639,7 +6639,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE41" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF41" t="n">
         <v>72.54088005962326</v>
@@ -6660,7 +6660,7 @@
         <v>-1.087848551133999</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.1416666666666667</v>
+        <v>0.1416666666666666</v>
       </c>
       <c r="AM41" t="n">
         <v>343.7415442513212</v>
@@ -6775,7 +6775,7 @@
         <v>358.5836439194787</v>
       </c>
       <c r="Z42" t="n">
-        <v>402.1132776925847</v>
+        <v>402.1132776925848</v>
       </c>
       <c r="AA42" t="n">
         <v>353.8256900743707</v>
@@ -6796,7 +6796,7 @@
         <v>29.75640165697176</v>
       </c>
       <c r="AG42" t="n">
-        <v>29.35926726899195</v>
+        <v>29.35926726899194</v>
       </c>
       <c r="AH42" t="n">
         <v>1.961972865230032</v>
@@ -6811,7 +6811,7 @@
         <v>-1.314785592954324</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.06504065040650407</v>
+        <v>0.065040650406504</v>
       </c>
       <c r="AM42" t="n">
         <v>331.5075848462072</v>
@@ -6893,7 +6893,7 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O43" t="n">
-        <v>24.36537388910131</v>
+        <v>24.36537388910132</v>
       </c>
       <c r="P43" t="n">
         <v>23.10090886896307</v>
@@ -7113,7 +7113,7 @@
         <v>-0.962333824746239</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.06504065040650407</v>
+        <v>0.065040650406504</v>
       </c>
       <c r="AM44" t="n">
         <v>374.3965238054668</v>
@@ -7225,7 +7225,7 @@
         <v>119.4195224010036</v>
       </c>
       <c r="Y45" t="n">
-        <v>112.9405048750319</v>
+        <v>112.940504875032</v>
       </c>
       <c r="Z45" t="n">
         <v>125.8985399269753</v>
@@ -7240,7 +7240,7 @@
         <v>84</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE45" t="n">
         <v>42.60474344487245</v>
@@ -7258,10 +7258,10 @@
         <v>3.775396801176525</v>
       </c>
       <c r="AJ45" t="n">
-        <v>39.1276670915807</v>
+        <v>39.12766709158071</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.02134979489948309</v>
+        <v>0.021349794899483</v>
       </c>
       <c r="AL45" t="n">
         <v>0.3095238095238095</v>
@@ -7364,7 +7364,7 @@
         <v>-1.483902860433661</v>
       </c>
       <c r="U46" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="V46" t="n">
         <v>200.7269200650692</v>
@@ -7415,7 +7415,7 @@
         <v>-1.595428378030136</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.0133333333333333</v>
       </c>
       <c r="AM46" t="n">
         <v>200.7269200650692</v>
@@ -7433,10 +7433,1369 @@
         <v>275.4039618847078</v>
       </c>
       <c r="AR46" t="n">
-        <v>214.7784073506891</v>
+        <v>214.778407350689</v>
       </c>
       <c r="AS46" t="n">
         <v>288.3552723289022</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>291.13</v>
+      </c>
+      <c r="I47" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J47" t="n">
+        <v>35.203144</v>
+      </c>
+      <c r="K47" t="n">
+        <v>67</v>
+      </c>
+      <c r="L47" t="n">
+        <v>63</v>
+      </c>
+      <c r="M47" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N47" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O47" t="n">
+        <v>34.46047008568137</v>
+      </c>
+      <c r="P47" t="n">
+        <v>34.3481020384197</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.033948720383977</v>
+      </c>
+      <c r="R47" t="n">
+        <v>31.87797449812104</v>
+      </c>
+      <c r="S47" t="n">
+        <v>37.37554517842955</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.3651389569833558</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="V47" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="W47" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="X47" t="n">
+        <v>284.9880876085849</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>268.1673316910094</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>301.8088435261603</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>263.630849099461</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>309.0957586256124</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>34.47527925916662</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>34.49936878832081</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.734253280622169</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>32.14202455931072</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>36.73190201255655</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.4196992151989811</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0.6854838709677419</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>285.1105594733079</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>270.7682848425626</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>299.4528341040533</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>265.8145431054996</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>303.7728296438427</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>511.57</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J48" t="n">
+        <v>169.39404</v>
+      </c>
+      <c r="K48" t="n">
+        <v>63</v>
+      </c>
+      <c r="L48" t="n">
+        <v>63</v>
+      </c>
+      <c r="M48" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N48" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="O48" t="n">
+        <v>121.6688400778806</v>
+      </c>
+      <c r="P48" t="n">
+        <v>128.8830220924233</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>33.86558964794703</v>
+      </c>
+      <c r="R48" t="n">
+        <v>76.53961987765331</v>
+      </c>
+      <c r="S48" t="n">
+        <v>166.8465596183402</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.409253475821659</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.9365079365079365</v>
+      </c>
+      <c r="V48" t="n">
+        <v>223.4116149902344</v>
+      </c>
+      <c r="W48" t="n">
+        <v>537.1837570440574</v>
+      </c>
+      <c r="X48" t="n">
+        <v>367.4398970351995</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>265.1658162983995</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>469.7139777719996</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>231.149652030513</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>503.8766100473873</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>108.8740742584979</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>105.5443373806958</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>30.25885474191501</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>75.52037537772701</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>153.1708223936988</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2.000074565203849</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>217.6109399183741</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>537.1837570440574</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>328.7997042606637</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>237.4179629400803</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>420.181445581247</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>228.0715336407356</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>462.5758836289704</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>238.55</v>
+      </c>
+      <c r="I49" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="J49" t="n">
+        <v>31.637932</v>
+      </c>
+      <c r="K49" t="n">
+        <v>67</v>
+      </c>
+      <c r="L49" t="n">
+        <v>63</v>
+      </c>
+      <c r="M49" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N49" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O49" t="n">
+        <v>31.63592970645751</v>
+      </c>
+      <c r="P49" t="n">
+        <v>31.70574133476002</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.401634424074888</v>
+      </c>
+      <c r="R49" t="n">
+        <v>28.91213431684209</v>
+      </c>
+      <c r="S49" t="n">
+        <v>34.92747542249608</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.0008337212035342672</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.4603174603174603</v>
+      </c>
+      <c r="V49" t="n">
+        <v>209.6267186035837</v>
+      </c>
+      <c r="W49" t="n">
+        <v>277.6129046537221</v>
+      </c>
+      <c r="X49" t="n">
+        <v>238.5349099866896</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>220.426586429165</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>256.6432335442142</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>217.9974927489894</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>263.3531646856205</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>31.57608116134857</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>31.76495310222133</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>2.306978518232265</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>28.87192711313345</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>34.70906596802268</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.02681032275013304</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0.4677419354838709</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>209.0483332465051</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>277.6129046537221</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>238.0836519565682</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>220.689033929097</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>255.4782699840395</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>217.6943304330262</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>261.706357398891</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" t="n">
+        <v>63.678333</v>
+      </c>
+      <c r="K50" t="n">
+        <v>34</v>
+      </c>
+      <c r="L50" t="n">
+        <v>63</v>
+      </c>
+      <c r="M50" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N50" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O50" t="n">
+        <v>74.80647690972003</v>
+      </c>
+      <c r="P50" t="n">
+        <v>78.39571411846676</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>9.868637933682905</v>
+      </c>
+      <c r="R50" t="n">
+        <v>61.29707440530581</v>
+      </c>
+      <c r="S50" t="n">
+        <v>83.47290277016327</v>
+      </c>
+      <c r="T50" t="n">
+        <v>-1.127627134007853</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.2698412698412698</v>
+      </c>
+      <c r="V50" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="W50" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="X50" t="n">
+        <v>448.8388614583202</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>389.6270338562227</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>508.0506890604177</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>367.7824464318349</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>500.8374166209796</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>72.46676022926599</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>71.58281178344471</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>7.719909269812946</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>62.34697784364341</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>82.38791304025038</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>-1.13841068879284</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0.1487603305785124</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>434.8005613755959</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>388.4811057567183</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>481.1200169944736</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>374.0818670618605</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>494.3274782415023</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>358.16</v>
+      </c>
+      <c r="I51" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J51" t="n">
+        <v>27.319605</v>
+      </c>
+      <c r="K51" t="n">
+        <v>37</v>
+      </c>
+      <c r="L51" t="n">
+        <v>63</v>
+      </c>
+      <c r="M51" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N51" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O51" t="n">
+        <v>28.96346032916235</v>
+      </c>
+      <c r="P51" t="n">
+        <v>29.20629058470889</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.658874014097456</v>
+      </c>
+      <c r="R51" t="n">
+        <v>26.98642291338911</v>
+      </c>
+      <c r="S51" t="n">
+        <v>31.19926064462159</v>
+      </c>
+      <c r="T51" t="n">
+        <v>-0.9909464583763012</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="V51" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W51" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X51" t="n">
+        <v>379.7109649153184</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>357.9631265905008</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>401.4588032401361</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>353.7920043945313</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>409.022307050989</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>29.73675006002484</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>29.35926726899195</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.966196599893645</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>27.39668848622242</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>32.6446195792587</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>-1.229350645889425</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>389.8487932869257</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>364.07195586232</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>415.6256307115314</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>359.1705860543759</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>427.9709626840815</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>566.98</v>
+      </c>
+      <c r="I52" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>20.617455</v>
+      </c>
+      <c r="K52" t="n">
+        <v>55</v>
+      </c>
+      <c r="L52" t="n">
+        <v>63</v>
+      </c>
+      <c r="M52" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="N52" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O52" t="n">
+        <v>24.30588309459538</v>
+      </c>
+      <c r="P52" t="n">
+        <v>23.10036399147727</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2.68129515973201</v>
+      </c>
+      <c r="R52" t="n">
+        <v>21.74094549005682</v>
+      </c>
+      <c r="S52" t="n">
+        <v>28.57616075407753</v>
+      </c>
+      <c r="T52" t="n">
+        <v>-1.375614348613536</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.01587301587301587</v>
+      </c>
+      <c r="V52" t="n">
+        <v>566.97998046875</v>
+      </c>
+      <c r="W52" t="n">
+        <v>806.0930040147568</v>
+      </c>
+      <c r="X52" t="n">
+        <v>668.4117851013729</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>594.6761682087426</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>742.1474019940031</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>597.8760009765624</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>785.8444207371321</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>26.34200828476493</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>27.45083045228688</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2.905026086314118</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>22.02749090021307</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>29.30748211845921</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>-1.970568633353723</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0.008064516129032258</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>566.97998046875</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>864.3475918629769</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>724.4052278310355</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>644.5170104573972</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>804.2934452046737</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>605.7559997558594</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>805.9557582576283</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="I53" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>23.258333</v>
+      </c>
+      <c r="K53" t="n">
+        <v>67</v>
+      </c>
+      <c r="L53" t="n">
+        <v>63</v>
+      </c>
+      <c r="M53" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N53" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O53" t="n">
+        <v>24.67432185491951</v>
+      </c>
+      <c r="P53" t="n">
+        <v>24.62023780459449</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.213687795692693</v>
+      </c>
+      <c r="R53" t="n">
+        <v>23.21050739722864</v>
+      </c>
+      <c r="S53" t="n">
+        <v>26.50944369222463</v>
+      </c>
+      <c r="T53" t="n">
+        <v>-1.166682947579083</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="V53" t="n">
+        <v>374.8427651926008</v>
+      </c>
+      <c r="W53" t="n">
+        <v>460.5199890136719</v>
+      </c>
+      <c r="X53" t="n">
+        <v>414.5286071626478</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>394.1386521950106</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>434.9185621302851</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>389.9365242734411</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>445.3586540293738</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>26.99875633117543</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>25.23606385982762</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>3.913124346735808</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>23.33877439421367</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>34.02489348800898</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>-0.9558662081095273</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.07258064516129033</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>374.8427651926008</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>583.1248801870332</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>453.5791063637472</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>387.8386173385856</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>519.3195953889089</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>392.0914098227897</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>571.6182105985508</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>25.916128</v>
+      </c>
+      <c r="K54" t="n">
+        <v>67</v>
+      </c>
+      <c r="L54" t="n">
+        <v>23</v>
+      </c>
+      <c r="M54" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="N54" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="O54" t="n">
+        <v>38.52242658096891</v>
+      </c>
+      <c r="P54" t="n">
+        <v>37.7667996252007</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.090005653539248</v>
+      </c>
+      <c r="R54" t="n">
+        <v>36.32885356194415</v>
+      </c>
+      <c r="S54" t="n">
+        <v>41.7612647256361</v>
+      </c>
+      <c r="T54" t="n">
+        <v>-6.031705493055107</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>111.4039503255851</v>
+      </c>
+      <c r="W54" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="X54" t="n">
+        <v>119.4195224010036</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>112.9405048750319</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>125.8985399269753</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>112.6194460420269</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>129.4599206494719</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>25.89235394481071</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>32.69960456214874</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>15.16530049649943</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>3.775396801176525</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>39.1276670915807</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0.00156766133284206</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.3095238095238095</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>80.2662972289132</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>33.25386568976496</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>127.2787287680614</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>11.70373008364723</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>121.2957679839002</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:48:21</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>205.19</v>
+      </c>
+      <c r="I55" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J55" t="n">
+        <v>31.422665</v>
+      </c>
+      <c r="K55" t="n">
+        <v>65</v>
+      </c>
+      <c r="L55" t="n">
+        <v>63</v>
+      </c>
+      <c r="M55" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N55" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O55" t="n">
+        <v>37.96999520523957</v>
+      </c>
+      <c r="P55" t="n">
+        <v>37.12856993383291</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.589118170261171</v>
+      </c>
+      <c r="R55" t="n">
+        <v>32.37856060220855</v>
+      </c>
+      <c r="S55" t="n">
+        <v>44.66816368881537</v>
+      </c>
+      <c r="T55" t="n">
+        <v>-1.426707694665216</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="V55" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="W55" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X55" t="n">
+        <v>247.9440686902144</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>217.977127038409</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>277.9110103420199</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>211.4320007324218</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>291.6831088879644</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>37.86935421942142</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>37.258162206533</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>4.195060680497946</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>32.68376769552187</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>44.06224464883609</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>-1.536733246646675</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>247.2868830528219</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>219.8931368091703</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>274.6806292964735</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>213.4250030517578</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>287.7264575568997</v>
       </c>
     </row>
   </sheetData>
@@ -7683,12 +9042,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7717,19 +9076,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>356.56</v>
+        <v>358.16</v>
       </c>
       <c r="I2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.176828</v>
+        <v>27.319605</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -7738,49 +9097,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.9899741468012</v>
+        <v>28.96346032916235</v>
       </c>
       <c r="P2" t="n">
-        <v>29.21870597964289</v>
+        <v>29.20629058470889</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.658903726109226</v>
+        <v>1.658874014097456</v>
       </c>
       <c r="R2" t="n">
-        <v>26.96842149957094</v>
+        <v>26.98642291338911</v>
       </c>
       <c r="S2" t="n">
-        <v>31.22081491927324</v>
+        <v>31.19926064462159</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.092978524470333</v>
+        <v>-0.9909464583763012</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="V2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="W2" t="n">
-        <v>422.9955833357424</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>380.3484608060317</v>
+        <v>379.7109649153184</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.5836439194787</v>
+        <v>357.9631265905008</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.1132776925847</v>
+        <v>401.4588032401361</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.8256900743707</v>
+        <v>353.7920043945313</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.6170917408649</v>
+        <v>409.022307050989</v>
       </c>
       <c r="AC2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -7789,57 +9148,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.75640165697176</v>
+        <v>29.73675006002484</v>
       </c>
       <c r="AG2" t="n">
         <v>29.35926726899195</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.961972865230032</v>
+        <v>1.966196599893645</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.53833242970753</v>
+        <v>27.39668848622242</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.64955541341467</v>
+        <v>32.6446195792587</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.314785592954324</v>
+        <v>-1.229350645889425</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.06504065040650407</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.7016702785662</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>390.4039897394695</v>
+        <v>389.8487932869257</v>
       </c>
       <c r="AP2" t="n">
-        <v>364.6629057476515</v>
+        <v>364.07195586232</v>
       </c>
       <c r="AQ2" t="n">
-        <v>416.1450737312875</v>
+        <v>415.6256307115314</v>
       </c>
       <c r="AR2" t="n">
-        <v>361.3029214777628</v>
+        <v>359.1705860543759</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.3621670240005</v>
+        <v>427.9709626840815</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7868,19 +9227,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>390.34</v>
+        <v>390.74</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.8</v>
       </c>
       <c r="J3" t="n">
-        <v>23.262217</v>
+        <v>23.258333</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M3" t="n">
         <v>22.31206935670243</v>
@@ -7889,49 +9248,49 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.69716038883682</v>
+        <v>24.67432185491951</v>
       </c>
       <c r="P3" t="n">
-        <v>24.63035674322219</v>
+        <v>24.62023780459449</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.209870578371996</v>
+        <v>1.213687795692693</v>
       </c>
       <c r="R3" t="n">
-        <v>23.20750537293958</v>
+        <v>23.21050739722864</v>
       </c>
       <c r="S3" t="n">
-        <v>26.51801151659729</v>
+        <v>26.50944369222463</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.186030484985995</v>
+        <v>-1.166682947579083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="V3" t="n">
-        <v>374.3965238054668</v>
+        <v>374.8427651926008</v>
       </c>
       <c r="W3" t="n">
-        <v>459.9717509315128</v>
+        <v>460.5199890136719</v>
       </c>
       <c r="X3" t="n">
-        <v>414.418351324682</v>
+        <v>414.5286071626478</v>
       </c>
       <c r="Y3" t="n">
-        <v>394.1167230195999</v>
+        <v>394.1386521950106</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.719979629764</v>
+        <v>434.9185621302851</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.4219401579262</v>
+        <v>389.9365242734411</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.9722332485025</v>
+        <v>445.3586540293738</v>
       </c>
       <c r="AC3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD3" t="n">
         <v>22.31206935670243</v>
@@ -7940,57 +9299,57 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>27.02916627897323</v>
+        <v>26.99875633117543</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.26141292531465</v>
+        <v>25.23606385982762</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.91438935440781</v>
+        <v>3.913124346735808</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.36672861028866</v>
+        <v>23.33877439421367</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34.02773861186433</v>
+        <v>34.02489348800898</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.962333824746239</v>
+        <v>-0.9558662081095273</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.06504065040650407</v>
+        <v>0.07258064516129033</v>
       </c>
       <c r="AM3" t="n">
-        <v>374.3965238054668</v>
+        <v>374.8427651926008</v>
       </c>
       <c r="AN3" t="n">
-        <v>582.4306839010962</v>
+        <v>583.1248801870332</v>
       </c>
       <c r="AO3" t="n">
-        <v>453.5494101611708</v>
+        <v>453.5791063637472</v>
       </c>
       <c r="AP3" t="n">
-        <v>387.8659567942078</v>
+        <v>387.8386173385856</v>
       </c>
       <c r="AQ3" t="n">
-        <v>519.2328635281339</v>
+        <v>519.3195953889089</v>
       </c>
       <c r="AR3" t="n">
-        <v>392.0937060806437</v>
+        <v>392.0914098227897</v>
       </c>
       <c r="AS3" t="n">
-        <v>570.9854539070835</v>
+        <v>571.6182105985508</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8019,129 +9378,129 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>568.4299999999999</v>
+        <v>566.98</v>
       </c>
       <c r="I4" t="n">
-        <v>27.51</v>
+        <v>27.5</v>
       </c>
       <c r="J4" t="n">
-        <v>20.662668</v>
+        <v>20.617455</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M4" t="n">
-        <v>20.67018155184659</v>
+        <v>20.61745383522727</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.36537388910131</v>
+        <v>24.30588309459538</v>
       </c>
       <c r="P4" t="n">
-        <v>23.10090886896307</v>
+        <v>23.10036399147727</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.660935905533687</v>
+        <v>2.68129515973201</v>
       </c>
       <c r="R4" t="n">
-        <v>21.78258123224432</v>
+        <v>21.74094549005682</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57799154893039</v>
+        <v>28.57616075407753</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.391505102171443</v>
+        <v>-1.375614348613536</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.01587301587301587</v>
       </c>
       <c r="V4" t="n">
-        <v>568.6366944912997</v>
+        <v>566.97998046875</v>
       </c>
       <c r="W4" t="n">
-        <v>806.3861287434895</v>
+        <v>806.0930040147568</v>
       </c>
       <c r="X4" t="n">
-        <v>670.2914356891772</v>
+        <v>668.4117851013729</v>
       </c>
       <c r="Y4" t="n">
-        <v>597.0890889279455</v>
+        <v>594.6761682087426</v>
       </c>
       <c r="Z4" t="n">
-        <v>743.493782450409</v>
+        <v>742.1474019940031</v>
       </c>
       <c r="AA4" t="n">
-        <v>599.2388096990412</v>
+        <v>597.8760009765624</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.1805475110751</v>
+        <v>785.8444207371321</v>
       </c>
       <c r="AC4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.67018155184659</v>
+        <v>20.61745383522727</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.3885493778506</v>
+        <v>26.34200828476493</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.45253236915975</v>
+        <v>27.45083045228688</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.870114189878805</v>
+        <v>2.905026086314118</v>
       </c>
       <c r="AI4" t="n">
-        <v>22.09650923295455</v>
+        <v>22.02749090021307</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.3091457033941</v>
+        <v>29.30748211845921</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.995001243519298</v>
+        <v>-1.970568633353723</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.008064516129032258</v>
       </c>
       <c r="AM4" t="n">
-        <v>568.6366944912997</v>
+        <v>566.97998046875</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.6619000781998</v>
+        <v>864.3475918629769</v>
       </c>
       <c r="AO4" t="n">
-        <v>725.94899338467</v>
+        <v>724.4052278310355</v>
       </c>
       <c r="AP4" t="n">
-        <v>646.9921520211041</v>
+        <v>644.5170104573972</v>
       </c>
       <c r="AQ4" t="n">
-        <v>804.905834748236</v>
+        <v>804.2934452046737</v>
       </c>
       <c r="AR4" t="n">
-        <v>607.8749689985796</v>
+        <v>605.7559997558594</v>
       </c>
       <c r="AS4" t="n">
-        <v>806.2945983003717</v>
+        <v>805.9557582576283</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8170,19 +9529,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>241.51</v>
+        <v>238.55</v>
       </c>
       <c r="I5" t="n">
-        <v>7.63</v>
+        <v>7.54</v>
       </c>
       <c r="J5" t="n">
-        <v>31.652685</v>
+        <v>31.637932</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -8191,49 +9550,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.68594971204137</v>
+        <v>31.63592970645751</v>
       </c>
       <c r="P5" t="n">
-        <v>31.71949797269831</v>
+        <v>31.70574133476002</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38792644284783</v>
+        <v>2.401634424074888</v>
       </c>
       <c r="R5" t="n">
-        <v>28.95578722242199</v>
+        <v>28.91213431684209</v>
       </c>
       <c r="S5" t="n">
-        <v>34.93654088827689</v>
+        <v>34.92747542249608</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0139303755109381</v>
+        <v>0.0008337212035342672</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4603174603174603</v>
       </c>
       <c r="V5" t="n">
-        <v>212.1288942898334</v>
+        <v>209.6267186035837</v>
       </c>
       <c r="W5" t="n">
-        <v>280.9265865395092</v>
+        <v>277.6129046537221</v>
       </c>
       <c r="X5" t="n">
-        <v>241.7637963028756</v>
+        <v>238.5349099866896</v>
       </c>
       <c r="Y5" t="n">
-        <v>223.5439175439467</v>
+        <v>220.426586429165</v>
       </c>
       <c r="Z5" t="n">
-        <v>259.9836750618046</v>
+        <v>256.6432335442142</v>
       </c>
       <c r="AA5" t="n">
-        <v>220.9326565070797</v>
+        <v>217.9974927489894</v>
       </c>
       <c r="AB5" t="n">
-        <v>266.5658069775527</v>
+        <v>263.3531646856205</v>
       </c>
       <c r="AC5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -8242,57 +9601,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.60080792395906</v>
+        <v>31.57608116134857</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.79665159380607</v>
+        <v>31.76495310222133</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.299855960956872</v>
+        <v>2.306978518232265</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.89175755032901</v>
+        <v>28.87192711313345</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.71631846833595</v>
+        <v>34.70906596802268</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02255666307874404</v>
+        <v>0.02681032275013304</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="AM5" t="n">
-        <v>211.5436051287578</v>
+        <v>209.0483332465051</v>
       </c>
       <c r="AN5" t="n">
-        <v>280.9265865395092</v>
+        <v>277.6129046537221</v>
       </c>
       <c r="AO5" t="n">
-        <v>241.1141644598076</v>
+        <v>238.0836519565682</v>
       </c>
       <c r="AP5" t="n">
-        <v>223.5662634777067</v>
+        <v>220.689033929097</v>
       </c>
       <c r="AQ5" t="n">
-        <v>258.6620654419085</v>
+        <v>255.4782699840395</v>
       </c>
       <c r="AR5" t="n">
-        <v>220.4441101090104</v>
+        <v>217.6943304330262</v>
       </c>
       <c r="AS5" t="n">
-        <v>264.8855099134033</v>
+        <v>261.706357398891</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8321,19 +9680,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>295.63</v>
+        <v>291.13</v>
       </c>
       <c r="I6" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
       <c r="J6" t="n">
-        <v>35.83394</v>
+        <v>35.203144</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -8342,49 +9701,49 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.44780406604713</v>
+        <v>34.46047008568137</v>
       </c>
       <c r="P6" t="n">
-        <v>34.32974706722212</v>
+        <v>34.3481020384197</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.04804627672053</v>
+        <v>2.033948720383977</v>
       </c>
       <c r="R6" t="n">
-        <v>31.86556948891169</v>
+        <v>31.87797449812104</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38147763305368</v>
+        <v>37.37554517842955</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6768088932894814</v>
+        <v>0.3651389569833558</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="V6" t="n">
-        <v>257.5566506687599</v>
+        <v>258.1810304279569</v>
       </c>
       <c r="W6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.5816102847638</v>
       </c>
       <c r="X6" t="n">
-        <v>284.1943835448889</v>
+        <v>284.9880876085849</v>
       </c>
       <c r="Y6" t="n">
-        <v>267.2980017619445</v>
+        <v>268.1673316910094</v>
       </c>
       <c r="Z6" t="n">
-        <v>301.0907653278332</v>
+        <v>301.8088435261603</v>
       </c>
       <c r="AA6" t="n">
-        <v>262.8909482835215</v>
+        <v>263.630849099461</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.3971904726929</v>
+        <v>309.0957586256124</v>
       </c>
       <c r="AC6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -8393,57 +9752,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.46901516124925</v>
+        <v>34.47527925916662</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.44810312005538</v>
+        <v>34.49936878832081</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.739937261532854</v>
+        <v>1.734253280622169</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13645490815368</v>
+        <v>32.14202455931072</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.7359232966446</v>
+        <v>36.73190201255655</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.7844678477362328</v>
+        <v>0.4196992151989811</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7479674796747967</v>
+        <v>0.6854838709677419</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.5566506687599</v>
+        <v>258.1810304279569</v>
       </c>
       <c r="AN6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.5816102847638</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.3693750803063</v>
+        <v>285.1105594733079</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.0148926726603</v>
+        <v>270.7682848425626</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.7238574879523</v>
+        <v>299.4528341040533</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.1257529922678</v>
+        <v>265.8145431054996</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.071367197318</v>
+        <v>303.7728296438427</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8472,19 +9831,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>204.87</v>
+        <v>205.19</v>
       </c>
       <c r="I7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.325687</v>
+        <v>31.422665</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M7" t="n">
         <v>30.69218961239591</v>
@@ -8493,49 +9852,49 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>38.0755973053453</v>
+        <v>37.96999520523957</v>
       </c>
       <c r="P7" t="n">
-        <v>37.14387699049346</v>
+        <v>37.12856993383291</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.548754831143522</v>
+        <v>4.589118170261171</v>
       </c>
       <c r="R7" t="n">
-        <v>32.58269609389954</v>
+        <v>32.37856060220855</v>
       </c>
       <c r="S7" t="n">
-        <v>44.72591882822464</v>
+        <v>44.66816368881537</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.483902860433661</v>
+        <v>-1.426707694665216</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="V7" t="n">
-        <v>200.7269200650692</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="W7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>249.0144063769583</v>
+        <v>247.9440686902144</v>
       </c>
       <c r="Y7" t="n">
-        <v>219.2655497812797</v>
+        <v>217.977127038409</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.7632629726369</v>
+        <v>277.9110103420199</v>
       </c>
       <c r="AA7" t="n">
-        <v>213.090832454103</v>
+        <v>211.4320007324218</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.5075091365892</v>
+        <v>291.6831088879644</v>
       </c>
       <c r="AC7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AD7" t="n">
         <v>30.69218961239591</v>
@@ -8544,57 +9903,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.95531007569792</v>
+        <v>37.86935421942142</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.2755089584662</v>
+        <v>37.258162206533</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.155387460190137</v>
+        <v>4.195060680497946</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.8407350689127</v>
+        <v>32.68376769552187</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.0910202337771</v>
+        <v>44.06224464883609</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.595428378030136</v>
+        <v>-1.536733246646675</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="AM7" t="n">
-        <v>200.7269200650692</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>248.2277278950644</v>
+        <v>247.2868830528219</v>
       </c>
       <c r="AP7" t="n">
-        <v>221.0514939054209</v>
+        <v>219.8931368091703</v>
       </c>
       <c r="AQ7" t="n">
-        <v>275.4039618847078</v>
+        <v>274.6806292964735</v>
       </c>
       <c r="AR7" t="n">
-        <v>214.7784073506891</v>
+        <v>213.4250030517578</v>
       </c>
       <c r="AS7" t="n">
-        <v>288.3552723289022</v>
+        <v>287.7264575568997</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8623,19 +9982,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>488.45</v>
+        <v>511.57</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="J8" t="n">
-        <v>163.9094</v>
+        <v>169.39404</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M8" t="n">
         <v>73.97735595703125</v>
@@ -8644,49 +10003,49 @@
         <v>177.8754162397541</v>
       </c>
       <c r="O8" t="n">
-        <v>120.9259524782684</v>
+        <v>121.6688400778806</v>
       </c>
       <c r="P8" t="n">
-        <v>128.047168659714</v>
+        <v>128.8830220924233</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.62054285667178</v>
+        <v>33.86558964794703</v>
       </c>
       <c r="R8" t="n">
-        <v>76.51131799086085</v>
+        <v>76.53961987765331</v>
       </c>
       <c r="S8" t="n">
-        <v>164.9360701764216</v>
+        <v>166.8465596183402</v>
       </c>
       <c r="T8" t="n">
-        <v>1.278487611130344</v>
+        <v>1.409253475821659</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8870967741935484</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="V8" t="n">
-        <v>220.4525207519531</v>
+        <v>223.4116149902344</v>
       </c>
       <c r="W8" t="n">
-        <v>530.0687403944672</v>
+        <v>537.1837570440574</v>
       </c>
       <c r="X8" t="n">
-        <v>360.3593383852397</v>
+        <v>367.4398970351995</v>
       </c>
       <c r="Y8" t="n">
-        <v>260.1701206723578</v>
+        <v>265.1658162983995</v>
       </c>
       <c r="Z8" t="n">
-        <v>460.5485560981215</v>
+        <v>469.7139777719996</v>
       </c>
       <c r="AA8" t="n">
-        <v>228.0037276127653</v>
+        <v>231.149652030513</v>
       </c>
       <c r="AB8" t="n">
-        <v>491.5094891257364</v>
+        <v>503.8766100473873</v>
       </c>
       <c r="AC8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -8695,57 +10054,57 @@
         <v>177.8754162397541</v>
       </c>
       <c r="AF8" t="n">
-        <v>108.3955881040642</v>
+        <v>108.8740742584979</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.4975387498076</v>
+        <v>105.5443373806958</v>
       </c>
       <c r="AH8" t="n">
-        <v>29.90787214180765</v>
+        <v>30.25885474191501</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51924334831958</v>
+        <v>75.52037537772701</v>
       </c>
       <c r="AJ8" t="n">
-        <v>152.4137723328637</v>
+        <v>153.1708223936988</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.856160533010106</v>
+        <v>2.000074565203849</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.943089430894309</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="AM8" t="n">
-        <v>214.728675813495</v>
+        <v>217.6109399183741</v>
       </c>
       <c r="AN8" t="n">
-        <v>530.0687403944672</v>
+        <v>537.1837570440574</v>
       </c>
       <c r="AO8" t="n">
-        <v>323.0188525501114</v>
+        <v>328.7997042606637</v>
       </c>
       <c r="AP8" t="n">
-        <v>233.8933935675246</v>
+        <v>237.4179629400803</v>
       </c>
       <c r="AQ8" t="n">
-        <v>412.1443115326982</v>
+        <v>420.181445581247</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.0473451779923</v>
+        <v>228.0715336407356</v>
       </c>
       <c r="AS8" t="n">
-        <v>454.193041551934</v>
+        <v>462.5758836289704</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8774,19 +10133,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>385.57</v>
+        <v>382.07</v>
       </c>
       <c r="I9" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>64.15474</v>
+        <v>63.678333</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -8795,49 +10154,49 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>74.98767201170918</v>
+        <v>74.80647690972003</v>
       </c>
       <c r="P9" t="n">
-        <v>78.71540210865163</v>
+        <v>78.39571411846676</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.842980710970602</v>
+        <v>9.868637933682905</v>
       </c>
       <c r="R9" t="n">
-        <v>61.29473531920079</v>
+        <v>61.29707440530581</v>
       </c>
       <c r="S9" t="n">
-        <v>83.49376061274063</v>
+        <v>83.47290277016327</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1005743412293</v>
+        <v>-1.127627134007853</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2698412698412698</v>
       </c>
       <c r="V9" t="n">
-        <v>343.7415442513212</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="W9" t="n">
-        <v>564.1785076059562</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="X9" t="n">
-        <v>450.6759087903721</v>
+        <v>448.8388614583202</v>
       </c>
       <c r="Y9" t="n">
-        <v>391.5195947174388</v>
+        <v>389.6270338562227</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.8322228633055</v>
+        <v>508.0506890604177</v>
       </c>
       <c r="AA9" t="n">
-        <v>368.3813592683967</v>
+        <v>367.7824464318349</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.7975012825711</v>
+        <v>500.8374166209796</v>
       </c>
       <c r="AC9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -8846,57 +10205,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.54088005962326</v>
+        <v>72.46676022926599</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.70125773367891</v>
+        <v>71.58281178344471</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.708922396303556</v>
+        <v>7.719909269812946</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.32689989472924</v>
+        <v>62.34697784364341</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.39005759910303</v>
+        <v>82.38791304025038</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.087848551133999</v>
+        <v>-1.13841068879284</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1416666666666667</v>
+        <v>0.1487603305785124</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.7415442513212</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="AN9" t="n">
-        <v>564.1785076059562</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="AO9" t="n">
-        <v>435.9706891583358</v>
+        <v>434.8005613755959</v>
       </c>
       <c r="AP9" t="n">
-        <v>389.6400655565515</v>
+        <v>388.4811057567183</v>
       </c>
       <c r="AQ9" t="n">
-        <v>482.3013127601201</v>
+        <v>481.1200169944736</v>
       </c>
       <c r="AR9" t="n">
-        <v>374.5846683673227</v>
+        <v>374.0818670618605</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.1642461706092</v>
+        <v>494.3274782415023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-12 05:00:20</t>
+          <t>2026-06-13 02:48:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8925,13 +10284,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>81.27</v>
+        <v>80.34</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>26.21613</v>
+        <v>25.916128</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
@@ -8961,7 +10320,7 @@
         <v>41.7612647256361</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.888164254546028</v>
+        <v>-6.031705493055107</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -9012,7 +10371,7 @@
         <v>39.1276670915807</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02134979489948309</v>
+        <v>0.00156766133284206</v>
       </c>
       <c r="AL10" t="n">
         <v>0.3095238095238095</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS55"/>
+  <dimension ref="A1:AS64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7530,7 +7530,7 @@
         <v>268.1673316910094</v>
       </c>
       <c r="Z47" t="n">
-        <v>301.8088435261603</v>
+        <v>301.8088435261604</v>
       </c>
       <c r="AA47" t="n">
         <v>263.630849099461</v>
@@ -7563,7 +7563,7 @@
         <v>36.73190201255655</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.4196992151989811</v>
+        <v>0.419699215198981</v>
       </c>
       <c r="AL47" t="n">
         <v>0.6854838709677419</v>
@@ -7666,7 +7666,7 @@
         <v>1.409253475821659</v>
       </c>
       <c r="U48" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.9365079365079364</v>
       </c>
       <c r="V48" t="n">
         <v>223.4116149902344</v>
@@ -7729,7 +7729,7 @@
         <v>328.7997042606637</v>
       </c>
       <c r="AP48" t="n">
-        <v>237.4179629400803</v>
+        <v>237.4179629400804</v>
       </c>
       <c r="AQ48" t="n">
         <v>420.181445581247</v>
@@ -7814,7 +7814,7 @@
         <v>34.92747542249608</v>
       </c>
       <c r="T49" t="n">
-        <v>0.0008337212035342672</v>
+        <v>0.0008337212035342</v>
       </c>
       <c r="U49" t="n">
         <v>0.4603174603174603</v>
@@ -7865,7 +7865,7 @@
         <v>34.70906596802268</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.02681032275013304</v>
+        <v>0.026810322750133</v>
       </c>
       <c r="AL49" t="n">
         <v>0.4677419354838709</v>
@@ -7880,7 +7880,7 @@
         <v>238.0836519565682</v>
       </c>
       <c r="AP49" t="n">
-        <v>220.689033929097</v>
+        <v>220.6890339290969</v>
       </c>
       <c r="AQ49" t="n">
         <v>255.4782699840395</v>
@@ -7947,7 +7947,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N50" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O50" t="n">
         <v>74.80647690972003</v>
@@ -7965,7 +7965,7 @@
         <v>83.47290277016327</v>
       </c>
       <c r="T50" t="n">
-        <v>-1.127627134007853</v>
+        <v>-1.127627134007852</v>
       </c>
       <c r="U50" t="n">
         <v>0.2698412698412698</v>
@@ -7989,7 +7989,7 @@
         <v>367.7824464318349</v>
       </c>
       <c r="AB50" t="n">
-        <v>500.8374166209796</v>
+        <v>500.8374166209797</v>
       </c>
       <c r="AC50" t="n">
         <v>121</v>
@@ -7998,7 +7998,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE50" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF50" t="n">
         <v>72.46676022926599</v>
@@ -8110,7 +8110,7 @@
         <v>1.658874014097456</v>
       </c>
       <c r="R51" t="n">
-        <v>26.98642291338911</v>
+        <v>26.98642291338912</v>
       </c>
       <c r="S51" t="n">
         <v>31.19926064462159</v>
@@ -8119,7 +8119,7 @@
         <v>-0.9909464583763012</v>
       </c>
       <c r="U51" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1904761904761904</v>
       </c>
       <c r="V51" t="n">
         <v>331.2549113821476</v>
@@ -8155,7 +8155,7 @@
         <v>29.73675006002484</v>
       </c>
       <c r="AG51" t="n">
-        <v>29.35926726899195</v>
+        <v>29.35926726899194</v>
       </c>
       <c r="AH51" t="n">
         <v>1.966196599893645</v>
@@ -8191,7 +8191,7 @@
         <v>359.1705860543759</v>
       </c>
       <c r="AS51" t="n">
-        <v>427.9709626840815</v>
+        <v>427.9709626840816</v>
       </c>
     </row>
     <row r="52">
@@ -8246,7 +8246,7 @@
         <v>63</v>
       </c>
       <c r="M52" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="N52" t="n">
         <v>29.31247287326389</v>
@@ -8255,7 +8255,7 @@
         <v>24.30588309459538</v>
       </c>
       <c r="P52" t="n">
-        <v>23.10036399147727</v>
+        <v>23.10036399147728</v>
       </c>
       <c r="Q52" t="n">
         <v>2.68129515973201</v>
@@ -8270,7 +8270,7 @@
         <v>-1.375614348613536</v>
       </c>
       <c r="U52" t="n">
-        <v>0.01587301587301587</v>
+        <v>0.0158730158730158</v>
       </c>
       <c r="V52" t="n">
         <v>566.97998046875</v>
@@ -8297,7 +8297,7 @@
         <v>124</v>
       </c>
       <c r="AD52" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="AE52" t="n">
         <v>31.43082152229007</v>
@@ -8321,7 +8321,7 @@
         <v>-1.970568633353723</v>
       </c>
       <c r="AL52" t="n">
-        <v>0.008064516129032258</v>
+        <v>0.008064516129032201</v>
       </c>
       <c r="AM52" t="n">
         <v>566.97998046875</v>
@@ -8409,7 +8409,7 @@
         <v>24.62023780459449</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.213687795692693</v>
+        <v>1.213687795692694</v>
       </c>
       <c r="R53" t="n">
         <v>23.21050739722864</v>
@@ -8469,10 +8469,10 @@
         <v>34.02489348800898</v>
       </c>
       <c r="AK53" t="n">
-        <v>-0.9558662081095273</v>
+        <v>-0.9558662081095272</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.07258064516129033</v>
+        <v>0.0725806451612903</v>
       </c>
       <c r="AM53" t="n">
         <v>374.8427651926008</v>
@@ -8584,7 +8584,7 @@
         <v>119.4195224010036</v>
       </c>
       <c r="Y54" t="n">
-        <v>112.9405048750319</v>
+        <v>112.940504875032</v>
       </c>
       <c r="Z54" t="n">
         <v>125.8985399269753</v>
@@ -8599,7 +8599,7 @@
         <v>84</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE54" t="n">
         <v>42.60474344487245</v>
@@ -8617,10 +8617,10 @@
         <v>3.775396801176525</v>
       </c>
       <c r="AJ54" t="n">
-        <v>39.1276670915807</v>
+        <v>39.12766709158071</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.00156766133284206</v>
+        <v>0.001567661332842</v>
       </c>
       <c r="AL54" t="n">
         <v>0.3095238095238095</v>
@@ -8723,7 +8723,7 @@
         <v>-1.426707694665216</v>
       </c>
       <c r="U55" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.06349206349206341</v>
       </c>
       <c r="V55" t="n">
         <v>200.4199981689453</v>
@@ -8735,7 +8735,7 @@
         <v>247.9440686902144</v>
       </c>
       <c r="Y55" t="n">
-        <v>217.977127038409</v>
+        <v>217.9771270384089</v>
       </c>
       <c r="Z55" t="n">
         <v>277.9110103420199</v>
@@ -8774,7 +8774,7 @@
         <v>-1.536733246646675</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.0526315789473684</v>
       </c>
       <c r="AM55" t="n">
         <v>200.4199981689453</v>
@@ -8796,6 +8796,1365 @@
       </c>
       <c r="AS55" t="n">
         <v>287.7264575568997</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>298.84</v>
+      </c>
+      <c r="I56" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J56" t="n">
+        <v>36.135426</v>
+      </c>
+      <c r="K56" t="n">
+        <v>67</v>
+      </c>
+      <c r="L56" t="n">
+        <v>62</v>
+      </c>
+      <c r="M56" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N56" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O56" t="n">
+        <v>34.56477649129591</v>
+      </c>
+      <c r="P56" t="n">
+        <v>34.48382353042415</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.01457934377709</v>
+      </c>
+      <c r="R56" t="n">
+        <v>31.86556948891169</v>
+      </c>
+      <c r="S56" t="n">
+        <v>37.38147763305368</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.7796414241790633</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0.7258064516129032</v>
+      </c>
+      <c r="V56" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="W56" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="X56" t="n">
+        <v>285.8507015830172</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>269.1901304099806</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>302.5112727560537</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>263.5282596732997</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>309.144820025354</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>34.43549234620956</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.720621352838539</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>36.6958458621764</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0.9879766114642456</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.7786885245901639</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>284.781521703153</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>270.5519831151783</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>299.0110602911278</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>265.7224210753621</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>303.4746452801988</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>524.4299999999999</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J57" t="n">
+        <v>174.22923</v>
+      </c>
+      <c r="K57" t="n">
+        <v>63</v>
+      </c>
+      <c r="L57" t="n">
+        <v>62</v>
+      </c>
+      <c r="M57" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N57" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="O57" t="n">
+        <v>124.0132388334195</v>
+      </c>
+      <c r="P57" t="n">
+        <v>132.5094316590507</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>33.57727744203408</v>
+      </c>
+      <c r="R57" t="n">
+        <v>76.95094500847583</v>
+      </c>
+      <c r="S57" t="n">
+        <v>167.680658059042</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1.495534926953817</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V57" t="n">
+        <v>222.671841430664</v>
+      </c>
+      <c r="W57" t="n">
+        <v>535.4050028816598</v>
+      </c>
+      <c r="X57" t="n">
+        <v>373.2798488885927</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>272.2122437880701</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>474.3474539891153</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>231.6223444755122</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>504.7187807577164</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>177.8754162397541</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>109.5855964601589</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>105.8743819814597</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>31.00646812517777</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>155.642626152664</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>2.084843500358216</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.9918032786885246</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>216.8903738921543</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>535.4050028816598</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>329.8526453450783</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>236.5231762882932</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>423.1821144018634</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>227.3095150699255</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>468.4843047195184</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>247.55</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J58" t="n">
+        <v>31.859716</v>
+      </c>
+      <c r="K58" t="n">
+        <v>67</v>
+      </c>
+      <c r="L58" t="n">
+        <v>62</v>
+      </c>
+      <c r="M58" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N58" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O58" t="n">
+        <v>31.66337883541885</v>
+      </c>
+      <c r="P58" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.411037645956832</v>
+      </c>
+      <c r="R58" t="n">
+        <v>28.90795038667516</v>
+      </c>
+      <c r="S58" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.08143264163062355</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="V58" t="n">
+        <v>216.0211675795551</v>
+      </c>
+      <c r="W58" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="X58" t="n">
+        <v>246.0244535512045</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>227.2906910421199</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>264.758216060289</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>224.614774504466</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>271.4569227019115</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>31.56496108675321</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>31.82655590002617</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>2.332531065666415</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>28.86711905294752</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.1263669828819943</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.5081967213114754</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>215.4251391678176</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>245.2597476440724</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>227.1359812638444</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>263.3835140243004</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>224.2975150414022</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>269.8021464264044</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="I59" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J59" t="n">
+        <v>62.895523</v>
+      </c>
+      <c r="K59" t="n">
+        <v>34</v>
+      </c>
+      <c r="L59" t="n">
+        <v>62</v>
+      </c>
+      <c r="M59" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N59" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O59" t="n">
+        <v>74.99901067785036</v>
+      </c>
+      <c r="P59" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>9.829003352317653</v>
+      </c>
+      <c r="R59" t="n">
+        <v>61.29473531920079</v>
+      </c>
+      <c r="S59" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T59" t="n">
+        <v>-1.231405387098214</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="V59" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="W59" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X59" t="n">
+        <v>452.2440343874377</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>392.9751441729622</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>511.5129246019132</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>369.6072539747808</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>503.467376494826</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>72.38999481009056</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>71.47694073882994</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>7.734558769582204</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>62.37563283819902</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>82.37543771606209</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>-1.227538905959263</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>436.511668704846</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>389.8722793242654</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>483.1510580854268</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>376.1250660143401</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>496.7238894278544</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>370.73</v>
+      </c>
+      <c r="I60" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J60" t="n">
+        <v>28.278416</v>
+      </c>
+      <c r="K60" t="n">
+        <v>37</v>
+      </c>
+      <c r="L60" t="n">
+        <v>63</v>
+      </c>
+      <c r="M60" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N60" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O60" t="n">
+        <v>28.95534563673466</v>
+      </c>
+      <c r="P60" t="n">
+        <v>29.20629058470889</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.661984146055882</v>
+      </c>
+      <c r="R60" t="n">
+        <v>26.98642291338911</v>
+      </c>
+      <c r="S60" t="n">
+        <v>31.19926064462159</v>
+      </c>
+      <c r="T60" t="n">
+        <v>-0.4073021023341909</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.3650793650793651</v>
+      </c>
+      <c r="V60" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W60" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X60" t="n">
+        <v>379.6045812975913</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>357.8159691427987</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>401.3931934523839</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>353.7920043945313</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>409.022307050989</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>29.7015665992692</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>29.35392727477236</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.982236590562688</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>27.37684176855299</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>-0.7179519367389001</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>389.3875381164191</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>363.4004164141423</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>415.374659818696</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>358.9103955857297</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>428.0356714698664</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>594.75</v>
+      </c>
+      <c r="I61" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="J61" t="n">
+        <v>21.643013</v>
+      </c>
+      <c r="K61" t="n">
+        <v>55</v>
+      </c>
+      <c r="L61" t="n">
+        <v>63</v>
+      </c>
+      <c r="M61" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="N61" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O61" t="n">
+        <v>24.14703609047108</v>
+      </c>
+      <c r="P61" t="n">
+        <v>22.83439782387452</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.688383984358619</v>
+      </c>
+      <c r="R61" t="n">
+        <v>21.59094504616477</v>
+      </c>
+      <c r="S61" t="n">
+        <v>28.57616075407753</v>
+      </c>
+      <c r="T61" t="n">
+        <v>-0.931423154221949</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.126984126984127</v>
+      </c>
+      <c r="V61" t="n">
+        <v>566.5676313920454</v>
+      </c>
+      <c r="W61" t="n">
+        <v>805.5067545572916</v>
+      </c>
+      <c r="X61" t="n">
+        <v>663.5605517661452</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>589.6837598759703</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>737.4373436563201</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>593.319169868608</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>785.2728975220506</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>26.20387509204501</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>27.25952256560009</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>2.949849808349889</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>21.94152743252841</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>29.3091457033941</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>-1.546133663868231</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0.06504065040650407</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>566.5676313920454</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>863.718975432531</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>720.082487529397</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>639.020614795942</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>801.1443602628519</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>602.9531738458807</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>805.4153239292699</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>392.565</v>
+      </c>
+      <c r="I62" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J62" t="n">
+        <v>23.38088</v>
+      </c>
+      <c r="K62" t="n">
+        <v>67</v>
+      </c>
+      <c r="L62" t="n">
+        <v>62</v>
+      </c>
+      <c r="M62" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N62" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O62" t="n">
+        <v>24.64291408588499</v>
+      </c>
+      <c r="P62" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1.233164335900355</v>
+      </c>
+      <c r="R62" t="n">
+        <v>23.20750537293958</v>
+      </c>
+      <c r="S62" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T62" t="n">
+        <v>-1.023411113299477</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.2419354838709677</v>
+      </c>
+      <c r="V62" t="n">
+        <v>374.6196444990338</v>
+      </c>
+      <c r="W62" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X62" t="n">
+        <v>413.754527502009</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>393.0496983022421</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>434.459356701776</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>389.6540152116556</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>445.2374133636685</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>26.80080619782125</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>25.13133150998915</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>3.804583769963939</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>23.33389654392149</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>34.03058373571968</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>-0.8988962800137422</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0.1229508196721311</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>374.6196444990338</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>582.7777820440647</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>449.9855360614187</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>386.1065745637241</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>513.8644975591133</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>391.7761229724418</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>571.3735009227335</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>78.5899</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>25.35158</v>
+      </c>
+      <c r="K63" t="n">
+        <v>67</v>
+      </c>
+      <c r="L63" t="n">
+        <v>21</v>
+      </c>
+      <c r="M63" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="N63" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="O63" t="n">
+        <v>38.62337672102367</v>
+      </c>
+      <c r="P63" t="n">
+        <v>38.00395317228413</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.163128444509888</v>
+      </c>
+      <c r="R63" t="n">
+        <v>36.29248999795422</v>
+      </c>
+      <c r="S63" t="n">
+        <v>42.00790465584855</v>
+      </c>
+      <c r="T63" t="n">
+        <v>-6.135464010335611</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>111.4039503255851</v>
+      </c>
+      <c r="W63" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="X63" t="n">
+        <v>119.7324678351734</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>113.0267696571927</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>126.438166013154</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>112.5067189936581</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>130.2245044331305</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>81</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>26.70532199408146</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>32.86956666486535</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>14.82814270080998</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>3.77276523370193</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>39.13833859409738</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>-0.09129545226237379</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0.2839506172839506</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>82.78649818165253</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>36.8192558091416</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>128.7537405541634</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>11.69557222447598</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>121.3288496417019</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:12:27</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>209.58</v>
+      </c>
+      <c r="I64" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J64" t="n">
+        <v>32.144173</v>
+      </c>
+      <c r="K64" t="n">
+        <v>65</v>
+      </c>
+      <c r="L64" t="n">
+        <v>62</v>
+      </c>
+      <c r="M64" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N64" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O64" t="n">
+        <v>37.89823191285868</v>
+      </c>
+      <c r="P64" t="n">
+        <v>36.64081495635364</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>4.684825278144428</v>
+      </c>
+      <c r="R64" t="n">
+        <v>32.12436319675416</v>
+      </c>
+      <c r="S64" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T64" t="n">
+        <v>-1.228233407060542</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0.1129032258064516</v>
+      </c>
+      <c r="V64" t="n">
+        <v>200.1130762728213</v>
+      </c>
+      <c r="W64" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="X64" t="n">
+        <v>247.0964720718386</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>216.5514112583369</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>277.6415328853403</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>209.4508480428371</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>291.6129907600247</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>37.79444166572497</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>37.2408154545998</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>4.218896779690089</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>32.46799439785126</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>44.03346906389508</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>-1.339276346585569</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>200.1130762728213</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>246.4197596605268</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>218.9125526569474</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>273.9269666641061</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>211.6913234739902</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>287.0982182965959</v>
       </c>
     </row>
   </sheetData>
@@ -9042,12 +10401,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9076,13 +10435,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>358.16</v>
+        <v>370.73</v>
       </c>
       <c r="I2" t="n">
         <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.319605</v>
+        <v>28.278416</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -9097,13 +10456,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.96346032916235</v>
+        <v>28.95534563673466</v>
       </c>
       <c r="P2" t="n">
         <v>29.20629058470889</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.658874014097456</v>
+        <v>1.661984146055882</v>
       </c>
       <c r="R2" t="n">
         <v>26.98642291338911</v>
@@ -9112,10 +10471,10 @@
         <v>31.19926064462159</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9909464583763012</v>
+        <v>-0.4073021023341909</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.3650793650793651</v>
       </c>
       <c r="V2" t="n">
         <v>331.2549113821476</v>
@@ -9124,13 +10483,13 @@
         <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>379.7109649153184</v>
+        <v>379.6045812975913</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.9631265905008</v>
+        <v>357.8159691427987</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.4588032401361</v>
+        <v>401.3931934523839</v>
       </c>
       <c r="AA2" t="n">
         <v>353.7920043945313</v>
@@ -9139,7 +10498,7 @@
         <v>409.022307050989</v>
       </c>
       <c r="AC2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -9148,25 +10507,25 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.73675006002484</v>
+        <v>29.7015665992692</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.35926726899195</v>
+        <v>29.35392727477236</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.966196599893645</v>
+        <v>1.982236590562688</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.39668848622242</v>
+        <v>27.37684176855299</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.6446195792587</v>
+        <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.229350645889425</v>
+        <v>-0.7179519367389001</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="AM2" t="n">
         <v>331.2549113821476</v>
@@ -9175,30 +10534,30 @@
         <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>389.8487932869257</v>
+        <v>389.3875381164191</v>
       </c>
       <c r="AP2" t="n">
-        <v>364.07195586232</v>
+        <v>363.4004164141423</v>
       </c>
       <c r="AQ2" t="n">
-        <v>415.6256307115314</v>
+        <v>415.374659818696</v>
       </c>
       <c r="AR2" t="n">
-        <v>359.1705860543759</v>
+        <v>358.9103955857297</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.9709626840815</v>
+        <v>428.0356714698664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9227,19 +10586,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>390.74</v>
+        <v>392.565</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>23.258333</v>
+        <v>23.38088</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
         <v>22.31206935670243</v>
@@ -9248,49 +10607,49 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.67432185491951</v>
+        <v>24.64291408588499</v>
       </c>
       <c r="P3" t="n">
-        <v>24.62023780459449</v>
+        <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.213687795692693</v>
+        <v>1.233164335900355</v>
       </c>
       <c r="R3" t="n">
-        <v>23.21050739722864</v>
+        <v>23.20750537293958</v>
       </c>
       <c r="S3" t="n">
-        <v>26.50944369222463</v>
+        <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.166682947579083</v>
+        <v>-1.023411113299477</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="V3" t="n">
-        <v>374.8427651926008</v>
+        <v>374.6196444990338</v>
       </c>
       <c r="W3" t="n">
-        <v>460.5199890136719</v>
+        <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>414.5286071626478</v>
+        <v>413.754527502009</v>
       </c>
       <c r="Y3" t="n">
-        <v>394.1386521950106</v>
+        <v>393.0496983022421</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.9185621302851</v>
+        <v>434.459356701776</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.9365242734411</v>
+        <v>389.6540152116556</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.3586540293738</v>
+        <v>445.2374133636685</v>
       </c>
       <c r="AC3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD3" t="n">
         <v>22.31206935670243</v>
@@ -9299,57 +10658,57 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.99875633117543</v>
+        <v>26.80080619782125</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.23606385982762</v>
+        <v>25.13133150998915</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.913124346735808</v>
+        <v>3.804583769963939</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.33877439421367</v>
+        <v>23.33389654392149</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34.02489348800898</v>
+        <v>34.03058373571968</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.9558662081095273</v>
+        <v>-0.8988962800137422</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.07258064516129033</v>
+        <v>0.1229508196721311</v>
       </c>
       <c r="AM3" t="n">
-        <v>374.8427651926008</v>
+        <v>374.6196444990338</v>
       </c>
       <c r="AN3" t="n">
-        <v>583.1248801870332</v>
+        <v>582.7777820440647</v>
       </c>
       <c r="AO3" t="n">
-        <v>453.5791063637472</v>
+        <v>449.9855360614187</v>
       </c>
       <c r="AP3" t="n">
-        <v>387.8386173385856</v>
+        <v>386.1065745637241</v>
       </c>
       <c r="AQ3" t="n">
-        <v>519.3195953889089</v>
+        <v>513.8644975591133</v>
       </c>
       <c r="AR3" t="n">
-        <v>392.0914098227897</v>
+        <v>391.7761229724418</v>
       </c>
       <c r="AS3" t="n">
-        <v>571.6182105985508</v>
+        <v>571.3735009227335</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9378,13 +10737,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>566.98</v>
+        <v>594.75</v>
       </c>
       <c r="I4" t="n">
-        <v>27.5</v>
+        <v>27.48</v>
       </c>
       <c r="J4" t="n">
-        <v>20.617455</v>
+        <v>21.643013</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -9399,49 +10758,49 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.30588309459538</v>
+        <v>24.14703609047108</v>
       </c>
       <c r="P4" t="n">
-        <v>23.10036399147727</v>
+        <v>22.83439782387452</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.68129515973201</v>
+        <v>2.688383984358619</v>
       </c>
       <c r="R4" t="n">
-        <v>21.74094549005682</v>
+        <v>21.59094504616477</v>
       </c>
       <c r="S4" t="n">
         <v>28.57616075407753</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.375614348613536</v>
+        <v>-0.931423154221949</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01587301587301587</v>
+        <v>0.126984126984127</v>
       </c>
       <c r="V4" t="n">
-        <v>566.97998046875</v>
+        <v>566.5676313920454</v>
       </c>
       <c r="W4" t="n">
-        <v>806.0930040147568</v>
+        <v>805.5067545572916</v>
       </c>
       <c r="X4" t="n">
-        <v>668.4117851013729</v>
+        <v>663.5605517661452</v>
       </c>
       <c r="Y4" t="n">
-        <v>594.6761682087426</v>
+        <v>589.6837598759703</v>
       </c>
       <c r="Z4" t="n">
-        <v>742.1474019940031</v>
+        <v>737.4373436563201</v>
       </c>
       <c r="AA4" t="n">
-        <v>597.8760009765624</v>
+        <v>593.319169868608</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.8444207371321</v>
+        <v>785.2728975220506</v>
       </c>
       <c r="AC4" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD4" t="n">
         <v>20.61745383522727</v>
@@ -9450,57 +10809,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.34200828476493</v>
+        <v>26.20387509204501</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.45083045228688</v>
+        <v>27.25952256560009</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.905026086314118</v>
+        <v>2.949849808349889</v>
       </c>
       <c r="AI4" t="n">
-        <v>22.02749090021307</v>
+        <v>21.94152743252841</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.30748211845921</v>
+        <v>29.3091457033941</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.970568633353723</v>
+        <v>-1.546133663868231</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.008064516129032258</v>
+        <v>0.06504065040650407</v>
       </c>
       <c r="AM4" t="n">
-        <v>566.97998046875</v>
+        <v>566.5676313920454</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.3475918629769</v>
+        <v>863.718975432531</v>
       </c>
       <c r="AO4" t="n">
-        <v>724.4052278310355</v>
+        <v>720.082487529397</v>
       </c>
       <c r="AP4" t="n">
-        <v>644.5170104573972</v>
+        <v>639.020614795942</v>
       </c>
       <c r="AQ4" t="n">
-        <v>804.2934452046737</v>
+        <v>801.1443602628519</v>
       </c>
       <c r="AR4" t="n">
-        <v>605.7559997558594</v>
+        <v>602.9531738458807</v>
       </c>
       <c r="AS4" t="n">
-        <v>805.9557582576283</v>
+        <v>805.4153239292699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9529,19 +10888,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>238.55</v>
+        <v>247.55</v>
       </c>
       <c r="I5" t="n">
-        <v>7.54</v>
+        <v>7.77</v>
       </c>
       <c r="J5" t="n">
-        <v>31.637932</v>
+        <v>31.859716</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -9550,49 +10909,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.63592970645751</v>
+        <v>31.66337883541885</v>
       </c>
       <c r="P5" t="n">
-        <v>31.70574133476002</v>
+        <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.401634424074888</v>
+        <v>2.411037645956832</v>
       </c>
       <c r="R5" t="n">
-        <v>28.91213431684209</v>
+        <v>28.90795038667516</v>
       </c>
       <c r="S5" t="n">
-        <v>34.92747542249608</v>
+        <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0008337212035342672</v>
+        <v>0.08143264163062355</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4603174603174603</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="V5" t="n">
-        <v>209.6267186035837</v>
+        <v>216.0211675795551</v>
       </c>
       <c r="W5" t="n">
-        <v>277.6129046537221</v>
+        <v>286.0812028062892</v>
       </c>
       <c r="X5" t="n">
-        <v>238.5349099866896</v>
+        <v>246.0244535512045</v>
       </c>
       <c r="Y5" t="n">
-        <v>220.426586429165</v>
+        <v>227.2906910421199</v>
       </c>
       <c r="Z5" t="n">
-        <v>256.6432335442142</v>
+        <v>264.758216060289</v>
       </c>
       <c r="AA5" t="n">
-        <v>217.9974927489894</v>
+        <v>224.614774504466</v>
       </c>
       <c r="AB5" t="n">
-        <v>263.3531646856205</v>
+        <v>271.4569227019115</v>
       </c>
       <c r="AC5" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -9601,57 +10960,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.57608116134857</v>
+        <v>31.56496108675321</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.76495310222133</v>
+        <v>31.82655590002617</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.306978518232265</v>
+        <v>2.332531065666415</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.87192711313345</v>
+        <v>28.86711905294752</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.70906596802268</v>
+        <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02681032275013304</v>
+        <v>0.1263669828819943</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.5081967213114754</v>
       </c>
       <c r="AM5" t="n">
-        <v>209.0483332465051</v>
+        <v>215.4251391678176</v>
       </c>
       <c r="AN5" t="n">
-        <v>277.6129046537221</v>
+        <v>286.0812028062892</v>
       </c>
       <c r="AO5" t="n">
-        <v>238.0836519565682</v>
+        <v>245.2597476440724</v>
       </c>
       <c r="AP5" t="n">
-        <v>220.689033929097</v>
+        <v>227.1359812638444</v>
       </c>
       <c r="AQ5" t="n">
-        <v>255.4782699840395</v>
+        <v>263.3835140243004</v>
       </c>
       <c r="AR5" t="n">
-        <v>217.6943304330262</v>
+        <v>224.2975150414022</v>
       </c>
       <c r="AS5" t="n">
-        <v>261.706357398891</v>
+        <v>269.8021464264044</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9680,19 +11039,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>291.13</v>
+        <v>298.84</v>
       </c>
       <c r="I6" t="n">
         <v>8.27</v>
       </c>
       <c r="J6" t="n">
-        <v>35.203144</v>
+        <v>36.135426</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -9701,25 +11060,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.46047008568137</v>
+        <v>34.56477649129591</v>
       </c>
       <c r="P6" t="n">
-        <v>34.3481020384197</v>
+        <v>34.48382353042415</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.033948720383977</v>
+        <v>2.01457934377709</v>
       </c>
       <c r="R6" t="n">
-        <v>31.87797449812104</v>
+        <v>31.86556948891169</v>
       </c>
       <c r="S6" t="n">
-        <v>37.37554517842955</v>
+        <v>37.38147763305368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3651389569833558</v>
+        <v>0.7796414241790633</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7258064516129032</v>
       </c>
       <c r="V6" t="n">
         <v>258.1810304279569</v>
@@ -9728,22 +11087,22 @@
         <v>315.5816102847638</v>
       </c>
       <c r="X6" t="n">
-        <v>284.9880876085849</v>
+        <v>285.8507015830172</v>
       </c>
       <c r="Y6" t="n">
-        <v>268.1673316910094</v>
+        <v>269.1901304099806</v>
       </c>
       <c r="Z6" t="n">
-        <v>301.8088435261603</v>
+        <v>302.5112727560537</v>
       </c>
       <c r="AA6" t="n">
-        <v>263.630849099461</v>
+        <v>263.5282596732997</v>
       </c>
       <c r="AB6" t="n">
-        <v>309.0957586256124</v>
+        <v>309.144820025354</v>
       </c>
       <c r="AC6" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -9752,25 +11111,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.47527925916662</v>
+        <v>34.43549234620956</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.49936878832081</v>
+        <v>34.42623029342849</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.734253280622169</v>
+        <v>1.720621352838539</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.14202455931072</v>
+        <v>32.13088525699663</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.73190201255655</v>
+        <v>36.6958458621764</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.4196992151989811</v>
+        <v>0.9879766114642456</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.6854838709677419</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="AM6" t="n">
         <v>258.1810304279569</v>
@@ -9779,30 +11138,30 @@
         <v>315.5816102847638</v>
       </c>
       <c r="AO6" t="n">
-        <v>285.1105594733079</v>
+        <v>284.781521703153</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.7682848425626</v>
+        <v>270.5519831151783</v>
       </c>
       <c r="AQ6" t="n">
-        <v>299.4528341040533</v>
+        <v>299.0110602911278</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.8145431054996</v>
+        <v>265.7224210753621</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.7728296438427</v>
+        <v>303.4746452801988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9831,19 +11190,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>205.19</v>
+        <v>209.58</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="J7" t="n">
-        <v>31.422665</v>
+        <v>32.144173</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
         <v>30.69218961239591</v>
@@ -9852,49 +11211,49 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.96999520523957</v>
+        <v>37.89823191285868</v>
       </c>
       <c r="P7" t="n">
-        <v>37.12856993383291</v>
+        <v>36.64081495635364</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.589118170261171</v>
+        <v>4.684825278144428</v>
       </c>
       <c r="R7" t="n">
-        <v>32.37856060220855</v>
+        <v>32.12436319675416</v>
       </c>
       <c r="S7" t="n">
-        <v>44.66816368881537</v>
+        <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.426707694665216</v>
+        <v>-1.228233407060542</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="V7" t="n">
-        <v>200.4199981689453</v>
+        <v>200.1130762728213</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="X7" t="n">
-        <v>247.9440686902144</v>
+        <v>247.0964720718386</v>
       </c>
       <c r="Y7" t="n">
-        <v>217.977127038409</v>
+        <v>216.5514112583369</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.9110103420199</v>
+        <v>277.6415328853403</v>
       </c>
       <c r="AA7" t="n">
-        <v>211.4320007324218</v>
+        <v>209.4508480428371</v>
       </c>
       <c r="AB7" t="n">
-        <v>291.6831088879644</v>
+        <v>291.6129907600247</v>
       </c>
       <c r="AC7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AD7" t="n">
         <v>30.69218961239591</v>
@@ -9903,57 +11262,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.86935421942142</v>
+        <v>37.79444166572497</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.258162206533</v>
+        <v>37.2408154545998</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.195060680497946</v>
+        <v>4.218896779690089</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.68376769552187</v>
+        <v>32.46799439785126</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.06224464883609</v>
+        <v>44.03346906389508</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.536733246646675</v>
+        <v>-1.339276346585569</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AM7" t="n">
-        <v>200.4199981689453</v>
+        <v>200.1130762728213</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="AO7" t="n">
-        <v>247.2868830528219</v>
+        <v>246.4197596605268</v>
       </c>
       <c r="AP7" t="n">
-        <v>219.8931368091703</v>
+        <v>218.9125526569474</v>
       </c>
       <c r="AQ7" t="n">
-        <v>274.6806292964735</v>
+        <v>273.9269666641061</v>
       </c>
       <c r="AR7" t="n">
-        <v>213.4250030517578</v>
+        <v>211.6913234739902</v>
       </c>
       <c r="AS7" t="n">
-        <v>287.7264575568997</v>
+        <v>287.0982182965959</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9982,19 +11341,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>511.57</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="J8" t="n">
-        <v>169.39404</v>
+        <v>174.22923</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
         <v>73.97735595703125</v>
@@ -10003,49 +11362,49 @@
         <v>177.8754162397541</v>
       </c>
       <c r="O8" t="n">
-        <v>121.6688400778806</v>
+        <v>124.0132388334195</v>
       </c>
       <c r="P8" t="n">
-        <v>128.8830220924233</v>
+        <v>132.5094316590507</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.86558964794703</v>
+        <v>33.57727744203408</v>
       </c>
       <c r="R8" t="n">
-        <v>76.53961987765331</v>
+        <v>76.95094500847583</v>
       </c>
       <c r="S8" t="n">
-        <v>166.8465596183402</v>
+        <v>167.680658059042</v>
       </c>
       <c r="T8" t="n">
-        <v>1.409253475821659</v>
+        <v>1.495534926953817</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="V8" t="n">
-        <v>223.4116149902344</v>
+        <v>222.671841430664</v>
       </c>
       <c r="W8" t="n">
-        <v>537.1837570440574</v>
+        <v>535.4050028816598</v>
       </c>
       <c r="X8" t="n">
-        <v>367.4398970351995</v>
+        <v>373.2798488885927</v>
       </c>
       <c r="Y8" t="n">
-        <v>265.1658162983995</v>
+        <v>272.2122437880701</v>
       </c>
       <c r="Z8" t="n">
-        <v>469.7139777719996</v>
+        <v>474.3474539891153</v>
       </c>
       <c r="AA8" t="n">
-        <v>231.149652030513</v>
+        <v>231.6223444755122</v>
       </c>
       <c r="AB8" t="n">
-        <v>503.8766100473873</v>
+        <v>504.7187807577164</v>
       </c>
       <c r="AC8" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -10054,57 +11413,57 @@
         <v>177.8754162397541</v>
       </c>
       <c r="AF8" t="n">
-        <v>108.8740742584979</v>
+        <v>109.5855964601589</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.5443373806958</v>
+        <v>105.8743819814597</v>
       </c>
       <c r="AH8" t="n">
-        <v>30.25885474191501</v>
+        <v>31.00646812517777</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.52037537772701</v>
+        <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>153.1708223936988</v>
+        <v>155.642626152664</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.000074565203849</v>
+        <v>2.084843500358216</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.967741935483871</v>
+        <v>0.9918032786885246</v>
       </c>
       <c r="AM8" t="n">
-        <v>217.6109399183741</v>
+        <v>216.8903738921543</v>
       </c>
       <c r="AN8" t="n">
-        <v>537.1837570440574</v>
+        <v>535.4050028816598</v>
       </c>
       <c r="AO8" t="n">
-        <v>328.7997042606637</v>
+        <v>329.8526453450783</v>
       </c>
       <c r="AP8" t="n">
-        <v>237.4179629400803</v>
+        <v>236.5231762882932</v>
       </c>
       <c r="AQ8" t="n">
-        <v>420.181445581247</v>
+        <v>423.1821144018634</v>
       </c>
       <c r="AR8" t="n">
-        <v>228.0715336407356</v>
+        <v>227.3095150699255</v>
       </c>
       <c r="AS8" t="n">
-        <v>462.5758836289704</v>
+        <v>468.4843047195184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10133,19 +11492,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>382.07</v>
+        <v>379.26</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="J9" t="n">
-        <v>63.678333</v>
+        <v>62.895523</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -10154,49 +11513,49 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>74.80647690972003</v>
+        <v>74.99901067785036</v>
       </c>
       <c r="P9" t="n">
-        <v>78.39571411846676</v>
+        <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.868637933682905</v>
+        <v>9.829003352317653</v>
       </c>
       <c r="R9" t="n">
-        <v>61.29707440530581</v>
+        <v>61.29473531920079</v>
       </c>
       <c r="S9" t="n">
-        <v>83.47290277016327</v>
+        <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.127627134007853</v>
+        <v>-1.231405387098214</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2698412698412698</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="V9" t="n">
-        <v>343.1695949264438</v>
+        <v>344.885442901076</v>
       </c>
       <c r="W9" t="n">
-        <v>563.2397746482092</v>
+        <v>566.0559735214503</v>
       </c>
       <c r="X9" t="n">
-        <v>448.8388614583202</v>
+        <v>452.2440343874377</v>
       </c>
       <c r="Y9" t="n">
-        <v>389.6270338562227</v>
+        <v>392.9751441729622</v>
       </c>
       <c r="Z9" t="n">
-        <v>508.0506890604177</v>
+        <v>511.5129246019132</v>
       </c>
       <c r="AA9" t="n">
-        <v>367.7824464318349</v>
+        <v>369.6072539747808</v>
       </c>
       <c r="AB9" t="n">
-        <v>500.8374166209796</v>
+        <v>503.467376494826</v>
       </c>
       <c r="AC9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -10205,57 +11564,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.46676022926599</v>
+        <v>72.38999481009056</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.58281178344471</v>
+        <v>71.47694073882994</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.719909269812946</v>
+        <v>7.734558769582204</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.34697784364341</v>
+        <v>62.37563283819902</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.38791304025038</v>
+        <v>82.37543771606209</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.13841068879284</v>
+        <v>-1.227538905959263</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1487603305785124</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.1695949264438</v>
+        <v>344.885442901076</v>
       </c>
       <c r="AN9" t="n">
-        <v>563.2397746482092</v>
+        <v>566.0559735214503</v>
       </c>
       <c r="AO9" t="n">
-        <v>434.8005613755959</v>
+        <v>436.511668704846</v>
       </c>
       <c r="AP9" t="n">
-        <v>388.4811057567183</v>
+        <v>389.8722793242654</v>
       </c>
       <c r="AQ9" t="n">
-        <v>481.1200169944736</v>
+        <v>483.1510580854268</v>
       </c>
       <c r="AR9" t="n">
-        <v>374.0818670618605</v>
+        <v>376.1250660143401</v>
       </c>
       <c r="AS9" t="n">
-        <v>494.3274782415023</v>
+        <v>496.7238894278544</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-13 02:48:21</t>
+          <t>2026-06-16 09:12:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10284,19 +11643,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>80.34</v>
+        <v>78.5899</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>25.916128</v>
+        <v>25.35158</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M10" t="n">
         <v>35.93675816954359</v>
@@ -10305,22 +11664,22 @@
         <v>42.60474344487245</v>
       </c>
       <c r="O10" t="n">
-        <v>38.52242658096891</v>
+        <v>38.62337672102367</v>
       </c>
       <c r="P10" t="n">
-        <v>37.7667996252007</v>
+        <v>38.00395317228413</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.090005653539248</v>
+        <v>2.163128444509888</v>
       </c>
       <c r="R10" t="n">
-        <v>36.32885356194415</v>
+        <v>36.29248999795422</v>
       </c>
       <c r="S10" t="n">
-        <v>41.7612647256361</v>
+        <v>42.00790465584855</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.031705493055107</v>
+        <v>-6.135464010335611</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -10332,22 +11691,22 @@
         <v>132.0747046791046</v>
       </c>
       <c r="X10" t="n">
-        <v>119.4195224010036</v>
+        <v>119.7324678351734</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.9405048750319</v>
+        <v>113.0267696571927</v>
       </c>
       <c r="Z10" t="n">
-        <v>125.8985399269753</v>
+        <v>126.438166013154</v>
       </c>
       <c r="AA10" t="n">
-        <v>112.6194460420269</v>
+        <v>112.5067189936581</v>
       </c>
       <c r="AB10" t="n">
-        <v>129.4599206494719</v>
+        <v>130.2245044331305</v>
       </c>
       <c r="AC10" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -10356,25 +11715,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>25.89235394481071</v>
+        <v>26.70532199408146</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.69960456214874</v>
+        <v>32.86956666486535</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.16530049649943</v>
+        <v>14.82814270080998</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.775396801176525</v>
+        <v>3.77276523370193</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.1276670915807</v>
+        <v>39.13833859409738</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.00156766133284206</v>
+        <v>-0.09129545226237379</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -10383,19 +11742,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>80.2662972289132</v>
+        <v>82.78649818165253</v>
       </c>
       <c r="AP10" t="n">
-        <v>33.25386568976496</v>
+        <v>36.8192558091416</v>
       </c>
       <c r="AQ10" t="n">
-        <v>127.2787287680614</v>
+        <v>128.7537405541634</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.70373008364723</v>
+        <v>11.69557222447598</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.2957679839002</v>
+        <v>121.3288496417019</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS64"/>
+  <dimension ref="A1:AS73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7684,7 +7684,7 @@
         <v>469.7139777719996</v>
       </c>
       <c r="AA48" t="n">
-        <v>231.149652030513</v>
+        <v>231.1496520305129</v>
       </c>
       <c r="AB48" t="n">
         <v>503.8766100473873</v>
@@ -9025,7 +9025,7 @@
         <v>1.495534926953817</v>
       </c>
       <c r="U57" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V57" t="n">
         <v>222.671841430664</v>
@@ -9043,7 +9043,7 @@
         <v>474.3474539891153</v>
       </c>
       <c r="AA57" t="n">
-        <v>231.6223444755122</v>
+        <v>231.6223444755123</v>
       </c>
       <c r="AB57" t="n">
         <v>504.7187807577164</v>
@@ -9094,7 +9094,7 @@
         <v>423.1821144018634</v>
       </c>
       <c r="AR57" t="n">
-        <v>227.3095150699255</v>
+        <v>227.3095150699256</v>
       </c>
       <c r="AS57" t="n">
         <v>468.4843047195184</v>
@@ -9161,7 +9161,7 @@
         <v>31.66337883541885</v>
       </c>
       <c r="P58" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q58" t="n">
         <v>2.411037645956832</v>
@@ -9173,7 +9173,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T58" t="n">
-        <v>0.08143264163062355</v>
+        <v>0.0814326416306235</v>
       </c>
       <c r="U58" t="n">
         <v>0.5483870967741935</v>
@@ -9224,7 +9224,7 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.1263669828819943</v>
+        <v>0.1263669828819942</v>
       </c>
       <c r="AL58" t="n">
         <v>0.5081967213114754</v>
@@ -9306,7 +9306,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N59" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O59" t="n">
         <v>74.99901067785036</v>
@@ -9339,7 +9339,7 @@
         <v>452.2440343874377</v>
       </c>
       <c r="Y59" t="n">
-        <v>392.9751441729622</v>
+        <v>392.9751441729623</v>
       </c>
       <c r="Z59" t="n">
         <v>511.5129246019132</v>
@@ -9357,7 +9357,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE59" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF59" t="n">
         <v>72.38999481009056</v>
@@ -9375,10 +9375,10 @@
         <v>82.37543771606209</v>
       </c>
       <c r="AK59" t="n">
-        <v>-1.227538905959263</v>
+        <v>-1.227538905959262</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.1311475409836065</v>
       </c>
       <c r="AM59" t="n">
         <v>344.885442901076</v>
@@ -9387,7 +9387,7 @@
         <v>566.0559735214503</v>
       </c>
       <c r="AO59" t="n">
-        <v>436.511668704846</v>
+        <v>436.5116687048461</v>
       </c>
       <c r="AP59" t="n">
         <v>389.8722793242654</v>
@@ -9469,7 +9469,7 @@
         <v>1.661984146055882</v>
       </c>
       <c r="R60" t="n">
-        <v>26.98642291338911</v>
+        <v>26.98642291338912</v>
       </c>
       <c r="S60" t="n">
         <v>31.19926064462159</v>
@@ -9478,7 +9478,7 @@
         <v>-0.4073021023341909</v>
       </c>
       <c r="U60" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.365079365079365</v>
       </c>
       <c r="V60" t="n">
         <v>331.2549113821476</v>
@@ -9520,7 +9520,7 @@
         <v>1.982236590562688</v>
       </c>
       <c r="AI60" t="n">
-        <v>27.37684176855299</v>
+        <v>27.376841768553</v>
       </c>
       <c r="AJ60" t="n">
         <v>32.64955541341467</v>
@@ -9538,7 +9538,7 @@
         <v>446.3611964445124</v>
       </c>
       <c r="AO60" t="n">
-        <v>389.3875381164191</v>
+        <v>389.3875381164192</v>
       </c>
       <c r="AP60" t="n">
         <v>363.4004164141423</v>
@@ -9605,7 +9605,7 @@
         <v>63</v>
       </c>
       <c r="M61" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="N61" t="n">
         <v>29.31247287326389</v>
@@ -9629,7 +9629,7 @@
         <v>-0.931423154221949</v>
       </c>
       <c r="U61" t="n">
-        <v>0.126984126984127</v>
+        <v>0.1269841269841269</v>
       </c>
       <c r="V61" t="n">
         <v>566.5676313920454</v>
@@ -9656,7 +9656,7 @@
         <v>123</v>
       </c>
       <c r="AD61" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="AE61" t="n">
         <v>31.43082152229007</v>
@@ -9680,7 +9680,7 @@
         <v>-1.546133663868231</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.06504065040650407</v>
+        <v>0.065040650406504</v>
       </c>
       <c r="AM61" t="n">
         <v>566.5676313920454</v>
@@ -9762,7 +9762,7 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O62" t="n">
-        <v>24.64291408588499</v>
+        <v>24.642914085885</v>
       </c>
       <c r="P62" t="n">
         <v>24.57421541107486</v>
@@ -9777,7 +9777,7 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.023411113299477</v>
+        <v>-1.023411113299476</v>
       </c>
       <c r="U62" t="n">
         <v>0.2419354838709677</v>
@@ -9816,7 +9816,7 @@
         <v>26.80080619782125</v>
       </c>
       <c r="AG62" t="n">
-        <v>25.13133150998915</v>
+        <v>25.13133150998916</v>
       </c>
       <c r="AH62" t="n">
         <v>3.804583769963939</v>
@@ -9958,13 +9958,13 @@
         <v>81</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE63" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF63" t="n">
-        <v>26.70532199408146</v>
+        <v>26.70532199408147</v>
       </c>
       <c r="AG63" t="n">
         <v>32.86956666486535</v>
@@ -9979,7 +9979,7 @@
         <v>39.13833859409738</v>
       </c>
       <c r="AK63" t="n">
-        <v>-0.09129545226237379</v>
+        <v>-0.09129545226237371</v>
       </c>
       <c r="AL63" t="n">
         <v>0.2839506172839506</v>
@@ -10064,7 +10064,7 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O64" t="n">
-        <v>37.89823191285868</v>
+        <v>37.89823191285869</v>
       </c>
       <c r="P64" t="n">
         <v>36.64081495635364</v>
@@ -10133,7 +10133,7 @@
         <v>-1.339276346585569</v>
       </c>
       <c r="AL64" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="AM64" t="n">
         <v>200.1130762728213</v>
@@ -10155,6 +10155,1365 @@
       </c>
       <c r="AS64" t="n">
         <v>287.0982182965959</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>299.24</v>
+      </c>
+      <c r="I65" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J65" t="n">
+        <v>36.2276</v>
+      </c>
+      <c r="K65" t="n">
+        <v>67</v>
+      </c>
+      <c r="L65" t="n">
+        <v>62</v>
+      </c>
+      <c r="M65" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N65" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O65" t="n">
+        <v>34.6339015743772</v>
+      </c>
+      <c r="P65" t="n">
+        <v>34.57088615320906</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1.985923699247501</v>
+      </c>
+      <c r="R65" t="n">
+        <v>31.98063234739666</v>
+      </c>
+      <c r="S65" t="n">
+        <v>37.38147763305368</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.8024973095525688</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0.7580645161290323</v>
+      </c>
+      <c r="V65" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="W65" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X65" t="n">
+        <v>286.0760270043556</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>269.6722972485713</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>302.47975676014</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>264.1600231894964</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>308.7710052490234</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>34.43087869573493</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.715878971266023</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>36.6958458621764</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>1.047114239612952</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0.8032786885245902</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>284.3990580267705</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>270.2258977241131</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>298.5722183294278</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>265.4011122227922</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>303.107686821577</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>507.29</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J66" t="n">
+        <v>169.66222</v>
+      </c>
+      <c r="K66" t="n">
+        <v>63</v>
+      </c>
+      <c r="L66" t="n">
+        <v>62</v>
+      </c>
+      <c r="M66" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N66" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="O66" t="n">
+        <v>125.602624598074</v>
+      </c>
+      <c r="P66" t="n">
+        <v>133.8455581547047</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>33.58486969512436</v>
+      </c>
+      <c r="R66" t="n">
+        <v>77.46415221016363</v>
+      </c>
+      <c r="S66" t="n">
+        <v>167.680658059042</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.311888234252172</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0.9193548387096774</v>
+      </c>
+      <c r="V66" t="n">
+        <v>221.1922943115235</v>
+      </c>
+      <c r="W66" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="X66" t="n">
+        <v>375.5518475482413</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>275.1330871598195</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>475.9706079366632</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>231.6178151083893</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>501.3651675965356</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>110.1984285150581</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>105.8965523254695</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>31.54184879705103</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>159.7232826107839</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.885234815103842</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0.9590163934426229</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>329.4933012600239</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>235.1831733568413</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>423.8034291632065</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>225.7991528435473</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>477.5726150062438</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>246</v>
+      </c>
+      <c r="I67" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J67" t="n">
+        <v>31.660233</v>
+      </c>
+      <c r="K67" t="n">
+        <v>67</v>
+      </c>
+      <c r="L67" t="n">
+        <v>62</v>
+      </c>
+      <c r="M67" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N67" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O67" t="n">
+        <v>31.662931286491</v>
+      </c>
+      <c r="P67" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.41126094160941</v>
+      </c>
+      <c r="R67" t="n">
+        <v>28.90795038667516</v>
+      </c>
+      <c r="S67" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T67" t="n">
+        <v>-0.001119035457521161</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="V67" t="n">
+        <v>216.0211675795551</v>
+      </c>
+      <c r="W67" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="X67" t="n">
+        <v>246.020976096035</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>227.2854785797299</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>264.7564736123401</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>224.614774504466</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>271.4569227019115</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>31.54212973675997</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>31.76495310222133</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>2.341453727939681</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>28.86711905294752</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0.05044014401427146</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0.4672131147540984</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>215.4251391678176</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>245.082348054625</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>226.8892525885337</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>263.2754435207163</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>224.2975150414022</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>269.8021464264044</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J68" t="n">
+        <v>62.472633</v>
+      </c>
+      <c r="K68" t="n">
+        <v>34</v>
+      </c>
+      <c r="L68" t="n">
+        <v>62</v>
+      </c>
+      <c r="M68" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N68" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O68" t="n">
+        <v>75.05613615223172</v>
+      </c>
+      <c r="P68" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>9.761540481703538</v>
+      </c>
+      <c r="R68" t="n">
+        <v>61.29473531920079</v>
+      </c>
+      <c r="S68" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T68" t="n">
+        <v>-1.289089890659932</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V68" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="W68" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X68" t="n">
+        <v>452.5885009979573</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>393.7264118932849</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>511.4505901026296</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>369.6072539747808</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>503.467376494826</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>72.35695660990616</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>71.47694073882994</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>7.758154083548289</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>62.37563283819902</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>82.37543771606209</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>-1.274056109670026</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0.1065573770491803</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>436.3124483577342</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>389.530779233938</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>483.0941174815304</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>376.1250660143401</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>496.7238894278544</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>28.328243</v>
+      </c>
+      <c r="K69" t="n">
+        <v>37</v>
+      </c>
+      <c r="L69" t="n">
+        <v>61</v>
+      </c>
+      <c r="M69" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N69" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O69" t="n">
+        <v>28.97675210847605</v>
+      </c>
+      <c r="P69" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1.685097699409057</v>
+      </c>
+      <c r="R69" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S69" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T69" t="n">
+        <v>-0.3848495601788979</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.3770491803278688</v>
+      </c>
+      <c r="V69" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="W69" t="n">
+        <v>422.3507729952915</v>
+      </c>
+      <c r="X69" t="n">
+        <v>379.5954526210362</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>357.5206727587776</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>401.6702324832949</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>353.0505031233612</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>409.2750364404161</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>29.71105352646061</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>29.35392727477236</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1.994219353477789</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>27.33714833321415</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>32.65942708172662</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>-0.6934094406661305</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0.2892561983471074</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>446.0207226104586</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>389.2148011966339</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>363.0905276660749</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>415.339074727193</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>358.1166431651054</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>427.8384947706187</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>600.21</v>
+      </c>
+      <c r="I70" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J70" t="n">
+        <v>21.83376</v>
+      </c>
+      <c r="K70" t="n">
+        <v>55</v>
+      </c>
+      <c r="L70" t="n">
+        <v>61</v>
+      </c>
+      <c r="M70" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="N70" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O70" t="n">
+        <v>24.15446897245624</v>
+      </c>
+      <c r="P70" t="n">
+        <v>22.83439782387452</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.700324830523031</v>
+      </c>
+      <c r="R70" t="n">
+        <v>21.58109019886364</v>
+      </c>
+      <c r="S70" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T70" t="n">
+        <v>-0.8594184470787313</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0.1475409836065574</v>
+      </c>
+      <c r="V70" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="W70" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X70" t="n">
+        <v>664.0063520528221</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>589.7744224617439</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>738.2382816439002</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>593.2641695667613</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>785.6593162306017</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>26.21503956803088</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>27.25952256560009</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>2.930130264166549</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>21.99854625355114</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>29.29583702391497</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>-1.495250781718095</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0.0743801652892562</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>720.6514377251689</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>640.1021567632305</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>801.2007186871074</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>604.7400365101207</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>805.3425597874225</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>393.83</v>
+      </c>
+      <c r="I71" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J71" t="n">
+        <v>23.470201</v>
+      </c>
+      <c r="K71" t="n">
+        <v>67</v>
+      </c>
+      <c r="L71" t="n">
+        <v>62</v>
+      </c>
+      <c r="M71" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N71" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O71" t="n">
+        <v>24.6326829309555</v>
+      </c>
+      <c r="P71" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1.236566882805114</v>
+      </c>
+      <c r="R71" t="n">
+        <v>23.20750537293958</v>
+      </c>
+      <c r="S71" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T71" t="n">
+        <v>-0.9400881967002434</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="V71" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="W71" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X71" t="n">
+        <v>413.3364195814333</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>392.5868272879635</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>434.0860118749031</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>389.4219401579262</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>444.9722332485025</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>26.71429293477805</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>25.12695427012488</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>3.749374809894066</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>23.33389654392149</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>33.99836316386802</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>-0.8652354323759147</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>582.4306839010962</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>448.2658354455758</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>385.3513261355534</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>511.1803447555982</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>391.5427840070027</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>570.4925338897054</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>25.393549</v>
+      </c>
+      <c r="K72" t="n">
+        <v>67</v>
+      </c>
+      <c r="L72" t="n">
+        <v>20</v>
+      </c>
+      <c r="M72" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="N72" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="O72" t="n">
+        <v>38.68300411540999</v>
+      </c>
+      <c r="P72" t="n">
+        <v>38.50000102529411</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2.201545083765738</v>
+      </c>
+      <c r="R72" t="n">
+        <v>36.28932787024455</v>
+      </c>
+      <c r="S72" t="n">
+        <v>42.06442640704127</v>
+      </c>
+      <c r="T72" t="n">
+        <v>-6.036421971735596</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>111.4039503255851</v>
+      </c>
+      <c r="W72" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="X72" t="n">
+        <v>119.917312757771</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>113.0925229980972</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>126.7421025174447</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>112.4969163977581</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>130.3997218618279</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>26.99005748308434</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>32.93478291025274</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>14.69717264676027</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>3.769172917033795</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>39.14426750816374</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>-0.1086269122269761</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>83.66917819756146</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>38.10794299260461</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>129.2304134025183</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>11.68443604280477</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>121.3472292753076</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-06-17 05:57:56</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>207.41</v>
+      </c>
+      <c r="I73" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J73" t="n">
+        <v>31.762634</v>
+      </c>
+      <c r="K73" t="n">
+        <v>65</v>
+      </c>
+      <c r="L73" t="n">
+        <v>62</v>
+      </c>
+      <c r="M73" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N73" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O73" t="n">
+        <v>37.82371058343767</v>
+      </c>
+      <c r="P73" t="n">
+        <v>36.45306022799745</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>4.739261878545491</v>
+      </c>
+      <c r="R73" t="n">
+        <v>31.98928015155412</v>
+      </c>
+      <c r="S73" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T73" t="n">
+        <v>-1.278907293744622</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="V73" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="W73" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X73" t="n">
+        <v>246.988830109848</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>216.0414500429459</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>277.93621017675</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>208.8899993896484</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>37.72266680925278</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>37.19999975087691</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>4.23952472587639</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>32.47427223287351</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>44.00469347895407</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>-1.405825698544718</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>246.3290142644207</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>218.6449178044478</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>274.0131107243935</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>212.056997680664</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>287.3506484175701</v>
       </c>
     </row>
   </sheetData>
@@ -10401,12 +11760,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -10435,19 +11794,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>370.73</v>
+        <v>371.1</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="J2" t="n">
-        <v>28.278416</v>
+        <v>28.328243</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -10456,49 +11815,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.95534563673466</v>
+        <v>28.97675210847605</v>
       </c>
       <c r="P2" t="n">
-        <v>29.20629058470889</v>
+        <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.661984146055882</v>
+        <v>1.685097699409057</v>
       </c>
       <c r="R2" t="n">
-        <v>26.98642291338911</v>
+        <v>26.95042008575277</v>
       </c>
       <c r="S2" t="n">
-        <v>31.19926064462159</v>
+        <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4073021023341909</v>
+        <v>-0.3848495601788979</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="V2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.002237918088</v>
       </c>
       <c r="W2" t="n">
-        <v>422.673178165517</v>
+        <v>422.3507729952915</v>
       </c>
       <c r="X2" t="n">
-        <v>379.6045812975913</v>
+        <v>379.5954526210362</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.8159691427987</v>
+        <v>357.5206727587776</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.3931934523839</v>
+        <v>401.6702324832949</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.7920043945313</v>
+        <v>353.0505031233612</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.022307050989</v>
+        <v>409.2750364404161</v>
       </c>
       <c r="AC2" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -10507,57 +11866,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.7015665992692</v>
+        <v>29.71105352646061</v>
       </c>
       <c r="AG2" t="n">
         <v>29.35392727477236</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.982236590562688</v>
+        <v>1.994219353477789</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.37684176855299</v>
+        <v>27.33714833321415</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.64955541341467</v>
+        <v>32.65942708172662</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.7179519367389001</v>
+        <v>-0.6934094406661305</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2892561983471074</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.002237918088</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.3611964445124</v>
+        <v>446.0207226104586</v>
       </c>
       <c r="AO2" t="n">
-        <v>389.3875381164191</v>
+        <v>389.2148011966339</v>
       </c>
       <c r="AP2" t="n">
-        <v>363.4004164141423</v>
+        <v>363.0905276660749</v>
       </c>
       <c r="AQ2" t="n">
-        <v>415.374659818696</v>
+        <v>415.339074727193</v>
       </c>
       <c r="AR2" t="n">
-        <v>358.9103955857297</v>
+        <v>358.1166431651054</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.0356714698664</v>
+        <v>427.8384947706187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10586,13 +11945,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>392.565</v>
+        <v>393.83</v>
       </c>
       <c r="I3" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>23.38088</v>
+        <v>23.470201</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -10607,13 +11966,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.64291408588499</v>
+        <v>24.6326829309555</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.233164335900355</v>
+        <v>1.236566882805114</v>
       </c>
       <c r="R3" t="n">
         <v>23.20750537293958</v>
@@ -10622,31 +11981,31 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.023411113299477</v>
+        <v>-0.9400881967002434</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="V3" t="n">
-        <v>374.6196444990338</v>
+        <v>374.3965238054668</v>
       </c>
       <c r="W3" t="n">
-        <v>460.2458699725923</v>
+        <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>413.754527502009</v>
+        <v>413.3364195814333</v>
       </c>
       <c r="Y3" t="n">
-        <v>393.0496983022421</v>
+        <v>392.5868272879635</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.459356701776</v>
+        <v>434.0860118749031</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.6540152116556</v>
+        <v>389.4219401579262</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.2374133636685</v>
+        <v>444.9722332485025</v>
       </c>
       <c r="AC3" t="n">
         <v>122</v>
@@ -10658,57 +12017,57 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.80080619782125</v>
+        <v>26.71429293477805</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.13133150998915</v>
+        <v>25.12695427012488</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.804583769963939</v>
+        <v>3.749374809894066</v>
       </c>
       <c r="AI3" t="n">
         <v>23.33389654392149</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34.03058373571968</v>
+        <v>33.99836316386802</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8988962800137422</v>
+        <v>-0.8652354323759147</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1229508196721311</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="AM3" t="n">
-        <v>374.6196444990338</v>
+        <v>374.3965238054668</v>
       </c>
       <c r="AN3" t="n">
-        <v>582.7777820440647</v>
+        <v>582.4306839010962</v>
       </c>
       <c r="AO3" t="n">
-        <v>449.9855360614187</v>
+        <v>448.2658354455758</v>
       </c>
       <c r="AP3" t="n">
-        <v>386.1065745637241</v>
+        <v>385.3513261355534</v>
       </c>
       <c r="AQ3" t="n">
-        <v>513.8644975591133</v>
+        <v>511.1803447555982</v>
       </c>
       <c r="AR3" t="n">
-        <v>391.7761229724418</v>
+        <v>391.5427840070027</v>
       </c>
       <c r="AS3" t="n">
-        <v>571.3735009227335</v>
+        <v>570.4925338897054</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -10737,19 +12096,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>594.75</v>
+        <v>600.21</v>
       </c>
       <c r="I4" t="n">
-        <v>27.48</v>
+        <v>27.49</v>
       </c>
       <c r="J4" t="n">
-        <v>21.643013</v>
+        <v>21.83376</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M4" t="n">
         <v>20.61745383522727</v>
@@ -10758,49 +12117,49 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.14703609047108</v>
+        <v>24.15446897245624</v>
       </c>
       <c r="P4" t="n">
         <v>22.83439782387452</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.688383984358619</v>
+        <v>2.700324830523031</v>
       </c>
       <c r="R4" t="n">
-        <v>21.59094504616477</v>
+        <v>21.58109019886364</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57616075407753</v>
+        <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.931423154221949</v>
+        <v>-0.8594184470787313</v>
       </c>
       <c r="U4" t="n">
-        <v>0.126984126984127</v>
+        <v>0.1475409836065574</v>
       </c>
       <c r="V4" t="n">
-        <v>566.5676313920454</v>
+        <v>566.7738059303977</v>
       </c>
       <c r="W4" t="n">
-        <v>805.5067545572916</v>
+        <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>663.5605517661452</v>
+        <v>664.0063520528221</v>
       </c>
       <c r="Y4" t="n">
-        <v>589.6837598759703</v>
+        <v>589.7744224617439</v>
       </c>
       <c r="Z4" t="n">
-        <v>737.4373436563201</v>
+        <v>738.2382816439002</v>
       </c>
       <c r="AA4" t="n">
-        <v>593.319169868608</v>
+        <v>593.2641695667613</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.2728975220506</v>
+        <v>785.6593162306017</v>
       </c>
       <c r="AC4" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD4" t="n">
         <v>20.61745383522727</v>
@@ -10809,57 +12168,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.20387509204501</v>
+        <v>26.21503956803088</v>
       </c>
       <c r="AG4" t="n">
         <v>27.25952256560009</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.949849808349889</v>
+        <v>2.930130264166549</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.94152743252841</v>
+        <v>21.99854625355114</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.3091457033941</v>
+        <v>29.29583702391497</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.546133663868231</v>
+        <v>-1.495250781718095</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.06504065040650407</v>
+        <v>0.0743801652892562</v>
       </c>
       <c r="AM4" t="n">
-        <v>566.5676313920454</v>
+        <v>566.7738059303977</v>
       </c>
       <c r="AN4" t="n">
-        <v>863.718975432531</v>
+        <v>864.0332836477539</v>
       </c>
       <c r="AO4" t="n">
-        <v>720.082487529397</v>
+        <v>720.6514377251689</v>
       </c>
       <c r="AP4" t="n">
-        <v>639.020614795942</v>
+        <v>640.1021567632305</v>
       </c>
       <c r="AQ4" t="n">
-        <v>801.1443602628519</v>
+        <v>801.2007186871074</v>
       </c>
       <c r="AR4" t="n">
-        <v>602.9531738458807</v>
+        <v>604.7400365101207</v>
       </c>
       <c r="AS4" t="n">
-        <v>805.4153239292699</v>
+        <v>805.3425597874225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -10888,13 +12247,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>247.55</v>
+        <v>246</v>
       </c>
       <c r="I5" t="n">
         <v>7.77</v>
       </c>
       <c r="J5" t="n">
-        <v>31.859716</v>
+        <v>31.660233</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -10909,13 +12268,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.66337883541885</v>
+        <v>31.662931286491</v>
       </c>
       <c r="P5" t="n">
         <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.411037645956832</v>
+        <v>2.41126094160941</v>
       </c>
       <c r="R5" t="n">
         <v>28.90795038667516</v>
@@ -10924,10 +12283,10 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08143264163062355</v>
+        <v>-0.001119035457521161</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="V5" t="n">
         <v>216.0211675795551</v>
@@ -10936,13 +12295,13 @@
         <v>286.0812028062892</v>
       </c>
       <c r="X5" t="n">
-        <v>246.0244535512045</v>
+        <v>246.020976096035</v>
       </c>
       <c r="Y5" t="n">
-        <v>227.2906910421199</v>
+        <v>227.2854785797299</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.758216060289</v>
+        <v>264.7564736123401</v>
       </c>
       <c r="AA5" t="n">
         <v>224.614774504466</v>
@@ -10960,13 +12319,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.56496108675321</v>
+        <v>31.54212973675997</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.82655590002617</v>
+        <v>31.76495310222133</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.332531065666415</v>
+        <v>2.341453727939681</v>
       </c>
       <c r="AI5" t="n">
         <v>28.86711905294752</v>
@@ -10975,10 +12334,10 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1263669828819943</v>
+        <v>0.05044014401427146</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5081967213114754</v>
+        <v>0.4672131147540984</v>
       </c>
       <c r="AM5" t="n">
         <v>215.4251391678176</v>
@@ -10987,13 +12346,13 @@
         <v>286.0812028062892</v>
       </c>
       <c r="AO5" t="n">
-        <v>245.2597476440724</v>
+        <v>245.082348054625</v>
       </c>
       <c r="AP5" t="n">
-        <v>227.1359812638444</v>
+        <v>226.8892525885337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>263.3835140243004</v>
+        <v>263.2754435207163</v>
       </c>
       <c r="AR5" t="n">
         <v>224.2975150414022</v>
@@ -11005,12 +12364,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -11039,13 +12398,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>298.84</v>
+        <v>299.24</v>
       </c>
       <c r="I6" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>36.135426</v>
+        <v>36.2276</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -11060,46 +12419,46 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.56477649129591</v>
+        <v>34.6339015743772</v>
       </c>
       <c r="P6" t="n">
-        <v>34.48382353042415</v>
+        <v>34.57088615320906</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.01457934377709</v>
+        <v>1.985923699247501</v>
       </c>
       <c r="R6" t="n">
-        <v>31.86556948891169</v>
+        <v>31.98063234739666</v>
       </c>
       <c r="S6" t="n">
         <v>37.38147763305368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7796414241790633</v>
+        <v>0.8024973095525688</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.7580645161290323</v>
       </c>
       <c r="V6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="W6" t="n">
-        <v>315.5816102847638</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>285.8507015830172</v>
+        <v>286.0760270043556</v>
       </c>
       <c r="Y6" t="n">
-        <v>269.1901304099806</v>
+        <v>269.6722972485713</v>
       </c>
       <c r="Z6" t="n">
-        <v>302.5112727560537</v>
+        <v>302.47975676014</v>
       </c>
       <c r="AA6" t="n">
-        <v>263.5282596732997</v>
+        <v>264.1600231894964</v>
       </c>
       <c r="AB6" t="n">
-        <v>309.144820025354</v>
+        <v>308.7710052490234</v>
       </c>
       <c r="AC6" t="n">
         <v>122</v>
@@ -11111,13 +12470,13 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.43549234620956</v>
+        <v>34.43087869573493</v>
       </c>
       <c r="AG6" t="n">
         <v>34.42623029342849</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.720621352838539</v>
+        <v>1.715878971266023</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13088525699663</v>
@@ -11126,42 +12485,42 @@
         <v>36.6958458621764</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9879766114642456</v>
+        <v>1.047114239612952</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7786885245901639</v>
+        <v>0.8032786885245902</v>
       </c>
       <c r="AM6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.5816102847638</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.781521703153</v>
+        <v>284.3990580267705</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.5519831151783</v>
+        <v>270.2258977241131</v>
       </c>
       <c r="AQ6" t="n">
-        <v>299.0110602911278</v>
+        <v>298.5722183294278</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.7224210753621</v>
+        <v>265.4011122227922</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.4746452801988</v>
+        <v>303.107686821577</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11190,13 +12549,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>209.58</v>
+        <v>207.41</v>
       </c>
       <c r="I7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>32.144173</v>
+        <v>31.762634</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -11211,49 +12570,49 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.89823191285868</v>
+        <v>37.82371058343767</v>
       </c>
       <c r="P7" t="n">
-        <v>36.64081495635364</v>
+        <v>36.45306022799745</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.684825278144428</v>
+        <v>4.739261878545491</v>
       </c>
       <c r="R7" t="n">
-        <v>32.12436319675416</v>
+        <v>31.98928015155412</v>
       </c>
       <c r="S7" t="n">
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.228233407060542</v>
+        <v>-1.278907293744622</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="V7" t="n">
-        <v>200.1130762728213</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="W7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>247.0964720718386</v>
+        <v>246.988830109848</v>
       </c>
       <c r="Y7" t="n">
-        <v>216.5514112583369</v>
+        <v>216.0414500429459</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.6415328853403</v>
+        <v>277.93621017675</v>
       </c>
       <c r="AA7" t="n">
-        <v>209.4508480428371</v>
+        <v>208.8899993896484</v>
       </c>
       <c r="AB7" t="n">
-        <v>291.6129907600247</v>
+        <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD7" t="n">
         <v>30.69218961239591</v>
@@ -11262,57 +12621,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.79444166572497</v>
+        <v>37.72266680925278</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.2408154545998</v>
+        <v>37.19999975087691</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.218896779690089</v>
+        <v>4.23952472587639</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.46799439785126</v>
+        <v>32.47427223287351</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.03346906389508</v>
+        <v>44.00469347895407</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.339276346585569</v>
+        <v>-1.405825698544718</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="AM7" t="n">
-        <v>200.1130762728213</v>
+        <v>200.4199981689453</v>
       </c>
       <c r="AN7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>246.4197596605268</v>
+        <v>246.3290142644207</v>
       </c>
       <c r="AP7" t="n">
-        <v>218.9125526569474</v>
+        <v>218.6449178044478</v>
       </c>
       <c r="AQ7" t="n">
-        <v>273.9269666641061</v>
+        <v>274.0131107243935</v>
       </c>
       <c r="AR7" t="n">
-        <v>211.6913234739902</v>
+        <v>212.056997680664</v>
       </c>
       <c r="AS7" t="n">
-        <v>287.0982182965959</v>
+        <v>287.3506484175701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11341,13 +12700,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>524.4299999999999</v>
+        <v>507.29</v>
       </c>
       <c r="I8" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>174.22923</v>
+        <v>169.66222</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -11359,49 +12718,49 @@
         <v>73.97735595703125</v>
       </c>
       <c r="N8" t="n">
-        <v>177.8754162397541</v>
+        <v>179.4295113985656</v>
       </c>
       <c r="O8" t="n">
-        <v>124.0132388334195</v>
+        <v>125.602624598074</v>
       </c>
       <c r="P8" t="n">
-        <v>132.5094316590507</v>
+        <v>133.8455581547047</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.57727744203408</v>
+        <v>33.58486969512436</v>
       </c>
       <c r="R8" t="n">
-        <v>76.95094500847583</v>
+        <v>77.46415221016363</v>
       </c>
       <c r="S8" t="n">
         <v>167.680658059042</v>
       </c>
       <c r="T8" t="n">
-        <v>1.495534926953817</v>
+        <v>1.311888234252172</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9193548387096774</v>
       </c>
       <c r="V8" t="n">
-        <v>222.671841430664</v>
+        <v>221.1922943115235</v>
       </c>
       <c r="W8" t="n">
-        <v>535.4050028816598</v>
+        <v>536.4942390817112</v>
       </c>
       <c r="X8" t="n">
-        <v>373.2798488885927</v>
+        <v>375.5518475482413</v>
       </c>
       <c r="Y8" t="n">
-        <v>272.2122437880701</v>
+        <v>275.1330871598195</v>
       </c>
       <c r="Z8" t="n">
-        <v>474.3474539891153</v>
+        <v>475.9706079366632</v>
       </c>
       <c r="AA8" t="n">
-        <v>231.6223444755122</v>
+        <v>231.6178151083893</v>
       </c>
       <c r="AB8" t="n">
-        <v>504.7187807577164</v>
+        <v>501.3651675965356</v>
       </c>
       <c r="AC8" t="n">
         <v>122</v>
@@ -11410,60 +12769,60 @@
         <v>72.05660262197819</v>
       </c>
       <c r="AE8" t="n">
-        <v>177.8754162397541</v>
+        <v>179.4295113985656</v>
       </c>
       <c r="AF8" t="n">
-        <v>109.5855964601589</v>
+        <v>110.1984285150581</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.8743819814597</v>
+        <v>105.8965523254695</v>
       </c>
       <c r="AH8" t="n">
-        <v>31.00646812517777</v>
+        <v>31.54184879705103</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>155.642626152664</v>
+        <v>159.7232826107839</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.084843500358216</v>
+        <v>1.885234815103842</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9590163934426229</v>
       </c>
       <c r="AM8" t="n">
-        <v>216.8903738921543</v>
+        <v>215.4492418397148</v>
       </c>
       <c r="AN8" t="n">
-        <v>535.4050028816598</v>
+        <v>536.4942390817112</v>
       </c>
       <c r="AO8" t="n">
-        <v>329.8526453450783</v>
+        <v>329.4933012600239</v>
       </c>
       <c r="AP8" t="n">
-        <v>236.5231762882932</v>
+        <v>235.1831733568413</v>
       </c>
       <c r="AQ8" t="n">
-        <v>423.1821144018634</v>
+        <v>423.8034291632065</v>
       </c>
       <c r="AR8" t="n">
-        <v>227.3095150699255</v>
+        <v>225.7991528435473</v>
       </c>
       <c r="AS8" t="n">
-        <v>468.4843047195184</v>
+        <v>477.5726150062438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11492,13 +12851,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>379.26</v>
+        <v>376.71</v>
       </c>
       <c r="I9" t="n">
         <v>6.03</v>
       </c>
       <c r="J9" t="n">
-        <v>62.895523</v>
+        <v>62.472633</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -11513,13 +12872,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>74.99901067785036</v>
+        <v>75.05613615223172</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.829003352317653</v>
+        <v>9.761540481703538</v>
       </c>
       <c r="R9" t="n">
         <v>61.29473531920079</v>
@@ -11528,10 +12887,10 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.231405387098214</v>
+        <v>-1.289089890659932</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="V9" t="n">
         <v>344.885442901076</v>
@@ -11540,13 +12899,13 @@
         <v>566.0559735214503</v>
       </c>
       <c r="X9" t="n">
-        <v>452.2440343874377</v>
+        <v>452.5885009979573</v>
       </c>
       <c r="Y9" t="n">
-        <v>392.9751441729622</v>
+        <v>393.7264118932849</v>
       </c>
       <c r="Z9" t="n">
-        <v>511.5129246019132</v>
+        <v>511.4505901026296</v>
       </c>
       <c r="AA9" t="n">
         <v>369.6072539747808</v>
@@ -11564,13 +12923,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.38999481009056</v>
+        <v>72.35695660990616</v>
       </c>
       <c r="AG9" t="n">
         <v>71.47694073882994</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.734558769582204</v>
+        <v>7.758154083548289</v>
       </c>
       <c r="AI9" t="n">
         <v>62.37563283819902</v>
@@ -11579,10 +12938,10 @@
         <v>82.37543771606209</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.227538905959263</v>
+        <v>-1.274056109670026</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.1065573770491803</v>
       </c>
       <c r="AM9" t="n">
         <v>344.885442901076</v>
@@ -11591,13 +12950,13 @@
         <v>566.0559735214503</v>
       </c>
       <c r="AO9" t="n">
-        <v>436.511668704846</v>
+        <v>436.3124483577342</v>
       </c>
       <c r="AP9" t="n">
-        <v>389.8722793242654</v>
+        <v>389.530779233938</v>
       </c>
       <c r="AQ9" t="n">
-        <v>483.1510580854268</v>
+        <v>483.0941174815304</v>
       </c>
       <c r="AR9" t="n">
         <v>376.1250660143401</v>
@@ -11609,12 +12968,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-16 09:12:27</t>
+          <t>2026-06-17 05:57:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -11643,19 +13002,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>78.5899</v>
+        <v>78.72</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>25.35158</v>
+        <v>25.393549</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M10" t="n">
         <v>35.93675816954359</v>
@@ -11664,22 +13023,22 @@
         <v>42.60474344487245</v>
       </c>
       <c r="O10" t="n">
-        <v>38.62337672102367</v>
+        <v>38.68300411540999</v>
       </c>
       <c r="P10" t="n">
-        <v>38.00395317228413</v>
+        <v>38.50000102529411</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.163128444509888</v>
+        <v>2.201545083765738</v>
       </c>
       <c r="R10" t="n">
-        <v>36.29248999795422</v>
+        <v>36.28932787024455</v>
       </c>
       <c r="S10" t="n">
-        <v>42.00790465584855</v>
+        <v>42.06442640704127</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.135464010335611</v>
+        <v>-6.036421971735596</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -11691,22 +13050,22 @@
         <v>132.0747046791046</v>
       </c>
       <c r="X10" t="n">
-        <v>119.7324678351734</v>
+        <v>119.917312757771</v>
       </c>
       <c r="Y10" t="n">
-        <v>113.0267696571927</v>
+        <v>113.0925229980972</v>
       </c>
       <c r="Z10" t="n">
-        <v>126.438166013154</v>
+        <v>126.7421025174447</v>
       </c>
       <c r="AA10" t="n">
-        <v>112.5067189936581</v>
+        <v>112.4969163977581</v>
       </c>
       <c r="AB10" t="n">
-        <v>130.2245044331305</v>
+        <v>130.3997218618279</v>
       </c>
       <c r="AC10" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -11715,25 +13074,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>26.70532199408146</v>
+        <v>26.99005748308434</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.86956666486535</v>
+        <v>32.93478291025274</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.82814270080998</v>
+        <v>14.69717264676027</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.77276523370193</v>
+        <v>3.769172917033795</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.13833859409738</v>
+        <v>39.14426750816374</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.09129545226237379</v>
+        <v>-0.1086269122269761</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.2839506172839506</v>
+        <v>0.275</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -11742,19 +13101,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>82.78649818165253</v>
+        <v>83.66917819756146</v>
       </c>
       <c r="AP10" t="n">
-        <v>36.8192558091416</v>
+        <v>38.10794299260461</v>
       </c>
       <c r="AQ10" t="n">
-        <v>128.7537405541634</v>
+        <v>129.2304134025183</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.69557222447598</v>
+        <v>11.68443604280477</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.3288496417019</v>
+        <v>121.3472292753076</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS73"/>
+  <dimension ref="A1:AS82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10145,7 +10145,7 @@
         <v>246.4197596605268</v>
       </c>
       <c r="AP64" t="n">
-        <v>218.9125526569474</v>
+        <v>218.9125526569473</v>
       </c>
       <c r="AQ64" t="n">
         <v>273.9269666641061</v>
@@ -10387,7 +10387,7 @@
         <v>0.9193548387096774</v>
       </c>
       <c r="V66" t="n">
-        <v>221.1922943115235</v>
+        <v>221.1922943115234</v>
       </c>
       <c r="W66" t="n">
         <v>536.4942390817112</v>
@@ -10429,13 +10429,13 @@
         <v>75.51811131891215</v>
       </c>
       <c r="AJ66" t="n">
-        <v>159.7232826107839</v>
+        <v>159.7232826107838</v>
       </c>
       <c r="AK66" t="n">
         <v>1.885234815103842</v>
       </c>
       <c r="AL66" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9590163934426228</v>
       </c>
       <c r="AM66" t="n">
         <v>215.4492418397148</v>
@@ -10520,7 +10520,7 @@
         <v>31.662931286491</v>
       </c>
       <c r="P67" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q67" t="n">
         <v>2.41126094160941</v>
@@ -10532,7 +10532,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T67" t="n">
-        <v>-0.001119035457521161</v>
+        <v>-0.0011190354575211</v>
       </c>
       <c r="U67" t="n">
         <v>0.4516129032258064</v>
@@ -10547,7 +10547,7 @@
         <v>246.020976096035</v>
       </c>
       <c r="Y67" t="n">
-        <v>227.2854785797299</v>
+        <v>227.28547857973</v>
       </c>
       <c r="Z67" t="n">
         <v>264.7564736123401</v>
@@ -10583,7 +10583,7 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.05044014401427146</v>
+        <v>0.0504401440142714</v>
       </c>
       <c r="AL67" t="n">
         <v>0.4672131147540984</v>
@@ -10665,7 +10665,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N68" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O68" t="n">
         <v>75.05613615223172</v>
@@ -10716,7 +10716,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE68" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF68" t="n">
         <v>72.35695660990616</v>
@@ -10725,7 +10725,7 @@
         <v>71.47694073882994</v>
       </c>
       <c r="AH68" t="n">
-        <v>7.758154083548289</v>
+        <v>7.758154083548288</v>
       </c>
       <c r="AI68" t="n">
         <v>62.37563283819902</v>
@@ -10843,7 +10843,7 @@
         <v>331.002237918088</v>
       </c>
       <c r="W69" t="n">
-        <v>422.3507729952915</v>
+        <v>422.3507729952916</v>
       </c>
       <c r="X69" t="n">
         <v>379.5954526210362</v>
@@ -10964,7 +10964,7 @@
         <v>61</v>
       </c>
       <c r="M70" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="N70" t="n">
         <v>29.31247287326389</v>
@@ -10988,7 +10988,7 @@
         <v>-0.8594184470787313</v>
       </c>
       <c r="U70" t="n">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="V70" t="n">
         <v>566.7738059303977</v>
@@ -11015,7 +11015,7 @@
         <v>121</v>
       </c>
       <c r="AD70" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="AE70" t="n">
         <v>31.43082152229007</v>
@@ -11139,7 +11139,7 @@
         <v>-0.9400881967002434</v>
       </c>
       <c r="U71" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2580645161290322</v>
       </c>
       <c r="V71" t="n">
         <v>374.3965238054668</v>
@@ -11154,7 +11154,7 @@
         <v>392.5868272879635</v>
       </c>
       <c r="Z71" t="n">
-        <v>434.0860118749031</v>
+        <v>434.0860118749032</v>
       </c>
       <c r="AA71" t="n">
         <v>389.4219401579262</v>
@@ -11190,7 +11190,7 @@
         <v>-0.8652354323759147</v>
       </c>
       <c r="AL71" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.1311475409836065</v>
       </c>
       <c r="AM71" t="n">
         <v>374.3965238054668</v>
@@ -11305,7 +11305,7 @@
         <v>113.0925229980972</v>
       </c>
       <c r="Z72" t="n">
-        <v>126.7421025174447</v>
+        <v>126.7421025174448</v>
       </c>
       <c r="AA72" t="n">
         <v>112.4969163977581</v>
@@ -11317,7 +11317,7 @@
         <v>80</v>
       </c>
       <c r="AD72" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE72" t="n">
         <v>42.60474344487245</v>
@@ -11441,7 +11441,7 @@
         <v>-1.278907293744622</v>
       </c>
       <c r="U73" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="V73" t="n">
         <v>200.4199981689453</v>
@@ -11486,13 +11486,13 @@
         <v>32.47427223287351</v>
       </c>
       <c r="AJ73" t="n">
-        <v>44.00469347895407</v>
+        <v>44.00469347895408</v>
       </c>
       <c r="AK73" t="n">
         <v>-1.405825698544718</v>
       </c>
       <c r="AL73" t="n">
-        <v>0.05128205128205128</v>
+        <v>0.0512820512820512</v>
       </c>
       <c r="AM73" t="n">
         <v>200.4199981689453</v>
@@ -11501,7 +11501,7 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO73" t="n">
-        <v>246.3290142644207</v>
+        <v>246.3290142644206</v>
       </c>
       <c r="AP73" t="n">
         <v>218.6449178044478</v>
@@ -11514,6 +11514,1333 @@
       </c>
       <c r="AS73" t="n">
         <v>287.3506484175701</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>295.95</v>
+      </c>
+      <c r="I74" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J74" t="n">
+        <v>35.8293</v>
+      </c>
+      <c r="K74" t="n">
+        <v>67</v>
+      </c>
+      <c r="L74" t="n">
+        <v>62</v>
+      </c>
+      <c r="M74" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N74" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O74" t="n">
+        <v>34.70350438725112</v>
+      </c>
+      <c r="P74" t="n">
+        <v>34.59493709515922</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.950081244083638</v>
+      </c>
+      <c r="R74" t="n">
+        <v>32.01911385451691</v>
+      </c>
+      <c r="S74" t="n">
+        <v>37.38147763305368</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.5773070307529214</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="V74" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="W74" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X74" t="n">
+        <v>286.6509462386942</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>270.5432751625633</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>302.7586173148251</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>264.4778804383097</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>308.7710052490234</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>34.42386485068192</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.708321117507143</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>36.69222629741434</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>0.8226996288431768</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0.7704918032786885</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>284.3411236666326</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>270.2303912360236</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>298.4518560972416</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>265.4011122227922</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>303.0777892166424</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>512.48</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J75" t="n">
+        <v>171.39798</v>
+      </c>
+      <c r="K75" t="n">
+        <v>63</v>
+      </c>
+      <c r="L75" t="n">
+        <v>62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="O75" t="n">
+        <v>127.0633640195864</v>
+      </c>
+      <c r="P75" t="n">
+        <v>133.9908448587141</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>33.42580347530961</v>
+      </c>
+      <c r="R75" t="n">
+        <v>77.68075331202094</v>
+      </c>
+      <c r="S75" t="n">
+        <v>167.9963879194416</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1.326359021202344</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.9516129032258065</v>
+      </c>
+      <c r="V75" t="n">
+        <v>221.1922943115235</v>
+      </c>
+      <c r="W75" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="X75" t="n">
+        <v>379.9194584185634</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>279.9763060273876</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>479.8626108097392</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>232.2654524029426</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>502.3091998791305</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>110.7139063484845</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>105.9187189111568</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>31.96944601810756</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>160.7022915199155</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.898189715803768</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0.9754098360655737</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>331.0345799819687</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>235.4459363878271</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>426.6232235761103</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>225.7991528435473</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>480.4998516445473</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J76" t="n">
+        <v>30.56628</v>
+      </c>
+      <c r="K76" t="n">
+        <v>67</v>
+      </c>
+      <c r="L76" t="n">
+        <v>62</v>
+      </c>
+      <c r="M76" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N76" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O76" t="n">
+        <v>31.6515334084853</v>
+      </c>
+      <c r="P76" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.425128953218685</v>
+      </c>
+      <c r="R76" t="n">
+        <v>28.89025643705661</v>
+      </c>
+      <c r="S76" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T76" t="n">
+        <v>-0.4475033820551787</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="V76" t="n">
+        <v>216.0211675795551</v>
+      </c>
+      <c r="W76" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="X76" t="n">
+        <v>245.9324145839307</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>227.0891626174216</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>264.7756665504399</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>224.4772925159299</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>271.4569227019115</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>31.51178144271168</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>2.357948337747321</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>28.66513197724623</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>-0.4009848000380581</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0.4262295081967213</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>215.4251391678176</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>244.8465418098697</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>226.525283225573</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>263.1678003941664</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>222.7280754632032</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>269.8021464264044</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="I77" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J77" t="n">
+        <v>65.15754</v>
+      </c>
+      <c r="K77" t="n">
+        <v>34</v>
+      </c>
+      <c r="L77" t="n">
+        <v>62</v>
+      </c>
+      <c r="M77" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N77" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O77" t="n">
+        <v>75.10496513901769</v>
+      </c>
+      <c r="P77" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>9.704328927584006</v>
+      </c>
+      <c r="R77" t="n">
+        <v>61.29473531920079</v>
+      </c>
+      <c r="S77" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T77" t="n">
+        <v>-1.025050285624872</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="V77" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="W77" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X77" t="n">
+        <v>452.8829397882767</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>394.3658363549452</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>511.4000432216083</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>369.6072539747808</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>503.467376494826</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>72.30794087549145</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>71.47694073882994</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>7.783390629820148</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>62.37563283819902</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>82.37543771606209</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>-0.9186742919077521</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0.1885245901639344</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>436.0168834792135</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>389.083037981398</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>482.950728977029</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>376.1250660143401</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>496.7238894278544</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>27.64122</v>
+      </c>
+      <c r="K78" t="n">
+        <v>37</v>
+      </c>
+      <c r="L78" t="n">
+        <v>62</v>
+      </c>
+      <c r="M78" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N78" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O78" t="n">
+        <v>28.9552662230043</v>
+      </c>
+      <c r="P78" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.679927861166365</v>
+      </c>
+      <c r="R78" t="n">
+        <v>26.96842149957094</v>
+      </c>
+      <c r="S78" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T78" t="n">
+        <v>-0.7822039585032925</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="V78" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="W78" t="n">
+        <v>422.3507729952915</v>
+      </c>
+      <c r="X78" t="n">
+        <v>379.3139875213564</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>357.306932540077</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>401.3210425026357</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>353.2863216443793</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>408.9926754424794</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>29.67622374554744</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>29.29405020358088</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.997637549235844</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>27.35699505088357</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>32.65449124757065</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>-1.018705193204786</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0.1557377049180328</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>446.0207226104586</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>388.7585310666714</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>362.5894791716818</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>414.927582961661</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>358.3766351665748</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>427.7738353431754</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>567.58</v>
+      </c>
+      <c r="I79" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J79" t="n">
+        <v>20.646782</v>
+      </c>
+      <c r="K79" t="n">
+        <v>55</v>
+      </c>
+      <c r="L79" t="n">
+        <v>62</v>
+      </c>
+      <c r="M79" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="N79" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O79" t="n">
+        <v>24.03322076144743</v>
+      </c>
+      <c r="P79" t="n">
+        <v>22.7372725053267</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.720813055804332</v>
+      </c>
+      <c r="R79" t="n">
+        <v>21.56538174715909</v>
+      </c>
+      <c r="S79" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T79" t="n">
+        <v>-1.244642205102301</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="V79" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="W79" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X79" t="n">
+        <v>660.6732387321899</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>585.8780878281289</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>735.468389636251</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>592.8323442294034</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>785.6089876800964</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>26.10909791497354</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>27.22584093921283</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>2.974413990681105</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>21.91450861150568</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>29.29193974808321</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>-1.836434313477235</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>717.7391016826225</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>635.972461078799</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>799.5057422864461</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>602.4298417302913</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>805.2354236748073</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="I80" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J80" t="n">
+        <v>22.581049</v>
+      </c>
+      <c r="K80" t="n">
+        <v>67</v>
+      </c>
+      <c r="L80" t="n">
+        <v>62</v>
+      </c>
+      <c r="M80" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N80" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O80" t="n">
+        <v>24.6040573176406</v>
+      </c>
+      <c r="P80" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1.263952497311645</v>
+      </c>
+      <c r="R80" t="n">
+        <v>23.19493411256791</v>
+      </c>
+      <c r="S80" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T80" t="n">
+        <v>-1.600541414288447</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="V80" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="W80" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X80" t="n">
+        <v>412.8560817900092</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>391.6469588851198</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>434.0652046948986</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>389.2109944088896</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>444.9722332485025</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>26.61588072770907</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>25.11874429557403</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>3.698958970643893</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>23.3207632974955</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>33.90867664668163</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>-1.090801968805485</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0.02459016393442623</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>582.4306839010962</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>446.6144786109582</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>384.5459470835536</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>508.6830101383628</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>391.3224081319746</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>568.9875941313179</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="I81" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>24.825808</v>
+      </c>
+      <c r="K81" t="n">
+        <v>67</v>
+      </c>
+      <c r="L81" t="n">
+        <v>19</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>27.28179525407055</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>32.99999915564012</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>14.55609959473293</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>3.76558060036566</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>39.1501964222301</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>-0.1687256423389164</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>84.57356528761872</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>39.44965654394665</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>129.6974740312908</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>11.67329986113355</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>121.3656089089133</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-06-18 05:04:25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>204.65</v>
+      </c>
+      <c r="I82" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J82" t="n">
+        <v>31.339968</v>
+      </c>
+      <c r="K82" t="n">
+        <v>65</v>
+      </c>
+      <c r="L82" t="n">
+        <v>62</v>
+      </c>
+      <c r="M82" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N82" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O82" t="n">
+        <v>37.74143885132728</v>
+      </c>
+      <c r="P82" t="n">
+        <v>36.40612232441805</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4.807445815012896</v>
+      </c>
+      <c r="R82" t="n">
+        <v>31.8889742934503</v>
+      </c>
+      <c r="S82" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T82" t="n">
+        <v>-1.331574207521278</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="V82" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="W82" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X82" t="n">
+        <v>246.4515956991671</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>215.0589745271329</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>277.8442168712014</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>208.2350021362304</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>37.64187315897667</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>37.15918404715401</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>4.273034170005802</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>32.25727402597985</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>43.97591789401307</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>-1.474808042306883</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0.01265822784810127</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>245.8014317281177</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>217.8985185979798</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>273.7043448582556</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>210.6399993896484</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>287.1627438479053</v>
       </c>
     </row>
   </sheetData>
@@ -11760,12 +13087,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11794,19 +13121,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>371.1</v>
+        <v>362.1</v>
       </c>
       <c r="I2" t="n">
         <v>13.1</v>
       </c>
       <c r="J2" t="n">
-        <v>28.328243</v>
+        <v>27.64122</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -11815,25 +13142,25 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.97675210847605</v>
+        <v>28.9552662230043</v>
       </c>
       <c r="P2" t="n">
-        <v>29.2311213745769</v>
+        <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.685097699409057</v>
+        <v>1.679927861166365</v>
       </c>
       <c r="R2" t="n">
-        <v>26.95042008575277</v>
+        <v>26.96842149957094</v>
       </c>
       <c r="S2" t="n">
-        <v>31.24236919392489</v>
+        <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3848495601788979</v>
+        <v>-0.7822039585032925</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3770491803278688</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="V2" t="n">
         <v>331.002237918088</v>
@@ -11842,22 +13169,22 @@
         <v>422.3507729952915</v>
       </c>
       <c r="X2" t="n">
-        <v>379.5954526210362</v>
+        <v>379.3139875213564</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.5206727587776</v>
+        <v>357.306932540077</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.6702324832949</v>
+        <v>401.3210425026357</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.0505031233612</v>
+        <v>353.2863216443793</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.2750364404161</v>
+        <v>408.9926754424794</v>
       </c>
       <c r="AC2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -11866,25 +13193,25 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.71105352646061</v>
+        <v>29.67622374554744</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.35392727477236</v>
+        <v>29.29405020358088</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.994219353477789</v>
+        <v>1.997637549235844</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.33714833321415</v>
+        <v>27.35699505088357</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65942708172662</v>
+        <v>32.65449124757065</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.6934094406661305</v>
+        <v>-1.018705193204786</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2892561983471074</v>
+        <v>0.1557377049180328</v>
       </c>
       <c r="AM2" t="n">
         <v>331.002237918088</v>
@@ -11893,30 +13220,30 @@
         <v>446.0207226104586</v>
       </c>
       <c r="AO2" t="n">
-        <v>389.2148011966339</v>
+        <v>388.7585310666714</v>
       </c>
       <c r="AP2" t="n">
-        <v>363.0905276660749</v>
+        <v>362.5894791716818</v>
       </c>
       <c r="AQ2" t="n">
-        <v>415.339074727193</v>
+        <v>414.927582961661</v>
       </c>
       <c r="AR2" t="n">
-        <v>358.1166431651054</v>
+        <v>358.3766351665748</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.8384947706187</v>
+        <v>427.7738353431754</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11945,13 +13272,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>393.83</v>
+        <v>378.91</v>
       </c>
       <c r="I3" t="n">
         <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>23.470201</v>
+        <v>22.581049</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -11966,25 +13293,25 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.6326829309555</v>
+        <v>24.6040573176406</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.236566882805114</v>
+        <v>1.263952497311645</v>
       </c>
       <c r="R3" t="n">
-        <v>23.20750537293958</v>
+        <v>23.19493411256791</v>
       </c>
       <c r="S3" t="n">
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9400881967002434</v>
+        <v>-1.600541414288447</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="V3" t="n">
         <v>374.3965238054668</v>
@@ -11993,16 +13320,16 @@
         <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>413.3364195814333</v>
+        <v>412.8560817900092</v>
       </c>
       <c r="Y3" t="n">
-        <v>392.5868272879635</v>
+        <v>391.6469588851198</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.0860118749031</v>
+        <v>434.0652046948986</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.4219401579262</v>
+        <v>389.2109944088896</v>
       </c>
       <c r="AB3" t="n">
         <v>444.9722332485025</v>
@@ -12017,25 +13344,25 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.71429293477805</v>
+        <v>26.61588072770907</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.12695427012488</v>
+        <v>25.11874429557403</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.749374809894066</v>
+        <v>3.698958970643893</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.33389654392149</v>
+        <v>23.3207632974955</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33.99836316386802</v>
+        <v>33.90867664668163</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8652354323759147</v>
+        <v>-1.090801968805485</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.02459016393442623</v>
       </c>
       <c r="AM3" t="n">
         <v>374.3965238054668</v>
@@ -12044,30 +13371,30 @@
         <v>582.4306839010962</v>
       </c>
       <c r="AO3" t="n">
-        <v>448.2658354455758</v>
+        <v>446.6144786109582</v>
       </c>
       <c r="AP3" t="n">
-        <v>385.3513261355534</v>
+        <v>384.5459470835536</v>
       </c>
       <c r="AQ3" t="n">
-        <v>511.1803447555982</v>
+        <v>508.6830101383628</v>
       </c>
       <c r="AR3" t="n">
-        <v>391.5427840070027</v>
+        <v>391.3224081319746</v>
       </c>
       <c r="AS3" t="n">
-        <v>570.4925338897054</v>
+        <v>568.9875941313179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -12096,19 +13423,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>600.21</v>
+        <v>567.58</v>
       </c>
       <c r="I4" t="n">
         <v>27.49</v>
       </c>
       <c r="J4" t="n">
-        <v>21.83376</v>
+        <v>20.646782</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
         <v>20.61745383522727</v>
@@ -12117,25 +13444,25 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.15446897245624</v>
+        <v>24.03322076144743</v>
       </c>
       <c r="P4" t="n">
-        <v>22.83439782387452</v>
+        <v>22.7372725053267</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.700324830523031</v>
+        <v>2.720813055804332</v>
       </c>
       <c r="R4" t="n">
-        <v>21.58109019886364</v>
+        <v>21.56538174715909</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57982234378326</v>
+        <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8594184470787313</v>
+        <v>-1.244642205102301</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1475409836065574</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="V4" t="n">
         <v>566.7738059303977</v>
@@ -12144,22 +13471,22 @@
         <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>664.0063520528221</v>
+        <v>660.6732387321899</v>
       </c>
       <c r="Y4" t="n">
-        <v>589.7744224617439</v>
+        <v>585.8780878281289</v>
       </c>
       <c r="Z4" t="n">
-        <v>738.2382816439002</v>
+        <v>735.468389636251</v>
       </c>
       <c r="AA4" t="n">
-        <v>593.2641695667613</v>
+        <v>592.8323442294034</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.6593162306017</v>
+        <v>785.6089876800964</v>
       </c>
       <c r="AC4" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD4" t="n">
         <v>20.61745383522727</v>
@@ -12168,25 +13495,25 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.21503956803088</v>
+        <v>26.10909791497354</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.25952256560009</v>
+        <v>27.22584093921283</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.930130264166549</v>
+        <v>2.974413990681105</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.99854625355114</v>
+        <v>21.91450861150568</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.29583702391497</v>
+        <v>29.29193974808321</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.495250781718095</v>
+        <v>-1.836434313477235</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0743801652892562</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="AM4" t="n">
         <v>566.7738059303977</v>
@@ -12195,30 +13522,30 @@
         <v>864.0332836477539</v>
       </c>
       <c r="AO4" t="n">
-        <v>720.6514377251689</v>
+        <v>717.7391016826225</v>
       </c>
       <c r="AP4" t="n">
-        <v>640.1021567632305</v>
+        <v>635.972461078799</v>
       </c>
       <c r="AQ4" t="n">
-        <v>801.2007186871074</v>
+        <v>799.5057422864461</v>
       </c>
       <c r="AR4" t="n">
-        <v>604.7400365101207</v>
+        <v>602.4298417302913</v>
       </c>
       <c r="AS4" t="n">
-        <v>805.3425597874225</v>
+        <v>805.2354236748073</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -12247,13 +13574,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>246</v>
+        <v>237.5</v>
       </c>
       <c r="I5" t="n">
         <v>7.77</v>
       </c>
       <c r="J5" t="n">
-        <v>31.660233</v>
+        <v>30.56628</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -12268,25 +13595,25 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.662931286491</v>
+        <v>31.6515334084853</v>
       </c>
       <c r="P5" t="n">
         <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.41126094160941</v>
+        <v>2.425128953218685</v>
       </c>
       <c r="R5" t="n">
-        <v>28.90795038667516</v>
+        <v>28.89025643705661</v>
       </c>
       <c r="S5" t="n">
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001119035457521161</v>
+        <v>-0.4475033820551787</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="V5" t="n">
         <v>216.0211675795551</v>
@@ -12295,16 +13622,16 @@
         <v>286.0812028062892</v>
       </c>
       <c r="X5" t="n">
-        <v>246.020976096035</v>
+        <v>245.9324145839307</v>
       </c>
       <c r="Y5" t="n">
-        <v>227.2854785797299</v>
+        <v>227.0891626174216</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.7564736123401</v>
+        <v>264.7756665504399</v>
       </c>
       <c r="AA5" t="n">
-        <v>224.614774504466</v>
+        <v>224.4772925159299</v>
       </c>
       <c r="AB5" t="n">
         <v>271.4569227019115</v>
@@ -12319,25 +13646,25 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.54212973675997</v>
+        <v>31.51178144271168</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.76495310222133</v>
+        <v>31.71949797269831</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.341453727939681</v>
+        <v>2.357948337747321</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.86711905294752</v>
+        <v>28.66513197724623</v>
       </c>
       <c r="AJ5" t="n">
         <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.05044014401427146</v>
+        <v>-0.4009848000380581</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4672131147540984</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="AM5" t="n">
         <v>215.4251391678176</v>
@@ -12346,16 +13673,16 @@
         <v>286.0812028062892</v>
       </c>
       <c r="AO5" t="n">
-        <v>245.082348054625</v>
+        <v>244.8465418098697</v>
       </c>
       <c r="AP5" t="n">
-        <v>226.8892525885337</v>
+        <v>226.525283225573</v>
       </c>
       <c r="AQ5" t="n">
-        <v>263.2754435207163</v>
+        <v>263.1678003941664</v>
       </c>
       <c r="AR5" t="n">
-        <v>224.2975150414022</v>
+        <v>222.7280754632032</v>
       </c>
       <c r="AS5" t="n">
         <v>269.8021464264044</v>
@@ -12364,12 +13691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12398,13 +13725,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>299.24</v>
+        <v>295.95</v>
       </c>
       <c r="I6" t="n">
         <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>36.2276</v>
+        <v>35.8293</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -12419,25 +13746,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.6339015743772</v>
+        <v>34.70350438725112</v>
       </c>
       <c r="P6" t="n">
-        <v>34.57088615320906</v>
+        <v>34.59493709515922</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.985923699247501</v>
+        <v>1.950081244083638</v>
       </c>
       <c r="R6" t="n">
-        <v>31.98063234739666</v>
+        <v>32.01911385451691</v>
       </c>
       <c r="S6" t="n">
         <v>37.38147763305368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8024973095525688</v>
+        <v>0.5773070307529214</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7580645161290323</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="V6" t="n">
         <v>257.8688405483584</v>
@@ -12446,16 +13773,16 @@
         <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>286.0760270043556</v>
+        <v>286.6509462386942</v>
       </c>
       <c r="Y6" t="n">
-        <v>269.6722972485713</v>
+        <v>270.5432751625633</v>
       </c>
       <c r="Z6" t="n">
-        <v>302.47975676014</v>
+        <v>302.7586173148251</v>
       </c>
       <c r="AA6" t="n">
-        <v>264.1600231894964</v>
+        <v>264.4778804383097</v>
       </c>
       <c r="AB6" t="n">
         <v>308.7710052490234</v>
@@ -12470,25 +13797,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.43087869573493</v>
+        <v>34.42386485068192</v>
       </c>
       <c r="AG6" t="n">
         <v>34.42623029342849</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.715878971266023</v>
+        <v>1.708321117507143</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13088525699663</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.6958458621764</v>
+        <v>36.69222629741434</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.047114239612952</v>
+        <v>0.8226996288431768</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.7704918032786885</v>
       </c>
       <c r="AM6" t="n">
         <v>257.8688405483584</v>
@@ -12497,30 +13824,30 @@
         <v>315.2000122070312</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.3990580267705</v>
+        <v>284.3411236666326</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.2258977241131</v>
+        <v>270.2303912360236</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.5722183294278</v>
+        <v>298.4518560972416</v>
       </c>
       <c r="AR6" t="n">
         <v>265.4011122227922</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.107686821577</v>
+        <v>303.0777892166424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -12549,13 +13876,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>207.41</v>
+        <v>204.65</v>
       </c>
       <c r="I7" t="n">
         <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.762634</v>
+        <v>31.339968</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -12570,25 +13897,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.82371058343767</v>
+        <v>37.74143885132728</v>
       </c>
       <c r="P7" t="n">
-        <v>36.45306022799745</v>
+        <v>36.40612232441805</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.739261878545491</v>
+        <v>4.807445815012896</v>
       </c>
       <c r="R7" t="n">
-        <v>31.98928015155412</v>
+        <v>31.8889742934503</v>
       </c>
       <c r="S7" t="n">
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.278907293744622</v>
+        <v>-1.331574207521278</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="V7" t="n">
         <v>200.4199981689453</v>
@@ -12597,22 +13924,22 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>246.988830109848</v>
+        <v>246.4515956991671</v>
       </c>
       <c r="Y7" t="n">
-        <v>216.0414500429459</v>
+        <v>215.0589745271329</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.93621017675</v>
+        <v>277.8442168712014</v>
       </c>
       <c r="AA7" t="n">
-        <v>208.8899993896484</v>
+        <v>208.2350021362304</v>
       </c>
       <c r="AB7" t="n">
         <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AD7" t="n">
         <v>30.69218961239591</v>
@@ -12621,25 +13948,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.72266680925278</v>
+        <v>37.64187315897667</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.19999975087691</v>
+        <v>37.15918404715401</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.23952472587639</v>
+        <v>4.273034170005802</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.47427223287351</v>
+        <v>32.25727402597985</v>
       </c>
       <c r="AJ7" t="n">
-        <v>44.00469347895407</v>
+        <v>43.97591789401307</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.405825698544718</v>
+        <v>-1.474808042306883</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.05128205128205128</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="AM7" t="n">
         <v>200.4199981689453</v>
@@ -12648,30 +13975,30 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>246.3290142644207</v>
+        <v>245.8014317281177</v>
       </c>
       <c r="AP7" t="n">
-        <v>218.6449178044478</v>
+        <v>217.8985185979798</v>
       </c>
       <c r="AQ7" t="n">
-        <v>274.0131107243935</v>
+        <v>273.7043448582556</v>
       </c>
       <c r="AR7" t="n">
-        <v>212.056997680664</v>
+        <v>210.6399993896484</v>
       </c>
       <c r="AS7" t="n">
-        <v>287.3506484175701</v>
+        <v>287.1627438479053</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12700,13 +14027,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>507.29</v>
+        <v>512.48</v>
       </c>
       <c r="I8" t="n">
         <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>169.66222</v>
+        <v>171.39798</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -12721,25 +14048,25 @@
         <v>179.4295113985656</v>
       </c>
       <c r="O8" t="n">
-        <v>125.602624598074</v>
+        <v>127.0633640195864</v>
       </c>
       <c r="P8" t="n">
-        <v>133.8455581547047</v>
+        <v>133.9908448587141</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.58486969512436</v>
+        <v>33.42580347530961</v>
       </c>
       <c r="R8" t="n">
-        <v>77.46415221016363</v>
+        <v>77.68075331202094</v>
       </c>
       <c r="S8" t="n">
-        <v>167.680658059042</v>
+        <v>167.9963879194416</v>
       </c>
       <c r="T8" t="n">
-        <v>1.311888234252172</v>
+        <v>1.326359021202344</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9516129032258065</v>
       </c>
       <c r="V8" t="n">
         <v>221.1922943115235</v>
@@ -12748,19 +14075,19 @@
         <v>536.4942390817112</v>
       </c>
       <c r="X8" t="n">
-        <v>375.5518475482413</v>
+        <v>379.9194584185634</v>
       </c>
       <c r="Y8" t="n">
-        <v>275.1330871598195</v>
+        <v>279.9763060273876</v>
       </c>
       <c r="Z8" t="n">
-        <v>475.9706079366632</v>
+        <v>479.8626108097392</v>
       </c>
       <c r="AA8" t="n">
-        <v>231.6178151083893</v>
+        <v>232.2654524029426</v>
       </c>
       <c r="AB8" t="n">
-        <v>501.3651675965356</v>
+        <v>502.3091998791305</v>
       </c>
       <c r="AC8" t="n">
         <v>122</v>
@@ -12772,25 +14099,25 @@
         <v>179.4295113985656</v>
       </c>
       <c r="AF8" t="n">
-        <v>110.1984285150581</v>
+        <v>110.7139063484845</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.8965523254695</v>
+        <v>105.9187189111568</v>
       </c>
       <c r="AH8" t="n">
-        <v>31.54184879705103</v>
+        <v>31.96944601810756</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>159.7232826107839</v>
+        <v>160.7022915199155</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.885234815103842</v>
+        <v>1.898189715803768</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9590163934426229</v>
+        <v>0.9754098360655737</v>
       </c>
       <c r="AM8" t="n">
         <v>215.4492418397148</v>
@@ -12799,30 +14126,30 @@
         <v>536.4942390817112</v>
       </c>
       <c r="AO8" t="n">
-        <v>329.4933012600239</v>
+        <v>331.0345799819687</v>
       </c>
       <c r="AP8" t="n">
-        <v>235.1831733568413</v>
+        <v>235.4459363878271</v>
       </c>
       <c r="AQ8" t="n">
-        <v>423.8034291632065</v>
+        <v>426.6232235761103</v>
       </c>
       <c r="AR8" t="n">
         <v>225.7991528435473</v>
       </c>
       <c r="AS8" t="n">
-        <v>477.5726150062438</v>
+        <v>480.4998516445473</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -12851,13 +14178,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>376.71</v>
+        <v>392.9</v>
       </c>
       <c r="I9" t="n">
         <v>6.03</v>
       </c>
       <c r="J9" t="n">
-        <v>62.472633</v>
+        <v>65.15754</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -12872,13 +14199,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.05613615223172</v>
+        <v>75.10496513901769</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.761540481703538</v>
+        <v>9.704328927584006</v>
       </c>
       <c r="R9" t="n">
         <v>61.29473531920079</v>
@@ -12887,10 +14214,10 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.289089890659932</v>
+        <v>-1.025050285624872</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="V9" t="n">
         <v>344.885442901076</v>
@@ -12899,13 +14226,13 @@
         <v>566.0559735214503</v>
       </c>
       <c r="X9" t="n">
-        <v>452.5885009979573</v>
+        <v>452.8829397882767</v>
       </c>
       <c r="Y9" t="n">
-        <v>393.7264118932849</v>
+        <v>394.3658363549452</v>
       </c>
       <c r="Z9" t="n">
-        <v>511.4505901026296</v>
+        <v>511.4000432216083</v>
       </c>
       <c r="AA9" t="n">
         <v>369.6072539747808</v>
@@ -12923,13 +14250,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.35695660990616</v>
+        <v>72.30794087549145</v>
       </c>
       <c r="AG9" t="n">
         <v>71.47694073882994</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.758154083548289</v>
+        <v>7.783390629820148</v>
       </c>
       <c r="AI9" t="n">
         <v>62.37563283819902</v>
@@ -12938,10 +14265,10 @@
         <v>82.37543771606209</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.274056109670026</v>
+        <v>-0.9186742919077521</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1065573770491803</v>
+        <v>0.1885245901639344</v>
       </c>
       <c r="AM9" t="n">
         <v>344.885442901076</v>
@@ -12950,13 +14277,13 @@
         <v>566.0559735214503</v>
       </c>
       <c r="AO9" t="n">
-        <v>436.3124483577342</v>
+        <v>436.0168834792135</v>
       </c>
       <c r="AP9" t="n">
-        <v>389.530779233938</v>
+        <v>389.083037981398</v>
       </c>
       <c r="AQ9" t="n">
-        <v>483.0941174815304</v>
+        <v>482.950728977029</v>
       </c>
       <c r="AR9" t="n">
         <v>376.1250660143401</v>
@@ -12968,12 +14295,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-17 05:57:56</t>
+          <t>2026-06-18 05:04:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13002,70 +14329,38 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>78.72</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>25.393549</v>
+        <v>24.825808</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
-      </c>
-      <c r="M10" t="n">
-        <v>35.93675816954359</v>
-      </c>
-      <c r="N10" t="n">
-        <v>42.60474344487245</v>
-      </c>
-      <c r="O10" t="n">
-        <v>38.68300411540999</v>
-      </c>
-      <c r="P10" t="n">
-        <v>38.50000102529411</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.201545083765738</v>
-      </c>
-      <c r="R10" t="n">
-        <v>36.28932787024455</v>
-      </c>
-      <c r="S10" t="n">
-        <v>42.06442640704127</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-6.036421971735596</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>111.4039503255851</v>
-      </c>
-      <c r="W10" t="n">
-        <v>132.0747046791046</v>
-      </c>
-      <c r="X10" t="n">
-        <v>119.917312757771</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>113.0925229980972</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>126.7421025174447</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>112.4969163977581</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>130.3997218618279</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -13074,25 +14369,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>26.99005748308434</v>
+        <v>27.28179525407055</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.93478291025274</v>
+        <v>32.99999915564012</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.69717264676027</v>
+        <v>14.55609959473293</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.769172917033795</v>
+        <v>3.76558060036566</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.14426750816374</v>
+        <v>39.1501964222301</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.1086269122269761</v>
+        <v>-0.1687256423389164</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.275</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -13101,19 +14396,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>83.66917819756146</v>
+        <v>84.57356528761872</v>
       </c>
       <c r="AP10" t="n">
-        <v>38.10794299260461</v>
+        <v>39.44965654394665</v>
       </c>
       <c r="AQ10" t="n">
-        <v>129.2304134025183</v>
+        <v>129.6974740312908</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.68443604280477</v>
+        <v>11.67329986113355</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.3472292753076</v>
+        <v>121.3656089089133</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS82"/>
+  <dimension ref="A1:AS91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11743,10 +11743,10 @@
         <v>1.326359021202344</v>
       </c>
       <c r="U75" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9516129032258064</v>
       </c>
       <c r="V75" t="n">
-        <v>221.1922943115235</v>
+        <v>221.1922943115234</v>
       </c>
       <c r="W75" t="n">
         <v>536.4942390817112</v>
@@ -11794,7 +11794,7 @@
         <v>1.898189715803768</v>
       </c>
       <c r="AL75" t="n">
-        <v>0.9754098360655737</v>
+        <v>0.9754098360655736</v>
       </c>
       <c r="AM75" t="n">
         <v>215.4492418397148</v>
@@ -11806,7 +11806,7 @@
         <v>331.0345799819687</v>
       </c>
       <c r="AP75" t="n">
-        <v>235.4459363878271</v>
+        <v>235.445936387827</v>
       </c>
       <c r="AQ75" t="n">
         <v>426.6232235761103</v>
@@ -11879,7 +11879,7 @@
         <v>31.6515334084853</v>
       </c>
       <c r="P76" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q76" t="n">
         <v>2.425128953218685</v>
@@ -11912,7 +11912,7 @@
         <v>264.7756665504399</v>
       </c>
       <c r="AA76" t="n">
-        <v>224.4772925159299</v>
+        <v>224.4772925159298</v>
       </c>
       <c r="AB76" t="n">
         <v>271.4569227019115</v>
@@ -11930,7 +11930,7 @@
         <v>31.51178144271168</v>
       </c>
       <c r="AG76" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="AH76" t="n">
         <v>2.357948337747321</v>
@@ -12024,7 +12024,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N77" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O77" t="n">
         <v>75.10496513901769</v>
@@ -12045,7 +12045,7 @@
         <v>-1.025050285624872</v>
       </c>
       <c r="U77" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2580645161290322</v>
       </c>
       <c r="V77" t="n">
         <v>344.885442901076</v>
@@ -12075,7 +12075,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE77" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF77" t="n">
         <v>72.30794087549145</v>
@@ -12093,7 +12093,7 @@
         <v>82.37543771606209</v>
       </c>
       <c r="AK77" t="n">
-        <v>-0.9186742919077521</v>
+        <v>-0.918674291907752</v>
       </c>
       <c r="AL77" t="n">
         <v>0.1885245901639344</v>
@@ -12202,7 +12202,7 @@
         <v>331.002237918088</v>
       </c>
       <c r="W78" t="n">
-        <v>422.3507729952915</v>
+        <v>422.3507729952916</v>
       </c>
       <c r="X78" t="n">
         <v>379.3139875213564</v>
@@ -12323,7 +12323,7 @@
         <v>62</v>
       </c>
       <c r="M79" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="N79" t="n">
         <v>29.31247287326389</v>
@@ -12347,7 +12347,7 @@
         <v>-1.244642205102301</v>
       </c>
       <c r="U79" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="V79" t="n">
         <v>566.7738059303977</v>
@@ -12374,7 +12374,7 @@
         <v>122</v>
       </c>
       <c r="AD79" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="AE79" t="n">
         <v>31.43082152229007</v>
@@ -12398,7 +12398,7 @@
         <v>-1.836434313477235</v>
       </c>
       <c r="AL79" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="AM79" t="n">
         <v>566.7738059303977</v>
@@ -12498,7 +12498,7 @@
         <v>-1.600541414288447</v>
       </c>
       <c r="U80" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.0483870967741935</v>
       </c>
       <c r="V80" t="n">
         <v>374.3965238054668</v>
@@ -12549,7 +12549,7 @@
         <v>-1.090801968805485</v>
       </c>
       <c r="AL80" t="n">
-        <v>0.02459016393442623</v>
+        <v>0.0245901639344262</v>
       </c>
       <c r="AM80" t="n">
         <v>374.3965238054668</v>
@@ -12644,7 +12644,7 @@
         <v>79</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE81" t="n">
         <v>42.60474344487245</v>
@@ -12665,10 +12665,10 @@
         <v>39.1501964222301</v>
       </c>
       <c r="AK81" t="n">
-        <v>-0.1687256423389164</v>
+        <v>-0.1687256423389163</v>
       </c>
       <c r="AL81" t="n">
-        <v>0.2658227848101266</v>
+        <v>0.2658227848101265</v>
       </c>
       <c r="AM81" t="n">
         <v>10.81762752038992</v>
@@ -12768,7 +12768,7 @@
         <v>-1.331574207521278</v>
       </c>
       <c r="U82" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="V82" t="n">
         <v>200.4199981689453</v>
@@ -12777,13 +12777,13 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X82" t="n">
-        <v>246.4515956991671</v>
+        <v>246.4515956991672</v>
       </c>
       <c r="Y82" t="n">
         <v>215.0589745271329</v>
       </c>
       <c r="Z82" t="n">
-        <v>277.8442168712014</v>
+        <v>277.8442168712013</v>
       </c>
       <c r="AA82" t="n">
         <v>208.2350021362304</v>
@@ -12819,7 +12819,7 @@
         <v>-1.474808042306883</v>
       </c>
       <c r="AL82" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.0126582278481012</v>
       </c>
       <c r="AM82" t="n">
         <v>200.4199981689453</v>
@@ -12840,6 +12840,1333 @@
         <v>210.6399993896484</v>
       </c>
       <c r="AS82" t="n">
+        <v>287.1627438479053</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="I83" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J83" t="n">
+        <v>36.078693</v>
+      </c>
+      <c r="K83" t="n">
+        <v>67</v>
+      </c>
+      <c r="L83" t="n">
+        <v>61</v>
+      </c>
+      <c r="M83" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N83" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O83" t="n">
+        <v>34.75780544383156</v>
+      </c>
+      <c r="P83" t="n">
+        <v>34.611391477947</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.918420379816403</v>
+      </c>
+      <c r="R83" t="n">
+        <v>32.08860759493671</v>
+      </c>
+      <c r="S83" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.6885287344032743</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0.7049180327868853</v>
+      </c>
+      <c r="V83" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="W83" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X83" t="n">
+        <v>287.0994729660487</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>271.2533206287652</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>302.9456253033322</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>265.0518987341772</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>308.8200073242188</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>34.42386485068192</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.708321117507143</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>36.69222629741434</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0.9686868190992587</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0.7868852459016393</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>284.3411236666326</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>270.2303912360236</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>298.4518560972416</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>265.4011122227922</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>303.0777892166424</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>537.37</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J84" t="n">
+        <v>179.72241</v>
+      </c>
+      <c r="K84" t="n">
+        <v>63</v>
+      </c>
+      <c r="L84" t="n">
+        <v>61</v>
+      </c>
+      <c r="M84" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N84" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="O84" t="n">
+        <v>127.9009013707825</v>
+      </c>
+      <c r="P84" t="n">
+        <v>134.0603810436321</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>33.04072980407927</v>
+      </c>
+      <c r="R84" t="n">
+        <v>79.32453083542158</v>
+      </c>
+      <c r="S84" t="n">
+        <v>168.0262231045082</v>
+      </c>
+      <c r="T84" t="n">
+        <v>1.568412953845212</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" t="n">
+        <v>221.1922943115235</v>
+      </c>
+      <c r="W84" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="X84" t="n">
+        <v>382.4236950986397</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>283.6319129844427</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>481.2154772128368</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>237.1803471979105</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>502.3984070824796</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>110.7139063484845</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>105.9187189111568</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>31.96944601810756</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>160.7022915199155</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>2.158576773974405</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>331.0345799819687</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>235.4459363878271</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>426.6232235761103</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>225.7991528435473</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>480.4998516445473</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>244.39</v>
+      </c>
+      <c r="I85" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J85" t="n">
+        <v>31.453024</v>
+      </c>
+      <c r="K85" t="n">
+        <v>67</v>
+      </c>
+      <c r="L85" t="n">
+        <v>61</v>
+      </c>
+      <c r="M85" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N85" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O85" t="n">
+        <v>31.7008543482426</v>
+      </c>
+      <c r="P85" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2.413698246265196</v>
+      </c>
+      <c r="R85" t="n">
+        <v>28.90376645650824</v>
+      </c>
+      <c r="S85" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T85" t="n">
+        <v>-0.1026766078262194</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0.4262295081967213</v>
+      </c>
+      <c r="V85" t="n">
+        <v>216.0211675795551</v>
+      </c>
+      <c r="W85" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="X85" t="n">
+        <v>246.315638285845</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>227.5612029123645</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>265.0700736593256</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>224.582265367069</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>271.5273613710284</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>31.51178144271168</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>2.357948337747321</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>28.66513197724623</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>-0.02491888468083014</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>0.459016393442623</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>215.4251391678176</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>244.8465418098697</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>226.525283225573</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>263.1678003941664</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>222.7280754632032</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>269.8021464264044</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J86" t="n">
+        <v>68.21725000000001</v>
+      </c>
+      <c r="K86" t="n">
+        <v>34</v>
+      </c>
+      <c r="L86" t="n">
+        <v>61</v>
+      </c>
+      <c r="M86" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N86" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O86" t="n">
+        <v>75.34392740341401</v>
+      </c>
+      <c r="P86" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>9.5991758213117</v>
+      </c>
+      <c r="R86" t="n">
+        <v>61.31578709414597</v>
+      </c>
+      <c r="S86" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T86" t="n">
+        <v>-0.7424259682369446</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0.2950819672131147</v>
+      </c>
+      <c r="V86" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="W86" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X86" t="n">
+        <v>454.3238822425865</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>396.4408520400769</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>512.2069124450961</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>369.7341961777002</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>503.5931492855676</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>72.30794087549145</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>71.47694073882994</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>7.783390629820148</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>62.37563283819902</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>82.37543771606209</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>-0.525566693237645</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>0.3032786885245902</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>436.0168834792135</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>389.083037981398</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>482.950728977029</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>376.1250660143401</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>496.7238894278544</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="I87" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>28.05038</v>
+      </c>
+      <c r="K87" t="n">
+        <v>37</v>
+      </c>
+      <c r="L87" t="n">
+        <v>61</v>
+      </c>
+      <c r="M87" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N87" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O87" t="n">
+        <v>28.9768255249951</v>
+      </c>
+      <c r="P87" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1.685198939276353</v>
+      </c>
+      <c r="R87" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S87" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T87" t="n">
+        <v>-0.5497543959960779</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0.3278688524590164</v>
+      </c>
+      <c r="V87" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="W87" t="n">
+        <v>422.3507729952915</v>
+      </c>
+      <c r="X87" t="n">
+        <v>379.5964143774358</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>357.5203082729156</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>401.6725204819561</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>353.0505031233612</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>409.2750364404161</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>29.67622374554744</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>29.29405020358088</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>1.997637549235844</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>27.35699505088357</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>32.65449124757065</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>-0.8138832523294173</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0.2131147540983606</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>446.0207226104586</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>388.7585310666714</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>362.5894791716818</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>414.927582961661</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>358.3766351665748</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>427.7738353431754</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>577.22</v>
+      </c>
+      <c r="I88" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J88" t="n">
+        <v>20.997452</v>
+      </c>
+      <c r="K88" t="n">
+        <v>55</v>
+      </c>
+      <c r="L88" t="n">
+        <v>61</v>
+      </c>
+      <c r="M88" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="N88" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O88" t="n">
+        <v>24.01289846353334</v>
+      </c>
+      <c r="P88" t="n">
+        <v>22.65381747159091</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>2.738644113046586</v>
+      </c>
+      <c r="R88" t="n">
+        <v>21.56363636363636</v>
+      </c>
+      <c r="S88" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T88" t="n">
+        <v>-1.101072771437552</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0.06557377049180328</v>
+      </c>
+      <c r="V88" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="W88" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X88" t="n">
+        <v>660.1145787625314</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>584.8292520948809</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>735.3999054301821</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>592.7843636363635</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>785.6593162306017</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>26.10909791497354</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>27.22584093921283</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>2.974413990681105</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>21.91450861150568</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>29.29193974808321</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>-1.718538821760664</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>717.7391016826225</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>635.972461078799</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>799.5057422864461</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>602.4298417302913</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>805.2354236748073</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="I89" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J89" t="n">
+        <v>22.610249</v>
+      </c>
+      <c r="K89" t="n">
+        <v>67</v>
+      </c>
+      <c r="L89" t="n">
+        <v>61</v>
+      </c>
+      <c r="M89" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N89" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O89" t="n">
+        <v>24.6158975880882</v>
+      </c>
+      <c r="P89" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1.270970263767823</v>
+      </c>
+      <c r="R89" t="n">
+        <v>23.19387086411429</v>
+      </c>
+      <c r="S89" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T89" t="n">
+        <v>-1.578045250360461</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="V89" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="W89" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X89" t="n">
+        <v>413.05476152812</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>391.7278805020959</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>434.381642554144</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>389.1931530998378</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>445.1160013414757</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>26.61588072770907</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>25.11874429557403</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>3.698958970643893</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>23.3207632974955</v>
+      </c>
+      <c r="AJ89" t="n">
+        <v>33.90867664668163</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>-1.082907855831608</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>0.02459016393442623</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>582.4306839010962</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>446.6144786109582</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>384.5459470835536</v>
+      </c>
+      <c r="AQ89" t="n">
+        <v>508.6830101383628</v>
+      </c>
+      <c r="AR89" t="n">
+        <v>391.3224081319746</v>
+      </c>
+      <c r="AS89" t="n">
+        <v>568.9875941313179</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>24.96129</v>
+      </c>
+      <c r="K90" t="n">
+        <v>67</v>
+      </c>
+      <c r="L90" t="n">
+        <v>18</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>27.28179525407055</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>32.99999915564012</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>14.55609959473293</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>3.76558060036566</v>
+      </c>
+      <c r="AJ90" t="n">
+        <v>39.1501964222301</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>-0.1594180665616095</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>84.57356528761872</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>39.44965654394665</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>129.6974740312908</v>
+      </c>
+      <c r="AR90" t="n">
+        <v>11.67329986113355</v>
+      </c>
+      <c r="AS90" t="n">
+        <v>121.3656089089133</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-06-19 05:54:11</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>210.69</v>
+      </c>
+      <c r="I91" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J91" t="n">
+        <v>32.26493</v>
+      </c>
+      <c r="K91" t="n">
+        <v>65</v>
+      </c>
+      <c r="L91" t="n">
+        <v>61</v>
+      </c>
+      <c r="M91" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N91" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O91" t="n">
+        <v>37.78236576140846</v>
+      </c>
+      <c r="P91" t="n">
+        <v>36.46530462771046</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>4.836439385635218</v>
+      </c>
+      <c r="R91" t="n">
+        <v>31.88208306912806</v>
+      </c>
+      <c r="S91" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T91" t="n">
+        <v>-1.140805315951209</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="V91" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="W91" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X91" t="n">
+        <v>246.7188484219972</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>215.1368992337993</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>278.3007976101952</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>208.1900024414062</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>292.4373910086495</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>37.64187315897667</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>37.15918404715401</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>4.273034170005802</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>32.25727402597985</v>
+      </c>
+      <c r="AJ91" t="n">
+        <v>43.97591789401307</v>
+      </c>
+      <c r="AK91" t="n">
+        <v>-1.258343122252489</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>0.1012658227848101</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>245.8014317281177</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>217.8985185979798</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>273.7043448582556</v>
+      </c>
+      <c r="AR91" t="n">
+        <v>210.6399993896484</v>
+      </c>
+      <c r="AS91" t="n">
         <v>287.1627438479053</v>
       </c>
     </row>
@@ -13087,12 +14414,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13121,19 +14448,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>362.1</v>
+        <v>367.46</v>
       </c>
       <c r="I2" t="n">
         <v>13.1</v>
       </c>
       <c r="J2" t="n">
-        <v>27.64122</v>
+        <v>28.05038</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -13142,25 +14469,25 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.9552662230043</v>
+        <v>28.9768255249951</v>
       </c>
       <c r="P2" t="n">
-        <v>29.21870597964289</v>
+        <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.679927861166365</v>
+        <v>1.685198939276353</v>
       </c>
       <c r="R2" t="n">
-        <v>26.96842149957094</v>
+        <v>26.95042008575277</v>
       </c>
       <c r="S2" t="n">
-        <v>31.22081491927324</v>
+        <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7822039585032925</v>
+        <v>-0.5497543959960779</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="V2" t="n">
         <v>331.002237918088</v>
@@ -13169,19 +14496,19 @@
         <v>422.3507729952915</v>
       </c>
       <c r="X2" t="n">
-        <v>379.3139875213564</v>
+        <v>379.5964143774358</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.306932540077</v>
+        <v>357.5203082729156</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.3210425026357</v>
+        <v>401.6725204819561</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.2863216443793</v>
+        <v>353.0505031233612</v>
       </c>
       <c r="AB2" t="n">
-        <v>408.9926754424794</v>
+        <v>409.2750364404161</v>
       </c>
       <c r="AC2" t="n">
         <v>122</v>
@@ -13208,10 +14535,10 @@
         <v>32.65449124757065</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.018705193204786</v>
+        <v>-0.8138832523294173</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1557377049180328</v>
+        <v>0.2131147540983606</v>
       </c>
       <c r="AM2" t="n">
         <v>331.002237918088</v>
@@ -13238,12 +14565,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13272,19 +14599,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>378.91</v>
+        <v>379.4</v>
       </c>
       <c r="I3" t="n">
         <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>22.581049</v>
+        <v>22.610249</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M3" t="n">
         <v>22.31206935670243</v>
@@ -13293,25 +14620,25 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.6040573176406</v>
+        <v>24.6158975880882</v>
       </c>
       <c r="P3" t="n">
-        <v>24.57421541107486</v>
+        <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.263952497311645</v>
+        <v>1.270970263767823</v>
       </c>
       <c r="R3" t="n">
-        <v>23.19493411256791</v>
+        <v>23.19387086411429</v>
       </c>
       <c r="S3" t="n">
-        <v>26.51801151659729</v>
+        <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.600541414288447</v>
+        <v>-1.578045250360461</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.04918032786885246</v>
       </c>
       <c r="V3" t="n">
         <v>374.3965238054668</v>
@@ -13320,19 +14647,19 @@
         <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>412.8560817900092</v>
+        <v>413.05476152812</v>
       </c>
       <c r="Y3" t="n">
-        <v>391.6469588851198</v>
+        <v>391.7278805020959</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.0652046948986</v>
+        <v>434.381642554144</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.2109944088896</v>
+        <v>389.1931530998378</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.9722332485025</v>
+        <v>445.1160013414757</v>
       </c>
       <c r="AC3" t="n">
         <v>122</v>
@@ -13359,7 +14686,7 @@
         <v>33.90867664668163</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.090801968805485</v>
+        <v>-1.082907855831608</v>
       </c>
       <c r="AL3" t="n">
         <v>0.02459016393442623</v>
@@ -13389,12 +14716,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13423,19 +14750,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>567.58</v>
+        <v>577.22</v>
       </c>
       <c r="I4" t="n">
         <v>27.49</v>
       </c>
       <c r="J4" t="n">
-        <v>20.646782</v>
+        <v>20.997452</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M4" t="n">
         <v>20.61745383522727</v>
@@ -13444,25 +14771,25 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.03322076144743</v>
+        <v>24.01289846353334</v>
       </c>
       <c r="P4" t="n">
-        <v>22.7372725053267</v>
+        <v>22.65381747159091</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.720813055804332</v>
+        <v>2.738644113046586</v>
       </c>
       <c r="R4" t="n">
-        <v>21.56538174715909</v>
+        <v>21.56363636363636</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57799154893039</v>
+        <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.244642205102301</v>
+        <v>-1.101072771437552</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="V4" t="n">
         <v>566.7738059303977</v>
@@ -13471,19 +14798,19 @@
         <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>660.6732387321899</v>
+        <v>660.1145787625314</v>
       </c>
       <c r="Y4" t="n">
-        <v>585.8780878281289</v>
+        <v>584.8292520948809</v>
       </c>
       <c r="Z4" t="n">
-        <v>735.468389636251</v>
+        <v>735.3999054301821</v>
       </c>
       <c r="AA4" t="n">
-        <v>592.8323442294034</v>
+        <v>592.7843636363635</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.6089876800964</v>
+        <v>785.6593162306017</v>
       </c>
       <c r="AC4" t="n">
         <v>122</v>
@@ -13510,10 +14837,10 @@
         <v>29.29193974808321</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.836434313477235</v>
+        <v>-1.718538821760664</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="AM4" t="n">
         <v>566.7738059303977</v>
@@ -13540,12 +14867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13574,19 +14901,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>237.5</v>
+        <v>244.39</v>
       </c>
       <c r="I5" t="n">
         <v>7.77</v>
       </c>
       <c r="J5" t="n">
-        <v>30.56628</v>
+        <v>31.453024</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -13595,25 +14922,25 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.6515334084853</v>
+        <v>31.7008543482426</v>
       </c>
       <c r="P5" t="n">
-        <v>31.71949797269831</v>
+        <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.425128953218685</v>
+        <v>2.413698246265196</v>
       </c>
       <c r="R5" t="n">
-        <v>28.89025643705661</v>
+        <v>28.90376645650824</v>
       </c>
       <c r="S5" t="n">
-        <v>34.93654088827689</v>
+        <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4475033820551787</v>
+        <v>-0.1026766078262194</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.4262295081967213</v>
       </c>
       <c r="V5" t="n">
         <v>216.0211675795551</v>
@@ -13622,19 +14949,19 @@
         <v>286.0812028062892</v>
       </c>
       <c r="X5" t="n">
-        <v>245.9324145839307</v>
+        <v>246.315638285845</v>
       </c>
       <c r="Y5" t="n">
-        <v>227.0891626174216</v>
+        <v>227.5612029123645</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.7756665504399</v>
+        <v>265.0700736593256</v>
       </c>
       <c r="AA5" t="n">
-        <v>224.4772925159299</v>
+        <v>224.582265367069</v>
       </c>
       <c r="AB5" t="n">
-        <v>271.4569227019115</v>
+        <v>271.5273613710284</v>
       </c>
       <c r="AC5" t="n">
         <v>122</v>
@@ -13661,10 +14988,10 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.4009848000380581</v>
+        <v>-0.02491888468083014</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4262295081967213</v>
+        <v>0.459016393442623</v>
       </c>
       <c r="AM5" t="n">
         <v>215.4251391678176</v>
@@ -13691,12 +15018,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13725,19 +15052,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>295.95</v>
+        <v>298.01</v>
       </c>
       <c r="I6" t="n">
         <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>35.8293</v>
+        <v>36.078693</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -13746,25 +15073,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.70350438725112</v>
+        <v>34.75780544383156</v>
       </c>
       <c r="P6" t="n">
-        <v>34.59493709515922</v>
+        <v>34.611391477947</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.950081244083638</v>
+        <v>1.918420379816403</v>
       </c>
       <c r="R6" t="n">
-        <v>32.01911385451691</v>
+        <v>32.08860759493671</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38147763305368</v>
+        <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5773070307529214</v>
+        <v>0.6885287344032743</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.7049180327868853</v>
       </c>
       <c r="V6" t="n">
         <v>257.8688405483584</v>
@@ -13773,19 +15100,19 @@
         <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>286.6509462386942</v>
+        <v>287.0994729660487</v>
       </c>
       <c r="Y6" t="n">
-        <v>270.5432751625633</v>
+        <v>271.2533206287652</v>
       </c>
       <c r="Z6" t="n">
-        <v>302.7586173148251</v>
+        <v>302.9456253033322</v>
       </c>
       <c r="AA6" t="n">
-        <v>264.4778804383097</v>
+        <v>265.0518987341772</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.7710052490234</v>
+        <v>308.8200073242188</v>
       </c>
       <c r="AC6" t="n">
         <v>122</v>
@@ -13812,10 +15139,10 @@
         <v>36.69222629741434</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.8226996288431768</v>
+        <v>0.9686868190992587</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7704918032786885</v>
+        <v>0.7868852459016393</v>
       </c>
       <c r="AM6" t="n">
         <v>257.8688405483584</v>
@@ -13842,12 +15169,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13876,19 +15203,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>204.65</v>
+        <v>210.69</v>
       </c>
       <c r="I7" t="n">
         <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.339968</v>
+        <v>32.26493</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M7" t="n">
         <v>30.69218961239591</v>
@@ -13897,25 +15224,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.74143885132728</v>
+        <v>37.78236576140846</v>
       </c>
       <c r="P7" t="n">
-        <v>36.40612232441805</v>
+        <v>36.46530462771046</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.807445815012896</v>
+        <v>4.836439385635218</v>
       </c>
       <c r="R7" t="n">
-        <v>31.8889742934503</v>
+        <v>31.88208306912806</v>
       </c>
       <c r="S7" t="n">
-        <v>44.72591882822464</v>
+        <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.331574207521278</v>
+        <v>-1.140805315951209</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="V7" t="n">
         <v>200.4199981689453</v>
@@ -13924,19 +15251,19 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>246.4515956991671</v>
+        <v>246.7188484219972</v>
       </c>
       <c r="Y7" t="n">
-        <v>215.0589745271329</v>
+        <v>215.1368992337993</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.8442168712014</v>
+        <v>278.3007976101952</v>
       </c>
       <c r="AA7" t="n">
-        <v>208.2350021362304</v>
+        <v>208.1900024414062</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.0602499483069</v>
+        <v>292.4373910086495</v>
       </c>
       <c r="AC7" t="n">
         <v>79</v>
@@ -13963,10 +15290,10 @@
         <v>43.97591789401307</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.474808042306883</v>
+        <v>-1.258343122252489</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01265822784810127</v>
+        <v>0.1012658227848101</v>
       </c>
       <c r="AM7" t="n">
         <v>200.4199981689453</v>
@@ -13993,12 +15320,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14027,19 +15354,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>512.48</v>
+        <v>537.37</v>
       </c>
       <c r="I8" t="n">
         <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>171.39798</v>
+        <v>179.72241</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
         <v>73.97735595703125</v>
@@ -14048,25 +15375,25 @@
         <v>179.4295113985656</v>
       </c>
       <c r="O8" t="n">
-        <v>127.0633640195864</v>
+        <v>127.9009013707825</v>
       </c>
       <c r="P8" t="n">
-        <v>133.9908448587141</v>
+        <v>134.0603810436321</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.42580347530961</v>
+        <v>33.04072980407927</v>
       </c>
       <c r="R8" t="n">
-        <v>77.68075331202094</v>
+        <v>79.32453083542158</v>
       </c>
       <c r="S8" t="n">
-        <v>167.9963879194416</v>
+        <v>168.0262231045082</v>
       </c>
       <c r="T8" t="n">
-        <v>1.326359021202344</v>
+        <v>1.568412953845212</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9516129032258065</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>221.1922943115235</v>
@@ -14075,19 +15402,19 @@
         <v>536.4942390817112</v>
       </c>
       <c r="X8" t="n">
-        <v>379.9194584185634</v>
+        <v>382.4236950986397</v>
       </c>
       <c r="Y8" t="n">
-        <v>279.9763060273876</v>
+        <v>283.6319129844427</v>
       </c>
       <c r="Z8" t="n">
-        <v>479.8626108097392</v>
+        <v>481.2154772128368</v>
       </c>
       <c r="AA8" t="n">
-        <v>232.2654524029426</v>
+        <v>237.1803471979105</v>
       </c>
       <c r="AB8" t="n">
-        <v>502.3091998791305</v>
+        <v>502.3984070824796</v>
       </c>
       <c r="AC8" t="n">
         <v>122</v>
@@ -14114,10 +15441,10 @@
         <v>160.7022915199155</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.898189715803768</v>
+        <v>2.158576773974405</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9754098360655737</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
         <v>215.4492418397148</v>
@@ -14144,12 +15471,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14178,19 +15505,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>392.9</v>
+        <v>411.35</v>
       </c>
       <c r="I9" t="n">
         <v>6.03</v>
       </c>
       <c r="J9" t="n">
-        <v>65.15754</v>
+        <v>68.21725000000001</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -14199,25 +15526,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.10496513901769</v>
+        <v>75.34392740341401</v>
       </c>
       <c r="P9" t="n">
-        <v>78.71540210865163</v>
+        <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.704328927584006</v>
+        <v>9.5991758213117</v>
       </c>
       <c r="R9" t="n">
-        <v>61.29473531920079</v>
+        <v>61.31578709414597</v>
       </c>
       <c r="S9" t="n">
-        <v>83.49376061274063</v>
+        <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.025050285624872</v>
+        <v>-0.7424259682369446</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2950819672131147</v>
       </c>
       <c r="V9" t="n">
         <v>344.885442901076</v>
@@ -14226,19 +15553,19 @@
         <v>566.0559735214503</v>
       </c>
       <c r="X9" t="n">
-        <v>452.8829397882767</v>
+        <v>454.3238822425865</v>
       </c>
       <c r="Y9" t="n">
-        <v>394.3658363549452</v>
+        <v>396.4408520400769</v>
       </c>
       <c r="Z9" t="n">
-        <v>511.4000432216083</v>
+        <v>512.2069124450961</v>
       </c>
       <c r="AA9" t="n">
-        <v>369.6072539747808</v>
+        <v>369.7341961777002</v>
       </c>
       <c r="AB9" t="n">
-        <v>503.467376494826</v>
+        <v>503.5931492855676</v>
       </c>
       <c r="AC9" t="n">
         <v>122</v>
@@ -14265,10 +15592,10 @@
         <v>82.37543771606209</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.9186742919077521</v>
+        <v>-0.525566693237645</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1885245901639344</v>
+        <v>0.3032786885245902</v>
       </c>
       <c r="AM9" t="n">
         <v>344.885442901076</v>
@@ -14295,12 +15622,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-18 05:04:25</t>
+          <t>2026-06-19 05:54:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14329,19 +15656,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>76.95999999999999</v>
+        <v>77.38</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>24.825808</v>
+        <v>24.96129</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -14384,7 +15711,7 @@
         <v>39.1501964222301</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.1687256423389164</v>
+        <v>-0.1594180665616095</v>
       </c>
       <c r="AL10" t="n">
         <v>0.2658227848101266</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS91"/>
+  <dimension ref="A1:AS100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12967,7 +12967,7 @@
         <v>36.69222629741434</v>
       </c>
       <c r="AK83" t="n">
-        <v>0.9686868190992587</v>
+        <v>0.9686868190992588</v>
       </c>
       <c r="AL83" t="n">
         <v>0.7868852459016393</v>
@@ -13073,7 +13073,7 @@
         <v>1</v>
       </c>
       <c r="V84" t="n">
-        <v>221.1922943115235</v>
+        <v>221.1922943115234</v>
       </c>
       <c r="W84" t="n">
         <v>536.4942390817112</v>
@@ -13133,7 +13133,7 @@
         <v>331.0345799819687</v>
       </c>
       <c r="AP84" t="n">
-        <v>235.4459363878271</v>
+        <v>235.445936387827</v>
       </c>
       <c r="AQ84" t="n">
         <v>426.6232235761103</v>
@@ -13218,7 +13218,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T85" t="n">
-        <v>-0.1026766078262194</v>
+        <v>-0.1026766078262193</v>
       </c>
       <c r="U85" t="n">
         <v>0.4262295081967213</v>
@@ -13257,7 +13257,7 @@
         <v>31.51178144271168</v>
       </c>
       <c r="AG85" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="AH85" t="n">
         <v>2.357948337747321</v>
@@ -13269,10 +13269,10 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK85" t="n">
-        <v>-0.02491888468083014</v>
+        <v>-0.0249188846808301</v>
       </c>
       <c r="AL85" t="n">
-        <v>0.459016393442623</v>
+        <v>0.4590163934426229</v>
       </c>
       <c r="AM85" t="n">
         <v>215.4251391678176</v>
@@ -13351,7 +13351,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N86" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O86" t="n">
         <v>75.34392740341401</v>
@@ -13402,7 +13402,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE86" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF86" t="n">
         <v>72.30794087549145</v>
@@ -13423,7 +13423,7 @@
         <v>-0.525566693237645</v>
       </c>
       <c r="AL86" t="n">
-        <v>0.3032786885245902</v>
+        <v>0.3032786885245901</v>
       </c>
       <c r="AM86" t="n">
         <v>344.885442901076</v>
@@ -13523,16 +13523,16 @@
         <v>-0.5497543959960779</v>
       </c>
       <c r="U87" t="n">
-        <v>0.3278688524590164</v>
+        <v>0.3278688524590163</v>
       </c>
       <c r="V87" t="n">
         <v>331.002237918088</v>
       </c>
       <c r="W87" t="n">
-        <v>422.3507729952915</v>
+        <v>422.3507729952916</v>
       </c>
       <c r="X87" t="n">
-        <v>379.5964143774358</v>
+        <v>379.5964143774359</v>
       </c>
       <c r="Y87" t="n">
         <v>357.5203082729156</v>
@@ -13650,7 +13650,7 @@
         <v>61</v>
       </c>
       <c r="M88" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="N88" t="n">
         <v>29.31247287326389</v>
@@ -13674,7 +13674,7 @@
         <v>-1.101072771437552</v>
       </c>
       <c r="U88" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.0655737704918032</v>
       </c>
       <c r="V88" t="n">
         <v>566.7738059303977</v>
@@ -13701,7 +13701,7 @@
         <v>122</v>
       </c>
       <c r="AD88" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="AE88" t="n">
         <v>31.43082152229007</v>
@@ -13725,7 +13725,7 @@
         <v>-1.718538821760664</v>
       </c>
       <c r="AL88" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.0327868852459016</v>
       </c>
       <c r="AM88" t="n">
         <v>566.7738059303977</v>
@@ -13810,7 +13810,7 @@
         <v>24.6158975880882</v>
       </c>
       <c r="P89" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q89" t="n">
         <v>1.270970263767823</v>
@@ -13819,13 +13819,13 @@
         <v>23.19387086411429</v>
       </c>
       <c r="S89" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T89" t="n">
         <v>-1.578045250360461</v>
       </c>
       <c r="U89" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="V89" t="n">
         <v>374.3965238054668</v>
@@ -13876,7 +13876,7 @@
         <v>-1.082907855831608</v>
       </c>
       <c r="AL89" t="n">
-        <v>0.02459016393442623</v>
+        <v>0.0245901639344262</v>
       </c>
       <c r="AM89" t="n">
         <v>374.3965238054668</v>
@@ -13971,7 +13971,7 @@
         <v>79</v>
       </c>
       <c r="AD90" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE90" t="n">
         <v>42.60474344487245</v>
@@ -13992,10 +13992,10 @@
         <v>39.1501964222301</v>
       </c>
       <c r="AK90" t="n">
-        <v>-0.1594180665616095</v>
+        <v>-0.1594180665616094</v>
       </c>
       <c r="AL90" t="n">
-        <v>0.2658227848101266</v>
+        <v>0.2658227848101265</v>
       </c>
       <c r="AM90" t="n">
         <v>10.81762752038992</v>
@@ -14095,7 +14095,7 @@
         <v>-1.140805315951209</v>
       </c>
       <c r="U91" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.1311475409836065</v>
       </c>
       <c r="V91" t="n">
         <v>200.4199981689453</v>
@@ -14168,6 +14168,1333 @@
       </c>
       <c r="AS91" t="n">
         <v>287.1627438479053</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>298.01</v>
+      </c>
+      <c r="I92" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J92" t="n">
+        <v>36.122425</v>
+      </c>
+      <c r="K92" t="n">
+        <v>67</v>
+      </c>
+      <c r="L92" t="n">
+        <v>62</v>
+      </c>
+      <c r="M92" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N92" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O92" t="n">
+        <v>34.77911009274114</v>
+      </c>
+      <c r="P92" t="n">
+        <v>34.70521162525717</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1.910011629370365</v>
+      </c>
+      <c r="R92" t="n">
+        <v>32.092278396027</v>
+      </c>
+      <c r="S92" t="n">
+        <v>37.38147763305368</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0.7033019519895181</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0.7258064516129032</v>
+      </c>
+      <c r="V92" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="W92" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X92" t="n">
+        <v>286.9276582651144</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>271.1700623228089</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>302.6852542074199</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>264.7612967672227</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>308.3971904726929</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>34.43731874357252</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>34.44810312005538</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.707836039599991</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>36.68740034742586</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>0.9866908868032591</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>0.7967479674796748</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>284.1078796344733</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>270.0182323077734</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>298.1975269611732</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS92" t="n">
+        <v>302.6710528662633</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>537.37</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J93" t="n">
+        <v>179.72241</v>
+      </c>
+      <c r="K93" t="n">
+        <v>63</v>
+      </c>
+      <c r="L93" t="n">
+        <v>62</v>
+      </c>
+      <c r="M93" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N93" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="O93" t="n">
+        <v>128.6797075364954</v>
+      </c>
+      <c r="P93" t="n">
+        <v>134.9072377009912</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>33.33764677019743</v>
+      </c>
+      <c r="R93" t="n">
+        <v>79.59962492169075</v>
+      </c>
+      <c r="S93" t="n">
+        <v>169.0944183849898</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1.53108294701637</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>221.1922943115235</v>
+      </c>
+      <c r="W93" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="X93" t="n">
+        <v>384.7523255341212</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>285.0727616912308</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>484.4318893770115</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>238.0028785158553</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>505.5923109711194</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>179.4295113985656</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>111.2462069769113</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>105.9310311754349</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>32.3808487181543</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>162.1304931640625</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>2.114713039769633</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>536.4942390817112</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>332.6261588609648</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>235.8074211936834</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>429.4448965282461</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>225.8025376114755</v>
+      </c>
+      <c r="AS93" t="n">
+        <v>484.7701745605469</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>244.39</v>
+      </c>
+      <c r="I94" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J94" t="n">
+        <v>31.453024</v>
+      </c>
+      <c r="K94" t="n">
+        <v>67</v>
+      </c>
+      <c r="L94" t="n">
+        <v>62</v>
+      </c>
+      <c r="M94" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N94" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O94" t="n">
+        <v>31.66105433481141</v>
+      </c>
+      <c r="P94" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>2.414258182116304</v>
+      </c>
+      <c r="R94" t="n">
+        <v>28.90795038667516</v>
+      </c>
+      <c r="S94" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T94" t="n">
+        <v>-0.08616739350927723</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0.4354838709677419</v>
+      </c>
+      <c r="V94" t="n">
+        <v>216.0211675795551</v>
+      </c>
+      <c r="W94" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="X94" t="n">
+        <v>246.0063921814846</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>227.2476061064409</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>264.7651782565283</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>224.614774504466</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>271.4569227019115</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>31.49325682541734</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>31.70574133476002</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>2.357234842691278</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>28.68730787120271</v>
+      </c>
+      <c r="AJ94" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>-0.01706780533220313</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>0.4634146341463415</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>215.4251391678176</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>244.7026055334927</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>226.3868908057815</v>
+      </c>
+      <c r="AQ94" t="n">
+        <v>263.0183202612039</v>
+      </c>
+      <c r="AR94" t="n">
+        <v>222.9003821592451</v>
+      </c>
+      <c r="AS94" t="n">
+        <v>269.7457944989703</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>411.35</v>
+      </c>
+      <c r="I95" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J95" t="n">
+        <v>68.21725000000001</v>
+      </c>
+      <c r="K95" t="n">
+        <v>34</v>
+      </c>
+      <c r="L95" t="n">
+        <v>62</v>
+      </c>
+      <c r="M95" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N95" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O95" t="n">
+        <v>75.23264245469682</v>
+      </c>
+      <c r="P95" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>9.560410307465348</v>
+      </c>
+      <c r="R95" t="n">
+        <v>61.37555624003113</v>
+      </c>
+      <c r="S95" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T95" t="n">
+        <v>-0.7337961686873171</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="V95" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="W95" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X95" t="n">
+        <v>453.6528340018218</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>396.0035598478058</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>511.3021081558379</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>370.0946041273878</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>503.467376494826</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>72.27652884059273</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>71.37106969421515</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>7.759250530291868</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>62.40428783275464</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>-0.5231534701380538</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>0.3008130081300813</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>435.8274689087742</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>389.0391882111143</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>482.6157496064341</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>376.2978556315105</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>496.648663222999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="I96" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J96" t="n">
+        <v>28.007622</v>
+      </c>
+      <c r="K96" t="n">
+        <v>37</v>
+      </c>
+      <c r="L96" t="n">
+        <v>62</v>
+      </c>
+      <c r="M96" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N96" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O96" t="n">
+        <v>28.96153777226066</v>
+      </c>
+      <c r="P96" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1.675658126040633</v>
+      </c>
+      <c r="R96" t="n">
+        <v>26.96842149957094</v>
+      </c>
+      <c r="S96" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T96" t="n">
+        <v>-0.5692782778517255</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="V96" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="W96" t="n">
+        <v>422.9955833357424</v>
+      </c>
+      <c r="X96" t="n">
+        <v>379.9753755720599</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>357.9907409584068</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>401.960010185713</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>353.8256900743707</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>409.6170917408649</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>29.66283155944916</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>29.27688843052775</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>1.994970284061954</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>27.37684176855299</v>
+      </c>
+      <c r="AJ96" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>-0.8296913355917233</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>446.7016702785662</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>389.176350059973</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>363.0023399330802</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>415.3503601868658</v>
+      </c>
+      <c r="AR96" t="n">
+        <v>359.1841640034152</v>
+      </c>
+      <c r="AS96" t="n">
+        <v>428.3621670240005</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>577.22</v>
+      </c>
+      <c r="I97" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J97" t="n">
+        <v>20.997452</v>
+      </c>
+      <c r="K97" t="n">
+        <v>55</v>
+      </c>
+      <c r="L97" t="n">
+        <v>62</v>
+      </c>
+      <c r="M97" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="N97" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O97" t="n">
+        <v>23.96413908696792</v>
+      </c>
+      <c r="P97" t="n">
+        <v>22.57109042080966</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>2.743104355887455</v>
+      </c>
+      <c r="R97" t="n">
+        <v>21.31458229758523</v>
+      </c>
+      <c r="S97" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T97" t="n">
+        <v>-1.081507191150274</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="V97" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="W97" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X97" t="n">
+        <v>658.7741835007481</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>583.366244757402</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>734.1821222440943</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>585.9378673606179</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>785.6089876800964</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>26.06747774588008</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>27.21583600651208</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>2.997947029388669</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>21.85083540482955</v>
+      </c>
+      <c r="AJ97" t="n">
+        <v>29.28804247225144</v>
+      </c>
+      <c r="AK97" t="n">
+        <v>-1.691165886581371</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>0.04065040650406504</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>566.7738059303977</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>716.5949632342432</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>634.1813993963488</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>799.0085270721378</v>
+      </c>
+      <c r="AR97" t="n">
+        <v>600.6794652787642</v>
+      </c>
+      <c r="AS97" t="n">
+        <v>805.1282875621921</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>379.4</v>
+      </c>
+      <c r="I98" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J98" t="n">
+        <v>22.610249</v>
+      </c>
+      <c r="K98" t="n">
+        <v>67</v>
+      </c>
+      <c r="L98" t="n">
+        <v>62</v>
+      </c>
+      <c r="M98" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="N98" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O98" t="n">
+        <v>24.58311428779691</v>
+      </c>
+      <c r="P98" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1.286669416528865</v>
+      </c>
+      <c r="R98" t="n">
+        <v>23.15447226996121</v>
+      </c>
+      <c r="S98" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T98" t="n">
+        <v>-1.533311713524089</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="V98" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="W98" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X98" t="n">
+        <v>412.5046577492323</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>390.9143449398779</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>434.0949705585866</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>388.5320446899491</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>444.9722332485025</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>22.31206935670243</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>34.70981429684721</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>26.58309578658972</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>25.11428651355562</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>3.701669127308623</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>23.3125699289595</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>33.87852024387669</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>-1.073258211351338</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>0.03252032520325204</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>374.3965238054668</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>582.4306839010962</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>446.0643472989755</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>383.9503393427368</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>508.1783552552142</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>391.1849234079405</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>568.4815696922508</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>77.38</v>
+      </c>
+      <c r="I99" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>24.96129</v>
+      </c>
+      <c r="K99" t="n">
+        <v>67</v>
+      </c>
+      <c r="L99" t="n">
+        <v>18</v>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>27.28179525407055</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>32.99999915564012</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>14.55609959473293</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>3.76558060036566</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>39.1501964222301</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>-0.1594180665616095</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>84.57356528761872</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>39.44965654394665</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>129.6974740312908</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>11.67329986113355</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>121.3656089089133</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-06-20 03:12:44</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>210.69</v>
+      </c>
+      <c r="I100" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J100" t="n">
+        <v>32.26493</v>
+      </c>
+      <c r="K100" t="n">
+        <v>65</v>
+      </c>
+      <c r="L100" t="n">
+        <v>62</v>
+      </c>
+      <c r="M100" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N100" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O100" t="n">
+        <v>37.69337488559808</v>
+      </c>
+      <c r="P100" t="n">
+        <v>36.40612232441805</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>4.847544309526713</v>
+      </c>
+      <c r="R100" t="n">
+        <v>31.8889742934503</v>
+      </c>
+      <c r="S100" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T100" t="n">
+        <v>-1.11983398995028</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="V100" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="W100" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X100" t="n">
+        <v>246.1377380029554</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>214.483273661746</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>277.7922023441649</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>208.2350021362304</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>37.57466138775402</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>37.14387699049346</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>4.28825028148125</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>32.23353784628338</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>43.94714230907206</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>-1.23820463807442</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>245.3625388620338</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>217.3602645239612</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>273.3648132001063</v>
+      </c>
+      <c r="AR100" t="n">
+        <v>210.4850021362305</v>
+      </c>
+      <c r="AS100" t="n">
+        <v>286.9748392782406</v>
       </c>
     </row>
   </sheetData>
@@ -14414,12 +15741,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -14451,16 +15778,16 @@
         <v>367.46</v>
       </c>
       <c r="I2" t="n">
-        <v>13.1</v>
+        <v>13.12</v>
       </c>
       <c r="J2" t="n">
-        <v>28.05038</v>
+        <v>28.007622</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -14469,49 +15796,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.9768255249951</v>
+        <v>28.96153777226066</v>
       </c>
       <c r="P2" t="n">
-        <v>29.2311213745769</v>
+        <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.685198939276353</v>
+        <v>1.675658126040633</v>
       </c>
       <c r="R2" t="n">
-        <v>26.95042008575277</v>
+        <v>26.96842149957094</v>
       </c>
       <c r="S2" t="n">
-        <v>31.24236919392489</v>
+        <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5497543959960779</v>
+        <v>-0.5692782778517255</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3278688524590164</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="V2" t="n">
-        <v>331.002237918088</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="W2" t="n">
-        <v>422.3507729952915</v>
+        <v>422.9955833357424</v>
       </c>
       <c r="X2" t="n">
-        <v>379.5964143774358</v>
+        <v>379.9753755720599</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.5203082729156</v>
+        <v>357.9907409584068</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.6725204819561</v>
+        <v>401.960010185713</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.0505031233612</v>
+        <v>353.8256900743707</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.2750364404161</v>
+        <v>409.6170917408649</v>
       </c>
       <c r="AC2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -14520,57 +15847,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.67622374554744</v>
+        <v>29.66283155944916</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.29405020358088</v>
+        <v>29.27688843052775</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.997637549235844</v>
+        <v>1.994970284061954</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.35699505088357</v>
+        <v>27.37684176855299</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65449124757065</v>
+        <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.8138832523294173</v>
+        <v>-0.8296913355917233</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2131147540983606</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.002237918088</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.0207226104586</v>
+        <v>446.7016702785662</v>
       </c>
       <c r="AO2" t="n">
-        <v>388.7585310666714</v>
+        <v>389.176350059973</v>
       </c>
       <c r="AP2" t="n">
-        <v>362.5894791716818</v>
+        <v>363.0023399330802</v>
       </c>
       <c r="AQ2" t="n">
-        <v>414.927582961661</v>
+        <v>415.3503601868658</v>
       </c>
       <c r="AR2" t="n">
-        <v>358.3766351665748</v>
+        <v>359.1841640034152</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.7738353431754</v>
+        <v>428.3621670240005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14611,7 +15938,7 @@
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
         <v>22.31206935670243</v>
@@ -14620,25 +15947,25 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.6158975880882</v>
+        <v>24.58311428779691</v>
       </c>
       <c r="P3" t="n">
-        <v>24.58473954668934</v>
+        <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.270970263767823</v>
+        <v>1.286669416528865</v>
       </c>
       <c r="R3" t="n">
-        <v>23.19387086411429</v>
+        <v>23.15447226996121</v>
       </c>
       <c r="S3" t="n">
-        <v>26.52657934096994</v>
+        <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.578045250360461</v>
+        <v>-1.533311713524089</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="V3" t="n">
         <v>374.3965238054668</v>
@@ -14647,22 +15974,22 @@
         <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>413.05476152812</v>
+        <v>412.5046577492323</v>
       </c>
       <c r="Y3" t="n">
-        <v>391.7278805020959</v>
+        <v>390.9143449398779</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.381642554144</v>
+        <v>434.0949705585866</v>
       </c>
       <c r="AA3" t="n">
-        <v>389.1931530998378</v>
+        <v>388.5320446899491</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.1160013414757</v>
+        <v>444.9722332485025</v>
       </c>
       <c r="AC3" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD3" t="n">
         <v>22.31206935670243</v>
@@ -14671,25 +15998,25 @@
         <v>34.70981429684721</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.61588072770907</v>
+        <v>26.58309578658972</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.11874429557403</v>
+        <v>25.11428651355562</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.698958970643893</v>
+        <v>3.701669127308623</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.3207632974955</v>
+        <v>23.3125699289595</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33.90867664668163</v>
+        <v>33.87852024387669</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.082907855831608</v>
+        <v>-1.073258211351338</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.02459016393442623</v>
+        <v>0.03252032520325204</v>
       </c>
       <c r="AM3" t="n">
         <v>374.3965238054668</v>
@@ -14698,30 +16025,30 @@
         <v>582.4306839010962</v>
       </c>
       <c r="AO3" t="n">
-        <v>446.6144786109582</v>
+        <v>446.0643472989755</v>
       </c>
       <c r="AP3" t="n">
-        <v>384.5459470835536</v>
+        <v>383.9503393427368</v>
       </c>
       <c r="AQ3" t="n">
-        <v>508.6830101383628</v>
+        <v>508.1783552552142</v>
       </c>
       <c r="AR3" t="n">
-        <v>391.3224081319746</v>
+        <v>391.1849234079405</v>
       </c>
       <c r="AS3" t="n">
-        <v>568.9875941313179</v>
+        <v>568.4815696922508</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14762,7 +16089,7 @@
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
         <v>20.61745383522727</v>
@@ -14771,25 +16098,25 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>24.01289846353334</v>
+        <v>23.96413908696792</v>
       </c>
       <c r="P4" t="n">
-        <v>22.65381747159091</v>
+        <v>22.57109042080966</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.738644113046586</v>
+        <v>2.743104355887455</v>
       </c>
       <c r="R4" t="n">
-        <v>21.56363636363636</v>
+        <v>21.31458229758523</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57982234378326</v>
+        <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.101072771437552</v>
+        <v>-1.081507191150274</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="V4" t="n">
         <v>566.7738059303977</v>
@@ -14798,22 +16125,22 @@
         <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>660.1145787625314</v>
+        <v>658.7741835007481</v>
       </c>
       <c r="Y4" t="n">
-        <v>584.8292520948809</v>
+        <v>583.366244757402</v>
       </c>
       <c r="Z4" t="n">
-        <v>735.3999054301821</v>
+        <v>734.1821222440943</v>
       </c>
       <c r="AA4" t="n">
-        <v>592.7843636363635</v>
+        <v>585.9378673606179</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.6593162306017</v>
+        <v>785.6089876800964</v>
       </c>
       <c r="AC4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD4" t="n">
         <v>20.61745383522727</v>
@@ -14822,25 +16149,25 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.10909791497354</v>
+        <v>26.06747774588008</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.22584093921283</v>
+        <v>27.21583600651208</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.974413990681105</v>
+        <v>2.997947029388669</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.91450861150568</v>
+        <v>21.85083540482955</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.29193974808321</v>
+        <v>29.28804247225144</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.718538821760664</v>
+        <v>-1.691165886581371</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.04065040650406504</v>
       </c>
       <c r="AM4" t="n">
         <v>566.7738059303977</v>
@@ -14849,30 +16176,30 @@
         <v>864.0332836477539</v>
       </c>
       <c r="AO4" t="n">
-        <v>717.7391016826225</v>
+        <v>716.5949632342432</v>
       </c>
       <c r="AP4" t="n">
-        <v>635.972461078799</v>
+        <v>634.1813993963488</v>
       </c>
       <c r="AQ4" t="n">
-        <v>799.5057422864461</v>
+        <v>799.0085270721378</v>
       </c>
       <c r="AR4" t="n">
-        <v>602.4298417302913</v>
+        <v>600.6794652787642</v>
       </c>
       <c r="AS4" t="n">
-        <v>805.2354236748073</v>
+        <v>805.1282875621921</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14913,7 +16240,7 @@
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -14922,25 +16249,25 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.7008543482426</v>
+        <v>31.66105433481141</v>
       </c>
       <c r="P5" t="n">
-        <v>31.73325461063659</v>
+        <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.413698246265196</v>
+        <v>2.414258182116304</v>
       </c>
       <c r="R5" t="n">
-        <v>28.90376645650824</v>
+        <v>28.90795038667516</v>
       </c>
       <c r="S5" t="n">
-        <v>34.94560635405771</v>
+        <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1026766078262194</v>
+        <v>-0.08616739350927723</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4262295081967213</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="V5" t="n">
         <v>216.0211675795551</v>
@@ -14949,22 +16276,22 @@
         <v>286.0812028062892</v>
       </c>
       <c r="X5" t="n">
-        <v>246.315638285845</v>
+        <v>246.0063921814846</v>
       </c>
       <c r="Y5" t="n">
-        <v>227.5612029123645</v>
+        <v>227.2476061064409</v>
       </c>
       <c r="Z5" t="n">
-        <v>265.0700736593256</v>
+        <v>264.7651782565283</v>
       </c>
       <c r="AA5" t="n">
-        <v>224.582265367069</v>
+        <v>224.614774504466</v>
       </c>
       <c r="AB5" t="n">
-        <v>271.5273613710284</v>
+        <v>271.4569227019115</v>
       </c>
       <c r="AC5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -14973,25 +16300,25 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.51178144271168</v>
+        <v>31.49325682541734</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.71949797269831</v>
+        <v>31.70574133476002</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.357948337747321</v>
+        <v>2.357234842691278</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.66513197724623</v>
+        <v>28.68730787120271</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.72357096864921</v>
+        <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.02491888468083014</v>
+        <v>-0.01706780533220313</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.459016393442623</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="AM5" t="n">
         <v>215.4251391678176</v>
@@ -15000,30 +16327,30 @@
         <v>286.0812028062892</v>
       </c>
       <c r="AO5" t="n">
-        <v>244.8465418098697</v>
+        <v>244.7026055334927</v>
       </c>
       <c r="AP5" t="n">
-        <v>226.525283225573</v>
+        <v>226.3868908057815</v>
       </c>
       <c r="AQ5" t="n">
-        <v>263.1678003941664</v>
+        <v>263.0183202612039</v>
       </c>
       <c r="AR5" t="n">
-        <v>222.7280754632032</v>
+        <v>222.9003821592451</v>
       </c>
       <c r="AS5" t="n">
-        <v>269.8021464264044</v>
+        <v>269.7457944989703</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15055,16 +16382,16 @@
         <v>298.01</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>36.078693</v>
+        <v>36.122425</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -15073,49 +16400,49 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.75780544383156</v>
+        <v>34.77911009274114</v>
       </c>
       <c r="P6" t="n">
-        <v>34.611391477947</v>
+        <v>34.70521162525717</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.918420379816403</v>
+        <v>1.910011629370365</v>
       </c>
       <c r="R6" t="n">
-        <v>32.08860759493671</v>
+        <v>32.092278396027</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38741008767781</v>
+        <v>37.38147763305368</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6885287344032743</v>
+        <v>0.7033019519895181</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7049180327868853</v>
+        <v>0.7258064516129032</v>
       </c>
       <c r="V6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="W6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>287.0994729660487</v>
+        <v>286.9276582651144</v>
       </c>
       <c r="Y6" t="n">
-        <v>271.2533206287652</v>
+        <v>271.1700623228089</v>
       </c>
       <c r="Z6" t="n">
-        <v>302.9456253033322</v>
+        <v>302.6852542074199</v>
       </c>
       <c r="AA6" t="n">
-        <v>265.0518987341772</v>
+        <v>264.7612967672227</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.8200073242188</v>
+        <v>308.3971904726929</v>
       </c>
       <c r="AC6" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -15124,57 +16451,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.42386485068192</v>
+        <v>34.43731874357252</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.42623029342849</v>
+        <v>34.44810312005538</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.708321117507143</v>
+        <v>1.707836039599991</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13088525699663</v>
+        <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.69222629741434</v>
+        <v>36.68740034742586</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9686868190992587</v>
+        <v>0.9866908868032591</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7868852459016393</v>
+        <v>0.7967479674796748</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.3411236666326</v>
+        <v>284.1078796344733</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.2303912360236</v>
+        <v>270.0182323077734</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.4518560972416</v>
+        <v>298.1975269611732</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.4011122227922</v>
+        <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.0777892166424</v>
+        <v>302.6710528662633</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15215,7 +16542,7 @@
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
         <v>30.69218961239591</v>
@@ -15224,25 +16551,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.78236576140846</v>
+        <v>37.69337488559808</v>
       </c>
       <c r="P7" t="n">
-        <v>36.46530462771046</v>
+        <v>36.40612232441805</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.836439385635218</v>
+        <v>4.847544309526713</v>
       </c>
       <c r="R7" t="n">
-        <v>31.88208306912806</v>
+        <v>31.8889742934503</v>
       </c>
       <c r="S7" t="n">
-        <v>44.78367396763392</v>
+        <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.140805315951209</v>
+        <v>-1.11983398995028</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="V7" t="n">
         <v>200.4199981689453</v>
@@ -15251,22 +16578,22 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>246.7188484219972</v>
+        <v>246.1377380029554</v>
       </c>
       <c r="Y7" t="n">
-        <v>215.1368992337993</v>
+        <v>214.483273661746</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.3007976101952</v>
+        <v>277.7922023441649</v>
       </c>
       <c r="AA7" t="n">
-        <v>208.1900024414062</v>
+        <v>208.2350021362304</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.4373910086495</v>
+        <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="n">
         <v>30.69218961239591</v>
@@ -15275,25 +16602,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.64187315897667</v>
+        <v>37.57466138775402</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.15918404715401</v>
+        <v>37.14387699049346</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.273034170005802</v>
+        <v>4.28825028148125</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.25727402597985</v>
+        <v>32.23353784628338</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.97591789401307</v>
+        <v>43.94714230907206</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.258343122252489</v>
+        <v>-1.23820463807442</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1012658227848101</v>
+        <v>0.1</v>
       </c>
       <c r="AM7" t="n">
         <v>200.4199981689453</v>
@@ -15302,30 +16629,30 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>245.8014317281177</v>
+        <v>245.3625388620338</v>
       </c>
       <c r="AP7" t="n">
-        <v>217.8985185979798</v>
+        <v>217.3602645239612</v>
       </c>
       <c r="AQ7" t="n">
-        <v>273.7043448582556</v>
+        <v>273.3648132001063</v>
       </c>
       <c r="AR7" t="n">
-        <v>210.6399993896484</v>
+        <v>210.4850021362305</v>
       </c>
       <c r="AS7" t="n">
-        <v>287.1627438479053</v>
+        <v>286.9748392782406</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15366,7 +16693,7 @@
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
         <v>73.97735595703125</v>
@@ -15375,22 +16702,22 @@
         <v>179.4295113985656</v>
       </c>
       <c r="O8" t="n">
-        <v>127.9009013707825</v>
+        <v>128.6797075364954</v>
       </c>
       <c r="P8" t="n">
-        <v>134.0603810436321</v>
+        <v>134.9072377009912</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.04072980407927</v>
+        <v>33.33764677019743</v>
       </c>
       <c r="R8" t="n">
-        <v>79.32453083542158</v>
+        <v>79.59962492169075</v>
       </c>
       <c r="S8" t="n">
-        <v>168.0262231045082</v>
+        <v>169.0944183849898</v>
       </c>
       <c r="T8" t="n">
-        <v>1.568412953845212</v>
+        <v>1.53108294701637</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -15402,22 +16729,22 @@
         <v>536.4942390817112</v>
       </c>
       <c r="X8" t="n">
-        <v>382.4236950986397</v>
+        <v>384.7523255341212</v>
       </c>
       <c r="Y8" t="n">
-        <v>283.6319129844427</v>
+        <v>285.0727616912308</v>
       </c>
       <c r="Z8" t="n">
-        <v>481.2154772128368</v>
+        <v>484.4318893770115</v>
       </c>
       <c r="AA8" t="n">
-        <v>237.1803471979105</v>
+        <v>238.0028785158553</v>
       </c>
       <c r="AB8" t="n">
-        <v>502.3984070824796</v>
+        <v>505.5923109711194</v>
       </c>
       <c r="AC8" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -15426,22 +16753,22 @@
         <v>179.4295113985656</v>
       </c>
       <c r="AF8" t="n">
-        <v>110.7139063484845</v>
+        <v>111.2462069769113</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.9187189111568</v>
+        <v>105.9310311754349</v>
       </c>
       <c r="AH8" t="n">
-        <v>31.96944601810756</v>
+        <v>32.3808487181543</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51811131891215</v>
+        <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>160.7022915199155</v>
+        <v>162.1304931640625</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.158576773974405</v>
+        <v>2.114713039769633</v>
       </c>
       <c r="AL8" t="n">
         <v>1</v>
@@ -15453,30 +16780,30 @@
         <v>536.4942390817112</v>
       </c>
       <c r="AO8" t="n">
-        <v>331.0345799819687</v>
+        <v>332.6261588609648</v>
       </c>
       <c r="AP8" t="n">
-        <v>235.4459363878271</v>
+        <v>235.8074211936834</v>
       </c>
       <c r="AQ8" t="n">
-        <v>426.6232235761103</v>
+        <v>429.4448965282461</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.7991528435473</v>
+        <v>225.8025376114755</v>
       </c>
       <c r="AS8" t="n">
-        <v>480.4998516445473</v>
+        <v>484.7701745605469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15517,7 +16844,7 @@
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -15526,25 +16853,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.34392740341401</v>
+        <v>75.23264245469682</v>
       </c>
       <c r="P9" t="n">
-        <v>79.03509009883652</v>
+        <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.5991758213117</v>
+        <v>9.560410307465348</v>
       </c>
       <c r="R9" t="n">
-        <v>61.31578709414597</v>
+        <v>61.37555624003113</v>
       </c>
       <c r="S9" t="n">
-        <v>83.514618455318</v>
+        <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7424259682369446</v>
+        <v>-0.7337961686873171</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2950819672131147</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="V9" t="n">
         <v>344.885442901076</v>
@@ -15553,22 +16880,22 @@
         <v>566.0559735214503</v>
       </c>
       <c r="X9" t="n">
-        <v>454.3238822425865</v>
+        <v>453.6528340018218</v>
       </c>
       <c r="Y9" t="n">
-        <v>396.4408520400769</v>
+        <v>396.0035598478058</v>
       </c>
       <c r="Z9" t="n">
-        <v>512.2069124450961</v>
+        <v>511.3021081558379</v>
       </c>
       <c r="AA9" t="n">
-        <v>369.7341961777002</v>
+        <v>370.0946041273878</v>
       </c>
       <c r="AB9" t="n">
-        <v>503.5931492855676</v>
+        <v>503.467376494826</v>
       </c>
       <c r="AC9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -15577,25 +16904,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.30794087549145</v>
+        <v>72.27652884059273</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.47694073882994</v>
+        <v>71.37106969421515</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.783390629820148</v>
+        <v>7.759250530291868</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.37563283819902</v>
+        <v>62.40428783275464</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.37543771606209</v>
+        <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.525566693237645</v>
+        <v>-0.5231534701380538</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.3032786885245902</v>
+        <v>0.3008130081300813</v>
       </c>
       <c r="AM9" t="n">
         <v>344.885442901076</v>
@@ -15604,30 +16931,30 @@
         <v>566.0559735214503</v>
       </c>
       <c r="AO9" t="n">
-        <v>436.0168834792135</v>
+        <v>435.8274689087742</v>
       </c>
       <c r="AP9" t="n">
-        <v>389.083037981398</v>
+        <v>389.0391882111143</v>
       </c>
       <c r="AQ9" t="n">
-        <v>482.950728977029</v>
+        <v>482.6157496064341</v>
       </c>
       <c r="AR9" t="n">
-        <v>376.1250660143401</v>
+        <v>376.2978556315105</v>
       </c>
       <c r="AS9" t="n">
-        <v>496.7238894278544</v>
+        <v>496.648663222999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-19 05:54:11</t>
+          <t>2026-06-20 03:12:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS100"/>
+  <dimension ref="A1:AS109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14294,7 +14294,7 @@
         <v>36.68740034742586</v>
       </c>
       <c r="AK92" t="n">
-        <v>0.9866908868032591</v>
+        <v>0.9866908868032592</v>
       </c>
       <c r="AL92" t="n">
         <v>0.7967479674796748</v>
@@ -14400,7 +14400,7 @@
         <v>1</v>
       </c>
       <c r="V93" t="n">
-        <v>221.1922943115235</v>
+        <v>221.1922943115234</v>
       </c>
       <c r="W93" t="n">
         <v>536.4942390817112</v>
@@ -14466,7 +14466,7 @@
         <v>429.4448965282461</v>
       </c>
       <c r="AR93" t="n">
-        <v>225.8025376114755</v>
+        <v>225.8025376114756</v>
       </c>
       <c r="AS93" t="n">
         <v>484.7701745605469</v>
@@ -14533,7 +14533,7 @@
         <v>31.66105433481141</v>
       </c>
       <c r="P94" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q94" t="n">
         <v>2.414258182116304</v>
@@ -14545,7 +14545,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T94" t="n">
-        <v>-0.08616739350927723</v>
+        <v>-0.0861673935092772</v>
       </c>
       <c r="U94" t="n">
         <v>0.4354838709677419</v>
@@ -14596,7 +14596,7 @@
         <v>34.71631846833595</v>
       </c>
       <c r="AK94" t="n">
-        <v>-0.01706780533220313</v>
+        <v>-0.0170678053322031</v>
       </c>
       <c r="AL94" t="n">
         <v>0.4634146341463415</v>
@@ -14617,7 +14617,7 @@
         <v>263.0183202612039</v>
       </c>
       <c r="AR94" t="n">
-        <v>222.9003821592451</v>
+        <v>222.900382159245</v>
       </c>
       <c r="AS94" t="n">
         <v>269.7457944989703</v>
@@ -14678,7 +14678,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N95" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O95" t="n">
         <v>75.23264245469682</v>
@@ -14729,7 +14729,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE95" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF95" t="n">
         <v>72.27652884059273</v>
@@ -14892,7 +14892,7 @@
         <v>1.994970284061954</v>
       </c>
       <c r="AI96" t="n">
-        <v>27.37684176855299</v>
+        <v>27.376841768553</v>
       </c>
       <c r="AJ96" t="n">
         <v>32.64955541341467</v>
@@ -14977,7 +14977,7 @@
         <v>62</v>
       </c>
       <c r="M97" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="N97" t="n">
         <v>29.31247287326389</v>
@@ -14989,7 +14989,7 @@
         <v>22.57109042080966</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.743104355887455</v>
+        <v>2.743104355887456</v>
       </c>
       <c r="R97" t="n">
         <v>21.31458229758523</v>
@@ -15001,7 +15001,7 @@
         <v>-1.081507191150274</v>
       </c>
       <c r="U97" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.0806451612903225</v>
       </c>
       <c r="V97" t="n">
         <v>566.7738059303977</v>
@@ -15028,7 +15028,7 @@
         <v>123</v>
       </c>
       <c r="AD97" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="AE97" t="n">
         <v>31.43082152229007</v>
@@ -15043,16 +15043,16 @@
         <v>2.997947029388669</v>
       </c>
       <c r="AI97" t="n">
-        <v>21.85083540482955</v>
+        <v>21.85083540482954</v>
       </c>
       <c r="AJ97" t="n">
         <v>29.28804247225144</v>
       </c>
       <c r="AK97" t="n">
-        <v>-1.691165886581371</v>
+        <v>-1.691165886581372</v>
       </c>
       <c r="AL97" t="n">
-        <v>0.04065040650406504</v>
+        <v>0.040650406504065</v>
       </c>
       <c r="AM97" t="n">
         <v>566.7738059303977</v>
@@ -15134,7 +15134,7 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O98" t="n">
-        <v>24.58311428779691</v>
+        <v>24.58311428779692</v>
       </c>
       <c r="P98" t="n">
         <v>24.57421541107486</v>
@@ -15152,7 +15152,7 @@
         <v>-1.533311713524089</v>
       </c>
       <c r="U98" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="V98" t="n">
         <v>374.3965238054668</v>
@@ -15203,7 +15203,7 @@
         <v>-1.073258211351338</v>
       </c>
       <c r="AL98" t="n">
-        <v>0.03252032520325204</v>
+        <v>0.032520325203252</v>
       </c>
       <c r="AM98" t="n">
         <v>374.3965238054668</v>
@@ -15298,7 +15298,7 @@
         <v>79</v>
       </c>
       <c r="AD99" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE99" t="n">
         <v>42.60474344487245</v>
@@ -15319,10 +15319,10 @@
         <v>39.1501964222301</v>
       </c>
       <c r="AK99" t="n">
-        <v>-0.1594180665616095</v>
+        <v>-0.1594180665616094</v>
       </c>
       <c r="AL99" t="n">
-        <v>0.2658227848101266</v>
+        <v>0.2658227848101265</v>
       </c>
       <c r="AM99" t="n">
         <v>10.81762752038992</v>
@@ -15495,6 +15495,1333 @@
       </c>
       <c r="AS100" t="n">
         <v>286.9748392782406</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>297.01</v>
+      </c>
+      <c r="I101" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J101" t="n">
+        <v>35.957626</v>
+      </c>
+      <c r="K101" t="n">
+        <v>67</v>
+      </c>
+      <c r="L101" t="n">
+        <v>61</v>
+      </c>
+      <c r="M101" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N101" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O101" t="n">
+        <v>34.89467396164991</v>
+      </c>
+      <c r="P101" t="n">
+        <v>34.80750723554782</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>1.85237359571992</v>
+      </c>
+      <c r="R101" t="n">
+        <v>32.3582284661788</v>
+      </c>
+      <c r="S101" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0.5738324281916628</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0.6557377049180327</v>
+      </c>
+      <c r="V101" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="W101" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X101" t="n">
+        <v>288.2300069232283</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>272.9294010225818</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>303.5306128238748</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>267.2789671306369</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>308.8200073242188</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>34.39844332940564</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>34.40435746680161</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.69553378949728</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>32.1253156058396</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>36.64879274751802</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>0.9195821871863996</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>0.7851239669421488</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>284.1311419008906</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>270.126032799643</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>298.1362510021382</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>265.3551069042351</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>302.7190280944988</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>551.63</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J102" t="n">
+        <v>185.11073</v>
+      </c>
+      <c r="K102" t="n">
+        <v>63</v>
+      </c>
+      <c r="L102" t="n">
+        <v>61</v>
+      </c>
+      <c r="M102" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N102" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="O102" t="n">
+        <v>131.229885843878</v>
+      </c>
+      <c r="P102" t="n">
+        <v>136.0528334131781</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>32.8576689364245</v>
+      </c>
+      <c r="R102" t="n">
+        <v>83.08678968897406</v>
+      </c>
+      <c r="S102" t="n">
+        <v>169.8655825755635</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1.639825523240091</v>
+      </c>
+      <c r="U102" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" t="n">
+        <v>220.4525207519531</v>
+      </c>
+      <c r="W102" t="n">
+        <v>538.9696441150103</v>
+      </c>
+      <c r="X102" t="n">
+        <v>391.0650598147565</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>293.1492063842114</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>488.9809132453015</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>247.5986332731427</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>506.1994360751793</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>111.9542641297903</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>106.2118229607643</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>33.24393869274672</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>75.51697928950472</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>165.2098408683402</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>2.200595619741389</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>214.728675813495</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>538.9696441150103</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>333.623707106775</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>234.5567698023898</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>432.6906444111602</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>225.0405982827241</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>492.3253257876537</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>232.79</v>
+      </c>
+      <c r="I103" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="J103" t="n">
+        <v>31.629074</v>
+      </c>
+      <c r="K103" t="n">
+        <v>67</v>
+      </c>
+      <c r="L103" t="n">
+        <v>61</v>
+      </c>
+      <c r="M103" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N103" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O103" t="n">
+        <v>31.68227978086741</v>
+      </c>
+      <c r="P103" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>2.439051291645331</v>
+      </c>
+      <c r="R103" t="n">
+        <v>28.88875532378421</v>
+      </c>
+      <c r="S103" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T103" t="n">
+        <v>-0.02181412955506843</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V103" t="n">
+        <v>204.6223672310844</v>
+      </c>
+      <c r="W103" t="n">
+        <v>270.9855408821479</v>
+      </c>
+      <c r="X103" t="n">
+        <v>233.1815791871841</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>215.2301616806745</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>251.1329966936938</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>212.6212391830518</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>257.1996627658647</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>31.43505776156092</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>31.68181642961274</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>2.392275986747657</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>28.62901035878116</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>34.73082346896248</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>0.08110111020377905</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0.4958677685950413</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>204.0577894819997</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>270.9855408821479</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>231.3620251250884</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>213.7548738626257</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>248.9691763875512</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>210.7095162406294</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>255.6188607315638</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="I104" t="n">
+        <v>6</v>
+      </c>
+      <c r="J104" t="n">
+        <v>65.355</v>
+      </c>
+      <c r="K104" t="n">
+        <v>34</v>
+      </c>
+      <c r="L104" t="n">
+        <v>61</v>
+      </c>
+      <c r="M104" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N104" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O104" t="n">
+        <v>75.48783286839652</v>
+      </c>
+      <c r="P104" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>9.437891127587715</v>
+      </c>
+      <c r="R104" t="n">
+        <v>61.31578709414597</v>
+      </c>
+      <c r="S104" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T104" t="n">
+        <v>-1.073633159295241</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0.2459016393442623</v>
+      </c>
+      <c r="V104" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="W104" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="X104" t="n">
+        <v>452.9269972103791</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>396.2996504448528</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>509.5543439759055</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>367.8947225648758</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>501.087710731908</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>72.20679671751905</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>70.01886587722747</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>7.848172999741466</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>62.34697784364341</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>82.38791304025038</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>-0.8730435373614677</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0.2066115702479339</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>433.2407803051143</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>386.1517423066655</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>480.3298183035631</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>374.0818670618605</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>494.3274782415023</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="I105" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J105" t="n">
+        <v>26.60412</v>
+      </c>
+      <c r="K105" t="n">
+        <v>37</v>
+      </c>
+      <c r="L105" t="n">
+        <v>61</v>
+      </c>
+      <c r="M105" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N105" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O105" t="n">
+        <v>28.98041032106441</v>
+      </c>
+      <c r="P105" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1.684465465516435</v>
+      </c>
+      <c r="R105" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S105" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T105" t="n">
+        <v>-1.410708838922898</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0.08196721311475409</v>
+      </c>
+      <c r="V105" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W105" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X105" t="n">
+        <v>379.9331793091544</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>357.8498370562339</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>402.0165215620749</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>353.3200073242188</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>409.5874601323553</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>29.60391866605167</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>29.25019078723899</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>2.018334193268439</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>27.31960363555373</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>32.65942708172662</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>-1.486274510958894</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>0.04132231404958678</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>388.1073737119373</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>361.6470124381881</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>414.5677349856866</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>358.1600036621094</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>428.165089041436</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>563.85</v>
+      </c>
+      <c r="I106" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="J106" t="n">
+        <v>20.488733</v>
+      </c>
+      <c r="K106" t="n">
+        <v>55</v>
+      </c>
+      <c r="L106" t="n">
+        <v>61</v>
+      </c>
+      <c r="M106" t="n">
+        <v>20.50363547585227</v>
+      </c>
+      <c r="N106" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O106" t="n">
+        <v>23.85775830687447</v>
+      </c>
+      <c r="P106" t="n">
+        <v>22.42945445667614</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2.785640648891408</v>
+      </c>
+      <c r="R106" t="n">
+        <v>21.25781915838068</v>
+      </c>
+      <c r="S106" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T106" t="n">
+        <v>-1.209425669536819</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>564.2600482954546</v>
+      </c>
+      <c r="W106" t="n">
+        <v>806.6792534722222</v>
+      </c>
+      <c r="X106" t="n">
+        <v>656.5655086051854</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>579.9046779476938</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>733.226339262677</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>585.0151832386363</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>786.5167109009152</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>20.50363547585227</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>25.93798019953039</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>27.16815635060797</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>3.015721856594646</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>21.82581898082386</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>29.17581833602054</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>-1.806946216745492</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>564.2600482954546</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>864.9762082934226</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>713.8132150910762</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>630.8205495975916</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>796.8058805845609</v>
+      </c>
+      <c r="AR106" t="n">
+        <v>600.6465383522727</v>
+      </c>
+      <c r="AS106" t="n">
+        <v>802.9185206072852</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="I107" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J107" t="n">
+        <v>21.878498</v>
+      </c>
+      <c r="K107" t="n">
+        <v>67</v>
+      </c>
+      <c r="L107" t="n">
+        <v>61</v>
+      </c>
+      <c r="M107" t="n">
+        <v>21.86547597249349</v>
+      </c>
+      <c r="N107" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O107" t="n">
+        <v>24.56975857165021</v>
+      </c>
+      <c r="P107" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1.331320387986226</v>
+      </c>
+      <c r="R107" t="n">
+        <v>23.10006223372029</v>
+      </c>
+      <c r="S107" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T107" t="n">
+        <v>-2.021497301427984</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V107" t="n">
+        <v>367.1213415781656</v>
+      </c>
+      <c r="W107" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X107" t="n">
+        <v>412.526246418007</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>390.1733771037183</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>434.8791157322958</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>387.8500449041637</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>445.3812671348853</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>121</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>21.86547597249349</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>34.68776610633557</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>26.34512818442852</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>25.08693024693168</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>3.528267993412961</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>23.28267720731219</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>33.47581887821724</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>-1.265955475255115</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0.008264462809917356</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>367.1213415781656</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>582.4075929253742</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>442.3347022165548</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>383.0950826071512</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>501.5743218259584</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>390.9161503107716</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>562.0589989652674</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>23.509678</v>
+      </c>
+      <c r="K108" t="n">
+        <v>67</v>
+      </c>
+      <c r="L108" t="n">
+        <v>16</v>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>28.20461135814696</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>33.44466318726067</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>14.05813075953811</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>3.754803650361255</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>39.16798316442917</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>-0.3339656913463799</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>87.43429521025557</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>43.85408985568741</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>131.0145005648237</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>11.63989131611989</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>121.4207478097304</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:47:51</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>208.65</v>
+      </c>
+      <c r="I109" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J109" t="n">
+        <v>31.952524</v>
+      </c>
+      <c r="K109" t="n">
+        <v>65</v>
+      </c>
+      <c r="L109" t="n">
+        <v>61</v>
+      </c>
+      <c r="M109" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="N109" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O109" t="n">
+        <v>37.66134048392047</v>
+      </c>
+      <c r="P109" t="n">
+        <v>36.46530462771046</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>4.931431187568819</v>
+      </c>
+      <c r="R109" t="n">
+        <v>31.88208306912806</v>
+      </c>
+      <c r="S109" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T109" t="n">
+        <v>-1.157638881449119</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="V109" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="W109" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X109" t="n">
+        <v>245.9285533600007</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>213.7263077051763</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>278.1307990148251</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>208.1900024414062</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>292.4373910086495</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>81</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>37.50525230722248</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>37.12856993383291</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>4.306907719344029</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>31.95252586469898</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>43.91836672413105</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>-1.289261035773526</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>0.09876543209876543</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>200.4199981689453</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>244.9092975661628</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>216.7851901588463</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>273.0334049734793</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>208.6499938964843</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>286.7869347085758</v>
       </c>
     </row>
   </sheetData>
@@ -15741,12 +17068,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -15775,19 +17102,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>367.46</v>
+        <v>348.78</v>
       </c>
       <c r="I2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>28.007622</v>
+        <v>26.60412</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M2" t="n">
         <v>25.26734640596091</v>
@@ -15796,49 +17123,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.96153777226066</v>
+        <v>28.98041032106441</v>
       </c>
       <c r="P2" t="n">
-        <v>29.21870597964289</v>
+        <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.675658126040633</v>
+        <v>1.684465465516435</v>
       </c>
       <c r="R2" t="n">
-        <v>26.96842149957094</v>
+        <v>26.95042008575277</v>
       </c>
       <c r="S2" t="n">
-        <v>31.22081491927324</v>
+        <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5692782778517255</v>
+        <v>-1.410708838922898</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.08196721311475409</v>
       </c>
       <c r="V2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="W2" t="n">
-        <v>422.9955833357424</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>379.9753755720599</v>
+        <v>379.9331793091544</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.9907409584068</v>
+        <v>357.8498370562339</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.960010185713</v>
+        <v>402.0165215620749</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.8256900743707</v>
+        <v>353.3200073242188</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.6170917408649</v>
+        <v>409.5874601323553</v>
       </c>
       <c r="AC2" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -15847,57 +17174,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.66283155944916</v>
+        <v>29.60391866605167</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.27688843052775</v>
+        <v>29.25019078723899</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.994970284061954</v>
+        <v>2.018334193268439</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.37684176855299</v>
+        <v>27.31960363555373</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.64955541341467</v>
+        <v>32.65942708172662</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.8296913355917233</v>
+        <v>-1.486274510958894</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.04132231404958678</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.7016702785662</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>389.176350059973</v>
+        <v>388.1073737119373</v>
       </c>
       <c r="AP2" t="n">
-        <v>363.0023399330802</v>
+        <v>361.6470124381881</v>
       </c>
       <c r="AQ2" t="n">
-        <v>415.3503601868658</v>
+        <v>414.5677349856866</v>
       </c>
       <c r="AR2" t="n">
-        <v>359.1841640034152</v>
+        <v>358.1600036621094</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.3621670240005</v>
+        <v>428.165089041436</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -15926,129 +17253,129 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>379.4</v>
+        <v>367.34</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>22.610249</v>
+        <v>21.878498</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M3" t="n">
-        <v>22.31206935670243</v>
+        <v>21.86547597249349</v>
       </c>
       <c r="N3" t="n">
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.58311428779691</v>
+        <v>24.56975857165021</v>
       </c>
       <c r="P3" t="n">
-        <v>24.57421541107486</v>
+        <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.286669416528865</v>
+        <v>1.331320387986226</v>
       </c>
       <c r="R3" t="n">
-        <v>23.15447226996121</v>
+        <v>23.10006223372029</v>
       </c>
       <c r="S3" t="n">
-        <v>26.51801151659729</v>
+        <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.533311713524089</v>
+        <v>-2.021497301427984</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="V3" t="n">
-        <v>374.3965238054668</v>
+        <v>367.1213415781656</v>
       </c>
       <c r="W3" t="n">
-        <v>459.9717509315128</v>
+        <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>412.5046577492323</v>
+        <v>412.526246418007</v>
       </c>
       <c r="Y3" t="n">
-        <v>390.9143449398779</v>
+        <v>390.1733771037183</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.0949705585866</v>
+        <v>434.8791157322958</v>
       </c>
       <c r="AA3" t="n">
-        <v>388.5320446899491</v>
+        <v>387.8500449041637</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.9722332485025</v>
+        <v>445.3812671348853</v>
       </c>
       <c r="AC3" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD3" t="n">
-        <v>22.31206935670243</v>
+        <v>21.86547597249349</v>
       </c>
       <c r="AE3" t="n">
-        <v>34.70981429684721</v>
+        <v>34.68776610633557</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.58309578658972</v>
+        <v>26.34512818442852</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.11428651355562</v>
+        <v>25.08693024693168</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.701669127308623</v>
+        <v>3.528267993412961</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.3125699289595</v>
+        <v>23.28267720731219</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33.87852024387669</v>
+        <v>33.47581887821724</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.073258211351338</v>
+        <v>-1.265955475255115</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.03252032520325204</v>
+        <v>0.008264462809917356</v>
       </c>
       <c r="AM3" t="n">
-        <v>374.3965238054668</v>
+        <v>367.1213415781656</v>
       </c>
       <c r="AN3" t="n">
-        <v>582.4306839010962</v>
+        <v>582.4075929253742</v>
       </c>
       <c r="AO3" t="n">
-        <v>446.0643472989755</v>
+        <v>442.3347022165548</v>
       </c>
       <c r="AP3" t="n">
-        <v>383.9503393427368</v>
+        <v>383.0950826071512</v>
       </c>
       <c r="AQ3" t="n">
-        <v>508.1783552552142</v>
+        <v>501.5743218259584</v>
       </c>
       <c r="AR3" t="n">
-        <v>391.1849234079405</v>
+        <v>390.9161503107716</v>
       </c>
       <c r="AS3" t="n">
-        <v>568.4815696922508</v>
+        <v>562.0589989652674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -16077,129 +17404,129 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>577.22</v>
+        <v>563.85</v>
       </c>
       <c r="I4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="J4" t="n">
-        <v>20.997452</v>
+        <v>20.488733</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M4" t="n">
-        <v>20.61745383522727</v>
+        <v>20.50363547585227</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.96413908696792</v>
+        <v>23.85775830687447</v>
       </c>
       <c r="P4" t="n">
-        <v>22.57109042080966</v>
+        <v>22.42945445667614</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.743104355887455</v>
+        <v>2.785640648891408</v>
       </c>
       <c r="R4" t="n">
-        <v>21.31458229758523</v>
+        <v>21.25781915838068</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57799154893039</v>
+        <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.081507191150274</v>
+        <v>-1.209425669536819</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08064516129032258</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>566.7738059303977</v>
+        <v>564.2600482954546</v>
       </c>
       <c r="W4" t="n">
-        <v>805.7998792860242</v>
+        <v>806.6792534722222</v>
       </c>
       <c r="X4" t="n">
-        <v>658.7741835007481</v>
+        <v>656.5655086051854</v>
       </c>
       <c r="Y4" t="n">
-        <v>583.366244757402</v>
+        <v>579.9046779476938</v>
       </c>
       <c r="Z4" t="n">
-        <v>734.1821222440943</v>
+        <v>733.226339262677</v>
       </c>
       <c r="AA4" t="n">
-        <v>585.9378673606179</v>
+        <v>585.0151832386363</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.6089876800964</v>
+        <v>786.5167109009152</v>
       </c>
       <c r="AC4" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.61745383522727</v>
+        <v>20.50363547585227</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>26.06747774588008</v>
+        <v>25.93798019953039</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.21583600651208</v>
+        <v>27.16815635060797</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.997947029388669</v>
+        <v>3.015721856594646</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.85083540482955</v>
+        <v>21.82581898082386</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.28804247225144</v>
+        <v>29.17581833602054</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.691165886581371</v>
+        <v>-1.806946216745492</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04065040650406504</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>566.7738059303977</v>
+        <v>564.2600482954546</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.0332836477539</v>
+        <v>864.9762082934226</v>
       </c>
       <c r="AO4" t="n">
-        <v>716.5949632342432</v>
+        <v>713.8132150910762</v>
       </c>
       <c r="AP4" t="n">
-        <v>634.1813993963488</v>
+        <v>630.8205495975916</v>
       </c>
       <c r="AQ4" t="n">
-        <v>799.0085270721378</v>
+        <v>796.8058805845609</v>
       </c>
       <c r="AR4" t="n">
-        <v>600.6794652787642</v>
+        <v>600.6465383522727</v>
       </c>
       <c r="AS4" t="n">
-        <v>805.1282875621921</v>
+        <v>802.9185206072852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -16228,19 +17555,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>244.39</v>
+        <v>232.79</v>
       </c>
       <c r="I5" t="n">
-        <v>7.77</v>
+        <v>7.36</v>
       </c>
       <c r="J5" t="n">
-        <v>31.453024</v>
+        <v>31.629074</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M5" t="n">
         <v>27.80195206944081</v>
@@ -16249,49 +17576,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.66105433481141</v>
+        <v>31.68227978086741</v>
       </c>
       <c r="P5" t="n">
-        <v>31.71949797269831</v>
+        <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.414258182116304</v>
+        <v>2.439051291645331</v>
       </c>
       <c r="R5" t="n">
-        <v>28.90795038667516</v>
+        <v>28.88875532378421</v>
       </c>
       <c r="S5" t="n">
-        <v>34.93654088827689</v>
+        <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.08616739350927723</v>
+        <v>-0.02181412955506843</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>216.0211675795551</v>
+        <v>204.6223672310844</v>
       </c>
       <c r="W5" t="n">
-        <v>286.0812028062892</v>
+        <v>270.9855408821479</v>
       </c>
       <c r="X5" t="n">
-        <v>246.0063921814846</v>
+        <v>233.1815791871841</v>
       </c>
       <c r="Y5" t="n">
-        <v>227.2476061064409</v>
+        <v>215.2301616806745</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.7651782565283</v>
+        <v>251.1329966936938</v>
       </c>
       <c r="AA5" t="n">
-        <v>224.614774504466</v>
+        <v>212.6212391830518</v>
       </c>
       <c r="AB5" t="n">
-        <v>271.4569227019115</v>
+        <v>257.1996627658647</v>
       </c>
       <c r="AC5" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -16300,57 +17627,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.49325682541734</v>
+        <v>31.43505776156092</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.70574133476002</v>
+        <v>31.68181642961274</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.357234842691278</v>
+        <v>2.392275986747657</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.68730787120271</v>
+        <v>28.62901035878116</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.71631846833595</v>
+        <v>34.73082346896248</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01706780533220313</v>
+        <v>0.08110111020377905</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4958677685950413</v>
       </c>
       <c r="AM5" t="n">
-        <v>215.4251391678176</v>
+        <v>204.0577894819997</v>
       </c>
       <c r="AN5" t="n">
-        <v>286.0812028062892</v>
+        <v>270.9855408821479</v>
       </c>
       <c r="AO5" t="n">
-        <v>244.7026055334927</v>
+        <v>231.3620251250884</v>
       </c>
       <c r="AP5" t="n">
-        <v>226.3868908057815</v>
+        <v>213.7548738626257</v>
       </c>
       <c r="AQ5" t="n">
-        <v>263.0183202612039</v>
+        <v>248.9691763875512</v>
       </c>
       <c r="AR5" t="n">
-        <v>222.9003821592451</v>
+        <v>210.7095162406294</v>
       </c>
       <c r="AS5" t="n">
-        <v>269.7457944989703</v>
+        <v>255.6188607315638</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -16379,19 +17706,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>298.01</v>
+        <v>297.01</v>
       </c>
       <c r="I6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>36.122425</v>
+        <v>35.957626</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M6" t="n">
         <v>31.21898795984968</v>
@@ -16400,49 +17727,49 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.77911009274114</v>
+        <v>34.89467396164991</v>
       </c>
       <c r="P6" t="n">
-        <v>34.70521162525717</v>
+        <v>34.80750723554782</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.910011629370365</v>
+        <v>1.85237359571992</v>
       </c>
       <c r="R6" t="n">
-        <v>32.092278396027</v>
+        <v>32.3582284661788</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38147763305368</v>
+        <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7033019519895181</v>
+        <v>0.5738324281916628</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="V6" t="n">
-        <v>257.5566506687599</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="W6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>286.9276582651144</v>
+        <v>288.2300069232283</v>
       </c>
       <c r="Y6" t="n">
-        <v>271.1700623228089</v>
+        <v>272.9294010225818</v>
       </c>
       <c r="Z6" t="n">
-        <v>302.6852542074199</v>
+        <v>303.5306128238748</v>
       </c>
       <c r="AA6" t="n">
-        <v>264.7612967672227</v>
+        <v>267.2789671306369</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.3971904726929</v>
+        <v>308.8200073242188</v>
       </c>
       <c r="AC6" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -16451,57 +17778,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.43731874357252</v>
+        <v>34.39844332940564</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.44810312005538</v>
+        <v>34.40435746680161</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.707836039599991</v>
+        <v>1.69553378949728</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13645490815368</v>
+        <v>32.1253156058396</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.68740034742586</v>
+        <v>36.64879274751802</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9866908868032591</v>
+        <v>0.9195821871863996</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7967479674796748</v>
+        <v>0.7851239669421488</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.5566506687599</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="AN6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.1078796344733</v>
+        <v>284.1311419008906</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.0182323077734</v>
+        <v>270.126032799643</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.1975269611732</v>
+        <v>298.1362510021382</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.1257529922678</v>
+        <v>265.3551069042351</v>
       </c>
       <c r="AS6" t="n">
-        <v>302.6710528662633</v>
+        <v>302.7190280944988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -16530,19 +17857,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>210.69</v>
+        <v>208.65</v>
       </c>
       <c r="I7" t="n">
         <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>32.26493</v>
+        <v>31.952524</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M7" t="n">
         <v>30.69218961239591</v>
@@ -16551,25 +17878,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.69337488559808</v>
+        <v>37.66134048392047</v>
       </c>
       <c r="P7" t="n">
-        <v>36.40612232441805</v>
+        <v>36.46530462771046</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.847544309526713</v>
+        <v>4.931431187568819</v>
       </c>
       <c r="R7" t="n">
-        <v>31.8889742934503</v>
+        <v>31.88208306912806</v>
       </c>
       <c r="S7" t="n">
-        <v>44.72591882822464</v>
+        <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.11983398995028</v>
+        <v>-1.157638881449119</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="V7" t="n">
         <v>200.4199981689453</v>
@@ -16578,22 +17905,22 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>246.1377380029554</v>
+        <v>245.9285533600007</v>
       </c>
       <c r="Y7" t="n">
-        <v>214.483273661746</v>
+        <v>213.7263077051763</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.7922023441649</v>
+        <v>278.1307990148251</v>
       </c>
       <c r="AA7" t="n">
-        <v>208.2350021362304</v>
+        <v>208.1900024414062</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.0602499483069</v>
+        <v>292.4373910086495</v>
       </c>
       <c r="AC7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AD7" t="n">
         <v>30.69218961239591</v>
@@ -16602,25 +17929,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.57466138775402</v>
+        <v>37.50525230722248</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.14387699049346</v>
+        <v>37.12856993383291</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.28825028148125</v>
+        <v>4.306907719344029</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.23353784628338</v>
+        <v>31.95252586469898</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.94714230907206</v>
+        <v>43.91836672413105</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.23820463807442</v>
+        <v>-1.289261035773526</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1</v>
+        <v>0.09876543209876543</v>
       </c>
       <c r="AM7" t="n">
         <v>200.4199981689453</v>
@@ -16629,30 +17956,30 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>245.3625388620338</v>
+        <v>244.9092975661628</v>
       </c>
       <c r="AP7" t="n">
-        <v>217.3602645239612</v>
+        <v>216.7851901588463</v>
       </c>
       <c r="AQ7" t="n">
-        <v>273.3648132001063</v>
+        <v>273.0334049734793</v>
       </c>
       <c r="AR7" t="n">
-        <v>210.4850021362305</v>
+        <v>208.6499938964843</v>
       </c>
       <c r="AS7" t="n">
-        <v>286.9748392782406</v>
+        <v>286.7869347085758</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -16681,129 +18008,129 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>537.37</v>
+        <v>551.63</v>
       </c>
       <c r="I8" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="n">
-        <v>179.72241</v>
+        <v>185.11073</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
         <v>73.97735595703125</v>
       </c>
       <c r="N8" t="n">
-        <v>179.4295113985656</v>
+        <v>180.8622966828894</v>
       </c>
       <c r="O8" t="n">
-        <v>128.6797075364954</v>
+        <v>131.229885843878</v>
       </c>
       <c r="P8" t="n">
-        <v>134.9072377009912</v>
+        <v>136.0528334131781</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.33764677019743</v>
+        <v>32.8576689364245</v>
       </c>
       <c r="R8" t="n">
-        <v>79.59962492169075</v>
+        <v>83.08678968897406</v>
       </c>
       <c r="S8" t="n">
-        <v>169.0944183849898</v>
+        <v>169.8655825755635</v>
       </c>
       <c r="T8" t="n">
-        <v>1.53108294701637</v>
+        <v>1.639825523240091</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>221.1922943115235</v>
+        <v>220.4525207519531</v>
       </c>
       <c r="W8" t="n">
-        <v>536.4942390817112</v>
+        <v>538.9696441150103</v>
       </c>
       <c r="X8" t="n">
-        <v>384.7523255341212</v>
+        <v>391.0650598147565</v>
       </c>
       <c r="Y8" t="n">
-        <v>285.0727616912308</v>
+        <v>293.1492063842114</v>
       </c>
       <c r="Z8" t="n">
-        <v>484.4318893770115</v>
+        <v>488.9809132453015</v>
       </c>
       <c r="AA8" t="n">
-        <v>238.0028785158553</v>
+        <v>247.5986332731427</v>
       </c>
       <c r="AB8" t="n">
-        <v>505.5923109711194</v>
+        <v>506.1994360751793</v>
       </c>
       <c r="AC8" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
       </c>
       <c r="AE8" t="n">
-        <v>179.4295113985656</v>
+        <v>180.8622966828894</v>
       </c>
       <c r="AF8" t="n">
-        <v>111.2462069769113</v>
+        <v>111.9542641297903</v>
       </c>
       <c r="AG8" t="n">
-        <v>105.9310311754349</v>
+        <v>106.2118229607643</v>
       </c>
       <c r="AH8" t="n">
-        <v>32.3808487181543</v>
+        <v>33.24393869274672</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51924334831958</v>
+        <v>75.51697928950472</v>
       </c>
       <c r="AJ8" t="n">
-        <v>162.1304931640625</v>
+        <v>165.2098408683402</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.114713039769633</v>
+        <v>2.200595619741389</v>
       </c>
       <c r="AL8" t="n">
         <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>215.4492418397148</v>
+        <v>214.728675813495</v>
       </c>
       <c r="AN8" t="n">
-        <v>536.4942390817112</v>
+        <v>538.9696441150103</v>
       </c>
       <c r="AO8" t="n">
-        <v>332.6261588609648</v>
+        <v>333.623707106775</v>
       </c>
       <c r="AP8" t="n">
-        <v>235.8074211936834</v>
+        <v>234.5567698023898</v>
       </c>
       <c r="AQ8" t="n">
-        <v>429.4448965282461</v>
+        <v>432.6906444111602</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.8025376114755</v>
+        <v>225.0405982827241</v>
       </c>
       <c r="AS8" t="n">
-        <v>484.7701745605469</v>
+        <v>492.3253257876537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -16832,19 +18159,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>411.35</v>
+        <v>392.13</v>
       </c>
       <c r="I9" t="n">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>68.21725000000001</v>
+        <v>65.355</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -16853,49 +18180,49 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.23264245469682</v>
+        <v>75.48783286839652</v>
       </c>
       <c r="P9" t="n">
-        <v>78.71540210865163</v>
+        <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.560410307465348</v>
+        <v>9.437891127587715</v>
       </c>
       <c r="R9" t="n">
-        <v>61.37555624003113</v>
+        <v>61.31578709414597</v>
       </c>
       <c r="S9" t="n">
-        <v>83.49376061274063</v>
+        <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7337961686873171</v>
+        <v>-1.073633159295241</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2459016393442623</v>
       </c>
       <c r="V9" t="n">
-        <v>344.885442901076</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="W9" t="n">
-        <v>566.0559735214503</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="X9" t="n">
-        <v>453.6528340018218</v>
+        <v>452.9269972103791</v>
       </c>
       <c r="Y9" t="n">
-        <v>396.0035598478058</v>
+        <v>396.2996504448528</v>
       </c>
       <c r="Z9" t="n">
-        <v>511.3021081558379</v>
+        <v>509.5543439759055</v>
       </c>
       <c r="AA9" t="n">
-        <v>370.0946041273878</v>
+        <v>367.8947225648758</v>
       </c>
       <c r="AB9" t="n">
-        <v>503.467376494826</v>
+        <v>501.087710731908</v>
       </c>
       <c r="AC9" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -16904,57 +18231,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.27652884059273</v>
+        <v>72.20679671751905</v>
       </c>
       <c r="AG9" t="n">
-        <v>71.37106969421515</v>
+        <v>70.01886587722747</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.759250530291868</v>
+        <v>7.848172999741466</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.40428783275464</v>
+        <v>62.34697784364341</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.36296239187379</v>
+        <v>82.38791304025038</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.5231534701380538</v>
+        <v>-0.8730435373614677</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.3008130081300813</v>
+        <v>0.2066115702479339</v>
       </c>
       <c r="AM9" t="n">
-        <v>344.885442901076</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="AN9" t="n">
-        <v>566.0559735214503</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="AO9" t="n">
-        <v>435.8274689087742</v>
+        <v>433.2407803051143</v>
       </c>
       <c r="AP9" t="n">
-        <v>389.0391882111143</v>
+        <v>386.1517423066655</v>
       </c>
       <c r="AQ9" t="n">
-        <v>482.6157496064341</v>
+        <v>480.3298183035631</v>
       </c>
       <c r="AR9" t="n">
-        <v>376.2978556315105</v>
+        <v>374.0818670618605</v>
       </c>
       <c r="AS9" t="n">
-        <v>496.648663222999</v>
+        <v>494.3274782415023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-20 03:12:44</t>
+          <t>2026-06-23 03:47:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -16983,19 +18310,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>77.38</v>
+        <v>72.88</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>24.96129</v>
+        <v>23.509678</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -17014,7 +18341,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -17023,25 +18350,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>27.28179525407055</v>
+        <v>28.20461135814696</v>
       </c>
       <c r="AG10" t="n">
-        <v>32.99999915564012</v>
+        <v>33.44466318726067</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.55609959473293</v>
+        <v>14.05813075953811</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.76558060036566</v>
+        <v>3.754803650361255</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.1501964222301</v>
+        <v>39.16798316442917</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.1594180665616095</v>
+        <v>-0.3339656913463799</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.2658227848101266</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -17050,19 +18377,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>84.57356528761872</v>
+        <v>87.43429521025557</v>
       </c>
       <c r="AP10" t="n">
-        <v>39.44965654394665</v>
+        <v>43.85408985568741</v>
       </c>
       <c r="AQ10" t="n">
-        <v>129.6974740312908</v>
+        <v>131.0145005648237</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.67329986113355</v>
+        <v>11.63989131611989</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.3656089089133</v>
+        <v>121.4207478097304</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS109"/>
+  <dimension ref="A1:AS118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15727,7 +15727,7 @@
         <v>1</v>
       </c>
       <c r="V102" t="n">
-        <v>220.4525207519531</v>
+        <v>220.4525207519532</v>
       </c>
       <c r="W102" t="n">
         <v>538.9696441150103</v>
@@ -15787,7 +15787,7 @@
         <v>333.623707106775</v>
       </c>
       <c r="AP102" t="n">
-        <v>234.5567698023898</v>
+        <v>234.5567698023899</v>
       </c>
       <c r="AQ102" t="n">
         <v>432.6906444111602</v>
@@ -15872,7 +15872,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T103" t="n">
-        <v>-0.02181412955506843</v>
+        <v>-0.0218141295550684</v>
       </c>
       <c r="U103" t="n">
         <v>0.4426229508196721</v>
@@ -15896,7 +15896,7 @@
         <v>212.6212391830518</v>
       </c>
       <c r="AB103" t="n">
-        <v>257.1996627658647</v>
+        <v>257.1996627658648</v>
       </c>
       <c r="AC103" t="n">
         <v>121</v>
@@ -15923,7 +15923,7 @@
         <v>34.73082346896248</v>
       </c>
       <c r="AK103" t="n">
-        <v>0.08110111020377905</v>
+        <v>0.081101110203779</v>
       </c>
       <c r="AL103" t="n">
         <v>0.4958677685950413</v>
@@ -16005,7 +16005,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N104" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O104" t="n">
         <v>75.48783286839652</v>
@@ -16014,7 +16014,7 @@
         <v>79.03509009883652</v>
       </c>
       <c r="Q104" t="n">
-        <v>9.437891127587715</v>
+        <v>9.437891127587717</v>
       </c>
       <c r="R104" t="n">
         <v>61.31578709414597</v>
@@ -16056,7 +16056,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE104" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF104" t="n">
         <v>72.20679671751905</v>
@@ -16089,7 +16089,7 @@
         <v>433.2407803051143</v>
       </c>
       <c r="AP104" t="n">
-        <v>386.1517423066655</v>
+        <v>386.1517423066656</v>
       </c>
       <c r="AQ104" t="n">
         <v>480.3298183035631</v>
@@ -16177,7 +16177,7 @@
         <v>-1.410708838922898</v>
       </c>
       <c r="U105" t="n">
-        <v>0.08196721311475409</v>
+        <v>0.081967213114754</v>
       </c>
       <c r="V105" t="n">
         <v>331.2549113821476</v>
@@ -16228,7 +16228,7 @@
         <v>-1.486274510958894</v>
       </c>
       <c r="AL105" t="n">
-        <v>0.04132231404958678</v>
+        <v>0.0413223140495867</v>
       </c>
       <c r="AM105" t="n">
         <v>331.2549113821476</v>
@@ -16304,7 +16304,7 @@
         <v>61</v>
       </c>
       <c r="M106" t="n">
-        <v>20.50363547585227</v>
+        <v>20.50363547585228</v>
       </c>
       <c r="N106" t="n">
         <v>29.31247287326389</v>
@@ -16355,13 +16355,13 @@
         <v>121</v>
       </c>
       <c r="AD106" t="n">
-        <v>20.50363547585227</v>
+        <v>20.50363547585228</v>
       </c>
       <c r="AE106" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF106" t="n">
-        <v>25.93798019953039</v>
+        <v>25.93798019953038</v>
       </c>
       <c r="AG106" t="n">
         <v>27.16815635060797</v>
@@ -16464,7 +16464,7 @@
         <v>24.56975857165021</v>
       </c>
       <c r="P107" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q107" t="n">
         <v>1.331320387986226</v>
@@ -16473,13 +16473,13 @@
         <v>23.10006223372029</v>
       </c>
       <c r="S107" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T107" t="n">
         <v>-2.021497301427984</v>
       </c>
       <c r="U107" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V107" t="n">
         <v>367.1213415781656</v>
@@ -16491,7 +16491,7 @@
         <v>412.526246418007</v>
       </c>
       <c r="Y107" t="n">
-        <v>390.1733771037183</v>
+        <v>390.1733771037184</v>
       </c>
       <c r="Z107" t="n">
         <v>434.8791157322958</v>
@@ -16530,7 +16530,7 @@
         <v>-1.265955475255115</v>
       </c>
       <c r="AL107" t="n">
-        <v>0.008264462809917356</v>
+        <v>0.0082644628099173</v>
       </c>
       <c r="AM107" t="n">
         <v>367.1213415781656</v>
@@ -16625,7 +16625,7 @@
         <v>76</v>
       </c>
       <c r="AD108" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE108" t="n">
         <v>42.60474344487245</v>
@@ -16649,7 +16649,7 @@
         <v>-0.3339656913463799</v>
       </c>
       <c r="AL108" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2368421052631578</v>
       </c>
       <c r="AM108" t="n">
         <v>10.81762752038992</v>
@@ -16749,7 +16749,7 @@
         <v>-1.157638881449119</v>
       </c>
       <c r="U109" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.1311475409836065</v>
       </c>
       <c r="V109" t="n">
         <v>200.4199981689453</v>
@@ -16800,7 +16800,7 @@
         <v>-1.289261035773526</v>
       </c>
       <c r="AL109" t="n">
-        <v>0.09876543209876543</v>
+        <v>0.0987654320987654</v>
       </c>
       <c r="AM109" t="n">
         <v>200.4199981689453</v>
@@ -16812,7 +16812,7 @@
         <v>244.9092975661628</v>
       </c>
       <c r="AP109" t="n">
-        <v>216.7851901588463</v>
+        <v>216.7851901588462</v>
       </c>
       <c r="AQ109" t="n">
         <v>273.0334049734793</v>
@@ -16822,6 +16822,1333 @@
       </c>
       <c r="AS109" t="n">
         <v>286.7869347085758</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="I110" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J110" t="n">
+        <v>35.586452</v>
+      </c>
+      <c r="K110" t="n">
+        <v>67</v>
+      </c>
+      <c r="L110" t="n">
+        <v>61</v>
+      </c>
+      <c r="M110" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N110" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O110" t="n">
+        <v>34.95454812397662</v>
+      </c>
+      <c r="P110" t="n">
+        <v>35.17554331634005</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1.815154047699106</v>
+      </c>
+      <c r="R110" t="n">
+        <v>32.39493647708169</v>
+      </c>
+      <c r="S110" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0.3481268583371105</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+      <c r="V110" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="W110" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="X110" t="n">
+        <v>289.0741129852867</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>274.062789010815</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>304.0854369597582</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>267.9061246654655</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>309.1938814250955</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>34.40853427321154</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.692187571665709</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>36.64450310510222</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>0.6960917019553404</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>0.7377049180327869</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>284.5585784394594</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>270.564187221784</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>298.5529696571348</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>265.7224210753621</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>303.0500406791953</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>519.85</v>
+      </c>
+      <c r="I111" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J111" t="n">
+        <v>172.13576</v>
+      </c>
+      <c r="K111" t="n">
+        <v>63</v>
+      </c>
+      <c r="L111" t="n">
+        <v>61</v>
+      </c>
+      <c r="M111" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N111" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="O111" t="n">
+        <v>132.6613917228449</v>
+      </c>
+      <c r="P111" t="n">
+        <v>138.029504994877</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>32.62814033498378</v>
+      </c>
+      <c r="R111" t="n">
+        <v>83.08678968897406</v>
+      </c>
+      <c r="S111" t="n">
+        <v>170.442614946209</v>
+      </c>
+      <c r="T111" t="n">
+        <v>1.209825870303459</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0.9344262295081968</v>
+      </c>
+      <c r="V111" t="n">
+        <v>223.4116149902344</v>
+      </c>
+      <c r="W111" t="n">
+        <v>546.2041359823259</v>
+      </c>
+      <c r="X111" t="n">
+        <v>400.6374030029914</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>302.1004191913404</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>499.1743868146425</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>250.9221048607017</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>514.7366971375512</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>112.4336768414003</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>106.7832681283774</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>33.5270930653851</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>166.2131177558274</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.780711588749067</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>0.9672131147540983</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>217.6109399183741</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>546.2041359823259</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>339.5497040610288</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>238.2978830035658</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>440.8015251184917</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>228.0646961831147</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>501.9636156225986</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>234.11</v>
+      </c>
+      <c r="I112" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J112" t="n">
+        <v>31.636486</v>
+      </c>
+      <c r="K112" t="n">
+        <v>67</v>
+      </c>
+      <c r="L112" t="n">
+        <v>61</v>
+      </c>
+      <c r="M112" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N112" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O112" t="n">
+        <v>31.65730258415679</v>
+      </c>
+      <c r="P112" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>2.46910444743712</v>
+      </c>
+      <c r="R112" t="n">
+        <v>28.53468936025811</v>
+      </c>
+      <c r="S112" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T112" t="n">
+        <v>-0.008430823644740536</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V112" t="n">
+        <v>205.734445313862</v>
+      </c>
+      <c r="W112" t="n">
+        <v>272.4582883869421</v>
+      </c>
+      <c r="X112" t="n">
+        <v>234.2640391227602</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>215.9926662117255</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>252.5354120337949</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>211.15670126591</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>258.5974870200271</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>31.40693096507071</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>31.63875598086125</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>2.402540996553121</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>28.57754546395572</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0.09554677121373961</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>205.1667992074453</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>272.4582883869421</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>232.4112891415233</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>214.6324857670302</v>
+      </c>
+      <c r="AQ112" t="n">
+        <v>250.1900925160163</v>
+      </c>
+      <c r="AR112" t="n">
+        <v>211.4738364332723</v>
+      </c>
+      <c r="AS112" t="n">
+        <v>256.9544251680042</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>380.15</v>
+      </c>
+      <c r="I113" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="J113" t="n">
+        <v>63.252907</v>
+      </c>
+      <c r="K113" t="n">
+        <v>34</v>
+      </c>
+      <c r="L113" t="n">
+        <v>61</v>
+      </c>
+      <c r="M113" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N113" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O113" t="n">
+        <v>75.5059756953405</v>
+      </c>
+      <c r="P113" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>9.412847039944809</v>
+      </c>
+      <c r="R113" t="n">
+        <v>61.31578709414597</v>
+      </c>
+      <c r="S113" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T113" t="n">
+        <v>-1.301738851523114</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0.1475409836065574</v>
+      </c>
+      <c r="V113" t="n">
+        <v>343.7415442513212</v>
+      </c>
+      <c r="W113" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="X113" t="n">
+        <v>453.7909139289964</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>397.2197032189281</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>510.3621246390646</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>368.5078804358172</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>501.9228569164612</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>72.13340420998271</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>69.96855345911951</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>7.857603180592716</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>62.37563283819902</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>82.37543771606209</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>-1.130178886090407</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0.139344262295082</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>343.7415442513212</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>433.5217593019961</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>386.2975641866338</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>480.7459544173583</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>374.8775533575761</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>495.0763806735332</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>346.08</v>
+      </c>
+      <c r="I114" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J114" t="n">
+        <v>26.378048</v>
+      </c>
+      <c r="K114" t="n">
+        <v>37</v>
+      </c>
+      <c r="L114" t="n">
+        <v>61</v>
+      </c>
+      <c r="M114" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N114" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O114" t="n">
+        <v>28.97400186974647</v>
+      </c>
+      <c r="P114" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1.693659701972064</v>
+      </c>
+      <c r="R114" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S114" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T114" t="n">
+        <v>-1.532748205984823</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="V114" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="W114" t="n">
+        <v>422.9955833357424</v>
+      </c>
+      <c r="X114" t="n">
+        <v>380.1389045310736</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>357.9180892412002</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>402.3597198209471</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>353.5895115250763</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>409.8998838242946</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>29.57764202380655</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>29.24065608090794</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>2.030823121933937</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>27.28422627538108</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>32.65449124757065</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>-1.575515853276088</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>0.02459016393442623</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>446.7016702785662</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>388.058663352342</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>361.4142639925687</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>414.7030627121152</v>
+      </c>
+      <c r="AR114" t="n">
+        <v>357.9690487329997</v>
+      </c>
+      <c r="AS114" t="n">
+        <v>428.4269251681268</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>562.2</v>
+      </c>
+      <c r="I115" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J115" t="n">
+        <v>20.451075</v>
+      </c>
+      <c r="K115" t="n">
+        <v>55</v>
+      </c>
+      <c r="L115" t="n">
+        <v>61</v>
+      </c>
+      <c r="M115" t="n">
+        <v>20.44363680752841</v>
+      </c>
+      <c r="N115" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O115" t="n">
+        <v>23.77773193636481</v>
+      </c>
+      <c r="P115" t="n">
+        <v>22.42290926846591</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>2.812767555526313</v>
+      </c>
+      <c r="R115" t="n">
+        <v>20.98981711647727</v>
+      </c>
+      <c r="S115" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T115" t="n">
+        <v>-1.182698844001113</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V115" t="n">
+        <v>561.9955758389559</v>
+      </c>
+      <c r="W115" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X115" t="n">
+        <v>653.6498509306684</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>576.3268708292501</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>730.9728310320868</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>577.0100725319602</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>785.6593162306017</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>20.44363680752841</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>25.8929445979566</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>27.15715217824146</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>3.044151371398461</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>21.78163596413352</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>29.17568561564092</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>-1.787647503040116</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>0.00819672131147541</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>561.9955758389559</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>711.797046997827</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>628.1133257980833</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>795.4807681975707</v>
+      </c>
+      <c r="AR115" t="n">
+        <v>598.7771726540306</v>
+      </c>
+      <c r="AS115" t="n">
+        <v>802.0395975739689</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="I116" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J116" t="n">
+        <v>22.27159</v>
+      </c>
+      <c r="K116" t="n">
+        <v>67</v>
+      </c>
+      <c r="L116" t="n">
+        <v>61</v>
+      </c>
+      <c r="M116" t="n">
+        <v>21.86547597249349</v>
+      </c>
+      <c r="N116" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O116" t="n">
+        <v>24.55424759017488</v>
+      </c>
+      <c r="P116" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1.35282991442224</v>
+      </c>
+      <c r="R116" t="n">
+        <v>22.88742971986886</v>
+      </c>
+      <c r="S116" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T116" t="n">
+        <v>-1.687320457538632</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="V116" t="n">
+        <v>367.1213415781656</v>
+      </c>
+      <c r="W116" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X116" t="n">
+        <v>412.2658170390362</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>389.5518027758868</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>434.9798313021857</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>384.2799449965982</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>445.3812671348853</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>21.86547597249349</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>34.68776610633557</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>26.31162986716808</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>25.07501266985255</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>3.533085643899507</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>23.26076719757274</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>33.47304494757402</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>-1.143487668956997</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>367.1213415781656</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>582.4075929253742</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>441.772265469752</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>382.4517575086793</v>
+      </c>
+      <c r="AQ116" t="n">
+        <v>501.0927734308248</v>
+      </c>
+      <c r="AR116" t="n">
+        <v>390.5482812472462</v>
+      </c>
+      <c r="AS116" t="n">
+        <v>562.0124246697677</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>72.81999999999999</v>
+      </c>
+      <c r="I117" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>23.490324</v>
+      </c>
+      <c r="K117" t="n">
+        <v>67</v>
+      </c>
+      <c r="L117" t="n">
+        <v>15</v>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
+      <c r="AC117" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>28.20461135814696</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>33.44466318726067</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>14.05813075953811</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>3.754803650361255</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>39.16798316442917</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.3353424035374276</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>87.43429521025557</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>43.85408985568741</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>131.0145005648237</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>11.63989131611989</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>121.4207478097304</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-06-24 03:29:26</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>200.04</v>
+      </c>
+      <c r="I118" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J118" t="n">
+        <v>30.68098</v>
+      </c>
+      <c r="K118" t="n">
+        <v>65</v>
+      </c>
+      <c r="L118" t="n">
+        <v>61</v>
+      </c>
+      <c r="M118" t="n">
+        <v>30.63399590905556</v>
+      </c>
+      <c r="N118" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O118" t="n">
+        <v>37.56574525902448</v>
+      </c>
+      <c r="P118" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>5.010882221391974</v>
+      </c>
+      <c r="R118" t="n">
+        <v>31.76263455775028</v>
+      </c>
+      <c r="S118" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T118" t="n">
+        <v>-1.373962698550907</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V118" t="n">
+        <v>199.7336533270422</v>
+      </c>
+      <c r="W118" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="X118" t="n">
+        <v>244.9286590888396</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>212.2577070053639</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>277.5996111723153</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>207.0923773165318</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>291.9895542689732</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>30.63399590905556</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>37.42145649748873</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>36.97244760941486</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>4.346979524970016</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>31.9511483675853</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>43.8769381776148</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-1.550611512837808</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>199.7336533270422</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>243.9878963636265</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>215.645589860822</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>272.330202866431</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>208.3214873566561</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>286.0776369180485</v>
       </c>
     </row>
   </sheetData>
@@ -17068,12 +18395,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -17102,13 +18429,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>348.78</v>
+        <v>346.08</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.12</v>
       </c>
       <c r="J2" t="n">
-        <v>26.60412</v>
+        <v>26.378048</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -17123,13 +18450,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.98041032106441</v>
+        <v>28.97400186974647</v>
       </c>
       <c r="P2" t="n">
         <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.684465465516435</v>
+        <v>1.693659701972064</v>
       </c>
       <c r="R2" t="n">
         <v>26.95042008575277</v>
@@ -17138,34 +18465,34 @@
         <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.410708838922898</v>
+        <v>-1.532748205984823</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08196721311475409</v>
+        <v>0.04918032786885246</v>
       </c>
       <c r="V2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="W2" t="n">
-        <v>422.673178165517</v>
+        <v>422.9955833357424</v>
       </c>
       <c r="X2" t="n">
-        <v>379.9331793091544</v>
+        <v>380.1389045310736</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.8498370562339</v>
+        <v>357.9180892412002</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.0165215620749</v>
+        <v>402.3597198209471</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.3200073242188</v>
+        <v>353.5895115250763</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.5874601323553</v>
+        <v>409.8998838242946</v>
       </c>
       <c r="AC2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -17174,57 +18501,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.60391866605167</v>
+        <v>29.57764202380655</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.25019078723899</v>
+        <v>29.24065608090794</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.018334193268439</v>
+        <v>2.030823121933937</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.31960363555373</v>
+        <v>27.28422627538108</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65942708172662</v>
+        <v>32.65449124757065</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.486274510958894</v>
+        <v>-1.575515853276088</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04132231404958678</v>
+        <v>0.02459016393442623</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.3611964445124</v>
+        <v>446.7016702785662</v>
       </c>
       <c r="AO2" t="n">
-        <v>388.1073737119373</v>
+        <v>388.058663352342</v>
       </c>
       <c r="AP2" t="n">
-        <v>361.6470124381881</v>
+        <v>361.4142639925687</v>
       </c>
       <c r="AQ2" t="n">
-        <v>414.5677349856866</v>
+        <v>414.7030627121152</v>
       </c>
       <c r="AR2" t="n">
-        <v>358.1600036621094</v>
+        <v>357.9690487329997</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.165089041436</v>
+        <v>428.4269251681268</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -17253,13 +18580,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>367.34</v>
+        <v>373.94</v>
       </c>
       <c r="I3" t="n">
         <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>21.878498</v>
+        <v>22.27159</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -17274,25 +18601,25 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.56975857165021</v>
+        <v>24.55424759017488</v>
       </c>
       <c r="P3" t="n">
         <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.331320387986226</v>
+        <v>1.35282991442224</v>
       </c>
       <c r="R3" t="n">
-        <v>23.10006223372029</v>
+        <v>22.88742971986886</v>
       </c>
       <c r="S3" t="n">
         <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.021497301427984</v>
+        <v>-1.687320457538632</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="V3" t="n">
         <v>367.1213415781656</v>
@@ -17301,22 +18628,22 @@
         <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>412.526246418007</v>
+        <v>412.2658170390362</v>
       </c>
       <c r="Y3" t="n">
-        <v>390.1733771037183</v>
+        <v>389.5518027758868</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.8791157322958</v>
+        <v>434.9798313021857</v>
       </c>
       <c r="AA3" t="n">
-        <v>387.8500449041637</v>
+        <v>384.2799449965982</v>
       </c>
       <c r="AB3" t="n">
         <v>445.3812671348853</v>
       </c>
       <c r="AC3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD3" t="n">
         <v>21.86547597249349</v>
@@ -17325,25 +18652,25 @@
         <v>34.68776610633557</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.34512818442852</v>
+        <v>26.31162986716808</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.08693024693168</v>
+        <v>25.07501266985255</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.528267993412961</v>
+        <v>3.533085643899507</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.28267720731219</v>
+        <v>23.26076719757274</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33.47581887821724</v>
+        <v>33.47304494757402</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.265955475255115</v>
+        <v>-1.143487668956997</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.008264462809917356</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="AM3" t="n">
         <v>367.1213415781656</v>
@@ -17352,30 +18679,30 @@
         <v>582.4075929253742</v>
       </c>
       <c r="AO3" t="n">
-        <v>442.3347022165548</v>
+        <v>441.772265469752</v>
       </c>
       <c r="AP3" t="n">
-        <v>383.0950826071512</v>
+        <v>382.4517575086793</v>
       </c>
       <c r="AQ3" t="n">
-        <v>501.5743218259584</v>
+        <v>501.0927734308248</v>
       </c>
       <c r="AR3" t="n">
-        <v>390.9161503107716</v>
+        <v>390.5482812472462</v>
       </c>
       <c r="AS3" t="n">
-        <v>562.0589989652674</v>
+        <v>562.0124246697677</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -17404,13 +18731,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>563.85</v>
+        <v>562.2</v>
       </c>
       <c r="I4" t="n">
-        <v>27.52</v>
+        <v>27.49</v>
       </c>
       <c r="J4" t="n">
-        <v>20.488733</v>
+        <v>20.451075</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -17419,114 +18746,114 @@
         <v>61</v>
       </c>
       <c r="M4" t="n">
-        <v>20.50363547585227</v>
+        <v>20.44363680752841</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.85775830687447</v>
+        <v>23.77773193636481</v>
       </c>
       <c r="P4" t="n">
-        <v>22.42945445667614</v>
+        <v>22.42290926846591</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.785640648891408</v>
+        <v>2.812767555526313</v>
       </c>
       <c r="R4" t="n">
-        <v>21.25781915838068</v>
+        <v>20.98981711647727</v>
       </c>
       <c r="S4" t="n">
         <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.209425669536819</v>
+        <v>-1.182698844001113</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="V4" t="n">
-        <v>564.2600482954546</v>
+        <v>561.9955758389559</v>
       </c>
       <c r="W4" t="n">
-        <v>806.6792534722222</v>
+        <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>656.5655086051854</v>
+        <v>653.6498509306684</v>
       </c>
       <c r="Y4" t="n">
-        <v>579.9046779476938</v>
+        <v>576.3268708292501</v>
       </c>
       <c r="Z4" t="n">
-        <v>733.226339262677</v>
+        <v>730.9728310320868</v>
       </c>
       <c r="AA4" t="n">
-        <v>585.0151832386363</v>
+        <v>577.0100725319602</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.5167109009152</v>
+        <v>785.6593162306017</v>
       </c>
       <c r="AC4" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.50363547585227</v>
+        <v>20.44363680752841</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.93798019953039</v>
+        <v>25.8929445979566</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.16815635060797</v>
+        <v>27.15715217824146</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.015721856594646</v>
+        <v>3.044151371398461</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.82581898082386</v>
+        <v>21.78163596413352</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.17581833602054</v>
+        <v>29.17568561564092</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.806946216745492</v>
+        <v>-1.787647503040116</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.00819672131147541</v>
       </c>
       <c r="AM4" t="n">
-        <v>564.2600482954546</v>
+        <v>561.9955758389559</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.9762082934226</v>
+        <v>864.0332836477539</v>
       </c>
       <c r="AO4" t="n">
-        <v>713.8132150910762</v>
+        <v>711.797046997827</v>
       </c>
       <c r="AP4" t="n">
-        <v>630.8205495975916</v>
+        <v>628.1133257980833</v>
       </c>
       <c r="AQ4" t="n">
-        <v>796.8058805845609</v>
+        <v>795.4807681975707</v>
       </c>
       <c r="AR4" t="n">
-        <v>600.6465383522727</v>
+        <v>598.7771726540306</v>
       </c>
       <c r="AS4" t="n">
-        <v>802.9185206072852</v>
+        <v>802.0395975739689</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -17555,13 +18882,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>232.79</v>
+        <v>234.11</v>
       </c>
       <c r="I5" t="n">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>31.629074</v>
+        <v>31.636486</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -17576,49 +18903,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.68227978086741</v>
+        <v>31.65730258415679</v>
       </c>
       <c r="P5" t="n">
         <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.439051291645331</v>
+        <v>2.46910444743712</v>
       </c>
       <c r="R5" t="n">
-        <v>28.88875532378421</v>
+        <v>28.53468936025811</v>
       </c>
       <c r="S5" t="n">
         <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.02181412955506843</v>
+        <v>-0.008430823644740536</v>
       </c>
       <c r="U5" t="n">
         <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>204.6223672310844</v>
+        <v>205.734445313862</v>
       </c>
       <c r="W5" t="n">
-        <v>270.9855408821479</v>
+        <v>272.4582883869421</v>
       </c>
       <c r="X5" t="n">
-        <v>233.1815791871841</v>
+        <v>234.2640391227602</v>
       </c>
       <c r="Y5" t="n">
-        <v>215.2301616806745</v>
+        <v>215.9926662117255</v>
       </c>
       <c r="Z5" t="n">
-        <v>251.1329966936938</v>
+        <v>252.5354120337949</v>
       </c>
       <c r="AA5" t="n">
-        <v>212.6212391830518</v>
+        <v>211.15670126591</v>
       </c>
       <c r="AB5" t="n">
-        <v>257.1996627658647</v>
+        <v>258.5974870200271</v>
       </c>
       <c r="AC5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD5" t="n">
         <v>27.72524313614126</v>
@@ -17627,57 +18954,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.43505776156092</v>
+        <v>31.40693096507071</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.68181642961274</v>
+        <v>31.63875598086125</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.392275986747657</v>
+        <v>2.402540996553121</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.62901035878116</v>
+        <v>28.57754546395572</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.73082346896248</v>
+        <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.08110111020377905</v>
+        <v>0.09554677121373961</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4958677685950413</v>
+        <v>0.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>204.0577894819997</v>
+        <v>205.1667992074453</v>
       </c>
       <c r="AN5" t="n">
-        <v>270.9855408821479</v>
+        <v>272.4582883869421</v>
       </c>
       <c r="AO5" t="n">
-        <v>231.3620251250884</v>
+        <v>232.4112891415233</v>
       </c>
       <c r="AP5" t="n">
-        <v>213.7548738626257</v>
+        <v>214.6324857670302</v>
       </c>
       <c r="AQ5" t="n">
-        <v>248.9691763875512</v>
+        <v>250.1900925160163</v>
       </c>
       <c r="AR5" t="n">
-        <v>210.7095162406294</v>
+        <v>211.4738364332723</v>
       </c>
       <c r="AS5" t="n">
-        <v>255.6188607315638</v>
+        <v>256.9544251680042</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -17706,13 +19033,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>297.01</v>
+        <v>294.3</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>8.27</v>
       </c>
       <c r="J6" t="n">
-        <v>35.957626</v>
+        <v>35.586452</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -17727,49 +19054,49 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.89467396164991</v>
+        <v>34.95454812397662</v>
       </c>
       <c r="P6" t="n">
-        <v>34.80750723554782</v>
+        <v>35.17554331634005</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.85237359571992</v>
+        <v>1.815154047699106</v>
       </c>
       <c r="R6" t="n">
-        <v>32.3582284661788</v>
+        <v>32.39493647708169</v>
       </c>
       <c r="S6" t="n">
         <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5738324281916628</v>
+        <v>0.3481268583371105</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6557377049180327</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="V6" t="n">
-        <v>257.8688405483584</v>
+        <v>258.1810304279569</v>
       </c>
       <c r="W6" t="n">
-        <v>315.2000122070312</v>
+        <v>315.5816102847638</v>
       </c>
       <c r="X6" t="n">
-        <v>288.2300069232283</v>
+        <v>289.0741129852867</v>
       </c>
       <c r="Y6" t="n">
-        <v>272.9294010225818</v>
+        <v>274.062789010815</v>
       </c>
       <c r="Z6" t="n">
-        <v>303.5306128238748</v>
+        <v>304.0854369597582</v>
       </c>
       <c r="AA6" t="n">
-        <v>267.2789671306369</v>
+        <v>267.9061246654655</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.8200073242188</v>
+        <v>309.1938814250955</v>
       </c>
       <c r="AC6" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -17778,57 +19105,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.39844332940564</v>
+        <v>34.40853427321154</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.40435746680161</v>
+        <v>34.42623029342849</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.69553378949728</v>
+        <v>1.692187571665709</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.1253156058396</v>
+        <v>32.13088525699663</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.64879274751802</v>
+        <v>36.64450310510222</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.9195821871863996</v>
+        <v>0.6960917019553404</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7851239669421488</v>
+        <v>0.7377049180327869</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.8688405483584</v>
+        <v>258.1810304279569</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.2000122070312</v>
+        <v>315.5816102847638</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.1311419008906</v>
+        <v>284.5585784394594</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.126032799643</v>
+        <v>270.564187221784</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.1362510021382</v>
+        <v>298.5529696571348</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.3551069042351</v>
+        <v>265.7224210753621</v>
       </c>
       <c r="AS6" t="n">
-        <v>302.7190280944988</v>
+        <v>303.0500406791953</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -17857,13 +19184,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>208.65</v>
+        <v>200.04</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="J7" t="n">
-        <v>31.952524</v>
+        <v>30.68098</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -17872,114 +19199,114 @@
         <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>30.69218961239591</v>
+        <v>30.63399590905556</v>
       </c>
       <c r="N7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.66134048392047</v>
+        <v>37.56574525902448</v>
       </c>
       <c r="P7" t="n">
-        <v>36.46530462771046</v>
+        <v>36.34694002112563</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.931431187568819</v>
+        <v>5.010882221391974</v>
       </c>
       <c r="R7" t="n">
-        <v>31.88208306912806</v>
+        <v>31.76263455775028</v>
       </c>
       <c r="S7" t="n">
         <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.157638881449119</v>
+        <v>-1.373962698550907</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1311475409836066</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="V7" t="n">
-        <v>200.4199981689453</v>
+        <v>199.7336533270422</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="X7" t="n">
-        <v>245.9285533600007</v>
+        <v>244.9286590888396</v>
       </c>
       <c r="Y7" t="n">
-        <v>213.7263077051763</v>
+        <v>212.2577070053639</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.1307990148251</v>
+        <v>277.5996111723153</v>
       </c>
       <c r="AA7" t="n">
-        <v>208.1900024414062</v>
+        <v>207.0923773165318</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.4373910086495</v>
+        <v>291.9895542689732</v>
       </c>
       <c r="AC7" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD7" t="n">
-        <v>30.69218961239591</v>
+        <v>30.63399590905556</v>
       </c>
       <c r="AE7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.50525230722248</v>
+        <v>37.42145649748873</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.12856993383291</v>
+        <v>36.97244760941486</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.306907719344029</v>
+        <v>4.346979524970016</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.95252586469898</v>
+        <v>31.9511483675853</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.91836672413105</v>
+        <v>43.8769381776148</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.289261035773526</v>
+        <v>-1.550611512837808</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.09876543209876543</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="AM7" t="n">
-        <v>200.4199981689453</v>
+        <v>199.7336533270422</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="AO7" t="n">
-        <v>244.9092975661628</v>
+        <v>243.9878963636265</v>
       </c>
       <c r="AP7" t="n">
-        <v>216.7851901588463</v>
+        <v>215.645589860822</v>
       </c>
       <c r="AQ7" t="n">
-        <v>273.0334049734793</v>
+        <v>272.330202866431</v>
       </c>
       <c r="AR7" t="n">
-        <v>208.6499938964843</v>
+        <v>208.3214873566561</v>
       </c>
       <c r="AS7" t="n">
-        <v>286.7869347085758</v>
+        <v>286.0776369180485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -18008,13 +19335,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>551.63</v>
+        <v>519.85</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="J8" t="n">
-        <v>185.11073</v>
+        <v>172.13576</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -18029,49 +19356,49 @@
         <v>180.8622966828894</v>
       </c>
       <c r="O8" t="n">
-        <v>131.229885843878</v>
+        <v>132.6613917228449</v>
       </c>
       <c r="P8" t="n">
-        <v>136.0528334131781</v>
+        <v>138.029504994877</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.8576689364245</v>
+        <v>32.62814033498378</v>
       </c>
       <c r="R8" t="n">
         <v>83.08678968897406</v>
       </c>
       <c r="S8" t="n">
-        <v>169.8655825755635</v>
+        <v>170.442614946209</v>
       </c>
       <c r="T8" t="n">
-        <v>1.639825523240091</v>
+        <v>1.209825870303459</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0.9344262295081968</v>
       </c>
       <c r="V8" t="n">
-        <v>220.4525207519531</v>
+        <v>223.4116149902344</v>
       </c>
       <c r="W8" t="n">
-        <v>538.9696441150103</v>
+        <v>546.2041359823259</v>
       </c>
       <c r="X8" t="n">
-        <v>391.0650598147565</v>
+        <v>400.6374030029914</v>
       </c>
       <c r="Y8" t="n">
-        <v>293.1492063842114</v>
+        <v>302.1004191913404</v>
       </c>
       <c r="Z8" t="n">
-        <v>488.9809132453015</v>
+        <v>499.1743868146425</v>
       </c>
       <c r="AA8" t="n">
-        <v>247.5986332731427</v>
+        <v>250.9221048607017</v>
       </c>
       <c r="AB8" t="n">
-        <v>506.1994360751793</v>
+        <v>514.7366971375512</v>
       </c>
       <c r="AC8" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -18080,57 +19407,57 @@
         <v>180.8622966828894</v>
       </c>
       <c r="AF8" t="n">
-        <v>111.9542641297903</v>
+        <v>112.4336768414003</v>
       </c>
       <c r="AG8" t="n">
-        <v>106.2118229607643</v>
+        <v>106.7832681283774</v>
       </c>
       <c r="AH8" t="n">
-        <v>33.24393869274672</v>
+        <v>33.5270930653851</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51697928950472</v>
+        <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>165.2098408683402</v>
+        <v>166.2131177558274</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.200595619741389</v>
+        <v>1.780711588749067</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0.9672131147540983</v>
       </c>
       <c r="AM8" t="n">
-        <v>214.728675813495</v>
+        <v>217.6109399183741</v>
       </c>
       <c r="AN8" t="n">
-        <v>538.9696441150103</v>
+        <v>546.2041359823259</v>
       </c>
       <c r="AO8" t="n">
-        <v>333.623707106775</v>
+        <v>339.5497040610288</v>
       </c>
       <c r="AP8" t="n">
-        <v>234.5567698023898</v>
+        <v>238.2978830035658</v>
       </c>
       <c r="AQ8" t="n">
-        <v>432.6906444111602</v>
+        <v>440.8015251184917</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.0405982827241</v>
+        <v>228.0646961831147</v>
       </c>
       <c r="AS8" t="n">
-        <v>492.3253257876537</v>
+        <v>501.9636156225986</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -18159,13 +19486,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>392.13</v>
+        <v>380.15</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="J9" t="n">
-        <v>65.355</v>
+        <v>63.252907</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -18180,13 +19507,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.48783286839652</v>
+        <v>75.5059756953405</v>
       </c>
       <c r="P9" t="n">
         <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.437891127587715</v>
+        <v>9.412847039944809</v>
       </c>
       <c r="R9" t="n">
         <v>61.31578709414597</v>
@@ -18195,34 +19522,34 @@
         <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.073633159295241</v>
+        <v>-1.301738851523114</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2459016393442623</v>
+        <v>0.1475409836065574</v>
       </c>
       <c r="V9" t="n">
-        <v>343.1695949264438</v>
+        <v>343.7415442513212</v>
       </c>
       <c r="W9" t="n">
-        <v>563.2397746482092</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="X9" t="n">
-        <v>452.9269972103791</v>
+        <v>453.7909139289964</v>
       </c>
       <c r="Y9" t="n">
-        <v>396.2996504448528</v>
+        <v>397.2197032189281</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.5543439759055</v>
+        <v>510.3621246390646</v>
       </c>
       <c r="AA9" t="n">
-        <v>367.8947225648758</v>
+        <v>368.5078804358172</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.087710731908</v>
+        <v>501.9228569164612</v>
       </c>
       <c r="AC9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -18231,57 +19558,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.20679671751905</v>
+        <v>72.13340420998271</v>
       </c>
       <c r="AG9" t="n">
-        <v>70.01886587722747</v>
+        <v>69.96855345911951</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.848172999741466</v>
+        <v>7.857603180592716</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.34697784364341</v>
+        <v>62.37563283819902</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.38791304025038</v>
+        <v>82.37543771606209</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.8730435373614677</v>
+        <v>-1.130178886090407</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.2066115702479339</v>
+        <v>0.139344262295082</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.1695949264438</v>
+        <v>343.7415442513212</v>
       </c>
       <c r="AN9" t="n">
-        <v>563.2397746482092</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="AO9" t="n">
-        <v>433.2407803051143</v>
+        <v>433.5217593019961</v>
       </c>
       <c r="AP9" t="n">
-        <v>386.1517423066655</v>
+        <v>386.2975641866338</v>
       </c>
       <c r="AQ9" t="n">
-        <v>480.3298183035631</v>
+        <v>480.7459544173583</v>
       </c>
       <c r="AR9" t="n">
-        <v>374.0818670618605</v>
+        <v>374.8775533575761</v>
       </c>
       <c r="AS9" t="n">
-        <v>494.3274782415023</v>
+        <v>495.0763806735332</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:51</t>
+          <t>2026-06-24 03:29:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -18310,19 +19637,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>72.88</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.509678</v>
+        <v>23.490324</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -18365,7 +19692,7 @@
         <v>39.16798316442917</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.3339656913463799</v>
+        <v>-0.3353424035374276</v>
       </c>
       <c r="AL10" t="n">
         <v>0.2368421052631579</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS118"/>
+  <dimension ref="A1:AS127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16640,7 +16640,7 @@
         <v>14.05813075953811</v>
       </c>
       <c r="AI108" t="n">
-        <v>3.754803650361255</v>
+        <v>3.754803650361256</v>
       </c>
       <c r="AJ108" t="n">
         <v>39.16798316442917</v>
@@ -17033,7 +17033,7 @@
         <v>180.8622966828894</v>
       </c>
       <c r="O111" t="n">
-        <v>132.6613917228449</v>
+        <v>132.6613917228448</v>
       </c>
       <c r="P111" t="n">
         <v>138.029504994877</v>
@@ -17102,7 +17102,7 @@
         <v>1.780711588749067</v>
       </c>
       <c r="AL111" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9672131147540984</v>
       </c>
       <c r="AM111" t="n">
         <v>217.6109399183741</v>
@@ -17193,13 +17193,13 @@
         <v>2.46910444743712</v>
       </c>
       <c r="R112" t="n">
-        <v>28.53468936025811</v>
+        <v>28.53468936025812</v>
       </c>
       <c r="S112" t="n">
         <v>34.94560635405771</v>
       </c>
       <c r="T112" t="n">
-        <v>-0.008430823644740536</v>
+        <v>-0.008430823644740499</v>
       </c>
       <c r="U112" t="n">
         <v>0.4426229508196721</v>
@@ -17250,7 +17250,7 @@
         <v>34.72357096864921</v>
       </c>
       <c r="AK112" t="n">
-        <v>0.09554677121373961</v>
+        <v>0.0955467712137396</v>
       </c>
       <c r="AL112" t="n">
         <v>0.5</v>
@@ -17265,13 +17265,13 @@
         <v>232.4112891415233</v>
       </c>
       <c r="AP112" t="n">
-        <v>214.6324857670302</v>
+        <v>214.6324857670301</v>
       </c>
       <c r="AQ112" t="n">
-        <v>250.1900925160163</v>
+        <v>250.1900925160164</v>
       </c>
       <c r="AR112" t="n">
-        <v>211.4738364332723</v>
+        <v>211.4738364332724</v>
       </c>
       <c r="AS112" t="n">
         <v>256.9544251680042</v>
@@ -17332,7 +17332,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N113" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O113" t="n">
         <v>75.5059756953405</v>
@@ -17353,7 +17353,7 @@
         <v>-1.301738851523114</v>
       </c>
       <c r="U113" t="n">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="V113" t="n">
         <v>343.7415442513212</v>
@@ -17371,7 +17371,7 @@
         <v>510.3621246390646</v>
       </c>
       <c r="AA113" t="n">
-        <v>368.5078804358172</v>
+        <v>368.5078804358173</v>
       </c>
       <c r="AB113" t="n">
         <v>501.9228569164612</v>
@@ -17383,7 +17383,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE113" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF113" t="n">
         <v>72.13340420998271</v>
@@ -17404,7 +17404,7 @@
         <v>-1.130178886090407</v>
       </c>
       <c r="AL113" t="n">
-        <v>0.139344262295082</v>
+        <v>0.1393442622950819</v>
       </c>
       <c r="AM113" t="n">
         <v>343.7415442513212</v>
@@ -17419,7 +17419,7 @@
         <v>386.2975641866338</v>
       </c>
       <c r="AQ113" t="n">
-        <v>480.7459544173583</v>
+        <v>480.7459544173584</v>
       </c>
       <c r="AR113" t="n">
         <v>374.8775533575761</v>
@@ -17504,7 +17504,7 @@
         <v>-1.532748205984823</v>
       </c>
       <c r="U114" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="V114" t="n">
         <v>331.5075848462072</v>
@@ -17513,7 +17513,7 @@
         <v>422.9955833357424</v>
       </c>
       <c r="X114" t="n">
-        <v>380.1389045310736</v>
+        <v>380.1389045310737</v>
       </c>
       <c r="Y114" t="n">
         <v>357.9180892412002</v>
@@ -17537,7 +17537,7 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF114" t="n">
-        <v>29.57764202380655</v>
+        <v>29.57764202380656</v>
       </c>
       <c r="AG114" t="n">
         <v>29.24065608090794</v>
@@ -17555,7 +17555,7 @@
         <v>-1.575515853276088</v>
       </c>
       <c r="AL114" t="n">
-        <v>0.02459016393442623</v>
+        <v>0.0245901639344262</v>
       </c>
       <c r="AM114" t="n">
         <v>331.5075848462072</v>
@@ -17567,7 +17567,7 @@
         <v>388.058663352342</v>
       </c>
       <c r="AP114" t="n">
-        <v>361.4142639925687</v>
+        <v>361.4142639925688</v>
       </c>
       <c r="AQ114" t="n">
         <v>414.7030627121152</v>
@@ -17576,7 +17576,7 @@
         <v>357.9690487329997</v>
       </c>
       <c r="AS114" t="n">
-        <v>428.4269251681268</v>
+        <v>428.4269251681269</v>
       </c>
     </row>
     <row r="115">
@@ -17646,7 +17646,7 @@
         <v>2.812767555526313</v>
       </c>
       <c r="R115" t="n">
-        <v>20.98981711647727</v>
+        <v>20.98981711647728</v>
       </c>
       <c r="S115" t="n">
         <v>28.57982234378326</v>
@@ -17655,7 +17655,7 @@
         <v>-1.182698844001113</v>
       </c>
       <c r="U115" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V115" t="n">
         <v>561.9955758389559</v>
@@ -17706,7 +17706,7 @@
         <v>-1.787647503040116</v>
       </c>
       <c r="AL115" t="n">
-        <v>0.00819672131147541</v>
+        <v>0.0081967213114754</v>
       </c>
       <c r="AM115" t="n">
         <v>561.9955758389559</v>
@@ -17791,7 +17791,7 @@
         <v>24.55424759017488</v>
       </c>
       <c r="P116" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q116" t="n">
         <v>1.35282991442224</v>
@@ -17800,13 +17800,13 @@
         <v>22.88742971986886</v>
       </c>
       <c r="S116" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T116" t="n">
         <v>-1.687320457538632</v>
       </c>
       <c r="U116" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.0327868852459016</v>
       </c>
       <c r="V116" t="n">
         <v>367.1213415781656</v>
@@ -17845,7 +17845,7 @@
         <v>25.07501266985255</v>
       </c>
       <c r="AH116" t="n">
-        <v>3.533085643899507</v>
+        <v>3.533085643899508</v>
       </c>
       <c r="AI116" t="n">
         <v>23.26076719757274</v>
@@ -17857,7 +17857,7 @@
         <v>-1.143487668956997</v>
       </c>
       <c r="AL116" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="AM116" t="n">
         <v>367.1213415781656</v>
@@ -17952,7 +17952,7 @@
         <v>76</v>
       </c>
       <c r="AD117" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE117" t="n">
         <v>42.60474344487245</v>
@@ -17976,7 +17976,7 @@
         <v>-0.3353424035374276</v>
       </c>
       <c r="AL117" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2368421052631578</v>
       </c>
       <c r="AM117" t="n">
         <v>10.81762752038992</v>
@@ -18076,7 +18076,7 @@
         <v>-1.373962698550907</v>
       </c>
       <c r="U118" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V118" t="n">
         <v>199.7336533270422</v>
@@ -18088,7 +18088,7 @@
         <v>244.9286590888396</v>
       </c>
       <c r="Y118" t="n">
-        <v>212.2577070053639</v>
+        <v>212.257707005364</v>
       </c>
       <c r="Z118" t="n">
         <v>277.5996111723153</v>
@@ -18127,7 +18127,7 @@
         <v>-1.550611512837808</v>
       </c>
       <c r="AL118" t="n">
-        <v>0.01219512195121951</v>
+        <v>0.0121951219512195</v>
       </c>
       <c r="AM118" t="n">
         <v>199.7336533270422</v>
@@ -18149,6 +18149,1333 @@
       </c>
       <c r="AS118" t="n">
         <v>286.0776369180485</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>293.08</v>
+      </c>
+      <c r="I119" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J119" t="n">
+        <v>35.48184</v>
+      </c>
+      <c r="K119" t="n">
+        <v>67</v>
+      </c>
+      <c r="L119" t="n">
+        <v>61</v>
+      </c>
+      <c r="M119" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N119" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O119" t="n">
+        <v>35.01144068529248</v>
+      </c>
+      <c r="P119" t="n">
+        <v>35.24576330300393</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>1.775319124406818</v>
+      </c>
+      <c r="R119" t="n">
+        <v>32.7632894395273</v>
+      </c>
+      <c r="S119" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.2649660606031533</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.5573770491803278</v>
+      </c>
+      <c r="V119" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="W119" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X119" t="n">
+        <v>289.1945000605159</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>274.5303640929156</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>303.8586360281162</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>270.6247707704955</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>308.8200073242188</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>34.39896907501936</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>34.42623029342849</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.682691208373762</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>36.60450765954701</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.6435351415588489</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.7377049180327869</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>284.1354845596599</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>270.2364551784926</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>298.0345139408271</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>265.4011122227922</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>302.3532332678583</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>519.74</v>
+      </c>
+      <c r="I120" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J120" t="n">
+        <v>172.6711</v>
+      </c>
+      <c r="K120" t="n">
+        <v>63</v>
+      </c>
+      <c r="L120" t="n">
+        <v>61</v>
+      </c>
+      <c r="M120" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N120" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="O120" t="n">
+        <v>134.1943788202271</v>
+      </c>
+      <c r="P120" t="n">
+        <v>138.1606605404713</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>32.15771365621515</v>
+      </c>
+      <c r="R120" t="n">
+        <v>83.59622595445165</v>
+      </c>
+      <c r="S120" t="n">
+        <v>170.442614946209</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1.196500522117701</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.9344262295081968</v>
+      </c>
+      <c r="V120" t="n">
+        <v>222.671841430664</v>
+      </c>
+      <c r="W120" t="n">
+        <v>544.3955130154969</v>
+      </c>
+      <c r="X120" t="n">
+        <v>403.9250802488834</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>307.1303621436758</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>500.719798354091</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>251.6246401228995</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>513.0322709880892</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>112.962366575239</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>108.1034653230453</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>33.9294517208715</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>167.162624671811</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1.75979069499763</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.9672131147540983</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>216.8903738921543</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>544.3955130154969</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>340.0167233914694</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>237.8890737116462</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>442.1443730712926</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>227.3095150699255</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>503.159500262151</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>234.27</v>
+      </c>
+      <c r="I121" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J121" t="n">
+        <v>31.658108</v>
+      </c>
+      <c r="K121" t="n">
+        <v>67</v>
+      </c>
+      <c r="L121" t="n">
+        <v>61</v>
+      </c>
+      <c r="M121" t="n">
+        <v>27.80195206944081</v>
+      </c>
+      <c r="N121" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O121" t="n">
+        <v>31.64217343703564</v>
+      </c>
+      <c r="P121" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>2.488746264983075</v>
+      </c>
+      <c r="R121" t="n">
+        <v>28.4688995215311</v>
+      </c>
+      <c r="S121" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.006402646661317796</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V121" t="n">
+        <v>205.734445313862</v>
+      </c>
+      <c r="W121" t="n">
+        <v>272.4582883869421</v>
+      </c>
+      <c r="X121" t="n">
+        <v>234.1520834340637</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>215.735361073189</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>252.5688057949385</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>210.6698564593302</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>258.5974870200271</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>27.72524313614126</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>31.36743030335536</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>31.52454285372481</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>2.418318849109844</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>28.56303961207178</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.1201982512569153</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.5081967213114754</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>205.1667992074453</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>272.4582883869421</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>232.1189842448297</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>214.2234247614168</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>250.0145437282425</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>211.3664931293312</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>256.9544251680042</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="I122" t="n">
+        <v>6</v>
+      </c>
+      <c r="J122" t="n">
+        <v>63.678333</v>
+      </c>
+      <c r="K122" t="n">
+        <v>34</v>
+      </c>
+      <c r="L122" t="n">
+        <v>61</v>
+      </c>
+      <c r="M122" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N122" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O122" t="n">
+        <v>75.55936239198338</v>
+      </c>
+      <c r="P122" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>9.334163522278317</v>
+      </c>
+      <c r="R122" t="n">
+        <v>61.91347855299761</v>
+      </c>
+      <c r="S122" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T122" t="n">
+        <v>-1.272854215980504</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.180327868852459</v>
+      </c>
+      <c r="V122" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="W122" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="X122" t="n">
+        <v>453.3561743519003</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>397.3511932182304</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>509.3611554855702</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>371.4808713179856</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>501.087710731908</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>72.04939254299691</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>69.88993710691824</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>7.894109435643674</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>62.37563283819902</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>82.37543771606209</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-1.060418481811222</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>0.1721311475409836</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>432.2963552579815</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>384.9316986441195</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>479.6610118718435</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>374.2537970291942</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>494.2526262963726</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>345.04</v>
+      </c>
+      <c r="I123" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J123" t="n">
+        <v>26.318842</v>
+      </c>
+      <c r="K123" t="n">
+        <v>37</v>
+      </c>
+      <c r="L123" t="n">
+        <v>61</v>
+      </c>
+      <c r="M123" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N123" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O123" t="n">
+        <v>28.97971407228829</v>
+      </c>
+      <c r="P123" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1.683920207132963</v>
+      </c>
+      <c r="R123" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S123" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T123" t="n">
+        <v>-1.580165177077294</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="V123" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W123" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X123" t="n">
+        <v>379.9240514876995</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>357.8478575721863</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>402.0002454032127</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>353.3200073242188</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>409.5874601323553</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>29.53851936446002</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>2.047319773501952</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>27.24366250686575</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>32.65449124757065</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>-1.57263042448554</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>387.2499888680708</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>360.4096266374602</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>414.0903510986814</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>357.1644154650099</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>428.1003802556511</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>557.67</v>
+      </c>
+      <c r="I124" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J124" t="n">
+        <v>20.286285</v>
+      </c>
+      <c r="K124" t="n">
+        <v>55</v>
+      </c>
+      <c r="L124" t="n">
+        <v>61</v>
+      </c>
+      <c r="M124" t="n">
+        <v>20.27890846946023</v>
+      </c>
+      <c r="N124" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O124" t="n">
+        <v>23.7280502315028</v>
+      </c>
+      <c r="P124" t="n">
+        <v>22.3805862368295</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>2.847723161160523</v>
+      </c>
+      <c r="R124" t="n">
+        <v>20.76290838068182</v>
+      </c>
+      <c r="S124" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T124" t="n">
+        <v>-1.208602464749484</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V124" t="n">
+        <v>557.4671938254615</v>
+      </c>
+      <c r="W124" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X124" t="n">
+        <v>652.2841008640119</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>574.0001911637091</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>730.5680105643147</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>570.7723513849431</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>785.6593162306017</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>20.27890846946023</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>25.81838557111327</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>27.13735667641555</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>3.069448882937269</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>21.73647283380682</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>29.17418109093017</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>-1.802310702050005</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.00819672131147541</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>557.4671938254615</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>709.7474193499038</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>625.3682695579582</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>794.1265691418494</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>597.5356382013495</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>801.9982381896702</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="I125" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="J125" t="n">
+        <v>21.792486</v>
+      </c>
+      <c r="K125" t="n">
+        <v>67</v>
+      </c>
+      <c r="L125" t="n">
+        <v>61</v>
+      </c>
+      <c r="M125" t="n">
+        <v>21.75357091994513</v>
+      </c>
+      <c r="N125" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O125" t="n">
+        <v>24.5356597409958</v>
+      </c>
+      <c r="P125" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1.383554351681298</v>
+      </c>
+      <c r="R125" t="n">
+        <v>22.58333297002883</v>
+      </c>
+      <c r="S125" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T125" t="n">
+        <v>-1.982700381565995</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V125" t="n">
+        <v>364.8073843274798</v>
+      </c>
+      <c r="W125" t="n">
+        <v>459.6976318904332</v>
+      </c>
+      <c r="X125" t="n">
+        <v>411.4630138564996</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>388.2608073788043</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>434.665220334195</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>378.7224939073835</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>444.8507355480659</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>21.75357091994513</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>34.67140903174453</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>26.20561187383701</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>25.05812684918583</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>3.473216267182116</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>23.23690450759161</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>33.41728308122833</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-1.270616493287778</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.00819672131147541</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>364.8073843274798</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>581.4395294623557</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>439.4681111242466</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>381.2222743236025</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>497.7139479248907</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>389.6828885923113</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>560.407837272199</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>23.174192</v>
+      </c>
+      <c r="K126" t="n">
+        <v>67</v>
+      </c>
+      <c r="L126" t="n">
+        <v>14</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr"/>
+      <c r="AB126" t="inlineStr"/>
+      <c r="AC126" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>28.52805797173277</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>33.45454521329976</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>13.86518441531513</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>3.751211333693119</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>39.17391207849554</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.3861373791623735</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>88.4369797123716</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>45.45490802489469</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>131.4190513998485</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>11.62875513444867</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>121.4391274433362</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-06-25 03:21:48</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>199</v>
+      </c>
+      <c r="I127" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J127" t="n">
+        <v>30.474731</v>
+      </c>
+      <c r="K127" t="n">
+        <v>65</v>
+      </c>
+      <c r="L127" t="n">
+        <v>61</v>
+      </c>
+      <c r="M127" t="n">
+        <v>30.47473200612557</v>
+      </c>
+      <c r="N127" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O127" t="n">
+        <v>37.49243037557468</v>
+      </c>
+      <c r="P127" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>5.082048284936918</v>
+      </c>
+      <c r="R127" t="n">
+        <v>31.42266499868395</v>
+      </c>
+      <c r="S127" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T127" t="n">
+        <v>-1.380880106230984</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>199</v>
+      </c>
+      <c r="W127" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X127" t="n">
+        <v>244.8255703525027</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>211.6397950518646</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>278.0113456531407</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>205.1900024414062</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>292.4373910086495</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>83</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>30.47473200612557</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>37.33776102168918</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>36.81632528499681</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>4.38716292844407</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>31.89586551777253</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>43.83550963109852</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-1.564343548126029</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>199</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>243.8155794716303</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>215.1674055488905</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>272.4637533943701</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>208.2800018310546</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>286.2458778910733</v>
       </c>
     </row>
   </sheetData>
@@ -18395,12 +19722,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -18429,13 +19756,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>346.08</v>
+        <v>345.04</v>
       </c>
       <c r="I2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>26.378048</v>
+        <v>26.318842</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -18450,13 +19777,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.97400186974647</v>
+        <v>28.97971407228829</v>
       </c>
       <c r="P2" t="n">
         <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.693659701972064</v>
+        <v>1.683920207132963</v>
       </c>
       <c r="R2" t="n">
         <v>26.95042008575277</v>
@@ -18465,31 +19792,31 @@
         <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.532748205984823</v>
+        <v>-1.580165177077294</v>
       </c>
       <c r="U2" t="n">
         <v>0.04918032786885246</v>
       </c>
       <c r="V2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="W2" t="n">
-        <v>422.9955833357424</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>380.1389045310736</v>
+        <v>379.9240514876995</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.9180892412002</v>
+        <v>357.8478575721863</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.3597198209471</v>
+        <v>402.0002454032127</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.5895115250763</v>
+        <v>353.3200073242188</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.8998838242946</v>
+        <v>409.5874601323553</v>
       </c>
       <c r="AC2" t="n">
         <v>122</v>
@@ -18501,57 +19828,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.57764202380655</v>
+        <v>29.53851936446002</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.24065608090794</v>
+        <v>29.21870597964289</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.030823121933937</v>
+        <v>2.047319773501952</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.28422627538108</v>
+        <v>27.24366250686575</v>
       </c>
       <c r="AJ2" t="n">
         <v>32.65449124757065</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.575515853276088</v>
+        <v>-1.57263042448554</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02459016393442623</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.7016702785662</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>388.058663352342</v>
+        <v>387.2499888680708</v>
       </c>
       <c r="AP2" t="n">
-        <v>361.4142639925687</v>
+        <v>360.4096266374602</v>
       </c>
       <c r="AQ2" t="n">
-        <v>414.7030627121152</v>
+        <v>414.0903510986814</v>
       </c>
       <c r="AR2" t="n">
-        <v>357.9690487329997</v>
+        <v>357.1644154650099</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.4269251681268</v>
+        <v>428.1003802556511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -18580,13 +19907,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>373.94</v>
+        <v>365.46</v>
       </c>
       <c r="I3" t="n">
-        <v>16.79</v>
+        <v>16.77</v>
       </c>
       <c r="J3" t="n">
-        <v>22.27159</v>
+        <v>21.792486</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -18595,114 +19922,114 @@
         <v>61</v>
       </c>
       <c r="M3" t="n">
-        <v>21.86547597249349</v>
+        <v>21.75357091994513</v>
       </c>
       <c r="N3" t="n">
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.55424759017488</v>
+        <v>24.5356597409958</v>
       </c>
       <c r="P3" t="n">
         <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.35282991442224</v>
+        <v>1.383554351681298</v>
       </c>
       <c r="R3" t="n">
-        <v>22.88742971986886</v>
+        <v>22.58333297002883</v>
       </c>
       <c r="S3" t="n">
         <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.687320457538632</v>
+        <v>-1.982700381565995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="V3" t="n">
-        <v>367.1213415781656</v>
+        <v>364.8073843274798</v>
       </c>
       <c r="W3" t="n">
-        <v>460.2458699725923</v>
+        <v>459.6976318904332</v>
       </c>
       <c r="X3" t="n">
-        <v>412.2658170390362</v>
+        <v>411.4630138564996</v>
       </c>
       <c r="Y3" t="n">
-        <v>389.5518027758868</v>
+        <v>388.2608073788043</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.9798313021857</v>
+        <v>434.665220334195</v>
       </c>
       <c r="AA3" t="n">
-        <v>384.2799449965982</v>
+        <v>378.7224939073835</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.3812671348853</v>
+        <v>444.8507355480659</v>
       </c>
       <c r="AC3" t="n">
         <v>122</v>
       </c>
       <c r="AD3" t="n">
-        <v>21.86547597249349</v>
+        <v>21.75357091994513</v>
       </c>
       <c r="AE3" t="n">
-        <v>34.68776610633557</v>
+        <v>34.67140903174453</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.31162986716808</v>
+        <v>26.20561187383701</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.07501266985255</v>
+        <v>25.05812684918583</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.533085643899507</v>
+        <v>3.473216267182116</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.26076719757274</v>
+        <v>23.23690450759161</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33.47304494757402</v>
+        <v>33.41728308122833</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.143487668956997</v>
+        <v>-1.270616493287778</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.00819672131147541</v>
       </c>
       <c r="AM3" t="n">
-        <v>367.1213415781656</v>
+        <v>364.8073843274798</v>
       </c>
       <c r="AN3" t="n">
-        <v>582.4075929253742</v>
+        <v>581.4395294623557</v>
       </c>
       <c r="AO3" t="n">
-        <v>441.772265469752</v>
+        <v>439.4681111242466</v>
       </c>
       <c r="AP3" t="n">
-        <v>382.4517575086793</v>
+        <v>381.2222743236025</v>
       </c>
       <c r="AQ3" t="n">
-        <v>501.0927734308248</v>
+        <v>497.7139479248907</v>
       </c>
       <c r="AR3" t="n">
-        <v>390.5482812472462</v>
+        <v>389.6828885923113</v>
       </c>
       <c r="AS3" t="n">
-        <v>562.0124246697677</v>
+        <v>560.407837272199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18731,13 +20058,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>562.2</v>
+        <v>557.67</v>
       </c>
       <c r="I4" t="n">
         <v>27.49</v>
       </c>
       <c r="J4" t="n">
-        <v>20.451075</v>
+        <v>20.286285</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -18746,49 +20073,49 @@
         <v>61</v>
       </c>
       <c r="M4" t="n">
-        <v>20.44363680752841</v>
+        <v>20.27890846946023</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.77773193636481</v>
+        <v>23.7280502315028</v>
       </c>
       <c r="P4" t="n">
-        <v>22.42290926846591</v>
+        <v>22.3805862368295</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.812767555526313</v>
+        <v>2.847723161160523</v>
       </c>
       <c r="R4" t="n">
-        <v>20.98981711647727</v>
+        <v>20.76290838068182</v>
       </c>
       <c r="S4" t="n">
         <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.182698844001113</v>
+        <v>-1.208602464749484</v>
       </c>
       <c r="U4" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="V4" t="n">
-        <v>561.9955758389559</v>
+        <v>557.4671938254615</v>
       </c>
       <c r="W4" t="n">
         <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>653.6498509306684</v>
+        <v>652.2841008640119</v>
       </c>
       <c r="Y4" t="n">
-        <v>576.3268708292501</v>
+        <v>574.0001911637091</v>
       </c>
       <c r="Z4" t="n">
-        <v>730.9728310320868</v>
+        <v>730.5680105643147</v>
       </c>
       <c r="AA4" t="n">
-        <v>577.0100725319602</v>
+        <v>570.7723513849431</v>
       </c>
       <c r="AB4" t="n">
         <v>785.6593162306017</v>
@@ -18797,63 +20124,63 @@
         <v>122</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.44363680752841</v>
+        <v>20.27890846946023</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.8929445979566</v>
+        <v>25.81838557111327</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.15715217824146</v>
+        <v>27.13735667641555</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.044151371398461</v>
+        <v>3.069448882937269</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.78163596413352</v>
+        <v>21.73647283380682</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.17568561564092</v>
+        <v>29.17418109093017</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.787647503040116</v>
+        <v>-1.802310702050005</v>
       </c>
       <c r="AL4" t="n">
         <v>0.00819672131147541</v>
       </c>
       <c r="AM4" t="n">
-        <v>561.9955758389559</v>
+        <v>557.4671938254615</v>
       </c>
       <c r="AN4" t="n">
         <v>864.0332836477539</v>
       </c>
       <c r="AO4" t="n">
-        <v>711.797046997827</v>
+        <v>709.7474193499038</v>
       </c>
       <c r="AP4" t="n">
-        <v>628.1133257980833</v>
+        <v>625.3682695579582</v>
       </c>
       <c r="AQ4" t="n">
-        <v>795.4807681975707</v>
+        <v>794.1265691418494</v>
       </c>
       <c r="AR4" t="n">
-        <v>598.7771726540306</v>
+        <v>597.5356382013495</v>
       </c>
       <c r="AS4" t="n">
-        <v>802.0395975739689</v>
+        <v>801.9982381896702</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -18882,13 +20209,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>234.11</v>
+        <v>234.27</v>
       </c>
       <c r="I5" t="n">
         <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>31.636486</v>
+        <v>31.658108</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -18903,22 +20230,22 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.65730258415679</v>
+        <v>31.64217343703564</v>
       </c>
       <c r="P5" t="n">
         <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46910444743712</v>
+        <v>2.488746264983075</v>
       </c>
       <c r="R5" t="n">
-        <v>28.53468936025811</v>
+        <v>28.4688995215311</v>
       </c>
       <c r="S5" t="n">
         <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.008430823644740536</v>
+        <v>0.006402646661317796</v>
       </c>
       <c r="U5" t="n">
         <v>0.4426229508196721</v>
@@ -18930,16 +20257,16 @@
         <v>272.4582883869421</v>
       </c>
       <c r="X5" t="n">
-        <v>234.2640391227602</v>
+        <v>234.1520834340637</v>
       </c>
       <c r="Y5" t="n">
-        <v>215.9926662117255</v>
+        <v>215.735361073189</v>
       </c>
       <c r="Z5" t="n">
-        <v>252.5354120337949</v>
+        <v>252.5688057949385</v>
       </c>
       <c r="AA5" t="n">
-        <v>211.15670126591</v>
+        <v>210.6698564593302</v>
       </c>
       <c r="AB5" t="n">
         <v>258.5974870200271</v>
@@ -18954,25 +20281,25 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.40693096507071</v>
+        <v>31.36743030335536</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.63875598086125</v>
+        <v>31.52454285372481</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.402540996553121</v>
+        <v>2.418318849109844</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.57754546395572</v>
+        <v>28.56303961207178</v>
       </c>
       <c r="AJ5" t="n">
         <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.09554677121373961</v>
+        <v>0.1201982512569153</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5</v>
+        <v>0.5081967213114754</v>
       </c>
       <c r="AM5" t="n">
         <v>205.1667992074453</v>
@@ -18981,16 +20308,16 @@
         <v>272.4582883869421</v>
       </c>
       <c r="AO5" t="n">
-        <v>232.4112891415233</v>
+        <v>232.1189842448297</v>
       </c>
       <c r="AP5" t="n">
-        <v>214.6324857670302</v>
+        <v>214.2234247614168</v>
       </c>
       <c r="AQ5" t="n">
-        <v>250.1900925160163</v>
+        <v>250.0145437282425</v>
       </c>
       <c r="AR5" t="n">
-        <v>211.4738364332723</v>
+        <v>211.3664931293312</v>
       </c>
       <c r="AS5" t="n">
         <v>256.9544251680042</v>
@@ -18999,12 +20326,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -19033,13 +20360,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>294.3</v>
+        <v>293.08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>35.586452</v>
+        <v>35.48184</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -19054,46 +20381,46 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>34.95454812397662</v>
+        <v>35.01144068529248</v>
       </c>
       <c r="P6" t="n">
-        <v>35.17554331634005</v>
+        <v>35.24576330300393</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.815154047699106</v>
+        <v>1.775319124406818</v>
       </c>
       <c r="R6" t="n">
-        <v>32.39493647708169</v>
+        <v>32.7632894395273</v>
       </c>
       <c r="S6" t="n">
         <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3481268583371105</v>
+        <v>0.2649660606031533</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5737704918032787</v>
+        <v>0.5573770491803278</v>
       </c>
       <c r="V6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="W6" t="n">
-        <v>315.5816102847638</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>289.0741129852867</v>
+        <v>289.1945000605159</v>
       </c>
       <c r="Y6" t="n">
-        <v>274.062789010815</v>
+        <v>274.5303640929156</v>
       </c>
       <c r="Z6" t="n">
-        <v>304.0854369597582</v>
+        <v>303.8586360281162</v>
       </c>
       <c r="AA6" t="n">
-        <v>267.9061246654655</v>
+        <v>270.6247707704955</v>
       </c>
       <c r="AB6" t="n">
-        <v>309.1938814250955</v>
+        <v>308.8200073242188</v>
       </c>
       <c r="AC6" t="n">
         <v>122</v>
@@ -19105,57 +20432,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.40853427321154</v>
+        <v>34.39896907501936</v>
       </c>
       <c r="AG6" t="n">
         <v>34.42623029342849</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.692187571665709</v>
+        <v>1.682691208373762</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13088525699663</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.64450310510222</v>
+        <v>36.60450765954701</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.6960917019553404</v>
+        <v>0.6435351415588489</v>
       </c>
       <c r="AL6" t="n">
         <v>0.7377049180327869</v>
       </c>
       <c r="AM6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.5816102847638</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.5585784394594</v>
+        <v>284.1354845596599</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.564187221784</v>
+        <v>270.2364551784926</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.5529696571348</v>
+        <v>298.0345139408271</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.7224210753621</v>
+        <v>265.4011122227922</v>
       </c>
       <c r="AS6" t="n">
-        <v>303.0500406791953</v>
+        <v>302.3532332678583</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -19184,13 +20511,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>200.04</v>
+        <v>199</v>
       </c>
       <c r="I7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>30.68098</v>
+        <v>30.474731</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -19199,114 +20526,114 @@
         <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>30.63399590905556</v>
+        <v>30.47473200612557</v>
       </c>
       <c r="N7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.56574525902448</v>
+        <v>37.49243037557468</v>
       </c>
       <c r="P7" t="n">
         <v>36.34694002112563</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.010882221391974</v>
+        <v>5.082048284936918</v>
       </c>
       <c r="R7" t="n">
-        <v>31.76263455775028</v>
+        <v>31.42266499868395</v>
       </c>
       <c r="S7" t="n">
         <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.373962698550907</v>
+        <v>-1.380880106230984</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01639344262295082</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>199.7336533270422</v>
+        <v>199</v>
       </c>
       <c r="W7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>244.9286590888396</v>
+        <v>244.8255703525027</v>
       </c>
       <c r="Y7" t="n">
-        <v>212.2577070053639</v>
+        <v>211.6397950518646</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.5996111723153</v>
+        <v>278.0113456531407</v>
       </c>
       <c r="AA7" t="n">
-        <v>207.0923773165318</v>
+        <v>205.1900024414062</v>
       </c>
       <c r="AB7" t="n">
-        <v>291.9895542689732</v>
+        <v>292.4373910086495</v>
       </c>
       <c r="AC7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD7" t="n">
-        <v>30.63399590905556</v>
+        <v>30.47473200612557</v>
       </c>
       <c r="AE7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.42145649748873</v>
+        <v>37.33776102168918</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.97244760941486</v>
+        <v>36.81632528499681</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.346979524970016</v>
+        <v>4.38716292844407</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.9511483675853</v>
+        <v>31.89586551777253</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.8769381776148</v>
+        <v>43.83550963109852</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.550611512837808</v>
+        <v>-1.564343548126029</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01219512195121951</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>199.7336533270422</v>
+        <v>199</v>
       </c>
       <c r="AN7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>243.9878963636265</v>
+        <v>243.8155794716303</v>
       </c>
       <c r="AP7" t="n">
-        <v>215.645589860822</v>
+        <v>215.1674055488905</v>
       </c>
       <c r="AQ7" t="n">
-        <v>272.330202866431</v>
+        <v>272.4637533943701</v>
       </c>
       <c r="AR7" t="n">
-        <v>208.3214873566561</v>
+        <v>208.2800018310546</v>
       </c>
       <c r="AS7" t="n">
-        <v>286.0776369180485</v>
+        <v>286.2458778910733</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -19335,13 +20662,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>519.85</v>
+        <v>519.74</v>
       </c>
       <c r="I8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="J8" t="n">
-        <v>172.13576</v>
+        <v>172.6711</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -19356,46 +20683,46 @@
         <v>180.8622966828894</v>
       </c>
       <c r="O8" t="n">
-        <v>132.6613917228449</v>
+        <v>134.1943788202271</v>
       </c>
       <c r="P8" t="n">
-        <v>138.029504994877</v>
+        <v>138.1606605404713</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.62814033498378</v>
+        <v>32.15771365621515</v>
       </c>
       <c r="R8" t="n">
-        <v>83.08678968897406</v>
+        <v>83.59622595445165</v>
       </c>
       <c r="S8" t="n">
         <v>170.442614946209</v>
       </c>
       <c r="T8" t="n">
-        <v>1.209825870303459</v>
+        <v>1.196500522117701</v>
       </c>
       <c r="U8" t="n">
         <v>0.9344262295081968</v>
       </c>
       <c r="V8" t="n">
-        <v>223.4116149902344</v>
+        <v>222.671841430664</v>
       </c>
       <c r="W8" t="n">
-        <v>546.2041359823259</v>
+        <v>544.3955130154969</v>
       </c>
       <c r="X8" t="n">
-        <v>400.6374030029914</v>
+        <v>403.9250802488834</v>
       </c>
       <c r="Y8" t="n">
-        <v>302.1004191913404</v>
+        <v>307.1303621436758</v>
       </c>
       <c r="Z8" t="n">
-        <v>499.1743868146425</v>
+        <v>500.719798354091</v>
       </c>
       <c r="AA8" t="n">
-        <v>250.9221048607017</v>
+        <v>251.6246401228995</v>
       </c>
       <c r="AB8" t="n">
-        <v>514.7366971375512</v>
+        <v>513.0322709880892</v>
       </c>
       <c r="AC8" t="n">
         <v>122</v>
@@ -19407,57 +20734,57 @@
         <v>180.8622966828894</v>
       </c>
       <c r="AF8" t="n">
-        <v>112.4336768414003</v>
+        <v>112.962366575239</v>
       </c>
       <c r="AG8" t="n">
-        <v>106.7832681283774</v>
+        <v>108.1034653230453</v>
       </c>
       <c r="AH8" t="n">
-        <v>33.5270930653851</v>
+        <v>33.9294517208715</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>166.2131177558274</v>
+        <v>167.162624671811</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.780711588749067</v>
+        <v>1.75979069499763</v>
       </c>
       <c r="AL8" t="n">
         <v>0.9672131147540983</v>
       </c>
       <c r="AM8" t="n">
-        <v>217.6109399183741</v>
+        <v>216.8903738921543</v>
       </c>
       <c r="AN8" t="n">
-        <v>546.2041359823259</v>
+        <v>544.3955130154969</v>
       </c>
       <c r="AO8" t="n">
-        <v>339.5497040610288</v>
+        <v>340.0167233914694</v>
       </c>
       <c r="AP8" t="n">
-        <v>238.2978830035658</v>
+        <v>237.8890737116462</v>
       </c>
       <c r="AQ8" t="n">
-        <v>440.8015251184917</v>
+        <v>442.1443730712926</v>
       </c>
       <c r="AR8" t="n">
-        <v>228.0646961831147</v>
+        <v>227.3095150699255</v>
       </c>
       <c r="AS8" t="n">
-        <v>501.9636156225986</v>
+        <v>503.159500262151</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -19486,13 +20813,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>380.15</v>
+        <v>382.07</v>
       </c>
       <c r="I9" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>63.252907</v>
+        <v>63.678333</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -19507,46 +20834,46 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.5059756953405</v>
+        <v>75.55936239198338</v>
       </c>
       <c r="P9" t="n">
         <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.412847039944809</v>
+        <v>9.334163522278317</v>
       </c>
       <c r="R9" t="n">
-        <v>61.31578709414597</v>
+        <v>61.91347855299761</v>
       </c>
       <c r="S9" t="n">
         <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.301738851523114</v>
+        <v>-1.272854215980504</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1475409836065574</v>
+        <v>0.180327868852459</v>
       </c>
       <c r="V9" t="n">
-        <v>343.7415442513212</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="W9" t="n">
-        <v>564.1785076059562</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="X9" t="n">
-        <v>453.7909139289964</v>
+        <v>453.3561743519003</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.2197032189281</v>
+        <v>397.3511932182304</v>
       </c>
       <c r="Z9" t="n">
-        <v>510.3621246390646</v>
+        <v>509.3611554855702</v>
       </c>
       <c r="AA9" t="n">
-        <v>368.5078804358172</v>
+        <v>371.4808713179856</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.9228569164612</v>
+        <v>501.087710731908</v>
       </c>
       <c r="AC9" t="n">
         <v>122</v>
@@ -19558,13 +20885,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.13340420998271</v>
+        <v>72.04939254299691</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.96855345911951</v>
+        <v>69.88993710691824</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.857603180592716</v>
+        <v>7.894109435643674</v>
       </c>
       <c r="AI9" t="n">
         <v>62.37563283819902</v>
@@ -19573,42 +20900,42 @@
         <v>82.37543771606209</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.130178886090407</v>
+        <v>-1.060418481811222</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.139344262295082</v>
+        <v>0.1721311475409836</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.7415442513212</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="AN9" t="n">
-        <v>564.1785076059562</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="AO9" t="n">
-        <v>433.5217593019961</v>
+        <v>432.2963552579815</v>
       </c>
       <c r="AP9" t="n">
-        <v>386.2975641866338</v>
+        <v>384.9316986441195</v>
       </c>
       <c r="AQ9" t="n">
-        <v>480.7459544173583</v>
+        <v>479.6610118718435</v>
       </c>
       <c r="AR9" t="n">
-        <v>374.8775533575761</v>
+        <v>374.2537970291942</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.0763806735332</v>
+        <v>494.2526262963726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-24 03:29:26</t>
+          <t>2026-06-25 03:21:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -19637,19 +20964,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>72.81999999999999</v>
+        <v>71.84</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.490324</v>
+        <v>23.174192</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -19668,7 +20995,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -19677,25 +21004,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>28.20461135814696</v>
+        <v>28.52805797173277</v>
       </c>
       <c r="AG10" t="n">
-        <v>33.44466318726067</v>
+        <v>33.45454521329976</v>
       </c>
       <c r="AH10" t="n">
-        <v>14.05813075953811</v>
+        <v>13.86518441531513</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.754803650361255</v>
+        <v>3.751211333693119</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.16798316442917</v>
+        <v>39.17391207849554</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.3353424035374276</v>
+        <v>-0.3861373791623735</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2266666666666667</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -19704,19 +21031,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>87.43429521025557</v>
+        <v>88.4369797123716</v>
       </c>
       <c r="AP10" t="n">
-        <v>43.85408985568741</v>
+        <v>45.45490802489469</v>
       </c>
       <c r="AQ10" t="n">
-        <v>131.0145005648237</v>
+        <v>131.4190513998485</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.63989131611989</v>
+        <v>11.62875513444867</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.4207478097304</v>
+        <v>121.4391274433362</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS127"/>
+  <dimension ref="A1:AS136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17967,7 +17967,7 @@
         <v>14.05813075953811</v>
       </c>
       <c r="AI117" t="n">
-        <v>3.754803650361255</v>
+        <v>3.754803650361256</v>
       </c>
       <c r="AJ117" t="n">
         <v>39.16798316442917</v>
@@ -18224,7 +18224,7 @@
         <v>37.38741008767781</v>
       </c>
       <c r="T119" t="n">
-        <v>0.2649660606031533</v>
+        <v>0.2649660606031532</v>
       </c>
       <c r="U119" t="n">
         <v>0.5573770491803278</v>
@@ -18375,7 +18375,7 @@
         <v>170.442614946209</v>
       </c>
       <c r="T120" t="n">
-        <v>1.196500522117701</v>
+        <v>1.1965005221177</v>
       </c>
       <c r="U120" t="n">
         <v>0.9344262295081968</v>
@@ -18429,7 +18429,7 @@
         <v>1.75979069499763</v>
       </c>
       <c r="AL120" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9672131147540984</v>
       </c>
       <c r="AM120" t="n">
         <v>216.8903738921543</v>
@@ -18441,13 +18441,13 @@
         <v>340.0167233914694</v>
       </c>
       <c r="AP120" t="n">
-        <v>237.8890737116462</v>
+        <v>237.8890737116461</v>
       </c>
       <c r="AQ120" t="n">
         <v>442.1443730712926</v>
       </c>
       <c r="AR120" t="n">
-        <v>227.3095150699255</v>
+        <v>227.3095150699256</v>
       </c>
       <c r="AS120" t="n">
         <v>503.159500262151</v>
@@ -18526,7 +18526,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T121" t="n">
-        <v>0.006402646661317796</v>
+        <v>0.0064026466613177</v>
       </c>
       <c r="U121" t="n">
         <v>0.4426229508196721</v>
@@ -18659,7 +18659,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N122" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O122" t="n">
         <v>75.55936239198338</v>
@@ -18698,7 +18698,7 @@
         <v>509.3611554855702</v>
       </c>
       <c r="AA122" t="n">
-        <v>371.4808713179856</v>
+        <v>371.4808713179857</v>
       </c>
       <c r="AB122" t="n">
         <v>501.087710731908</v>
@@ -18710,7 +18710,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE122" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF122" t="n">
         <v>72.04939254299691</v>
@@ -18746,7 +18746,7 @@
         <v>384.9316986441195</v>
       </c>
       <c r="AQ122" t="n">
-        <v>479.6610118718435</v>
+        <v>479.6610118718434</v>
       </c>
       <c r="AR122" t="n">
         <v>374.2537970291942</v>
@@ -18831,7 +18831,7 @@
         <v>-1.580165177077294</v>
       </c>
       <c r="U123" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="V123" t="n">
         <v>331.2549113821476</v>
@@ -18864,7 +18864,7 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF123" t="n">
-        <v>29.53851936446002</v>
+        <v>29.53851936446001</v>
       </c>
       <c r="AG123" t="n">
         <v>29.21870597964289</v>
@@ -18882,7 +18882,7 @@
         <v>-1.57263042448554</v>
       </c>
       <c r="AL123" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.0327868852459016</v>
       </c>
       <c r="AM123" t="n">
         <v>331.2549113821476</v>
@@ -18903,7 +18903,7 @@
         <v>357.1644154650099</v>
       </c>
       <c r="AS123" t="n">
-        <v>428.1003802556511</v>
+        <v>428.1003802556512</v>
       </c>
     </row>
     <row r="124">
@@ -18970,10 +18970,10 @@
         <v>22.3805862368295</v>
       </c>
       <c r="Q124" t="n">
-        <v>2.847723161160523</v>
+        <v>2.847723161160524</v>
       </c>
       <c r="R124" t="n">
-        <v>20.76290838068182</v>
+        <v>20.76290838068181</v>
       </c>
       <c r="S124" t="n">
         <v>28.57982234378326</v>
@@ -18982,7 +18982,7 @@
         <v>-1.208602464749484</v>
       </c>
       <c r="U124" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V124" t="n">
         <v>557.4671938254615</v>
@@ -19033,7 +19033,7 @@
         <v>-1.802310702050005</v>
       </c>
       <c r="AL124" t="n">
-        <v>0.00819672131147541</v>
+        <v>0.0081967213114754</v>
       </c>
       <c r="AM124" t="n">
         <v>557.4671938254615</v>
@@ -19118,7 +19118,7 @@
         <v>24.5356597409958</v>
       </c>
       <c r="P125" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q125" t="n">
         <v>1.383554351681298</v>
@@ -19127,13 +19127,13 @@
         <v>22.58333297002883</v>
       </c>
       <c r="S125" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T125" t="n">
-        <v>-1.982700381565995</v>
+        <v>-1.982700381565996</v>
       </c>
       <c r="U125" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V125" t="n">
         <v>364.8073843274798</v>
@@ -19184,7 +19184,7 @@
         <v>-1.270616493287778</v>
       </c>
       <c r="AL125" t="n">
-        <v>0.00819672131147541</v>
+        <v>0.0081967213114754</v>
       </c>
       <c r="AM125" t="n">
         <v>364.8073843274798</v>
@@ -19279,7 +19279,7 @@
         <v>75</v>
       </c>
       <c r="AD126" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE126" t="n">
         <v>42.60474344487245</v>
@@ -19294,16 +19294,16 @@
         <v>13.86518441531513</v>
       </c>
       <c r="AI126" t="n">
-        <v>3.751211333693119</v>
+        <v>3.75121133369312</v>
       </c>
       <c r="AJ126" t="n">
         <v>39.17391207849554</v>
       </c>
       <c r="AK126" t="n">
-        <v>-0.3861373791623735</v>
+        <v>-0.3861373791623734</v>
       </c>
       <c r="AL126" t="n">
-        <v>0.2266666666666667</v>
+        <v>0.2266666666666666</v>
       </c>
       <c r="AM126" t="n">
         <v>10.81762752038992</v>
@@ -19394,7 +19394,7 @@
         <v>5.082048284936918</v>
       </c>
       <c r="R127" t="n">
-        <v>31.42266499868395</v>
+        <v>31.42266499868396</v>
       </c>
       <c r="S127" t="n">
         <v>44.78367396763392</v>
@@ -19476,6 +19476,1333 @@
       </c>
       <c r="AS127" t="n">
         <v>286.2458778910733</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="I128" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J128" t="n">
+        <v>33.351513</v>
+      </c>
+      <c r="K128" t="n">
+        <v>67</v>
+      </c>
+      <c r="L128" t="n">
+        <v>61</v>
+      </c>
+      <c r="M128" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N128" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O128" t="n">
+        <v>35.04123520993558</v>
+      </c>
+      <c r="P128" t="n">
+        <v>35.24576330300393</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1.729969455973103</v>
+      </c>
+      <c r="R128" t="n">
+        <v>32.76708675336234</v>
+      </c>
+      <c r="S128" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T128" t="n">
+        <v>-0.976735285181736</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.2131147540983606</v>
+      </c>
+      <c r="V128" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="W128" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X128" t="n">
+        <v>289.0901904819685</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>274.8179424701904</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>303.3624384937467</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>270.3284657152393</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>308.446133223342</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>34.3901249140485</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>34.40435746680161</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.678648878759581</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>36.60311899573401</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>-0.6187189752367825</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>283.7185305409001</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>269.8696772911336</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>297.5673837906667</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>301.9757317148055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>532.5700000000001</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J129" t="n">
+        <v>178.71477</v>
+      </c>
+      <c r="K129" t="n">
+        <v>63</v>
+      </c>
+      <c r="L129" t="n">
+        <v>61</v>
+      </c>
+      <c r="M129" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N129" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="O129" t="n">
+        <v>135.8073374033935</v>
+      </c>
+      <c r="P129" t="n">
+        <v>139.0491823290215</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>31.66527157075409</v>
+      </c>
+      <c r="R129" t="n">
+        <v>87.479248046875</v>
+      </c>
+      <c r="S129" t="n">
+        <v>170.9967141073258</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1.355031252478996</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.9672131147540983</v>
+      </c>
+      <c r="V129" t="n">
+        <v>220.4525207519531</v>
+      </c>
+      <c r="W129" t="n">
+        <v>538.9696441150103</v>
+      </c>
+      <c r="X129" t="n">
+        <v>404.7058654621127</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>310.3433561812656</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>499.06837474296</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>260.6881591796875</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>509.570208039831</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>113.4635921897125</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>108.8522173501</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>34.24430610745814</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>167.6334448642418</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.905460651050432</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.983739837398374</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>214.728675813495</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>538.9696441150103</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>338.1215047253433</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>236.073472525118</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>440.1695369255685</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>225.0473451779923</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>499.5476656954406</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>227.01</v>
+      </c>
+      <c r="I130" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="J130" t="n">
+        <v>31.661087</v>
+      </c>
+      <c r="K130" t="n">
+        <v>67</v>
+      </c>
+      <c r="L130" t="n">
+        <v>61</v>
+      </c>
+      <c r="M130" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N130" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O130" t="n">
+        <v>31.63155628119264</v>
+      </c>
+      <c r="P130" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>2.506718505758223</v>
+      </c>
+      <c r="R130" t="n">
+        <v>28.4688995215311</v>
+      </c>
+      <c r="S130" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.0117806282354875</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V130" t="n">
+        <v>194.6963708868437</v>
+      </c>
+      <c r="W130" t="n">
+        <v>263.989990234375</v>
+      </c>
+      <c r="X130" t="n">
+        <v>226.7982585361513</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>208.8250868498648</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>244.7714302224377</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>204.122009569378</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>250.5599975585938</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>31.33317725668595</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>31.45339017533987</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>2.438163613726255</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>28.54016413217114</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.1344904589125991</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>194.6963708868437</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>263.989990234375</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>224.6588809304383</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>207.177247820021</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>242.1405140408555</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>204.6329768276671</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>248.9160034179687</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="I131" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J131" t="n">
+        <v>62.94186</v>
+      </c>
+      <c r="K131" t="n">
+        <v>34</v>
+      </c>
+      <c r="L131" t="n">
+        <v>61</v>
+      </c>
+      <c r="M131" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N131" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O131" t="n">
+        <v>75.63205919994044</v>
+      </c>
+      <c r="P131" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>9.216500957717233</v>
+      </c>
+      <c r="R131" t="n">
+        <v>62.68053102413946</v>
+      </c>
+      <c r="S131" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T131" t="n">
+        <v>-1.376899894890651</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.1147540983606557</v>
+      </c>
+      <c r="V131" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="W131" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X131" t="n">
+        <v>455.3049963836414</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>399.8216606181837</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>510.7883321490992</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>377.3367967653195</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>502.7580031010143</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>71.97619902335984</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>69.86163317282495</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>7.903487573773657</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>62.40428783275464</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>-1.143082587152881</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.1382113821138211</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>433.2967181206262</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>385.7177229265088</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>480.8757133147436</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>375.6738127531829</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>495.8250335990802</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>342.19</v>
+      </c>
+      <c r="I132" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J132" t="n">
+        <v>26.10145</v>
+      </c>
+      <c r="K132" t="n">
+        <v>37</v>
+      </c>
+      <c r="L132" t="n">
+        <v>61</v>
+      </c>
+      <c r="M132" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N132" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O132" t="n">
+        <v>28.99244766582514</v>
+      </c>
+      <c r="P132" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1.658566781901173</v>
+      </c>
+      <c r="R132" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S132" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T132" t="n">
+        <v>-1.743069798197248</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="V132" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="W132" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X132" t="n">
+        <v>380.0909888989675</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>358.3471783882432</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>401.8347994096919</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>353.3200073242188</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>409.5874601323553</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>29.51057570671308</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>29.20629058470889</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>2.062330199793983</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>27.20596557896525</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>-1.653045524452697</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.03252032520325204</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>386.8836475150085</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>359.8464985957094</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>413.9207964343076</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>356.6702087402344</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>428.0356714698664</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>542.87</v>
+      </c>
+      <c r="I133" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="J133" t="n">
+        <v>19.72638</v>
+      </c>
+      <c r="K133" t="n">
+        <v>55</v>
+      </c>
+      <c r="L133" t="n">
+        <v>61</v>
+      </c>
+      <c r="M133" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N133" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O133" t="n">
+        <v>23.68477385213134</v>
+      </c>
+      <c r="P133" t="n">
+        <v>22.33563565340909</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>2.888311142021387</v>
+      </c>
+      <c r="R133" t="n">
+        <v>20.67018155184659</v>
+      </c>
+      <c r="S133" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T133" t="n">
+        <v>-1.370487339311045</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="W133" t="n">
+        <v>806.6792534722222</v>
+      </c>
+      <c r="X133" t="n">
+        <v>651.8049764106544</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>572.3186537822259</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>731.2912990390829</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>568.8433963068181</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>786.5167109009152</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>25.76897371358528</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>27.12856534695615</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>3.105575517525062</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>21.61127219460228</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>29.17387104963602</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>-1.94572428829579</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>864.9762082934226</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>709.1621565978669</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>623.6967183555772</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>794.6275948401566</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>594.7422107954546</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>802.8649312859832</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="I134" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J134" t="n">
+        <v>21.014292</v>
+      </c>
+      <c r="K134" t="n">
+        <v>67</v>
+      </c>
+      <c r="L134" t="n">
+        <v>61</v>
+      </c>
+      <c r="M134" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N134" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O134" t="n">
+        <v>24.51417966818127</v>
+      </c>
+      <c r="P134" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1.428105567565726</v>
+      </c>
+      <c r="R134" t="n">
+        <v>22.58333297002883</v>
+      </c>
+      <c r="S134" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T134" t="n">
+        <v>-2.450720554326383</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V134" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W134" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X134" t="n">
+        <v>411.5930766287635</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>387.615184149335</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>435.5709691081921</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>379.1741605667841</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>445.3812671348853</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>34.67140903174453</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>26.16330433758643</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>25.05315860559822</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>3.490632233814055</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>23.21050739722864</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>33.38648659067167</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>-1.475094479363223</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.008130081300813009</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>582.1329576429906</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>439.2818798280761</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>380.6741646223381</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>497.8895950338141</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>389.7044191994688</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>560.5591098573774</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="I135" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>22.87097</v>
+      </c>
+      <c r="K135" t="n">
+        <v>67</v>
+      </c>
+      <c r="L135" t="n">
+        <v>13</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
+      <c r="AB135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>28.52805797173277</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>33.45454521329976</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>13.86518441531513</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>3.751211333693119</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>39.17391207849554</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.4080066879950111</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>88.4369797123716</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>45.45490802489469</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>131.4190513998485</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>11.62875513444867</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>121.4391274433362</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-06-26 03:34:29</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>195.74</v>
+      </c>
+      <c r="I136" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J136" t="n">
+        <v>29.929665</v>
+      </c>
+      <c r="K136" t="n">
+        <v>65</v>
+      </c>
+      <c r="L136" t="n">
+        <v>61</v>
+      </c>
+      <c r="M136" t="n">
+        <v>29.97549854412926</v>
+      </c>
+      <c r="N136" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O136" t="n">
+        <v>37.42337697508546</v>
+      </c>
+      <c r="P136" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>5.155782201865747</v>
+      </c>
+      <c r="R136" t="n">
+        <v>31.4088830173837</v>
+      </c>
+      <c r="S136" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-1.453457823019304</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>196.0397604786053</v>
+      </c>
+      <c r="W136" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="X136" t="n">
+        <v>244.7488854170589</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>211.0300698168569</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>278.4677010172609</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>205.4140949336894</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>292.8852277483259</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>29.97549854412926</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>37.25011503981347</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>36.80101978535555</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>4.434024957735758</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>31.79846911116362</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>43.79408108458227</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-1.650971771604927</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>196.0397604786053</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>243.6157523603801</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>214.6172291367882</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>272.6142755839719</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>207.96198798701</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>286.413290293168</v>
       </c>
     </row>
   </sheetData>
@@ -19722,12 +21049,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -19756,13 +21083,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>345.04</v>
+        <v>342.19</v>
       </c>
       <c r="I2" t="n">
         <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>26.318842</v>
+        <v>26.10145</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -19777,13 +21104,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.97971407228829</v>
+        <v>28.99244766582514</v>
       </c>
       <c r="P2" t="n">
         <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.683920207132963</v>
+        <v>1.658566781901173</v>
       </c>
       <c r="R2" t="n">
         <v>26.95042008575277</v>
@@ -19792,10 +21119,10 @@
         <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.580165177077294</v>
+        <v>-1.743069798197248</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="V2" t="n">
         <v>331.2549113821476</v>
@@ -19804,13 +21131,13 @@
         <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>379.9240514876995</v>
+        <v>380.0909888989675</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.8478575721863</v>
+        <v>358.3471783882432</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.0002454032127</v>
+        <v>401.8347994096919</v>
       </c>
       <c r="AA2" t="n">
         <v>353.3200073242188</v>
@@ -19819,7 +21146,7 @@
         <v>409.5874601323553</v>
       </c>
       <c r="AC2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -19828,25 +21155,25 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.53851936446002</v>
+        <v>29.51057570671308</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.21870597964289</v>
+        <v>29.20629058470889</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.047319773501952</v>
+        <v>2.062330199793983</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.24366250686575</v>
+        <v>27.20596557896525</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65449124757065</v>
+        <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.57263042448554</v>
+        <v>-1.653045524452697</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.03252032520325204</v>
       </c>
       <c r="AM2" t="n">
         <v>331.2549113821476</v>
@@ -19855,30 +21182,30 @@
         <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>387.2499888680708</v>
+        <v>386.8836475150085</v>
       </c>
       <c r="AP2" t="n">
-        <v>360.4096266374602</v>
+        <v>359.8464985957094</v>
       </c>
       <c r="AQ2" t="n">
-        <v>414.0903510986814</v>
+        <v>413.9207964343076</v>
       </c>
       <c r="AR2" t="n">
-        <v>357.1644154650099</v>
+        <v>356.6702087402344</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.1003802556511</v>
+        <v>428.0356714698664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -19907,13 +21234,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>365.46</v>
+        <v>352.83</v>
       </c>
       <c r="I3" t="n">
-        <v>16.77</v>
+        <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>21.792486</v>
+        <v>21.014292</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -19922,19 +21249,19 @@
         <v>61</v>
       </c>
       <c r="M3" t="n">
-        <v>21.75357091994513</v>
+        <v>21.00178491501581</v>
       </c>
       <c r="N3" t="n">
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.5356597409958</v>
+        <v>24.51417966818127</v>
       </c>
       <c r="P3" t="n">
         <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.383554351681298</v>
+        <v>1.428105567565726</v>
       </c>
       <c r="R3" t="n">
         <v>22.58333297002883</v>
@@ -19943,93 +21270,93 @@
         <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.982700381565995</v>
+        <v>-2.450720554326383</v>
       </c>
       <c r="U3" t="n">
         <v>0.01639344262295082</v>
       </c>
       <c r="V3" t="n">
-        <v>364.8073843274798</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="W3" t="n">
-        <v>459.6976318904332</v>
+        <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>411.4630138564996</v>
+        <v>411.5930766287635</v>
       </c>
       <c r="Y3" t="n">
-        <v>388.2608073788043</v>
+        <v>387.615184149335</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.665220334195</v>
+        <v>435.5709691081921</v>
       </c>
       <c r="AA3" t="n">
-        <v>378.7224939073835</v>
+        <v>379.1741605667841</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.8507355480659</v>
+        <v>445.3812671348853</v>
       </c>
       <c r="AC3" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD3" t="n">
-        <v>21.75357091994513</v>
+        <v>21.00178491501581</v>
       </c>
       <c r="AE3" t="n">
         <v>34.67140903174453</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.20561187383701</v>
+        <v>26.16330433758643</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.05812684918583</v>
+        <v>25.05315860559822</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.473216267182116</v>
+        <v>3.490632233814055</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.23690450759161</v>
+        <v>23.21050739722864</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33.41728308122833</v>
+        <v>33.38648659067167</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.270616493287778</v>
+        <v>-1.475094479363223</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.00819672131147541</v>
+        <v>0.008130081300813009</v>
       </c>
       <c r="AM3" t="n">
-        <v>364.8073843274798</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="AN3" t="n">
-        <v>581.4395294623557</v>
+        <v>582.1329576429906</v>
       </c>
       <c r="AO3" t="n">
-        <v>439.4681111242466</v>
+        <v>439.2818798280761</v>
       </c>
       <c r="AP3" t="n">
-        <v>381.2222743236025</v>
+        <v>380.6741646223381</v>
       </c>
       <c r="AQ3" t="n">
-        <v>497.7139479248907</v>
+        <v>497.8895950338141</v>
       </c>
       <c r="AR3" t="n">
-        <v>389.6828885923113</v>
+        <v>389.7044191994688</v>
       </c>
       <c r="AS3" t="n">
-        <v>560.407837272199</v>
+        <v>560.5591098573774</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -20058,13 +21385,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>557.67</v>
+        <v>542.87</v>
       </c>
       <c r="I4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="J4" t="n">
-        <v>20.286285</v>
+        <v>19.72638</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -20073,114 +21400,114 @@
         <v>61</v>
       </c>
       <c r="M4" t="n">
-        <v>20.27890846946023</v>
+        <v>19.74072709517046</v>
       </c>
       <c r="N4" t="n">
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.7280502315028</v>
+        <v>23.68477385213134</v>
       </c>
       <c r="P4" t="n">
-        <v>22.3805862368295</v>
+        <v>22.33563565340909</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.847723161160523</v>
+        <v>2.888311142021387</v>
       </c>
       <c r="R4" t="n">
-        <v>20.76290838068182</v>
+        <v>20.67018155184659</v>
       </c>
       <c r="S4" t="n">
         <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.208602464749484</v>
+        <v>-1.370487339311045</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01639344262295082</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>557.4671938254615</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="W4" t="n">
-        <v>805.7998792860242</v>
+        <v>806.6792534722222</v>
       </c>
       <c r="X4" t="n">
-        <v>652.2841008640119</v>
+        <v>651.8049764106544</v>
       </c>
       <c r="Y4" t="n">
-        <v>574.0001911637091</v>
+        <v>572.3186537822259</v>
       </c>
       <c r="Z4" t="n">
-        <v>730.5680105643147</v>
+        <v>731.2912990390829</v>
       </c>
       <c r="AA4" t="n">
-        <v>570.7723513849431</v>
+        <v>568.8433963068181</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.6593162306017</v>
+        <v>786.5167109009152</v>
       </c>
       <c r="AC4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD4" t="n">
-        <v>20.27890846946023</v>
+        <v>19.74072709517046</v>
       </c>
       <c r="AE4" t="n">
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.81838557111327</v>
+        <v>25.76897371358528</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.13735667641555</v>
+        <v>27.12856534695615</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.069448882937269</v>
+        <v>3.105575517525062</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.73647283380682</v>
+        <v>21.61127219460228</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.17418109093017</v>
+        <v>29.17387104963602</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.802310702050005</v>
+        <v>-1.94572428829579</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.00819672131147541</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>557.4671938254615</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.0332836477539</v>
+        <v>864.9762082934226</v>
       </c>
       <c r="AO4" t="n">
-        <v>709.7474193499038</v>
+        <v>709.1621565978669</v>
       </c>
       <c r="AP4" t="n">
-        <v>625.3682695579582</v>
+        <v>623.6967183555772</v>
       </c>
       <c r="AQ4" t="n">
-        <v>794.1265691418494</v>
+        <v>794.6275948401566</v>
       </c>
       <c r="AR4" t="n">
-        <v>597.5356382013495</v>
+        <v>594.7422107954546</v>
       </c>
       <c r="AS4" t="n">
-        <v>801.9982381896702</v>
+        <v>802.8649312859832</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20209,13 +21536,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>234.27</v>
+        <v>227.01</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>7.17</v>
       </c>
       <c r="J5" t="n">
-        <v>31.658108</v>
+        <v>31.661087</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -20224,19 +21551,19 @@
         <v>61</v>
       </c>
       <c r="M5" t="n">
-        <v>27.80195206944081</v>
+        <v>27.15430556301865</v>
       </c>
       <c r="N5" t="n">
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.64217343703564</v>
+        <v>31.63155628119264</v>
       </c>
       <c r="P5" t="n">
         <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.488746264983075</v>
+        <v>2.506718505758223</v>
       </c>
       <c r="R5" t="n">
         <v>28.4688995215311</v>
@@ -20245,93 +21572,93 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006402646661317796</v>
+        <v>0.0117806282354875</v>
       </c>
       <c r="U5" t="n">
         <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>205.734445313862</v>
+        <v>194.6963708868437</v>
       </c>
       <c r="W5" t="n">
-        <v>272.4582883869421</v>
+        <v>263.989990234375</v>
       </c>
       <c r="X5" t="n">
-        <v>234.1520834340637</v>
+        <v>226.7982585361513</v>
       </c>
       <c r="Y5" t="n">
-        <v>215.735361073189</v>
+        <v>208.8250868498648</v>
       </c>
       <c r="Z5" t="n">
-        <v>252.5688057949385</v>
+        <v>244.7714302224377</v>
       </c>
       <c r="AA5" t="n">
-        <v>210.6698564593302</v>
+        <v>204.122009569378</v>
       </c>
       <c r="AB5" t="n">
-        <v>258.5974870200271</v>
+        <v>250.5599975585938</v>
       </c>
       <c r="AC5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD5" t="n">
-        <v>27.72524313614126</v>
+        <v>27.15430556301865</v>
       </c>
       <c r="AE5" t="n">
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.36743030335536</v>
+        <v>31.33317725668595</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.52454285372481</v>
+        <v>31.45339017533987</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.418318849109844</v>
+        <v>2.438163613726255</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.56303961207178</v>
+        <v>28.54016413217114</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.72357096864921</v>
+        <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1201982512569153</v>
+        <v>0.1344904589125991</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5081967213114754</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="AM5" t="n">
-        <v>205.1667992074453</v>
+        <v>194.6963708868437</v>
       </c>
       <c r="AN5" t="n">
-        <v>272.4582883869421</v>
+        <v>263.989990234375</v>
       </c>
       <c r="AO5" t="n">
-        <v>232.1189842448297</v>
+        <v>224.6588809304383</v>
       </c>
       <c r="AP5" t="n">
-        <v>214.2234247614168</v>
+        <v>207.177247820021</v>
       </c>
       <c r="AQ5" t="n">
-        <v>250.0145437282425</v>
+        <v>242.1405140408555</v>
       </c>
       <c r="AR5" t="n">
-        <v>211.3664931293312</v>
+        <v>204.6329768276671</v>
       </c>
       <c r="AS5" t="n">
-        <v>256.9544251680042</v>
+        <v>248.9160034179687</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -20360,13 +21687,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>293.08</v>
+        <v>275.15</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>35.48184</v>
+        <v>33.351513</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -20381,49 +21708,49 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.01144068529248</v>
+        <v>35.04123520993558</v>
       </c>
       <c r="P6" t="n">
         <v>35.24576330300393</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.775319124406818</v>
+        <v>1.729969455973103</v>
       </c>
       <c r="R6" t="n">
-        <v>32.7632894395273</v>
+        <v>32.76708675336234</v>
       </c>
       <c r="S6" t="n">
         <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2649660606031533</v>
+        <v>-0.976735285181736</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5573770491803278</v>
+        <v>0.2131147540983606</v>
       </c>
       <c r="V6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="W6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>289.1945000605159</v>
+        <v>289.0901904819685</v>
       </c>
       <c r="Y6" t="n">
-        <v>274.5303640929156</v>
+        <v>274.8179424701904</v>
       </c>
       <c r="Z6" t="n">
-        <v>303.8586360281162</v>
+        <v>303.3624384937467</v>
       </c>
       <c r="AA6" t="n">
-        <v>270.6247707704955</v>
+        <v>270.3284657152393</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.8200073242188</v>
+        <v>308.446133223342</v>
       </c>
       <c r="AC6" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -20432,57 +21759,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.39896907501936</v>
+        <v>34.3901249140485</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.42623029342849</v>
+        <v>34.40435746680161</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.682691208373762</v>
+        <v>1.678648878759581</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13088525699663</v>
+        <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.60450765954701</v>
+        <v>36.60311899573401</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.6435351415588489</v>
+        <v>-0.6187189752367825</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7377049180327869</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.1354845596599</v>
+        <v>283.7185305409001</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.2364551784926</v>
+        <v>269.8696772911336</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.0345139408271</v>
+        <v>297.5673837906667</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.4011122227922</v>
+        <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>302.3532332678583</v>
+        <v>301.9757317148055</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20511,13 +21838,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>199</v>
+        <v>195.74</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="J7" t="n">
-        <v>30.474731</v>
+        <v>29.929665</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -20526,114 +21853,114 @@
         <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>30.47473200612557</v>
+        <v>29.97549854412926</v>
       </c>
       <c r="N7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.49243037557468</v>
+        <v>37.42337697508546</v>
       </c>
       <c r="P7" t="n">
         <v>36.34694002112563</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.082048284936918</v>
+        <v>5.155782201865747</v>
       </c>
       <c r="R7" t="n">
-        <v>31.42266499868395</v>
+        <v>31.4088830173837</v>
       </c>
       <c r="S7" t="n">
         <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.380880106230984</v>
+        <v>-1.453457823019304</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>199</v>
+        <v>196.0397604786053</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="X7" t="n">
-        <v>244.8255703525027</v>
+        <v>244.7488854170589</v>
       </c>
       <c r="Y7" t="n">
-        <v>211.6397950518646</v>
+        <v>211.0300698168569</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.0113456531407</v>
+        <v>278.4677010172609</v>
       </c>
       <c r="AA7" t="n">
-        <v>205.1900024414062</v>
+        <v>205.4140949336894</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.4373910086495</v>
+        <v>292.8852277483259</v>
       </c>
       <c r="AC7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD7" t="n">
-        <v>30.47473200612557</v>
+        <v>29.97549854412926</v>
       </c>
       <c r="AE7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.33776102168918</v>
+        <v>37.25011503981347</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.81632528499681</v>
+        <v>36.80101978535555</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.38716292844407</v>
+        <v>4.434024957735758</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.89586551777253</v>
+        <v>31.79846911116362</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.83550963109852</v>
+        <v>43.79408108458227</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.564343548126029</v>
+        <v>-1.650971771604927</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>199</v>
+        <v>196.0397604786053</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="AO7" t="n">
-        <v>243.8155794716303</v>
+        <v>243.6157523603801</v>
       </c>
       <c r="AP7" t="n">
-        <v>215.1674055488905</v>
+        <v>214.6172291367882</v>
       </c>
       <c r="AQ7" t="n">
-        <v>272.4637533943701</v>
+        <v>272.6142755839719</v>
       </c>
       <c r="AR7" t="n">
-        <v>208.2800018310546</v>
+        <v>207.96198798701</v>
       </c>
       <c r="AS7" t="n">
-        <v>286.2458778910733</v>
+        <v>286.413290293168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20662,13 +21989,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>519.74</v>
+        <v>532.5700000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="n">
-        <v>172.6711</v>
+        <v>178.71477</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -20683,49 +22010,49 @@
         <v>180.8622966828894</v>
       </c>
       <c r="O8" t="n">
-        <v>134.1943788202271</v>
+        <v>135.8073374033935</v>
       </c>
       <c r="P8" t="n">
-        <v>138.1606605404713</v>
+        <v>139.0491823290215</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.15771365621515</v>
+        <v>31.66527157075409</v>
       </c>
       <c r="R8" t="n">
-        <v>83.59622595445165</v>
+        <v>87.479248046875</v>
       </c>
       <c r="S8" t="n">
-        <v>170.442614946209</v>
+        <v>170.9967141073258</v>
       </c>
       <c r="T8" t="n">
-        <v>1.196500522117701</v>
+        <v>1.355031252478996</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9344262295081968</v>
+        <v>0.9672131147540983</v>
       </c>
       <c r="V8" t="n">
-        <v>222.671841430664</v>
+        <v>220.4525207519531</v>
       </c>
       <c r="W8" t="n">
-        <v>544.3955130154969</v>
+        <v>538.9696441150103</v>
       </c>
       <c r="X8" t="n">
-        <v>403.9250802488834</v>
+        <v>404.7058654621127</v>
       </c>
       <c r="Y8" t="n">
-        <v>307.1303621436758</v>
+        <v>310.3433561812656</v>
       </c>
       <c r="Z8" t="n">
-        <v>500.719798354091</v>
+        <v>499.06837474296</v>
       </c>
       <c r="AA8" t="n">
-        <v>251.6246401228995</v>
+        <v>260.6881591796875</v>
       </c>
       <c r="AB8" t="n">
-        <v>513.0322709880892</v>
+        <v>509.570208039831</v>
       </c>
       <c r="AC8" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -20734,57 +22061,57 @@
         <v>180.8622966828894</v>
       </c>
       <c r="AF8" t="n">
-        <v>112.962366575239</v>
+        <v>113.4635921897125</v>
       </c>
       <c r="AG8" t="n">
-        <v>108.1034653230453</v>
+        <v>108.8522173501</v>
       </c>
       <c r="AH8" t="n">
-        <v>33.9294517208715</v>
+        <v>34.24430610745814</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51811131891215</v>
+        <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>167.162624671811</v>
+        <v>167.6334448642418</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75979069499763</v>
+        <v>1.905460651050432</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.983739837398374</v>
       </c>
       <c r="AM8" t="n">
-        <v>216.8903738921543</v>
+        <v>214.728675813495</v>
       </c>
       <c r="AN8" t="n">
-        <v>544.3955130154969</v>
+        <v>538.9696441150103</v>
       </c>
       <c r="AO8" t="n">
-        <v>340.0167233914694</v>
+        <v>338.1215047253433</v>
       </c>
       <c r="AP8" t="n">
-        <v>237.8890737116462</v>
+        <v>236.073472525118</v>
       </c>
       <c r="AQ8" t="n">
-        <v>442.1443730712926</v>
+        <v>440.1695369255685</v>
       </c>
       <c r="AR8" t="n">
-        <v>227.3095150699255</v>
+        <v>225.0473451779923</v>
       </c>
       <c r="AS8" t="n">
-        <v>503.159500262151</v>
+        <v>499.5476656954406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20813,13 +22140,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>382.07</v>
+        <v>378.91</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>63.678333</v>
+        <v>62.94186</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -20834,49 +22161,49 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.55936239198338</v>
+        <v>75.63205919994044</v>
       </c>
       <c r="P9" t="n">
         <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.334163522278317</v>
+        <v>9.216500957717233</v>
       </c>
       <c r="R9" t="n">
-        <v>61.91347855299761</v>
+        <v>62.68053102413946</v>
       </c>
       <c r="S9" t="n">
         <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.272854215980504</v>
+        <v>-1.376899894890651</v>
       </c>
       <c r="U9" t="n">
-        <v>0.180327868852459</v>
+        <v>0.1147540983606557</v>
       </c>
       <c r="V9" t="n">
-        <v>343.1695949264438</v>
+        <v>344.3134935761985</v>
       </c>
       <c r="W9" t="n">
-        <v>563.2397746482092</v>
+        <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>453.3561743519003</v>
+        <v>455.3049963836414</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.3511932182304</v>
+        <v>399.8216606181837</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.3611554855702</v>
+        <v>510.7883321490992</v>
       </c>
       <c r="AA9" t="n">
-        <v>371.4808713179856</v>
+        <v>377.3367967653195</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.087710731908</v>
+        <v>502.7580031010143</v>
       </c>
       <c r="AC9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -20885,57 +22212,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>72.04939254299691</v>
+        <v>71.97619902335984</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.88993710691824</v>
+        <v>69.86163317282495</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.894109435643674</v>
+        <v>7.903487573773657</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.37563283819902</v>
+        <v>62.40428783275464</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.37543771606209</v>
+        <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.060418481811222</v>
+        <v>-1.143082587152881</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1721311475409836</v>
+        <v>0.1382113821138211</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.1695949264438</v>
+        <v>344.3134935761985</v>
       </c>
       <c r="AN9" t="n">
-        <v>563.2397746482092</v>
+        <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>432.2963552579815</v>
+        <v>433.2967181206262</v>
       </c>
       <c r="AP9" t="n">
-        <v>384.9316986441195</v>
+        <v>385.7177229265088</v>
       </c>
       <c r="AQ9" t="n">
-        <v>479.6610118718435</v>
+        <v>480.8757133147436</v>
       </c>
       <c r="AR9" t="n">
-        <v>374.2537970291942</v>
+        <v>375.6738127531829</v>
       </c>
       <c r="AS9" t="n">
-        <v>494.2526262963726</v>
+        <v>495.8250335990802</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-25 03:21:48</t>
+          <t>2026-06-26 03:34:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20964,19 +22291,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>71.84</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.174192</v>
+        <v>22.87097</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -21019,7 +22346,7 @@
         <v>39.17391207849554</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.3861373791623735</v>
+        <v>-0.4080066879950111</v>
       </c>
       <c r="AL10" t="n">
         <v>0.2266666666666667</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS136"/>
+  <dimension ref="A1:AS145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18541,7 +18541,7 @@
         <v>234.1520834340637</v>
       </c>
       <c r="Y121" t="n">
-        <v>215.735361073189</v>
+        <v>215.7353610731889</v>
       </c>
       <c r="Z121" t="n">
         <v>252.5688057949385</v>
@@ -19415,7 +19415,7 @@
         <v>244.8255703525027</v>
       </c>
       <c r="Y127" t="n">
-        <v>211.6397950518646</v>
+        <v>211.6397950518645</v>
       </c>
       <c r="Z127" t="n">
         <v>278.0113456531407</v>
@@ -19593,7 +19593,7 @@
         <v>34.40435746680161</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.678648878759581</v>
+        <v>1.678648878759582</v>
       </c>
       <c r="AI128" t="n">
         <v>32.13645490815368</v>
@@ -19705,16 +19705,16 @@
         <v>1.355031252478996</v>
       </c>
       <c r="U129" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9672131147540984</v>
       </c>
       <c r="V129" t="n">
-        <v>220.4525207519531</v>
+        <v>220.4525207519532</v>
       </c>
       <c r="W129" t="n">
         <v>538.9696441150103</v>
       </c>
       <c r="X129" t="n">
-        <v>404.7058654621127</v>
+        <v>404.7058654621128</v>
       </c>
       <c r="Y129" t="n">
         <v>310.3433561812656</v>
@@ -19774,7 +19774,7 @@
         <v>440.1695369255685</v>
       </c>
       <c r="AR129" t="n">
-        <v>225.0473451779923</v>
+        <v>225.0473451779924</v>
       </c>
       <c r="AS129" t="n">
         <v>499.5476656954406</v>
@@ -19844,7 +19844,7 @@
         <v>31.73325461063659</v>
       </c>
       <c r="Q130" t="n">
-        <v>2.506718505758223</v>
+        <v>2.506718505758222</v>
       </c>
       <c r="R130" t="n">
         <v>28.4688995215311</v>
@@ -19889,10 +19889,10 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF130" t="n">
-        <v>31.33317725668595</v>
+        <v>31.33317725668596</v>
       </c>
       <c r="AG130" t="n">
-        <v>31.45339017533987</v>
+        <v>31.45339017533986</v>
       </c>
       <c r="AH130" t="n">
         <v>2.438163613726255</v>
@@ -19919,7 +19919,7 @@
         <v>224.6588809304383</v>
       </c>
       <c r="AP130" t="n">
-        <v>207.177247820021</v>
+        <v>207.1772478200211</v>
       </c>
       <c r="AQ130" t="n">
         <v>242.1405140408555</v>
@@ -19928,7 +19928,7 @@
         <v>204.6329768276671</v>
       </c>
       <c r="AS130" t="n">
-        <v>248.9160034179687</v>
+        <v>248.9160034179688</v>
       </c>
     </row>
     <row r="131">
@@ -19986,7 +19986,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N131" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O131" t="n">
         <v>75.63205919994044</v>
@@ -19995,7 +19995,7 @@
         <v>79.03509009883652</v>
       </c>
       <c r="Q131" t="n">
-        <v>9.216500957717233</v>
+        <v>9.216500957717232</v>
       </c>
       <c r="R131" t="n">
         <v>62.68053102413946</v>
@@ -20037,7 +20037,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE131" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF131" t="n">
         <v>71.97619902335984</v>
@@ -20158,7 +20158,7 @@
         <v>-1.743069798197248</v>
       </c>
       <c r="U132" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.0327868852459016</v>
       </c>
       <c r="V132" t="n">
         <v>331.2549113821476</v>
@@ -20209,7 +20209,7 @@
         <v>-1.653045524452697</v>
       </c>
       <c r="AL132" t="n">
-        <v>0.03252032520325204</v>
+        <v>0.032520325203252</v>
       </c>
       <c r="AM132" t="n">
         <v>331.2549113821476</v>
@@ -20445,7 +20445,7 @@
         <v>24.51417966818127</v>
       </c>
       <c r="P134" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q134" t="n">
         <v>1.428105567565726</v>
@@ -20454,13 +20454,13 @@
         <v>22.58333297002883</v>
       </c>
       <c r="S134" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T134" t="n">
         <v>-2.450720554326383</v>
       </c>
       <c r="U134" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V134" t="n">
         <v>352.6199687231154</v>
@@ -20511,7 +20511,7 @@
         <v>-1.475094479363223</v>
       </c>
       <c r="AL134" t="n">
-        <v>0.008130081300813009</v>
+        <v>0.008130081300813</v>
       </c>
       <c r="AM134" t="n">
         <v>352.6199687231154</v>
@@ -20606,7 +20606,7 @@
         <v>75</v>
       </c>
       <c r="AD135" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE135" t="n">
         <v>42.60474344487245</v>
@@ -20621,7 +20621,7 @@
         <v>13.86518441531513</v>
       </c>
       <c r="AI135" t="n">
-        <v>3.751211333693119</v>
+        <v>3.75121133369312</v>
       </c>
       <c r="AJ135" t="n">
         <v>39.17391207849554</v>
@@ -20630,7 +20630,7 @@
         <v>-0.4080066879950111</v>
       </c>
       <c r="AL135" t="n">
-        <v>0.2266666666666667</v>
+        <v>0.2266666666666666</v>
       </c>
       <c r="AM135" t="n">
         <v>10.81762752038992</v>
@@ -20706,7 +20706,7 @@
         <v>61</v>
       </c>
       <c r="M136" t="n">
-        <v>29.97549854412926</v>
+        <v>29.97549854412925</v>
       </c>
       <c r="N136" t="n">
         <v>48.11020520268654</v>
@@ -20757,7 +20757,7 @@
         <v>84</v>
       </c>
       <c r="AD136" t="n">
-        <v>29.97549854412926</v>
+        <v>29.97549854412925</v>
       </c>
       <c r="AE136" t="n">
         <v>48.11020520268654</v>
@@ -20803,6 +20803,1333 @@
       </c>
       <c r="AS136" t="n">
         <v>286.413290293168</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="I137" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.35593</v>
+      </c>
+      <c r="K137" t="n">
+        <v>67</v>
+      </c>
+      <c r="L137" t="n">
+        <v>61</v>
+      </c>
+      <c r="M137" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="N137" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O137" t="n">
+        <v>35.04123520993558</v>
+      </c>
+      <c r="P137" t="n">
+        <v>35.24576330300393</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.729969455973103</v>
+      </c>
+      <c r="R137" t="n">
+        <v>32.76708675336234</v>
+      </c>
+      <c r="S137" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.396137173156098</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.3770491803278688</v>
+      </c>
+      <c r="V137" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="W137" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X137" t="n">
+        <v>289.4406028340679</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>275.15105512773</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>303.7301505404057</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>270.6561365827729</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>308.8200073242188</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>34.3901249140485</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>34.40435746680161</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.678648878759581</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>36.60311899573401</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>-0.02037049825081136</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.4878048780487805</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>284.0624317900406</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>270.1967920514865</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>297.9280715285947</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>265.4471175413494</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>302.3417629047629</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>521.58</v>
+      </c>
+      <c r="I138" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="J138" t="n">
+        <v>172.13863</v>
+      </c>
+      <c r="K138" t="n">
+        <v>63</v>
+      </c>
+      <c r="L138" t="n">
+        <v>62</v>
+      </c>
+      <c r="M138" t="n">
+        <v>73.97735595703125</v>
+      </c>
+      <c r="N138" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="O138" t="n">
+        <v>136.375119730255</v>
+      </c>
+      <c r="P138" t="n">
+        <v>142.5573780497567</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>31.72127443684333</v>
+      </c>
+      <c r="R138" t="n">
+        <v>87.66113453991008</v>
+      </c>
+      <c r="S138" t="n">
+        <v>171.0085289126537</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.127429805537913</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.9193548387096774</v>
+      </c>
+      <c r="V138" t="n">
+        <v>224.1513885498047</v>
+      </c>
+      <c r="W138" t="n">
+        <v>548.0127589491548</v>
+      </c>
+      <c r="X138" t="n">
+        <v>413.2166127826725</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>317.1011512390372</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>509.3320743263077</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>265.6132376559275</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>518.1558426053407</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>113.9276748468019</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>108.8793110964921</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>34.4941269548093</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>75.52037537772701</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>167.9367175493084</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.687561341368638</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.9596774193548387</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>218.3315059445939</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>548.0127589491548</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>345.2008547858098</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>240.6836501127377</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>449.7180594588821</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>228.8267373945128</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>508.8482541744045</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>232.69</v>
+      </c>
+      <c r="I139" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="J139" t="n">
+        <v>31.658504</v>
+      </c>
+      <c r="K139" t="n">
+        <v>67</v>
+      </c>
+      <c r="L139" t="n">
+        <v>61</v>
+      </c>
+      <c r="M139" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N139" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O139" t="n">
+        <v>31.63155628119264</v>
+      </c>
+      <c r="P139" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2.506718505758223</v>
+      </c>
+      <c r="R139" t="n">
+        <v>28.4688995215311</v>
+      </c>
+      <c r="S139" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.01075019741764165</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V139" t="n">
+        <v>199.5841458881871</v>
+      </c>
+      <c r="W139" t="n">
+        <v>270.6173540059493</v>
+      </c>
+      <c r="X139" t="n">
+        <v>232.4919386667659</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>214.067557649443</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>250.9163196840888</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>209.2464114832536</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>256.8502067023242</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>31.33317725668595</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>31.45339017533987</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>2.438163613726255</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>28.54016413217114</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.133431055029506</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5121951219512195</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>199.5841458881871</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>270.6173540059493</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>230.2988528366417</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>212.3783502757537</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>248.2193553975297</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>209.7702063714579</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>255.1649407422692</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>365.02</v>
+      </c>
+      <c r="I140" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J140" t="n">
+        <v>60.63455</v>
+      </c>
+      <c r="K140" t="n">
+        <v>34</v>
+      </c>
+      <c r="L140" t="n">
+        <v>62</v>
+      </c>
+      <c r="M140" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="N140" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O140" t="n">
+        <v>75.39179113387321</v>
+      </c>
+      <c r="P140" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>9.334374602497062</v>
+      </c>
+      <c r="R140" t="n">
+        <v>61.99018380011179</v>
+      </c>
+      <c r="S140" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T140" t="n">
+        <v>-1.580956599912486</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="V140" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="W140" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X140" t="n">
+        <v>453.8585826259167</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>397.6656475188844</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>510.051517732949</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>373.180906476673</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>502.6324388886986</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>71.88554773368574</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>69.8280926270555</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>7.935758233607503</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>62.20643220124423</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>82.35048706768551</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>-1.417759639657164</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.04032258064516129</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>432.7509973567881</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>384.977732790471</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>480.5242619231053</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>374.4827218514902</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>495.7499321474667</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>334.69</v>
+      </c>
+      <c r="I141" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J141" t="n">
+        <v>25.509909</v>
+      </c>
+      <c r="K141" t="n">
+        <v>37</v>
+      </c>
+      <c r="L141" t="n">
+        <v>61</v>
+      </c>
+      <c r="M141" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="N141" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O141" t="n">
+        <v>28.99244766582514</v>
+      </c>
+      <c r="P141" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>1.658566781901173</v>
+      </c>
+      <c r="R141" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S141" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T141" t="n">
+        <v>-2.099727731091533</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V141" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="W141" t="n">
+        <v>422.9955833357424</v>
+      </c>
+      <c r="X141" t="n">
+        <v>380.3809133756258</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>358.6205171970824</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>402.1413095541691</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>353.5895115250763</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>409.8998838242946</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>29.51057570671308</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>29.20629058470889</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>2.062330199793983</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>27.20596557896525</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>-1.939876896101666</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.01626016260162602</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>446.7016702785662</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>387.1787532720756</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>360.1209810507785</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>414.2365254933727</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>356.942268396024</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>428.3621670240005</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>550.25</v>
+      </c>
+      <c r="I142" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J142" t="n">
+        <v>20.001818</v>
+      </c>
+      <c r="K142" t="n">
+        <v>55</v>
+      </c>
+      <c r="L142" t="n">
+        <v>62</v>
+      </c>
+      <c r="M142" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N142" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O142" t="n">
+        <v>23.62548864337262</v>
+      </c>
+      <c r="P142" t="n">
+        <v>22.31109064275568</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>2.902325824413882</v>
+      </c>
+      <c r="R142" t="n">
+        <v>20.64236416903409</v>
+      </c>
+      <c r="S142" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T142" t="n">
+        <v>-1.248540261362424</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="V142" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="W142" t="n">
+        <v>806.3861287434895</v>
+      </c>
+      <c r="X142" t="n">
+        <v>649.9371925791808</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>570.0942091495549</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>729.7801760088067</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>567.8714382901279</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>786.1805475110751</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>25.7225230458071</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>27.07066899312207</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>3.135879194302828</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>21.56887251420455</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>29.17356100834187</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>-1.824274690236889</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.008064516129032258</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>707.6266089901533</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>621.3585723548825</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>793.8946456254241</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>593.3596828657671</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>802.5646633394849</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="I143" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J143" t="n">
+        <v>22.227055</v>
+      </c>
+      <c r="K143" t="n">
+        <v>67</v>
+      </c>
+      <c r="L143" t="n">
+        <v>61</v>
+      </c>
+      <c r="M143" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N143" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O143" t="n">
+        <v>24.51417966818127</v>
+      </c>
+      <c r="P143" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.428105567565726</v>
+      </c>
+      <c r="R143" t="n">
+        <v>22.58333297002883</v>
+      </c>
+      <c r="S143" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T143" t="n">
+        <v>-1.601509524313236</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="V143" t="n">
+        <v>352.4099508739653</v>
+      </c>
+      <c r="W143" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X143" t="n">
+        <v>411.3479348320818</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>387.3843234083288</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>435.3115462558346</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>378.9483272370838</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>445.1160013414757</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>34.67140903174453</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>26.16330433758643</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>25.05315860559822</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>3.490632233814055</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>23.21050739722864</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>33.38648659067167</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>-1.127660857381549</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>352.4099508739653</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>581.7862435526732</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>439.0202467847003</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>380.4474379013005</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>497.5930556681001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>389.4723141254966</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>560.2252449914707</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="I144" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>23.809677</v>
+      </c>
+      <c r="K144" t="n">
+        <v>67</v>
+      </c>
+      <c r="L144" t="n">
+        <v>13</v>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr"/>
+      <c r="Y144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>28.52805797173277</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>33.45454521329976</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>13.86518441531513</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>3.751211333693119</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>39.17391207849554</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>-0.3403042347219678</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>88.4369797123716</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>45.45490802489469</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>131.4190513998485</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>11.62875513444867</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>121.4391274433362</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-06-27 01:17:57</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>192.53</v>
+      </c>
+      <c r="I145" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J145" t="n">
+        <v>29.48392</v>
+      </c>
+      <c r="K145" t="n">
+        <v>65</v>
+      </c>
+      <c r="L145" t="n">
+        <v>61</v>
+      </c>
+      <c r="M145" t="n">
+        <v>29.97549854412926</v>
+      </c>
+      <c r="N145" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O145" t="n">
+        <v>37.42337697508546</v>
+      </c>
+      <c r="P145" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>5.155782201865747</v>
+      </c>
+      <c r="R145" t="n">
+        <v>31.4088830173837</v>
+      </c>
+      <c r="S145" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T145" t="n">
+        <v>-1.53991318178886</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>195.740005493164</v>
+      </c>
+      <c r="W145" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X145" t="n">
+        <v>244.3746516473081</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>210.7073938691247</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>278.0419094254914</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>205.1000061035156</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>292.4373910086495</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>29.97549854412926</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>37.25011503981347</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>36.80101978535555</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>4.434024957735758</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>31.79846911116362</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>43.79408108458227</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>-1.751500073598883</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>195.740005493164</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>243.2432512099819</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>214.2890682359674</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>272.1974341839964</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>207.6440032958984</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>285.9753494823222</v>
       </c>
     </row>
   </sheetData>
@@ -21049,12 +22376,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -21083,13 +22410,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>342.19</v>
+        <v>334.69</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.12</v>
       </c>
       <c r="J2" t="n">
-        <v>26.10145</v>
+        <v>25.509909</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -21119,31 +22446,31 @@
         <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.743069798197248</v>
+        <v>-2.099727731091533</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="V2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="W2" t="n">
-        <v>422.673178165517</v>
+        <v>422.9955833357424</v>
       </c>
       <c r="X2" t="n">
-        <v>380.0909888989675</v>
+        <v>380.3809133756258</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.3471783882432</v>
+        <v>358.6205171970824</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.8347994096919</v>
+        <v>402.1413095541691</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.3200073242188</v>
+        <v>353.5895115250763</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.5874601323553</v>
+        <v>409.8998838242946</v>
       </c>
       <c r="AC2" t="n">
         <v>123</v>
@@ -21170,42 +22497,42 @@
         <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.653045524452697</v>
+        <v>-1.939876896101666</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03252032520325204</v>
+        <v>0.01626016260162602</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.3611964445124</v>
+        <v>446.7016702785662</v>
       </c>
       <c r="AO2" t="n">
-        <v>386.8836475150085</v>
+        <v>387.1787532720756</v>
       </c>
       <c r="AP2" t="n">
-        <v>359.8464985957094</v>
+        <v>360.1209810507785</v>
       </c>
       <c r="AQ2" t="n">
-        <v>413.9207964343076</v>
+        <v>414.2365254933727</v>
       </c>
       <c r="AR2" t="n">
-        <v>356.6702087402344</v>
+        <v>356.942268396024</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.0356714698664</v>
+        <v>428.3621670240005</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -21234,13 +22561,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>352.83</v>
+        <v>372.97</v>
       </c>
       <c r="I3" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>21.014292</v>
+        <v>22.227055</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -21270,31 +22597,31 @@
         <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.450720554326383</v>
+        <v>-1.601509524313236</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.04918032786885246</v>
       </c>
       <c r="V3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.4099508739653</v>
       </c>
       <c r="W3" t="n">
-        <v>460.2458699725923</v>
+        <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>411.5930766287635</v>
+        <v>411.3479348320818</v>
       </c>
       <c r="Y3" t="n">
-        <v>387.615184149335</v>
+        <v>387.3843234083288</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.5709691081921</v>
+        <v>435.3115462558346</v>
       </c>
       <c r="AA3" t="n">
-        <v>379.1741605667841</v>
+        <v>378.9483272370838</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.3812671348853</v>
+        <v>445.1160013414757</v>
       </c>
       <c r="AC3" t="n">
         <v>123</v>
@@ -21321,42 +22648,42 @@
         <v>33.38648659067167</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.475094479363223</v>
+        <v>-1.127660857381549</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.008130081300813009</v>
+        <v>0.02439024390243903</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.4099508739653</v>
       </c>
       <c r="AN3" t="n">
-        <v>582.1329576429906</v>
+        <v>581.7862435526732</v>
       </c>
       <c r="AO3" t="n">
-        <v>439.2818798280761</v>
+        <v>439.0202467847003</v>
       </c>
       <c r="AP3" t="n">
-        <v>380.6741646223381</v>
+        <v>380.4474379013005</v>
       </c>
       <c r="AQ3" t="n">
-        <v>497.8895950338141</v>
+        <v>497.5930556681001</v>
       </c>
       <c r="AR3" t="n">
-        <v>389.7044191994688</v>
+        <v>389.4723141254966</v>
       </c>
       <c r="AS3" t="n">
-        <v>560.5591098573774</v>
+        <v>560.2252449914707</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -21385,19 +22712,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>542.87</v>
+        <v>550.25</v>
       </c>
       <c r="I4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="J4" t="n">
-        <v>19.72638</v>
+        <v>20.001818</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
         <v>19.74072709517046</v>
@@ -21406,49 +22733,49 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.68477385213134</v>
+        <v>23.62548864337262</v>
       </c>
       <c r="P4" t="n">
-        <v>22.33563565340909</v>
+        <v>22.31109064275568</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.888311142021387</v>
+        <v>2.902325824413882</v>
       </c>
       <c r="R4" t="n">
-        <v>20.67018155184659</v>
+        <v>20.64236416903409</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57982234378326</v>
+        <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.370487339311045</v>
+        <v>-1.248540261362424</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="V4" t="n">
-        <v>543.2648096590909</v>
+        <v>543.0674023881393</v>
       </c>
       <c r="W4" t="n">
-        <v>806.6792534722222</v>
+        <v>806.3861287434895</v>
       </c>
       <c r="X4" t="n">
-        <v>651.8049764106544</v>
+        <v>649.9371925791808</v>
       </c>
       <c r="Y4" t="n">
-        <v>572.3186537822259</v>
+        <v>570.0942091495549</v>
       </c>
       <c r="Z4" t="n">
-        <v>731.2912990390829</v>
+        <v>729.7801760088067</v>
       </c>
       <c r="AA4" t="n">
-        <v>568.8433963068181</v>
+        <v>567.8714382901279</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.5167109009152</v>
+        <v>786.1805475110751</v>
       </c>
       <c r="AC4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD4" t="n">
         <v>19.74072709517046</v>
@@ -21457,57 +22784,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.76897371358528</v>
+        <v>25.7225230458071</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.12856534695615</v>
+        <v>27.07066899312207</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.105575517525062</v>
+        <v>3.135879194302828</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.61127219460228</v>
+        <v>21.56887251420455</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.17387104963602</v>
+        <v>29.17356100834187</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.94572428829579</v>
+        <v>-1.824274690236889</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.008064516129032258</v>
       </c>
       <c r="AM4" t="n">
-        <v>543.2648096590909</v>
+        <v>543.0674023881393</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.9762082934226</v>
+        <v>864.6619000781998</v>
       </c>
       <c r="AO4" t="n">
-        <v>709.1621565978669</v>
+        <v>707.6266089901533</v>
       </c>
       <c r="AP4" t="n">
-        <v>623.6967183555772</v>
+        <v>621.3585723548825</v>
       </c>
       <c r="AQ4" t="n">
-        <v>794.6275948401566</v>
+        <v>793.8946456254241</v>
       </c>
       <c r="AR4" t="n">
-        <v>594.7422107954546</v>
+        <v>593.3596828657671</v>
       </c>
       <c r="AS4" t="n">
-        <v>802.8649312859832</v>
+        <v>802.5646633394849</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -21536,13 +22863,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>227.01</v>
+        <v>232.69</v>
       </c>
       <c r="I5" t="n">
-        <v>7.17</v>
+        <v>7.35</v>
       </c>
       <c r="J5" t="n">
-        <v>31.661087</v>
+        <v>31.658504</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -21572,31 +22899,31 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0117806282354875</v>
+        <v>0.01075019741764165</v>
       </c>
       <c r="U5" t="n">
         <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>194.6963708868437</v>
+        <v>199.5841458881871</v>
       </c>
       <c r="W5" t="n">
-        <v>263.989990234375</v>
+        <v>270.6173540059493</v>
       </c>
       <c r="X5" t="n">
-        <v>226.7982585361513</v>
+        <v>232.4919386667659</v>
       </c>
       <c r="Y5" t="n">
-        <v>208.8250868498648</v>
+        <v>214.067557649443</v>
       </c>
       <c r="Z5" t="n">
-        <v>244.7714302224377</v>
+        <v>250.9163196840888</v>
       </c>
       <c r="AA5" t="n">
-        <v>204.122009569378</v>
+        <v>209.2464114832536</v>
       </c>
       <c r="AB5" t="n">
-        <v>250.5599975585938</v>
+        <v>256.8502067023242</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -21623,42 +22950,42 @@
         <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1344904589125991</v>
+        <v>0.133431055029506</v>
       </c>
       <c r="AL5" t="n">
         <v>0.5121951219512195</v>
       </c>
       <c r="AM5" t="n">
-        <v>194.6963708868437</v>
+        <v>199.5841458881871</v>
       </c>
       <c r="AN5" t="n">
-        <v>263.989990234375</v>
+        <v>270.6173540059493</v>
       </c>
       <c r="AO5" t="n">
-        <v>224.6588809304383</v>
+        <v>230.2988528366417</v>
       </c>
       <c r="AP5" t="n">
-        <v>207.177247820021</v>
+        <v>212.3783502757537</v>
       </c>
       <c r="AQ5" t="n">
-        <v>242.1405140408555</v>
+        <v>248.2193553975297</v>
       </c>
       <c r="AR5" t="n">
-        <v>204.6329768276671</v>
+        <v>209.7702063714579</v>
       </c>
       <c r="AS5" t="n">
-        <v>248.9160034179687</v>
+        <v>255.1649407422692</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -21687,13 +23014,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>275.15</v>
+        <v>283.78</v>
       </c>
       <c r="I6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>33.351513</v>
+        <v>34.35593</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -21723,31 +23050,31 @@
         <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.976735285181736</v>
+        <v>-0.396137173156098</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2131147540983606</v>
+        <v>0.3770491803278688</v>
       </c>
       <c r="V6" t="n">
-        <v>257.5566506687599</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="W6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>289.0901904819685</v>
+        <v>289.4406028340679</v>
       </c>
       <c r="Y6" t="n">
-        <v>274.8179424701904</v>
+        <v>275.15105512773</v>
       </c>
       <c r="Z6" t="n">
-        <v>303.3624384937467</v>
+        <v>303.7301505404057</v>
       </c>
       <c r="AA6" t="n">
-        <v>270.3284657152393</v>
+        <v>270.6561365827729</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.446133223342</v>
+        <v>308.8200073242188</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -21774,42 +23101,42 @@
         <v>36.60311899573401</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.6187189752367825</v>
+        <v>-0.02037049825081136</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.5566506687599</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="AN6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="AO6" t="n">
-        <v>283.7185305409001</v>
+        <v>284.0624317900406</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.8696772911336</v>
+        <v>270.1967920514865</v>
       </c>
       <c r="AQ6" t="n">
-        <v>297.5673837906667</v>
+        <v>297.9280715285947</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.1257529922678</v>
+        <v>265.4471175413494</v>
       </c>
       <c r="AS6" t="n">
-        <v>301.9757317148055</v>
+        <v>302.3417629047629</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -21838,13 +23165,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>195.74</v>
+        <v>192.53</v>
       </c>
       <c r="I7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>29.929665</v>
+        <v>29.48392</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -21874,31 +23201,31 @@
         <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.453457823019304</v>
+        <v>-1.53991318178886</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>196.0397604786053</v>
+        <v>195.740005493164</v>
       </c>
       <c r="W7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>244.7488854170589</v>
+        <v>244.3746516473081</v>
       </c>
       <c r="Y7" t="n">
-        <v>211.0300698168569</v>
+        <v>210.7073938691247</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.4677010172609</v>
+        <v>278.0419094254914</v>
       </c>
       <c r="AA7" t="n">
-        <v>205.4140949336894</v>
+        <v>205.1000061035156</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.8852277483259</v>
+        <v>292.4373910086495</v>
       </c>
       <c r="AC7" t="n">
         <v>84</v>
@@ -21925,42 +23252,42 @@
         <v>43.79408108458227</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.650971771604927</v>
+        <v>-1.751500073598883</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>196.0397604786053</v>
+        <v>195.740005493164</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>243.6157523603801</v>
+        <v>243.2432512099819</v>
       </c>
       <c r="AP7" t="n">
-        <v>214.6172291367882</v>
+        <v>214.2890682359674</v>
       </c>
       <c r="AQ7" t="n">
-        <v>272.6142755839719</v>
+        <v>272.1974341839964</v>
       </c>
       <c r="AR7" t="n">
-        <v>207.96198798701</v>
+        <v>207.6440032958984</v>
       </c>
       <c r="AS7" t="n">
-        <v>286.413290293168</v>
+        <v>285.9753494823222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -21989,19 +23316,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>532.5700000000001</v>
+        <v>521.58</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="J8" t="n">
-        <v>178.71477</v>
+        <v>172.13863</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
         <v>73.97735595703125</v>
@@ -22010,49 +23337,49 @@
         <v>180.8622966828894</v>
       </c>
       <c r="O8" t="n">
-        <v>135.8073374033935</v>
+        <v>136.375119730255</v>
       </c>
       <c r="P8" t="n">
-        <v>139.0491823290215</v>
+        <v>142.5573780497567</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.66527157075409</v>
+        <v>31.72127443684333</v>
       </c>
       <c r="R8" t="n">
-        <v>87.479248046875</v>
+        <v>87.66113453991008</v>
       </c>
       <c r="S8" t="n">
-        <v>170.9967141073258</v>
+        <v>171.0085289126537</v>
       </c>
       <c r="T8" t="n">
-        <v>1.355031252478996</v>
+        <v>1.127429805537913</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9193548387096774</v>
       </c>
       <c r="V8" t="n">
-        <v>220.4525207519531</v>
+        <v>224.1513885498047</v>
       </c>
       <c r="W8" t="n">
-        <v>538.9696441150103</v>
+        <v>548.0127589491548</v>
       </c>
       <c r="X8" t="n">
-        <v>404.7058654621127</v>
+        <v>413.2166127826725</v>
       </c>
       <c r="Y8" t="n">
-        <v>310.3433561812656</v>
+        <v>317.1011512390372</v>
       </c>
       <c r="Z8" t="n">
-        <v>499.06837474296</v>
+        <v>509.3320743263077</v>
       </c>
       <c r="AA8" t="n">
-        <v>260.6881591796875</v>
+        <v>265.6132376559275</v>
       </c>
       <c r="AB8" t="n">
-        <v>509.570208039831</v>
+        <v>518.1558426053407</v>
       </c>
       <c r="AC8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -22061,57 +23388,57 @@
         <v>180.8622966828894</v>
       </c>
       <c r="AF8" t="n">
-        <v>113.4635921897125</v>
+        <v>113.9276748468019</v>
       </c>
       <c r="AG8" t="n">
-        <v>108.8522173501</v>
+        <v>108.8793110964921</v>
       </c>
       <c r="AH8" t="n">
-        <v>34.24430610745814</v>
+        <v>34.4941269548093</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51924334831958</v>
+        <v>75.52037537772701</v>
       </c>
       <c r="AJ8" t="n">
-        <v>167.6334448642418</v>
+        <v>167.9367175493084</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.905460651050432</v>
+        <v>1.687561341368638</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.983739837398374</v>
+        <v>0.9596774193548387</v>
       </c>
       <c r="AM8" t="n">
-        <v>214.728675813495</v>
+        <v>218.3315059445939</v>
       </c>
       <c r="AN8" t="n">
-        <v>538.9696441150103</v>
+        <v>548.0127589491548</v>
       </c>
       <c r="AO8" t="n">
-        <v>338.1215047253433</v>
+        <v>345.2008547858098</v>
       </c>
       <c r="AP8" t="n">
-        <v>236.073472525118</v>
+        <v>240.6836501127377</v>
       </c>
       <c r="AQ8" t="n">
-        <v>440.1695369255685</v>
+        <v>449.7180594588821</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.0473451779923</v>
+        <v>228.8267373945128</v>
       </c>
       <c r="AS8" t="n">
-        <v>499.5476656954406</v>
+        <v>508.8482541744045</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -22140,19 +23467,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>378.91</v>
+        <v>365.02</v>
       </c>
       <c r="I9" t="n">
         <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>62.94186</v>
+        <v>60.63455</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
         <v>57.19493248774063</v>
@@ -22161,25 +23488,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.63205919994044</v>
+        <v>75.39179113387321</v>
       </c>
       <c r="P9" t="n">
-        <v>79.03509009883652</v>
+        <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.216500957717233</v>
+        <v>9.334374602497062</v>
       </c>
       <c r="R9" t="n">
-        <v>62.68053102413946</v>
+        <v>61.99018380011179</v>
       </c>
       <c r="S9" t="n">
-        <v>83.514618455318</v>
+        <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.376899894890651</v>
+        <v>-1.580956599912486</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1147540983606557</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="V9" t="n">
         <v>344.3134935761985</v>
@@ -22188,22 +23515,22 @@
         <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>455.3049963836414</v>
+        <v>453.8585826259167</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.8216606181837</v>
+        <v>397.6656475188844</v>
       </c>
       <c r="Z9" t="n">
-        <v>510.7883321490992</v>
+        <v>510.051517732949</v>
       </c>
       <c r="AA9" t="n">
-        <v>377.3367967653195</v>
+        <v>373.180906476673</v>
       </c>
       <c r="AB9" t="n">
-        <v>502.7580031010143</v>
+        <v>502.6324388886986</v>
       </c>
       <c r="AC9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -22212,25 +23539,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.97619902335984</v>
+        <v>71.88554773368574</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.86163317282495</v>
+        <v>69.8280926270555</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.903487573773657</v>
+        <v>7.935758233607503</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.40428783275464</v>
+        <v>62.20643220124423</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.36296239187379</v>
+        <v>82.35048706768551</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.143082587152881</v>
+        <v>-1.417759639657164</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1382113821138211</v>
+        <v>0.04032258064516129</v>
       </c>
       <c r="AM9" t="n">
         <v>344.3134935761985</v>
@@ -22239,30 +23566,30 @@
         <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>433.2967181206262</v>
+        <v>432.7509973567881</v>
       </c>
       <c r="AP9" t="n">
-        <v>385.7177229265088</v>
+        <v>384.977732790471</v>
       </c>
       <c r="AQ9" t="n">
-        <v>480.8757133147436</v>
+        <v>480.5242619231053</v>
       </c>
       <c r="AR9" t="n">
-        <v>375.6738127531829</v>
+        <v>374.4827218514902</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.8250335990802</v>
+        <v>495.7499321474667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-26 03:34:29</t>
+          <t>2026-06-27 01:17:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -22291,13 +23618,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>70.90000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>22.87097</v>
+        <v>23.809677</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
@@ -22346,7 +23673,7 @@
         <v>39.17391207849554</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.4080066879950111</v>
+        <v>-0.3403042347219678</v>
       </c>
       <c r="AL10" t="n">
         <v>0.2266666666666667</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS145"/>
+  <dimension ref="A1:AS154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19877,7 +19877,7 @@
         <v>204.122009569378</v>
       </c>
       <c r="AB130" t="n">
-        <v>250.5599975585938</v>
+        <v>250.5599975585937</v>
       </c>
       <c r="AC130" t="n">
         <v>123</v>
@@ -20920,7 +20920,7 @@
         <v>34.40435746680161</v>
       </c>
       <c r="AH137" t="n">
-        <v>1.678648878759581</v>
+        <v>1.678648878759582</v>
       </c>
       <c r="AI137" t="n">
         <v>32.13645490815368</v>
@@ -20929,7 +20929,7 @@
         <v>36.60311899573401</v>
       </c>
       <c r="AK137" t="n">
-        <v>-0.02037049825081136</v>
+        <v>-0.0203704982508113</v>
       </c>
       <c r="AL137" t="n">
         <v>0.4878048780487805</v>
@@ -21035,7 +21035,7 @@
         <v>0.9193548387096774</v>
       </c>
       <c r="V138" t="n">
-        <v>224.1513885498047</v>
+        <v>224.1513885498046</v>
       </c>
       <c r="W138" t="n">
         <v>548.0127589491548</v>
@@ -21171,7 +21171,7 @@
         <v>31.73325461063659</v>
       </c>
       <c r="Q139" t="n">
-        <v>2.506718505758223</v>
+        <v>2.506718505758222</v>
       </c>
       <c r="R139" t="n">
         <v>28.4688995215311</v>
@@ -21180,7 +21180,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T139" t="n">
-        <v>0.01075019741764165</v>
+        <v>0.0107501974176416</v>
       </c>
       <c r="U139" t="n">
         <v>0.4426229508196721</v>
@@ -21216,10 +21216,10 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF139" t="n">
-        <v>31.33317725668595</v>
+        <v>31.33317725668596</v>
       </c>
       <c r="AG139" t="n">
-        <v>31.45339017533987</v>
+        <v>31.45339017533986</v>
       </c>
       <c r="AH139" t="n">
         <v>2.438163613726255</v>
@@ -21313,7 +21313,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="N140" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O140" t="n">
         <v>75.39179113387321</v>
@@ -21331,10 +21331,10 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T140" t="n">
-        <v>-1.580956599912486</v>
+        <v>-1.580956599912485</v>
       </c>
       <c r="U140" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.032258064516129</v>
       </c>
       <c r="V140" t="n">
         <v>344.3134935761985</v>
@@ -21364,7 +21364,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE140" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF140" t="n">
         <v>71.88554773368574</v>
@@ -21385,7 +21385,7 @@
         <v>-1.417759639657164</v>
       </c>
       <c r="AL140" t="n">
-        <v>0.04032258064516129</v>
+        <v>0.0403225806451612</v>
       </c>
       <c r="AM140" t="n">
         <v>344.3134935761985</v>
@@ -21485,7 +21485,7 @@
         <v>-2.099727731091533</v>
       </c>
       <c r="U141" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V141" t="n">
         <v>331.5075848462072</v>
@@ -21536,7 +21536,7 @@
         <v>-1.939876896101666</v>
       </c>
       <c r="AL141" t="n">
-        <v>0.01626016260162602</v>
+        <v>0.016260162601626</v>
       </c>
       <c r="AM141" t="n">
         <v>331.5075848462072</v>
@@ -21636,7 +21636,7 @@
         <v>-1.248540261362424</v>
       </c>
       <c r="U142" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="V142" t="n">
         <v>543.0674023881393</v>
@@ -21678,7 +21678,7 @@
         <v>3.135879194302828</v>
       </c>
       <c r="AI142" t="n">
-        <v>21.56887251420455</v>
+        <v>21.56887251420454</v>
       </c>
       <c r="AJ142" t="n">
         <v>29.17356100834187</v>
@@ -21687,7 +21687,7 @@
         <v>-1.824274690236889</v>
       </c>
       <c r="AL142" t="n">
-        <v>0.008064516129032258</v>
+        <v>0.008064516129032201</v>
       </c>
       <c r="AM142" t="n">
         <v>543.0674023881393</v>
@@ -21772,7 +21772,7 @@
         <v>24.51417966818127</v>
       </c>
       <c r="P143" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q143" t="n">
         <v>1.428105567565726</v>
@@ -21781,13 +21781,13 @@
         <v>22.58333297002883</v>
       </c>
       <c r="S143" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T143" t="n">
         <v>-1.601509524313236</v>
       </c>
       <c r="U143" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="V143" t="n">
         <v>352.4099508739653</v>
@@ -21838,7 +21838,7 @@
         <v>-1.127660857381549</v>
       </c>
       <c r="AL143" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.024390243902439</v>
       </c>
       <c r="AM143" t="n">
         <v>352.4099508739653</v>
@@ -21933,7 +21933,7 @@
         <v>75</v>
       </c>
       <c r="AD144" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE144" t="n">
         <v>42.60474344487245</v>
@@ -21948,7 +21948,7 @@
         <v>13.86518441531513</v>
       </c>
       <c r="AI144" t="n">
-        <v>3.751211333693119</v>
+        <v>3.75121133369312</v>
       </c>
       <c r="AJ144" t="n">
         <v>39.17391207849554</v>
@@ -21957,7 +21957,7 @@
         <v>-0.3403042347219678</v>
       </c>
       <c r="AL144" t="n">
-        <v>0.2266666666666667</v>
+        <v>0.2266666666666666</v>
       </c>
       <c r="AM144" t="n">
         <v>10.81762752038992</v>
@@ -22033,7 +22033,7 @@
         <v>61</v>
       </c>
       <c r="M145" t="n">
-        <v>29.97549854412926</v>
+        <v>29.97549854412925</v>
       </c>
       <c r="N145" t="n">
         <v>48.11020520268654</v>
@@ -22069,7 +22069,7 @@
         <v>244.3746516473081</v>
       </c>
       <c r="Y145" t="n">
-        <v>210.7073938691247</v>
+        <v>210.7073938691248</v>
       </c>
       <c r="Z145" t="n">
         <v>278.0419094254914</v>
@@ -22084,7 +22084,7 @@
         <v>84</v>
       </c>
       <c r="AD145" t="n">
-        <v>29.97549854412926</v>
+        <v>29.97549854412925</v>
       </c>
       <c r="AE145" t="n">
         <v>48.11020520268654</v>
@@ -22117,7 +22117,7 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO145" t="n">
-        <v>243.2432512099819</v>
+        <v>243.243251209982</v>
       </c>
       <c r="AP145" t="n">
         <v>214.2890682359674</v>
@@ -22130,6 +22130,1333 @@
       </c>
       <c r="AS145" t="n">
         <v>285.9753494823222</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>281.74</v>
+      </c>
+      <c r="I146" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.150303</v>
+      </c>
+      <c r="K146" t="n">
+        <v>67</v>
+      </c>
+      <c r="L146" t="n">
+        <v>61</v>
+      </c>
+      <c r="M146" t="n">
+        <v>32.08860759493671</v>
+      </c>
+      <c r="N146" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O146" t="n">
+        <v>35.12517924510622</v>
+      </c>
+      <c r="P146" t="n">
+        <v>35.24576330300393</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>1.619487764315308</v>
+      </c>
+      <c r="R146" t="n">
+        <v>32.81012812747231</v>
+      </c>
+      <c r="S146" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T146" t="n">
+        <v>-0.6019657984377408</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0.2786885245901639</v>
+      </c>
+      <c r="V146" t="n">
+        <v>264.7310126582279</v>
+      </c>
+      <c r="W146" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X146" t="n">
+        <v>289.7827287721263</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>276.421954716525</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>303.1435028277276</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>270.6835570516466</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>308.446133223342</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>34.33364711707023</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>34.35201704701232</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.64900930047169</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>32.13088525699663</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>36.49019476865163</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>-0.1111844044892789</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>0.4344262295081967</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>283.2525887158294</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>269.6482619869379</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>296.8569154447208</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>265.0798033702222</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>301.044106841376</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>539.49</v>
+      </c>
+      <c r="I147" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J147" t="n">
+        <v>178.63907</v>
+      </c>
+      <c r="K147" t="n">
+        <v>63</v>
+      </c>
+      <c r="L147" t="n">
+        <v>61</v>
+      </c>
+      <c r="M147" t="n">
+        <v>79.32453083542158</v>
+      </c>
+      <c r="N147" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="O147" t="n">
+        <v>139.0392786288205</v>
+      </c>
+      <c r="P147" t="n">
+        <v>146.7475365810707</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>30.31548355458364</v>
+      </c>
+      <c r="R147" t="n">
+        <v>92.4679219947671</v>
+      </c>
+      <c r="S147" t="n">
+        <v>171.5409876088627</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.306256299685249</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0.9672131147540983</v>
+      </c>
+      <c r="V147" t="n">
+        <v>239.5600831229732</v>
+      </c>
+      <c r="W147" t="n">
+        <v>546.2041359823259</v>
+      </c>
+      <c r="X147" t="n">
+        <v>419.8986214590381</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>328.3458611241954</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>511.4513817938806</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>279.2531244241966</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>518.0537825787654</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>180.8622966828894</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>114.6403726833946</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>110.1157653507928</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>35.21597796876289</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>75.51811131891215</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>169.0944183849898</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.817319893071639</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>0.9836065573770492</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>217.6109399183741</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>546.2041359823259</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>346.2139255038518</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>239.8616720381879</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>452.5661789695157</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>228.0646961831147</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>510.665143522669</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>240.14</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="J148" t="n">
+        <v>31.638998</v>
+      </c>
+      <c r="K148" t="n">
+        <v>67</v>
+      </c>
+      <c r="L148" t="n">
+        <v>61</v>
+      </c>
+      <c r="M148" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N148" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O148" t="n">
+        <v>31.62310863171025</v>
+      </c>
+      <c r="P148" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>2.517313189294332</v>
+      </c>
+      <c r="R148" t="n">
+        <v>28.4688995215311</v>
+      </c>
+      <c r="S148" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0.006312034735022313</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V148" t="n">
+        <v>206.1011792233116</v>
+      </c>
+      <c r="W148" t="n">
+        <v>279.453839034715</v>
+      </c>
+      <c r="X148" t="n">
+        <v>240.0193945146808</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>220.9129874079368</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>259.1258016214247</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>216.0789473684211</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>265.237152227298</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>31.248493848305</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>30.93963562410059</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>2.468718556387847</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>28.4754785054038</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>34.72357096864921</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>0.1581809115845018</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>0.5327868852459017</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>206.1011792233116</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>279.453839034715</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>237.1760683086349</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>218.4384944656511</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>255.9136421516187</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>216.1288818560149</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>263.5519036520475</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>372.45</v>
+      </c>
+      <c r="I149" t="n">
+        <v>6</v>
+      </c>
+      <c r="J149" t="n">
+        <v>62.075</v>
+      </c>
+      <c r="K149" t="n">
+        <v>34</v>
+      </c>
+      <c r="L149" t="n">
+        <v>61</v>
+      </c>
+      <c r="M149" t="n">
+        <v>60.73543910377236</v>
+      </c>
+      <c r="N149" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O149" t="n">
+        <v>75.7169589904405</v>
+      </c>
+      <c r="P149" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>9.065253611492661</v>
+      </c>
+      <c r="R149" t="n">
+        <v>62.68053102413946</v>
+      </c>
+      <c r="S149" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T149" t="n">
+        <v>-1.504862365146147</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="V149" t="n">
+        <v>364.4126346226341</v>
+      </c>
+      <c r="W149" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="X149" t="n">
+        <v>454.301753942643</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>399.910232273687</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>508.693275611599</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>376.0831861448368</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>501.087710731908</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>71.77566214941169</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>69.76519890551299</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>8.048642351971177</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>62.05497221175226</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>82.37543771606209</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>-1.205254467175562</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>0.1065573770491803</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>430.6539728964701</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>382.3621187846431</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>478.9458270082972</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>372.3298332705136</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>494.2526262963726</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="I150" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>26.815266</v>
+      </c>
+      <c r="K150" t="n">
+        <v>37</v>
+      </c>
+      <c r="L150" t="n">
+        <v>61</v>
+      </c>
+      <c r="M150" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N150" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O150" t="n">
+        <v>29.00097708905417</v>
+      </c>
+      <c r="P150" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>1.642969091778331</v>
+      </c>
+      <c r="R150" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S150" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T150" t="n">
+        <v>-1.330342183545509</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="V150" t="n">
+        <v>334.434708770589</v>
+      </c>
+      <c r="W150" t="n">
+        <v>422.3507729952915</v>
+      </c>
+      <c r="X150" t="n">
+        <v>379.9127998666096</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>358.3899047643135</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>401.4356949689057</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>353.0505031233612</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>409.2750364404161</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>29.41853137011541</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>29.12303349356426</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>2.101223953493667</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>26.96842149957094</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>32.65449124757065</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>-1.238928085598398</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>446.0207226104586</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>385.3827609485118</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>357.8567271577448</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>412.9087947392788</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>353.2863216443793</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>427.7738353431754</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>562.6</v>
+      </c>
+      <c r="I151" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J151" t="n">
+        <v>20.450745</v>
+      </c>
+      <c r="K151" t="n">
+        <v>55</v>
+      </c>
+      <c r="L151" t="n">
+        <v>61</v>
+      </c>
+      <c r="M151" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N151" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O151" t="n">
+        <v>23.57455339260127</v>
+      </c>
+      <c r="P151" t="n">
+        <v>22.26691006747159</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>2.951120816087783</v>
+      </c>
+      <c r="R151" t="n">
+        <v>20.61745383522727</v>
+      </c>
+      <c r="S151" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T151" t="n">
+        <v>-1.058515929124994</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0.06557377049180328</v>
+      </c>
+      <c r="V151" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="W151" t="n">
+        <v>806.3861287434895</v>
+      </c>
+      <c r="X151" t="n">
+        <v>648.535963830461</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>567.350630179886</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>729.7212974810359</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>567.1861550071023</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>786.2309126774775</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>25.59142081717489</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>26.78430634084441</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>3.144888871598961</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>21.31458229758523</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>28.88378002025463</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>-1.634612867754912</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>704.0199866804812</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>617.5040938227938</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>790.5358795381687</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>586.3641590065697</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>794.5927883572048</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>368.57</v>
+      </c>
+      <c r="I152" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="J152" t="n">
+        <v>21.92564</v>
+      </c>
+      <c r="K152" t="n">
+        <v>67</v>
+      </c>
+      <c r="L152" t="n">
+        <v>61</v>
+      </c>
+      <c r="M152" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N152" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O152" t="n">
+        <v>24.49024788891508</v>
+      </c>
+      <c r="P152" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>1.46170242334417</v>
+      </c>
+      <c r="R152" t="n">
+        <v>22.55416688464937</v>
+      </c>
+      <c r="S152" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T152" t="n">
+        <v>-1.754534882036809</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="V152" t="n">
+        <v>353.0400044214157</v>
+      </c>
+      <c r="W152" t="n">
+        <v>460.7941080547514</v>
+      </c>
+      <c r="X152" t="n">
+        <v>411.6810670126625</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>387.109849276247</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>436.252284749078</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>379.1355453309558</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>445.9117987217047</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>122</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>34.38620207828614</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>25.88945130204413</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>25.00156404973567</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>3.276265109396637</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>23.15447226996121</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>32.65348540261324</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>-1.209856702583542</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>0.02459016393442623</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>353.0400044214157</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>578.03205693599</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>435.2016763873617</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>380.1276598984043</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>490.2756928763192</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>389.2266788580479</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>548.9050896179285</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>73.78</v>
+      </c>
+      <c r="I153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>23.800001</v>
+      </c>
+      <c r="K153" t="n">
+        <v>67</v>
+      </c>
+      <c r="L153" t="n">
+        <v>11</v>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>29.55330344716235</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>33.84980213029581</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>13.18021137026943</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>3.740434383688714</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>39.19169882069462</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>-0.4365106359477703</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>91.61524068620328</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>50.75658543836802</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>132.4738959340385</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>11.59534658943501</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>121.4942663441533</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-06-30 03:43:40</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>194.97</v>
+      </c>
+      <c r="I154" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J154" t="n">
+        <v>29.85758</v>
+      </c>
+      <c r="K154" t="n">
+        <v>65</v>
+      </c>
+      <c r="L154" t="n">
+        <v>61</v>
+      </c>
+      <c r="M154" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N154" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O154" t="n">
+        <v>37.2601229158231</v>
+      </c>
+      <c r="P154" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>5.317296510649731</v>
+      </c>
+      <c r="R154" t="n">
+        <v>31.33996843744017</v>
+      </c>
+      <c r="S154" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T154" t="n">
+        <v>-1.392162897253697</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="V154" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W154" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X154" t="n">
+        <v>243.3086026403249</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>208.5866564257821</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>278.0305488548676</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>204.6499938964843</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>292.4373910086495</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>86</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>37.07385074546544</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>36.76530643385284</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>4.529795896678524</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>31.41577400803383</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>43.71122399154974</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>-1.593067526675269</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>0.01162790697674419</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>242.0922453678893</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>212.5126781625786</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>271.6718125732</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>205.1450042724609</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>285.4342926648198</v>
       </c>
     </row>
   </sheetData>
@@ -22376,12 +23703,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -22410,13 +23737,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>334.69</v>
+        <v>351.28</v>
       </c>
       <c r="I2" t="n">
-        <v>13.12</v>
+        <v>13.1</v>
       </c>
       <c r="J2" t="n">
-        <v>25.509909</v>
+        <v>26.815266</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -22425,19 +23752,19 @@
         <v>61</v>
       </c>
       <c r="M2" t="n">
-        <v>25.26734640596091</v>
+        <v>25.52936708172435</v>
       </c>
       <c r="N2" t="n">
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.99244766582514</v>
+        <v>29.00097708905417</v>
       </c>
       <c r="P2" t="n">
         <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.658566781901173</v>
+        <v>1.642969091778331</v>
       </c>
       <c r="R2" t="n">
         <v>26.95042008575277</v>
@@ -22446,34 +23773,34 @@
         <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.099727731091533</v>
+        <v>-1.330342183545509</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="V2" t="n">
-        <v>331.5075848462072</v>
+        <v>334.434708770589</v>
       </c>
       <c r="W2" t="n">
-        <v>422.9955833357424</v>
+        <v>422.3507729952915</v>
       </c>
       <c r="X2" t="n">
-        <v>380.3809133756258</v>
+        <v>379.9127998666096</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.6205171970824</v>
+        <v>358.3899047643135</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.1413095541691</v>
+        <v>401.4356949689057</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.5895115250763</v>
+        <v>353.0505031233612</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.8998838242946</v>
+        <v>409.2750364404161</v>
       </c>
       <c r="AC2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -22482,57 +23809,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.51057570671308</v>
+        <v>29.41853137011541</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.20629058470889</v>
+        <v>29.12303349356426</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.062330199793983</v>
+        <v>2.101223953493667</v>
       </c>
       <c r="AI2" t="n">
-        <v>27.20596557896525</v>
+        <v>26.96842149957094</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.64955541341467</v>
+        <v>32.65449124757065</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.939876896101666</v>
+        <v>-1.238928085598398</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01626016260162602</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.002237918088</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.7016702785662</v>
+        <v>446.0207226104586</v>
       </c>
       <c r="AO2" t="n">
-        <v>387.1787532720756</v>
+        <v>385.3827609485118</v>
       </c>
       <c r="AP2" t="n">
-        <v>360.1209810507785</v>
+        <v>357.8567271577448</v>
       </c>
       <c r="AQ2" t="n">
-        <v>414.2365254933727</v>
+        <v>412.9087947392788</v>
       </c>
       <c r="AR2" t="n">
-        <v>356.942268396024</v>
+        <v>353.2863216443793</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.3621670240005</v>
+        <v>427.7738353431754</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -22561,13 +23888,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>372.97</v>
+        <v>368.57</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.81</v>
       </c>
       <c r="J3" t="n">
-        <v>22.227055</v>
+        <v>21.92564</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -22582,108 +23909,108 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.51417966818127</v>
+        <v>24.49024788891508</v>
       </c>
       <c r="P3" t="n">
         <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.428105567565726</v>
+        <v>1.46170242334417</v>
       </c>
       <c r="R3" t="n">
-        <v>22.58333297002883</v>
+        <v>22.55416688464937</v>
       </c>
       <c r="S3" t="n">
         <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.601509524313236</v>
+        <v>-1.754534882036809</v>
       </c>
       <c r="U3" t="n">
         <v>0.04918032786885246</v>
       </c>
       <c r="V3" t="n">
-        <v>352.4099508739653</v>
+        <v>353.0400044214157</v>
       </c>
       <c r="W3" t="n">
-        <v>459.9717509315128</v>
+        <v>460.7941080547514</v>
       </c>
       <c r="X3" t="n">
-        <v>411.3479348320818</v>
+        <v>411.6810670126625</v>
       </c>
       <c r="Y3" t="n">
-        <v>387.3843234083288</v>
+        <v>387.109849276247</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.3115462558346</v>
+        <v>436.252284749078</v>
       </c>
       <c r="AA3" t="n">
-        <v>378.9483272370838</v>
+        <v>379.1355453309558</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.1160013414757</v>
+        <v>445.9117987217047</v>
       </c>
       <c r="AC3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AD3" t="n">
         <v>21.00178491501581</v>
       </c>
       <c r="AE3" t="n">
-        <v>34.67140903174453</v>
+        <v>34.38620207828614</v>
       </c>
       <c r="AF3" t="n">
-        <v>26.16330433758643</v>
+        <v>25.88945130204413</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.05315860559822</v>
+        <v>25.00156404973567</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.490632233814055</v>
+        <v>3.276265109396637</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.21050739722864</v>
+        <v>23.15447226996121</v>
       </c>
       <c r="AJ3" t="n">
-        <v>33.38648659067167</v>
+        <v>32.65348540261324</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.127660857381549</v>
+        <v>-1.209856702583542</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02459016393442623</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.4099508739653</v>
+        <v>353.0400044214157</v>
       </c>
       <c r="AN3" t="n">
-        <v>581.7862435526732</v>
+        <v>578.03205693599</v>
       </c>
       <c r="AO3" t="n">
-        <v>439.0202467847003</v>
+        <v>435.2016763873617</v>
       </c>
       <c r="AP3" t="n">
-        <v>380.4474379013005</v>
+        <v>380.1276598984043</v>
       </c>
       <c r="AQ3" t="n">
-        <v>497.5930556681001</v>
+        <v>490.2756928763192</v>
       </c>
       <c r="AR3" t="n">
-        <v>389.4723141254966</v>
+        <v>389.2266788580479</v>
       </c>
       <c r="AS3" t="n">
-        <v>560.2252449914707</v>
+        <v>548.9050896179285</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -22712,19 +24039,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>550.25</v>
+        <v>562.6</v>
       </c>
       <c r="I4" t="n">
         <v>27.51</v>
       </c>
       <c r="J4" t="n">
-        <v>20.001818</v>
+        <v>20.450745</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M4" t="n">
         <v>19.74072709517046</v>
@@ -22733,25 +24060,25 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.62548864337262</v>
+        <v>23.57455339260127</v>
       </c>
       <c r="P4" t="n">
-        <v>22.31109064275568</v>
+        <v>22.26691006747159</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.902325824413882</v>
+        <v>2.951120816087783</v>
       </c>
       <c r="R4" t="n">
-        <v>20.64236416903409</v>
+        <v>20.61745383522727</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57799154893039</v>
+        <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.248540261362424</v>
+        <v>-1.058515929124994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="V4" t="n">
         <v>543.0674023881393</v>
@@ -22760,22 +24087,22 @@
         <v>806.3861287434895</v>
       </c>
       <c r="X4" t="n">
-        <v>649.9371925791808</v>
+        <v>648.535963830461</v>
       </c>
       <c r="Y4" t="n">
-        <v>570.0942091495549</v>
+        <v>567.350630179886</v>
       </c>
       <c r="Z4" t="n">
-        <v>729.7801760088067</v>
+        <v>729.7212974810359</v>
       </c>
       <c r="AA4" t="n">
-        <v>567.8714382901279</v>
+        <v>567.1861550071023</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.1805475110751</v>
+        <v>786.2309126774775</v>
       </c>
       <c r="AC4" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD4" t="n">
         <v>19.74072709517046</v>
@@ -22784,25 +24111,25 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.7225230458071</v>
+        <v>25.59142081717489</v>
       </c>
       <c r="AG4" t="n">
-        <v>27.07066899312207</v>
+        <v>26.78430634084441</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.135879194302828</v>
+        <v>3.144888871598961</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.56887251420455</v>
+        <v>21.31458229758523</v>
       </c>
       <c r="AJ4" t="n">
-        <v>29.17356100834187</v>
+        <v>28.88378002025463</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.824274690236889</v>
+        <v>-1.634612867754912</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.008064516129032258</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="AM4" t="n">
         <v>543.0674023881393</v>
@@ -22811,30 +24138,30 @@
         <v>864.6619000781998</v>
       </c>
       <c r="AO4" t="n">
-        <v>707.6266089901533</v>
+        <v>704.0199866804812</v>
       </c>
       <c r="AP4" t="n">
-        <v>621.3585723548825</v>
+        <v>617.5040938227938</v>
       </c>
       <c r="AQ4" t="n">
-        <v>793.8946456254241</v>
+        <v>790.5358795381687</v>
       </c>
       <c r="AR4" t="n">
-        <v>593.3596828657671</v>
+        <v>586.3641590065697</v>
       </c>
       <c r="AS4" t="n">
-        <v>802.5646633394849</v>
+        <v>794.5927883572048</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -22863,13 +24190,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>232.69</v>
+        <v>240.14</v>
       </c>
       <c r="I5" t="n">
-        <v>7.35</v>
+        <v>7.59</v>
       </c>
       <c r="J5" t="n">
-        <v>31.658504</v>
+        <v>31.638998</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -22884,13 +24211,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.63155628119264</v>
+        <v>31.62310863171025</v>
       </c>
       <c r="P5" t="n">
         <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.506718505758223</v>
+        <v>2.517313189294332</v>
       </c>
       <c r="R5" t="n">
         <v>28.4688995215311</v>
@@ -22899,34 +24226,34 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01075019741764165</v>
+        <v>0.006312034735022313</v>
       </c>
       <c r="U5" t="n">
         <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>199.5841458881871</v>
+        <v>206.1011792233116</v>
       </c>
       <c r="W5" t="n">
-        <v>270.6173540059493</v>
+        <v>279.453839034715</v>
       </c>
       <c r="X5" t="n">
-        <v>232.4919386667659</v>
+        <v>240.0193945146808</v>
       </c>
       <c r="Y5" t="n">
-        <v>214.067557649443</v>
+        <v>220.9129874079368</v>
       </c>
       <c r="Z5" t="n">
-        <v>250.9163196840888</v>
+        <v>259.1258016214247</v>
       </c>
       <c r="AA5" t="n">
-        <v>209.2464114832536</v>
+        <v>216.0789473684211</v>
       </c>
       <c r="AB5" t="n">
-        <v>256.8502067023242</v>
+        <v>265.237152227298</v>
       </c>
       <c r="AC5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AD5" t="n">
         <v>27.15430556301865</v>
@@ -22935,57 +24262,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.33317725668595</v>
+        <v>31.248493848305</v>
       </c>
       <c r="AG5" t="n">
-        <v>31.45339017533987</v>
+        <v>30.93963562410059</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.438163613726255</v>
+        <v>2.468718556387847</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.54016413217114</v>
+        <v>28.4754785054038</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.71631846833595</v>
+        <v>34.72357096864921</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.133431055029506</v>
+        <v>0.1581809115845018</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5327868852459017</v>
       </c>
       <c r="AM5" t="n">
-        <v>199.5841458881871</v>
+        <v>206.1011792233116</v>
       </c>
       <c r="AN5" t="n">
-        <v>270.6173540059493</v>
+        <v>279.453839034715</v>
       </c>
       <c r="AO5" t="n">
-        <v>230.2988528366417</v>
+        <v>237.1760683086349</v>
       </c>
       <c r="AP5" t="n">
-        <v>212.3783502757537</v>
+        <v>218.4384944656511</v>
       </c>
       <c r="AQ5" t="n">
-        <v>248.2193553975297</v>
+        <v>255.9136421516187</v>
       </c>
       <c r="AR5" t="n">
-        <v>209.7702063714579</v>
+        <v>216.1288818560149</v>
       </c>
       <c r="AS5" t="n">
-        <v>255.1649407422692</v>
+        <v>263.5519036520475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23014,13 +24341,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>283.78</v>
+        <v>281.74</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>34.35593</v>
+        <v>34.150303</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -23029,55 +24356,55 @@
         <v>61</v>
       </c>
       <c r="M6" t="n">
-        <v>31.21898795984968</v>
+        <v>32.08860759493671</v>
       </c>
       <c r="N6" t="n">
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.04123520993558</v>
+        <v>35.12517924510622</v>
       </c>
       <c r="P6" t="n">
         <v>35.24576330300393</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.729969455973103</v>
+        <v>1.619487764315308</v>
       </c>
       <c r="R6" t="n">
-        <v>32.76708675336234</v>
+        <v>32.81012812747231</v>
       </c>
       <c r="S6" t="n">
         <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.396137173156098</v>
+        <v>-0.6019657984377408</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3770491803278688</v>
+        <v>0.2786885245901639</v>
       </c>
       <c r="V6" t="n">
-        <v>257.8688405483584</v>
+        <v>264.7310126582279</v>
       </c>
       <c r="W6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>289.4406028340679</v>
+        <v>289.7827287721263</v>
       </c>
       <c r="Y6" t="n">
-        <v>275.15105512773</v>
+        <v>276.421954716525</v>
       </c>
       <c r="Z6" t="n">
-        <v>303.7301505404057</v>
+        <v>303.1435028277276</v>
       </c>
       <c r="AA6" t="n">
-        <v>270.6561365827729</v>
+        <v>270.6835570516466</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.8200073242188</v>
+        <v>308.446133223342</v>
       </c>
       <c r="AC6" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -23086,57 +24413,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.3901249140485</v>
+        <v>34.33364711707023</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.40435746680161</v>
+        <v>34.35201704701232</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.678648878759581</v>
+        <v>1.64900930047169</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13645490815368</v>
+        <v>32.13088525699663</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.60311899573401</v>
+        <v>36.49019476865163</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.02037049825081136</v>
+        <v>-0.1111844044892789</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4344262295081967</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.2000122070312</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.0624317900406</v>
+        <v>283.2525887158294</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.1967920514865</v>
+        <v>269.6482619869379</v>
       </c>
       <c r="AQ6" t="n">
-        <v>297.9280715285947</v>
+        <v>296.8569154447208</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.4471175413494</v>
+        <v>265.0798033702222</v>
       </c>
       <c r="AS6" t="n">
-        <v>302.3417629047629</v>
+        <v>301.044106841376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23165,13 +24492,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>192.53</v>
+        <v>194.97</v>
       </c>
       <c r="I7" t="n">
         <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>29.48392</v>
+        <v>29.85758</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -23180,114 +24507,114 @@
         <v>61</v>
       </c>
       <c r="M7" t="n">
-        <v>29.97549854412926</v>
+        <v>29.48392018059676</v>
       </c>
       <c r="N7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.42337697508546</v>
+        <v>37.2601229158231</v>
       </c>
       <c r="P7" t="n">
         <v>36.34694002112563</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.155782201865747</v>
+        <v>5.317296510649731</v>
       </c>
       <c r="R7" t="n">
-        <v>31.4088830173837</v>
+        <v>31.33996843744017</v>
       </c>
       <c r="S7" t="n">
         <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.53991318178886</v>
+        <v>-1.392162897253697</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="V7" t="n">
-        <v>195.740005493164</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="W7" t="n">
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>244.3746516473081</v>
+        <v>243.3086026403249</v>
       </c>
       <c r="Y7" t="n">
-        <v>210.7073938691247</v>
+        <v>208.5866564257821</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.0419094254914</v>
+        <v>278.0305488548676</v>
       </c>
       <c r="AA7" t="n">
-        <v>205.1000061035156</v>
+        <v>204.6499938964843</v>
       </c>
       <c r="AB7" t="n">
         <v>292.4373910086495</v>
       </c>
       <c r="AC7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AD7" t="n">
-        <v>29.97549854412926</v>
+        <v>29.48392018059676</v>
       </c>
       <c r="AE7" t="n">
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.25011503981347</v>
+        <v>37.07385074546544</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.80101978535555</v>
+        <v>36.76530643385284</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.434024957735758</v>
+        <v>4.529795896678524</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.79846911116362</v>
+        <v>31.41577400803383</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.79408108458227</v>
+        <v>43.71122399154974</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.751500073598883</v>
+        <v>-1.593067526675269</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>0.01162790697674419</v>
       </c>
       <c r="AM7" t="n">
-        <v>195.740005493164</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="AN7" t="n">
         <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>243.2432512099819</v>
+        <v>242.0922453678893</v>
       </c>
       <c r="AP7" t="n">
-        <v>214.2890682359674</v>
+        <v>212.5126781625786</v>
       </c>
       <c r="AQ7" t="n">
-        <v>272.1974341839964</v>
+        <v>271.6718125732</v>
       </c>
       <c r="AR7" t="n">
-        <v>207.6440032958984</v>
+        <v>205.1450042724609</v>
       </c>
       <c r="AS7" t="n">
-        <v>285.9753494823222</v>
+        <v>285.4342926648198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23316,70 +24643,70 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>521.58</v>
+        <v>539.49</v>
       </c>
       <c r="I8" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="J8" t="n">
-        <v>172.13863</v>
+        <v>178.63907</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>73.97735595703125</v>
+        <v>79.32453083542158</v>
       </c>
       <c r="N8" t="n">
         <v>180.8622966828894</v>
       </c>
       <c r="O8" t="n">
-        <v>136.375119730255</v>
+        <v>139.0392786288205</v>
       </c>
       <c r="P8" t="n">
-        <v>142.5573780497567</v>
+        <v>146.7475365810707</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.72127443684333</v>
+        <v>30.31548355458364</v>
       </c>
       <c r="R8" t="n">
-        <v>87.66113453991008</v>
+        <v>92.4679219947671</v>
       </c>
       <c r="S8" t="n">
-        <v>171.0085289126537</v>
+        <v>171.5409876088627</v>
       </c>
       <c r="T8" t="n">
-        <v>1.127429805537913</v>
+        <v>1.306256299685249</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9672131147540983</v>
       </c>
       <c r="V8" t="n">
-        <v>224.1513885498047</v>
+        <v>239.5600831229732</v>
       </c>
       <c r="W8" t="n">
-        <v>548.0127589491548</v>
+        <v>546.2041359823259</v>
       </c>
       <c r="X8" t="n">
-        <v>413.2166127826725</v>
+        <v>419.8986214590381</v>
       </c>
       <c r="Y8" t="n">
-        <v>317.1011512390372</v>
+        <v>328.3458611241954</v>
       </c>
       <c r="Z8" t="n">
-        <v>509.3320743263077</v>
+        <v>511.4513817938806</v>
       </c>
       <c r="AA8" t="n">
-        <v>265.6132376559275</v>
+        <v>279.2531244241966</v>
       </c>
       <c r="AB8" t="n">
-        <v>518.1558426053407</v>
+        <v>518.0537825787654</v>
       </c>
       <c r="AC8" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -23388,57 +24715,57 @@
         <v>180.8622966828894</v>
       </c>
       <c r="AF8" t="n">
-        <v>113.9276748468019</v>
+        <v>114.6403726833946</v>
       </c>
       <c r="AG8" t="n">
-        <v>108.8793110964921</v>
+        <v>110.1157653507928</v>
       </c>
       <c r="AH8" t="n">
-        <v>34.4941269548093</v>
+        <v>35.21597796876289</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.52037537772701</v>
+        <v>75.51811131891215</v>
       </c>
       <c r="AJ8" t="n">
-        <v>167.9367175493084</v>
+        <v>169.0944183849898</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.687561341368638</v>
+        <v>1.817319893071639</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9596774193548387</v>
+        <v>0.9836065573770492</v>
       </c>
       <c r="AM8" t="n">
-        <v>218.3315059445939</v>
+        <v>217.6109399183741</v>
       </c>
       <c r="AN8" t="n">
-        <v>548.0127589491548</v>
+        <v>546.2041359823259</v>
       </c>
       <c r="AO8" t="n">
-        <v>345.2008547858098</v>
+        <v>346.2139255038518</v>
       </c>
       <c r="AP8" t="n">
-        <v>240.6836501127377</v>
+        <v>239.8616720381879</v>
       </c>
       <c r="AQ8" t="n">
-        <v>449.7180594588821</v>
+        <v>452.5661789695157</v>
       </c>
       <c r="AR8" t="n">
-        <v>228.8267373945128</v>
+        <v>228.0646961831147</v>
       </c>
       <c r="AS8" t="n">
-        <v>508.8482541744045</v>
+        <v>510.665143522669</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23467,70 +24794,70 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>365.02</v>
+        <v>372.45</v>
       </c>
       <c r="I9" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>60.63455</v>
+        <v>62.075</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
-        <v>57.19493248774063</v>
+        <v>60.73543910377236</v>
       </c>
       <c r="N9" t="n">
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.39179113387321</v>
+        <v>75.7169589904405</v>
       </c>
       <c r="P9" t="n">
-        <v>78.71540210865163</v>
+        <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.334374602497062</v>
+        <v>9.065253611492661</v>
       </c>
       <c r="R9" t="n">
-        <v>61.99018380011179</v>
+        <v>62.68053102413946</v>
       </c>
       <c r="S9" t="n">
-        <v>83.49376061274063</v>
+        <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.580956599912486</v>
+        <v>-1.504862365146147</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="V9" t="n">
-        <v>344.3134935761985</v>
+        <v>364.4126346226341</v>
       </c>
       <c r="W9" t="n">
-        <v>565.1172405637031</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="X9" t="n">
-        <v>453.8585826259167</v>
+        <v>454.301753942643</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.6656475188844</v>
+        <v>399.910232273687</v>
       </c>
       <c r="Z9" t="n">
-        <v>510.051517732949</v>
+        <v>508.693275611599</v>
       </c>
       <c r="AA9" t="n">
-        <v>373.180906476673</v>
+        <v>376.0831861448368</v>
       </c>
       <c r="AB9" t="n">
-        <v>502.6324388886986</v>
+        <v>501.087710731908</v>
       </c>
       <c r="AC9" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -23539,57 +24866,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.88554773368574</v>
+        <v>71.77566214941169</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.8280926270555</v>
+        <v>69.76519890551299</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.935758233607503</v>
+        <v>8.048642351971177</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.20643220124423</v>
+        <v>62.05497221175226</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.35048706768551</v>
+        <v>82.37543771606209</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.417759639657164</v>
+        <v>-1.205254467175562</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04032258064516129</v>
+        <v>0.1065573770491803</v>
       </c>
       <c r="AM9" t="n">
-        <v>344.3134935761985</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="AN9" t="n">
-        <v>565.1172405637031</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="AO9" t="n">
-        <v>432.7509973567881</v>
+        <v>430.6539728964701</v>
       </c>
       <c r="AP9" t="n">
-        <v>384.977732790471</v>
+        <v>382.3621187846431</v>
       </c>
       <c r="AQ9" t="n">
-        <v>480.5242619231053</v>
+        <v>478.9458270082972</v>
       </c>
       <c r="AR9" t="n">
-        <v>374.4827218514902</v>
+        <v>372.3298332705136</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.7499321474667</v>
+        <v>494.2526262963726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-27 01:17:57</t>
+          <t>2026-06-30 03:43:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -23618,19 +24945,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.81</v>
+        <v>73.78</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.809677</v>
+        <v>23.800001</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -23649,7 +24976,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -23658,25 +24985,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>28.52805797173277</v>
+        <v>29.55330344716235</v>
       </c>
       <c r="AG10" t="n">
-        <v>33.45454521329976</v>
+        <v>33.84980213029581</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.86518441531513</v>
+        <v>13.18021137026943</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.751211333693119</v>
+        <v>3.740434383688714</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.17391207849554</v>
+        <v>39.19169882069462</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.3403042347219678</v>
+        <v>-0.4365106359477703</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.2266666666666667</v>
+        <v>0.1944444444444444</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -23685,19 +25012,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>88.4369797123716</v>
+        <v>91.61524068620328</v>
       </c>
       <c r="AP10" t="n">
-        <v>45.45490802489469</v>
+        <v>50.75658543836802</v>
       </c>
       <c r="AQ10" t="n">
-        <v>131.4190513998485</v>
+        <v>132.4738959340385</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.62875513444867</v>
+        <v>11.59534658943501</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.4391274433362</v>
+        <v>121.4942663441533</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS154"/>
+  <dimension ref="A1:AS163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22359,7 +22359,7 @@
         <v>1.306256299685249</v>
       </c>
       <c r="U147" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9672131147540984</v>
       </c>
       <c r="V147" t="n">
         <v>239.5600831229732</v>
@@ -22422,7 +22422,7 @@
         <v>346.2139255038518</v>
       </c>
       <c r="AP147" t="n">
-        <v>239.8616720381879</v>
+        <v>239.8616720381878</v>
       </c>
       <c r="AQ147" t="n">
         <v>452.5661789695157</v>
@@ -22507,7 +22507,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T148" t="n">
-        <v>0.006312034735022313</v>
+        <v>0.0063120347350223</v>
       </c>
       <c r="U148" t="n">
         <v>0.4426229508196721</v>
@@ -22549,7 +22549,7 @@
         <v>30.93963562410059</v>
       </c>
       <c r="AH148" t="n">
-        <v>2.468718556387847</v>
+        <v>2.468718556387848</v>
       </c>
       <c r="AI148" t="n">
         <v>28.4754785054038</v>
@@ -22573,7 +22573,7 @@
         <v>237.1760683086349</v>
       </c>
       <c r="AP148" t="n">
-        <v>218.4384944656511</v>
+        <v>218.4384944656512</v>
       </c>
       <c r="AQ148" t="n">
         <v>255.9136421516187</v>
@@ -22640,7 +22640,7 @@
         <v>60.73543910377236</v>
       </c>
       <c r="N149" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O149" t="n">
         <v>75.7169589904405</v>
@@ -22649,7 +22649,7 @@
         <v>79.03509009883652</v>
       </c>
       <c r="Q149" t="n">
-        <v>9.065253611492661</v>
+        <v>9.065253611492659</v>
       </c>
       <c r="R149" t="n">
         <v>62.68053102413946</v>
@@ -22661,7 +22661,7 @@
         <v>-1.504862365146147</v>
       </c>
       <c r="U149" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="V149" t="n">
         <v>364.4126346226341</v>
@@ -22691,7 +22691,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE149" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF149" t="n">
         <v>71.77566214941169</v>
@@ -22709,7 +22709,7 @@
         <v>82.37543771606209</v>
       </c>
       <c r="AK149" t="n">
-        <v>-1.205254467175562</v>
+        <v>-1.205254467175563</v>
       </c>
       <c r="AL149" t="n">
         <v>0.1065573770491803</v>
@@ -22812,13 +22812,13 @@
         <v>-1.330342183545509</v>
       </c>
       <c r="U150" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="V150" t="n">
         <v>334.434708770589</v>
       </c>
       <c r="W150" t="n">
-        <v>422.3507729952915</v>
+        <v>422.3507729952916</v>
       </c>
       <c r="X150" t="n">
         <v>379.9127998666096</v>
@@ -22863,7 +22863,7 @@
         <v>-1.238928085598398</v>
       </c>
       <c r="AL150" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="AM150" t="n">
         <v>331.002237918088</v>
@@ -22878,7 +22878,7 @@
         <v>357.8567271577448</v>
       </c>
       <c r="AQ150" t="n">
-        <v>412.9087947392788</v>
+        <v>412.9087947392789</v>
       </c>
       <c r="AR150" t="n">
         <v>353.2863216443793</v>
@@ -22954,7 +22954,7 @@
         <v>2.951120816087783</v>
       </c>
       <c r="R151" t="n">
-        <v>20.61745383522727</v>
+        <v>20.61745383522728</v>
       </c>
       <c r="S151" t="n">
         <v>28.57982234378326</v>
@@ -22963,7 +22963,7 @@
         <v>-1.058515929124994</v>
       </c>
       <c r="U151" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.0655737704918032</v>
       </c>
       <c r="V151" t="n">
         <v>543.0674023881393</v>
@@ -23008,13 +23008,13 @@
         <v>21.31458229758523</v>
       </c>
       <c r="AJ151" t="n">
-        <v>28.88378002025463</v>
+        <v>28.88378002025462</v>
       </c>
       <c r="AK151" t="n">
         <v>-1.634612867754912</v>
       </c>
       <c r="AL151" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.0327868852459016</v>
       </c>
       <c r="AM151" t="n">
         <v>543.0674023881393</v>
@@ -23099,7 +23099,7 @@
         <v>24.49024788891508</v>
       </c>
       <c r="P152" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q152" t="n">
         <v>1.46170242334417</v>
@@ -23108,13 +23108,13 @@
         <v>22.55416688464937</v>
       </c>
       <c r="S152" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T152" t="n">
-        <v>-1.754534882036809</v>
+        <v>-1.754534882036808</v>
       </c>
       <c r="U152" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="V152" t="n">
         <v>353.0400044214157</v>
@@ -23150,7 +23150,7 @@
         <v>25.88945130204413</v>
       </c>
       <c r="AG152" t="n">
-        <v>25.00156404973567</v>
+        <v>25.00156404973568</v>
       </c>
       <c r="AH152" t="n">
         <v>3.276265109396637</v>
@@ -23165,7 +23165,7 @@
         <v>-1.209856702583542</v>
       </c>
       <c r="AL152" t="n">
-        <v>0.02459016393442623</v>
+        <v>0.0245901639344262</v>
       </c>
       <c r="AM152" t="n">
         <v>353.0400044214157</v>
@@ -23260,19 +23260,19 @@
         <v>72</v>
       </c>
       <c r="AD153" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE153" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF153" t="n">
-        <v>29.55330344716235</v>
+        <v>29.55330344716234</v>
       </c>
       <c r="AG153" t="n">
         <v>33.84980213029581</v>
       </c>
       <c r="AH153" t="n">
-        <v>13.18021137026943</v>
+        <v>13.18021137026944</v>
       </c>
       <c r="AI153" t="n">
         <v>3.740434383688714</v>
@@ -23384,7 +23384,7 @@
         <v>-1.392162897253697</v>
       </c>
       <c r="U154" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0163934426229508</v>
       </c>
       <c r="V154" t="n">
         <v>192.5299987792968</v>
@@ -23432,10 +23432,10 @@
         <v>43.71122399154974</v>
       </c>
       <c r="AK154" t="n">
-        <v>-1.593067526675269</v>
+        <v>-1.593067526675268</v>
       </c>
       <c r="AL154" t="n">
-        <v>0.01162790697674419</v>
+        <v>0.0116279069767441</v>
       </c>
       <c r="AM154" t="n">
         <v>192.5299987792968</v>
@@ -23457,6 +23457,1333 @@
       </c>
       <c r="AS154" t="n">
         <v>285.4342926648198</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>289.36</v>
+      </c>
+      <c r="I155" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J155" t="n">
+        <v>35.073936</v>
+      </c>
+      <c r="K155" t="n">
+        <v>67</v>
+      </c>
+      <c r="L155" t="n">
+        <v>61</v>
+      </c>
+      <c r="M155" t="n">
+        <v>32.08860759493671</v>
+      </c>
+      <c r="N155" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O155" t="n">
+        <v>35.16900296245017</v>
+      </c>
+      <c r="P155" t="n">
+        <v>35.24576330300393</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>1.579029498068575</v>
+      </c>
+      <c r="R155" t="n">
+        <v>32.97215328940862</v>
+      </c>
+      <c r="S155" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T155" t="n">
+        <v>-0.0602059445795356</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0.4754098360655737</v>
+      </c>
+      <c r="V155" t="n">
+        <v>264.7310126582279</v>
+      </c>
+      <c r="W155" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X155" t="n">
+        <v>290.1442744402139</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>277.1172810811482</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>303.1712677992796</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>272.0202646376212</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>308.446133223342</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>34.33932051631486</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.643442103115445</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>36.47433523404396</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>0.4469980915619369</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>283.2993942595976</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>269.7409969088952</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>296.8577916103001</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>300.9132656808627</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>580.91</v>
+      </c>
+      <c r="I156" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J156" t="n">
+        <v>192.3543</v>
+      </c>
+      <c r="K156" t="n">
+        <v>63</v>
+      </c>
+      <c r="L156" t="n">
+        <v>61</v>
+      </c>
+      <c r="M156" t="n">
+        <v>82.0754716981132</v>
+      </c>
+      <c r="N156" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O156" t="n">
+        <v>140.8612090458939</v>
+      </c>
+      <c r="P156" t="n">
+        <v>146.9803306704662</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>30.00491680356031</v>
+      </c>
+      <c r="R156" t="n">
+        <v>93.14339691737914</v>
+      </c>
+      <c r="S156" t="n">
+        <v>174.6131171554816</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.716155098553583</v>
+      </c>
+      <c r="U156" t="n">
+        <v>1</v>
+      </c>
+      <c r="V156" t="n">
+        <v>247.8679245283019</v>
+      </c>
+      <c r="W156" t="n">
+        <v>575.1961045562244</v>
+      </c>
+      <c r="X156" t="n">
+        <v>425.4008513185996</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>334.7860025718475</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>516.0157000653517</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>281.293058690485</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>527.3316138095544</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>115.256811005293</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>110.1477862578895</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>35.73148960979601</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>169.7350874103484</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>2.157690312848593</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>217.6109399183741</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>575.1961045562244</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>348.0755692359849</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>240.1664706144009</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>455.9846678575688</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>228.0681149119251</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>512.599963979252</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>238.34</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="J157" t="n">
+        <v>31.652058</v>
+      </c>
+      <c r="K157" t="n">
+        <v>67</v>
+      </c>
+      <c r="L157" t="n">
+        <v>61</v>
+      </c>
+      <c r="M157" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N157" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O157" t="n">
+        <v>31.60903268222844</v>
+      </c>
+      <c r="P157" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.532486855384522</v>
+      </c>
+      <c r="R157" t="n">
+        <v>28.4688995215311</v>
+      </c>
+      <c r="S157" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0.01698935482333459</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V157" t="n">
+        <v>204.4719208895305</v>
+      </c>
+      <c r="W157" t="n">
+        <v>277.2447177775235</v>
+      </c>
+      <c r="X157" t="n">
+        <v>238.0160160971802</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>218.9463900761347</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>257.0856421182256</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>214.3708133971292</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>263.1404158460546</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>31.22622616612316</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>30.85774058577406</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>2.470952309836587</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>0.1723351082826053</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>204.4719208895305</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>277.2447177775235</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>235.1334830309074</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>216.5272121378379</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>253.7397539239769</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>214.4320615412516</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>261.4138780665697</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="I158" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="J158" t="n">
+        <v>62.853577</v>
+      </c>
+      <c r="K158" t="n">
+        <v>34</v>
+      </c>
+      <c r="L158" t="n">
+        <v>61</v>
+      </c>
+      <c r="M158" t="n">
+        <v>60.73543910377236</v>
+      </c>
+      <c r="N158" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O158" t="n">
+        <v>75.74555599833079</v>
+      </c>
+      <c r="P158" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>9.021047878378754</v>
+      </c>
+      <c r="R158" t="n">
+        <v>62.85357737104825</v>
+      </c>
+      <c r="S158" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T158" t="n">
+        <v>-1.429099941840427</v>
+      </c>
+      <c r="U158" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="V158" t="n">
+        <v>365.0199890136719</v>
+      </c>
+      <c r="W158" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="X158" t="n">
+        <v>455.230791549968</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>401.0142938009117</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>509.4472892990243</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>501.9228569164612</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>71.70312487479084</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>69.76310042215344</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>8.05585740569148</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>62.06510844983554</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>-1.098523400940367</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>343.7415442513212</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>430.9357804974929</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>382.5200774892871</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>479.3514835056988</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>373.0113017835116</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>495.0014039751615</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="I159" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J159" t="n">
+        <v>26.951181</v>
+      </c>
+      <c r="K159" t="n">
+        <v>37</v>
+      </c>
+      <c r="L159" t="n">
+        <v>61</v>
+      </c>
+      <c r="M159" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N159" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O159" t="n">
+        <v>28.99558177465687</v>
+      </c>
+      <c r="P159" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>1.649242190130955</v>
+      </c>
+      <c r="R159" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S159" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T159" t="n">
+        <v>-1.239600094449766</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0.1147540983606557</v>
+      </c>
+      <c r="V159" t="n">
+        <v>334.6900024414062</v>
+      </c>
+      <c r="W159" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X159" t="n">
+        <v>380.1320770657516</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>358.5105119531347</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>401.7536421783684</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>353.3200073242188</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>409.5874601323553</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>29.39847161327991</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>29.11563276913737</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>2.104387525200074</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>26.95057232447202</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>-1.162946740547339</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>0.1056910569105691</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>385.4139628500996</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>357.8254423947266</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>413.0024833054725</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>353.3220031738281</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>428.0356714698664</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>563.29</v>
+      </c>
+      <c r="I160" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J160" t="n">
+        <v>20.490723</v>
+      </c>
+      <c r="K160" t="n">
+        <v>55</v>
+      </c>
+      <c r="L160" t="n">
+        <v>61</v>
+      </c>
+      <c r="M160" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N160" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O160" t="n">
+        <v>23.50610576377159</v>
+      </c>
+      <c r="P160" t="n">
+        <v>22.25127175071023</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>2.973891860300616</v>
+      </c>
+      <c r="R160" t="n">
+        <v>20.50363547585227</v>
+      </c>
+      <c r="S160" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T160" t="n">
+        <v>-1.013951718966264</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="V160" t="n">
+        <v>542.6725878462358</v>
+      </c>
+      <c r="W160" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X160" t="n">
+        <v>646.1828474460809</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>564.4305602064171</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>727.9351346857449</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>563.644939231179</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>785.6593162306017</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>25.54989115141141</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>26.75464991661592</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>3.165659091676049</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>21.26363725142046</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>28.87781993334929</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>-1.598140546691922</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>542.6725878462358</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>702.3665077522996</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>615.3425393221252</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>789.3904761824742</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>584.5373880415483</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>793.8512699677721</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>373.02</v>
+      </c>
+      <c r="I161" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J161" t="n">
+        <v>22.216793</v>
+      </c>
+      <c r="K161" t="n">
+        <v>67</v>
+      </c>
+      <c r="L161" t="n">
+        <v>61</v>
+      </c>
+      <c r="M161" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N161" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O161" t="n">
+        <v>24.47555130761841</v>
+      </c>
+      <c r="P161" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>1.480301428618054</v>
+      </c>
+      <c r="R161" t="n">
+        <v>22.25833347865513</v>
+      </c>
+      <c r="S161" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T161" t="n">
+        <v>-1.525877273338235</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="V161" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W161" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X161" t="n">
+        <v>410.9445064549131</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>386.090245468416</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>435.7987674414102</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>373.7174191066197</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>445.3812671348853</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>34.38620207828614</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>25.85948479369111</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>24.99061951866889</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>3.279692537825873</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>23.11006871665396</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>32.63413973248021</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>-1.11068087989305</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>577.3443328944243</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>434.1807496860737</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>379.1147119759773</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>489.2467873961701</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>388.01805375262</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>547.9272061083428</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="I162" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>23.032259</v>
+      </c>
+      <c r="K162" t="n">
+        <v>67</v>
+      </c>
+      <c r="L162" t="n">
+        <v>10</v>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+      <c r="W162" t="inlineStr"/>
+      <c r="X162" t="inlineStr"/>
+      <c r="Y162" t="inlineStr"/>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>29.55330344716235</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>33.84980213029581</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>13.18021137026943</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>3.740434383688714</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>39.19169882069462</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>-0.4947602328951907</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>0.1944444444444444</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>91.61524068620328</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>50.75658543836802</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>132.4738959340385</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>11.59534658943501</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>121.4942663441533</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:57:12</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>200.09</v>
+      </c>
+      <c r="I163" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J163" t="n">
+        <v>30.68865</v>
+      </c>
+      <c r="K163" t="n">
+        <v>65</v>
+      </c>
+      <c r="L163" t="n">
+        <v>61</v>
+      </c>
+      <c r="M163" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N163" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O163" t="n">
+        <v>37.17445580771598</v>
+      </c>
+      <c r="P163" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>5.381813782576301</v>
+      </c>
+      <c r="R163" t="n">
+        <v>30.69218961239591</v>
+      </c>
+      <c r="S163" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T163" t="n">
+        <v>-1.205133821001735</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="V163" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="W163" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="X163" t="n">
+        <v>242.3774518663082</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>207.2880260039107</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>277.4668777287056</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>200.1130762728213</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>291.9895542689732</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>87</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>36.99991744200308</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>36.74489858199139</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>4.555876518656343</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>31.39479352358106</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>43.66979544503348</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>-1.385302568267248</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0.06896551724137931</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>241.2394617218601</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>211.5351468202207</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>270.9437766234994</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>204.6940537737485</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>284.7270663016183</v>
       </c>
     </row>
   </sheetData>
@@ -23703,12 +25030,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -23737,13 +25064,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>351.28</v>
+        <v>353.33</v>
       </c>
       <c r="I2" t="n">
-        <v>13.1</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>26.815266</v>
+        <v>26.951181</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -23758,13 +25085,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>29.00097708905417</v>
+        <v>28.99558177465687</v>
       </c>
       <c r="P2" t="n">
         <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.642969091778331</v>
+        <v>1.649242190130955</v>
       </c>
       <c r="R2" t="n">
         <v>26.95042008575277</v>
@@ -23773,34 +25100,34 @@
         <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.330342183545509</v>
+        <v>-1.239600094449766</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.1147540983606557</v>
       </c>
       <c r="V2" t="n">
-        <v>334.434708770589</v>
+        <v>334.6900024414062</v>
       </c>
       <c r="W2" t="n">
-        <v>422.3507729952915</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>379.9127998666096</v>
+        <v>380.1320770657516</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.3899047643135</v>
+        <v>358.5105119531347</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.4356949689057</v>
+        <v>401.7536421783684</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.0505031233612</v>
+        <v>353.3200073242188</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.2750364404161</v>
+        <v>409.5874601323553</v>
       </c>
       <c r="AC2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -23809,57 +25136,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.41853137011541</v>
+        <v>29.39847161327991</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.12303349356426</v>
+        <v>29.11563276913737</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.101223953493667</v>
+        <v>2.104387525200074</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.96842149957094</v>
+        <v>26.95057232447202</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.65449124757065</v>
+        <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.238928085598398</v>
+        <v>-1.162946740547339</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.1056910569105691</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.002237918088</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.0207226104586</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>385.3827609485118</v>
+        <v>385.4139628500996</v>
       </c>
       <c r="AP2" t="n">
-        <v>357.8567271577448</v>
+        <v>357.8254423947266</v>
       </c>
       <c r="AQ2" t="n">
-        <v>412.9087947392788</v>
+        <v>413.0024833054725</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.2863216443793</v>
+        <v>353.3220031738281</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.7738353431754</v>
+        <v>428.0356714698664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -23888,13 +25215,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>368.57</v>
+        <v>373.02</v>
       </c>
       <c r="I3" t="n">
-        <v>16.81</v>
+        <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>21.92564</v>
+        <v>22.216793</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -23909,49 +25236,49 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.49024788891508</v>
+        <v>24.47555130761841</v>
       </c>
       <c r="P3" t="n">
         <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.46170242334417</v>
+        <v>1.480301428618054</v>
       </c>
       <c r="R3" t="n">
-        <v>22.55416688464937</v>
+        <v>22.25833347865513</v>
       </c>
       <c r="S3" t="n">
         <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.754534882036809</v>
+        <v>-1.525877273338235</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="V3" t="n">
-        <v>353.0400044214157</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="W3" t="n">
-        <v>460.7941080547514</v>
+        <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>411.6810670126625</v>
+        <v>410.9445064549131</v>
       </c>
       <c r="Y3" t="n">
-        <v>387.109849276247</v>
+        <v>386.090245468416</v>
       </c>
       <c r="Z3" t="n">
-        <v>436.252284749078</v>
+        <v>435.7987674414102</v>
       </c>
       <c r="AA3" t="n">
-        <v>379.1355453309558</v>
+        <v>373.7174191066197</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.9117987217047</v>
+        <v>445.3812671348853</v>
       </c>
       <c r="AC3" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD3" t="n">
         <v>21.00178491501581</v>
@@ -23960,57 +25287,57 @@
         <v>34.38620207828614</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.88945130204413</v>
+        <v>25.85948479369111</v>
       </c>
       <c r="AG3" t="n">
-        <v>25.00156404973567</v>
+        <v>24.99061951866889</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.276265109396637</v>
+        <v>3.279692537825873</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.15447226996121</v>
+        <v>23.11006871665396</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32.65348540261324</v>
+        <v>32.63413973248021</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.209856702583542</v>
+        <v>-1.11068087989305</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.02459016393442623</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="AM3" t="n">
-        <v>353.0400044214157</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="AN3" t="n">
-        <v>578.03205693599</v>
+        <v>577.3443328944243</v>
       </c>
       <c r="AO3" t="n">
-        <v>435.2016763873617</v>
+        <v>434.1807496860737</v>
       </c>
       <c r="AP3" t="n">
-        <v>380.1276598984043</v>
+        <v>379.1147119759773</v>
       </c>
       <c r="AQ3" t="n">
-        <v>490.2756928763192</v>
+        <v>489.2467873961701</v>
       </c>
       <c r="AR3" t="n">
-        <v>389.2266788580479</v>
+        <v>388.01805375262</v>
       </c>
       <c r="AS3" t="n">
-        <v>548.9050896179285</v>
+        <v>547.9272061083428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -24039,13 +25366,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>562.6</v>
+        <v>563.29</v>
       </c>
       <c r="I4" t="n">
-        <v>27.51</v>
+        <v>27.49</v>
       </c>
       <c r="J4" t="n">
-        <v>20.450745</v>
+        <v>20.490723</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -24060,49 +25387,49 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.57455339260127</v>
+        <v>23.50610576377159</v>
       </c>
       <c r="P4" t="n">
-        <v>22.26691006747159</v>
+        <v>22.25127175071023</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.951120816087783</v>
+        <v>2.973891860300616</v>
       </c>
       <c r="R4" t="n">
-        <v>20.61745383522727</v>
+        <v>20.50363547585227</v>
       </c>
       <c r="S4" t="n">
         <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.058515929124994</v>
+        <v>-1.013951718966264</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="V4" t="n">
-        <v>543.0674023881393</v>
+        <v>542.6725878462358</v>
       </c>
       <c r="W4" t="n">
-        <v>806.3861287434895</v>
+        <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>648.535963830461</v>
+        <v>646.1828474460809</v>
       </c>
       <c r="Y4" t="n">
-        <v>567.350630179886</v>
+        <v>564.4305602064171</v>
       </c>
       <c r="Z4" t="n">
-        <v>729.7212974810359</v>
+        <v>727.9351346857449</v>
       </c>
       <c r="AA4" t="n">
-        <v>567.1861550071023</v>
+        <v>563.644939231179</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.2309126774775</v>
+        <v>785.6593162306017</v>
       </c>
       <c r="AC4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD4" t="n">
         <v>19.74072709517046</v>
@@ -24111,57 +25438,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.59142081717489</v>
+        <v>25.54989115141141</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.78430634084441</v>
+        <v>26.75464991661592</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.144888871598961</v>
+        <v>3.165659091676049</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.31458229758523</v>
+        <v>21.26363725142046</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28.88378002025463</v>
+        <v>28.87781993334929</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.634612867754912</v>
+        <v>-1.598140546691922</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.04878048780487805</v>
       </c>
       <c r="AM4" t="n">
-        <v>543.0674023881393</v>
+        <v>542.6725878462358</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.6619000781998</v>
+        <v>864.0332836477539</v>
       </c>
       <c r="AO4" t="n">
-        <v>704.0199866804812</v>
+        <v>702.3665077522996</v>
       </c>
       <c r="AP4" t="n">
-        <v>617.5040938227938</v>
+        <v>615.3425393221252</v>
       </c>
       <c r="AQ4" t="n">
-        <v>790.5358795381687</v>
+        <v>789.3904761824742</v>
       </c>
       <c r="AR4" t="n">
-        <v>586.3641590065697</v>
+        <v>584.5373880415483</v>
       </c>
       <c r="AS4" t="n">
-        <v>794.5927883572048</v>
+        <v>793.8512699677721</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -24190,13 +25517,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>240.14</v>
+        <v>238.34</v>
       </c>
       <c r="I5" t="n">
-        <v>7.59</v>
+        <v>7.53</v>
       </c>
       <c r="J5" t="n">
-        <v>31.638998</v>
+        <v>31.652058</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -24211,13 +25538,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.62310863171025</v>
+        <v>31.60903268222844</v>
       </c>
       <c r="P5" t="n">
         <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.517313189294332</v>
+        <v>2.532486855384522</v>
       </c>
       <c r="R5" t="n">
         <v>28.4688995215311</v>
@@ -24226,34 +25553,34 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>0.006312034735022313</v>
+        <v>0.01698935482333459</v>
       </c>
       <c r="U5" t="n">
         <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>206.1011792233116</v>
+        <v>204.4719208895305</v>
       </c>
       <c r="W5" t="n">
-        <v>279.453839034715</v>
+        <v>277.2447177775235</v>
       </c>
       <c r="X5" t="n">
-        <v>240.0193945146808</v>
+        <v>238.0160160971802</v>
       </c>
       <c r="Y5" t="n">
-        <v>220.9129874079368</v>
+        <v>218.9463900761347</v>
       </c>
       <c r="Z5" t="n">
-        <v>259.1258016214247</v>
+        <v>257.0856421182256</v>
       </c>
       <c r="AA5" t="n">
-        <v>216.0789473684211</v>
+        <v>214.3708133971292</v>
       </c>
       <c r="AB5" t="n">
-        <v>265.237152227298</v>
+        <v>263.1404158460546</v>
       </c>
       <c r="AC5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD5" t="n">
         <v>27.15430556301865</v>
@@ -24262,57 +25589,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.248493848305</v>
+        <v>31.22622616612316</v>
       </c>
       <c r="AG5" t="n">
-        <v>30.93963562410059</v>
+        <v>30.85774058577406</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.468718556387847</v>
+        <v>2.470952309836587</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.4754785054038</v>
+        <v>28.4770334052127</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.72357096864921</v>
+        <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1581809115845018</v>
+        <v>0.1723351082826053</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5327868852459017</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="AM5" t="n">
-        <v>206.1011792233116</v>
+        <v>204.4719208895305</v>
       </c>
       <c r="AN5" t="n">
-        <v>279.453839034715</v>
+        <v>277.2447177775235</v>
       </c>
       <c r="AO5" t="n">
-        <v>237.1760683086349</v>
+        <v>235.1334830309074</v>
       </c>
       <c r="AP5" t="n">
-        <v>218.4384944656511</v>
+        <v>216.5272121378379</v>
       </c>
       <c r="AQ5" t="n">
-        <v>255.9136421516187</v>
+        <v>253.7397539239769</v>
       </c>
       <c r="AR5" t="n">
-        <v>216.1288818560149</v>
+        <v>214.4320615412516</v>
       </c>
       <c r="AS5" t="n">
-        <v>263.5519036520475</v>
+        <v>261.4138780665697</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -24341,13 +25668,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>281.74</v>
+        <v>289.36</v>
       </c>
       <c r="I6" t="n">
         <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>34.150303</v>
+        <v>35.073936</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -24362,25 +25689,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.12517924510622</v>
+        <v>35.16900296245017</v>
       </c>
       <c r="P6" t="n">
         <v>35.24576330300393</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.619487764315308</v>
+        <v>1.579029498068575</v>
       </c>
       <c r="R6" t="n">
-        <v>32.81012812747231</v>
+        <v>32.97215328940862</v>
       </c>
       <c r="S6" t="n">
         <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6019657984377408</v>
+        <v>-0.0602059445795356</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2786885245901639</v>
+        <v>0.4754098360655737</v>
       </c>
       <c r="V6" t="n">
         <v>264.7310126582279</v>
@@ -24389,22 +25716,22 @@
         <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>289.7827287721263</v>
+        <v>290.1442744402139</v>
       </c>
       <c r="Y6" t="n">
-        <v>276.421954716525</v>
+        <v>277.1172810811482</v>
       </c>
       <c r="Z6" t="n">
-        <v>303.1435028277276</v>
+        <v>303.1712677992796</v>
       </c>
       <c r="AA6" t="n">
-        <v>270.6835570516466</v>
+        <v>272.0202646376212</v>
       </c>
       <c r="AB6" t="n">
         <v>308.446133223342</v>
       </c>
       <c r="AC6" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -24413,25 +25740,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.33364711707023</v>
+        <v>34.33932051631486</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.35201704701232</v>
+        <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.64900930047169</v>
+        <v>1.643442103115445</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13088525699663</v>
+        <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.49019476865163</v>
+        <v>36.47433523404396</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1111844044892789</v>
+        <v>0.4469980915619369</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.4344262295081967</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="AM6" t="n">
         <v>257.5566506687599</v>
@@ -24440,30 +25767,30 @@
         <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>283.2525887158294</v>
+        <v>283.2993942595976</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.6482619869379</v>
+        <v>269.7409969088952</v>
       </c>
       <c r="AQ6" t="n">
-        <v>296.8569154447208</v>
+        <v>296.8577916103001</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.0798033702222</v>
+        <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>301.044106841376</v>
+        <v>300.9132656808627</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -24492,13 +25819,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>194.97</v>
+        <v>200.09</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="J7" t="n">
-        <v>29.85758</v>
+        <v>30.68865</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -24513,49 +25840,49 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.2601229158231</v>
+        <v>37.17445580771598</v>
       </c>
       <c r="P7" t="n">
         <v>36.34694002112563</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.317296510649731</v>
+        <v>5.381813782576301</v>
       </c>
       <c r="R7" t="n">
-        <v>31.33996843744017</v>
+        <v>30.69218961239591</v>
       </c>
       <c r="S7" t="n">
         <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.392162897253697</v>
+        <v>-1.205133821001735</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.09836065573770492</v>
       </c>
       <c r="V7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.2351595774909</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="X7" t="n">
-        <v>243.3086026403249</v>
+        <v>242.3774518663082</v>
       </c>
       <c r="Y7" t="n">
-        <v>208.5866564257821</v>
+        <v>207.2880260039107</v>
       </c>
       <c r="Z7" t="n">
-        <v>278.0305488548676</v>
+        <v>277.4668777287056</v>
       </c>
       <c r="AA7" t="n">
-        <v>204.6499938964843</v>
+        <v>200.1130762728213</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.4373910086495</v>
+        <v>291.9895542689732</v>
       </c>
       <c r="AC7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -24564,57 +25891,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>37.07385074546544</v>
+        <v>36.99991744200308</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.76530643385284</v>
+        <v>36.74489858199139</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.529795896678524</v>
+        <v>4.555876518656343</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.41577400803383</v>
+        <v>31.39479352358106</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.71122399154974</v>
+        <v>43.66979544503348</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.593067526675269</v>
+        <v>-1.385302568267248</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01162790697674419</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="AM7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.2351595774909</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="AO7" t="n">
-        <v>242.0922453678893</v>
+        <v>241.2394617218601</v>
       </c>
       <c r="AP7" t="n">
-        <v>212.5126781625786</v>
+        <v>211.5351468202207</v>
       </c>
       <c r="AQ7" t="n">
-        <v>271.6718125732</v>
+        <v>270.9437766234994</v>
       </c>
       <c r="AR7" t="n">
-        <v>205.1450042724609</v>
+        <v>204.6940537737485</v>
       </c>
       <c r="AS7" t="n">
-        <v>285.4342926648198</v>
+        <v>284.7270663016183</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -24643,13 +25970,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>539.49</v>
+        <v>580.91</v>
       </c>
       <c r="I8" t="n">
         <v>3.02</v>
       </c>
       <c r="J8" t="n">
-        <v>178.63907</v>
+        <v>192.3543</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -24658,114 +25985,114 @@
         <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>79.32453083542158</v>
+        <v>82.0754716981132</v>
       </c>
       <c r="N8" t="n">
-        <v>180.8622966828894</v>
+        <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>139.0392786288205</v>
+        <v>140.8612090458939</v>
       </c>
       <c r="P8" t="n">
-        <v>146.7475365810707</v>
+        <v>146.9803306704662</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.31548355458364</v>
+        <v>30.00491680356031</v>
       </c>
       <c r="R8" t="n">
-        <v>92.4679219947671</v>
+        <v>93.14339691737914</v>
       </c>
       <c r="S8" t="n">
-        <v>171.5409876088627</v>
+        <v>174.6131171554816</v>
       </c>
       <c r="T8" t="n">
-        <v>1.306256299685249</v>
+        <v>1.716155098553583</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9672131147540983</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>239.5600831229732</v>
+        <v>247.8679245283019</v>
       </c>
       <c r="W8" t="n">
-        <v>546.2041359823259</v>
+        <v>575.1961045562244</v>
       </c>
       <c r="X8" t="n">
-        <v>419.8986214590381</v>
+        <v>425.4008513185996</v>
       </c>
       <c r="Y8" t="n">
-        <v>328.3458611241954</v>
+        <v>334.7860025718475</v>
       </c>
       <c r="Z8" t="n">
-        <v>511.4513817938806</v>
+        <v>516.0157000653517</v>
       </c>
       <c r="AA8" t="n">
-        <v>279.2531244241966</v>
+        <v>281.293058690485</v>
       </c>
       <c r="AB8" t="n">
-        <v>518.0537825787654</v>
+        <v>527.3316138095544</v>
       </c>
       <c r="AC8" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
       </c>
       <c r="AE8" t="n">
-        <v>180.8622966828894</v>
+        <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>114.6403726833946</v>
+        <v>115.256811005293</v>
       </c>
       <c r="AG8" t="n">
-        <v>110.1157653507928</v>
+        <v>110.1477862578895</v>
       </c>
       <c r="AH8" t="n">
-        <v>35.21597796876289</v>
+        <v>35.73148960979601</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51811131891215</v>
+        <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>169.0944183849898</v>
+        <v>169.7350874103484</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.817319893071639</v>
+        <v>2.157690312848593</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9836065573770492</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
         <v>217.6109399183741</v>
       </c>
       <c r="AN8" t="n">
-        <v>546.2041359823259</v>
+        <v>575.1961045562244</v>
       </c>
       <c r="AO8" t="n">
-        <v>346.2139255038518</v>
+        <v>348.0755692359849</v>
       </c>
       <c r="AP8" t="n">
-        <v>239.8616720381879</v>
+        <v>240.1664706144009</v>
       </c>
       <c r="AQ8" t="n">
-        <v>452.5661789695157</v>
+        <v>455.9846678575688</v>
       </c>
       <c r="AR8" t="n">
-        <v>228.0646961831147</v>
+        <v>228.0681149119251</v>
       </c>
       <c r="AS8" t="n">
-        <v>510.665143522669</v>
+        <v>512.599963979252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -24794,13 +26121,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>372.45</v>
+        <v>377.75</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="J9" t="n">
-        <v>62.075</v>
+        <v>62.853577</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -24815,49 +26142,49 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.7169589904405</v>
+        <v>75.74555599833079</v>
       </c>
       <c r="P9" t="n">
         <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.065253611492661</v>
+        <v>9.021047878378754</v>
       </c>
       <c r="R9" t="n">
-        <v>62.68053102413946</v>
+        <v>62.85357737104825</v>
       </c>
       <c r="S9" t="n">
         <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.504862365146147</v>
+        <v>-1.429099941840427</v>
       </c>
       <c r="U9" t="n">
         <v>0.09836065573770492</v>
       </c>
       <c r="V9" t="n">
-        <v>364.4126346226341</v>
+        <v>365.0199890136719</v>
       </c>
       <c r="W9" t="n">
-        <v>563.2397746482092</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="X9" t="n">
-        <v>454.301753942643</v>
+        <v>455.230791549968</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.910232273687</v>
+        <v>401.0142938009117</v>
       </c>
       <c r="Z9" t="n">
-        <v>508.693275611599</v>
+        <v>509.4472892990243</v>
       </c>
       <c r="AA9" t="n">
-        <v>376.0831861448368</v>
+        <v>377.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.087710731908</v>
+        <v>501.9228569164612</v>
       </c>
       <c r="AC9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -24866,57 +26193,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.77566214941169</v>
+        <v>71.70312487479084</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.76519890551299</v>
+        <v>69.76310042215344</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.048642351971177</v>
+        <v>8.05585740569148</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.05497221175226</v>
+        <v>62.06510844983554</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.37543771606209</v>
+        <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.205254467175562</v>
+        <v>-1.098523400940367</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1065573770491803</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.1695949264438</v>
+        <v>343.7415442513212</v>
       </c>
       <c r="AN9" t="n">
-        <v>563.2397746482092</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="AO9" t="n">
-        <v>430.6539728964701</v>
+        <v>430.9357804974929</v>
       </c>
       <c r="AP9" t="n">
-        <v>382.3621187846431</v>
+        <v>382.5200774892871</v>
       </c>
       <c r="AQ9" t="n">
-        <v>478.9458270082972</v>
+        <v>479.3514835056988</v>
       </c>
       <c r="AR9" t="n">
-        <v>372.3298332705136</v>
+        <v>373.0113017835116</v>
       </c>
       <c r="AS9" t="n">
-        <v>494.2526262963726</v>
+        <v>495.0014039751615</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30 03:43:40</t>
+          <t>2026-07-01 03:57:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24945,19 +26272,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.78</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.800001</v>
+        <v>23.032259</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -25000,7 +26327,7 @@
         <v>39.19169882069462</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.4365106359477703</v>
+        <v>-0.4947602328951907</v>
       </c>
       <c r="AL10" t="n">
         <v>0.1944444444444444</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS163"/>
+  <dimension ref="A1:AS172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23583,7 +23583,7 @@
         <v>36.47433523404396</v>
       </c>
       <c r="AK155" t="n">
-        <v>0.4469980915619369</v>
+        <v>0.4469980915619368</v>
       </c>
       <c r="AL155" t="n">
         <v>0.7073170731707317</v>
@@ -23674,7 +23674,7 @@
         <v>146.9803306704662</v>
       </c>
       <c r="Q156" t="n">
-        <v>30.00491680356031</v>
+        <v>30.0049168035603</v>
       </c>
       <c r="R156" t="n">
         <v>93.14339691737914</v>
@@ -23722,7 +23722,7 @@
         <v>115.256811005293</v>
       </c>
       <c r="AG156" t="n">
-        <v>110.1477862578895</v>
+        <v>110.1477862578894</v>
       </c>
       <c r="AH156" t="n">
         <v>35.73148960979601</v>
@@ -23755,7 +23755,7 @@
         <v>455.9846678575688</v>
       </c>
       <c r="AR156" t="n">
-        <v>228.0681149119251</v>
+        <v>228.0681149119252</v>
       </c>
       <c r="AS156" t="n">
         <v>512.599963979252</v>
@@ -23834,7 +23834,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T157" t="n">
-        <v>0.01698935482333459</v>
+        <v>0.0169893548233345</v>
       </c>
       <c r="U157" t="n">
         <v>0.4426229508196721</v>
@@ -23876,7 +23876,7 @@
         <v>30.85774058577406</v>
       </c>
       <c r="AH157" t="n">
-        <v>2.470952309836587</v>
+        <v>2.470952309836586</v>
       </c>
       <c r="AI157" t="n">
         <v>28.4770334052127</v>
@@ -23967,7 +23967,7 @@
         <v>60.73543910377236</v>
       </c>
       <c r="N158" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O158" t="n">
         <v>75.74555599833079</v>
@@ -23988,7 +23988,7 @@
         <v>-1.429099941840427</v>
       </c>
       <c r="U158" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="V158" t="n">
         <v>365.0199890136719</v>
@@ -24018,7 +24018,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE158" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF158" t="n">
         <v>71.70312487479084</v>
@@ -24281,7 +24281,7 @@
         <v>2.973891860300616</v>
       </c>
       <c r="R160" t="n">
-        <v>20.50363547585227</v>
+        <v>20.50363547585228</v>
       </c>
       <c r="S160" t="n">
         <v>28.57982234378326</v>
@@ -24290,7 +24290,7 @@
         <v>-1.013951718966264</v>
       </c>
       <c r="U160" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="V160" t="n">
         <v>542.6725878462358</v>
@@ -24332,7 +24332,7 @@
         <v>3.165659091676049</v>
       </c>
       <c r="AI160" t="n">
-        <v>21.26363725142046</v>
+        <v>21.26363725142045</v>
       </c>
       <c r="AJ160" t="n">
         <v>28.87781993334929</v>
@@ -24341,7 +24341,7 @@
         <v>-1.598140546691922</v>
       </c>
       <c r="AL160" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.048780487804878</v>
       </c>
       <c r="AM160" t="n">
         <v>542.6725878462358</v>
@@ -24426,7 +24426,7 @@
         <v>24.47555130761841</v>
       </c>
       <c r="P161" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q161" t="n">
         <v>1.480301428618054</v>
@@ -24435,13 +24435,13 @@
         <v>22.25833347865513</v>
       </c>
       <c r="S161" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T161" t="n">
         <v>-1.525877273338235</v>
       </c>
       <c r="U161" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="V161" t="n">
         <v>352.6199687231154</v>
@@ -24492,7 +24492,7 @@
         <v>-1.11068087989305</v>
       </c>
       <c r="AL161" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.048780487804878</v>
       </c>
       <c r="AM161" t="n">
         <v>352.6199687231154</v>
@@ -24587,19 +24587,19 @@
         <v>72</v>
       </c>
       <c r="AD162" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE162" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF162" t="n">
-        <v>29.55330344716235</v>
+        <v>29.55330344716234</v>
       </c>
       <c r="AG162" t="n">
         <v>33.84980213029581</v>
       </c>
       <c r="AH162" t="n">
-        <v>13.18021137026943</v>
+        <v>13.18021137026944</v>
       </c>
       <c r="AI162" t="n">
         <v>3.740434383688714</v>
@@ -24711,7 +24711,7 @@
         <v>-1.205133821001735</v>
       </c>
       <c r="U163" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="V163" t="n">
         <v>192.2351595774909</v>
@@ -24720,7 +24720,7 @@
         <v>313.6785379215162</v>
       </c>
       <c r="X163" t="n">
-        <v>242.3774518663082</v>
+        <v>242.3774518663081</v>
       </c>
       <c r="Y163" t="n">
         <v>207.2880260039107</v>
@@ -24762,7 +24762,7 @@
         <v>-1.385302568267248</v>
       </c>
       <c r="AL163" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.0689655172413793</v>
       </c>
       <c r="AM163" t="n">
         <v>192.2351595774909</v>
@@ -24774,7 +24774,7 @@
         <v>241.2394617218601</v>
       </c>
       <c r="AP163" t="n">
-        <v>211.5351468202207</v>
+        <v>211.5351468202208</v>
       </c>
       <c r="AQ163" t="n">
         <v>270.9437766234994</v>
@@ -24784,6 +24784,1333 @@
       </c>
       <c r="AS163" t="n">
         <v>284.7270663016183</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>294.38</v>
+      </c>
+      <c r="I164" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J164" t="n">
+        <v>35.59613</v>
+      </c>
+      <c r="K164" t="n">
+        <v>67</v>
+      </c>
+      <c r="L164" t="n">
+        <v>61</v>
+      </c>
+      <c r="M164" t="n">
+        <v>32.08860759493671</v>
+      </c>
+      <c r="N164" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O164" t="n">
+        <v>35.22218803287076</v>
+      </c>
+      <c r="P164" t="n">
+        <v>35.3002405051169</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>1.538143720081978</v>
+      </c>
+      <c r="R164" t="n">
+        <v>32.97341648536393</v>
+      </c>
+      <c r="S164" t="n">
+        <v>37.38741008767781</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0.2431125012877933</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0.5573770491803278</v>
+      </c>
+      <c r="V164" t="n">
+        <v>265.3727848101266</v>
+      </c>
+      <c r="W164" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="X164" t="n">
+        <v>291.2874950318412</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>278.5670464667633</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>304.0079435969191</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>272.6901543339596</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>309.1938814250955</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>34.33371731495804</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.637769911448881</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>36.47433523404396</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>0.7708119902661731</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>0.7723577235772358</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>283.939842194703</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>270.3954850270208</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>297.4841993623851</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>265.768482090431</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>301.6427523855435</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>540.88</v>
+      </c>
+      <c r="I165" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J165" t="n">
+        <v>182.11447</v>
+      </c>
+      <c r="K165" t="n">
+        <v>63</v>
+      </c>
+      <c r="L165" t="n">
+        <v>61</v>
+      </c>
+      <c r="M165" t="n">
+        <v>83.08678968897406</v>
+      </c>
+      <c r="N165" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O165" t="n">
+        <v>142.4228850265634</v>
+      </c>
+      <c r="P165" t="n">
+        <v>147.4065561763576</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>29.36656407995038</v>
+      </c>
+      <c r="R165" t="n">
+        <v>96.25283295253539</v>
+      </c>
+      <c r="S165" t="n">
+        <v>176.1868836449795</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.351591042975827</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0.9836065573770492</v>
+      </c>
+      <c r="V165" t="n">
+        <v>246.767765376253</v>
+      </c>
+      <c r="W165" t="n">
+        <v>565.6729902423797</v>
+      </c>
+      <c r="X165" t="n">
+        <v>422.9959685288934</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>335.7772732114407</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>510.214663846346</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>285.8709138690301</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>523.2750444255893</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>115.8035911847666</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>112.2758611669681</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>36.16364269973715</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>170.2983598552766</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.833633834008523</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>0.9918699186991869</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>214.0081097872752</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>565.6729902423797</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>343.936665818757</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>236.5306470005376</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>451.3426846369763</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>224.2921527445092</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>505.7861287701716</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="J166" t="n">
+        <v>31.636126</v>
+      </c>
+      <c r="K166" t="n">
+        <v>67</v>
+      </c>
+      <c r="L166" t="n">
+        <v>61</v>
+      </c>
+      <c r="M166" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N166" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O166" t="n">
+        <v>31.60337460791702</v>
+      </c>
+      <c r="P166" t="n">
+        <v>31.73325461063659</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>2.53820928506987</v>
+      </c>
+      <c r="R166" t="n">
+        <v>28.4688995215311</v>
+      </c>
+      <c r="S166" t="n">
+        <v>34.94560635405771</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0.01290334578619301</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0.4426229508196721</v>
+      </c>
+      <c r="V166" t="n">
+        <v>207.4588945014625</v>
+      </c>
+      <c r="W166" t="n">
+        <v>281.2947734157078</v>
+      </c>
+      <c r="X166" t="n">
+        <v>241.449782004486</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>222.0578630665522</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>260.8417009424198</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>217.5023923444976</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>266.9844325450009</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>31.20118516990215</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>30.68420921216171</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>2.478727653003602</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>0.1754693903425845</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>0.5447154471544715</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>207.4588945014625</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>281.2947734157078</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>238.3770546980524</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>219.4395754291049</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>257.314533967</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>217.564535215825</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>265.2326730980867</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>369.34</v>
+      </c>
+      <c r="I167" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J167" t="n">
+        <v>61.352158</v>
+      </c>
+      <c r="K167" t="n">
+        <v>34</v>
+      </c>
+      <c r="L167" t="n">
+        <v>61</v>
+      </c>
+      <c r="M167" t="n">
+        <v>60.73543910377236</v>
+      </c>
+      <c r="N167" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O167" t="n">
+        <v>75.74782575611718</v>
+      </c>
+      <c r="P167" t="n">
+        <v>79.03509009883652</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>9.017373408435702</v>
+      </c>
+      <c r="R167" t="n">
+        <v>62.85357737104825</v>
+      </c>
+      <c r="S167" t="n">
+        <v>83.514618455318</v>
+      </c>
+      <c r="T167" t="n">
+        <v>-1.596436911734199</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="V167" t="n">
+        <v>365.6273434047096</v>
+      </c>
+      <c r="W167" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X167" t="n">
+        <v>456.0019110518254</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>401.7173231330424</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>510.2864989706083</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>378.3785357737104</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>502.7580031010143</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>71.61026254202848</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>69.73794421309945</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>8.107887706903377</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>61.98633986788272</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>-1.265200618564848</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>431.0937805030114</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>382.2842965074531</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>479.9032644985698</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>373.1577660046539</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>495.8250335990802</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="I168" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>27.319847</v>
+      </c>
+      <c r="K168" t="n">
+        <v>37</v>
+      </c>
+      <c r="L168" t="n">
+        <v>61</v>
+      </c>
+      <c r="M168" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N168" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O168" t="n">
+        <v>28.9965558292287</v>
+      </c>
+      <c r="P168" t="n">
+        <v>29.2311213745769</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>1.648205024782476</v>
+      </c>
+      <c r="R168" t="n">
+        <v>26.95042008575277</v>
+      </c>
+      <c r="S168" t="n">
+        <v>31.24236919392489</v>
+      </c>
+      <c r="T168" t="n">
+        <v>-1.017293846346566</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0.1967213114754098</v>
+      </c>
+      <c r="V168" t="n">
+        <v>334.434708770589</v>
+      </c>
+      <c r="W168" t="n">
+        <v>422.3507729952915</v>
+      </c>
+      <c r="X168" t="n">
+        <v>379.854881362896</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>358.2633955382455</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>401.4463671875464</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>353.0505031233612</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>409.2750364404161</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>29.36734693249652</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>28.9580484094918</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>2.106916980459543</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>26.95057232447202</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>-0.9717990559124611</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>0.1626016260162602</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>446.0207226104586</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>384.7122448157044</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>357.1116323716843</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>412.3128572597244</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>353.0524974505834</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>427.7091759157322</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>612.91</v>
+      </c>
+      <c r="I169" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="J169" t="n">
+        <v>22.271437</v>
+      </c>
+      <c r="K169" t="n">
+        <v>55</v>
+      </c>
+      <c r="L169" t="n">
+        <v>61</v>
+      </c>
+      <c r="M169" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N169" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O169" t="n">
+        <v>23.47056677143422</v>
+      </c>
+      <c r="P169" t="n">
+        <v>22.25127175071023</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>2.975310117728943</v>
+      </c>
+      <c r="R169" t="n">
+        <v>20.50363547585227</v>
+      </c>
+      <c r="S169" t="n">
+        <v>28.57982234378326</v>
+      </c>
+      <c r="T169" t="n">
+        <v>-0.4030268187134441</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0.5245901639344263</v>
+      </c>
+      <c r="V169" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="W169" t="n">
+        <v>806.6792534722222</v>
+      </c>
+      <c r="X169" t="n">
+        <v>645.9099975498697</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>564.0294631099692</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>727.7905319897701</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>564.2600482954546</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>786.5167109009152</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>25.49690694130231</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>26.75138419107865</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>3.165274918874282</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>21.26363725142046</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>28.87781993334929</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>-1.019017312546563</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>0.2601626016260163</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>864.9762082934226</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>701.6748790246396</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>614.5665132572193</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>788.7832447920598</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>585.175297159091</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>794.7176045657725</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>384.28</v>
+      </c>
+      <c r="I170" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J170" t="n">
+        <v>22.887432</v>
+      </c>
+      <c r="K170" t="n">
+        <v>67</v>
+      </c>
+      <c r="L170" t="n">
+        <v>61</v>
+      </c>
+      <c r="M170" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N170" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O170" t="n">
+        <v>24.46764905484648</v>
+      </c>
+      <c r="P170" t="n">
+        <v>24.58473954668934</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>1.487646737525759</v>
+      </c>
+      <c r="R170" t="n">
+        <v>22.25833347865513</v>
+      </c>
+      <c r="S170" t="n">
+        <v>26.52657934096994</v>
+      </c>
+      <c r="T170" t="n">
+        <v>-1.062226007684245</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0.1639344262295082</v>
+      </c>
+      <c r="V170" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W170" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X170" t="n">
+        <v>410.8118276308724</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>385.8342389078149</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>435.7894163539298</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>373.7174191066197</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>445.3812671348853</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>34.38620207828614</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>25.77197699230665</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>24.97873693946901</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>3.213390511238094</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>22.92995622263915</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>32.44893319576258</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>-0.8976640038671363</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>0.1056910569105691</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>577.3443328944243</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>432.7114937008287</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>378.7586670171411</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>486.6643203845162</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>384.9939649781113</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>544.8175883568537</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="I171" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>23.93226</v>
+      </c>
+      <c r="K171" t="n">
+        <v>67</v>
+      </c>
+      <c r="L171" t="n">
+        <v>9</v>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
+      <c r="W171" t="inlineStr"/>
+      <c r="X171" t="inlineStr"/>
+      <c r="Y171" t="inlineStr"/>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr"/>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>29.91601544232707</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>33.87351658033287</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>12.9070530658301</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>3.736842067020579</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>39.19762773476098</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>-0.4636035361292781</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>0.1830985915492958</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>92.73964787121393</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>52.72778336714062</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>132.7515123752872</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>11.58421040776379</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>121.512645977759</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-07-02 02:49:13</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>197.58</v>
+      </c>
+      <c r="I172" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J172" t="n">
+        <v>30.30368</v>
+      </c>
+      <c r="K172" t="n">
+        <v>65</v>
+      </c>
+      <c r="L172" t="n">
+        <v>61</v>
+      </c>
+      <c r="M172" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N172" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O172" t="n">
+        <v>37.0770006226027</v>
+      </c>
+      <c r="P172" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>5.453068913605417</v>
+      </c>
+      <c r="R172" t="n">
+        <v>30.64165334424052</v>
+      </c>
+      <c r="S172" t="n">
+        <v>44.78367396763392</v>
+      </c>
+      <c r="T172" t="n">
+        <v>-1.242111686082539</v>
+      </c>
+      <c r="U172" t="n">
+        <v>0.06557377049180328</v>
+      </c>
+      <c r="V172" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="W172" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="X172" t="n">
+        <v>241.7420440593696</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>206.1880347426623</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>277.2960533760769</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>199.7835798044482</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>291.9895542689732</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>88</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>36.92329649834232</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>36.60510160485092</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>4.586290842119341</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>31.36355202924602</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>43.62836689851721</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>-1.44334860701581</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>240.7398931691919</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>210.8372768785738</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>270.64250945981</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>204.490359230684</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>284.4569521783322</v>
       </c>
     </row>
   </sheetData>
@@ -25030,12 +26357,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -25064,13 +26391,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>353.33</v>
+        <v>357.89</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="J2" t="n">
-        <v>26.951181</v>
+        <v>27.319847</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -25085,13 +26412,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.99558177465687</v>
+        <v>28.9965558292287</v>
       </c>
       <c r="P2" t="n">
         <v>29.2311213745769</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.649242190130955</v>
+        <v>1.648205024782476</v>
       </c>
       <c r="R2" t="n">
         <v>26.95042008575277</v>
@@ -25100,31 +26427,31 @@
         <v>31.24236919392489</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.239600094449766</v>
+        <v>-1.017293846346566</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1147540983606557</v>
+        <v>0.1967213114754098</v>
       </c>
       <c r="V2" t="n">
-        <v>334.6900024414062</v>
+        <v>334.434708770589</v>
       </c>
       <c r="W2" t="n">
-        <v>422.673178165517</v>
+        <v>422.3507729952915</v>
       </c>
       <c r="X2" t="n">
-        <v>380.1320770657516</v>
+        <v>379.854881362896</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.5105119531347</v>
+        <v>358.2633955382455</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.7536421783684</v>
+        <v>401.4463671875464</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.3200073242188</v>
+        <v>353.0505031233612</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.5874601323553</v>
+        <v>409.2750364404161</v>
       </c>
       <c r="AC2" t="n">
         <v>123</v>
@@ -25136,13 +26463,13 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.39847161327991</v>
+        <v>29.36734693249652</v>
       </c>
       <c r="AG2" t="n">
-        <v>29.11563276913737</v>
+        <v>28.9580484094918</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.104387525200074</v>
+        <v>2.106916980459543</v>
       </c>
       <c r="AI2" t="n">
         <v>26.95057232447202</v>
@@ -25151,42 +26478,42 @@
         <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.162946740547339</v>
+        <v>-0.9717990559124611</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1056910569105691</v>
+        <v>0.1626016260162602</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.002237918088</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.3611964445124</v>
+        <v>446.0207226104586</v>
       </c>
       <c r="AO2" t="n">
-        <v>385.4139628500996</v>
+        <v>384.7122448157044</v>
       </c>
       <c r="AP2" t="n">
-        <v>357.8254423947266</v>
+        <v>357.1116323716843</v>
       </c>
       <c r="AQ2" t="n">
-        <v>413.0024833054725</v>
+        <v>412.3128572597244</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.3220031738281</v>
+        <v>353.0524974505834</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.0356714698664</v>
+        <v>427.7091759157322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -25215,13 +26542,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>373.02</v>
+        <v>384.28</v>
       </c>
       <c r="I3" t="n">
         <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>22.216793</v>
+        <v>22.887432</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -25236,13 +26563,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.47555130761841</v>
+        <v>24.46764905484648</v>
       </c>
       <c r="P3" t="n">
         <v>24.58473954668934</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.480301428618054</v>
+        <v>1.487646737525759</v>
       </c>
       <c r="R3" t="n">
         <v>22.25833347865513</v>
@@ -25251,10 +26578,10 @@
         <v>26.52657934096994</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.525877273338235</v>
+        <v>-1.062226007684245</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.1639344262295082</v>
       </c>
       <c r="V3" t="n">
         <v>352.6199687231154</v>
@@ -25263,13 +26590,13 @@
         <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>410.9445064549131</v>
+        <v>410.8118276308724</v>
       </c>
       <c r="Y3" t="n">
-        <v>386.090245468416</v>
+        <v>385.8342389078149</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.7987674414102</v>
+        <v>435.7894163539298</v>
       </c>
       <c r="AA3" t="n">
         <v>373.7174191066197</v>
@@ -25287,25 +26614,25 @@
         <v>34.38620207828614</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.85948479369111</v>
+        <v>25.77197699230665</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.99061951866889</v>
+        <v>24.97873693946901</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.279692537825873</v>
+        <v>3.213390511238094</v>
       </c>
       <c r="AI3" t="n">
-        <v>23.11006871665396</v>
+        <v>22.92995622263915</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32.63413973248021</v>
+        <v>32.44893319576258</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1.11068087989305</v>
+        <v>-0.8976640038671363</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.1056910569105691</v>
       </c>
       <c r="AM3" t="n">
         <v>352.6199687231154</v>
@@ -25314,30 +26641,30 @@
         <v>577.3443328944243</v>
       </c>
       <c r="AO3" t="n">
-        <v>434.1807496860737</v>
+        <v>432.7114937008287</v>
       </c>
       <c r="AP3" t="n">
-        <v>379.1147119759773</v>
+        <v>378.7586670171411</v>
       </c>
       <c r="AQ3" t="n">
-        <v>489.2467873961701</v>
+        <v>486.6643203845162</v>
       </c>
       <c r="AR3" t="n">
-        <v>388.01805375262</v>
+        <v>384.9939649781113</v>
       </c>
       <c r="AS3" t="n">
-        <v>547.9272061083428</v>
+        <v>544.8175883568537</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -25366,13 +26693,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>563.29</v>
+        <v>612.91</v>
       </c>
       <c r="I4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="J4" t="n">
-        <v>20.490723</v>
+        <v>22.271437</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -25387,13 +26714,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.50610576377159</v>
+        <v>23.47056677143422</v>
       </c>
       <c r="P4" t="n">
         <v>22.25127175071023</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.973891860300616</v>
+        <v>2.975310117728943</v>
       </c>
       <c r="R4" t="n">
         <v>20.50363547585227</v>
@@ -25402,31 +26729,31 @@
         <v>28.57982234378326</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.013951718966264</v>
+        <v>-0.4030268187134441</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.5245901639344263</v>
       </c>
       <c r="V4" t="n">
-        <v>542.6725878462358</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="W4" t="n">
-        <v>805.7998792860242</v>
+        <v>806.6792534722222</v>
       </c>
       <c r="X4" t="n">
-        <v>646.1828474460809</v>
+        <v>645.9099975498697</v>
       </c>
       <c r="Y4" t="n">
-        <v>564.4305602064171</v>
+        <v>564.0294631099692</v>
       </c>
       <c r="Z4" t="n">
-        <v>727.9351346857449</v>
+        <v>727.7905319897701</v>
       </c>
       <c r="AA4" t="n">
-        <v>563.644939231179</v>
+        <v>564.2600482954546</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.6593162306017</v>
+        <v>786.5167109009152</v>
       </c>
       <c r="AC4" t="n">
         <v>123</v>
@@ -25438,13 +26765,13 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.54989115141141</v>
+        <v>25.49690694130231</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.75464991661592</v>
+        <v>26.75138419107865</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.165659091676049</v>
+        <v>3.165274918874282</v>
       </c>
       <c r="AI4" t="n">
         <v>21.26363725142046</v>
@@ -25453,42 +26780,42 @@
         <v>28.87781993334929</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.598140546691922</v>
+        <v>-1.019017312546563</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.2601626016260163</v>
       </c>
       <c r="AM4" t="n">
-        <v>542.6725878462358</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.0332836477539</v>
+        <v>864.9762082934226</v>
       </c>
       <c r="AO4" t="n">
-        <v>702.3665077522996</v>
+        <v>701.6748790246396</v>
       </c>
       <c r="AP4" t="n">
-        <v>615.3425393221252</v>
+        <v>614.5665132572193</v>
       </c>
       <c r="AQ4" t="n">
-        <v>789.3904761824742</v>
+        <v>788.7832447920598</v>
       </c>
       <c r="AR4" t="n">
-        <v>584.5373880415483</v>
+        <v>585.175297159091</v>
       </c>
       <c r="AS4" t="n">
-        <v>793.8512699677721</v>
+        <v>794.7176045657725</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -25517,13 +26844,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>238.34</v>
+        <v>241.7</v>
       </c>
       <c r="I5" t="n">
-        <v>7.53</v>
+        <v>7.64</v>
       </c>
       <c r="J5" t="n">
-        <v>31.652058</v>
+        <v>31.636126</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -25538,13 +26865,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.60903268222844</v>
+        <v>31.60337460791702</v>
       </c>
       <c r="P5" t="n">
         <v>31.73325461063659</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.532486855384522</v>
+        <v>2.53820928506987</v>
       </c>
       <c r="R5" t="n">
         <v>28.4688995215311</v>
@@ -25553,31 +26880,31 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01698935482333459</v>
+        <v>0.01290334578619301</v>
       </c>
       <c r="U5" t="n">
         <v>0.4426229508196721</v>
       </c>
       <c r="V5" t="n">
-        <v>204.4719208895305</v>
+        <v>207.4588945014625</v>
       </c>
       <c r="W5" t="n">
-        <v>277.2447177775235</v>
+        <v>281.2947734157078</v>
       </c>
       <c r="X5" t="n">
-        <v>238.0160160971802</v>
+        <v>241.449782004486</v>
       </c>
       <c r="Y5" t="n">
-        <v>218.9463900761347</v>
+        <v>222.0578630665522</v>
       </c>
       <c r="Z5" t="n">
-        <v>257.0856421182256</v>
+        <v>260.8417009424198</v>
       </c>
       <c r="AA5" t="n">
-        <v>214.3708133971292</v>
+        <v>217.5023923444976</v>
       </c>
       <c r="AB5" t="n">
-        <v>263.1404158460546</v>
+        <v>266.9844325450009</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -25589,13 +26916,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.22622616612316</v>
+        <v>31.20118516990215</v>
       </c>
       <c r="AG5" t="n">
-        <v>30.85774058577406</v>
+        <v>30.68420921216171</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.470952309836587</v>
+        <v>2.478727653003602</v>
       </c>
       <c r="AI5" t="n">
         <v>28.4770334052127</v>
@@ -25604,42 +26931,42 @@
         <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1723351082826053</v>
+        <v>0.1754693903425845</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5447154471544715</v>
       </c>
       <c r="AM5" t="n">
-        <v>204.4719208895305</v>
+        <v>207.4588945014625</v>
       </c>
       <c r="AN5" t="n">
-        <v>277.2447177775235</v>
+        <v>281.2947734157078</v>
       </c>
       <c r="AO5" t="n">
-        <v>235.1334830309074</v>
+        <v>238.3770546980524</v>
       </c>
       <c r="AP5" t="n">
-        <v>216.5272121378379</v>
+        <v>219.4395754291049</v>
       </c>
       <c r="AQ5" t="n">
-        <v>253.7397539239769</v>
+        <v>257.314533967</v>
       </c>
       <c r="AR5" t="n">
-        <v>214.4320615412516</v>
+        <v>217.564535215825</v>
       </c>
       <c r="AS5" t="n">
-        <v>261.4138780665697</v>
+        <v>265.2326730980867</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -25668,13 +26995,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>289.36</v>
+        <v>294.38</v>
       </c>
       <c r="I6" t="n">
-        <v>8.25</v>
+        <v>8.27</v>
       </c>
       <c r="J6" t="n">
-        <v>35.073936</v>
+        <v>35.59613</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -25689,46 +27016,46 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.16900296245017</v>
+        <v>35.22218803287076</v>
       </c>
       <c r="P6" t="n">
-        <v>35.24576330300393</v>
+        <v>35.3002405051169</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.579029498068575</v>
+        <v>1.538143720081978</v>
       </c>
       <c r="R6" t="n">
-        <v>32.97215328940862</v>
+        <v>32.97341648536393</v>
       </c>
       <c r="S6" t="n">
         <v>37.38741008767781</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0602059445795356</v>
+        <v>0.2431125012877933</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4754098360655737</v>
+        <v>0.5573770491803278</v>
       </c>
       <c r="V6" t="n">
-        <v>264.7310126582279</v>
+        <v>265.3727848101266</v>
       </c>
       <c r="W6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.5816102847638</v>
       </c>
       <c r="X6" t="n">
-        <v>290.1442744402139</v>
+        <v>291.2874950318412</v>
       </c>
       <c r="Y6" t="n">
-        <v>277.1172810811482</v>
+        <v>278.5670464667633</v>
       </c>
       <c r="Z6" t="n">
-        <v>303.1712677992796</v>
+        <v>304.0079435969191</v>
       </c>
       <c r="AA6" t="n">
-        <v>272.0202646376212</v>
+        <v>272.6901543339596</v>
       </c>
       <c r="AB6" t="n">
-        <v>308.446133223342</v>
+        <v>309.1938814250955</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -25740,13 +27067,13 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.33932051631486</v>
+        <v>34.33371731495804</v>
       </c>
       <c r="AG6" t="n">
         <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.643442103115445</v>
+        <v>1.637769911448881</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13645490815368</v>
@@ -25755,42 +27082,42 @@
         <v>36.47433523404396</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.4469980915619369</v>
+        <v>0.7708119902661731</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.7723577235772358</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.5566506687599</v>
+        <v>258.1810304279569</v>
       </c>
       <c r="AN6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.5816102847638</v>
       </c>
       <c r="AO6" t="n">
-        <v>283.2993942595976</v>
+        <v>283.939842194703</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.7409969088952</v>
+        <v>270.3954850270208</v>
       </c>
       <c r="AQ6" t="n">
-        <v>296.8577916103001</v>
+        <v>297.4841993623851</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.1257529922678</v>
+        <v>265.768482090431</v>
       </c>
       <c r="AS6" t="n">
-        <v>300.9132656808627</v>
+        <v>301.6427523855435</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -25819,13 +27146,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>200.09</v>
+        <v>197.58</v>
       </c>
       <c r="I7" t="n">
         <v>6.52</v>
       </c>
       <c r="J7" t="n">
-        <v>30.68865</v>
+        <v>30.30368</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -25840,25 +27167,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.17445580771598</v>
+        <v>37.0770006226027</v>
       </c>
       <c r="P7" t="n">
         <v>36.34694002112563</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.381813782576301</v>
+        <v>5.453068913605417</v>
       </c>
       <c r="R7" t="n">
-        <v>30.69218961239591</v>
+        <v>30.64165334424052</v>
       </c>
       <c r="S7" t="n">
         <v>44.78367396763392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.205133821001735</v>
+        <v>-1.242111686082539</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.06557377049180328</v>
       </c>
       <c r="V7" t="n">
         <v>192.2351595774909</v>
@@ -25867,22 +27194,22 @@
         <v>313.6785379215162</v>
       </c>
       <c r="X7" t="n">
-        <v>242.3774518663082</v>
+        <v>241.7420440593696</v>
       </c>
       <c r="Y7" t="n">
-        <v>207.2880260039107</v>
+        <v>206.1880347426623</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.4668777287056</v>
+        <v>277.2960533760769</v>
       </c>
       <c r="AA7" t="n">
-        <v>200.1130762728213</v>
+        <v>199.7835798044482</v>
       </c>
       <c r="AB7" t="n">
         <v>291.9895542689732</v>
       </c>
       <c r="AC7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -25891,25 +27218,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.99991744200308</v>
+        <v>36.92329649834232</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.74489858199139</v>
+        <v>36.60510160485092</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.555876518656343</v>
+        <v>4.586290842119341</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.39479352358106</v>
+        <v>31.36355202924602</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.66979544503348</v>
+        <v>43.62836689851721</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.385302568267248</v>
+        <v>-1.44334860701581</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="AM7" t="n">
         <v>192.2351595774909</v>
@@ -25918,30 +27245,30 @@
         <v>313.6785379215162</v>
       </c>
       <c r="AO7" t="n">
-        <v>241.2394617218601</v>
+        <v>240.7398931691919</v>
       </c>
       <c r="AP7" t="n">
-        <v>211.5351468202207</v>
+        <v>210.8372768785738</v>
       </c>
       <c r="AQ7" t="n">
-        <v>270.9437766234994</v>
+        <v>270.64250945981</v>
       </c>
       <c r="AR7" t="n">
-        <v>204.6940537737485</v>
+        <v>204.490359230684</v>
       </c>
       <c r="AS7" t="n">
-        <v>284.7270663016183</v>
+        <v>284.4569521783322</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -25970,13 +27297,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>580.91</v>
+        <v>540.88</v>
       </c>
       <c r="I8" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="J8" t="n">
-        <v>192.3543</v>
+        <v>182.11447</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -25985,52 +27312,52 @@
         <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>82.0754716981132</v>
+        <v>83.08678968897406</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>140.8612090458939</v>
+        <v>142.4228850265634</v>
       </c>
       <c r="P8" t="n">
-        <v>146.9803306704662</v>
+        <v>147.4065561763576</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.00491680356031</v>
+        <v>29.36656407995038</v>
       </c>
       <c r="R8" t="n">
-        <v>93.14339691737914</v>
+        <v>96.25283295253539</v>
       </c>
       <c r="S8" t="n">
-        <v>174.6131171554816</v>
+        <v>176.1868836449795</v>
       </c>
       <c r="T8" t="n">
-        <v>1.716155098553583</v>
+        <v>1.351591042975827</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0.9836065573770492</v>
       </c>
       <c r="V8" t="n">
-        <v>247.8679245283019</v>
+        <v>246.767765376253</v>
       </c>
       <c r="W8" t="n">
-        <v>575.1961045562244</v>
+        <v>565.6729902423797</v>
       </c>
       <c r="X8" t="n">
-        <v>425.4008513185996</v>
+        <v>422.9959685288934</v>
       </c>
       <c r="Y8" t="n">
-        <v>334.7860025718475</v>
+        <v>335.7772732114407</v>
       </c>
       <c r="Z8" t="n">
-        <v>516.0157000653517</v>
+        <v>510.214663846346</v>
       </c>
       <c r="AA8" t="n">
-        <v>281.293058690485</v>
+        <v>285.8709138690301</v>
       </c>
       <c r="AB8" t="n">
-        <v>527.3316138095544</v>
+        <v>523.2750444255893</v>
       </c>
       <c r="AC8" t="n">
         <v>123</v>
@@ -26042,57 +27369,57 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>115.256811005293</v>
+        <v>115.8035911847666</v>
       </c>
       <c r="AG8" t="n">
-        <v>110.1477862578895</v>
+        <v>112.2758611669681</v>
       </c>
       <c r="AH8" t="n">
-        <v>35.73148960979601</v>
+        <v>36.16364269973715</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>169.7350874103484</v>
+        <v>170.2983598552766</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.157690312848593</v>
+        <v>1.833633834008523</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0.9918699186991869</v>
       </c>
       <c r="AM8" t="n">
-        <v>217.6109399183741</v>
+        <v>214.0081097872752</v>
       </c>
       <c r="AN8" t="n">
-        <v>575.1961045562244</v>
+        <v>565.6729902423797</v>
       </c>
       <c r="AO8" t="n">
-        <v>348.0755692359849</v>
+        <v>343.936665818757</v>
       </c>
       <c r="AP8" t="n">
-        <v>240.1664706144009</v>
+        <v>236.5306470005376</v>
       </c>
       <c r="AQ8" t="n">
-        <v>455.9846678575688</v>
+        <v>451.3426846369763</v>
       </c>
       <c r="AR8" t="n">
-        <v>228.0681149119251</v>
+        <v>224.2921527445092</v>
       </c>
       <c r="AS8" t="n">
-        <v>512.599963979252</v>
+        <v>505.7861287701716</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -26121,13 +27448,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>377.75</v>
+        <v>369.34</v>
       </c>
       <c r="I9" t="n">
-        <v>6.01</v>
+        <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>62.853577</v>
+        <v>61.352158</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -26142,13 +27469,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.74555599833079</v>
+        <v>75.74782575611718</v>
       </c>
       <c r="P9" t="n">
         <v>79.03509009883652</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.021047878378754</v>
+        <v>9.017373408435702</v>
       </c>
       <c r="R9" t="n">
         <v>62.85357737104825</v>
@@ -26157,31 +27484,31 @@
         <v>83.514618455318</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.429099941840427</v>
+        <v>-1.596436911734199</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09836065573770492</v>
+        <v>0.03278688524590164</v>
       </c>
       <c r="V9" t="n">
-        <v>365.0199890136719</v>
+        <v>365.6273434047096</v>
       </c>
       <c r="W9" t="n">
-        <v>564.1785076059562</v>
+        <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>455.230791549968</v>
+        <v>456.0019110518254</v>
       </c>
       <c r="Y9" t="n">
-        <v>401.0142938009117</v>
+        <v>401.7173231330424</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.4472892990243</v>
+        <v>510.2864989706083</v>
       </c>
       <c r="AA9" t="n">
-        <v>377.75</v>
+        <v>378.3785357737104</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.9228569164612</v>
+        <v>502.7580031010143</v>
       </c>
       <c r="AC9" t="n">
         <v>123</v>
@@ -26193,57 +27520,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.70312487479084</v>
+        <v>71.61026254202848</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.76310042215344</v>
+        <v>69.73794421309945</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.05585740569148</v>
+        <v>8.107887706903377</v>
       </c>
       <c r="AI9" t="n">
-        <v>62.06510844983554</v>
+        <v>61.98633986788272</v>
       </c>
       <c r="AJ9" t="n">
         <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.098523400940367</v>
+        <v>-1.265200618564848</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.07317073170731707</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.7415442513212</v>
+        <v>344.3134935761985</v>
       </c>
       <c r="AN9" t="n">
-        <v>564.1785076059562</v>
+        <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>430.9357804974929</v>
+        <v>431.0937805030114</v>
       </c>
       <c r="AP9" t="n">
-        <v>382.5200774892871</v>
+        <v>382.2842965074531</v>
       </c>
       <c r="AQ9" t="n">
-        <v>479.3514835056988</v>
+        <v>479.9032644985698</v>
       </c>
       <c r="AR9" t="n">
-        <v>373.0113017835116</v>
+        <v>373.1577660046539</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.0014039751615</v>
+        <v>495.8250335990802</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-01 03:57:12</t>
+          <t>2026-07-02 02:49:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -26272,19 +27599,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>71.40000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.032259</v>
+        <v>23.93226</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -26303,7 +27630,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -26312,25 +27639,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>29.55330344716235</v>
+        <v>29.91601544232707</v>
       </c>
       <c r="AG10" t="n">
-        <v>33.84980213029581</v>
+        <v>33.87351658033287</v>
       </c>
       <c r="AH10" t="n">
-        <v>13.18021137026943</v>
+        <v>12.9070530658301</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.740434383688714</v>
+        <v>3.736842067020579</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.19169882069462</v>
+        <v>39.19762773476098</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.4947602328951907</v>
+        <v>-0.4636035361292781</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1944444444444444</v>
+        <v>0.1830985915492958</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -26339,19 +27666,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>91.61524068620328</v>
+        <v>92.73964787121393</v>
       </c>
       <c r="AP10" t="n">
-        <v>50.75658543836802</v>
+        <v>52.72778336714062</v>
       </c>
       <c r="AQ10" t="n">
-        <v>132.4738959340385</v>
+        <v>132.7515123752872</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.59534658943501</v>
+        <v>11.58421040776379</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.4942663441533</v>
+        <v>121.512645977759</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS172"/>
+  <dimension ref="A1:AS181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24931,10 +24931,10 @@
         <v>297.4841993623851</v>
       </c>
       <c r="AR164" t="n">
-        <v>265.768482090431</v>
+        <v>265.7684820904309</v>
       </c>
       <c r="AS164" t="n">
-        <v>301.6427523855435</v>
+        <v>301.6427523855436</v>
       </c>
     </row>
     <row r="165">
@@ -25004,7 +25004,7 @@
         <v>29.36656407995038</v>
       </c>
       <c r="R165" t="n">
-        <v>96.25283295253539</v>
+        <v>96.2528329525354</v>
       </c>
       <c r="S165" t="n">
         <v>176.1868836449795</v>
@@ -25025,7 +25025,7 @@
         <v>422.9959685288934</v>
       </c>
       <c r="Y165" t="n">
-        <v>335.7772732114407</v>
+        <v>335.7772732114408</v>
       </c>
       <c r="Z165" t="n">
         <v>510.214663846346</v>
@@ -25161,7 +25161,7 @@
         <v>34.94560635405771</v>
       </c>
       <c r="T166" t="n">
-        <v>0.01290334578619301</v>
+        <v>0.012903345786193</v>
       </c>
       <c r="U166" t="n">
         <v>0.4426229508196721</v>
@@ -25197,7 +25197,7 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF166" t="n">
-        <v>31.20118516990215</v>
+        <v>31.20118516990216</v>
       </c>
       <c r="AG166" t="n">
         <v>30.68420921216171</v>
@@ -25294,7 +25294,7 @@
         <v>60.73543910377236</v>
       </c>
       <c r="N167" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O167" t="n">
         <v>75.74782575611718</v>
@@ -25315,7 +25315,7 @@
         <v>-1.596436911734199</v>
       </c>
       <c r="U167" t="n">
-        <v>0.03278688524590164</v>
+        <v>0.0327868852459016</v>
       </c>
       <c r="V167" t="n">
         <v>365.6273434047096</v>
@@ -25345,7 +25345,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE167" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF167" t="n">
         <v>71.61026254202848</v>
@@ -25366,7 +25366,7 @@
         <v>-1.265200618564848</v>
       </c>
       <c r="AL167" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.073170731707317</v>
       </c>
       <c r="AM167" t="n">
         <v>344.3134935761985</v>
@@ -25472,7 +25472,7 @@
         <v>334.434708770589</v>
       </c>
       <c r="W168" t="n">
-        <v>422.3507729952915</v>
+        <v>422.3507729952916</v>
       </c>
       <c r="X168" t="n">
         <v>379.854881362896</v>
@@ -25505,7 +25505,7 @@
         <v>28.9580484094918</v>
       </c>
       <c r="AH168" t="n">
-        <v>2.106916980459543</v>
+        <v>2.106916980459544</v>
       </c>
       <c r="AI168" t="n">
         <v>26.95057232447202</v>
@@ -25514,10 +25514,10 @@
         <v>32.64955541341467</v>
       </c>
       <c r="AK168" t="n">
-        <v>-0.9717990559124611</v>
+        <v>-0.9717990559124612</v>
       </c>
       <c r="AL168" t="n">
-        <v>0.1626016260162602</v>
+        <v>0.1626016260162601</v>
       </c>
       <c r="AM168" t="n">
         <v>331.002237918088</v>
@@ -25608,7 +25608,7 @@
         <v>2.975310117728943</v>
       </c>
       <c r="R169" t="n">
-        <v>20.50363547585227</v>
+        <v>20.50363547585228</v>
       </c>
       <c r="S169" t="n">
         <v>28.57982234378326</v>
@@ -25659,7 +25659,7 @@
         <v>3.165274918874282</v>
       </c>
       <c r="AI169" t="n">
-        <v>21.26363725142046</v>
+        <v>21.26363725142045</v>
       </c>
       <c r="AJ169" t="n">
         <v>28.87781993334929</v>
@@ -25753,7 +25753,7 @@
         <v>24.46764905484648</v>
       </c>
       <c r="P170" t="n">
-        <v>24.58473954668934</v>
+        <v>24.58473954668933</v>
       </c>
       <c r="Q170" t="n">
         <v>1.487646737525759</v>
@@ -25762,13 +25762,13 @@
         <v>22.25833347865513</v>
       </c>
       <c r="S170" t="n">
-        <v>26.52657934096994</v>
+        <v>26.52657934096995</v>
       </c>
       <c r="T170" t="n">
         <v>-1.062226007684245</v>
       </c>
       <c r="U170" t="n">
-        <v>0.1639344262295082</v>
+        <v>0.1639344262295081</v>
       </c>
       <c r="V170" t="n">
         <v>352.6199687231154</v>
@@ -25914,13 +25914,13 @@
         <v>71</v>
       </c>
       <c r="AD171" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE171" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF171" t="n">
-        <v>29.91601544232707</v>
+        <v>29.91601544232708</v>
       </c>
       <c r="AG171" t="n">
         <v>33.87351658033287</v>
@@ -25929,16 +25929,16 @@
         <v>12.9070530658301</v>
       </c>
       <c r="AI171" t="n">
-        <v>3.736842067020579</v>
+        <v>3.736842067020578</v>
       </c>
       <c r="AJ171" t="n">
         <v>39.19762773476098</v>
       </c>
       <c r="AK171" t="n">
-        <v>-0.4636035361292781</v>
+        <v>-0.463603536129278</v>
       </c>
       <c r="AL171" t="n">
-        <v>0.1830985915492958</v>
+        <v>0.1830985915492957</v>
       </c>
       <c r="AM171" t="n">
         <v>10.81762752038992</v>
@@ -25947,7 +25947,7 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO171" t="n">
-        <v>92.73964787121393</v>
+        <v>92.73964787121392</v>
       </c>
       <c r="AP171" t="n">
         <v>52.72778336714062</v>
@@ -25956,7 +25956,7 @@
         <v>132.7515123752872</v>
       </c>
       <c r="AR171" t="n">
-        <v>11.58421040776379</v>
+        <v>11.5842104077638</v>
       </c>
       <c r="AS171" t="n">
         <v>121.512645977759</v>
@@ -26038,7 +26038,7 @@
         <v>-1.242111686082539</v>
       </c>
       <c r="U172" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.0655737704918032</v>
       </c>
       <c r="V172" t="n">
         <v>192.2351595774909</v>
@@ -26089,7 +26089,7 @@
         <v>-1.44334860701581</v>
       </c>
       <c r="AL172" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.0454545454545454</v>
       </c>
       <c r="AM172" t="n">
         <v>192.2351595774909</v>
@@ -26111,6 +26111,1333 @@
       </c>
       <c r="AS172" t="n">
         <v>284.4569521783322</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="I173" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J173" t="n">
+        <v>37.319225</v>
+      </c>
+      <c r="K173" t="n">
+        <v>67</v>
+      </c>
+      <c r="L173" t="n">
+        <v>62</v>
+      </c>
+      <c r="M173" t="n">
+        <v>32.08860759493671</v>
+      </c>
+      <c r="N173" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O173" t="n">
+        <v>35.25673995767608</v>
+      </c>
+      <c r="P173" t="n">
+        <v>35.36682683099558</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>1.549554415635675</v>
+      </c>
+      <c r="R173" t="n">
+        <v>33.00718856438788</v>
+      </c>
+      <c r="S173" t="n">
+        <v>37.38510981599008</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.3310181439984</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0.8548387096774194</v>
+      </c>
+      <c r="V173" t="n">
+        <v>265.3727848101266</v>
+      </c>
+      <c r="W173" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="X173" t="n">
+        <v>291.5732394499812</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>278.7584244326741</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>304.3880544672882</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>272.9694494274877</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>309.174858178238</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>34.35815836379547</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>34.36563375175731</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.653649384978973</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>32.14202455931072</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>36.56622307063881</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.790625427071523</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>0.9274193548387096</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>284.1419696685885</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>270.4662892548124</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>297.8176500823646</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>265.8145431054996</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>302.4026647941829</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>517.8200000000001</v>
+      </c>
+      <c r="I174" t="n">
+        <v>3</v>
+      </c>
+      <c r="J174" t="n">
+        <v>172.60667</v>
+      </c>
+      <c r="K174" t="n">
+        <v>63</v>
+      </c>
+      <c r="L174" t="n">
+        <v>62</v>
+      </c>
+      <c r="M174" t="n">
+        <v>83.08678968897406</v>
+      </c>
+      <c r="N174" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O174" t="n">
+        <v>142.8640812613239</v>
+      </c>
+      <c r="P174" t="n">
+        <v>147.4245915647413</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>29.33131461071225</v>
+      </c>
+      <c r="R174" t="n">
+        <v>96.36792683151533</v>
+      </c>
+      <c r="S174" t="n">
+        <v>176.0295069960297</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.014021673880708</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="V174" t="n">
+        <v>249.2603690669222</v>
+      </c>
+      <c r="W174" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="X174" t="n">
+        <v>428.5922437839716</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>340.5982999518349</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>516.5861876161084</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>289.103780494546</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>528.0885209880892</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>116.2388610266775</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>113.2389162561576</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>36.34101648219581</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>75.52037537772701</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>170.2442626953125</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.55107959076869</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>216.1698078659346</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>348.7165830800325</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>239.693533633445</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>457.73963252662</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>226.561126133181</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>510.7327880859375</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>242.67</v>
+      </c>
+      <c r="I175" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="J175" t="n">
+        <v>31.638851</v>
+      </c>
+      <c r="K175" t="n">
+        <v>67</v>
+      </c>
+      <c r="L175" t="n">
+        <v>62</v>
+      </c>
+      <c r="M175" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N175" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O175" t="n">
+        <v>31.56182843267153</v>
+      </c>
+      <c r="P175" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>2.538485526099796</v>
+      </c>
+      <c r="R175" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S175" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0.03034193677157169</v>
+      </c>
+      <c r="U175" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="V175" t="n">
+        <v>208.2735236683531</v>
+      </c>
+      <c r="W175" t="n">
+        <v>282.3993340443035</v>
+      </c>
+      <c r="X175" t="n">
+        <v>242.0792240785906</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>222.6090400934052</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>261.5494080637761</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>218.3876527740625</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>267.9632686130838</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>31.18365554548921</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>30.60988720311058</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>2.476336507625177</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>28.48110034705349</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>34.70906596802268</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>0.1838180930213433</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>208.2735236683531</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>282.3993340443035</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>239.1786380339022</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>220.1851370204171</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>258.1721390473873</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>218.4500396619003</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>266.218535974734</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="I176" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J176" t="n">
+        <v>59.875416</v>
+      </c>
+      <c r="K176" t="n">
+        <v>34</v>
+      </c>
+      <c r="L176" t="n">
+        <v>62</v>
+      </c>
+      <c r="M176" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N176" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O176" t="n">
+        <v>75.49342604438073</v>
+      </c>
+      <c r="P176" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>9.164748443552837</v>
+      </c>
+      <c r="R176" t="n">
+        <v>62.69783565883034</v>
+      </c>
+      <c r="S176" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T176" t="n">
+        <v>-1.70413952336767</v>
+      </c>
+      <c r="U176" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" t="n">
+        <v>361.0497626433158</v>
+      </c>
+      <c r="W176" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X176" t="n">
+        <v>454.470424787172</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>399.2986391569839</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>509.64221041736</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>377.4409706661586</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>502.6324388886986</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>71.51643013143517</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>69.73270440251574</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>8.142183349539311</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>61.93094973952918</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>82.35048706768551</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>-1.429716530774737</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>430.5289093912397</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>381.512965627013</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>479.5448531554663</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>372.8243174319656</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>495.7499321474667</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="I177" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J177" t="n">
+        <v>27.168573</v>
+      </c>
+      <c r="K177" t="n">
+        <v>37</v>
+      </c>
+      <c r="L177" t="n">
+        <v>62</v>
+      </c>
+      <c r="M177" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N177" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O177" t="n">
+        <v>28.96707223600337</v>
+      </c>
+      <c r="P177" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>1.651042461380934</v>
+      </c>
+      <c r="R177" t="n">
+        <v>26.95049620511239</v>
+      </c>
+      <c r="S177" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T177" t="n">
+        <v>-1.089311315772648</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0.1451612903225807</v>
+      </c>
+      <c r="V177" t="n">
+        <v>334.6900024414062</v>
+      </c>
+      <c r="W177" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X177" t="n">
+        <v>379.7583170140042</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>358.1131503453002</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>401.4034836827083</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>353.3210052490235</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>29.34961488505105</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>28.95774755253947</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>2.107604727712076</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>26.95064844383164</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>32.6446195792587</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>-1.034843894765171</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>0.1209677419354839</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>384.7734511430193</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>357.1427531627139</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>412.4041491233245</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>353.3230010986328</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>427.9709626840815</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="I178" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J178" t="n">
+        <v>21.18866</v>
+      </c>
+      <c r="K178" t="n">
+        <v>55</v>
+      </c>
+      <c r="L178" t="n">
+        <v>62</v>
+      </c>
+      <c r="M178" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N178" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O178" t="n">
+        <v>23.43388609002637</v>
+      </c>
+      <c r="P178" t="n">
+        <v>22.23854536576705</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>2.964922784976071</v>
+      </c>
+      <c r="R178" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S178" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T178" t="n">
+        <v>-0.7572629214505817</v>
+      </c>
+      <c r="U178" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V178" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="W178" t="n">
+        <v>806.3861287434895</v>
+      </c>
+      <c r="X178" t="n">
+        <v>644.6662063366256</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>563.1011805219339</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>726.2312321513173</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>564.3681262473367</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>786.1805475110751</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>25.46222514761558</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>26.73137562485033</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>3.17595038285713</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>21.21480091441762</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>28.87185984644396</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>-1.345601987576084</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>700.4658138109046</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>613.0954187785048</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>787.8362088433042</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>583.6191731556287</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>794.2648643756735</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="I179" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J179" t="n">
+        <v>23.257294</v>
+      </c>
+      <c r="K179" t="n">
+        <v>67</v>
+      </c>
+      <c r="L179" t="n">
+        <v>62</v>
+      </c>
+      <c r="M179" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N179" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O179" t="n">
+        <v>24.44790393782742</v>
+      </c>
+      <c r="P179" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>1.483571543147153</v>
+      </c>
+      <c r="R179" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S179" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T179" t="n">
+        <v>-0.8025295061279878</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="V179" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W179" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X179" t="n">
+        <v>410.4803071161224</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>385.5711409066817</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>435.3894733255631</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>374.2141233952839</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>445.2374133636685</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>34.38620207828614</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>25.75158566010793</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>24.96228502740982</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>3.208346668075609</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>22.95121947402429</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>32.43371260793585</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>-0.777438325143344</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>0.1532258064516129</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>577.3443328944243</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>432.3691232332121</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>378.5009826762227</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>486.2372637902016</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>385.3509749688678</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>544.5620346872429</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="I180" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>25.048388</v>
+      </c>
+      <c r="K180" t="n">
+        <v>67</v>
+      </c>
+      <c r="L180" t="n">
+        <v>9</v>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr"/>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>29.91601544232707</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>33.87351658033287</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>12.9070530658301</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>3.736842067020579</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>39.19762773476098</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>-0.3771292654876847</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>0.1830985915492958</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>92.73964787121393</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>52.72778336714062</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>132.7515123752872</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>11.58421040776379</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>121.512645977759</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-07-03 02:46:50</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>194.83</v>
+      </c>
+      <c r="I181" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J181" t="n">
+        <v>29.83614</v>
+      </c>
+      <c r="K181" t="n">
+        <v>65</v>
+      </c>
+      <c r="L181" t="n">
+        <v>62</v>
+      </c>
+      <c r="M181" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N181" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O181" t="n">
+        <v>36.96021256689322</v>
+      </c>
+      <c r="P181" t="n">
+        <v>36.30000056052694</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>5.485811855165738</v>
+      </c>
+      <c r="R181" t="n">
+        <v>30.63476165257405</v>
+      </c>
+      <c r="S181" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T181" t="n">
+        <v>-1.298635964006823</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="V181" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W181" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X181" t="n">
+        <v>241.3501880618127</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>205.5278366475804</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>277.172539476045</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>200.0449935913086</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>36.84366553958133</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>36.46530462771046</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>4.621622789810543</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>31.21041267243132</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>43.58693835200096</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>-1.516247832910785</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>240.5891359734661</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>210.4099391560032</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>270.768332790929</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>203.8039947509765</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>284.6227074385662</v>
       </c>
     </row>
   </sheetData>
@@ -26357,12 +27684,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -26391,19 +27718,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>357.89</v>
+        <v>356.18</v>
       </c>
       <c r="I2" t="n">
-        <v>13.1</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.319847</v>
+        <v>27.168573</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M2" t="n">
         <v>25.52936708172435</v>
@@ -26412,49 +27739,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.9965558292287</v>
+        <v>28.96707223600337</v>
       </c>
       <c r="P2" t="n">
-        <v>29.2311213745769</v>
+        <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.648205024782476</v>
+        <v>1.651042461380934</v>
       </c>
       <c r="R2" t="n">
-        <v>26.95042008575277</v>
+        <v>26.95049620511239</v>
       </c>
       <c r="S2" t="n">
-        <v>31.24236919392489</v>
+        <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.017293846346566</v>
+        <v>-1.089311315772648</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1967213114754098</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="V2" t="n">
-        <v>334.434708770589</v>
+        <v>334.6900024414062</v>
       </c>
       <c r="W2" t="n">
-        <v>422.3507729952915</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>379.854881362896</v>
+        <v>379.7583170140042</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.2633955382455</v>
+        <v>358.1131503453002</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.4463671875464</v>
+        <v>401.4034836827083</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.0505031233612</v>
+        <v>353.3210052490235</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.2750364404161</v>
+        <v>409.3048835916722</v>
       </c>
       <c r="AC2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -26463,57 +27790,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.36734693249652</v>
+        <v>29.34961488505105</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.9580484094918</v>
+        <v>28.95774755253947</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.106916980459543</v>
+        <v>2.107604727712076</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.95057232447202</v>
+        <v>26.95064844383164</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.64955541341467</v>
+        <v>32.6446195792587</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.9717990559124611</v>
+        <v>-1.034843894765171</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1626016260162602</v>
+        <v>0.1209677419354839</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.002237918088</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.0207226104586</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>384.7122448157044</v>
+        <v>384.7734511430193</v>
       </c>
       <c r="AP2" t="n">
-        <v>357.1116323716843</v>
+        <v>357.1427531627139</v>
       </c>
       <c r="AQ2" t="n">
-        <v>412.3128572597244</v>
+        <v>412.4041491233245</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.0524974505834</v>
+        <v>353.3230010986328</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.7091759157322</v>
+        <v>427.9709626840815</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -26542,19 +27869,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>384.28</v>
+        <v>390.49</v>
       </c>
       <c r="I3" t="n">
         <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>22.887432</v>
+        <v>23.257294</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
       </c>
       <c r="L3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M3" t="n">
         <v>21.00178491501581</v>
@@ -26563,25 +27890,25 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.46764905484648</v>
+        <v>24.44790393782742</v>
       </c>
       <c r="P3" t="n">
-        <v>24.58473954668934</v>
+        <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.487646737525759</v>
+        <v>1.483571543147153</v>
       </c>
       <c r="R3" t="n">
-        <v>22.25833347865513</v>
+        <v>22.28791681925455</v>
       </c>
       <c r="S3" t="n">
-        <v>26.52657934096994</v>
+        <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.062226007684245</v>
+        <v>-0.8025295061279878</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1639344262295082</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="V3" t="n">
         <v>352.6199687231154</v>
@@ -26590,22 +27917,22 @@
         <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>410.8118276308724</v>
+        <v>410.4803071161224</v>
       </c>
       <c r="Y3" t="n">
-        <v>385.8342389078149</v>
+        <v>385.5711409066817</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.7894163539298</v>
+        <v>435.3894733255631</v>
       </c>
       <c r="AA3" t="n">
-        <v>373.7174191066197</v>
+        <v>374.2141233952839</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.3812671348853</v>
+        <v>445.2374133636685</v>
       </c>
       <c r="AC3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD3" t="n">
         <v>21.00178491501581</v>
@@ -26614,25 +27941,25 @@
         <v>34.38620207828614</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.77197699230665</v>
+        <v>25.75158566010793</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.97873693946901</v>
+        <v>24.96228502740982</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.213390511238094</v>
+        <v>3.208346668075609</v>
       </c>
       <c r="AI3" t="n">
-        <v>22.92995622263915</v>
+        <v>22.95121947402429</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32.44893319576258</v>
+        <v>32.43371260793585</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8976640038671363</v>
+        <v>-0.777438325143344</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1056910569105691</v>
+        <v>0.1532258064516129</v>
       </c>
       <c r="AM3" t="n">
         <v>352.6199687231154</v>
@@ -26641,30 +27968,30 @@
         <v>577.3443328944243</v>
       </c>
       <c r="AO3" t="n">
-        <v>432.7114937008287</v>
+        <v>432.3691232332121</v>
       </c>
       <c r="AP3" t="n">
-        <v>378.7586670171411</v>
+        <v>378.5009826762227</v>
       </c>
       <c r="AQ3" t="n">
-        <v>486.6643203845162</v>
+        <v>486.2372637902016</v>
       </c>
       <c r="AR3" t="n">
-        <v>384.9939649781113</v>
+        <v>385.3509749688678</v>
       </c>
       <c r="AS3" t="n">
-        <v>544.8175883568537</v>
+        <v>544.5620346872429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -26693,19 +28020,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>612.91</v>
+        <v>582.9</v>
       </c>
       <c r="I4" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="J4" t="n">
-        <v>22.271437</v>
+        <v>21.18866</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
       </c>
       <c r="L4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
         <v>19.74072709517046</v>
@@ -26714,49 +28041,49 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.47056677143422</v>
+        <v>23.43388609002637</v>
       </c>
       <c r="P4" t="n">
-        <v>22.25127175071023</v>
+        <v>22.23854536576705</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.975310117728943</v>
+        <v>2.964922784976071</v>
       </c>
       <c r="R4" t="n">
-        <v>20.50363547585227</v>
+        <v>20.51501731178977</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57982234378326</v>
+        <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4030268187134441</v>
+        <v>-0.7572629214505817</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5245901639344263</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="V4" t="n">
-        <v>543.2648096590909</v>
+        <v>543.0674023881393</v>
       </c>
       <c r="W4" t="n">
-        <v>806.6792534722222</v>
+        <v>806.3861287434895</v>
       </c>
       <c r="X4" t="n">
-        <v>645.9099975498697</v>
+        <v>644.6662063366256</v>
       </c>
       <c r="Y4" t="n">
-        <v>564.0294631099692</v>
+        <v>563.1011805219339</v>
       </c>
       <c r="Z4" t="n">
-        <v>727.7905319897701</v>
+        <v>726.2312321513173</v>
       </c>
       <c r="AA4" t="n">
-        <v>564.2600482954546</v>
+        <v>564.3681262473367</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.5167109009152</v>
+        <v>786.1805475110751</v>
       </c>
       <c r="AC4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD4" t="n">
         <v>19.74072709517046</v>
@@ -26765,57 +28092,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.49690694130231</v>
+        <v>25.46222514761558</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.75138419107865</v>
+        <v>26.73137562485033</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.165274918874282</v>
+        <v>3.17595038285713</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.26363725142046</v>
+        <v>21.21480091441762</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28.87781993334929</v>
+        <v>28.87185984644396</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.019017312546563</v>
+        <v>-1.345601987576084</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.2601626016260163</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="AM4" t="n">
-        <v>543.2648096590909</v>
+        <v>543.0674023881393</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.9762082934226</v>
+        <v>864.6619000781998</v>
       </c>
       <c r="AO4" t="n">
-        <v>701.6748790246396</v>
+        <v>700.4658138109046</v>
       </c>
       <c r="AP4" t="n">
-        <v>614.5665132572193</v>
+        <v>613.0954187785048</v>
       </c>
       <c r="AQ4" t="n">
-        <v>788.7832447920598</v>
+        <v>787.8362088433042</v>
       </c>
       <c r="AR4" t="n">
-        <v>585.175297159091</v>
+        <v>583.6191731556287</v>
       </c>
       <c r="AS4" t="n">
-        <v>794.7176045657725</v>
+        <v>794.2648643756735</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -26844,19 +28171,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>241.7</v>
+        <v>242.67</v>
       </c>
       <c r="I5" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="J5" t="n">
-        <v>31.636126</v>
+        <v>31.638851</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M5" t="n">
         <v>27.15430556301865</v>
@@ -26865,49 +28192,49 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.60337460791702</v>
+        <v>31.56182843267153</v>
       </c>
       <c r="P5" t="n">
-        <v>31.73325461063659</v>
+        <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.53820928506987</v>
+        <v>2.538485526099796</v>
       </c>
       <c r="R5" t="n">
-        <v>28.4688995215311</v>
+        <v>28.4729664633719</v>
       </c>
       <c r="S5" t="n">
-        <v>34.94560635405771</v>
+        <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01290334578619301</v>
+        <v>0.03034193677157169</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4426229508196721</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="V5" t="n">
-        <v>207.4588945014625</v>
+        <v>208.2735236683531</v>
       </c>
       <c r="W5" t="n">
-        <v>281.2947734157078</v>
+        <v>282.3993340443035</v>
       </c>
       <c r="X5" t="n">
-        <v>241.449782004486</v>
+        <v>242.0792240785906</v>
       </c>
       <c r="Y5" t="n">
-        <v>222.0578630665522</v>
+        <v>222.6090400934052</v>
       </c>
       <c r="Z5" t="n">
-        <v>260.8417009424198</v>
+        <v>261.5494080637761</v>
       </c>
       <c r="AA5" t="n">
-        <v>217.5023923444976</v>
+        <v>218.3876527740625</v>
       </c>
       <c r="AB5" t="n">
-        <v>266.9844325450009</v>
+        <v>267.9632686130838</v>
       </c>
       <c r="AC5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD5" t="n">
         <v>27.15430556301865</v>
@@ -26916,57 +28243,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.20118516990215</v>
+        <v>31.18365554548921</v>
       </c>
       <c r="AG5" t="n">
-        <v>30.68420921216171</v>
+        <v>30.60988720311058</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.478727653003602</v>
+        <v>2.476336507625177</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.4770334052127</v>
+        <v>28.48110034705349</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.71631846833595</v>
+        <v>34.70906596802268</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1754693903425845</v>
+        <v>0.1838180930213433</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5447154471544715</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="AM5" t="n">
-        <v>207.4588945014625</v>
+        <v>208.2735236683531</v>
       </c>
       <c r="AN5" t="n">
-        <v>281.2947734157078</v>
+        <v>282.3993340443035</v>
       </c>
       <c r="AO5" t="n">
-        <v>238.3770546980524</v>
+        <v>239.1786380339022</v>
       </c>
       <c r="AP5" t="n">
-        <v>219.4395754291049</v>
+        <v>220.1851370204171</v>
       </c>
       <c r="AQ5" t="n">
-        <v>257.314533967</v>
+        <v>258.1721390473873</v>
       </c>
       <c r="AR5" t="n">
-        <v>217.564535215825</v>
+        <v>218.4500396619003</v>
       </c>
       <c r="AS5" t="n">
-        <v>265.2326730980867</v>
+        <v>266.218535974734</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -26995,19 +28322,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>294.38</v>
+        <v>308.63</v>
       </c>
       <c r="I6" t="n">
         <v>8.27</v>
       </c>
       <c r="J6" t="n">
-        <v>35.59613</v>
+        <v>37.319225</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
       </c>
       <c r="L6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M6" t="n">
         <v>32.08860759493671</v>
@@ -27016,25 +28343,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.22218803287076</v>
+        <v>35.25673995767608</v>
       </c>
       <c r="P6" t="n">
-        <v>35.3002405051169</v>
+        <v>35.36682683099558</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.538143720081978</v>
+        <v>1.549554415635675</v>
       </c>
       <c r="R6" t="n">
-        <v>32.97341648536393</v>
+        <v>33.00718856438788</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38741008767781</v>
+        <v>37.38510981599008</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2431125012877933</v>
+        <v>1.3310181439984</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5573770491803278</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="V6" t="n">
         <v>265.3727848101266</v>
@@ -27043,22 +28370,22 @@
         <v>315.5816102847638</v>
       </c>
       <c r="X6" t="n">
-        <v>291.2874950318412</v>
+        <v>291.5732394499812</v>
       </c>
       <c r="Y6" t="n">
-        <v>278.5670464667633</v>
+        <v>278.7584244326741</v>
       </c>
       <c r="Z6" t="n">
-        <v>304.0079435969191</v>
+        <v>304.3880544672882</v>
       </c>
       <c r="AA6" t="n">
-        <v>272.6901543339596</v>
+        <v>272.9694494274877</v>
       </c>
       <c r="AB6" t="n">
-        <v>309.1938814250955</v>
+        <v>309.174858178238</v>
       </c>
       <c r="AC6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -27067,25 +28394,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.33371731495804</v>
+        <v>34.35815836379547</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.35593205560495</v>
+        <v>34.36563375175731</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.637769911448881</v>
+        <v>1.653649384978973</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13645490815368</v>
+        <v>32.14202455931072</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.47433523404396</v>
+        <v>36.56622307063881</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.7708119902661731</v>
+        <v>1.790625427071523</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.7723577235772358</v>
+        <v>0.9274193548387096</v>
       </c>
       <c r="AM6" t="n">
         <v>258.1810304279569</v>
@@ -27094,30 +28421,30 @@
         <v>315.5816102847638</v>
       </c>
       <c r="AO6" t="n">
-        <v>283.939842194703</v>
+        <v>284.1419696685885</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.3954850270208</v>
+        <v>270.4662892548124</v>
       </c>
       <c r="AQ6" t="n">
-        <v>297.4841993623851</v>
+        <v>297.8176500823646</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.768482090431</v>
+        <v>265.8145431054996</v>
       </c>
       <c r="AS6" t="n">
-        <v>301.6427523855435</v>
+        <v>302.4026647941829</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -27146,19 +28473,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>197.58</v>
+        <v>194.83</v>
       </c>
       <c r="I7" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>30.30368</v>
+        <v>29.83614</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
         <v>29.48392018059676</v>
@@ -27167,49 +28494,49 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>37.0770006226027</v>
+        <v>36.96021256689322</v>
       </c>
       <c r="P7" t="n">
-        <v>36.34694002112563</v>
+        <v>36.30000056052694</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.453068913605417</v>
+        <v>5.485811855165738</v>
       </c>
       <c r="R7" t="n">
-        <v>30.64165334424052</v>
+        <v>30.63476165257405</v>
       </c>
       <c r="S7" t="n">
-        <v>44.78367396763392</v>
+        <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.242111686082539</v>
+        <v>-1.298635964006823</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06557377049180328</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="V7" t="n">
-        <v>192.2351595774909</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="W7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>241.7420440593696</v>
+        <v>241.3501880618127</v>
       </c>
       <c r="Y7" t="n">
-        <v>206.1880347426623</v>
+        <v>205.5278366475804</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.2960533760769</v>
+        <v>277.172539476045</v>
       </c>
       <c r="AA7" t="n">
-        <v>199.7835798044482</v>
+        <v>200.0449935913086</v>
       </c>
       <c r="AB7" t="n">
-        <v>291.9895542689732</v>
+        <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -27218,57 +28545,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.92329649834232</v>
+        <v>36.84366553958133</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.60510160485092</v>
+        <v>36.46530462771046</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.586290842119341</v>
+        <v>4.621622789810543</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.36355202924602</v>
+        <v>31.21041267243132</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.62836689851721</v>
+        <v>43.58693835200096</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.44334860701581</v>
+        <v>-1.516247832910785</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.01123595505617977</v>
       </c>
       <c r="AM7" t="n">
-        <v>192.2351595774909</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="AN7" t="n">
-        <v>313.6785379215162</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>240.7398931691919</v>
+        <v>240.5891359734661</v>
       </c>
       <c r="AP7" t="n">
-        <v>210.8372768785738</v>
+        <v>210.4099391560032</v>
       </c>
       <c r="AQ7" t="n">
-        <v>270.64250945981</v>
+        <v>270.768332790929</v>
       </c>
       <c r="AR7" t="n">
-        <v>204.490359230684</v>
+        <v>203.8039947509765</v>
       </c>
       <c r="AS7" t="n">
-        <v>284.4569521783322</v>
+        <v>284.6227074385662</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -27297,19 +28624,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>540.88</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>182.11447</v>
+        <v>172.60667</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
       </c>
       <c r="L8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
         <v>83.08678968897406</v>
@@ -27318,49 +28645,49 @@
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>142.4228850265634</v>
+        <v>142.8640812613239</v>
       </c>
       <c r="P8" t="n">
-        <v>147.4065561763576</v>
+        <v>147.4245915647413</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.36656407995038</v>
+        <v>29.33131461071225</v>
       </c>
       <c r="R8" t="n">
-        <v>96.25283295253539</v>
+        <v>96.36792683151533</v>
       </c>
       <c r="S8" t="n">
-        <v>176.1868836449795</v>
+        <v>176.0295069960297</v>
       </c>
       <c r="T8" t="n">
-        <v>1.351591042975827</v>
+        <v>1.014021673880708</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="V8" t="n">
-        <v>246.767765376253</v>
+        <v>249.2603690669222</v>
       </c>
       <c r="W8" t="n">
-        <v>565.6729902423797</v>
+        <v>571.3868588306865</v>
       </c>
       <c r="X8" t="n">
-        <v>422.9959685288934</v>
+        <v>428.5922437839716</v>
       </c>
       <c r="Y8" t="n">
-        <v>335.7772732114407</v>
+        <v>340.5982999518349</v>
       </c>
       <c r="Z8" t="n">
-        <v>510.214663846346</v>
+        <v>516.5861876161084</v>
       </c>
       <c r="AA8" t="n">
-        <v>285.8709138690301</v>
+        <v>289.103780494546</v>
       </c>
       <c r="AB8" t="n">
-        <v>523.2750444255893</v>
+        <v>528.0885209880892</v>
       </c>
       <c r="AC8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -27369,57 +28696,57 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>115.8035911847666</v>
+        <v>116.2388610266775</v>
       </c>
       <c r="AG8" t="n">
-        <v>112.2758611669681</v>
+        <v>113.2389162561576</v>
       </c>
       <c r="AH8" t="n">
-        <v>36.16364269973715</v>
+        <v>36.34101648219581</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51924334831958</v>
+        <v>75.52037537772701</v>
       </c>
       <c r="AJ8" t="n">
-        <v>170.2983598552766</v>
+        <v>170.2442626953125</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.833633834008523</v>
+        <v>1.55107959076869</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9918699186991869</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="AM8" t="n">
-        <v>214.0081097872752</v>
+        <v>216.1698078659346</v>
       </c>
       <c r="AN8" t="n">
-        <v>565.6729902423797</v>
+        <v>571.3868588306865</v>
       </c>
       <c r="AO8" t="n">
-        <v>343.936665818757</v>
+        <v>348.7165830800325</v>
       </c>
       <c r="AP8" t="n">
-        <v>236.5306470005376</v>
+        <v>239.693533633445</v>
       </c>
       <c r="AQ8" t="n">
-        <v>451.3426846369763</v>
+        <v>457.73963252662</v>
       </c>
       <c r="AR8" t="n">
-        <v>224.2921527445092</v>
+        <v>226.561126133181</v>
       </c>
       <c r="AS8" t="n">
-        <v>505.7861287701716</v>
+        <v>510.7327880859375</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -27448,70 +28775,70 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>369.34</v>
+        <v>360.45</v>
       </c>
       <c r="I9" t="n">
         <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>61.352158</v>
+        <v>59.875416</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M9" t="n">
-        <v>60.73543910377236</v>
+        <v>59.97504362845778</v>
       </c>
       <c r="N9" t="n">
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.74782575611718</v>
+        <v>75.49342604438073</v>
       </c>
       <c r="P9" t="n">
-        <v>79.03509009883652</v>
+        <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.017373408435702</v>
+        <v>9.164748443552837</v>
       </c>
       <c r="R9" t="n">
-        <v>62.85357737104825</v>
+        <v>62.69783565883034</v>
       </c>
       <c r="S9" t="n">
-        <v>83.514618455318</v>
+        <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.596436911734199</v>
+        <v>-1.70413952336767</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03278688524590164</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>365.6273434047096</v>
+        <v>361.0497626433158</v>
       </c>
       <c r="W9" t="n">
         <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>456.0019110518254</v>
+        <v>454.470424787172</v>
       </c>
       <c r="Y9" t="n">
-        <v>401.7173231330424</v>
+        <v>399.2986391569839</v>
       </c>
       <c r="Z9" t="n">
-        <v>510.2864989706083</v>
+        <v>509.64221041736</v>
       </c>
       <c r="AA9" t="n">
-        <v>378.3785357737104</v>
+        <v>377.4409706661586</v>
       </c>
       <c r="AB9" t="n">
-        <v>502.7580031010143</v>
+        <v>502.6324388886986</v>
       </c>
       <c r="AC9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -27520,25 +28847,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.61026254202848</v>
+        <v>71.51643013143517</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.73794421309945</v>
+        <v>69.73270440251574</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.107887706903377</v>
+        <v>8.142183349539311</v>
       </c>
       <c r="AI9" t="n">
-        <v>61.98633986788272</v>
+        <v>61.93094973952918</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.36296239187379</v>
+        <v>82.35048706768551</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.265200618564848</v>
+        <v>-1.429716530774737</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="AM9" t="n">
         <v>344.3134935761985</v>
@@ -27547,30 +28874,30 @@
         <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>431.0937805030114</v>
+        <v>430.5289093912397</v>
       </c>
       <c r="AP9" t="n">
-        <v>382.2842965074531</v>
+        <v>381.512965627013</v>
       </c>
       <c r="AQ9" t="n">
-        <v>479.9032644985698</v>
+        <v>479.5448531554663</v>
       </c>
       <c r="AR9" t="n">
-        <v>373.1577660046539</v>
+        <v>372.8243174319656</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.8250335990802</v>
+        <v>495.7499321474667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02 02:49:13</t>
+          <t>2026-07-03 02:46:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -27599,13 +28926,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>74.19</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.93226</v>
+        <v>25.048388</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
@@ -27654,7 +28981,7 @@
         <v>39.19762773476098</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.4636035361292781</v>
+        <v>-0.3771292654876847</v>
       </c>
       <c r="AL10" t="n">
         <v>0.1830985915492958</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS181"/>
+  <dimension ref="A1:AS190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25016,7 +25016,7 @@
         <v>0.9836065573770492</v>
       </c>
       <c r="V165" t="n">
-        <v>246.767765376253</v>
+        <v>246.7677653762529</v>
       </c>
       <c r="W165" t="n">
         <v>565.6729902423797</v>
@@ -26056,7 +26056,7 @@
         <v>277.2960533760769</v>
       </c>
       <c r="AA172" t="n">
-        <v>199.7835798044482</v>
+        <v>199.7835798044481</v>
       </c>
       <c r="AB172" t="n">
         <v>291.9895542689732</v>
@@ -26331,7 +26331,7 @@
         <v>29.33131461071225</v>
       </c>
       <c r="R174" t="n">
-        <v>96.36792683151533</v>
+        <v>96.36792683151532</v>
       </c>
       <c r="S174" t="n">
         <v>176.0295069960297</v>
@@ -26349,7 +26349,7 @@
         <v>571.3868588306865</v>
       </c>
       <c r="X174" t="n">
-        <v>428.5922437839716</v>
+        <v>428.5922437839717</v>
       </c>
       <c r="Y174" t="n">
         <v>340.5982999518349</v>
@@ -26388,10 +26388,10 @@
         <v>170.2442626953125</v>
       </c>
       <c r="AK174" t="n">
-        <v>1.55107959076869</v>
+        <v>1.551079590768691</v>
       </c>
       <c r="AL174" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="AM174" t="n">
         <v>216.1698078659346</v>
@@ -26476,7 +26476,7 @@
         <v>31.56182843267153</v>
       </c>
       <c r="P175" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q175" t="n">
         <v>2.538485526099796</v>
@@ -26488,7 +26488,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T175" t="n">
-        <v>0.03034193677157169</v>
+        <v>0.0303419367715716</v>
       </c>
       <c r="U175" t="n">
         <v>0.4516129032258064</v>
@@ -26621,7 +26621,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N176" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O176" t="n">
         <v>75.49342604438073</v>
@@ -26639,7 +26639,7 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T176" t="n">
-        <v>-1.70413952336767</v>
+        <v>-1.704139523367669</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -26657,7 +26657,7 @@
         <v>399.2986391569839</v>
       </c>
       <c r="Z176" t="n">
-        <v>509.64221041736</v>
+        <v>509.6422104173601</v>
       </c>
       <c r="AA176" t="n">
         <v>377.4409706661586</v>
@@ -26672,7 +26672,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE176" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF176" t="n">
         <v>71.51643013143517</v>
@@ -26693,7 +26693,7 @@
         <v>-1.429716530774737</v>
       </c>
       <c r="AL176" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="AM176" t="n">
         <v>344.3134935761985</v>
@@ -26708,7 +26708,7 @@
         <v>381.512965627013</v>
       </c>
       <c r="AQ176" t="n">
-        <v>479.5448531554663</v>
+        <v>479.5448531554664</v>
       </c>
       <c r="AR176" t="n">
         <v>372.8243174319656</v>
@@ -26784,7 +26784,7 @@
         <v>1.651042461380934</v>
       </c>
       <c r="R177" t="n">
-        <v>26.95049620511239</v>
+        <v>26.9504962051124</v>
       </c>
       <c r="S177" t="n">
         <v>31.22081491927324</v>
@@ -26793,7 +26793,7 @@
         <v>-1.089311315772648</v>
       </c>
       <c r="U177" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.1451612903225806</v>
       </c>
       <c r="V177" t="n">
         <v>334.6900024414062</v>
@@ -26808,7 +26808,7 @@
         <v>358.1131503453002</v>
       </c>
       <c r="Z177" t="n">
-        <v>401.4034836827083</v>
+        <v>401.4034836827082</v>
       </c>
       <c r="AA177" t="n">
         <v>353.3210052490235</v>
@@ -26829,7 +26829,7 @@
         <v>29.34961488505105</v>
       </c>
       <c r="AG177" t="n">
-        <v>28.95774755253947</v>
+        <v>28.95774755253946</v>
       </c>
       <c r="AH177" t="n">
         <v>2.107604727712076</v>
@@ -26844,7 +26844,7 @@
         <v>-1.034843894765171</v>
       </c>
       <c r="AL177" t="n">
-        <v>0.1209677419354839</v>
+        <v>0.1209677419354838</v>
       </c>
       <c r="AM177" t="n">
         <v>331.2549113821476</v>
@@ -26865,7 +26865,7 @@
         <v>353.3230010986328</v>
       </c>
       <c r="AS177" t="n">
-        <v>427.9709626840815</v>
+        <v>427.9709626840816</v>
       </c>
     </row>
     <row r="178">
@@ -26932,7 +26932,7 @@
         <v>22.23854536576705</v>
       </c>
       <c r="Q178" t="n">
-        <v>2.964922784976071</v>
+        <v>2.964922784976072</v>
       </c>
       <c r="R178" t="n">
         <v>20.51501731178977</v>
@@ -27241,13 +27241,13 @@
         <v>71</v>
       </c>
       <c r="AD180" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE180" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF180" t="n">
-        <v>29.91601544232707</v>
+        <v>29.91601544232708</v>
       </c>
       <c r="AG180" t="n">
         <v>33.87351658033287</v>
@@ -27256,16 +27256,16 @@
         <v>12.9070530658301</v>
       </c>
       <c r="AI180" t="n">
-        <v>3.736842067020579</v>
+        <v>3.736842067020578</v>
       </c>
       <c r="AJ180" t="n">
         <v>39.19762773476098</v>
       </c>
       <c r="AK180" t="n">
-        <v>-0.3771292654876847</v>
+        <v>-0.3771292654876846</v>
       </c>
       <c r="AL180" t="n">
-        <v>0.1830985915492958</v>
+        <v>0.1830985915492957</v>
       </c>
       <c r="AM180" t="n">
         <v>10.81762752038992</v>
@@ -27274,7 +27274,7 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO180" t="n">
-        <v>92.73964787121393</v>
+        <v>92.73964787121392</v>
       </c>
       <c r="AP180" t="n">
         <v>52.72778336714062</v>
@@ -27283,7 +27283,7 @@
         <v>132.7515123752872</v>
       </c>
       <c r="AR180" t="n">
-        <v>11.58421040776379</v>
+        <v>11.5842104077638</v>
       </c>
       <c r="AS180" t="n">
         <v>121.512645977759</v>
@@ -27362,10 +27362,10 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T181" t="n">
-        <v>-1.298635964006823</v>
+        <v>-1.298635964006824</v>
       </c>
       <c r="U181" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="V181" t="n">
         <v>192.5299987792968</v>
@@ -27374,7 +27374,7 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X181" t="n">
-        <v>241.3501880618127</v>
+        <v>241.3501880618128</v>
       </c>
       <c r="Y181" t="n">
         <v>205.5278366475804</v>
@@ -27416,7 +27416,7 @@
         <v>-1.516247832910785</v>
       </c>
       <c r="AL181" t="n">
-        <v>0.01123595505617977</v>
+        <v>0.0112359550561797</v>
       </c>
       <c r="AM181" t="n">
         <v>192.5299987792968</v>
@@ -27437,6 +27437,1333 @@
         <v>203.8039947509765</v>
       </c>
       <c r="AS181" t="n">
+        <v>284.6227074385662</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="I182" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J182" t="n">
+        <v>37.319225</v>
+      </c>
+      <c r="K182" t="n">
+        <v>67</v>
+      </c>
+      <c r="L182" t="n">
+        <v>62</v>
+      </c>
+      <c r="M182" t="n">
+        <v>32.08860759493671</v>
+      </c>
+      <c r="N182" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O182" t="n">
+        <v>35.25673995767608</v>
+      </c>
+      <c r="P182" t="n">
+        <v>35.36682683099558</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>1.549554415635675</v>
+      </c>
+      <c r="R182" t="n">
+        <v>33.00718856438788</v>
+      </c>
+      <c r="S182" t="n">
+        <v>37.38510981599008</v>
+      </c>
+      <c r="T182" t="n">
+        <v>1.3310181439984</v>
+      </c>
+      <c r="U182" t="n">
+        <v>0.8548387096774194</v>
+      </c>
+      <c r="V182" t="n">
+        <v>265.3727848101266</v>
+      </c>
+      <c r="W182" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="X182" t="n">
+        <v>291.5732394499812</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>278.7584244326741</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>304.3880544672882</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>272.9694494274877</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>309.174858178238</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>34.35815836379547</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>34.36563375175731</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.653649384978973</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>32.14202455931072</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>36.56622307063881</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.790625427071523</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>0.9274193548387096</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>284.1419696685885</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>270.4662892548124</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>297.8176500823646</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>265.8145431054996</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>302.4026647941829</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>517.8200000000001</v>
+      </c>
+      <c r="I183" t="n">
+        <v>3</v>
+      </c>
+      <c r="J183" t="n">
+        <v>172.60667</v>
+      </c>
+      <c r="K183" t="n">
+        <v>63</v>
+      </c>
+      <c r="L183" t="n">
+        <v>62</v>
+      </c>
+      <c r="M183" t="n">
+        <v>83.08678968897406</v>
+      </c>
+      <c r="N183" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O183" t="n">
+        <v>142.8640812613239</v>
+      </c>
+      <c r="P183" t="n">
+        <v>147.4245915647413</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>29.33131461071225</v>
+      </c>
+      <c r="R183" t="n">
+        <v>96.36792683151533</v>
+      </c>
+      <c r="S183" t="n">
+        <v>176.0295069960297</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1.014021673880708</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="V183" t="n">
+        <v>249.2603690669222</v>
+      </c>
+      <c r="W183" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="X183" t="n">
+        <v>428.5922437839716</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>340.5982999518349</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>516.5861876161084</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>289.103780494546</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>528.0885209880892</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>116.2388610266775</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>113.2389162561576</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>36.34101648219581</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>75.52037537772701</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>170.2442626953125</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.55107959076869</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>216.1698078659346</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>348.7165830800325</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>239.693533633445</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>457.73963252662</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>226.561126133181</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>510.7327880859375</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>242.67</v>
+      </c>
+      <c r="I184" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="J184" t="n">
+        <v>31.638851</v>
+      </c>
+      <c r="K184" t="n">
+        <v>67</v>
+      </c>
+      <c r="L184" t="n">
+        <v>62</v>
+      </c>
+      <c r="M184" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N184" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O184" t="n">
+        <v>31.56182843267153</v>
+      </c>
+      <c r="P184" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>2.538485526099796</v>
+      </c>
+      <c r="R184" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S184" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0.03034193677157169</v>
+      </c>
+      <c r="U184" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="V184" t="n">
+        <v>208.2735236683531</v>
+      </c>
+      <c r="W184" t="n">
+        <v>282.3993340443035</v>
+      </c>
+      <c r="X184" t="n">
+        <v>242.0792240785906</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>222.6090400934052</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>261.5494080637761</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>218.3876527740625</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>267.9632686130838</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>31.18365554548921</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>30.60988720311058</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>2.476336507625177</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>28.48110034705349</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>34.70906596802268</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>0.1838180930213433</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>208.2735236683531</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>282.3993340443035</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>239.1786380339022</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>220.1851370204171</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>258.1721390473873</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>218.4500396619003</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>266.218535974734</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="I185" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J185" t="n">
+        <v>59.875416</v>
+      </c>
+      <c r="K185" t="n">
+        <v>34</v>
+      </c>
+      <c r="L185" t="n">
+        <v>62</v>
+      </c>
+      <c r="M185" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N185" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O185" t="n">
+        <v>75.49342604438073</v>
+      </c>
+      <c r="P185" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>9.164748443552837</v>
+      </c>
+      <c r="R185" t="n">
+        <v>62.69783565883034</v>
+      </c>
+      <c r="S185" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T185" t="n">
+        <v>-1.70413952336767</v>
+      </c>
+      <c r="U185" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" t="n">
+        <v>361.0497626433158</v>
+      </c>
+      <c r="W185" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X185" t="n">
+        <v>454.470424787172</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>399.2986391569839</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>509.64221041736</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>377.4409706661586</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>502.6324388886986</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>71.51643013143517</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>69.73270440251574</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>8.142183349539311</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>61.93094973952918</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>82.35048706768551</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>-1.429716530774737</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>430.5289093912397</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>381.512965627013</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>479.5448531554663</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>372.8243174319656</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>495.7499321474667</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="I186" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J186" t="n">
+        <v>27.168573</v>
+      </c>
+      <c r="K186" t="n">
+        <v>37</v>
+      </c>
+      <c r="L186" t="n">
+        <v>62</v>
+      </c>
+      <c r="M186" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N186" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O186" t="n">
+        <v>28.96707223600337</v>
+      </c>
+      <c r="P186" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>1.651042461380934</v>
+      </c>
+      <c r="R186" t="n">
+        <v>26.95049620511239</v>
+      </c>
+      <c r="S186" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T186" t="n">
+        <v>-1.089311315772648</v>
+      </c>
+      <c r="U186" t="n">
+        <v>0.1451612903225807</v>
+      </c>
+      <c r="V186" t="n">
+        <v>334.6900024414062</v>
+      </c>
+      <c r="W186" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X186" t="n">
+        <v>379.7583170140042</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>358.1131503453002</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>401.4034836827083</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>353.3210052490235</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>29.34961488505105</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>28.95774755253947</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>2.107604727712076</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>26.95064844383164</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>32.6446195792587</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>-1.034843894765171</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>0.1209677419354839</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>384.7734511430193</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>357.1427531627139</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>412.4041491233245</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>353.3230010986328</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>427.9709626840815</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="I187" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J187" t="n">
+        <v>21.18866</v>
+      </c>
+      <c r="K187" t="n">
+        <v>55</v>
+      </c>
+      <c r="L187" t="n">
+        <v>62</v>
+      </c>
+      <c r="M187" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N187" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O187" t="n">
+        <v>23.43388609002637</v>
+      </c>
+      <c r="P187" t="n">
+        <v>22.23854536576705</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>2.964922784976071</v>
+      </c>
+      <c r="R187" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S187" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T187" t="n">
+        <v>-0.7572629214505817</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V187" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="W187" t="n">
+        <v>806.3861287434895</v>
+      </c>
+      <c r="X187" t="n">
+        <v>644.6662063366256</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>563.1011805219339</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>726.2312321513173</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>564.3681262473367</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>786.1805475110751</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>25.46222514761558</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>26.73137562485033</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>3.17595038285713</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>21.21480091441762</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>28.87185984644396</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>-1.345601987576084</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>700.4658138109046</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>613.0954187785048</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>787.8362088433042</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>583.6191731556287</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>794.2648643756735</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>390.49</v>
+      </c>
+      <c r="I188" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J188" t="n">
+        <v>23.257294</v>
+      </c>
+      <c r="K188" t="n">
+        <v>67</v>
+      </c>
+      <c r="L188" t="n">
+        <v>62</v>
+      </c>
+      <c r="M188" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N188" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O188" t="n">
+        <v>24.44790393782742</v>
+      </c>
+      <c r="P188" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>1.483571543147153</v>
+      </c>
+      <c r="R188" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S188" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T188" t="n">
+        <v>-0.8025295061279878</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="V188" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W188" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X188" t="n">
+        <v>410.4803071161224</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>385.5711409066817</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>435.3894733255631</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>374.2141233952839</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>445.2374133636685</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>34.38620207828614</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>25.75158566010793</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>24.96228502740982</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>3.208346668075609</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>22.95121947402429</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>32.43371260793585</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>-0.777438325143344</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>0.1532258064516129</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>577.3443328944243</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>432.3691232332121</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>378.5009826762227</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>486.2372637902016</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>385.3509749688678</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>544.5620346872429</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="I189" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>25.048388</v>
+      </c>
+      <c r="K189" t="n">
+        <v>67</v>
+      </c>
+      <c r="L189" t="n">
+        <v>9</v>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>29.91601544232707</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>33.87351658033287</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>12.9070530658301</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>3.736842067020579</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>39.19762773476098</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>-0.3771292654876847</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>0.1830985915492958</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>92.73964787121393</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>52.72778336714062</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>132.7515123752872</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>11.58421040776379</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>121.512645977759</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-07-04 01:13:41</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>194.83</v>
+      </c>
+      <c r="I190" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J190" t="n">
+        <v>29.83614</v>
+      </c>
+      <c r="K190" t="n">
+        <v>65</v>
+      </c>
+      <c r="L190" t="n">
+        <v>62</v>
+      </c>
+      <c r="M190" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N190" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O190" t="n">
+        <v>36.96021256689322</v>
+      </c>
+      <c r="P190" t="n">
+        <v>36.30000056052694</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>5.485811855165738</v>
+      </c>
+      <c r="R190" t="n">
+        <v>30.63476165257405</v>
+      </c>
+      <c r="S190" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T190" t="n">
+        <v>-1.298635964006823</v>
+      </c>
+      <c r="U190" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="V190" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W190" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X190" t="n">
+        <v>241.3501880618127</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>205.5278366475804</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>277.172539476045</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>200.0449935913086</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>36.84366553958133</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>36.46530462771046</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>4.621622789810543</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>31.21041267243132</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>43.58693835200096</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>-1.516247832910785</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>240.5891359734661</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>210.4099391560032</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>270.768332790929</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>203.8039947509765</v>
+      </c>
+      <c r="AS190" t="n">
         <v>284.6227074385662</v>
       </c>
     </row>
@@ -27684,12 +29011,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -27835,12 +29162,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -27986,12 +29313,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -28137,12 +29464,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -28288,12 +29615,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -28439,12 +29766,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -28590,12 +29917,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -28741,12 +30068,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -28892,12 +30219,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 02:46:50</t>
+          <t>2026-07-04 01:13:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS190"/>
+  <dimension ref="A1:AS199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26343,7 +26343,7 @@
         <v>0.8709677419354839</v>
       </c>
       <c r="V174" t="n">
-        <v>249.2603690669222</v>
+        <v>249.2603690669221</v>
       </c>
       <c r="W174" t="n">
         <v>571.3868588306865</v>
@@ -27383,7 +27383,7 @@
         <v>277.172539476045</v>
       </c>
       <c r="AA181" t="n">
-        <v>200.0449935913086</v>
+        <v>200.0449935913085</v>
       </c>
       <c r="AB181" t="n">
         <v>292.0602499483069</v>
@@ -27658,7 +27658,7 @@
         <v>29.33131461071225</v>
       </c>
       <c r="R183" t="n">
-        <v>96.36792683151533</v>
+        <v>96.36792683151532</v>
       </c>
       <c r="S183" t="n">
         <v>176.0295069960297</v>
@@ -27676,7 +27676,7 @@
         <v>571.3868588306865</v>
       </c>
       <c r="X183" t="n">
-        <v>428.5922437839716</v>
+        <v>428.5922437839717</v>
       </c>
       <c r="Y183" t="n">
         <v>340.5982999518349</v>
@@ -27715,10 +27715,10 @@
         <v>170.2442626953125</v>
       </c>
       <c r="AK183" t="n">
-        <v>1.55107959076869</v>
+        <v>1.551079590768691</v>
       </c>
       <c r="AL183" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="AM183" t="n">
         <v>216.1698078659346</v>
@@ -27803,7 +27803,7 @@
         <v>31.56182843267153</v>
       </c>
       <c r="P184" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q184" t="n">
         <v>2.538485526099796</v>
@@ -27815,7 +27815,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T184" t="n">
-        <v>0.03034193677157169</v>
+        <v>0.0303419367715716</v>
       </c>
       <c r="U184" t="n">
         <v>0.4516129032258064</v>
@@ -27948,7 +27948,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N185" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O185" t="n">
         <v>75.49342604438073</v>
@@ -27966,7 +27966,7 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T185" t="n">
-        <v>-1.70413952336767</v>
+        <v>-1.704139523367669</v>
       </c>
       <c r="U185" t="n">
         <v>0</v>
@@ -27984,7 +27984,7 @@
         <v>399.2986391569839</v>
       </c>
       <c r="Z185" t="n">
-        <v>509.64221041736</v>
+        <v>509.6422104173601</v>
       </c>
       <c r="AA185" t="n">
         <v>377.4409706661586</v>
@@ -27999,7 +27999,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE185" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF185" t="n">
         <v>71.51643013143517</v>
@@ -28020,7 +28020,7 @@
         <v>-1.429716530774737</v>
       </c>
       <c r="AL185" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="AM185" t="n">
         <v>344.3134935761985</v>
@@ -28035,7 +28035,7 @@
         <v>381.512965627013</v>
       </c>
       <c r="AQ185" t="n">
-        <v>479.5448531554663</v>
+        <v>479.5448531554664</v>
       </c>
       <c r="AR185" t="n">
         <v>372.8243174319656</v>
@@ -28111,7 +28111,7 @@
         <v>1.651042461380934</v>
       </c>
       <c r="R186" t="n">
-        <v>26.95049620511239</v>
+        <v>26.9504962051124</v>
       </c>
       <c r="S186" t="n">
         <v>31.22081491927324</v>
@@ -28120,7 +28120,7 @@
         <v>-1.089311315772648</v>
       </c>
       <c r="U186" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.1451612903225806</v>
       </c>
       <c r="V186" t="n">
         <v>334.6900024414062</v>
@@ -28135,7 +28135,7 @@
         <v>358.1131503453002</v>
       </c>
       <c r="Z186" t="n">
-        <v>401.4034836827083</v>
+        <v>401.4034836827082</v>
       </c>
       <c r="AA186" t="n">
         <v>353.3210052490235</v>
@@ -28156,7 +28156,7 @@
         <v>29.34961488505105</v>
       </c>
       <c r="AG186" t="n">
-        <v>28.95774755253947</v>
+        <v>28.95774755253946</v>
       </c>
       <c r="AH186" t="n">
         <v>2.107604727712076</v>
@@ -28171,7 +28171,7 @@
         <v>-1.034843894765171</v>
       </c>
       <c r="AL186" t="n">
-        <v>0.1209677419354839</v>
+        <v>0.1209677419354838</v>
       </c>
       <c r="AM186" t="n">
         <v>331.2549113821476</v>
@@ -28192,7 +28192,7 @@
         <v>353.3230010986328</v>
       </c>
       <c r="AS186" t="n">
-        <v>427.9709626840815</v>
+        <v>427.9709626840816</v>
       </c>
     </row>
     <row r="187">
@@ -28259,7 +28259,7 @@
         <v>22.23854536576705</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.964922784976071</v>
+        <v>2.964922784976072</v>
       </c>
       <c r="R187" t="n">
         <v>20.51501731178977</v>
@@ -28568,13 +28568,13 @@
         <v>71</v>
       </c>
       <c r="AD189" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE189" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF189" t="n">
-        <v>29.91601544232707</v>
+        <v>29.91601544232708</v>
       </c>
       <c r="AG189" t="n">
         <v>33.87351658033287</v>
@@ -28583,16 +28583,16 @@
         <v>12.9070530658301</v>
       </c>
       <c r="AI189" t="n">
-        <v>3.736842067020579</v>
+        <v>3.736842067020578</v>
       </c>
       <c r="AJ189" t="n">
         <v>39.19762773476098</v>
       </c>
       <c r="AK189" t="n">
-        <v>-0.3771292654876847</v>
+        <v>-0.3771292654876846</v>
       </c>
       <c r="AL189" t="n">
-        <v>0.1830985915492958</v>
+        <v>0.1830985915492957</v>
       </c>
       <c r="AM189" t="n">
         <v>10.81762752038992</v>
@@ -28601,7 +28601,7 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO189" t="n">
-        <v>92.73964787121393</v>
+        <v>92.73964787121392</v>
       </c>
       <c r="AP189" t="n">
         <v>52.72778336714062</v>
@@ -28610,7 +28610,7 @@
         <v>132.7515123752872</v>
       </c>
       <c r="AR189" t="n">
-        <v>11.58421040776379</v>
+        <v>11.5842104077638</v>
       </c>
       <c r="AS189" t="n">
         <v>121.512645977759</v>
@@ -28689,10 +28689,10 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T190" t="n">
-        <v>-1.298635964006823</v>
+        <v>-1.298635964006824</v>
       </c>
       <c r="U190" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.0161290322580645</v>
       </c>
       <c r="V190" t="n">
         <v>192.5299987792968</v>
@@ -28701,7 +28701,7 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X190" t="n">
-        <v>241.3501880618127</v>
+        <v>241.3501880618128</v>
       </c>
       <c r="Y190" t="n">
         <v>205.5278366475804</v>
@@ -28743,7 +28743,7 @@
         <v>-1.516247832910785</v>
       </c>
       <c r="AL190" t="n">
-        <v>0.01123595505617977</v>
+        <v>0.0112359550561797</v>
       </c>
       <c r="AM190" t="n">
         <v>192.5299987792968</v>
@@ -28765,6 +28765,1333 @@
       </c>
       <c r="AS190" t="n">
         <v>284.6227074385662</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>312.66</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J191" t="n">
+        <v>37.806526</v>
+      </c>
+      <c r="K191" t="n">
+        <v>67</v>
+      </c>
+      <c r="L191" t="n">
+        <v>62</v>
+      </c>
+      <c r="M191" t="n">
+        <v>32.08860759493671</v>
+      </c>
+      <c r="N191" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O191" t="n">
+        <v>35.33875953722645</v>
+      </c>
+      <c r="P191" t="n">
+        <v>35.45762586247257</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>1.55019685377843</v>
+      </c>
+      <c r="R191" t="n">
+        <v>33.31420068597328</v>
+      </c>
+      <c r="S191" t="n">
+        <v>37.54431108008286</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.591905219494314</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0.9516129032258065</v>
+      </c>
+      <c r="V191" t="n">
+        <v>265.3727848101266</v>
+      </c>
+      <c r="W191" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="X191" t="n">
+        <v>292.2515413728627</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>279.4314133921151</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>305.0716693536103</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>275.508439672999</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>310.4914526322852</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>34.36804309252805</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.683420464557244</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>36.85738404207022</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>2.042557388285224</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>0.975609756097561</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>315.5816102847638</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>284.223716375207</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>270.3018291333186</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>298.1456036170954</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>265.768482090431</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>304.8105660279207</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>552.05</v>
+      </c>
+      <c r="I192" t="n">
+        <v>3</v>
+      </c>
+      <c r="J192" t="n">
+        <v>184.01666</v>
+      </c>
+      <c r="K192" t="n">
+        <v>63</v>
+      </c>
+      <c r="L192" t="n">
+        <v>62</v>
+      </c>
+      <c r="M192" t="n">
+        <v>83.59622595445165</v>
+      </c>
+      <c r="N192" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O192" t="n">
+        <v>144.4433265243678</v>
+      </c>
+      <c r="P192" t="n">
+        <v>147.8852469022157</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>28.68891413876551</v>
+      </c>
+      <c r="R192" t="n">
+        <v>98.03886672685732</v>
+      </c>
+      <c r="S192" t="n">
+        <v>176.8124559746414</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.379394608113079</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V192" t="n">
+        <v>250.788677863355</v>
+      </c>
+      <c r="W192" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="X192" t="n">
+        <v>433.3299795731033</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>347.2632371568068</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>519.3967219893998</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>294.1166001805719</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>530.4373679239243</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>116.9115546540751</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>114.2463045167218</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>36.93298672151382</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>170.4354027920082</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.816942286631683</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>0.9918699186991869</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>216.1698078659346</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>350.7346639622253</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>239.9357037976838</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>461.5336241267667</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>226.5577300449587</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>511.3062083760246</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>244.16</v>
+      </c>
+      <c r="I193" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="J193" t="n">
+        <v>31.833117</v>
+      </c>
+      <c r="K193" t="n">
+        <v>67</v>
+      </c>
+      <c r="L193" t="n">
+        <v>62</v>
+      </c>
+      <c r="M193" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N193" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O193" t="n">
+        <v>31.55421421869486</v>
+      </c>
+      <c r="P193" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>2.544929088395211</v>
+      </c>
+      <c r="R193" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S193" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0.1095915727384818</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0.532258064516129</v>
+      </c>
+      <c r="V193" t="n">
+        <v>208.2735236683531</v>
+      </c>
+      <c r="W193" t="n">
+        <v>282.3993340443035</v>
+      </c>
+      <c r="X193" t="n">
+        <v>242.0208230573896</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>222.5012169493983</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>261.5404291653809</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>218.3876527740625</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>267.9632686130838</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>31.13033569895804</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>30.35765469929818</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>2.473996425543746</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>0.2840672257186058</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>0.6016260162601627</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>208.2735236683531</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>282.3993340443035</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>238.7696748110082</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>219.7941222270877</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>257.7452273949287</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>218.4188462179814</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>266.2741626521367</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="I194" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J194" t="n">
+        <v>62.109634</v>
+      </c>
+      <c r="K194" t="n">
+        <v>34</v>
+      </c>
+      <c r="L194" t="n">
+        <v>62</v>
+      </c>
+      <c r="M194" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N194" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O194" t="n">
+        <v>75.50827412697312</v>
+      </c>
+      <c r="P194" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>9.142081458394216</v>
+      </c>
+      <c r="R194" t="n">
+        <v>62.69783565883034</v>
+      </c>
+      <c r="S194" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T194" t="n">
+        <v>-1.465600606158519</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="V194" t="n">
+        <v>361.0497626433158</v>
+      </c>
+      <c r="W194" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X194" t="n">
+        <v>454.5598102443781</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>399.524479864845</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>509.5951406239113</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>377.4409706661586</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>502.6324388886986</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>71.43240100505803</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>69.71488648740501</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>8.218059790012594</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>61.92512601068532</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>-1.134424334121782</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0.1219512195121951</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>430.0230540504493</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>380.5503341145734</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>479.495773986325</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>372.7892585843256</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>495.8250335990802</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="I195" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J195" t="n">
+        <v>27.833715</v>
+      </c>
+      <c r="K195" t="n">
+        <v>37</v>
+      </c>
+      <c r="L195" t="n">
+        <v>62</v>
+      </c>
+      <c r="M195" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N195" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O195" t="n">
+        <v>28.97188028029558</v>
+      </c>
+      <c r="P195" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>1.647235201966106</v>
+      </c>
+      <c r="R195" t="n">
+        <v>26.95049620511239</v>
+      </c>
+      <c r="S195" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T195" t="n">
+        <v>-0.690954927952659</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="V195" t="n">
+        <v>334.6900024414062</v>
+      </c>
+      <c r="W195" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X195" t="n">
+        <v>379.821350474675</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>358.2260969768993</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>401.4166039724506</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>353.3210052490235</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>29.30739715383484</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>28.9382154754243</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>2.107067210226951</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>26.95057232447202</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>-0.6993996900915709</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>384.2199766867748</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>356.5963255606994</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>411.8436278128501</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>353.3220031738281</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>428.0356714698664</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>600.29</v>
+      </c>
+      <c r="I196" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J196" t="n">
+        <v>21.820791</v>
+      </c>
+      <c r="K196" t="n">
+        <v>55</v>
+      </c>
+      <c r="L196" t="n">
+        <v>62</v>
+      </c>
+      <c r="M196" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N196" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O196" t="n">
+        <v>23.39250730518757</v>
+      </c>
+      <c r="P196" t="n">
+        <v>22.21127263849432</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>2.969199679495231</v>
+      </c>
+      <c r="R196" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S196" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T196" t="n">
+        <v>-0.529340049455606</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0.3064516129032258</v>
+      </c>
+      <c r="V196" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="W196" t="n">
+        <v>806.3861287434895</v>
+      </c>
+      <c r="X196" t="n">
+        <v>643.5278759657102</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>561.8451927827964</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>725.210559148624</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>564.3681262473367</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>786.1805475110751</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>25.37164196891411</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>26.50744883544194</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>3.168314287052017</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>28.79957437007769</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>-1.120738237183542</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0.1544715447154472</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>697.9738705648272</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>610.8135445280262</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>785.1341966016281</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>583.4501114568537</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>792.2762909208373</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>386.74</v>
+      </c>
+      <c r="I197" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J197" t="n">
+        <v>23.033947</v>
+      </c>
+      <c r="K197" t="n">
+        <v>67</v>
+      </c>
+      <c r="L197" t="n">
+        <v>62</v>
+      </c>
+      <c r="M197" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N197" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O197" t="n">
+        <v>24.44307591322058</v>
+      </c>
+      <c r="P197" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>1.487784776697221</v>
+      </c>
+      <c r="R197" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S197" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T197" t="n">
+        <v>-0.9471322299376808</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0.1774193548387097</v>
+      </c>
+      <c r="V197" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W197" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X197" t="n">
+        <v>410.3992445829734</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>385.4193381822271</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>435.3791509837198</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>374.2141233952839</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>445.2374133636685</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>34.38620207828614</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>25.59798831190114</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>24.92495233226822</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>3.056819138174034</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>22.91399127868527</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>31.98677160661895</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>-0.8387939213939706</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0.1138211382113821</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>577.3443328944243</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>429.7902237568201</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>378.466230426878</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>481.1142170867621</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>384.7259135691257</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>537.0578952751322</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>76.02</v>
+      </c>
+      <c r="I198" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>24.522581</v>
+      </c>
+      <c r="K198" t="n">
+        <v>67</v>
+      </c>
+      <c r="L198" t="n">
+        <v>8</v>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="n">
+        <v>69</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>30.6729009040298</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>34.03952677730513</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>12.28232946342388</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>3.736424394319131</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>39.21501913560707</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>-0.5007453938070234</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>0.1594202898550725</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>95.08599280249238</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>57.01077146587834</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>133.1612141391064</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>11.58291562238931</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>121.5665593203819</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-07-06 16:34:43</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>195.55</v>
+      </c>
+      <c r="I199" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J199" t="n">
+        <v>29.946402</v>
+      </c>
+      <c r="K199" t="n">
+        <v>65</v>
+      </c>
+      <c r="L199" t="n">
+        <v>62</v>
+      </c>
+      <c r="M199" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N199" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O199" t="n">
+        <v>36.85849225386953</v>
+      </c>
+      <c r="P199" t="n">
+        <v>35.35264310477044</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>5.557145745061161</v>
+      </c>
+      <c r="R199" t="n">
+        <v>30.49065839641857</v>
+      </c>
+      <c r="S199" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T199" t="n">
+        <v>-1.243820221921039</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="V199" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W199" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X199" t="n">
+        <v>240.685954417768</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>204.3977927025186</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>276.9741161330174</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>199.1039993286133</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>90</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>36.7670292746133</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>36.45306022799745</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>4.652739464438709</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>30.68713598558037</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>43.54550980548469</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>-1.465937933285099</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>240.0887011632249</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>209.7063124604401</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>270.4710898660097</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>200.3869979858398</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>284.352179029815</v>
       </c>
     </row>
   </sheetData>
@@ -29011,12 +30338,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -29045,13 +30372,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>356.18</v>
+        <v>364.9</v>
       </c>
       <c r="I2" t="n">
         <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.168573</v>
+        <v>27.833715</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -29066,13 +30393,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.96707223600337</v>
+        <v>28.97188028029558</v>
       </c>
       <c r="P2" t="n">
         <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.651042461380934</v>
+        <v>1.647235201966106</v>
       </c>
       <c r="R2" t="n">
         <v>26.95049620511239</v>
@@ -29081,10 +30408,10 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.089311315772648</v>
+        <v>-0.690954927952659</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="V2" t="n">
         <v>334.6900024414062</v>
@@ -29093,13 +30420,13 @@
         <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>379.7583170140042</v>
+        <v>379.821350474675</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.1131503453002</v>
+        <v>358.2260969768993</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.4034836827083</v>
+        <v>401.4166039724506</v>
       </c>
       <c r="AA2" t="n">
         <v>353.3210052490235</v>
@@ -29108,7 +30435,7 @@
         <v>409.3048835916722</v>
       </c>
       <c r="AC2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -29117,25 +30444,25 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.34961488505105</v>
+        <v>29.30739715383484</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.95774755253947</v>
+        <v>28.9382154754243</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.107604727712076</v>
+        <v>2.107067210226951</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.95064844383164</v>
+        <v>26.95057232447202</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.6446195792587</v>
+        <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.034843894765171</v>
+        <v>-0.6993996900915709</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1209677419354839</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="AM2" t="n">
         <v>331.2549113821476</v>
@@ -29144,30 +30471,30 @@
         <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>384.7734511430193</v>
+        <v>384.2199766867748</v>
       </c>
       <c r="AP2" t="n">
-        <v>357.1427531627139</v>
+        <v>356.5963255606994</v>
       </c>
       <c r="AQ2" t="n">
-        <v>412.4041491233245</v>
+        <v>411.8436278128501</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.3230010986328</v>
+        <v>353.3220031738281</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.9709626840815</v>
+        <v>428.0356714698664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -29196,13 +30523,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>390.49</v>
+        <v>386.74</v>
       </c>
       <c r="I3" t="n">
         <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>23.257294</v>
+        <v>23.033947</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -29217,13 +30544,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.44790393782742</v>
+        <v>24.44307591322058</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.483571543147153</v>
+        <v>1.487784776697221</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -29232,10 +30559,10 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8025295061279878</v>
+        <v>-0.9471322299376808</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="V3" t="n">
         <v>352.6199687231154</v>
@@ -29244,13 +30571,13 @@
         <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>410.4803071161224</v>
+        <v>410.3992445829734</v>
       </c>
       <c r="Y3" t="n">
-        <v>385.5711409066817</v>
+        <v>385.4193381822271</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.3894733255631</v>
+        <v>435.3791509837198</v>
       </c>
       <c r="AA3" t="n">
         <v>374.2141233952839</v>
@@ -29259,7 +30586,7 @@
         <v>445.2374133636685</v>
       </c>
       <c r="AC3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD3" t="n">
         <v>21.00178491501581</v>
@@ -29268,25 +30595,25 @@
         <v>34.38620207828614</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.75158566010793</v>
+        <v>25.59798831190114</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.96228502740982</v>
+        <v>24.92495233226822</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.208346668075609</v>
+        <v>3.056819138174034</v>
       </c>
       <c r="AI3" t="n">
-        <v>22.95121947402429</v>
+        <v>22.91399127868527</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32.43371260793585</v>
+        <v>31.98677160661895</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.777438325143344</v>
+        <v>-0.8387939213939706</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1532258064516129</v>
+        <v>0.1138211382113821</v>
       </c>
       <c r="AM3" t="n">
         <v>352.6199687231154</v>
@@ -29295,30 +30622,30 @@
         <v>577.3443328944243</v>
       </c>
       <c r="AO3" t="n">
-        <v>432.3691232332121</v>
+        <v>429.7902237568201</v>
       </c>
       <c r="AP3" t="n">
-        <v>378.5009826762227</v>
+        <v>378.466230426878</v>
       </c>
       <c r="AQ3" t="n">
-        <v>486.2372637902016</v>
+        <v>481.1142170867621</v>
       </c>
       <c r="AR3" t="n">
-        <v>385.3509749688678</v>
+        <v>384.7259135691257</v>
       </c>
       <c r="AS3" t="n">
-        <v>544.5620346872429</v>
+        <v>537.0578952751322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -29347,13 +30674,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>582.9</v>
+        <v>600.29</v>
       </c>
       <c r="I4" t="n">
         <v>27.51</v>
       </c>
       <c r="J4" t="n">
-        <v>21.18866</v>
+        <v>21.820791</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -29368,13 +30695,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.43388609002637</v>
+        <v>23.39250730518757</v>
       </c>
       <c r="P4" t="n">
-        <v>22.23854536576705</v>
+        <v>22.21127263849432</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.964922784976071</v>
+        <v>2.969199679495231</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
@@ -29383,10 +30710,10 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7572629214505817</v>
+        <v>-0.529340049455606</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="V4" t="n">
         <v>543.0674023881393</v>
@@ -29395,13 +30722,13 @@
         <v>806.3861287434895</v>
       </c>
       <c r="X4" t="n">
-        <v>644.6662063366256</v>
+        <v>643.5278759657102</v>
       </c>
       <c r="Y4" t="n">
-        <v>563.1011805219339</v>
+        <v>561.8451927827964</v>
       </c>
       <c r="Z4" t="n">
-        <v>726.2312321513173</v>
+        <v>725.210559148624</v>
       </c>
       <c r="AA4" t="n">
         <v>564.3681262473367</v>
@@ -29410,7 +30737,7 @@
         <v>786.1805475110751</v>
       </c>
       <c r="AC4" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD4" t="n">
         <v>19.74072709517046</v>
@@ -29419,25 +30746,25 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.46222514761558</v>
+        <v>25.37164196891411</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.73137562485033</v>
+        <v>26.50744883544194</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.17595038285713</v>
+        <v>3.168314287052017</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.21480091441762</v>
+        <v>21.20865545099432</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28.87185984644396</v>
+        <v>28.79957437007769</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.345601987576084</v>
+        <v>-1.120738237183542</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.1544715447154472</v>
       </c>
       <c r="AM4" t="n">
         <v>543.0674023881393</v>
@@ -29446,30 +30773,30 @@
         <v>864.6619000781998</v>
       </c>
       <c r="AO4" t="n">
-        <v>700.4658138109046</v>
+        <v>697.9738705648272</v>
       </c>
       <c r="AP4" t="n">
-        <v>613.0954187785048</v>
+        <v>610.8135445280262</v>
       </c>
       <c r="AQ4" t="n">
-        <v>787.8362088433042</v>
+        <v>785.1341966016281</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.6191731556287</v>
+        <v>583.4501114568537</v>
       </c>
       <c r="AS4" t="n">
-        <v>794.2648643756735</v>
+        <v>792.2762909208373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -29498,13 +30825,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>242.67</v>
+        <v>244.16</v>
       </c>
       <c r="I5" t="n">
         <v>7.67</v>
       </c>
       <c r="J5" t="n">
-        <v>31.638851</v>
+        <v>31.833117</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -29519,13 +30846,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.56182843267153</v>
+        <v>31.55421421869486</v>
       </c>
       <c r="P5" t="n">
         <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.538485526099796</v>
+        <v>2.544929088395211</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -29534,10 +30861,10 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03034193677157169</v>
+        <v>0.1095915727384818</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="V5" t="n">
         <v>208.2735236683531</v>
@@ -29546,13 +30873,13 @@
         <v>282.3993340443035</v>
       </c>
       <c r="X5" t="n">
-        <v>242.0792240785906</v>
+        <v>242.0208230573896</v>
       </c>
       <c r="Y5" t="n">
-        <v>222.6090400934052</v>
+        <v>222.5012169493983</v>
       </c>
       <c r="Z5" t="n">
-        <v>261.5494080637761</v>
+        <v>261.5404291653809</v>
       </c>
       <c r="AA5" t="n">
         <v>218.3876527740625</v>
@@ -29561,7 +30888,7 @@
         <v>267.9632686130838</v>
       </c>
       <c r="AC5" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD5" t="n">
         <v>27.15430556301865</v>
@@ -29570,25 +30897,25 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.18365554548921</v>
+        <v>31.13033569895804</v>
       </c>
       <c r="AG5" t="n">
-        <v>30.60988720311058</v>
+        <v>30.35765469929818</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.476336507625177</v>
+        <v>2.473996425543746</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.48110034705349</v>
+        <v>28.4770334052127</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.70906596802268</v>
+        <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1838180930213433</v>
+        <v>0.2840672257186058</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6016260162601627</v>
       </c>
       <c r="AM5" t="n">
         <v>208.2735236683531</v>
@@ -29597,30 +30924,30 @@
         <v>282.3993340443035</v>
       </c>
       <c r="AO5" t="n">
-        <v>239.1786380339022</v>
+        <v>238.7696748110082</v>
       </c>
       <c r="AP5" t="n">
-        <v>220.1851370204171</v>
+        <v>219.7941222270877</v>
       </c>
       <c r="AQ5" t="n">
-        <v>258.1721390473873</v>
+        <v>257.7452273949287</v>
       </c>
       <c r="AR5" t="n">
-        <v>218.4500396619003</v>
+        <v>218.4188462179814</v>
       </c>
       <c r="AS5" t="n">
-        <v>266.218535974734</v>
+        <v>266.2741626521367</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -29649,13 +30976,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>308.63</v>
+        <v>312.66</v>
       </c>
       <c r="I6" t="n">
         <v>8.27</v>
       </c>
       <c r="J6" t="n">
-        <v>37.319225</v>
+        <v>37.806526</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -29670,25 +30997,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.25673995767608</v>
+        <v>35.33875953722645</v>
       </c>
       <c r="P6" t="n">
-        <v>35.36682683099558</v>
+        <v>35.45762586247257</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.549554415635675</v>
+        <v>1.55019685377843</v>
       </c>
       <c r="R6" t="n">
-        <v>33.00718856438788</v>
+        <v>33.31420068597328</v>
       </c>
       <c r="S6" t="n">
-        <v>37.38510981599008</v>
+        <v>37.54431108008286</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3310181439984</v>
+        <v>1.591905219494314</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.9516129032258065</v>
       </c>
       <c r="V6" t="n">
         <v>265.3727848101266</v>
@@ -29697,22 +31024,22 @@
         <v>315.5816102847638</v>
       </c>
       <c r="X6" t="n">
-        <v>291.5732394499812</v>
+        <v>292.2515413728627</v>
       </c>
       <c r="Y6" t="n">
-        <v>278.7584244326741</v>
+        <v>279.4314133921151</v>
       </c>
       <c r="Z6" t="n">
-        <v>304.3880544672882</v>
+        <v>305.0716693536103</v>
       </c>
       <c r="AA6" t="n">
-        <v>272.9694494274877</v>
+        <v>275.508439672999</v>
       </c>
       <c r="AB6" t="n">
-        <v>309.174858178238</v>
+        <v>310.4914526322852</v>
       </c>
       <c r="AC6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -29721,25 +31048,25 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.35815836379547</v>
+        <v>34.36804309252805</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.36563375175731</v>
+        <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.653649384978973</v>
+        <v>1.683420464557244</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.14202455931072</v>
+        <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.56622307063881</v>
+        <v>36.85738404207022</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.790625427071523</v>
+        <v>2.042557388285224</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.9274193548387096</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="AM6" t="n">
         <v>258.1810304279569</v>
@@ -29748,30 +31075,30 @@
         <v>315.5816102847638</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.1419696685885</v>
+        <v>284.223716375207</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.4662892548124</v>
+        <v>270.3018291333186</v>
       </c>
       <c r="AQ6" t="n">
-        <v>297.8176500823646</v>
+        <v>298.1456036170954</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.8145431054996</v>
+        <v>265.768482090431</v>
       </c>
       <c r="AS6" t="n">
-        <v>302.4026647941829</v>
+        <v>304.8105660279207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -29800,13 +31127,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>194.83</v>
+        <v>195.55</v>
       </c>
       <c r="I7" t="n">
         <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>29.83614</v>
+        <v>29.946402</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -29821,25 +31148,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.96021256689322</v>
+        <v>36.85849225386953</v>
       </c>
       <c r="P7" t="n">
-        <v>36.30000056052694</v>
+        <v>35.35264310477044</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.485811855165738</v>
+        <v>5.557145745061161</v>
       </c>
       <c r="R7" t="n">
-        <v>30.63476165257405</v>
+        <v>30.49065839641857</v>
       </c>
       <c r="S7" t="n">
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.298635964006823</v>
+        <v>-1.243820221921039</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="V7" t="n">
         <v>192.5299987792968</v>
@@ -29848,22 +31175,22 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>241.3501880618127</v>
+        <v>240.685954417768</v>
       </c>
       <c r="Y7" t="n">
-        <v>205.5278366475804</v>
+        <v>204.3977927025186</v>
       </c>
       <c r="Z7" t="n">
-        <v>277.172539476045</v>
+        <v>276.9741161330174</v>
       </c>
       <c r="AA7" t="n">
-        <v>200.0449935913086</v>
+        <v>199.1039993286133</v>
       </c>
       <c r="AB7" t="n">
         <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -29872,25 +31199,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.84366553958133</v>
+        <v>36.7670292746133</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.46530462771046</v>
+        <v>36.45306022799745</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.621622789810543</v>
+        <v>4.652739464438709</v>
       </c>
       <c r="AI7" t="n">
-        <v>31.21041267243132</v>
+        <v>30.68713598558037</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.58693835200096</v>
+        <v>43.54550980548469</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.516247832910785</v>
+        <v>-1.465937933285099</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01123595505617977</v>
+        <v>0.04444444444444445</v>
       </c>
       <c r="AM7" t="n">
         <v>192.5299987792968</v>
@@ -29899,30 +31226,30 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>240.5891359734661</v>
+        <v>240.0887011632249</v>
       </c>
       <c r="AP7" t="n">
-        <v>210.4099391560032</v>
+        <v>209.7063124604401</v>
       </c>
       <c r="AQ7" t="n">
-        <v>270.768332790929</v>
+        <v>270.4710898660097</v>
       </c>
       <c r="AR7" t="n">
-        <v>203.8039947509765</v>
+        <v>200.3869979858398</v>
       </c>
       <c r="AS7" t="n">
-        <v>284.6227074385662</v>
+        <v>284.352179029815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -29951,13 +31278,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>517.8200000000001</v>
+        <v>552.05</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>172.60667</v>
+        <v>184.01666</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -29966,55 +31293,55 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>83.08678968897406</v>
+        <v>83.59622595445165</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>142.8640812613239</v>
+        <v>144.4433265243678</v>
       </c>
       <c r="P8" t="n">
-        <v>147.4245915647413</v>
+        <v>147.8852469022157</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.33131461071225</v>
+        <v>28.68891413876551</v>
       </c>
       <c r="R8" t="n">
-        <v>96.36792683151533</v>
+        <v>98.03886672685732</v>
       </c>
       <c r="S8" t="n">
-        <v>176.0295069960297</v>
+        <v>176.8124559746414</v>
       </c>
       <c r="T8" t="n">
-        <v>1.014021673880708</v>
+        <v>1.379394608113079</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="V8" t="n">
-        <v>249.2603690669222</v>
+        <v>250.788677863355</v>
       </c>
       <c r="W8" t="n">
         <v>571.3868588306865</v>
       </c>
       <c r="X8" t="n">
-        <v>428.5922437839716</v>
+        <v>433.3299795731033</v>
       </c>
       <c r="Y8" t="n">
-        <v>340.5982999518349</v>
+        <v>347.2632371568068</v>
       </c>
       <c r="Z8" t="n">
-        <v>516.5861876161084</v>
+        <v>519.3967219893998</v>
       </c>
       <c r="AA8" t="n">
-        <v>289.103780494546</v>
+        <v>294.1166001805719</v>
       </c>
       <c r="AB8" t="n">
-        <v>528.0885209880892</v>
+        <v>530.4373679239243</v>
       </c>
       <c r="AC8" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -30023,25 +31350,25 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>116.2388610266775</v>
+        <v>116.9115546540751</v>
       </c>
       <c r="AG8" t="n">
-        <v>113.2389162561576</v>
+        <v>114.2463045167218</v>
       </c>
       <c r="AH8" t="n">
-        <v>36.34101648219581</v>
+        <v>36.93298672151382</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.52037537772701</v>
+        <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>170.2442626953125</v>
+        <v>170.4354027920082</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.55107959076869</v>
+        <v>1.816942286631683</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9918699186991869</v>
       </c>
       <c r="AM8" t="n">
         <v>216.1698078659346</v>
@@ -30050,30 +31377,30 @@
         <v>571.3868588306865</v>
       </c>
       <c r="AO8" t="n">
-        <v>348.7165830800325</v>
+        <v>350.7346639622253</v>
       </c>
       <c r="AP8" t="n">
-        <v>239.693533633445</v>
+        <v>239.9357037976838</v>
       </c>
       <c r="AQ8" t="n">
-        <v>457.73963252662</v>
+        <v>461.5336241267667</v>
       </c>
       <c r="AR8" t="n">
-        <v>226.561126133181</v>
+        <v>226.5577300449587</v>
       </c>
       <c r="AS8" t="n">
-        <v>510.7327880859375</v>
+        <v>511.3062083760246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -30102,13 +31429,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>360.45</v>
+        <v>373.9</v>
       </c>
       <c r="I9" t="n">
         <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>59.875416</v>
+        <v>62.109634</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -30123,13 +31450,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.49342604438073</v>
+        <v>75.50827412697312</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.164748443552837</v>
+        <v>9.142081458394216</v>
       </c>
       <c r="R9" t="n">
         <v>62.69783565883034</v>
@@ -30138,10 +31465,10 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.70413952336767</v>
+        <v>-1.465600606158519</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="V9" t="n">
         <v>361.0497626433158</v>
@@ -30150,13 +31477,13 @@
         <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>454.470424787172</v>
+        <v>454.5598102443781</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.2986391569839</v>
+        <v>399.524479864845</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.64221041736</v>
+        <v>509.5951406239113</v>
       </c>
       <c r="AA9" t="n">
         <v>377.4409706661586</v>
@@ -30165,7 +31492,7 @@
         <v>502.6324388886986</v>
       </c>
       <c r="AC9" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -30174,25 +31501,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.51643013143517</v>
+        <v>71.43240100505803</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.73270440251574</v>
+        <v>69.71488648740501</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.142183349539311</v>
+        <v>8.218059790012594</v>
       </c>
       <c r="AI9" t="n">
-        <v>61.93094973952918</v>
+        <v>61.92512601068532</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.35048706768551</v>
+        <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.429716530774737</v>
+        <v>-1.134424334121782</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="AM9" t="n">
         <v>344.3134935761985</v>
@@ -30201,30 +31528,30 @@
         <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>430.5289093912397</v>
+        <v>430.0230540504493</v>
       </c>
       <c r="AP9" t="n">
-        <v>381.512965627013</v>
+        <v>380.5503341145734</v>
       </c>
       <c r="AQ9" t="n">
-        <v>479.5448531554663</v>
+        <v>479.495773986325</v>
       </c>
       <c r="AR9" t="n">
-        <v>372.8243174319656</v>
+        <v>372.7892585843256</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.7499321474667</v>
+        <v>495.8250335990802</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-04 01:13:41</t>
+          <t>2026-07-06 16:34:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -30253,19 +31580,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>77.65000000000001</v>
+        <v>76.02</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>25.048388</v>
+        <v>24.522581</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -30284,7 +31611,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -30293,25 +31620,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>29.91601544232707</v>
+        <v>30.6729009040298</v>
       </c>
       <c r="AG10" t="n">
-        <v>33.87351658033287</v>
+        <v>34.03952677730513</v>
       </c>
       <c r="AH10" t="n">
-        <v>12.9070530658301</v>
+        <v>12.28232946342388</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.736842067020579</v>
+        <v>3.736424394319131</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.19762773476098</v>
+        <v>39.21501913560707</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.3771292654876847</v>
+        <v>-0.5007453938070234</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1830985915492958</v>
+        <v>0.1594202898550725</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -30320,19 +31647,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>92.73964787121393</v>
+        <v>95.08599280249238</v>
       </c>
       <c r="AP10" t="n">
-        <v>52.72778336714062</v>
+        <v>57.01077146587834</v>
       </c>
       <c r="AQ10" t="n">
-        <v>132.7515123752872</v>
+        <v>133.1612141391064</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.58421040776379</v>
+        <v>11.58291562238931</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.512645977759</v>
+        <v>121.5665593203819</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS199"/>
+  <dimension ref="A1:AS208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27670,7 +27670,7 @@
         <v>0.8709677419354839</v>
       </c>
       <c r="V183" t="n">
-        <v>249.2603690669222</v>
+        <v>249.2603690669221</v>
       </c>
       <c r="W183" t="n">
         <v>571.3868588306865</v>
@@ -28710,7 +28710,7 @@
         <v>277.172539476045</v>
       </c>
       <c r="AA190" t="n">
-        <v>200.0449935913086</v>
+        <v>200.0449935913085</v>
       </c>
       <c r="AB190" t="n">
         <v>292.0602499483069</v>
@@ -28843,7 +28843,7 @@
         <v>1.591905219494314</v>
       </c>
       <c r="U191" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9516129032258064</v>
       </c>
       <c r="V191" t="n">
         <v>265.3727848101266</v>
@@ -28912,7 +28912,7 @@
         <v>298.1456036170954</v>
       </c>
       <c r="AR191" t="n">
-        <v>265.768482090431</v>
+        <v>265.7684820904309</v>
       </c>
       <c r="AS191" t="n">
         <v>304.8105660279207</v>
@@ -28991,10 +28991,10 @@
         <v>176.8124559746414</v>
       </c>
       <c r="T192" t="n">
-        <v>1.379394608113079</v>
+        <v>1.37939460811308</v>
       </c>
       <c r="U192" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V192" t="n">
         <v>250.788677863355</v>
@@ -29063,7 +29063,7 @@
         <v>461.5336241267667</v>
       </c>
       <c r="AR192" t="n">
-        <v>226.5577300449587</v>
+        <v>226.5577300449588</v>
       </c>
       <c r="AS192" t="n">
         <v>511.3062083760246</v>
@@ -29130,10 +29130,10 @@
         <v>31.55421421869486</v>
       </c>
       <c r="P193" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q193" t="n">
-        <v>2.544929088395211</v>
+        <v>2.544929088395212</v>
       </c>
       <c r="R193" t="n">
         <v>28.4729664633719</v>
@@ -29142,7 +29142,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T193" t="n">
-        <v>0.1095915727384818</v>
+        <v>0.1095915727384817</v>
       </c>
       <c r="U193" t="n">
         <v>0.532258064516129</v>
@@ -29275,7 +29275,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N194" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O194" t="n">
         <v>75.50827412697312</v>
@@ -29296,7 +29296,7 @@
         <v>-1.465600606158519</v>
       </c>
       <c r="U194" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.0806451612903225</v>
       </c>
       <c r="V194" t="n">
         <v>361.0497626433158</v>
@@ -29326,7 +29326,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE194" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF194" t="n">
         <v>71.43240100505803</v>
@@ -29359,7 +29359,7 @@
         <v>430.0230540504493</v>
       </c>
       <c r="AP194" t="n">
-        <v>380.5503341145734</v>
+        <v>380.5503341145735</v>
       </c>
       <c r="AQ194" t="n">
         <v>479.495773986325</v>
@@ -29438,7 +29438,7 @@
         <v>1.647235201966106</v>
       </c>
       <c r="R195" t="n">
-        <v>26.95049620511239</v>
+        <v>26.9504962051124</v>
       </c>
       <c r="S195" t="n">
         <v>31.22081491927324</v>
@@ -29586,7 +29586,7 @@
         <v>22.21127263849432</v>
       </c>
       <c r="Q196" t="n">
-        <v>2.969199679495231</v>
+        <v>2.969199679495232</v>
       </c>
       <c r="R196" t="n">
         <v>20.51501731178977</v>
@@ -29649,7 +29649,7 @@
         <v>-1.120738237183542</v>
       </c>
       <c r="AL196" t="n">
-        <v>0.1544715447154472</v>
+        <v>0.1544715447154471</v>
       </c>
       <c r="AM196" t="n">
         <v>543.0674023881393</v>
@@ -29731,7 +29731,7 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O197" t="n">
-        <v>24.44307591322058</v>
+        <v>24.44307591322057</v>
       </c>
       <c r="P197" t="n">
         <v>24.57421541107486</v>
@@ -29812,7 +29812,7 @@
         <v>429.7902237568201</v>
       </c>
       <c r="AP197" t="n">
-        <v>378.466230426878</v>
+        <v>378.4662304268781</v>
       </c>
       <c r="AQ197" t="n">
         <v>481.1142170867621</v>
@@ -29895,7 +29895,7 @@
         <v>69</v>
       </c>
       <c r="AD198" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE198" t="n">
         <v>42.60474344487245</v>
@@ -29919,7 +29919,7 @@
         <v>-0.5007453938070234</v>
       </c>
       <c r="AL198" t="n">
-        <v>0.1594202898550725</v>
+        <v>0.1594202898550724</v>
       </c>
       <c r="AM198" t="n">
         <v>10.81762752038992</v>
@@ -30019,7 +30019,7 @@
         <v>-1.243820221921039</v>
       </c>
       <c r="U199" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="V199" t="n">
         <v>192.5299987792968</v>
@@ -30070,7 +30070,7 @@
         <v>-1.465937933285099</v>
       </c>
       <c r="AL199" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.0444444444444444</v>
       </c>
       <c r="AM199" t="n">
         <v>192.5299987792968</v>
@@ -30092,6 +30092,1333 @@
       </c>
       <c r="AS199" t="n">
         <v>284.352179029815</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>310.66</v>
+      </c>
+      <c r="I200" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J200" t="n">
+        <v>37.655758</v>
+      </c>
+      <c r="K200" t="n">
+        <v>67</v>
+      </c>
+      <c r="L200" t="n">
+        <v>62</v>
+      </c>
+      <c r="M200" t="n">
+        <v>32.7632894395273</v>
+      </c>
+      <c r="N200" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O200" t="n">
+        <v>35.42781699432231</v>
+      </c>
+      <c r="P200" t="n">
+        <v>35.49636766927871</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>1.518702037811088</v>
+      </c>
+      <c r="R200" t="n">
+        <v>33.3590468633119</v>
+      </c>
+      <c r="S200" t="n">
+        <v>37.6053273937604</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.467003368803552</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0.9193548387096774</v>
+      </c>
+      <c r="V200" t="n">
+        <v>270.2971378761002</v>
+      </c>
+      <c r="W200" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="X200" t="n">
+        <v>292.2794902031591</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>279.7501983912176</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>304.8087820151006</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>275.2121366223232</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>310.2439509985234</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>34.39010316482904</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>1.708005042001887</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>37.05157337696731</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.911970254691642</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>0.959349593495935</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>314.8184141292988</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>283.7183511098396</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>269.6273095133241</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>297.8093927063551</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>305.6754803599803</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>516.11</v>
+      </c>
+      <c r="I201" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J201" t="n">
+        <v>173.19127</v>
+      </c>
+      <c r="K201" t="n">
+        <v>63</v>
+      </c>
+      <c r="L201" t="n">
+        <v>62</v>
+      </c>
+      <c r="M201" t="n">
+        <v>87.479248046875</v>
+      </c>
+      <c r="N201" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O201" t="n">
+        <v>145.8242968902614</v>
+      </c>
+      <c r="P201" t="n">
+        <v>148.7852453012936</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>27.75755029866852</v>
+      </c>
+      <c r="R201" t="n">
+        <v>103.8796271558078</v>
+      </c>
+      <c r="S201" t="n">
+        <v>176.8124559746414</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0.9859289748292874</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0.8548387096774194</v>
+      </c>
+      <c r="V201" t="n">
+        <v>260.6881591796875</v>
+      </c>
+      <c r="W201" t="n">
+        <v>567.5776131051485</v>
+      </c>
+      <c r="X201" t="n">
+        <v>434.5564047329789</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>351.8389048429467</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>517.273904623011</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>309.5612889243072</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>526.9011188044313</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>117.4461746415253</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>114.513204322671</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>37.21153502478618</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>170.4354027920082</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.49805954850676</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>214.728675813495</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>567.5776131051485</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>349.9896004317454</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>239.0992260578826</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>460.8799748056082</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>225.0473451779923</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>507.8975003201845</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>245.98</v>
+      </c>
+      <c r="I202" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="J202" t="n">
+        <v>31.862694</v>
+      </c>
+      <c r="K202" t="n">
+        <v>67</v>
+      </c>
+      <c r="L202" t="n">
+        <v>62</v>
+      </c>
+      <c r="M202" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N202" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O202" t="n">
+        <v>31.54790678301238</v>
+      </c>
+      <c r="P202" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>2.549791488128202</v>
+      </c>
+      <c r="R202" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S202" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0.123456062369518</v>
+      </c>
+      <c r="U202" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="V202" t="n">
+        <v>209.631238946504</v>
+      </c>
+      <c r="W202" t="n">
+        <v>284.2402684252964</v>
+      </c>
+      <c r="X202" t="n">
+        <v>243.5498403648556</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>223.8654500765058</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>263.2342306532053</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>219.8113010972311</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>269.7100956574976</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>31.0921633472674</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>30.23988944549773</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>2.463711348559294</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>34.71631846833595</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>0.312752000425369</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>0.6178861788617886</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>209.631238946504</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>284.2402684252964</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>240.0315010409043</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>221.0116494300266</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>259.0513526517821</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>219.842697888242</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>268.0099785755535</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="I203" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J203" t="n">
+        <v>61.591362</v>
+      </c>
+      <c r="K203" t="n">
+        <v>34</v>
+      </c>
+      <c r="L203" t="n">
+        <v>62</v>
+      </c>
+      <c r="M203" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N203" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O203" t="n">
+        <v>75.45331410488485</v>
+      </c>
+      <c r="P203" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>9.215617814122464</v>
+      </c>
+      <c r="R203" t="n">
+        <v>62.25973272085587</v>
+      </c>
+      <c r="S203" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T203" t="n">
+        <v>-1.504180445031273</v>
+      </c>
+      <c r="U203" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="V203" t="n">
+        <v>361.0497626433158</v>
+      </c>
+      <c r="W203" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X203" t="n">
+        <v>454.2289509114068</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>398.7509316703895</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>509.706970152424</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>374.8035909795523</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>502.6324388886986</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>71.34850884875353</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>69.70230838287802</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>8.264624918986181</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>61.7377704233179</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>-1.18059161116176</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>0.0975609756097561</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>429.5180232694962</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>379.7649812571994</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>479.271065281793</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>371.6613779483737</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>495.8250335990802</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="I204" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>27.75725</v>
+      </c>
+      <c r="K204" t="n">
+        <v>37</v>
+      </c>
+      <c r="L204" t="n">
+        <v>62</v>
+      </c>
+      <c r="M204" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N204" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O204" t="n">
+        <v>28.96575844096208</v>
+      </c>
+      <c r="P204" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>1.651170148297226</v>
+      </c>
+      <c r="R204" t="n">
+        <v>26.95049620511239</v>
+      </c>
+      <c r="S204" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T204" t="n">
+        <v>-0.7319103014358367</v>
+      </c>
+      <c r="U204" t="n">
+        <v>0.2903225806451613</v>
+      </c>
+      <c r="V204" t="n">
+        <v>334.434708770589</v>
+      </c>
+      <c r="W204" t="n">
+        <v>422.3507729952915</v>
+      </c>
+      <c r="X204" t="n">
+        <v>379.4514355766032</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>357.8211066339096</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>401.0817645192968</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>353.0515002869723</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>408.9926754424794</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>29.27411958912855</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>28.83348773741038</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>2.099220338250603</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>26.95057232447202</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>-0.72258712508123</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>446.0207226104586</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>383.490966617584</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>355.9911801865011</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>410.9907530486669</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>353.0524974505834</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>427.7091759157322</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>615.58</v>
+      </c>
+      <c r="I205" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="J205" t="n">
+        <v>22.392872</v>
+      </c>
+      <c r="K205" t="n">
+        <v>55</v>
+      </c>
+      <c r="L205" t="n">
+        <v>62</v>
+      </c>
+      <c r="M205" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N205" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O205" t="n">
+        <v>23.35870244000214</v>
+      </c>
+      <c r="P205" t="n">
+        <v>22.21127263849432</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>2.968539157813888</v>
+      </c>
+      <c r="R205" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S205" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T205" t="n">
+        <v>-0.3253554656538201</v>
+      </c>
+      <c r="U205" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="V205" t="n">
+        <v>542.6725878462358</v>
+      </c>
+      <c r="W205" t="n">
+        <v>805.7998792860242</v>
+      </c>
+      <c r="X205" t="n">
+        <v>642.1307300756587</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>560.5255886273549</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>723.7358715239625</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>563.9578259011008</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>785.6089876800964</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>25.32006641583422</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>26.2103019444777</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>3.164853240545059</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>28.79957437007769</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>-0.9249068419141249</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>542.6725878462358</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>864.0332836477539</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>696.0486257712826</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>609.0468101886988</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>783.0504413538663</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>583.0259383478337</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>791.7002994334356</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="I206" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J206" t="n">
+        <v>23.172823</v>
+      </c>
+      <c r="K206" t="n">
+        <v>67</v>
+      </c>
+      <c r="L206" t="n">
+        <v>62</v>
+      </c>
+      <c r="M206" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N206" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O206" t="n">
+        <v>24.44085914983256</v>
+      </c>
+      <c r="P206" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>1.489643316249973</v>
+      </c>
+      <c r="R206" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S206" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T206" t="n">
+        <v>-0.8512347459287867</v>
+      </c>
+      <c r="U206" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V206" t="n">
+        <v>352.4099508739653</v>
+      </c>
+      <c r="W206" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X206" t="n">
+        <v>410.1176165341904</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>385.1214016875159</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>435.113831380865</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>373.9912442270914</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>444.9722332485025</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>25.50659835904723</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>24.91932404346955</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>2.958374398559627</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>22.91399127868527</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>31.2935561003528</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>-0.7888708610321596</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0.1382113821138211</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>352.4099508739653</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>573.551363775435</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>428.0007204648126</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>378.3591980569821</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>477.6422428726431</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>384.4967736563389</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>525.10587136392</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="I207" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J207" t="n">
+        <v>24.574194</v>
+      </c>
+      <c r="K207" t="n">
+        <v>67</v>
+      </c>
+      <c r="L207" t="n">
+        <v>7</v>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>31.06823927709822</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>34.98814247342436</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>11.92317314857364</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>3.736215557968407</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>39.22371483603013</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>-0.5446574662781865</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>0.1470588235294118</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>96.31154175900448</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>59.34970499842622</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>133.2733785195828</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>11.58226822970206</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>121.5935159916934</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-07-07 16:27:03</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>196.93</v>
+      </c>
+      <c r="I208" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J208" t="n">
+        <v>30.157732</v>
+      </c>
+      <c r="K208" t="n">
+        <v>65</v>
+      </c>
+      <c r="L208" t="n">
+        <v>62</v>
+      </c>
+      <c r="M208" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N208" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O208" t="n">
+        <v>36.75866632475287</v>
+      </c>
+      <c r="P208" t="n">
+        <v>34.29019922136712</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>5.621700711197021</v>
+      </c>
+      <c r="R208" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S208" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T208" t="n">
+        <v>-1.17418814409765</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="V208" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W208" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X208" t="n">
+        <v>240.0340911006362</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>203.3243854565197</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>276.7437967447528</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>197.7220016479492</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>91</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>36.69439963880319</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>36.44081582828444</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>4.678405945017813</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>30.64165334424052</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>43.50408125896843</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>-1.397199754707969</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>0.05494505494505494</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>239.6144296413848</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>209.0644388204185</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>270.1644204623512</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>200.0899963378906</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>284.0816506210638</v>
       </c>
     </row>
   </sheetData>
@@ -30338,12 +31665,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -30372,13 +31699,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>364.9</v>
+        <v>363.62</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="J2" t="n">
-        <v>27.833715</v>
+        <v>27.75725</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -30393,13 +31720,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.97188028029558</v>
+        <v>28.96575844096208</v>
       </c>
       <c r="P2" t="n">
         <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.647235201966106</v>
+        <v>1.651170148297226</v>
       </c>
       <c r="R2" t="n">
         <v>26.95049620511239</v>
@@ -30408,31 +31735,31 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.690954927952659</v>
+        <v>-0.7319103014358367</v>
       </c>
       <c r="U2" t="n">
         <v>0.2903225806451613</v>
       </c>
       <c r="V2" t="n">
-        <v>334.6900024414062</v>
+        <v>334.434708770589</v>
       </c>
       <c r="W2" t="n">
-        <v>422.673178165517</v>
+        <v>422.3507729952915</v>
       </c>
       <c r="X2" t="n">
-        <v>379.821350474675</v>
+        <v>379.4514355766032</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.2260969768993</v>
+        <v>357.8211066339096</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.4166039724506</v>
+        <v>401.0817645192968</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.3210052490235</v>
+        <v>353.0515002869723</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.3048835916722</v>
+        <v>408.9926754424794</v>
       </c>
       <c r="AC2" t="n">
         <v>123</v>
@@ -30444,13 +31771,13 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.30739715383484</v>
+        <v>29.27411958912855</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.9382154754243</v>
+        <v>28.83348773741038</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.107067210226951</v>
+        <v>2.099220338250603</v>
       </c>
       <c r="AI2" t="n">
         <v>26.95057232447202</v>
@@ -30459,42 +31786,42 @@
         <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.6993996900915709</v>
+        <v>-0.72258712508123</v>
       </c>
       <c r="AL2" t="n">
         <v>0.2439024390243902</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.002237918088</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.3611964445124</v>
+        <v>446.0207226104586</v>
       </c>
       <c r="AO2" t="n">
-        <v>384.2199766867748</v>
+        <v>383.490966617584</v>
       </c>
       <c r="AP2" t="n">
-        <v>356.5963255606994</v>
+        <v>355.9911801865011</v>
       </c>
       <c r="AQ2" t="n">
-        <v>411.8436278128501</v>
+        <v>410.9907530486669</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.3220031738281</v>
+        <v>353.0524974505834</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.0356714698664</v>
+        <v>427.7091759157322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -30523,13 +31850,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>386.74</v>
+        <v>388.84</v>
       </c>
       <c r="I3" t="n">
-        <v>16.79</v>
+        <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>23.033947</v>
+        <v>23.172823</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -30544,13 +31871,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.44307591322058</v>
+        <v>24.44085914983256</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.487784776697221</v>
+        <v>1.489643316249973</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -30559,31 +31886,31 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9471322299376808</v>
+        <v>-0.8512347459287867</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="V3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.4099508739653</v>
       </c>
       <c r="W3" t="n">
-        <v>460.2458699725923</v>
+        <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>410.3992445829734</v>
+        <v>410.1176165341904</v>
       </c>
       <c r="Y3" t="n">
-        <v>385.4193381822271</v>
+        <v>385.1214016875159</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.3791509837198</v>
+        <v>435.113831380865</v>
       </c>
       <c r="AA3" t="n">
-        <v>374.2141233952839</v>
+        <v>373.9912442270914</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.2374133636685</v>
+        <v>444.9722332485025</v>
       </c>
       <c r="AC3" t="n">
         <v>123</v>
@@ -30592,60 +31919,60 @@
         <v>21.00178491501581</v>
       </c>
       <c r="AE3" t="n">
-        <v>34.38620207828614</v>
+        <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.59798831190114</v>
+        <v>25.50659835904723</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.92495233226822</v>
+        <v>24.91932404346955</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.056819138174034</v>
+        <v>2.958374398559627</v>
       </c>
       <c r="AI3" t="n">
         <v>22.91399127868527</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31.98677160661895</v>
+        <v>31.2935561003528</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8387939213939706</v>
+        <v>-0.7888708610321596</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1138211382113821</v>
+        <v>0.1382113821138211</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.4099508739653</v>
       </c>
       <c r="AN3" t="n">
-        <v>577.3443328944243</v>
+        <v>573.551363775435</v>
       </c>
       <c r="AO3" t="n">
-        <v>429.7902237568201</v>
+        <v>428.0007204648126</v>
       </c>
       <c r="AP3" t="n">
-        <v>378.466230426878</v>
+        <v>378.3591980569821</v>
       </c>
       <c r="AQ3" t="n">
-        <v>481.1142170867621</v>
+        <v>477.6422428726431</v>
       </c>
       <c r="AR3" t="n">
-        <v>384.7259135691257</v>
+        <v>384.4967736563389</v>
       </c>
       <c r="AS3" t="n">
-        <v>537.0578952751322</v>
+        <v>525.10587136392</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -30674,13 +32001,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>600.29</v>
+        <v>615.58</v>
       </c>
       <c r="I4" t="n">
-        <v>27.51</v>
+        <v>27.49</v>
       </c>
       <c r="J4" t="n">
-        <v>21.820791</v>
+        <v>22.392872</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -30695,13 +32022,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.39250730518757</v>
+        <v>23.35870244000214</v>
       </c>
       <c r="P4" t="n">
         <v>22.21127263849432</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.969199679495231</v>
+        <v>2.968539157813888</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
@@ -30710,31 +32037,31 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.529340049455606</v>
+        <v>-0.3253554656538201</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="V4" t="n">
-        <v>543.0674023881393</v>
+        <v>542.6725878462358</v>
       </c>
       <c r="W4" t="n">
-        <v>806.3861287434895</v>
+        <v>805.7998792860242</v>
       </c>
       <c r="X4" t="n">
-        <v>643.5278759657102</v>
+        <v>642.1307300756587</v>
       </c>
       <c r="Y4" t="n">
-        <v>561.8451927827964</v>
+        <v>560.5255886273549</v>
       </c>
       <c r="Z4" t="n">
-        <v>725.210559148624</v>
+        <v>723.7358715239625</v>
       </c>
       <c r="AA4" t="n">
-        <v>564.3681262473367</v>
+        <v>563.9578259011008</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.1805475110751</v>
+        <v>785.6089876800964</v>
       </c>
       <c r="AC4" t="n">
         <v>123</v>
@@ -30746,13 +32073,13 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.37164196891411</v>
+        <v>25.32006641583422</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.50744883544194</v>
+        <v>26.2103019444777</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.168314287052017</v>
+        <v>3.164853240545059</v>
       </c>
       <c r="AI4" t="n">
         <v>21.20865545099432</v>
@@ -30761,42 +32088,42 @@
         <v>28.79957437007769</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.120738237183542</v>
+        <v>-0.9249068419141249</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1544715447154472</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="AM4" t="n">
-        <v>543.0674023881393</v>
+        <v>542.6725878462358</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.6619000781998</v>
+        <v>864.0332836477539</v>
       </c>
       <c r="AO4" t="n">
-        <v>697.9738705648272</v>
+        <v>696.0486257712826</v>
       </c>
       <c r="AP4" t="n">
-        <v>610.8135445280262</v>
+        <v>609.0468101886988</v>
       </c>
       <c r="AQ4" t="n">
-        <v>785.1341966016281</v>
+        <v>783.0504413538663</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.4501114568537</v>
+        <v>583.0259383478337</v>
       </c>
       <c r="AS4" t="n">
-        <v>792.2762909208373</v>
+        <v>791.7002994334356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -30825,13 +32152,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>244.16</v>
+        <v>245.98</v>
       </c>
       <c r="I5" t="n">
-        <v>7.67</v>
+        <v>7.72</v>
       </c>
       <c r="J5" t="n">
-        <v>31.833117</v>
+        <v>31.862694</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -30846,13 +32173,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.55421421869486</v>
+        <v>31.54790678301238</v>
       </c>
       <c r="P5" t="n">
         <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.544929088395211</v>
+        <v>2.549791488128202</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -30861,31 +32188,31 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1095915727384818</v>
+        <v>0.123456062369518</v>
       </c>
       <c r="U5" t="n">
-        <v>0.532258064516129</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="V5" t="n">
-        <v>208.2735236683531</v>
+        <v>209.631238946504</v>
       </c>
       <c r="W5" t="n">
-        <v>282.3993340443035</v>
+        <v>284.2402684252964</v>
       </c>
       <c r="X5" t="n">
-        <v>242.0208230573896</v>
+        <v>243.5498403648556</v>
       </c>
       <c r="Y5" t="n">
-        <v>222.5012169493983</v>
+        <v>223.8654500765058</v>
       </c>
       <c r="Z5" t="n">
-        <v>261.5404291653809</v>
+        <v>263.2342306532053</v>
       </c>
       <c r="AA5" t="n">
-        <v>218.3876527740625</v>
+        <v>219.8113010972311</v>
       </c>
       <c r="AB5" t="n">
-        <v>267.9632686130838</v>
+        <v>269.7100956574976</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -30897,13 +32224,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.13033569895804</v>
+        <v>31.0921633472674</v>
       </c>
       <c r="AG5" t="n">
-        <v>30.35765469929818</v>
+        <v>30.23988944549773</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.473996425543746</v>
+        <v>2.463711348559294</v>
       </c>
       <c r="AI5" t="n">
         <v>28.4770334052127</v>
@@ -30912,42 +32239,42 @@
         <v>34.71631846833595</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.2840672257186058</v>
+        <v>0.312752000425369</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6016260162601627</v>
+        <v>0.6178861788617886</v>
       </c>
       <c r="AM5" t="n">
-        <v>208.2735236683531</v>
+        <v>209.631238946504</v>
       </c>
       <c r="AN5" t="n">
-        <v>282.3993340443035</v>
+        <v>284.2402684252964</v>
       </c>
       <c r="AO5" t="n">
-        <v>238.7696748110082</v>
+        <v>240.0315010409043</v>
       </c>
       <c r="AP5" t="n">
-        <v>219.7941222270877</v>
+        <v>221.0116494300266</v>
       </c>
       <c r="AQ5" t="n">
-        <v>257.7452273949287</v>
+        <v>259.0513526517821</v>
       </c>
       <c r="AR5" t="n">
-        <v>218.4188462179814</v>
+        <v>219.842697888242</v>
       </c>
       <c r="AS5" t="n">
-        <v>266.2741626521367</v>
+        <v>268.0099785755535</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -30976,13 +32303,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>312.66</v>
+        <v>310.66</v>
       </c>
       <c r="I6" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>37.806526</v>
+        <v>37.655758</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -30991,52 +32318,52 @@
         <v>62</v>
       </c>
       <c r="M6" t="n">
-        <v>32.08860759493671</v>
+        <v>32.7632894395273</v>
       </c>
       <c r="N6" t="n">
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.33875953722645</v>
+        <v>35.42781699432231</v>
       </c>
       <c r="P6" t="n">
-        <v>35.45762586247257</v>
+        <v>35.49636766927871</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55019685377843</v>
+        <v>1.518702037811088</v>
       </c>
       <c r="R6" t="n">
-        <v>33.31420068597328</v>
+        <v>33.3590468633119</v>
       </c>
       <c r="S6" t="n">
-        <v>37.54431108008286</v>
+        <v>37.6053273937604</v>
       </c>
       <c r="T6" t="n">
-        <v>1.591905219494314</v>
+        <v>1.467003368803552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9193548387096774</v>
       </c>
       <c r="V6" t="n">
-        <v>265.3727848101266</v>
+        <v>270.2971378761002</v>
       </c>
       <c r="W6" t="n">
-        <v>315.5816102847638</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="X6" t="n">
-        <v>292.2515413728627</v>
+        <v>292.2794902031591</v>
       </c>
       <c r="Y6" t="n">
-        <v>279.4314133921151</v>
+        <v>279.7501983912176</v>
       </c>
       <c r="Z6" t="n">
-        <v>305.0716693536103</v>
+        <v>304.8087820151006</v>
       </c>
       <c r="AA6" t="n">
-        <v>275.508439672999</v>
+        <v>275.2121366223232</v>
       </c>
       <c r="AB6" t="n">
-        <v>310.4914526322852</v>
+        <v>310.2439509985234</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -31048,57 +32375,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.36804309252805</v>
+        <v>34.39010316482904</v>
       </c>
       <c r="AG6" t="n">
         <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.683420464557244</v>
+        <v>1.708005042001887</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36.85738404207022</v>
+        <v>37.05157337696731</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.042557388285224</v>
+        <v>1.911970254691642</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.975609756097561</v>
+        <v>0.959349593495935</v>
       </c>
       <c r="AM6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.5816102847638</v>
+        <v>314.8184141292988</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.223716375207</v>
+        <v>283.7183511098396</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.3018291333186</v>
+        <v>269.6273095133241</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.1456036170954</v>
+        <v>297.8093927063551</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.768482090431</v>
+        <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>304.8105660279207</v>
+        <v>305.6754803599803</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -31127,13 +32454,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>195.55</v>
+        <v>196.93</v>
       </c>
       <c r="I7" t="n">
         <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>29.946402</v>
+        <v>30.157732</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -31148,25 +32475,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.85849225386953</v>
+        <v>36.75866632475287</v>
       </c>
       <c r="P7" t="n">
-        <v>35.35264310477044</v>
+        <v>34.29019922136712</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.557145745061161</v>
+        <v>5.621700711197021</v>
       </c>
       <c r="R7" t="n">
-        <v>30.49065839641857</v>
+        <v>30.27902016048226</v>
       </c>
       <c r="S7" t="n">
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.243820221921039</v>
+        <v>-1.17418814409765</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="V7" t="n">
         <v>192.5299987792968</v>
@@ -31175,22 +32502,22 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>240.685954417768</v>
+        <v>240.0340911006362</v>
       </c>
       <c r="Y7" t="n">
-        <v>204.3977927025186</v>
+        <v>203.3243854565197</v>
       </c>
       <c r="Z7" t="n">
-        <v>276.9741161330174</v>
+        <v>276.7437967447528</v>
       </c>
       <c r="AA7" t="n">
-        <v>199.1039993286133</v>
+        <v>197.7220016479492</v>
       </c>
       <c r="AB7" t="n">
         <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -31199,25 +32526,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.7670292746133</v>
+        <v>36.69439963880319</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.45306022799745</v>
+        <v>36.44081582828444</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.652739464438709</v>
+        <v>4.678405945017813</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.68713598558037</v>
+        <v>30.64165334424052</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.54550980548469</v>
+        <v>43.50408125896843</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.465937933285099</v>
+        <v>-1.397199754707969</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04444444444444445</v>
+        <v>0.05494505494505494</v>
       </c>
       <c r="AM7" t="n">
         <v>192.5299987792968</v>
@@ -31226,30 +32553,30 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>240.0887011632249</v>
+        <v>239.6144296413848</v>
       </c>
       <c r="AP7" t="n">
-        <v>209.7063124604401</v>
+        <v>209.0644388204185</v>
       </c>
       <c r="AQ7" t="n">
-        <v>270.4710898660097</v>
+        <v>270.1644204623512</v>
       </c>
       <c r="AR7" t="n">
-        <v>200.3869979858398</v>
+        <v>200.0899963378906</v>
       </c>
       <c r="AS7" t="n">
-        <v>284.352179029815</v>
+        <v>284.0816506210638</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -31278,13 +32605,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>552.05</v>
+        <v>516.11</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="n">
-        <v>184.01666</v>
+        <v>173.19127</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -31293,52 +32620,52 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>83.59622595445165</v>
+        <v>87.479248046875</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>144.4433265243678</v>
+        <v>145.8242968902614</v>
       </c>
       <c r="P8" t="n">
-        <v>147.8852469022157</v>
+        <v>148.7852453012936</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.68891413876551</v>
+        <v>27.75755029866852</v>
       </c>
       <c r="R8" t="n">
-        <v>98.03886672685732</v>
+        <v>103.8796271558078</v>
       </c>
       <c r="S8" t="n">
         <v>176.8124559746414</v>
       </c>
       <c r="T8" t="n">
-        <v>1.379394608113079</v>
+        <v>0.9859289748292874</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="V8" t="n">
-        <v>250.788677863355</v>
+        <v>260.6881591796875</v>
       </c>
       <c r="W8" t="n">
-        <v>571.3868588306865</v>
+        <v>567.5776131051485</v>
       </c>
       <c r="X8" t="n">
-        <v>433.3299795731033</v>
+        <v>434.5564047329789</v>
       </c>
       <c r="Y8" t="n">
-        <v>347.2632371568068</v>
+        <v>351.8389048429467</v>
       </c>
       <c r="Z8" t="n">
-        <v>519.3967219893998</v>
+        <v>517.273904623011</v>
       </c>
       <c r="AA8" t="n">
-        <v>294.1166001805719</v>
+        <v>309.5612889243072</v>
       </c>
       <c r="AB8" t="n">
-        <v>530.4373679239243</v>
+        <v>526.9011188044313</v>
       </c>
       <c r="AC8" t="n">
         <v>123</v>
@@ -31350,13 +32677,13 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>116.9115546540751</v>
+        <v>117.4461746415253</v>
       </c>
       <c r="AG8" t="n">
-        <v>114.2463045167218</v>
+        <v>114.513204322671</v>
       </c>
       <c r="AH8" t="n">
-        <v>36.93298672151382</v>
+        <v>37.21153502478618</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51924334831958</v>
@@ -31365,42 +32692,42 @@
         <v>170.4354027920082</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.816942286631683</v>
+        <v>1.49805954850676</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9918699186991869</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="AM8" t="n">
-        <v>216.1698078659346</v>
+        <v>214.728675813495</v>
       </c>
       <c r="AN8" t="n">
-        <v>571.3868588306865</v>
+        <v>567.5776131051485</v>
       </c>
       <c r="AO8" t="n">
-        <v>350.7346639622253</v>
+        <v>349.9896004317454</v>
       </c>
       <c r="AP8" t="n">
-        <v>239.9357037976838</v>
+        <v>239.0992260578826</v>
       </c>
       <c r="AQ8" t="n">
-        <v>461.5336241267667</v>
+        <v>460.8799748056082</v>
       </c>
       <c r="AR8" t="n">
-        <v>226.5577300449587</v>
+        <v>225.0473451779923</v>
       </c>
       <c r="AS8" t="n">
-        <v>511.3062083760246</v>
+        <v>507.8975003201845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -31429,13 +32756,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>373.9</v>
+        <v>370.78</v>
       </c>
       <c r="I9" t="n">
         <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>62.109634</v>
+        <v>61.591362</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -31450,25 +32777,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.50827412697312</v>
+        <v>75.45331410488485</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.142081458394216</v>
+        <v>9.215617814122464</v>
       </c>
       <c r="R9" t="n">
-        <v>62.69783565883034</v>
+        <v>62.25973272085587</v>
       </c>
       <c r="S9" t="n">
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.465600606158519</v>
+        <v>-1.504180445031273</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="V9" t="n">
         <v>361.0497626433158</v>
@@ -31477,16 +32804,16 @@
         <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>454.5598102443781</v>
+        <v>454.2289509114068</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.524479864845</v>
+        <v>398.7509316703895</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.5951406239113</v>
+        <v>509.706970152424</v>
       </c>
       <c r="AA9" t="n">
-        <v>377.4409706661586</v>
+        <v>374.8035909795523</v>
       </c>
       <c r="AB9" t="n">
         <v>502.6324388886986</v>
@@ -31501,25 +32828,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.43240100505803</v>
+        <v>71.34850884875353</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.71488648740501</v>
+        <v>69.70230838287802</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.218059790012594</v>
+        <v>8.264624918986181</v>
       </c>
       <c r="AI9" t="n">
-        <v>61.92512601068532</v>
+        <v>61.7377704233179</v>
       </c>
       <c r="AJ9" t="n">
         <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.134424334121782</v>
+        <v>-1.18059161116176</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.0975609756097561</v>
       </c>
       <c r="AM9" t="n">
         <v>344.3134935761985</v>
@@ -31528,16 +32855,16 @@
         <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>430.0230540504493</v>
+        <v>429.5180232694962</v>
       </c>
       <c r="AP9" t="n">
-        <v>380.5503341145734</v>
+        <v>379.7649812571994</v>
       </c>
       <c r="AQ9" t="n">
-        <v>479.495773986325</v>
+        <v>479.271065281793</v>
       </c>
       <c r="AR9" t="n">
-        <v>372.7892585843256</v>
+        <v>371.6613779483737</v>
       </c>
       <c r="AS9" t="n">
         <v>495.8250335990802</v>
@@ -31546,12 +32873,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-06 16:34:43</t>
+          <t>2026-07-07 16:27:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -31580,19 +32907,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>76.02</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>24.522581</v>
+        <v>24.574194</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -31611,7 +32938,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -31620,25 +32947,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>30.6729009040298</v>
+        <v>31.06823927709822</v>
       </c>
       <c r="AG10" t="n">
-        <v>34.03952677730513</v>
+        <v>34.98814247342436</v>
       </c>
       <c r="AH10" t="n">
-        <v>12.28232946342388</v>
+        <v>11.92317314857364</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.736424394319131</v>
+        <v>3.736215557968407</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.21501913560707</v>
+        <v>39.22371483603013</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.5007453938070234</v>
+        <v>-0.5446574662781865</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1594202898550725</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -31647,19 +32974,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>95.08599280249238</v>
+        <v>96.31154175900448</v>
       </c>
       <c r="AP10" t="n">
-        <v>57.01077146587834</v>
+        <v>59.34970499842622</v>
       </c>
       <c r="AQ10" t="n">
-        <v>133.1612141391064</v>
+        <v>133.2733785195828</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.58291562238931</v>
+        <v>11.58226822970206</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.5665593203819</v>
+        <v>121.5935159916934</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS208"/>
+  <dimension ref="A1:AS217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29214,7 +29214,7 @@
         <v>257.7452273949287</v>
       </c>
       <c r="AR193" t="n">
-        <v>218.4188462179814</v>
+        <v>218.4188462179813</v>
       </c>
       <c r="AS193" t="n">
         <v>266.2741626521367</v>
@@ -30390,7 +30390,7 @@
         <v>460.8799748056082</v>
       </c>
       <c r="AR201" t="n">
-        <v>225.0473451779923</v>
+        <v>225.0473451779924</v>
       </c>
       <c r="AS201" t="n">
         <v>507.8975003201845</v>
@@ -30457,7 +30457,7 @@
         <v>31.54790678301238</v>
       </c>
       <c r="P202" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q202" t="n">
         <v>2.549791488128202</v>
@@ -30484,7 +30484,7 @@
         <v>243.5498403648556</v>
       </c>
       <c r="Y202" t="n">
-        <v>223.8654500765058</v>
+        <v>223.8654500765059</v>
       </c>
       <c r="Z202" t="n">
         <v>263.2342306532053</v>
@@ -30535,7 +30535,7 @@
         <v>240.0315010409043</v>
       </c>
       <c r="AP202" t="n">
-        <v>221.0116494300266</v>
+        <v>221.0116494300265</v>
       </c>
       <c r="AQ202" t="n">
         <v>259.0513526517821</v>
@@ -30602,7 +30602,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N203" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O203" t="n">
         <v>75.45331410488485</v>
@@ -30623,7 +30623,7 @@
         <v>-1.504180445031273</v>
       </c>
       <c r="U203" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.0483870967741935</v>
       </c>
       <c r="V203" t="n">
         <v>361.0497626433158</v>
@@ -30635,13 +30635,13 @@
         <v>454.2289509114068</v>
       </c>
       <c r="Y203" t="n">
-        <v>398.7509316703895</v>
+        <v>398.7509316703896</v>
       </c>
       <c r="Z203" t="n">
-        <v>509.706970152424</v>
+        <v>509.7069701524241</v>
       </c>
       <c r="AA203" t="n">
-        <v>374.8035909795523</v>
+        <v>374.8035909795522</v>
       </c>
       <c r="AB203" t="n">
         <v>502.6324388886986</v>
@@ -30653,7 +30653,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE203" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF203" t="n">
         <v>71.34850884875353</v>
@@ -30665,7 +30665,7 @@
         <v>8.264624918986181</v>
       </c>
       <c r="AI203" t="n">
-        <v>61.7377704233179</v>
+        <v>61.73777042331791</v>
       </c>
       <c r="AJ203" t="n">
         <v>82.36296239187379</v>
@@ -30765,7 +30765,7 @@
         <v>1.651170148297226</v>
       </c>
       <c r="R204" t="n">
-        <v>26.95049620511239</v>
+        <v>26.9504962051124</v>
       </c>
       <c r="S204" t="n">
         <v>31.22081491927324</v>
@@ -30780,7 +30780,7 @@
         <v>334.434708770589</v>
       </c>
       <c r="W204" t="n">
-        <v>422.3507729952915</v>
+        <v>422.3507729952916</v>
       </c>
       <c r="X204" t="n">
         <v>379.4514355766032</v>
@@ -30922,7 +30922,7 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T205" t="n">
-        <v>-0.3253554656538201</v>
+        <v>-0.32535546565382</v>
       </c>
       <c r="U205" t="n">
         <v>0.6129032258064516</v>
@@ -30964,7 +30964,7 @@
         <v>26.2103019444777</v>
       </c>
       <c r="AH205" t="n">
-        <v>3.164853240545059</v>
+        <v>3.16485324054506</v>
       </c>
       <c r="AI205" t="n">
         <v>21.20865545099432</v>
@@ -30973,7 +30973,7 @@
         <v>28.79957437007769</v>
       </c>
       <c r="AK205" t="n">
-        <v>-0.9249068419141249</v>
+        <v>-0.9249068419141248</v>
       </c>
       <c r="AL205" t="n">
         <v>0.3170731707317073</v>
@@ -31222,13 +31222,13 @@
         <v>68</v>
       </c>
       <c r="AD207" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE207" t="n">
         <v>42.60474344487245</v>
       </c>
       <c r="AF207" t="n">
-        <v>31.06823927709822</v>
+        <v>31.06823927709823</v>
       </c>
       <c r="AG207" t="n">
         <v>34.98814247342436</v>
@@ -31246,7 +31246,7 @@
         <v>-0.5446574662781865</v>
       </c>
       <c r="AL207" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.1470588235294117</v>
       </c>
       <c r="AM207" t="n">
         <v>10.81762752038992</v>
@@ -31346,7 +31346,7 @@
         <v>-1.17418814409765</v>
       </c>
       <c r="U208" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.0806451612903225</v>
       </c>
       <c r="V208" t="n">
         <v>192.5299987792968</v>
@@ -31397,7 +31397,7 @@
         <v>-1.397199754707969</v>
       </c>
       <c r="AL208" t="n">
-        <v>0.05494505494505494</v>
+        <v>0.0549450549450549</v>
       </c>
       <c r="AM208" t="n">
         <v>192.5299987792968</v>
@@ -31419,6 +31419,1333 @@
       </c>
       <c r="AS208" t="n">
         <v>284.0816506210638</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>313.39</v>
+      </c>
+      <c r="I209" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J209" t="n">
+        <v>37.940678</v>
+      </c>
+      <c r="K209" t="n">
+        <v>67</v>
+      </c>
+      <c r="L209" t="n">
+        <v>62</v>
+      </c>
+      <c r="M209" t="n">
+        <v>32.7632894395273</v>
+      </c>
+      <c r="N209" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="O209" t="n">
+        <v>35.51118035905431</v>
+      </c>
+      <c r="P209" t="n">
+        <v>35.57021762210579</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>1.512379845901221</v>
+      </c>
+      <c r="R209" t="n">
+        <v>33.53231427376279</v>
+      </c>
+      <c r="S209" t="n">
+        <v>37.63087238006961</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.606407046172956</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="V209" t="n">
+        <v>270.6247707704955</v>
+      </c>
+      <c r="W209" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="X209" t="n">
+        <v>293.3223497657886</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>280.8300922386445</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>305.8146072929327</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>276.9769159012807</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>310.831005859375</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>38.15980777324834</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>34.41625615673373</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>1.737530231088972</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>37.18329256441056</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>2.028408933672128</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>0.983739837398374</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>315.2000122070312</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>284.2782758546206</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>269.9262761458257</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>298.6302755634155</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>265.4471175413494</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>307.1339965820313</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>517.405</v>
+      </c>
+      <c r="I210" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J210" t="n">
+        <v>173.04517</v>
+      </c>
+      <c r="K210" t="n">
+        <v>63</v>
+      </c>
+      <c r="L210" t="n">
+        <v>62</v>
+      </c>
+      <c r="M210" t="n">
+        <v>89.29811297722583</v>
+      </c>
+      <c r="N210" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O210" t="n">
+        <v>147.14948632841</v>
+      </c>
+      <c r="P210" t="n">
+        <v>149.8327886862833</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>26.87359235682414</v>
+      </c>
+      <c r="R210" t="n">
+        <v>105.0086831146816</v>
+      </c>
+      <c r="S210" t="n">
+        <v>176.8124559746414</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0.9636107941115741</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0.8548387096774194</v>
+      </c>
+      <c r="V210" t="n">
+        <v>267.0013578019052</v>
+      </c>
+      <c r="W210" t="n">
+        <v>569.4822359679176</v>
+      </c>
+      <c r="X210" t="n">
+        <v>439.9769641219459</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>359.6249229750417</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>520.32900526885</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>313.975962512898</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>528.6692433641779</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>118.0056332643967</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>115.2188628574587</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>37.47598362909357</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>170.4354027920082</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.468661564172386</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>0.926829268292683</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>569.4822359679176</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>352.8368434605462</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>240.7836524095564</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>464.890034511536</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>225.8025376114755</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>509.6018543481046</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>243.62</v>
+      </c>
+      <c r="I211" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J211" t="n">
+        <v>31.353926</v>
+      </c>
+      <c r="K211" t="n">
+        <v>67</v>
+      </c>
+      <c r="L211" t="n">
+        <v>62</v>
+      </c>
+      <c r="M211" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N211" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O211" t="n">
+        <v>31.52021980164974</v>
+      </c>
+      <c r="P211" t="n">
+        <v>31.71949797269831</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>2.566672487168975</v>
+      </c>
+      <c r="R211" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S211" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T211" t="n">
+        <v>-0.06478964592524131</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0.4354838709677419</v>
+      </c>
+      <c r="V211" t="n">
+        <v>210.9889542246549</v>
+      </c>
+      <c r="W211" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="X211" t="n">
+        <v>244.9121078588184</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>224.9690626335155</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>264.8551530841214</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>221.2349494203997</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>271.4569227019115</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>31.04626436780183</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>30.013946575766</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>2.44684834231791</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>34.65216175116588</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>0.1257379245281394</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>210.9889542246549</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>286.0812028062892</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>241.2294741378202</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>222.21746251801</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>260.2414857576304</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>221.2665495585026</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>269.2472968065588</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="I212" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="J212" t="n">
+        <v>64.673874</v>
+      </c>
+      <c r="K212" t="n">
+        <v>34</v>
+      </c>
+      <c r="L212" t="n">
+        <v>62</v>
+      </c>
+      <c r="M212" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N212" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O212" t="n">
+        <v>75.39403907990172</v>
+      </c>
+      <c r="P212" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>9.273698435305844</v>
+      </c>
+      <c r="R212" t="n">
+        <v>62.25973272085587</v>
+      </c>
+      <c r="S212" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T212" t="n">
+        <v>-1.155975165106625</v>
+      </c>
+      <c r="U212" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="V212" t="n">
+        <v>360.4500122070312</v>
+      </c>
+      <c r="W212" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="X212" t="n">
+        <v>453.1181748702093</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>397.3832472740212</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>508.8531024663974</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>374.1809936523437</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>501.7975012825711</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>71.30762729505619</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>69.66666615484147</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>8.285245733190155</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>61.7377704233179</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>-0.8006706751595564</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>0.2520325203252032</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>343.7415442513212</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>564.1785076059562</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>428.5588400432877</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>378.7645131868149</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>478.3531668997605</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>371.0440002441406</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>495.0014039751615</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="I213" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J213" t="n">
+        <v>27.319878</v>
+      </c>
+      <c r="K213" t="n">
+        <v>37</v>
+      </c>
+      <c r="L213" t="n">
+        <v>62</v>
+      </c>
+      <c r="M213" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N213" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O213" t="n">
+        <v>28.93746687069029</v>
+      </c>
+      <c r="P213" t="n">
+        <v>29.21870597964289</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>1.663541126320117</v>
+      </c>
+      <c r="R213" t="n">
+        <v>26.95049620511239</v>
+      </c>
+      <c r="S213" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T213" t="n">
+        <v>-0.9723768442494257</v>
+      </c>
+      <c r="U213" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="V213" t="n">
+        <v>335.2005897830408</v>
+      </c>
+      <c r="W213" t="n">
+        <v>423.3179885059678</v>
+      </c>
+      <c r="X213" t="n">
+        <v>379.9489400121635</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>358.1066450235804</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>401.7912350007467</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>353.8600151731258</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>409.9292998900577</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>29.23492388656339</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>28.80943503013702</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>2.08945458718323</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>26.95057232447202</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>-0.9165290781193984</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>0.1707317073170732</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>331.7602583102668</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>447.04214411262</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>383.8545506305774</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>356.4200119008616</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>411.2890893602932</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>353.8610146203176</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>428.6886625781347</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>603.12</v>
+      </c>
+      <c r="I214" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="J214" t="n">
+        <v>21.915697</v>
+      </c>
+      <c r="K214" t="n">
+        <v>55</v>
+      </c>
+      <c r="L214" t="n">
+        <v>62</v>
+      </c>
+      <c r="M214" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N214" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O214" t="n">
+        <v>23.29193013545308</v>
+      </c>
+      <c r="P214" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>2.953037955418361</v>
+      </c>
+      <c r="R214" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S214" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T214" t="n">
+        <v>-0.4660397720008675</v>
+      </c>
+      <c r="U214" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="V214" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="W214" t="n">
+        <v>806.6792534722222</v>
+      </c>
+      <c r="X214" t="n">
+        <v>640.9939173276688</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>559.7263127945556</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>722.2615218607821</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>564.5732764204546</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>786.4663274265644</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>25.26575414132806</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>26.12643771701389</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>3.165217753481453</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>28.79957437007769</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>-1.058397052665114</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0.1869918699186992</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>864.9762082934226</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>695.3135539693483</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>608.2067613935387</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>782.4203465451579</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>583.6621980113637</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>792.564286664538</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>383.34</v>
+      </c>
+      <c r="I215" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J215" t="n">
+        <v>22.817858</v>
+      </c>
+      <c r="K215" t="n">
+        <v>67</v>
+      </c>
+      <c r="L215" t="n">
+        <v>62</v>
+      </c>
+      <c r="M215" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N215" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O215" t="n">
+        <v>24.43130433296766</v>
+      </c>
+      <c r="P215" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>1.498237226573082</v>
+      </c>
+      <c r="R215" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S215" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T215" t="n">
+        <v>-1.076896438261715</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="V215" t="n">
+        <v>352.8299865722656</v>
+      </c>
+      <c r="W215" t="n">
+        <v>460.5199890136719</v>
+      </c>
+      <c r="X215" t="n">
+        <v>410.4459127938567</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>385.275527387429</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>435.6162982002845</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>374.4370025634765</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>445.5025934788345</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>25.41564615826555</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>24.91488138834635</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2.865468283736575</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>22.87653350489267</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>29.57894141610352</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>-0.9065841604353843</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0.0975609756097561</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>352.8299865722656</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>574.2349768431054</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>426.9828554588612</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>378.8429882920867</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>475.1227226256357</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>384.3257628821969</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>496.9262157905391</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="I216" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>24.383871</v>
+      </c>
+      <c r="K216" t="n">
+        <v>67</v>
+      </c>
+      <c r="L216" t="n">
+        <v>6</v>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="n">
+        <v>67</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>31.47550348831933</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>35.93675816954359</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>11.52676783905264</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>3.736006721617684</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>39.23241053645317</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>-0.6152316579408244</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0.1343283582089552</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>97.57406081378991</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>61.84108051272673</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>133.3070411148531</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>11.58162083701482</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>121.6204726630048</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-07-08 16:34:09</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>204.12</v>
+      </c>
+      <c r="I217" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J217" t="n">
+        <v>31.211008</v>
+      </c>
+      <c r="K217" t="n">
+        <v>65</v>
+      </c>
+      <c r="L217" t="n">
+        <v>62</v>
+      </c>
+      <c r="M217" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N217" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O217" t="n">
+        <v>36.66349891698048</v>
+      </c>
+      <c r="P217" t="n">
+        <v>34.17228243069845</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>5.664588291130952</v>
+      </c>
+      <c r="R217" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S217" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T217" t="n">
+        <v>-0.9625573186876525</v>
+      </c>
+      <c r="U217" t="n">
+        <v>0.1774193548387097</v>
+      </c>
+      <c r="V217" t="n">
+        <v>192.8248379811028</v>
+      </c>
+      <c r="W217" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="X217" t="n">
+        <v>239.7792829170523</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>202.7328754930559</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>276.8256903410488</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>198.024791849554</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>292.5075091365892</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>92</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>36.63531708582996</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>36.39387792470504</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>4.687014959029563</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>30.64670697105606</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>43.46999966368383</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>-1.157305690987821</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0.1195652173913044</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>192.8248379811028</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>239.5949737413279</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>208.9418959092746</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>270.2480515733812</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>200.4294635907066</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>284.2937978004923</v>
       </c>
     </row>
   </sheetData>
@@ -31665,12 +32992,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -31699,13 +33026,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>363.62</v>
+        <v>358.71</v>
       </c>
       <c r="I2" t="n">
-        <v>13.1</v>
+        <v>13.13</v>
       </c>
       <c r="J2" t="n">
-        <v>27.75725</v>
+        <v>27.319878</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -31720,13 +33047,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.96575844096208</v>
+        <v>28.93746687069029</v>
       </c>
       <c r="P2" t="n">
         <v>29.21870597964289</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.651170148297226</v>
+        <v>1.663541126320117</v>
       </c>
       <c r="R2" t="n">
         <v>26.95049620511239</v>
@@ -31735,31 +33062,31 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7319103014358367</v>
+        <v>-0.9723768442494257</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="V2" t="n">
-        <v>334.434708770589</v>
+        <v>335.2005897830408</v>
       </c>
       <c r="W2" t="n">
-        <v>422.3507729952915</v>
+        <v>423.3179885059678</v>
       </c>
       <c r="X2" t="n">
-        <v>379.4514355766032</v>
+        <v>379.9489400121635</v>
       </c>
       <c r="Y2" t="n">
-        <v>357.8211066339096</v>
+        <v>358.1066450235804</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.0817645192968</v>
+        <v>401.7912350007467</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.0515002869723</v>
+        <v>353.8600151731258</v>
       </c>
       <c r="AB2" t="n">
-        <v>408.9926754424794</v>
+        <v>409.9292998900577</v>
       </c>
       <c r="AC2" t="n">
         <v>123</v>
@@ -31771,13 +33098,13 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.27411958912855</v>
+        <v>29.23492388656339</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.83348773741038</v>
+        <v>28.80943503013702</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.099220338250603</v>
+        <v>2.08945458718323</v>
       </c>
       <c r="AI2" t="n">
         <v>26.95057232447202</v>
@@ -31786,42 +33113,42 @@
         <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.72258712508123</v>
+        <v>-0.9165290781193984</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.002237918088</v>
+        <v>331.7602583102668</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.0207226104586</v>
+        <v>447.04214411262</v>
       </c>
       <c r="AO2" t="n">
-        <v>383.490966617584</v>
+        <v>383.8545506305774</v>
       </c>
       <c r="AP2" t="n">
-        <v>355.9911801865011</v>
+        <v>356.4200119008616</v>
       </c>
       <c r="AQ2" t="n">
-        <v>410.9907530486669</v>
+        <v>411.2890893602932</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.0524974505834</v>
+        <v>353.8610146203176</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.7091759157322</v>
+        <v>428.6886625781347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -31850,13 +33177,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>388.84</v>
+        <v>383.34</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.8</v>
       </c>
       <c r="J3" t="n">
-        <v>23.172823</v>
+        <v>22.817858</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -31871,13 +33198,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.44085914983256</v>
+        <v>24.43130433296766</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.489643316249973</v>
+        <v>1.498237226573082</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -31886,31 +33213,31 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8512347459287867</v>
+        <v>-1.076896438261715</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="V3" t="n">
-        <v>352.4099508739653</v>
+        <v>352.8299865722656</v>
       </c>
       <c r="W3" t="n">
-        <v>459.9717509315128</v>
+        <v>460.5199890136719</v>
       </c>
       <c r="X3" t="n">
-        <v>410.1176165341904</v>
+        <v>410.4459127938567</v>
       </c>
       <c r="Y3" t="n">
-        <v>385.1214016875159</v>
+        <v>385.275527387429</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.113831380865</v>
+        <v>435.6162982002845</v>
       </c>
       <c r="AA3" t="n">
-        <v>373.9912442270914</v>
+        <v>374.4370025634765</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.9722332485025</v>
+        <v>445.5025934788345</v>
       </c>
       <c r="AC3" t="n">
         <v>123</v>
@@ -31922,57 +33249,57 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.50659835904723</v>
+        <v>25.41564615826555</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.91932404346955</v>
+        <v>24.91488138834635</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.958374398559627</v>
+        <v>2.865468283736575</v>
       </c>
       <c r="AI3" t="n">
-        <v>22.91399127868527</v>
+        <v>22.87653350489267</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31.2935561003528</v>
+        <v>29.57894141610352</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.7888708610321596</v>
+        <v>-0.9065841604353843</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1382113821138211</v>
+        <v>0.0975609756097561</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.4099508739653</v>
+        <v>352.8299865722656</v>
       </c>
       <c r="AN3" t="n">
-        <v>573.551363775435</v>
+        <v>574.2349768431054</v>
       </c>
       <c r="AO3" t="n">
-        <v>428.0007204648126</v>
+        <v>426.9828554588612</v>
       </c>
       <c r="AP3" t="n">
-        <v>378.3591980569821</v>
+        <v>378.8429882920867</v>
       </c>
       <c r="AQ3" t="n">
-        <v>477.6422428726431</v>
+        <v>475.1227226256357</v>
       </c>
       <c r="AR3" t="n">
-        <v>384.4967736563389</v>
+        <v>384.3257628821969</v>
       </c>
       <c r="AS3" t="n">
-        <v>525.10587136392</v>
+        <v>496.9262157905391</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -32001,13 +33328,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>615.58</v>
+        <v>603.12</v>
       </c>
       <c r="I4" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="J4" t="n">
-        <v>22.392872</v>
+        <v>21.915697</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -32022,13 +33349,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.35870244000214</v>
+        <v>23.29193013545308</v>
       </c>
       <c r="P4" t="n">
-        <v>22.21127263849432</v>
+        <v>22.19399968927557</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.968539157813888</v>
+        <v>2.953037955418361</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
@@ -32037,31 +33364,31 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3253554656538201</v>
+        <v>-0.4660397720008675</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="V4" t="n">
-        <v>542.6725878462358</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="W4" t="n">
-        <v>805.7998792860242</v>
+        <v>806.6792534722222</v>
       </c>
       <c r="X4" t="n">
-        <v>642.1307300756587</v>
+        <v>640.9939173276688</v>
       </c>
       <c r="Y4" t="n">
-        <v>560.5255886273549</v>
+        <v>559.7263127945556</v>
       </c>
       <c r="Z4" t="n">
-        <v>723.7358715239625</v>
+        <v>722.2615218607821</v>
       </c>
       <c r="AA4" t="n">
-        <v>563.9578259011008</v>
+        <v>564.5732764204546</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.6089876800964</v>
+        <v>786.4663274265644</v>
       </c>
       <c r="AC4" t="n">
         <v>123</v>
@@ -32073,13 +33400,13 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.32006641583422</v>
+        <v>25.26575414132806</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.2103019444777</v>
+        <v>26.12643771701389</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.164853240545059</v>
+        <v>3.165217753481453</v>
       </c>
       <c r="AI4" t="n">
         <v>21.20865545099432</v>
@@ -32088,42 +33415,42 @@
         <v>28.79957437007769</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.9249068419141249</v>
+        <v>-1.058397052665114</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.1869918699186992</v>
       </c>
       <c r="AM4" t="n">
-        <v>542.6725878462358</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.0332836477539</v>
+        <v>864.9762082934226</v>
       </c>
       <c r="AO4" t="n">
-        <v>696.0486257712826</v>
+        <v>695.3135539693483</v>
       </c>
       <c r="AP4" t="n">
-        <v>609.0468101886988</v>
+        <v>608.2067613935387</v>
       </c>
       <c r="AQ4" t="n">
-        <v>783.0504413538663</v>
+        <v>782.4203465451579</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.0259383478337</v>
+        <v>583.6621980113637</v>
       </c>
       <c r="AS4" t="n">
-        <v>791.7002994334356</v>
+        <v>792.564286664538</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -32152,13 +33479,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>245.98</v>
+        <v>243.62</v>
       </c>
       <c r="I5" t="n">
-        <v>7.72</v>
+        <v>7.77</v>
       </c>
       <c r="J5" t="n">
-        <v>31.862694</v>
+        <v>31.353926</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -32173,13 +33500,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.54790678301238</v>
+        <v>31.52021980164974</v>
       </c>
       <c r="P5" t="n">
         <v>31.71949797269831</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.549791488128202</v>
+        <v>2.566672487168975</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -32188,31 +33515,31 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.123456062369518</v>
+        <v>-0.06478964592524131</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="V5" t="n">
-        <v>209.631238946504</v>
+        <v>210.9889542246549</v>
       </c>
       <c r="W5" t="n">
-        <v>284.2402684252964</v>
+        <v>286.0812028062892</v>
       </c>
       <c r="X5" t="n">
-        <v>243.5498403648556</v>
+        <v>244.9121078588184</v>
       </c>
       <c r="Y5" t="n">
-        <v>223.8654500765058</v>
+        <v>224.9690626335155</v>
       </c>
       <c r="Z5" t="n">
-        <v>263.2342306532053</v>
+        <v>264.8551530841214</v>
       </c>
       <c r="AA5" t="n">
-        <v>219.8113010972311</v>
+        <v>221.2349494203997</v>
       </c>
       <c r="AB5" t="n">
-        <v>269.7100956574976</v>
+        <v>271.4569227019115</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -32224,57 +33551,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.0921633472674</v>
+        <v>31.04626436780183</v>
       </c>
       <c r="AG5" t="n">
-        <v>30.23988944549773</v>
+        <v>30.013946575766</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.463711348559294</v>
+        <v>2.44684834231791</v>
       </c>
       <c r="AI5" t="n">
         <v>28.4770334052127</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.71631846833595</v>
+        <v>34.65216175116588</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.312752000425369</v>
+        <v>0.1257379245281394</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6178861788617886</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="AM5" t="n">
-        <v>209.631238946504</v>
+        <v>210.9889542246549</v>
       </c>
       <c r="AN5" t="n">
-        <v>284.2402684252964</v>
+        <v>286.0812028062892</v>
       </c>
       <c r="AO5" t="n">
-        <v>240.0315010409043</v>
+        <v>241.2294741378202</v>
       </c>
       <c r="AP5" t="n">
-        <v>221.0116494300266</v>
+        <v>222.21746251801</v>
       </c>
       <c r="AQ5" t="n">
-        <v>259.0513526517821</v>
+        <v>260.2414857576304</v>
       </c>
       <c r="AR5" t="n">
-        <v>219.842697888242</v>
+        <v>221.2665495585026</v>
       </c>
       <c r="AS5" t="n">
-        <v>268.0099785755535</v>
+        <v>269.2472968065588</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -32303,13 +33630,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>310.66</v>
+        <v>313.39</v>
       </c>
       <c r="I6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>37.655758</v>
+        <v>37.940678</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -32324,46 +33651,46 @@
         <v>38.15980777324834</v>
       </c>
       <c r="O6" t="n">
-        <v>35.42781699432231</v>
+        <v>35.51118035905431</v>
       </c>
       <c r="P6" t="n">
-        <v>35.49636766927871</v>
+        <v>35.57021762210579</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.518702037811088</v>
+        <v>1.512379845901221</v>
       </c>
       <c r="R6" t="n">
-        <v>33.3590468633119</v>
+        <v>33.53231427376279</v>
       </c>
       <c r="S6" t="n">
-        <v>37.6053273937604</v>
+        <v>37.63087238006961</v>
       </c>
       <c r="T6" t="n">
-        <v>1.467003368803552</v>
+        <v>1.606407046172956</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="V6" t="n">
-        <v>270.2971378761002</v>
+        <v>270.6247707704955</v>
       </c>
       <c r="W6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="X6" t="n">
-        <v>292.2794902031591</v>
+        <v>293.3223497657886</v>
       </c>
       <c r="Y6" t="n">
-        <v>279.7501983912176</v>
+        <v>280.8300922386445</v>
       </c>
       <c r="Z6" t="n">
-        <v>304.8087820151006</v>
+        <v>305.8146072929327</v>
       </c>
       <c r="AA6" t="n">
-        <v>275.2121366223232</v>
+        <v>276.9769159012807</v>
       </c>
       <c r="AB6" t="n">
-        <v>310.2439509985234</v>
+        <v>310.831005859375</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -32375,57 +33702,57 @@
         <v>38.15980777324834</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.39010316482904</v>
+        <v>34.41625615673373</v>
       </c>
       <c r="AG6" t="n">
         <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.708005042001887</v>
+        <v>1.737530231088972</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.05157337696731</v>
+        <v>37.18329256441056</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.911970254691642</v>
+        <v>2.028408933672128</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.959349593495935</v>
+        <v>0.983739837398374</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.5566506687599</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="AN6" t="n">
-        <v>314.8184141292988</v>
+        <v>315.2000122070312</v>
       </c>
       <c r="AO6" t="n">
-        <v>283.7183511098396</v>
+        <v>284.2782758546206</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.6273095133241</v>
+        <v>269.9262761458257</v>
       </c>
       <c r="AQ6" t="n">
-        <v>297.8093927063551</v>
+        <v>298.6302755634155</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.1257529922678</v>
+        <v>265.4471175413494</v>
       </c>
       <c r="AS6" t="n">
-        <v>305.6754803599803</v>
+        <v>307.1339965820313</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -32454,13 +33781,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>196.93</v>
+        <v>204.12</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="J7" t="n">
-        <v>30.157732</v>
+        <v>31.211008</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -32475,13 +33802,13 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.75866632475287</v>
+        <v>36.66349891698048</v>
       </c>
       <c r="P7" t="n">
-        <v>34.29019922136712</v>
+        <v>34.17228243069845</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.621700711197021</v>
+        <v>5.664588291130952</v>
       </c>
       <c r="R7" t="n">
         <v>30.27902016048226</v>
@@ -32490,34 +33817,34 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.17418814409765</v>
+        <v>-0.9625573186876525</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="V7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.8248379811028</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="X7" t="n">
-        <v>240.0340911006362</v>
+        <v>239.7792829170523</v>
       </c>
       <c r="Y7" t="n">
-        <v>203.3243854565197</v>
+        <v>202.7328754930559</v>
       </c>
       <c r="Z7" t="n">
-        <v>276.7437967447528</v>
+        <v>276.8256903410488</v>
       </c>
       <c r="AA7" t="n">
-        <v>197.7220016479492</v>
+        <v>198.024791849554</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.0602499483069</v>
+        <v>292.5075091365892</v>
       </c>
       <c r="AC7" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -32526,57 +33853,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.69439963880319</v>
+        <v>36.63531708582996</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.44081582828444</v>
+        <v>36.39387792470504</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.678405945017813</v>
+        <v>4.687014959029563</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.64165334424052</v>
+        <v>30.64670697105606</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.50408125896843</v>
+        <v>43.46999966368383</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.397199754707969</v>
+        <v>-1.157305690987821</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.05494505494505494</v>
+        <v>0.1195652173913044</v>
       </c>
       <c r="AM7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.8248379811028</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="AO7" t="n">
-        <v>239.6144296413848</v>
+        <v>239.5949737413279</v>
       </c>
       <c r="AP7" t="n">
-        <v>209.0644388204185</v>
+        <v>208.9418959092746</v>
       </c>
       <c r="AQ7" t="n">
-        <v>270.1644204623512</v>
+        <v>270.2480515733812</v>
       </c>
       <c r="AR7" t="n">
-        <v>200.0899963378906</v>
+        <v>200.4294635907066</v>
       </c>
       <c r="AS7" t="n">
-        <v>284.0816506210638</v>
+        <v>284.2937978004923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -32605,13 +33932,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>516.11</v>
+        <v>517.405</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>173.19127</v>
+        <v>173.04517</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -32620,52 +33947,52 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>87.479248046875</v>
+        <v>89.29811297722583</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>145.8242968902614</v>
+        <v>147.14948632841</v>
       </c>
       <c r="P8" t="n">
-        <v>148.7852453012936</v>
+        <v>149.8327886862833</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.75755029866852</v>
+        <v>26.87359235682414</v>
       </c>
       <c r="R8" t="n">
-        <v>103.8796271558078</v>
+        <v>105.0086831146816</v>
       </c>
       <c r="S8" t="n">
         <v>176.8124559746414</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9859289748292874</v>
+        <v>0.9636107941115741</v>
       </c>
       <c r="U8" t="n">
         <v>0.8548387096774194</v>
       </c>
       <c r="V8" t="n">
-        <v>260.6881591796875</v>
+        <v>267.0013578019052</v>
       </c>
       <c r="W8" t="n">
-        <v>567.5776131051485</v>
+        <v>569.4822359679176</v>
       </c>
       <c r="X8" t="n">
-        <v>434.5564047329789</v>
+        <v>439.9769641219459</v>
       </c>
       <c r="Y8" t="n">
-        <v>351.8389048429467</v>
+        <v>359.6249229750417</v>
       </c>
       <c r="Z8" t="n">
-        <v>517.273904623011</v>
+        <v>520.32900526885</v>
       </c>
       <c r="AA8" t="n">
-        <v>309.5612889243072</v>
+        <v>313.975962512898</v>
       </c>
       <c r="AB8" t="n">
-        <v>526.9011188044313</v>
+        <v>528.6692433641779</v>
       </c>
       <c r="AC8" t="n">
         <v>123</v>
@@ -32677,13 +34004,13 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>117.4461746415253</v>
+        <v>118.0056332643967</v>
       </c>
       <c r="AG8" t="n">
-        <v>114.513204322671</v>
+        <v>115.2188628574587</v>
       </c>
       <c r="AH8" t="n">
-        <v>37.21153502478618</v>
+        <v>37.47598362909357</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51924334831958</v>
@@ -32692,42 +34019,42 @@
         <v>170.4354027920082</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.49805954850676</v>
+        <v>1.468661564172386</v>
       </c>
       <c r="AL8" t="n">
         <v>0.926829268292683</v>
       </c>
       <c r="AM8" t="n">
-        <v>214.728675813495</v>
+        <v>215.4492418397148</v>
       </c>
       <c r="AN8" t="n">
-        <v>567.5776131051485</v>
+        <v>569.4822359679176</v>
       </c>
       <c r="AO8" t="n">
-        <v>349.9896004317454</v>
+        <v>352.8368434605462</v>
       </c>
       <c r="AP8" t="n">
-        <v>239.0992260578826</v>
+        <v>240.7836524095564</v>
       </c>
       <c r="AQ8" t="n">
-        <v>460.8799748056082</v>
+        <v>464.890034511536</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.0473451779923</v>
+        <v>225.8025376114755</v>
       </c>
       <c r="AS8" t="n">
-        <v>507.8975003201845</v>
+        <v>509.6018543481046</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -32756,13 +34083,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>370.78</v>
+        <v>388.69</v>
       </c>
       <c r="I9" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="J9" t="n">
-        <v>61.591362</v>
+        <v>64.673874</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -32777,13 +34104,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.45331410488485</v>
+        <v>75.39403907990172</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.215617814122464</v>
+        <v>9.273698435305844</v>
       </c>
       <c r="R9" t="n">
         <v>62.25973272085587</v>
@@ -32792,31 +34119,31 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.504180445031273</v>
+        <v>-1.155975165106625</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="V9" t="n">
-        <v>361.0497626433158</v>
+        <v>360.4500122070312</v>
       </c>
       <c r="W9" t="n">
-        <v>565.1172405637031</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="X9" t="n">
-        <v>454.2289509114068</v>
+        <v>453.1181748702093</v>
       </c>
       <c r="Y9" t="n">
-        <v>398.7509316703895</v>
+        <v>397.3832472740212</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.706970152424</v>
+        <v>508.8531024663974</v>
       </c>
       <c r="AA9" t="n">
-        <v>374.8035909795523</v>
+        <v>374.1809936523437</v>
       </c>
       <c r="AB9" t="n">
-        <v>502.6324388886986</v>
+        <v>501.7975012825711</v>
       </c>
       <c r="AC9" t="n">
         <v>123</v>
@@ -32828,13 +34155,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.34850884875353</v>
+        <v>71.30762729505619</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.70230838287802</v>
+        <v>69.66666615484147</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.264624918986181</v>
+        <v>8.285245733190155</v>
       </c>
       <c r="AI9" t="n">
         <v>61.7377704233179</v>
@@ -32843,42 +34170,42 @@
         <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.18059161116176</v>
+        <v>-0.8006706751595564</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0975609756097561</v>
+        <v>0.2520325203252032</v>
       </c>
       <c r="AM9" t="n">
-        <v>344.3134935761985</v>
+        <v>343.7415442513212</v>
       </c>
       <c r="AN9" t="n">
-        <v>565.1172405637031</v>
+        <v>564.1785076059562</v>
       </c>
       <c r="AO9" t="n">
-        <v>429.5180232694962</v>
+        <v>428.5588400432877</v>
       </c>
       <c r="AP9" t="n">
-        <v>379.7649812571994</v>
+        <v>378.7645131868149</v>
       </c>
       <c r="AQ9" t="n">
-        <v>479.271065281793</v>
+        <v>478.3531668997605</v>
       </c>
       <c r="AR9" t="n">
-        <v>371.6613779483737</v>
+        <v>371.0440002441406</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.8250335990802</v>
+        <v>495.0014039751615</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:03</t>
+          <t>2026-07-08 16:34:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -32907,19 +34234,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>76.18000000000001</v>
+        <v>75.59</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>24.574194</v>
+        <v>24.383871</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -32938,7 +34265,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -32947,25 +34274,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>31.06823927709822</v>
+        <v>31.47550348831933</v>
       </c>
       <c r="AG10" t="n">
-        <v>34.98814247342436</v>
+        <v>35.93675816954359</v>
       </c>
       <c r="AH10" t="n">
-        <v>11.92317314857364</v>
+        <v>11.52676783905264</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.736215557968407</v>
+        <v>3.736006721617684</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.22371483603013</v>
+        <v>39.23241053645317</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.5446574662781865</v>
+        <v>-0.6152316579408244</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -32974,19 +34301,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>96.31154175900448</v>
+        <v>97.57406081378991</v>
       </c>
       <c r="AP10" t="n">
-        <v>59.34970499842622</v>
+        <v>61.84108051272673</v>
       </c>
       <c r="AQ10" t="n">
-        <v>133.2733785195828</v>
+        <v>133.3070411148531</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.58226822970206</v>
+        <v>11.58162083701482</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.5935159916934</v>
+        <v>121.6204726630048</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS217"/>
+  <dimension ref="A1:AS226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30218,7 +30218,7 @@
         <v>37.05157337696731</v>
       </c>
       <c r="AK200" t="n">
-        <v>1.911970254691642</v>
+        <v>1.911970254691641</v>
       </c>
       <c r="AL200" t="n">
         <v>0.959349593495935</v>
@@ -31518,7 +31518,7 @@
         <v>276.9769159012807</v>
       </c>
       <c r="AB209" t="n">
-        <v>310.831005859375</v>
+        <v>310.8310058593749</v>
       </c>
       <c r="AC209" t="n">
         <v>123</v>
@@ -31645,7 +31645,7 @@
         <v>176.8124559746414</v>
       </c>
       <c r="T210" t="n">
-        <v>0.9636107941115741</v>
+        <v>0.963610794111574</v>
       </c>
       <c r="U210" t="n">
         <v>0.8548387096774194</v>
@@ -31717,7 +31717,7 @@
         <v>464.890034511536</v>
       </c>
       <c r="AR210" t="n">
-        <v>225.8025376114755</v>
+        <v>225.8025376114756</v>
       </c>
       <c r="AS210" t="n">
         <v>509.6018543481046</v>
@@ -31784,7 +31784,7 @@
         <v>31.52021980164974</v>
       </c>
       <c r="P211" t="n">
-        <v>31.71949797269831</v>
+        <v>31.7194979726983</v>
       </c>
       <c r="Q211" t="n">
         <v>2.566672487168975</v>
@@ -31796,7 +31796,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T211" t="n">
-        <v>-0.06478964592524131</v>
+        <v>-0.06478964592524129</v>
       </c>
       <c r="U211" t="n">
         <v>0.4354838709677419</v>
@@ -31814,7 +31814,7 @@
         <v>224.9690626335155</v>
       </c>
       <c r="Z211" t="n">
-        <v>264.8551530841214</v>
+        <v>264.8551530841213</v>
       </c>
       <c r="AA211" t="n">
         <v>221.2349494203997</v>
@@ -31929,7 +31929,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N212" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O212" t="n">
         <v>75.39403907990172</v>
@@ -31953,7 +31953,7 @@
         <v>0.2258064516129032</v>
       </c>
       <c r="V212" t="n">
-        <v>360.4500122070312</v>
+        <v>360.4500122070313</v>
       </c>
       <c r="W212" t="n">
         <v>564.1785076059562</v>
@@ -31971,7 +31971,7 @@
         <v>374.1809936523437</v>
       </c>
       <c r="AB212" t="n">
-        <v>501.7975012825711</v>
+        <v>501.7975012825712</v>
       </c>
       <c r="AC212" t="n">
         <v>123</v>
@@ -31980,7 +31980,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE212" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF212" t="n">
         <v>71.30762729505619</v>
@@ -31992,7 +31992,7 @@
         <v>8.285245733190155</v>
       </c>
       <c r="AI212" t="n">
-        <v>61.7377704233179</v>
+        <v>61.73777042331791</v>
       </c>
       <c r="AJ212" t="n">
         <v>82.36296239187379</v>
@@ -32092,13 +32092,13 @@
         <v>1.663541126320117</v>
       </c>
       <c r="R213" t="n">
-        <v>26.95049620511239</v>
+        <v>26.9504962051124</v>
       </c>
       <c r="S213" t="n">
         <v>31.22081491927324</v>
       </c>
       <c r="T213" t="n">
-        <v>-0.9723768442494257</v>
+        <v>-0.9723768442494256</v>
       </c>
       <c r="U213" t="n">
         <v>0.2096774193548387</v>
@@ -32134,7 +32134,7 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF213" t="n">
-        <v>29.23492388656339</v>
+        <v>29.2349238865634</v>
       </c>
       <c r="AG213" t="n">
         <v>28.80943503013702</v>
@@ -32152,7 +32152,7 @@
         <v>-0.9165290781193984</v>
       </c>
       <c r="AL213" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1707317073170731</v>
       </c>
       <c r="AM213" t="n">
         <v>331.7602583102668</v>
@@ -32303,7 +32303,7 @@
         <v>-1.058397052665114</v>
       </c>
       <c r="AL214" t="n">
-        <v>0.1869918699186992</v>
+        <v>0.1869918699186991</v>
       </c>
       <c r="AM214" t="n">
         <v>543.2648096590909</v>
@@ -32403,7 +32403,7 @@
         <v>-1.076896438261715</v>
       </c>
       <c r="U215" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1612903225806451</v>
       </c>
       <c r="V215" t="n">
         <v>352.8299865722656</v>
@@ -32451,7 +32451,7 @@
         <v>29.57894141610352</v>
       </c>
       <c r="AK215" t="n">
-        <v>-0.9065841604353843</v>
+        <v>-0.9065841604353844</v>
       </c>
       <c r="AL215" t="n">
         <v>0.0975609756097561</v>
@@ -32549,7 +32549,7 @@
         <v>67</v>
       </c>
       <c r="AD216" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE216" t="n">
         <v>42.60474344487245</v>
@@ -32670,7 +32670,7 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T217" t="n">
-        <v>-0.9625573186876525</v>
+        <v>-0.9625573186876524</v>
       </c>
       <c r="U217" t="n">
         <v>0.1774193548387097</v>
@@ -32682,10 +32682,10 @@
         <v>314.64074202557</v>
       </c>
       <c r="X217" t="n">
-        <v>239.7792829170523</v>
+        <v>239.7792829170524</v>
       </c>
       <c r="Y217" t="n">
-        <v>202.7328754930559</v>
+        <v>202.732875493056</v>
       </c>
       <c r="Z217" t="n">
         <v>276.8256903410488</v>
@@ -32724,7 +32724,7 @@
         <v>-1.157305690987821</v>
       </c>
       <c r="AL217" t="n">
-        <v>0.1195652173913044</v>
+        <v>0.1195652173913043</v>
       </c>
       <c r="AM217" t="n">
         <v>192.8248379811028</v>
@@ -32746,6 +32746,1333 @@
       </c>
       <c r="AS217" t="n">
         <v>284.2937978004923</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>316.22</v>
+      </c>
+      <c r="I218" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="J218" t="n">
+        <v>38.237</v>
+      </c>
+      <c r="K218" t="n">
+        <v>67</v>
+      </c>
+      <c r="L218" t="n">
+        <v>62</v>
+      </c>
+      <c r="M218" t="n">
+        <v>32.7632894395273</v>
+      </c>
+      <c r="N218" t="n">
+        <v>38.28329312599312</v>
+      </c>
+      <c r="O218" t="n">
+        <v>35.59682353067735</v>
+      </c>
+      <c r="P218" t="n">
+        <v>35.63438212323131</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>1.516653292199783</v>
+      </c>
+      <c r="R218" t="n">
+        <v>33.69569763956191</v>
+      </c>
+      <c r="S218" t="n">
+        <v>37.67457754213643</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.740791044928463</v>
+      </c>
+      <c r="U218" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V218" t="n">
+        <v>270.9524036648908</v>
+      </c>
+      <c r="W218" t="n">
+        <v>316.6028341519631</v>
+      </c>
+      <c r="X218" t="n">
+        <v>294.3857305987016</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>281.8430078722095</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>306.9284533251939</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>278.663419479177</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>311.5687562734682</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>38.28329312599312</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>34.44483499629292</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.771933052448062</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>37.3041148335824</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>2.140128826237489</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0.9918699186991869</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>258.1810304279569</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>316.6028341519631</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>284.8587854193424</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>270.2048990755969</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>299.5126717630879</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>265.768482090431</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>308.5050296737264</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>546.72</v>
+      </c>
+      <c r="I219" t="n">
+        <v>3</v>
+      </c>
+      <c r="J219" t="n">
+        <v>182.23999</v>
+      </c>
+      <c r="K219" t="n">
+        <v>63</v>
+      </c>
+      <c r="L219" t="n">
+        <v>62</v>
+      </c>
+      <c r="M219" t="n">
+        <v>92.4679219947671</v>
+      </c>
+      <c r="N219" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O219" t="n">
+        <v>148.6003888665921</v>
+      </c>
+      <c r="P219" t="n">
+        <v>151.667215316022</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>26.1166871992592</v>
+      </c>
+      <c r="R219" t="n">
+        <v>105.2830234743514</v>
+      </c>
+      <c r="S219" t="n">
+        <v>177.2921322681865</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.288050083716669</v>
+      </c>
+      <c r="U219" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V219" t="n">
+        <v>277.4037659843013</v>
+      </c>
+      <c r="W219" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="X219" t="n">
+        <v>445.8011665997764</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>367.4511050019988</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>524.151228197554</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>315.8490704230543</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>531.8763968045594</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>118.6492944628045</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>116.6157614421375</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>37.8437260581015</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>170.8858942751025</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.680349747790815</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0.9918699186991869</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>216.1698078659346</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>571.3868588306865</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>355.9478833884134</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>242.4167052141089</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>469.4790615627179</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>226.5577300449587</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>512.6576828253073</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>247.04</v>
+      </c>
+      <c r="I220" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J220" t="n">
+        <v>32.08312</v>
+      </c>
+      <c r="K220" t="n">
+        <v>67</v>
+      </c>
+      <c r="L220" t="n">
+        <v>62</v>
+      </c>
+      <c r="M220" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N220" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O220" t="n">
+        <v>31.47123706816419</v>
+      </c>
+      <c r="P220" t="n">
+        <v>31.70275163422361</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>2.574942171152248</v>
+      </c>
+      <c r="R220" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S220" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T220" t="n">
+        <v>0.2376297761910512</v>
+      </c>
+      <c r="U220" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="V220" t="n">
+        <v>209.0881528352436</v>
+      </c>
+      <c r="W220" t="n">
+        <v>283.5038946728993</v>
+      </c>
+      <c r="X220" t="n">
+        <v>242.3285254248643</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>222.501470706992</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>262.1555801427367</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>219.2418417679636</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>269.0113648397321</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>31.00243965053021</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>29.90669907565323</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>2.424697965464038</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>34.61395611388885</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>0.4456968929171228</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0.6422764227642277</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>209.0881528352436</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>283.5038946728993</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>238.7187853090826</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>220.0486109750095</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>257.3889596431557</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>219.2731572201378</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>266.5274620769441</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>401.11</v>
+      </c>
+      <c r="I221" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J221" t="n">
+        <v>66.62956</v>
+      </c>
+      <c r="K221" t="n">
+        <v>34</v>
+      </c>
+      <c r="L221" t="n">
+        <v>62</v>
+      </c>
+      <c r="M221" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N221" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O221" t="n">
+        <v>75.35463897657367</v>
+      </c>
+      <c r="P221" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>9.305652323737203</v>
+      </c>
+      <c r="R221" t="n">
+        <v>62.25973272085587</v>
+      </c>
+      <c r="S221" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T221" t="n">
+        <v>-0.937610677149136</v>
+      </c>
+      <c r="U221" t="n">
+        <v>0.3064516129032258</v>
+      </c>
+      <c r="V221" t="n">
+        <v>361.0497626433158</v>
+      </c>
+      <c r="W221" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X221" t="n">
+        <v>453.6349266389735</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>397.6148996500755</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>509.6549536278714</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>374.8035909795523</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>502.6324388886986</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>71.26225880076412</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>69.45492406561191</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>8.294925323900546</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>61.7377704233179</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>-0.558497951442156</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0.3414634146341464</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>428.9987979805999</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>379.0633475307187</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>478.9342484304812</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>371.6613779483737</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>495.8250335990802</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="I222" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="J222" t="n">
+        <v>27.214666</v>
+      </c>
+      <c r="K222" t="n">
+        <v>37</v>
+      </c>
+      <c r="L222" t="n">
+        <v>62</v>
+      </c>
+      <c r="M222" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N222" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O222" t="n">
+        <v>28.90370445121074</v>
+      </c>
+      <c r="P222" t="n">
+        <v>29.16988832978413</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>1.677935137236142</v>
+      </c>
+      <c r="R222" t="n">
+        <v>26.95049620511239</v>
+      </c>
+      <c r="S222" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T222" t="n">
+        <v>-1.006617248621952</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V222" t="n">
+        <v>334.1794150997717</v>
+      </c>
+      <c r="W222" t="n">
+        <v>422.0283678250661</v>
+      </c>
+      <c r="X222" t="n">
+        <v>378.3494912663486</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>356.3853203199275</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>400.3136622127697</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>352.7819953249212</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>408.6804672932867</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>29.19168436619016</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>28.80018377171745</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>2.076498146743965</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>26.95057232447202</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>32.64955541341467</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>-0.9520925262034103</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>330.7495644540284</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>445.6802487764048</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>382.1191483534292</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>354.9377876125507</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>409.3005090943078</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>352.7829917273387</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>427.3826803615981</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>631.48</v>
+      </c>
+      <c r="I223" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J223" t="n">
+        <v>22.962908</v>
+      </c>
+      <c r="K223" t="n">
+        <v>55</v>
+      </c>
+      <c r="L223" t="n">
+        <v>62</v>
+      </c>
+      <c r="M223" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N223" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O223" t="n">
+        <v>23.2308256868983</v>
+      </c>
+      <c r="P223" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>2.919283999802006</v>
+      </c>
+      <c r="R223" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S223" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T223" t="n">
+        <v>-0.09177513627193108</v>
+      </c>
+      <c r="U223" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="V223" t="n">
+        <v>542.8699951171875</v>
+      </c>
+      <c r="W223" t="n">
+        <v>806.0930040147568</v>
+      </c>
+      <c r="X223" t="n">
+        <v>638.8477063897031</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>558.567396395148</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>719.1280163842582</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>564.1629760742187</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>785.8947675955858</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>25.2173057963927</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>26.07151906812074</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>3.15438216046665</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>28.73427065040975</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>-0.7146875938644003</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>0.3739837398373984</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>542.8699951171875</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>864.3475918629769</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>693.4759094007992</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>606.7303999879663</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>780.221418813632</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>583.2380249023437</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>790.1924428862681</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>384.36</v>
+      </c>
+      <c r="I224" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J224" t="n">
+        <v>22.892195</v>
+      </c>
+      <c r="K224" t="n">
+        <v>67</v>
+      </c>
+      <c r="L224" t="n">
+        <v>62</v>
+      </c>
+      <c r="M224" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N224" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O224" t="n">
+        <v>24.42399970293323</v>
+      </c>
+      <c r="P224" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>1.504777164623128</v>
+      </c>
+      <c r="R224" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S224" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T224" t="n">
+        <v>-1.01796115660545</v>
+      </c>
+      <c r="U224" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V224" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W224" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X224" t="n">
+        <v>410.0789550122489</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>384.8137464182266</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>435.3441636062713</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>374.2141233952839</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>445.2374133636685</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>25.32451101344316</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>24.84642937069847</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>2.763836906020571</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>22.87476167224703</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>27.35166212313831</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>-0.8800504863889603</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>0.1219512195121951</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>573.8931703092702</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>425.1985399157107</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>378.7937182636253</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>471.6033615677961</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>384.0672484770275</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>459.2344070474921</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>75.47</v>
+      </c>
+      <c r="I225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J225" t="n">
+        <v>24.345163</v>
+      </c>
+      <c r="K225" t="n">
+        <v>67</v>
+      </c>
+      <c r="L225" t="n">
+        <v>5</v>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
+      <c r="W225" t="inlineStr"/>
+      <c r="X225" t="inlineStr"/>
+      <c r="Y225" t="inlineStr"/>
+      <c r="Z225" t="inlineStr"/>
+      <c r="AA225" t="inlineStr"/>
+      <c r="AB225" t="inlineStr"/>
+      <c r="AC225" t="n">
+        <v>66</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>31.89578623712688</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>36.09881344520055</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>11.08574236888346</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>3.753759468607635</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>39.24110623687622</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>-0.6811111954324959</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>98.87693733509334</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>64.5111359915546</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>133.2427386786321</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>11.63665435268367</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>121.6474293343163</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-07-09 16:42:08</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>202.78</v>
+      </c>
+      <c r="I226" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J226" t="n">
+        <v>31.053598</v>
+      </c>
+      <c r="K226" t="n">
+        <v>65</v>
+      </c>
+      <c r="L226" t="n">
+        <v>62</v>
+      </c>
+      <c r="M226" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N226" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O226" t="n">
+        <v>36.55899802632489</v>
+      </c>
+      <c r="P226" t="n">
+        <v>33.86906599012669</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>5.707888811030037</v>
+      </c>
+      <c r="R226" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S226" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T226" t="n">
+        <v>-0.964524749621287</v>
+      </c>
+      <c r="U226" t="n">
+        <v>0.1774193548387097</v>
+      </c>
+      <c r="V226" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W226" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X226" t="n">
+        <v>238.7302571119016</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>201.4577431758754</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>276.0027710479277</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>197.7220016479492</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>93</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>36.57529860735811</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>36.34694002112563</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>4.697268534130385</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>30.6517605978716</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>43.43591806839923</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>-1.175513081110307</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>0.1182795698924731</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>238.8366999060484</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>208.163536378177</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>269.5098634339199</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>200.1559967041015</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>283.636544986647</v>
       </c>
     </row>
   </sheetData>
@@ -32992,12 +34319,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -33026,13 +34353,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>358.71</v>
+        <v>356.24</v>
       </c>
       <c r="I2" t="n">
-        <v>13.13</v>
+        <v>13.09</v>
       </c>
       <c r="J2" t="n">
-        <v>27.319878</v>
+        <v>27.214666</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -33047,13 +34374,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.93746687069029</v>
+        <v>28.90370445121074</v>
       </c>
       <c r="P2" t="n">
-        <v>29.21870597964289</v>
+        <v>29.16988832978413</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.663541126320117</v>
+        <v>1.677935137236142</v>
       </c>
       <c r="R2" t="n">
         <v>26.95049620511239</v>
@@ -33062,31 +34389,31 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9723768442494257</v>
+        <v>-1.006617248621952</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="V2" t="n">
-        <v>335.2005897830408</v>
+        <v>334.1794150997717</v>
       </c>
       <c r="W2" t="n">
-        <v>423.3179885059678</v>
+        <v>422.0283678250661</v>
       </c>
       <c r="X2" t="n">
-        <v>379.9489400121635</v>
+        <v>378.3494912663486</v>
       </c>
       <c r="Y2" t="n">
-        <v>358.1066450235804</v>
+        <v>356.3853203199275</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.7912350007467</v>
+        <v>400.3136622127697</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.8600151731258</v>
+        <v>352.7819953249212</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.9292998900577</v>
+        <v>408.6804672932867</v>
       </c>
       <c r="AC2" t="n">
         <v>123</v>
@@ -33098,13 +34425,13 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.23492388656339</v>
+        <v>29.19168436619016</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.80943503013702</v>
+        <v>28.80018377171745</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.08945458718323</v>
+        <v>2.076498146743965</v>
       </c>
       <c r="AI2" t="n">
         <v>26.95057232447202</v>
@@ -33113,42 +34440,42 @@
         <v>32.64955541341467</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.9165290781193984</v>
+        <v>-0.9520925262034103</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.7602583102668</v>
+        <v>330.7495644540284</v>
       </c>
       <c r="AN2" t="n">
-        <v>447.04214411262</v>
+        <v>445.6802487764048</v>
       </c>
       <c r="AO2" t="n">
-        <v>383.8545506305774</v>
+        <v>382.1191483534292</v>
       </c>
       <c r="AP2" t="n">
-        <v>356.4200119008616</v>
+        <v>354.9377876125507</v>
       </c>
       <c r="AQ2" t="n">
-        <v>411.2890893602932</v>
+        <v>409.3005090943078</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.8610146203176</v>
+        <v>352.7829917273387</v>
       </c>
       <c r="AS2" t="n">
-        <v>428.6886625781347</v>
+        <v>427.3826803615981</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -33177,13 +34504,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>383.34</v>
+        <v>384.36</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>22.817858</v>
+        <v>22.892195</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -33198,13 +34525,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.43130433296766</v>
+        <v>24.42399970293323</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.498237226573082</v>
+        <v>1.504777164623128</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -33213,31 +34540,31 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.076896438261715</v>
+        <v>-1.01796115660545</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="V3" t="n">
-        <v>352.8299865722656</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="W3" t="n">
-        <v>460.5199890136719</v>
+        <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>410.4459127938567</v>
+        <v>410.0789550122489</v>
       </c>
       <c r="Y3" t="n">
-        <v>385.275527387429</v>
+        <v>384.8137464182266</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.6162982002845</v>
+        <v>435.3441636062713</v>
       </c>
       <c r="AA3" t="n">
-        <v>374.4370025634765</v>
+        <v>374.2141233952839</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.5025934788345</v>
+        <v>445.2374133636685</v>
       </c>
       <c r="AC3" t="n">
         <v>123</v>
@@ -33249,57 +34576,57 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.41564615826555</v>
+        <v>25.32451101344316</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.91488138834635</v>
+        <v>24.84642937069847</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.865468283736575</v>
+        <v>2.763836906020571</v>
       </c>
       <c r="AI3" t="n">
-        <v>22.87653350489267</v>
+        <v>22.87476167224703</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29.57894141610352</v>
+        <v>27.35166212313831</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.9065841604353843</v>
+        <v>-0.8800504863889603</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0975609756097561</v>
+        <v>0.1219512195121951</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.8299865722656</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="AN3" t="n">
-        <v>574.2349768431054</v>
+        <v>573.8931703092702</v>
       </c>
       <c r="AO3" t="n">
-        <v>426.9828554588612</v>
+        <v>425.1985399157107</v>
       </c>
       <c r="AP3" t="n">
-        <v>378.8429882920867</v>
+        <v>378.7937182636253</v>
       </c>
       <c r="AQ3" t="n">
-        <v>475.1227226256357</v>
+        <v>471.6033615677961</v>
       </c>
       <c r="AR3" t="n">
-        <v>384.3257628821969</v>
+        <v>384.0672484770275</v>
       </c>
       <c r="AS3" t="n">
-        <v>496.9262157905391</v>
+        <v>459.2344070474921</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -33328,13 +34655,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>603.12</v>
+        <v>631.48</v>
       </c>
       <c r="I4" t="n">
-        <v>27.52</v>
+        <v>27.5</v>
       </c>
       <c r="J4" t="n">
-        <v>21.915697</v>
+        <v>22.962908</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -33349,13 +34676,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.29193013545308</v>
+        <v>23.2308256868983</v>
       </c>
       <c r="P4" t="n">
         <v>22.19399968927557</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.953037955418361</v>
+        <v>2.919283999802006</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
@@ -33364,31 +34691,31 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4660397720008675</v>
+        <v>-0.09177513627193108</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="V4" t="n">
-        <v>543.2648096590909</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="W4" t="n">
-        <v>806.6792534722222</v>
+        <v>806.0930040147568</v>
       </c>
       <c r="X4" t="n">
-        <v>640.9939173276688</v>
+        <v>638.8477063897031</v>
       </c>
       <c r="Y4" t="n">
-        <v>559.7263127945556</v>
+        <v>558.567396395148</v>
       </c>
       <c r="Z4" t="n">
-        <v>722.2615218607821</v>
+        <v>719.1280163842582</v>
       </c>
       <c r="AA4" t="n">
-        <v>564.5732764204546</v>
+        <v>564.1629760742187</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.4663274265644</v>
+        <v>785.8947675955858</v>
       </c>
       <c r="AC4" t="n">
         <v>123</v>
@@ -33400,57 +34727,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.26575414132806</v>
+        <v>25.2173057963927</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.12643771701389</v>
+        <v>26.07151906812074</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.165217753481453</v>
+        <v>3.15438216046665</v>
       </c>
       <c r="AI4" t="n">
         <v>21.20865545099432</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28.79957437007769</v>
+        <v>28.73427065040975</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1.058397052665114</v>
+        <v>-0.7146875938644003</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1869918699186992</v>
+        <v>0.3739837398373984</v>
       </c>
       <c r="AM4" t="n">
-        <v>543.2648096590909</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.9762082934226</v>
+        <v>864.3475918629769</v>
       </c>
       <c r="AO4" t="n">
-        <v>695.3135539693483</v>
+        <v>693.4759094007992</v>
       </c>
       <c r="AP4" t="n">
-        <v>608.2067613935387</v>
+        <v>606.7303999879663</v>
       </c>
       <c r="AQ4" t="n">
-        <v>782.4203465451579</v>
+        <v>780.221418813632</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.6621980113637</v>
+        <v>583.2380249023437</v>
       </c>
       <c r="AS4" t="n">
-        <v>792.564286664538</v>
+        <v>790.1924428862681</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -33479,13 +34806,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>243.62</v>
+        <v>247.04</v>
       </c>
       <c r="I5" t="n">
-        <v>7.77</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
-        <v>31.353926</v>
+        <v>32.08312</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -33500,13 +34827,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.52021980164974</v>
+        <v>31.47123706816419</v>
       </c>
       <c r="P5" t="n">
-        <v>31.71949797269831</v>
+        <v>31.70275163422361</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.566672487168975</v>
+        <v>2.574942171152248</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -33515,31 +34842,31 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06478964592524131</v>
+        <v>0.2376297761910512</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="V5" t="n">
-        <v>210.9889542246549</v>
+        <v>209.0881528352436</v>
       </c>
       <c r="W5" t="n">
-        <v>286.0812028062892</v>
+        <v>283.5038946728993</v>
       </c>
       <c r="X5" t="n">
-        <v>244.9121078588184</v>
+        <v>242.3285254248643</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.9690626335155</v>
+        <v>222.501470706992</v>
       </c>
       <c r="Z5" t="n">
-        <v>264.8551530841214</v>
+        <v>262.1555801427367</v>
       </c>
       <c r="AA5" t="n">
-        <v>221.2349494203997</v>
+        <v>219.2418417679636</v>
       </c>
       <c r="AB5" t="n">
-        <v>271.4569227019115</v>
+        <v>269.0113648397321</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -33551,57 +34878,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.04626436780183</v>
+        <v>31.00243965053021</v>
       </c>
       <c r="AG5" t="n">
-        <v>30.013946575766</v>
+        <v>29.90669907565323</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.44684834231791</v>
+        <v>2.424697965464038</v>
       </c>
       <c r="AI5" t="n">
         <v>28.4770334052127</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.65216175116588</v>
+        <v>34.61395611388885</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1257379245281394</v>
+        <v>0.4456968929171228</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.6422764227642277</v>
       </c>
       <c r="AM5" t="n">
-        <v>210.9889542246549</v>
+        <v>209.0881528352436</v>
       </c>
       <c r="AN5" t="n">
-        <v>286.0812028062892</v>
+        <v>283.5038946728993</v>
       </c>
       <c r="AO5" t="n">
-        <v>241.2294741378202</v>
+        <v>238.7187853090826</v>
       </c>
       <c r="AP5" t="n">
-        <v>222.21746251801</v>
+        <v>220.0486109750095</v>
       </c>
       <c r="AQ5" t="n">
-        <v>260.2414857576304</v>
+        <v>257.3889596431557</v>
       </c>
       <c r="AR5" t="n">
-        <v>221.2665495585026</v>
+        <v>219.2731572201378</v>
       </c>
       <c r="AS5" t="n">
-        <v>269.2472968065588</v>
+        <v>266.5274620769441</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -33630,13 +34957,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>313.39</v>
+        <v>316.22</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>8.27</v>
       </c>
       <c r="J6" t="n">
-        <v>37.940678</v>
+        <v>38.237</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -33648,49 +34975,49 @@
         <v>32.7632894395273</v>
       </c>
       <c r="N6" t="n">
-        <v>38.15980777324834</v>
+        <v>38.28329312599312</v>
       </c>
       <c r="O6" t="n">
-        <v>35.51118035905431</v>
+        <v>35.59682353067735</v>
       </c>
       <c r="P6" t="n">
-        <v>35.57021762210579</v>
+        <v>35.63438212323131</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.512379845901221</v>
+        <v>1.516653292199783</v>
       </c>
       <c r="R6" t="n">
-        <v>33.53231427376279</v>
+        <v>33.69569763956191</v>
       </c>
       <c r="S6" t="n">
-        <v>37.63087238006961</v>
+        <v>37.67457754213643</v>
       </c>
       <c r="T6" t="n">
-        <v>1.606407046172956</v>
+        <v>1.740791044928463</v>
       </c>
       <c r="U6" t="n">
-        <v>0.967741935483871</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="V6" t="n">
-        <v>270.6247707704955</v>
+        <v>270.9524036648908</v>
       </c>
       <c r="W6" t="n">
-        <v>315.2000122070312</v>
+        <v>316.6028341519631</v>
       </c>
       <c r="X6" t="n">
-        <v>293.3223497657886</v>
+        <v>294.3857305987016</v>
       </c>
       <c r="Y6" t="n">
-        <v>280.8300922386445</v>
+        <v>281.8430078722095</v>
       </c>
       <c r="Z6" t="n">
-        <v>305.8146072929327</v>
+        <v>306.9284533251939</v>
       </c>
       <c r="AA6" t="n">
-        <v>276.9769159012807</v>
+        <v>278.663419479177</v>
       </c>
       <c r="AB6" t="n">
-        <v>310.831005859375</v>
+        <v>311.5687562734682</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -33699,60 +35026,60 @@
         <v>31.21898795984968</v>
       </c>
       <c r="AE6" t="n">
-        <v>38.15980777324834</v>
+        <v>38.28329312599312</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.41625615673373</v>
+        <v>34.44483499629292</v>
       </c>
       <c r="AG6" t="n">
         <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.737530231088972</v>
+        <v>1.771933052448062</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.18329256441056</v>
+        <v>37.3041148335824</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.028408933672128</v>
+        <v>2.140128826237489</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.983739837398374</v>
+        <v>0.9918699186991869</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.8688405483584</v>
+        <v>258.1810304279569</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.2000122070312</v>
+        <v>316.6028341519631</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.2782758546206</v>
+        <v>284.8587854193424</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.9262761458257</v>
+        <v>270.2048990755969</v>
       </c>
       <c r="AQ6" t="n">
-        <v>298.6302755634155</v>
+        <v>299.5126717630879</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.4471175413494</v>
+        <v>265.768482090431</v>
       </c>
       <c r="AS6" t="n">
-        <v>307.1339965820313</v>
+        <v>308.5050296737264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -33781,13 +35108,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>204.12</v>
+        <v>202.78</v>
       </c>
       <c r="I7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.211008</v>
+        <v>31.053598</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -33802,13 +35129,13 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.66349891698048</v>
+        <v>36.55899802632489</v>
       </c>
       <c r="P7" t="n">
-        <v>34.17228243069845</v>
+        <v>33.86906599012669</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.664588291130952</v>
+        <v>5.707888811030037</v>
       </c>
       <c r="R7" t="n">
         <v>30.27902016048226</v>
@@ -33817,34 +35144,34 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9625573186876525</v>
+        <v>-0.964524749621287</v>
       </c>
       <c r="U7" t="n">
         <v>0.1774193548387097</v>
       </c>
       <c r="V7" t="n">
-        <v>192.8248379811028</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="W7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>239.7792829170523</v>
+        <v>238.7302571119016</v>
       </c>
       <c r="Y7" t="n">
-        <v>202.7328754930559</v>
+        <v>201.4577431758754</v>
       </c>
       <c r="Z7" t="n">
-        <v>276.8256903410488</v>
+        <v>276.0027710479277</v>
       </c>
       <c r="AA7" t="n">
-        <v>198.024791849554</v>
+        <v>197.7220016479492</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.5075091365892</v>
+        <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -33853,57 +35180,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.63531708582996</v>
+        <v>36.57529860735811</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.39387792470504</v>
+        <v>36.34694002112563</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.687014959029563</v>
+        <v>4.697268534130385</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.64670697105606</v>
+        <v>30.6517605978716</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.46999966368383</v>
+        <v>43.43591806839923</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.157305690987821</v>
+        <v>-1.175513081110307</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1195652173913044</v>
+        <v>0.1182795698924731</v>
       </c>
       <c r="AM7" t="n">
-        <v>192.8248379811028</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>239.5949737413279</v>
+        <v>238.8366999060484</v>
       </c>
       <c r="AP7" t="n">
-        <v>208.9418959092746</v>
+        <v>208.163536378177</v>
       </c>
       <c r="AQ7" t="n">
-        <v>270.2480515733812</v>
+        <v>269.5098634339199</v>
       </c>
       <c r="AR7" t="n">
-        <v>200.4294635907066</v>
+        <v>200.1559967041015</v>
       </c>
       <c r="AS7" t="n">
-        <v>284.2937978004923</v>
+        <v>283.636544986647</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -33932,13 +35259,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>517.405</v>
+        <v>546.72</v>
       </c>
       <c r="I8" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>173.04517</v>
+        <v>182.23999</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -33947,52 +35274,52 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>89.29811297722583</v>
+        <v>92.4679219947671</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>147.14948632841</v>
+        <v>148.6003888665921</v>
       </c>
       <c r="P8" t="n">
-        <v>149.8327886862833</v>
+        <v>151.667215316022</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.87359235682414</v>
+        <v>26.1166871992592</v>
       </c>
       <c r="R8" t="n">
-        <v>105.0086831146816</v>
+        <v>105.2830234743514</v>
       </c>
       <c r="S8" t="n">
-        <v>176.8124559746414</v>
+        <v>177.2921322681865</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9636107941115741</v>
+        <v>1.288050083716669</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="V8" t="n">
-        <v>267.0013578019052</v>
+        <v>277.4037659843013</v>
       </c>
       <c r="W8" t="n">
-        <v>569.4822359679176</v>
+        <v>571.3868588306865</v>
       </c>
       <c r="X8" t="n">
-        <v>439.9769641219459</v>
+        <v>445.8011665997764</v>
       </c>
       <c r="Y8" t="n">
-        <v>359.6249229750417</v>
+        <v>367.4511050019988</v>
       </c>
       <c r="Z8" t="n">
-        <v>520.32900526885</v>
+        <v>524.151228197554</v>
       </c>
       <c r="AA8" t="n">
-        <v>313.975962512898</v>
+        <v>315.8490704230543</v>
       </c>
       <c r="AB8" t="n">
-        <v>528.6692433641779</v>
+        <v>531.8763968045594</v>
       </c>
       <c r="AC8" t="n">
         <v>123</v>
@@ -34004,57 +35331,57 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>118.0056332643967</v>
+        <v>118.6492944628045</v>
       </c>
       <c r="AG8" t="n">
-        <v>115.2188628574587</v>
+        <v>116.6157614421375</v>
       </c>
       <c r="AH8" t="n">
-        <v>37.47598362909357</v>
+        <v>37.8437260581015</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>170.4354027920082</v>
+        <v>170.8858942751025</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.468661564172386</v>
+        <v>1.680349747790815</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.926829268292683</v>
+        <v>0.9918699186991869</v>
       </c>
       <c r="AM8" t="n">
-        <v>215.4492418397148</v>
+        <v>216.1698078659346</v>
       </c>
       <c r="AN8" t="n">
-        <v>569.4822359679176</v>
+        <v>571.3868588306865</v>
       </c>
       <c r="AO8" t="n">
-        <v>352.8368434605462</v>
+        <v>355.9478833884134</v>
       </c>
       <c r="AP8" t="n">
-        <v>240.7836524095564</v>
+        <v>242.4167052141089</v>
       </c>
       <c r="AQ8" t="n">
-        <v>464.890034511536</v>
+        <v>469.4790615627179</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.8025376114755</v>
+        <v>226.5577300449587</v>
       </c>
       <c r="AS8" t="n">
-        <v>509.6018543481046</v>
+        <v>512.6576828253073</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -34083,13 +35410,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>388.69</v>
+        <v>401.11</v>
       </c>
       <c r="I9" t="n">
-        <v>6.01</v>
+        <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>64.673874</v>
+        <v>66.62956</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -34104,13 +35431,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.39403907990172</v>
+        <v>75.35463897657367</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.273698435305844</v>
+        <v>9.305652323737203</v>
       </c>
       <c r="R9" t="n">
         <v>62.25973272085587</v>
@@ -34119,31 +35446,31 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.155975165106625</v>
+        <v>-0.937610677149136</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="V9" t="n">
-        <v>360.4500122070312</v>
+        <v>361.0497626433158</v>
       </c>
       <c r="W9" t="n">
-        <v>564.1785076059562</v>
+        <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>453.1181748702093</v>
+        <v>453.6349266389735</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.3832472740212</v>
+        <v>397.6148996500755</v>
       </c>
       <c r="Z9" t="n">
-        <v>508.8531024663974</v>
+        <v>509.6549536278714</v>
       </c>
       <c r="AA9" t="n">
-        <v>374.1809936523437</v>
+        <v>374.8035909795523</v>
       </c>
       <c r="AB9" t="n">
-        <v>501.7975012825711</v>
+        <v>502.6324388886986</v>
       </c>
       <c r="AC9" t="n">
         <v>123</v>
@@ -34155,13 +35482,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.30762729505619</v>
+        <v>71.26225880076412</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.66666615484147</v>
+        <v>69.45492406561191</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.285245733190155</v>
+        <v>8.294925323900546</v>
       </c>
       <c r="AI9" t="n">
         <v>61.7377704233179</v>
@@ -34170,42 +35497,42 @@
         <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.8006706751595564</v>
+        <v>-0.558497951442156</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.2520325203252032</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.7415442513212</v>
+        <v>344.3134935761985</v>
       </c>
       <c r="AN9" t="n">
-        <v>564.1785076059562</v>
+        <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>428.5588400432877</v>
+        <v>428.9987979805999</v>
       </c>
       <c r="AP9" t="n">
-        <v>378.7645131868149</v>
+        <v>379.0633475307187</v>
       </c>
       <c r="AQ9" t="n">
-        <v>478.3531668997605</v>
+        <v>478.9342484304812</v>
       </c>
       <c r="AR9" t="n">
-        <v>371.0440002441406</v>
+        <v>371.6613779483737</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.0014039751615</v>
+        <v>495.8250335990802</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-08 16:34:09</t>
+          <t>2026-07-09 16:42:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -34234,19 +35561,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>75.59</v>
+        <v>75.47</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>24.383871</v>
+        <v>24.345163</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -34265,7 +35592,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -34274,25 +35601,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>31.47550348831933</v>
+        <v>31.89578623712688</v>
       </c>
       <c r="AG10" t="n">
-        <v>35.93675816954359</v>
+        <v>36.09881344520055</v>
       </c>
       <c r="AH10" t="n">
-        <v>11.52676783905264</v>
+        <v>11.08574236888346</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.736006721617684</v>
+        <v>3.753759468607635</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.23241053645317</v>
+        <v>39.24110623687622</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.6152316579408244</v>
+        <v>-0.6811111954324959</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1343283582089552</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -34301,19 +35628,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>97.57406081378991</v>
+        <v>98.87693733509334</v>
       </c>
       <c r="AP10" t="n">
-        <v>61.84108051272673</v>
+        <v>64.5111359915546</v>
       </c>
       <c r="AQ10" t="n">
-        <v>133.3070411148531</v>
+        <v>133.2427386786321</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.58162083701482</v>
+        <v>11.63665435268367</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.6204726630048</v>
+        <v>121.6474293343163</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS226"/>
+  <dimension ref="A1:AS235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32824,7 +32824,7 @@
         <v>1.740791044928463</v>
       </c>
       <c r="U218" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V218" t="n">
         <v>270.9524036648908</v>
@@ -32893,7 +32893,7 @@
         <v>299.5126717630879</v>
       </c>
       <c r="AR218" t="n">
-        <v>265.768482090431</v>
+        <v>265.7684820904309</v>
       </c>
       <c r="AS218" t="n">
         <v>308.5050296737264</v>
@@ -32975,7 +32975,7 @@
         <v>1.288050083716669</v>
       </c>
       <c r="U219" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V219" t="n">
         <v>277.4037659843013</v>
@@ -33011,7 +33011,7 @@
         <v>118.6492944628045</v>
       </c>
       <c r="AG219" t="n">
-        <v>116.6157614421375</v>
+        <v>116.6157614421374</v>
       </c>
       <c r="AH219" t="n">
         <v>37.8437260581015</v>
@@ -33044,7 +33044,7 @@
         <v>469.4790615627179</v>
       </c>
       <c r="AR219" t="n">
-        <v>226.5577300449587</v>
+        <v>226.5577300449588</v>
       </c>
       <c r="AS219" t="n">
         <v>512.6576828253073</v>
@@ -33108,7 +33108,7 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O220" t="n">
-        <v>31.47123706816419</v>
+        <v>31.4712370681642</v>
       </c>
       <c r="P220" t="n">
         <v>31.70275163422361</v>
@@ -33256,7 +33256,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N221" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O221" t="n">
         <v>75.35463897657367</v>
@@ -33265,7 +33265,7 @@
         <v>78.71540210865163</v>
       </c>
       <c r="Q221" t="n">
-        <v>9.305652323737203</v>
+        <v>9.305652323737204</v>
       </c>
       <c r="R221" t="n">
         <v>62.25973272085587</v>
@@ -33295,7 +33295,7 @@
         <v>509.6549536278714</v>
       </c>
       <c r="AA221" t="n">
-        <v>374.8035909795523</v>
+        <v>374.8035909795522</v>
       </c>
       <c r="AB221" t="n">
         <v>502.6324388886986</v>
@@ -33307,7 +33307,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE221" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF221" t="n">
         <v>71.26225880076412</v>
@@ -33319,7 +33319,7 @@
         <v>8.294925323900546</v>
       </c>
       <c r="AI221" t="n">
-        <v>61.7377704233179</v>
+        <v>61.73777042331791</v>
       </c>
       <c r="AJ221" t="n">
         <v>82.36296239187379</v>
@@ -33328,7 +33328,7 @@
         <v>-0.558497951442156</v>
       </c>
       <c r="AL221" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3414634146341463</v>
       </c>
       <c r="AM221" t="n">
         <v>344.3134935761985</v>
@@ -33419,7 +33419,7 @@
         <v>1.677935137236142</v>
       </c>
       <c r="R222" t="n">
-        <v>26.95049620511239</v>
+        <v>26.9504962051124</v>
       </c>
       <c r="S222" t="n">
         <v>31.22081491927324</v>
@@ -33440,7 +33440,7 @@
         <v>378.3494912663486</v>
       </c>
       <c r="Y222" t="n">
-        <v>356.3853203199275</v>
+        <v>356.3853203199276</v>
       </c>
       <c r="Z222" t="n">
         <v>400.3136622127697</v>
@@ -33476,7 +33476,7 @@
         <v>32.64955541341467</v>
       </c>
       <c r="AK222" t="n">
-        <v>-0.9520925262034103</v>
+        <v>-0.9520925262034104</v>
       </c>
       <c r="AL222" t="n">
         <v>0.1463414634146341</v>
@@ -33488,7 +33488,7 @@
         <v>445.6802487764048</v>
       </c>
       <c r="AO222" t="n">
-        <v>382.1191483534292</v>
+        <v>382.1191483534293</v>
       </c>
       <c r="AP222" t="n">
         <v>354.9377876125507</v>
@@ -33576,7 +33576,7 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T223" t="n">
-        <v>-0.09177513627193108</v>
+        <v>-0.091775136271931</v>
       </c>
       <c r="U223" t="n">
         <v>0.7096774193548387</v>
@@ -33630,7 +33630,7 @@
         <v>-0.7146875938644003</v>
       </c>
       <c r="AL223" t="n">
-        <v>0.3739837398373984</v>
+        <v>0.3739837398373983</v>
       </c>
       <c r="AM223" t="n">
         <v>542.8699951171875</v>
@@ -33727,7 +33727,7 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T224" t="n">
-        <v>-1.01796115660545</v>
+        <v>-1.017961156605451</v>
       </c>
       <c r="U224" t="n">
         <v>0.1935483870967742</v>
@@ -33766,7 +33766,7 @@
         <v>25.32451101344316</v>
       </c>
       <c r="AG224" t="n">
-        <v>24.84642937069847</v>
+        <v>24.84642937069848</v>
       </c>
       <c r="AH224" t="n">
         <v>2.763836906020571</v>
@@ -33876,7 +33876,7 @@
         <v>66</v>
       </c>
       <c r="AD225" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE225" t="n">
         <v>42.60474344487245</v>
@@ -34069,10 +34069,1337 @@
         <v>269.5098634339199</v>
       </c>
       <c r="AR226" t="n">
-        <v>200.1559967041015</v>
+        <v>200.1559967041016</v>
       </c>
       <c r="AS226" t="n">
         <v>283.636544986647</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>315.32</v>
+      </c>
+      <c r="I227" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J227" t="n">
+        <v>38.220608</v>
+      </c>
+      <c r="K227" t="n">
+        <v>67</v>
+      </c>
+      <c r="L227" t="n">
+        <v>62</v>
+      </c>
+      <c r="M227" t="n">
+        <v>32.7632894395273</v>
+      </c>
+      <c r="N227" t="n">
+        <v>38.28329312599312</v>
+      </c>
+      <c r="O227" t="n">
+        <v>35.68072968773762</v>
+      </c>
+      <c r="P227" t="n">
+        <v>35.66464846705698</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>1.512963904168078</v>
+      </c>
+      <c r="R227" t="n">
+        <v>33.74025214472903</v>
+      </c>
+      <c r="S227" t="n">
+        <v>37.76961245779263</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.678743494980447</v>
+      </c>
+      <c r="U227" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V227" t="n">
+        <v>270.2971378761002</v>
+      </c>
+      <c r="W227" t="n">
+        <v>315.8371682894432</v>
+      </c>
+      <c r="X227" t="n">
+        <v>294.3660199238353</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>281.8840677144487</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>306.847972133222</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>278.3570801940145</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>311.5993027767892</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>38.28329312599312</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>34.47491160944495</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>34.36563375175731</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.796215765368129</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>32.14202455931072</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>37.35351082199134</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>2.085326530795356</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>0.9919354838709677</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>315.8371682894432</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>284.4180207779208</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>269.5992407136338</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>299.2368008422079</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>265.1717026143135</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>308.1664642814286</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>557.89</v>
+      </c>
+      <c r="I228" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J228" t="n">
+        <v>185.34552</v>
+      </c>
+      <c r="K228" t="n">
+        <v>63</v>
+      </c>
+      <c r="L228" t="n">
+        <v>62</v>
+      </c>
+      <c r="M228" t="n">
+        <v>93.14339691737914</v>
+      </c>
+      <c r="N228" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O228" t="n">
+        <v>150.0592088166947</v>
+      </c>
+      <c r="P228" t="n">
+        <v>153.0967237128586</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>25.44735448575645</v>
+      </c>
+      <c r="R228" t="n">
+        <v>108.0705623986586</v>
+      </c>
+      <c r="S228" t="n">
+        <v>177.8216452676742</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.386639668302494</v>
+      </c>
+      <c r="U228" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V228" t="n">
+        <v>280.3616247213112</v>
+      </c>
+      <c r="W228" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="X228" t="n">
+        <v>451.678218538251</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>375.0816815361241</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>528.2747555403779</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>325.2923928199624</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>535.2431522556993</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>119.1675643373071</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>117.94088579751</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>38.12887330765528</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>75.52037537772701</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>171.0059034003586</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.735638898341277</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>0.9919354838709677</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>216.8903738921543</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>358.6943686552942</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>243.9264599992518</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>473.4622773113366</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>227.3163298869583</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>514.7277692350794</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>245.34</v>
+      </c>
+      <c r="I229" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="J229" t="n">
+        <v>31.413572</v>
+      </c>
+      <c r="K229" t="n">
+        <v>67</v>
+      </c>
+      <c r="L229" t="n">
+        <v>62</v>
+      </c>
+      <c r="M229" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N229" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O229" t="n">
+        <v>31.40833427636435</v>
+      </c>
+      <c r="P229" t="n">
+        <v>31.69078918164997</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>2.578488073820786</v>
+      </c>
+      <c r="R229" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S229" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0.002031315827605777</v>
+      </c>
+      <c r="U229" t="n">
+        <v>0.4677419354838709</v>
+      </c>
+      <c r="V229" t="n">
+        <v>212.0751264471757</v>
+      </c>
+      <c r="W229" t="n">
+        <v>287.5539503110835</v>
+      </c>
+      <c r="X229" t="n">
+        <v>245.2990906984056</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>225.1610988418653</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>265.437082554946</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>222.3738680789345</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>272.8543843374425</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>30.98908843975256</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>29.89965371014563</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>2.419393678579506</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>28.48110034705349</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>34.60712672457826</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>0.1754503882545747</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>0.5725806451612904</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>212.0751264471757</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>287.5539503110835</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>242.0247807144675</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>223.1293160847615</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>260.9202453441735</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>222.4373937104878</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>270.2816597189562</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>399.97</v>
+      </c>
+      <c r="I230" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="J230" t="n">
+        <v>66.4402</v>
+      </c>
+      <c r="K230" t="n">
+        <v>34</v>
+      </c>
+      <c r="L230" t="n">
+        <v>62</v>
+      </c>
+      <c r="M230" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N230" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O230" t="n">
+        <v>75.25986237576616</v>
+      </c>
+      <c r="P230" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>9.365689884193202</v>
+      </c>
+      <c r="R230" t="n">
+        <v>62.25973272085587</v>
+      </c>
+      <c r="S230" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T230" t="n">
+        <v>-0.9416991684351417</v>
+      </c>
+      <c r="U230" t="n">
+        <v>0.3064516129032258</v>
+      </c>
+      <c r="V230" t="n">
+        <v>361.0497626433158</v>
+      </c>
+      <c r="W230" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="X230" t="n">
+        <v>453.0643715021122</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>396.6829183992692</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>509.4458246049553</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>374.8035909795523</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>502.6324388886986</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>71.2242627536224</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>69.44129991831269</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>8.271965198433307</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>61.75973393952787</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>82.35048706768551</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>-0.5783465765219231</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>344.3134935761985</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>565.1172405637031</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>428.7700617768068</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>378.9728312822383</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>478.5672922713753</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>371.7935983159578</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>495.7499321474667</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>355.03</v>
+      </c>
+      <c r="I231" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J231" t="n">
+        <v>27.080854</v>
+      </c>
+      <c r="K231" t="n">
+        <v>37</v>
+      </c>
+      <c r="L231" t="n">
+        <v>62</v>
+      </c>
+      <c r="M231" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N231" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O231" t="n">
+        <v>28.86942321946665</v>
+      </c>
+      <c r="P231" t="n">
+        <v>29.04576724217558</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>1.693293462912648</v>
+      </c>
+      <c r="R231" t="n">
+        <v>26.95049620511239</v>
+      </c>
+      <c r="S231" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T231" t="n">
+        <v>-1.056266535388447</v>
+      </c>
+      <c r="U231" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="V231" t="n">
+        <v>334.6900024414062</v>
+      </c>
+      <c r="W231" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X231" t="n">
+        <v>378.4781384072077</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>356.2790611084229</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>400.6772157059926</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>353.3210052490235</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>29.17466154240294</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>28.78122109158187</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>2.076709222866049</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>26.95064844383164</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>32.6446195792587</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>-1.008233371985173</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>0.1129032258064516</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>382.4798128209026</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>355.2541549091287</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>409.7054707326765</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>353.3230010986328</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>427.9709626840815</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>669.21</v>
+      </c>
+      <c r="I232" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="J232" t="n">
+        <v>24.361486</v>
+      </c>
+      <c r="K232" t="n">
+        <v>55</v>
+      </c>
+      <c r="L232" t="n">
+        <v>62</v>
+      </c>
+      <c r="M232" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N232" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O232" t="n">
+        <v>23.19084096310542</v>
+      </c>
+      <c r="P232" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>2.886192027862101</v>
+      </c>
+      <c r="R232" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S232" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T232" t="n">
+        <v>0.4056019230853855</v>
+      </c>
+      <c r="U232" t="n">
+        <v>0.7903225806451613</v>
+      </c>
+      <c r="V232" t="n">
+        <v>542.2777733043324</v>
+      </c>
+      <c r="W232" t="n">
+        <v>805.2136298285589</v>
+      </c>
+      <c r="X232" t="n">
+        <v>637.052401256506</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>557.7687062511341</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>716.3360962618779</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>563.547525554865</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>785.0374278491179</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>25.21018970037271</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>25.94976575387798</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>3.142532527805395</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>21.21480091441762</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>28.73295069045338</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>-0.2700699810943277</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>0.4274193548387097</v>
+      </c>
+      <c r="AM232" t="n">
+        <v>542.2777733043324</v>
+      </c>
+      <c r="AN232" t="n">
+        <v>863.4046672173081</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>692.5239110692384</v>
+      </c>
+      <c r="AP232" t="n">
+        <v>606.1985425304241</v>
+      </c>
+      <c r="AQ232" t="n">
+        <v>778.8492796080526</v>
+      </c>
+      <c r="AR232" t="n">
+        <v>582.7705811190518</v>
+      </c>
+      <c r="AS232" t="n">
+        <v>789.2941554667544</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="I233" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J233" t="n">
+        <v>22.92262</v>
+      </c>
+      <c r="K233" t="n">
+        <v>67</v>
+      </c>
+      <c r="L233" t="n">
+        <v>62</v>
+      </c>
+      <c r="M233" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N233" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O233" t="n">
+        <v>24.41962467949467</v>
+      </c>
+      <c r="P233" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>1.508801241215612</v>
+      </c>
+      <c r="R233" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S233" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T233" t="n">
+        <v>-0.9921815005192874</v>
+      </c>
+      <c r="U233" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="V233" t="n">
+        <v>352.8299865722656</v>
+      </c>
+      <c r="W233" t="n">
+        <v>460.5199890136719</v>
+      </c>
+      <c r="X233" t="n">
+        <v>410.2496946155104</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>384.9018337630882</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>435.5975554679327</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>374.4370025634765</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>445.5025934788345</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>25.30514091987446</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>24.84441577935574</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>2.761017074974657</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>22.87523778279622</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>27.32154113072914</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>-0.8629142287706901</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="AM233" t="n">
+        <v>352.8299865722656</v>
+      </c>
+      <c r="AN233" t="n">
+        <v>574.2349768431054</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>425.126367453891</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>378.7412805943167</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>471.5114543134652</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>384.3039947509766</v>
+      </c>
+      <c r="AS233" t="n">
+        <v>459.0018909962495</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="I234" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J234" t="n">
+        <v>23.667744</v>
+      </c>
+      <c r="K234" t="n">
+        <v>67</v>
+      </c>
+      <c r="L234" t="n">
+        <v>4</v>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr"/>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr"/>
+      <c r="W234" t="inlineStr"/>
+      <c r="X234" t="inlineStr"/>
+      <c r="Y234" t="inlineStr"/>
+      <c r="Z234" t="inlineStr"/>
+      <c r="AA234" t="inlineStr"/>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="n">
+        <v>66</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>31.89578623712688</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>36.09881344520055</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>11.08574236888346</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>3.753759468607635</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>39.24110623687622</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>-0.7422184246516635</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>98.87693733509334</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>64.5111359915546</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>133.2427386786321</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>11.63665435268367</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>121.6474293343163</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-07-10 16:26:16</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>210.96</v>
+      </c>
+      <c r="I235" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J235" t="n">
+        <v>32.30628</v>
+      </c>
+      <c r="K235" t="n">
+        <v>65</v>
+      </c>
+      <c r="L235" t="n">
+        <v>62</v>
+      </c>
+      <c r="M235" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N235" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O235" t="n">
+        <v>36.45916512919501</v>
+      </c>
+      <c r="P235" t="n">
+        <v>33.55053584754558</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>5.727551610215001</v>
+      </c>
+      <c r="R235" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S235" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T235" t="n">
+        <v>-0.7250716207931498</v>
+      </c>
+      <c r="U235" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="V235" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W235" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X235" t="n">
+        <v>238.0783482936434</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>200.6774362789394</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>275.4792603083474</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>197.7220016479492</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>94</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>36.52988351304352</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>36.31836871711575</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>4.692649432659968</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>30.65681422468714</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>43.40183647311463</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>-0.9000466737719675</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>0.2446808510638298</v>
+      </c>
+      <c r="AM235" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN235" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>238.5401393401742</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>207.8971385449045</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>269.1831401354438</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>200.188996887207</v>
+      </c>
+      <c r="AS235" t="n">
+        <v>283.4139921694386</v>
       </c>
     </row>
   </sheetData>
@@ -34319,12 +35646,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -34353,13 +35680,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>356.24</v>
+        <v>355.03</v>
       </c>
       <c r="I2" t="n">
-        <v>13.09</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.214666</v>
+        <v>27.080854</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -34374,13 +35701,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.90370445121074</v>
+        <v>28.86942321946665</v>
       </c>
       <c r="P2" t="n">
-        <v>29.16988832978413</v>
+        <v>29.04576724217558</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.677935137236142</v>
+        <v>1.693293462912648</v>
       </c>
       <c r="R2" t="n">
         <v>26.95049620511239</v>
@@ -34389,34 +35716,34 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.006617248621952</v>
+        <v>-1.056266535388447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="V2" t="n">
-        <v>334.1794150997717</v>
+        <v>334.6900024414062</v>
       </c>
       <c r="W2" t="n">
-        <v>422.0283678250661</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>378.3494912663486</v>
+        <v>378.4781384072077</v>
       </c>
       <c r="Y2" t="n">
-        <v>356.3853203199275</v>
+        <v>356.2790611084229</v>
       </c>
       <c r="Z2" t="n">
-        <v>400.3136622127697</v>
+        <v>400.6772157059926</v>
       </c>
       <c r="AA2" t="n">
-        <v>352.7819953249212</v>
+        <v>353.3210052490235</v>
       </c>
       <c r="AB2" t="n">
-        <v>408.6804672932867</v>
+        <v>409.3048835916722</v>
       </c>
       <c r="AC2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -34425,57 +35752,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.19168436619016</v>
+        <v>29.17466154240294</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.80018377171745</v>
+        <v>28.78122109158187</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.076498146743965</v>
+        <v>2.076709222866049</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.95057232447202</v>
+        <v>26.95064844383164</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.64955541341467</v>
+        <v>32.6446195792587</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.9520925262034103</v>
+        <v>-1.008233371985173</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="AM2" t="n">
-        <v>330.7495644540284</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>445.6802487764048</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>382.1191483534292</v>
+        <v>382.4798128209026</v>
       </c>
       <c r="AP2" t="n">
-        <v>354.9377876125507</v>
+        <v>355.2541549091287</v>
       </c>
       <c r="AQ2" t="n">
-        <v>409.3005090943078</v>
+        <v>409.7054707326765</v>
       </c>
       <c r="AR2" t="n">
-        <v>352.7829917273387</v>
+        <v>353.3230010986328</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.3826803615981</v>
+        <v>427.9709626840815</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -34504,13 +35831,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>384.36</v>
+        <v>385.1</v>
       </c>
       <c r="I3" t="n">
-        <v>16.79</v>
+        <v>16.8</v>
       </c>
       <c r="J3" t="n">
-        <v>22.892195</v>
+        <v>22.92262</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -34525,13 +35852,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.42399970293323</v>
+        <v>24.41962467949467</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.504777164623128</v>
+        <v>1.508801241215612</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -34540,34 +35867,34 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.01796115660545</v>
+        <v>-0.9921815005192874</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="V3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.8299865722656</v>
       </c>
       <c r="W3" t="n">
-        <v>460.2458699725923</v>
+        <v>460.5199890136719</v>
       </c>
       <c r="X3" t="n">
-        <v>410.0789550122489</v>
+        <v>410.2496946155104</v>
       </c>
       <c r="Y3" t="n">
-        <v>384.8137464182266</v>
+        <v>384.9018337630882</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.3441636062713</v>
+        <v>435.5975554679327</v>
       </c>
       <c r="AA3" t="n">
-        <v>374.2141233952839</v>
+        <v>374.4370025634765</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.2374133636685</v>
+        <v>445.5025934788345</v>
       </c>
       <c r="AC3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD3" t="n">
         <v>21.00178491501581</v>
@@ -34576,57 +35903,57 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.32451101344316</v>
+        <v>25.30514091987446</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.84642937069847</v>
+        <v>24.84441577935574</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.763836906020571</v>
+        <v>2.761017074974657</v>
       </c>
       <c r="AI3" t="n">
-        <v>22.87476167224703</v>
+        <v>22.87523778279622</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27.35166212313831</v>
+        <v>27.32154113072914</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8800504863889603</v>
+        <v>-0.8629142287706901</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.8299865722656</v>
       </c>
       <c r="AN3" t="n">
-        <v>573.8931703092702</v>
+        <v>574.2349768431054</v>
       </c>
       <c r="AO3" t="n">
-        <v>425.1985399157107</v>
+        <v>425.126367453891</v>
       </c>
       <c r="AP3" t="n">
-        <v>378.7937182636253</v>
+        <v>378.7412805943167</v>
       </c>
       <c r="AQ3" t="n">
-        <v>471.6033615677961</v>
+        <v>471.5114543134652</v>
       </c>
       <c r="AR3" t="n">
-        <v>384.0672484770275</v>
+        <v>384.3039947509766</v>
       </c>
       <c r="AS3" t="n">
-        <v>459.2344070474921</v>
+        <v>459.0018909962495</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -34655,13 +35982,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>631.48</v>
+        <v>669.21</v>
       </c>
       <c r="I4" t="n">
-        <v>27.5</v>
+        <v>27.47</v>
       </c>
       <c r="J4" t="n">
-        <v>22.962908</v>
+        <v>24.361486</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -34676,13 +36003,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.2308256868983</v>
+        <v>23.19084096310542</v>
       </c>
       <c r="P4" t="n">
         <v>22.19399968927557</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.919283999802006</v>
+        <v>2.886192027862101</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
@@ -34691,34 +36018,34 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09177513627193108</v>
+        <v>0.4056019230853855</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7903225806451613</v>
       </c>
       <c r="V4" t="n">
-        <v>542.8699951171875</v>
+        <v>542.2777733043324</v>
       </c>
       <c r="W4" t="n">
-        <v>806.0930040147568</v>
+        <v>805.2136298285589</v>
       </c>
       <c r="X4" t="n">
-        <v>638.8477063897031</v>
+        <v>637.052401256506</v>
       </c>
       <c r="Y4" t="n">
-        <v>558.567396395148</v>
+        <v>557.7687062511341</v>
       </c>
       <c r="Z4" t="n">
-        <v>719.1280163842582</v>
+        <v>716.3360962618779</v>
       </c>
       <c r="AA4" t="n">
-        <v>564.1629760742187</v>
+        <v>563.547525554865</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.8947675955858</v>
+        <v>785.0374278491179</v>
       </c>
       <c r="AC4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD4" t="n">
         <v>19.74072709517046</v>
@@ -34727,57 +36054,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.2173057963927</v>
+        <v>25.21018970037271</v>
       </c>
       <c r="AG4" t="n">
-        <v>26.07151906812074</v>
+        <v>25.94976575387798</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.15438216046665</v>
+        <v>3.142532527805395</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.20865545099432</v>
+        <v>21.21480091441762</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28.73427065040975</v>
+        <v>28.73295069045338</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.7146875938644003</v>
+        <v>-0.2700699810943277</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.3739837398373984</v>
+        <v>0.4274193548387097</v>
       </c>
       <c r="AM4" t="n">
-        <v>542.8699951171875</v>
+        <v>542.2777733043324</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.3475918629769</v>
+        <v>863.4046672173081</v>
       </c>
       <c r="AO4" t="n">
-        <v>693.4759094007992</v>
+        <v>692.5239110692384</v>
       </c>
       <c r="AP4" t="n">
-        <v>606.7303999879663</v>
+        <v>606.1985425304241</v>
       </c>
       <c r="AQ4" t="n">
-        <v>780.221418813632</v>
+        <v>778.8492796080526</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.2380249023437</v>
+        <v>582.7705811190518</v>
       </c>
       <c r="AS4" t="n">
-        <v>790.1924428862681</v>
+        <v>789.2941554667544</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -34806,13 +36133,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>247.04</v>
+        <v>245.34</v>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>7.81</v>
       </c>
       <c r="J5" t="n">
-        <v>32.08312</v>
+        <v>31.413572</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -34827,13 +36154,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.47123706816419</v>
+        <v>31.40833427636435</v>
       </c>
       <c r="P5" t="n">
-        <v>31.70275163422361</v>
+        <v>31.69078918164997</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.574942171152248</v>
+        <v>2.578488073820786</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -34842,34 +36169,34 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2376297761910512</v>
+        <v>0.002031315827605777</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="V5" t="n">
-        <v>209.0881528352436</v>
+        <v>212.0751264471757</v>
       </c>
       <c r="W5" t="n">
-        <v>283.5038946728993</v>
+        <v>287.5539503110835</v>
       </c>
       <c r="X5" t="n">
-        <v>242.3285254248643</v>
+        <v>245.2990906984056</v>
       </c>
       <c r="Y5" t="n">
-        <v>222.501470706992</v>
+        <v>225.1610988418653</v>
       </c>
       <c r="Z5" t="n">
-        <v>262.1555801427367</v>
+        <v>265.437082554946</v>
       </c>
       <c r="AA5" t="n">
-        <v>219.2418417679636</v>
+        <v>222.3738680789345</v>
       </c>
       <c r="AB5" t="n">
-        <v>269.0113648397321</v>
+        <v>272.8543843374425</v>
       </c>
       <c r="AC5" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD5" t="n">
         <v>27.15430556301865</v>
@@ -34878,57 +36205,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>31.00243965053021</v>
+        <v>30.98908843975256</v>
       </c>
       <c r="AG5" t="n">
-        <v>29.90669907565323</v>
+        <v>29.89965371014563</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.424697965464038</v>
+        <v>2.419393678579506</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.4770334052127</v>
+        <v>28.48110034705349</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.61395611388885</v>
+        <v>34.60712672457826</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.4456968929171228</v>
+        <v>0.1754503882545747</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6422764227642277</v>
+        <v>0.5725806451612904</v>
       </c>
       <c r="AM5" t="n">
-        <v>209.0881528352436</v>
+        <v>212.0751264471757</v>
       </c>
       <c r="AN5" t="n">
-        <v>283.5038946728993</v>
+        <v>287.5539503110835</v>
       </c>
       <c r="AO5" t="n">
-        <v>238.7187853090826</v>
+        <v>242.0247807144675</v>
       </c>
       <c r="AP5" t="n">
-        <v>220.0486109750095</v>
+        <v>223.1293160847615</v>
       </c>
       <c r="AQ5" t="n">
-        <v>257.3889596431557</v>
+        <v>260.9202453441735</v>
       </c>
       <c r="AR5" t="n">
-        <v>219.2731572201378</v>
+        <v>222.4373937104878</v>
       </c>
       <c r="AS5" t="n">
-        <v>266.5274620769441</v>
+        <v>270.2816597189562</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -34957,13 +36284,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>316.22</v>
+        <v>315.32</v>
       </c>
       <c r="I6" t="n">
-        <v>8.27</v>
+        <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>38.237</v>
+        <v>38.220608</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -34978,49 +36305,49 @@
         <v>38.28329312599312</v>
       </c>
       <c r="O6" t="n">
-        <v>35.59682353067735</v>
+        <v>35.68072968773762</v>
       </c>
       <c r="P6" t="n">
-        <v>35.63438212323131</v>
+        <v>35.66464846705698</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.516653292199783</v>
+        <v>1.512963904168078</v>
       </c>
       <c r="R6" t="n">
-        <v>33.69569763956191</v>
+        <v>33.74025214472903</v>
       </c>
       <c r="S6" t="n">
-        <v>37.67457754213643</v>
+        <v>37.76961245779263</v>
       </c>
       <c r="T6" t="n">
-        <v>1.740791044928463</v>
+        <v>1.678743494980447</v>
       </c>
       <c r="U6" t="n">
         <v>0.9838709677419355</v>
       </c>
       <c r="V6" t="n">
-        <v>270.9524036648908</v>
+        <v>270.2971378761002</v>
       </c>
       <c r="W6" t="n">
-        <v>316.6028341519631</v>
+        <v>315.8371682894432</v>
       </c>
       <c r="X6" t="n">
-        <v>294.3857305987016</v>
+        <v>294.3660199238353</v>
       </c>
       <c r="Y6" t="n">
-        <v>281.8430078722095</v>
+        <v>281.8840677144487</v>
       </c>
       <c r="Z6" t="n">
-        <v>306.9284533251939</v>
+        <v>306.847972133222</v>
       </c>
       <c r="AA6" t="n">
-        <v>278.663419479177</v>
+        <v>278.3570801940145</v>
       </c>
       <c r="AB6" t="n">
-        <v>311.5687562734682</v>
+        <v>311.5993027767892</v>
       </c>
       <c r="AC6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
@@ -35029,57 +36356,57 @@
         <v>38.28329312599312</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.44483499629292</v>
+        <v>34.47491160944495</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.35593205560495</v>
+        <v>34.36563375175731</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.771933052448062</v>
+        <v>1.796215765368129</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.13645490815368</v>
+        <v>32.14202455931072</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.3041148335824</v>
+        <v>37.35351082199134</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.140128826237489</v>
+        <v>2.085326530795356</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.9918699186991869</v>
+        <v>0.9919354838709677</v>
       </c>
       <c r="AM6" t="n">
-        <v>258.1810304279569</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>316.6028341519631</v>
+        <v>315.8371682894432</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.8587854193424</v>
+        <v>284.4180207779208</v>
       </c>
       <c r="AP6" t="n">
-        <v>270.2048990755969</v>
+        <v>269.5992407136338</v>
       </c>
       <c r="AQ6" t="n">
-        <v>299.5126717630879</v>
+        <v>299.2368008422079</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.768482090431</v>
+        <v>265.1717026143135</v>
       </c>
       <c r="AS6" t="n">
-        <v>308.5050296737264</v>
+        <v>308.1664642814286</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -35108,13 +36435,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>202.78</v>
+        <v>210.96</v>
       </c>
       <c r="I7" t="n">
         <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.053598</v>
+        <v>32.30628</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -35129,13 +36456,13 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.55899802632489</v>
+        <v>36.45916512919501</v>
       </c>
       <c r="P7" t="n">
-        <v>33.86906599012669</v>
+        <v>33.55053584754558</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.707888811030037</v>
+        <v>5.727551610215001</v>
       </c>
       <c r="R7" t="n">
         <v>30.27902016048226</v>
@@ -35144,10 +36471,10 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.964524749621287</v>
+        <v>-0.7250716207931498</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="V7" t="n">
         <v>192.5299987792968</v>
@@ -35156,13 +36483,13 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>238.7302571119016</v>
+        <v>238.0783482936434</v>
       </c>
       <c r="Y7" t="n">
-        <v>201.4577431758754</v>
+        <v>200.6774362789394</v>
       </c>
       <c r="Z7" t="n">
-        <v>276.0027710479277</v>
+        <v>275.4792603083474</v>
       </c>
       <c r="AA7" t="n">
         <v>197.7220016479492</v>
@@ -35171,7 +36498,7 @@
         <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -35180,25 +36507,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.57529860735811</v>
+        <v>36.52988351304352</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.34694002112563</v>
+        <v>36.31836871711575</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.697268534130385</v>
+        <v>4.692649432659968</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.6517605978716</v>
+        <v>30.65681422468714</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.43591806839923</v>
+        <v>43.40183647311463</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.175513081110307</v>
+        <v>-0.9000466737719675</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1182795698924731</v>
+        <v>0.2446808510638298</v>
       </c>
       <c r="AM7" t="n">
         <v>192.5299987792968</v>
@@ -35207,30 +36534,30 @@
         <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>238.8366999060484</v>
+        <v>238.5401393401742</v>
       </c>
       <c r="AP7" t="n">
-        <v>208.163536378177</v>
+        <v>207.8971385449045</v>
       </c>
       <c r="AQ7" t="n">
-        <v>269.5098634339199</v>
+        <v>269.1831401354438</v>
       </c>
       <c r="AR7" t="n">
-        <v>200.1559967041015</v>
+        <v>200.188996887207</v>
       </c>
       <c r="AS7" t="n">
-        <v>283.636544986647</v>
+        <v>283.4139921694386</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -35259,13 +36586,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>546.72</v>
+        <v>557.89</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="J8" t="n">
-        <v>182.23999</v>
+        <v>185.34552</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -35274,55 +36601,55 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>92.4679219947671</v>
+        <v>93.14339691737914</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>148.6003888665921</v>
+        <v>150.0592088166947</v>
       </c>
       <c r="P8" t="n">
-        <v>151.667215316022</v>
+        <v>153.0967237128586</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.1166871992592</v>
+        <v>25.44735448575645</v>
       </c>
       <c r="R8" t="n">
-        <v>105.2830234743514</v>
+        <v>108.0705623986586</v>
       </c>
       <c r="S8" t="n">
-        <v>177.2921322681865</v>
+        <v>177.8216452676742</v>
       </c>
       <c r="T8" t="n">
-        <v>1.288050083716669</v>
+        <v>1.386639668302494</v>
       </c>
       <c r="U8" t="n">
         <v>0.9838709677419355</v>
       </c>
       <c r="V8" t="n">
-        <v>277.4037659843013</v>
+        <v>280.3616247213112</v>
       </c>
       <c r="W8" t="n">
-        <v>571.3868588306865</v>
+        <v>573.2914816934554</v>
       </c>
       <c r="X8" t="n">
-        <v>445.8011665997764</v>
+        <v>451.678218538251</v>
       </c>
       <c r="Y8" t="n">
-        <v>367.4511050019988</v>
+        <v>375.0816815361241</v>
       </c>
       <c r="Z8" t="n">
-        <v>524.151228197554</v>
+        <v>528.2747555403779</v>
       </c>
       <c r="AA8" t="n">
-        <v>315.8490704230543</v>
+        <v>325.2923928199624</v>
       </c>
       <c r="AB8" t="n">
-        <v>531.8763968045594</v>
+        <v>535.2431522556993</v>
       </c>
       <c r="AC8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -35331,57 +36658,57 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>118.6492944628045</v>
+        <v>119.1675643373071</v>
       </c>
       <c r="AG8" t="n">
-        <v>116.6157614421375</v>
+        <v>117.94088579751</v>
       </c>
       <c r="AH8" t="n">
-        <v>37.8437260581015</v>
+        <v>38.12887330765528</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.51924334831958</v>
+        <v>75.52037537772701</v>
       </c>
       <c r="AJ8" t="n">
-        <v>170.8858942751025</v>
+        <v>171.0059034003586</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.680349747790815</v>
+        <v>1.735638898341277</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9918699186991869</v>
+        <v>0.9919354838709677</v>
       </c>
       <c r="AM8" t="n">
-        <v>216.1698078659346</v>
+        <v>216.8903738921543</v>
       </c>
       <c r="AN8" t="n">
-        <v>571.3868588306865</v>
+        <v>573.2914816934554</v>
       </c>
       <c r="AO8" t="n">
-        <v>355.9478833884134</v>
+        <v>358.6943686552942</v>
       </c>
       <c r="AP8" t="n">
-        <v>242.4167052141089</v>
+        <v>243.9264599992518</v>
       </c>
       <c r="AQ8" t="n">
-        <v>469.4790615627179</v>
+        <v>473.4622773113366</v>
       </c>
       <c r="AR8" t="n">
-        <v>226.5577300449587</v>
+        <v>227.3163298869583</v>
       </c>
       <c r="AS8" t="n">
-        <v>512.6576828253073</v>
+        <v>514.7277692350794</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -35410,13 +36737,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>401.11</v>
+        <v>399.97</v>
       </c>
       <c r="I9" t="n">
         <v>6.02</v>
       </c>
       <c r="J9" t="n">
-        <v>66.62956</v>
+        <v>66.4402</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -35431,13 +36758,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.35463897657367</v>
+        <v>75.25986237576616</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.305652323737203</v>
+        <v>9.365689884193202</v>
       </c>
       <c r="R9" t="n">
         <v>62.25973272085587</v>
@@ -35446,7 +36773,7 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.937610677149136</v>
+        <v>-0.9416991684351417</v>
       </c>
       <c r="U9" t="n">
         <v>0.3064516129032258</v>
@@ -35458,13 +36785,13 @@
         <v>565.1172405637031</v>
       </c>
       <c r="X9" t="n">
-        <v>453.6349266389735</v>
+        <v>453.0643715021122</v>
       </c>
       <c r="Y9" t="n">
-        <v>397.6148996500755</v>
+        <v>396.6829183992692</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.6549536278714</v>
+        <v>509.4458246049553</v>
       </c>
       <c r="AA9" t="n">
         <v>374.8035909795523</v>
@@ -35473,7 +36800,7 @@
         <v>502.6324388886986</v>
       </c>
       <c r="AC9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -35482,25 +36809,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.26225880076412</v>
+        <v>71.2242627536224</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.45492406561191</v>
+        <v>69.44129991831269</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.294925323900546</v>
+        <v>8.271965198433307</v>
       </c>
       <c r="AI9" t="n">
-        <v>61.7377704233179</v>
+        <v>61.75973393952787</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.36296239187379</v>
+        <v>82.35048706768551</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.558497951442156</v>
+        <v>-0.5783465765219231</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="AM9" t="n">
         <v>344.3134935761985</v>
@@ -35509,30 +36836,30 @@
         <v>565.1172405637031</v>
       </c>
       <c r="AO9" t="n">
-        <v>428.9987979805999</v>
+        <v>428.7700617768068</v>
       </c>
       <c r="AP9" t="n">
-        <v>379.0633475307187</v>
+        <v>378.9728312822383</v>
       </c>
       <c r="AQ9" t="n">
-        <v>478.9342484304812</v>
+        <v>478.5672922713753</v>
       </c>
       <c r="AR9" t="n">
-        <v>371.6613779483737</v>
+        <v>371.7935983159578</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.8250335990802</v>
+        <v>495.7499321474667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-09 16:42:08</t>
+          <t>2026-07-10 16:26:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -35561,19 +36888,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>75.47</v>
+        <v>73.37</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>24.345163</v>
+        <v>23.667744</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -35616,7 +36943,7 @@
         <v>39.24110623687622</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.6811111954324959</v>
+        <v>-0.7422184246516635</v>
       </c>
       <c r="AL10" t="n">
         <v>0.1212121212121212</v>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS235"/>
+  <dimension ref="A1:AS244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34151,7 +34151,7 @@
         <v>1.678743494980447</v>
       </c>
       <c r="U227" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V227" t="n">
         <v>270.2971378761002</v>
@@ -34202,7 +34202,7 @@
         <v>2.085326530795356</v>
       </c>
       <c r="AL227" t="n">
-        <v>0.9919354838709677</v>
+        <v>0.9919354838709676</v>
       </c>
       <c r="AM227" t="n">
         <v>257.5566506687599</v>
@@ -34302,7 +34302,7 @@
         <v>1.386639668302494</v>
       </c>
       <c r="U228" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V228" t="n">
         <v>280.3616247213112</v>
@@ -34353,7 +34353,7 @@
         <v>1.735638898341277</v>
       </c>
       <c r="AL228" t="n">
-        <v>0.9919354838709677</v>
+        <v>0.9919354838709676</v>
       </c>
       <c r="AM228" t="n">
         <v>216.8903738921543</v>
@@ -34435,7 +34435,7 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O229" t="n">
-        <v>31.40833427636435</v>
+        <v>31.40833427636436</v>
       </c>
       <c r="P229" t="n">
         <v>31.69078918164997</v>
@@ -34450,7 +34450,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T229" t="n">
-        <v>0.002031315827605777</v>
+        <v>0.0020313158276057</v>
       </c>
       <c r="U229" t="n">
         <v>0.4677419354838709</v>
@@ -34516,7 +34516,7 @@
         <v>242.0247807144675</v>
       </c>
       <c r="AP229" t="n">
-        <v>223.1293160847615</v>
+        <v>223.1293160847616</v>
       </c>
       <c r="AQ229" t="n">
         <v>260.9202453441735</v>
@@ -34583,7 +34583,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N230" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O230" t="n">
         <v>75.25986237576616</v>
@@ -34601,7 +34601,7 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T230" t="n">
-        <v>-0.9416991684351417</v>
+        <v>-0.9416991684351416</v>
       </c>
       <c r="U230" t="n">
         <v>0.3064516129032258</v>
@@ -34622,7 +34622,7 @@
         <v>509.4458246049553</v>
       </c>
       <c r="AA230" t="n">
-        <v>374.8035909795523</v>
+        <v>374.8035909795522</v>
       </c>
       <c r="AB230" t="n">
         <v>502.6324388886986</v>
@@ -34634,7 +34634,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE230" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF230" t="n">
         <v>71.2242627536224</v>
@@ -34746,7 +34746,7 @@
         <v>1.693293462912648</v>
       </c>
       <c r="R231" t="n">
-        <v>26.95049620511239</v>
+        <v>26.9504962051124</v>
       </c>
       <c r="S231" t="n">
         <v>31.22081491927324</v>
@@ -34791,7 +34791,7 @@
         <v>29.17466154240294</v>
       </c>
       <c r="AG231" t="n">
-        <v>28.78122109158187</v>
+        <v>28.78122109158186</v>
       </c>
       <c r="AH231" t="n">
         <v>2.076709222866049</v>
@@ -34827,7 +34827,7 @@
         <v>353.3230010986328</v>
       </c>
       <c r="AS231" t="n">
-        <v>427.9709626840815</v>
+        <v>427.9709626840816</v>
       </c>
     </row>
     <row r="232">
@@ -35203,7 +35203,7 @@
         <v>66</v>
       </c>
       <c r="AD234" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE234" t="n">
         <v>42.60474344487245</v>
@@ -35369,16 +35369,16 @@
         <v>4.692649432659968</v>
       </c>
       <c r="AI235" t="n">
-        <v>30.65681422468714</v>
+        <v>30.65681422468713</v>
       </c>
       <c r="AJ235" t="n">
-        <v>43.40183647311463</v>
+        <v>43.40183647311464</v>
       </c>
       <c r="AK235" t="n">
         <v>-0.9000466737719675</v>
       </c>
       <c r="AL235" t="n">
-        <v>0.2446808510638298</v>
+        <v>0.2446808510638297</v>
       </c>
       <c r="AM235" t="n">
         <v>192.5299987792968</v>
@@ -35393,13 +35393,1340 @@
         <v>207.8971385449045</v>
       </c>
       <c r="AQ235" t="n">
-        <v>269.1831401354438</v>
+        <v>269.1831401354437</v>
       </c>
       <c r="AR235" t="n">
         <v>200.188996887207</v>
       </c>
       <c r="AS235" t="n">
         <v>283.4139921694386</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>317.31</v>
+      </c>
+      <c r="I236" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J236" t="n">
+        <v>38.415253</v>
+      </c>
+      <c r="K236" t="n">
+        <v>67</v>
+      </c>
+      <c r="L236" t="n">
+        <v>62</v>
+      </c>
+      <c r="M236" t="n">
+        <v>32.7632894395273</v>
+      </c>
+      <c r="N236" t="n">
+        <v>38.41525394171838</v>
+      </c>
+      <c r="O236" t="n">
+        <v>35.7711349428061</v>
+      </c>
+      <c r="P236" t="n">
+        <v>35.74031432662115</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>1.506070683051228</v>
+      </c>
+      <c r="R236" t="n">
+        <v>33.87873912213476</v>
+      </c>
+      <c r="S236" t="n">
+        <v>37.82869352844091</v>
+      </c>
+      <c r="T236" t="n">
+        <v>1.755640081803493</v>
+      </c>
+      <c r="U236" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V236" t="n">
+        <v>270.6247707704955</v>
+      </c>
+      <c r="W236" t="n">
+        <v>317.3099975585938</v>
+      </c>
+      <c r="X236" t="n">
+        <v>295.4695746275784</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>283.0294307855752</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>307.9097184695815</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>279.8383851488331</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>312.4650085449219</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>38.41525394171838</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>34.49938974455982</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>1.837364774767286</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>37.38280954430236</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>2.131238885831012</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>0.9918699186991869</v>
+      </c>
+      <c r="AM236" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN236" t="n">
+        <v>317.3099975585938</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>284.9649592900641</v>
+      </c>
+      <c r="AP236" t="n">
+        <v>269.7883262504863</v>
+      </c>
+      <c r="AQ236" t="n">
+        <v>300.1415923296419</v>
+      </c>
+      <c r="AR236" t="n">
+        <v>265.4471175413494</v>
+      </c>
+      <c r="AS236" t="n">
+        <v>308.7820068359375</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>534.39</v>
+      </c>
+      <c r="I237" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J237" t="n">
+        <v>177.53821</v>
+      </c>
+      <c r="K237" t="n">
+        <v>63</v>
+      </c>
+      <c r="L237" t="n">
+        <v>62</v>
+      </c>
+      <c r="M237" t="n">
+        <v>96.25283295253539</v>
+      </c>
+      <c r="N237" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O237" t="n">
+        <v>151.3828611384844</v>
+      </c>
+      <c r="P237" t="n">
+        <v>154.5934458247951</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>24.5571117805376</v>
+      </c>
+      <c r="R237" t="n">
+        <v>114.5837701761498</v>
+      </c>
+      <c r="S237" t="n">
+        <v>177.8216452676742</v>
+      </c>
+      <c r="T237" t="n">
+        <v>1.065082453313776</v>
+      </c>
+      <c r="U237" t="n">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="V237" t="n">
+        <v>289.7210271871315</v>
+      </c>
+      <c r="W237" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="X237" t="n">
+        <v>455.662412026838</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>381.7455055674197</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>529.5793184862562</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>344.8971482302108</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>535.2431522556993</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>119.844107766781</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>121.3152730406211</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>38.57211859517521</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>171.4347584208504</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>1.495746262701672</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>0.943089430894309</v>
+      </c>
+      <c r="AM237" t="n">
+        <v>216.8903738921543</v>
+      </c>
+      <c r="AN237" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>360.7307643780109</v>
+      </c>
+      <c r="AP237" t="n">
+        <v>244.6286874065335</v>
+      </c>
+      <c r="AQ237" t="n">
+        <v>476.8328413494882</v>
+      </c>
+      <c r="AR237" t="n">
+        <v>227.3129224784419</v>
+      </c>
+      <c r="AS237" t="n">
+        <v>516.0186228467597</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>247.31</v>
+      </c>
+      <c r="I238" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="J238" t="n">
+        <v>29.547192</v>
+      </c>
+      <c r="K238" t="n">
+        <v>67</v>
+      </c>
+      <c r="L238" t="n">
+        <v>62</v>
+      </c>
+      <c r="M238" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N238" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O238" t="n">
+        <v>31.34583547043713</v>
+      </c>
+      <c r="P238" t="n">
+        <v>31.63875598086125</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>2.574964858953528</v>
+      </c>
+      <c r="R238" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S238" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T238" t="n">
+        <v>-0.6985118512134212</v>
+      </c>
+      <c r="U238" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="V238" t="n">
+        <v>227.2815375624661</v>
+      </c>
+      <c r="W238" t="n">
+        <v>308.1724153782034</v>
+      </c>
+      <c r="X238" t="n">
+        <v>262.3646428875588</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>240.8121870181178</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>283.9170987569998</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>238.3187292984228</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>292.4188472348776</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>30.91993347538324</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>29.81450547733067</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>2.388523702572737</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>34.5121459098859</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>-0.5747238237178148</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>0.4471544715447154</v>
+      </c>
+      <c r="AM238" t="n">
+        <v>227.2815375624661</v>
+      </c>
+      <c r="AN238" t="n">
+        <v>308.1724153782034</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>258.7998431889577</v>
+      </c>
+      <c r="AP238" t="n">
+        <v>238.8078997984238</v>
+      </c>
+      <c r="AQ238" t="n">
+        <v>278.7917865794915</v>
+      </c>
+      <c r="AR238" t="n">
+        <v>238.3527696016303</v>
+      </c>
+      <c r="AS238" t="n">
+        <v>288.866661265745</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="I239" t="n">
+        <v>6</v>
+      </c>
+      <c r="J239" t="n">
+        <v>64.00833</v>
+      </c>
+      <c r="K239" t="n">
+        <v>34</v>
+      </c>
+      <c r="L239" t="n">
+        <v>62</v>
+      </c>
+      <c r="M239" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N239" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O239" t="n">
+        <v>75.09657990997806</v>
+      </c>
+      <c r="P239" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>9.475172797189035</v>
+      </c>
+      <c r="R239" t="n">
+        <v>62.25973272085587</v>
+      </c>
+      <c r="S239" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T239" t="n">
+        <v>-1.170242500829913</v>
+      </c>
+      <c r="U239" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="V239" t="n">
+        <v>359.8502617707467</v>
+      </c>
+      <c r="W239" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="X239" t="n">
+        <v>450.5794794598684</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>393.7284426767342</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>507.4305162430026</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>373.5583963251352</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>500.9625636764438</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>71.11813106554642</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>69.41509126867139</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>8.323384333990594</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>61.7377704233179</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>-0.8541959352413649</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>343.1695949264438</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>563.2397746482092</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>426.7087863932785</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>376.768480389335</v>
+      </c>
+      <c r="AQ239" t="n">
+        <v>476.649092397222</v>
+      </c>
+      <c r="AR239" t="n">
+        <v>370.4266225399074</v>
+      </c>
+      <c r="AS239" t="n">
+        <v>494.1777743512428</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="I240" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J240" t="n">
+        <v>26.768703</v>
+      </c>
+      <c r="K240" t="n">
+        <v>37</v>
+      </c>
+      <c r="L240" t="n">
+        <v>62</v>
+      </c>
+      <c r="M240" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N240" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O240" t="n">
+        <v>28.82457073369382</v>
+      </c>
+      <c r="P240" t="n">
+        <v>28.94813194245805</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>1.712256124281385</v>
+      </c>
+      <c r="R240" t="n">
+        <v>26.81037373255447</v>
+      </c>
+      <c r="S240" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T240" t="n">
+        <v>-1.200677693330864</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="V240" t="n">
+        <v>334.434708770589</v>
+      </c>
+      <c r="W240" t="n">
+        <v>422.3507729952915</v>
+      </c>
+      <c r="X240" t="n">
+        <v>377.601876611389</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>355.1713213833029</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>400.0324318394752</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>351.2158958964635</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>408.9926754424794</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>29.09226878046618</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>28.71319547488797</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>2.036036407113766</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>26.82593443846539</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>32.42053258807379</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>-1.14122015320935</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>0.08943089430894309</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>331.002237918088</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>446.0207226104586</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>381.108721024107</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>354.4366440909167</v>
+      </c>
+      <c r="AQ240" t="n">
+        <v>407.7807979572974</v>
+      </c>
+      <c r="AR240" t="n">
+        <v>351.4197411438966</v>
+      </c>
+      <c r="AS240" t="n">
+        <v>424.7089769037667</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>656.73</v>
+      </c>
+      <c r="I241" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J241" t="n">
+        <v>23.88109</v>
+      </c>
+      <c r="K241" t="n">
+        <v>55</v>
+      </c>
+      <c r="L241" t="n">
+        <v>62</v>
+      </c>
+      <c r="M241" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N241" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O241" t="n">
+        <v>23.1403299560018</v>
+      </c>
+      <c r="P241" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>2.845322499107136</v>
+      </c>
+      <c r="R241" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S241" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0.2603430873760875</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="V241" t="n">
+        <v>542.8699951171875</v>
+      </c>
+      <c r="W241" t="n">
+        <v>806.0930040147568</v>
+      </c>
+      <c r="X241" t="n">
+        <v>636.3590737900496</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>558.1127050646033</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>714.6054425154958</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>564.1629760742187</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>785.8947675955858</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>25.15093195827638</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>25.7156235657128</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>3.133829023683002</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>28.73427065040975</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>-0.4052046071052107</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>0.4146341463414634</v>
+      </c>
+      <c r="AM241" t="n">
+        <v>542.8699951171875</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>864.3475918629769</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>691.6506288526003</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>605.4703307013178</v>
+      </c>
+      <c r="AQ241" t="n">
+        <v>777.8309270038829</v>
+      </c>
+      <c r="AR241" t="n">
+        <v>583.2380249023437</v>
+      </c>
+      <c r="AS241" t="n">
+        <v>790.1924428862681</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>390.99</v>
+      </c>
+      <c r="I242" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="J242" t="n">
+        <v>23.287073</v>
+      </c>
+      <c r="K242" t="n">
+        <v>67</v>
+      </c>
+      <c r="L242" t="n">
+        <v>62</v>
+      </c>
+      <c r="M242" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N242" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O242" t="n">
+        <v>24.40728702089413</v>
+      </c>
+      <c r="P242" t="n">
+        <v>24.57421541107486</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>1.515086151785492</v>
+      </c>
+      <c r="R242" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S242" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T242" t="n">
+        <v>-0.739373150215907</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0.3064516129032258</v>
+      </c>
+      <c r="V242" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="W242" t="n">
+        <v>460.2458699725923</v>
+      </c>
+      <c r="X242" t="n">
+        <v>409.7983490808125</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>384.3600525923341</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>435.2366455692909</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>374.2141233952839</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>445.2374133636685</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>25.15200029139151</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>24.81926112267433</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>2.556891985278869</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>22.87476167224703</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>27.04152673240599</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>-0.7293727314758328</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>352.6199687231154</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>573.8931703092702</v>
+      </c>
+      <c r="AO242" t="n">
+        <v>422.3020848924635</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>379.3718684596312</v>
+      </c>
+      <c r="AQ242" t="n">
+        <v>465.2323013252957</v>
+      </c>
+      <c r="AR242" t="n">
+        <v>384.0672484770275</v>
+      </c>
+      <c r="AS242" t="n">
+        <v>454.0272338370966</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>73.83</v>
+      </c>
+      <c r="I243" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J243" t="n">
+        <v>23.81613</v>
+      </c>
+      <c r="K243" t="n">
+        <v>67</v>
+      </c>
+      <c r="L243" t="n">
+        <v>3</v>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr"/>
+      <c r="T243" t="inlineStr"/>
+      <c r="U243" t="inlineStr"/>
+      <c r="V243" t="inlineStr"/>
+      <c r="W243" t="inlineStr"/>
+      <c r="X243" t="inlineStr"/>
+      <c r="Y243" t="inlineStr"/>
+      <c r="Z243" t="inlineStr"/>
+      <c r="AA243" t="inlineStr"/>
+      <c r="AB243" t="inlineStr"/>
+      <c r="AC243" t="n">
+        <v>64</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>32.77522457364311</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>36.27667935940586</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>10.04327385547198</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>30.00316182615256</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>39.25849763772231</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>-0.8920492164775371</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>101.6031961782937</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>70.46904722633052</v>
+      </c>
+      <c r="AQ243" t="n">
+        <v>132.7373451302568</v>
+      </c>
+      <c r="AR243" t="n">
+        <v>93.00980166107296</v>
+      </c>
+      <c r="AS243" t="n">
+        <v>121.7013426769392</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-07-13 16:23:50</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>203.53</v>
+      </c>
+      <c r="I244" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J244" t="n">
+        <v>31.120794</v>
+      </c>
+      <c r="K244" t="n">
+        <v>65</v>
+      </c>
+      <c r="L244" t="n">
+        <v>62</v>
+      </c>
+      <c r="M244" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N244" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O244" t="n">
+        <v>36.33874189897329</v>
+      </c>
+      <c r="P244" t="n">
+        <v>33.23047515261592</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>5.759461632523198</v>
+      </c>
+      <c r="R244" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S244" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T244" t="n">
+        <v>-0.9059784111605109</v>
+      </c>
+      <c r="U244" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V244" t="n">
+        <v>192.8248379811028</v>
+      </c>
+      <c r="W244" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="X244" t="n">
+        <v>237.6553720192853</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>199.9884929425836</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>275.322251095987</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>198.024791849554</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>292.5075091365892</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>95</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>36.47344740349104</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>36.28979741310587</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>4.699922494426534</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>30.66186785150267</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>43.36775487783004</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>-1.138881207049383</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>192.8248379811028</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>314.64074202557</v>
+      </c>
+      <c r="AO244" t="n">
+        <v>238.5363460188314</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>207.7988529052818</v>
+      </c>
+      <c r="AQ244" t="n">
+        <v>269.2738391323809</v>
+      </c>
+      <c r="AR244" t="n">
+        <v>200.5286157488275</v>
+      </c>
+      <c r="AS244" t="n">
+        <v>283.6251169010084</v>
       </c>
     </row>
   </sheetData>
@@ -35646,12 +36973,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -35680,13 +37007,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>355.03</v>
+        <v>350.67</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="J2" t="n">
-        <v>27.080854</v>
+        <v>26.768703</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -35701,49 +37028,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.86942321946665</v>
+        <v>28.82457073369382</v>
       </c>
       <c r="P2" t="n">
-        <v>29.04576724217558</v>
+        <v>28.94813194245805</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.693293462912648</v>
+        <v>1.712256124281385</v>
       </c>
       <c r="R2" t="n">
-        <v>26.95049620511239</v>
+        <v>26.81037373255447</v>
       </c>
       <c r="S2" t="n">
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.056266535388447</v>
+        <v>-1.200677693330864</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="V2" t="n">
-        <v>334.6900024414062</v>
+        <v>334.434708770589</v>
       </c>
       <c r="W2" t="n">
-        <v>422.673178165517</v>
+        <v>422.3507729952915</v>
       </c>
       <c r="X2" t="n">
-        <v>378.4781384072077</v>
+        <v>377.601876611389</v>
       </c>
       <c r="Y2" t="n">
-        <v>356.2790611084229</v>
+        <v>355.1713213833029</v>
       </c>
       <c r="Z2" t="n">
-        <v>400.6772157059926</v>
+        <v>400.0324318394752</v>
       </c>
       <c r="AA2" t="n">
-        <v>353.3210052490235</v>
+        <v>351.2158958964635</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.3048835916722</v>
+        <v>408.9926754424794</v>
       </c>
       <c r="AC2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD2" t="n">
         <v>25.26734640596091</v>
@@ -35752,57 +37079,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.17466154240294</v>
+        <v>29.09226878046618</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.78122109158187</v>
+        <v>28.71319547488797</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.076709222866049</v>
+        <v>2.036036407113766</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.95064844383164</v>
+        <v>26.82593443846539</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.6446195792587</v>
+        <v>32.42053258807379</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.008233371985173</v>
+        <v>-1.14122015320935</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.08943089430894309</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.2549113821476</v>
+        <v>331.002237918088</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.3611964445124</v>
+        <v>446.0207226104586</v>
       </c>
       <c r="AO2" t="n">
-        <v>382.4798128209026</v>
+        <v>381.108721024107</v>
       </c>
       <c r="AP2" t="n">
-        <v>355.2541549091287</v>
+        <v>354.4366440909167</v>
       </c>
       <c r="AQ2" t="n">
-        <v>409.7054707326765</v>
+        <v>407.7807979572974</v>
       </c>
       <c r="AR2" t="n">
-        <v>353.3230010986328</v>
+        <v>351.4197411438966</v>
       </c>
       <c r="AS2" t="n">
-        <v>427.9709626840815</v>
+        <v>424.7089769037667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -35831,13 +37158,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>385.1</v>
+        <v>390.99</v>
       </c>
       <c r="I3" t="n">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="J3" t="n">
-        <v>22.92262</v>
+        <v>23.287073</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -35852,13 +37179,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.41962467949467</v>
+        <v>24.40728702089413</v>
       </c>
       <c r="P3" t="n">
         <v>24.57421541107486</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.508801241215612</v>
+        <v>1.515086151785492</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -35867,34 +37194,34 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9921815005192874</v>
+        <v>-0.739373150215907</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="V3" t="n">
-        <v>352.8299865722656</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="W3" t="n">
-        <v>460.5199890136719</v>
+        <v>460.2458699725923</v>
       </c>
       <c r="X3" t="n">
-        <v>410.2496946155104</v>
+        <v>409.7983490808125</v>
       </c>
       <c r="Y3" t="n">
-        <v>384.9018337630882</v>
+        <v>384.3600525923341</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.5975554679327</v>
+        <v>435.2366455692909</v>
       </c>
       <c r="AA3" t="n">
-        <v>374.4370025634765</v>
+        <v>374.2141233952839</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.5025934788345</v>
+        <v>445.2374133636685</v>
       </c>
       <c r="AC3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD3" t="n">
         <v>21.00178491501581</v>
@@ -35903,57 +37230,57 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.30514091987446</v>
+        <v>25.15200029139151</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.84441577935574</v>
+        <v>24.81926112267433</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.761017074974657</v>
+        <v>2.556891985278869</v>
       </c>
       <c r="AI3" t="n">
-        <v>22.87523778279622</v>
+        <v>22.87476167224703</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27.32154113072914</v>
+        <v>27.04152673240599</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8629142287706901</v>
+        <v>-0.7293727314758328</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.8299865722656</v>
+        <v>352.6199687231154</v>
       </c>
       <c r="AN3" t="n">
-        <v>574.2349768431054</v>
+        <v>573.8931703092702</v>
       </c>
       <c r="AO3" t="n">
-        <v>425.126367453891</v>
+        <v>422.3020848924635</v>
       </c>
       <c r="AP3" t="n">
-        <v>378.7412805943167</v>
+        <v>379.3718684596312</v>
       </c>
       <c r="AQ3" t="n">
-        <v>471.5114543134652</v>
+        <v>465.2323013252957</v>
       </c>
       <c r="AR3" t="n">
-        <v>384.3039947509766</v>
+        <v>384.0672484770275</v>
       </c>
       <c r="AS3" t="n">
-        <v>459.0018909962495</v>
+        <v>454.0272338370966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -35982,13 +37309,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>669.21</v>
+        <v>656.73</v>
       </c>
       <c r="I4" t="n">
-        <v>27.47</v>
+        <v>27.5</v>
       </c>
       <c r="J4" t="n">
-        <v>24.361486</v>
+        <v>23.88109</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -36003,13 +37330,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.19084096310542</v>
+        <v>23.1403299560018</v>
       </c>
       <c r="P4" t="n">
         <v>22.19399968927557</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.886192027862101</v>
+        <v>2.845322499107136</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
@@ -36018,34 +37345,34 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4056019230853855</v>
+        <v>0.2603430873760875</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="V4" t="n">
-        <v>542.2777733043324</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="W4" t="n">
-        <v>805.2136298285589</v>
+        <v>806.0930040147568</v>
       </c>
       <c r="X4" t="n">
-        <v>637.052401256506</v>
+        <v>636.3590737900496</v>
       </c>
       <c r="Y4" t="n">
-        <v>557.7687062511341</v>
+        <v>558.1127050646033</v>
       </c>
       <c r="Z4" t="n">
-        <v>716.3360962618779</v>
+        <v>714.6054425154958</v>
       </c>
       <c r="AA4" t="n">
-        <v>563.547525554865</v>
+        <v>564.1629760742187</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.0374278491179</v>
+        <v>785.8947675955858</v>
       </c>
       <c r="AC4" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD4" t="n">
         <v>19.74072709517046</v>
@@ -36054,57 +37381,57 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.21018970037271</v>
+        <v>25.15093195827638</v>
       </c>
       <c r="AG4" t="n">
-        <v>25.94976575387798</v>
+        <v>25.7156235657128</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.142532527805395</v>
+        <v>3.133829023683002</v>
       </c>
       <c r="AI4" t="n">
-        <v>21.21480091441762</v>
+        <v>21.20865545099432</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28.73295069045338</v>
+        <v>28.73427065040975</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.2700699810943277</v>
+        <v>-0.4052046071052107</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.4274193548387097</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="AM4" t="n">
-        <v>542.2777733043324</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="AN4" t="n">
-        <v>863.4046672173081</v>
+        <v>864.3475918629769</v>
       </c>
       <c r="AO4" t="n">
-        <v>692.5239110692384</v>
+        <v>691.6506288526003</v>
       </c>
       <c r="AP4" t="n">
-        <v>606.1985425304241</v>
+        <v>605.4703307013178</v>
       </c>
       <c r="AQ4" t="n">
-        <v>778.8492796080526</v>
+        <v>777.8309270038829</v>
       </c>
       <c r="AR4" t="n">
-        <v>582.7705811190518</v>
+        <v>583.2380249023437</v>
       </c>
       <c r="AS4" t="n">
-        <v>789.2941554667544</v>
+        <v>790.1924428862681</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -36133,13 +37460,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>245.34</v>
+        <v>247.31</v>
       </c>
       <c r="I5" t="n">
-        <v>7.81</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>31.413572</v>
+        <v>29.547192</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -36154,13 +37481,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.40833427636435</v>
+        <v>31.34583547043713</v>
       </c>
       <c r="P5" t="n">
-        <v>31.69078918164997</v>
+        <v>31.63875598086125</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.578488073820786</v>
+        <v>2.574964858953528</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -36169,34 +37496,34 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002031315827605777</v>
+        <v>-0.6985118512134212</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="V5" t="n">
-        <v>212.0751264471757</v>
+        <v>227.2815375624661</v>
       </c>
       <c r="W5" t="n">
-        <v>287.5539503110835</v>
+        <v>308.1724153782034</v>
       </c>
       <c r="X5" t="n">
-        <v>245.2990906984056</v>
+        <v>262.3646428875588</v>
       </c>
       <c r="Y5" t="n">
-        <v>225.1610988418653</v>
+        <v>240.8121870181178</v>
       </c>
       <c r="Z5" t="n">
-        <v>265.437082554946</v>
+        <v>283.9170987569998</v>
       </c>
       <c r="AA5" t="n">
-        <v>222.3738680789345</v>
+        <v>238.3187292984228</v>
       </c>
       <c r="AB5" t="n">
-        <v>272.8543843374425</v>
+        <v>292.4188472348776</v>
       </c>
       <c r="AC5" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD5" t="n">
         <v>27.15430556301865</v>
@@ -36205,57 +37532,57 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>30.98908843975256</v>
+        <v>30.91993347538324</v>
       </c>
       <c r="AG5" t="n">
-        <v>29.89965371014563</v>
+        <v>29.81450547733067</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.419393678579506</v>
+        <v>2.388523702572737</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.48110034705349</v>
+        <v>28.4770334052127</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34.60712672457826</v>
+        <v>34.5121459098859</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1754503882545747</v>
+        <v>-0.5747238237178148</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5725806451612904</v>
+        <v>0.4471544715447154</v>
       </c>
       <c r="AM5" t="n">
-        <v>212.0751264471757</v>
+        <v>227.2815375624661</v>
       </c>
       <c r="AN5" t="n">
-        <v>287.5539503110835</v>
+        <v>308.1724153782034</v>
       </c>
       <c r="AO5" t="n">
-        <v>242.0247807144675</v>
+        <v>258.7998431889577</v>
       </c>
       <c r="AP5" t="n">
-        <v>223.1293160847615</v>
+        <v>238.8078997984238</v>
       </c>
       <c r="AQ5" t="n">
-        <v>260.9202453441735</v>
+        <v>278.7917865794915</v>
       </c>
       <c r="AR5" t="n">
-        <v>222.4373937104878</v>
+        <v>238.3527696016303</v>
       </c>
       <c r="AS5" t="n">
-        <v>270.2816597189562</v>
+        <v>288.866661265745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -36284,13 +37611,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>315.32</v>
+        <v>317.31</v>
       </c>
       <c r="I6" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="J6" t="n">
-        <v>38.220608</v>
+        <v>38.415253</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -36302,111 +37629,111 @@
         <v>32.7632894395273</v>
       </c>
       <c r="N6" t="n">
-        <v>38.28329312599312</v>
+        <v>38.41525394171838</v>
       </c>
       <c r="O6" t="n">
-        <v>35.68072968773762</v>
+        <v>35.7711349428061</v>
       </c>
       <c r="P6" t="n">
-        <v>35.66464846705698</v>
+        <v>35.74031432662115</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.512963904168078</v>
+        <v>1.506070683051228</v>
       </c>
       <c r="R6" t="n">
-        <v>33.74025214472903</v>
+        <v>33.87873912213476</v>
       </c>
       <c r="S6" t="n">
-        <v>37.76961245779263</v>
+        <v>37.82869352844091</v>
       </c>
       <c r="T6" t="n">
-        <v>1.678743494980447</v>
+        <v>1.755640081803493</v>
       </c>
       <c r="U6" t="n">
         <v>0.9838709677419355</v>
       </c>
       <c r="V6" t="n">
-        <v>270.2971378761002</v>
+        <v>270.6247707704955</v>
       </c>
       <c r="W6" t="n">
-        <v>315.8371682894432</v>
+        <v>317.3099975585938</v>
       </c>
       <c r="X6" t="n">
-        <v>294.3660199238353</v>
+        <v>295.4695746275784</v>
       </c>
       <c r="Y6" t="n">
-        <v>281.8840677144487</v>
+        <v>283.0294307855752</v>
       </c>
       <c r="Z6" t="n">
-        <v>306.847972133222</v>
+        <v>307.9097184695815</v>
       </c>
       <c r="AA6" t="n">
-        <v>278.3570801940145</v>
+        <v>279.8383851488331</v>
       </c>
       <c r="AB6" t="n">
-        <v>311.5993027767892</v>
+        <v>312.4650085449219</v>
       </c>
       <c r="AC6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD6" t="n">
         <v>31.21898795984968</v>
       </c>
       <c r="AE6" t="n">
-        <v>38.28329312599312</v>
+        <v>38.41525394171838</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.47491160944495</v>
+        <v>34.49938974455982</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.36563375175731</v>
+        <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.796215765368129</v>
+        <v>1.837364774767286</v>
       </c>
       <c r="AI6" t="n">
-        <v>32.14202455931072</v>
+        <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.35351082199134</v>
+        <v>37.38280954430236</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.085326530795356</v>
+        <v>2.131238885831012</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.9919354838709677</v>
+        <v>0.9918699186991869</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.5566506687599</v>
+        <v>257.8688405483584</v>
       </c>
       <c r="AN6" t="n">
-        <v>315.8371682894432</v>
+        <v>317.3099975585938</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.4180207779208</v>
+        <v>284.9649592900641</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.5992407136338</v>
+        <v>269.7883262504863</v>
       </c>
       <c r="AQ6" t="n">
-        <v>299.2368008422079</v>
+        <v>300.1415923296419</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.1717026143135</v>
+        <v>265.4471175413494</v>
       </c>
       <c r="AS6" t="n">
-        <v>308.1664642814286</v>
+        <v>308.7820068359375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -36435,13 +37762,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>210.96</v>
+        <v>203.53</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="J7" t="n">
-        <v>32.30628</v>
+        <v>31.120794</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -36456,13 +37783,13 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.45916512919501</v>
+        <v>36.33874189897329</v>
       </c>
       <c r="P7" t="n">
-        <v>33.55053584754558</v>
+        <v>33.23047515261592</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.727551610215001</v>
+        <v>5.759461632523198</v>
       </c>
       <c r="R7" t="n">
         <v>30.27902016048226</v>
@@ -36471,34 +37798,34 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7250716207931498</v>
+        <v>-0.9059784111605109</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="V7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.8248379811028</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="X7" t="n">
-        <v>238.0783482936434</v>
+        <v>237.6553720192853</v>
       </c>
       <c r="Y7" t="n">
-        <v>200.6774362789394</v>
+        <v>199.9884929425836</v>
       </c>
       <c r="Z7" t="n">
-        <v>275.4792603083474</v>
+        <v>275.322251095987</v>
       </c>
       <c r="AA7" t="n">
-        <v>197.7220016479492</v>
+        <v>198.024791849554</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.0602499483069</v>
+        <v>292.5075091365892</v>
       </c>
       <c r="AC7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -36507,57 +37834,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.52988351304352</v>
+        <v>36.47344740349104</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.31836871711575</v>
+        <v>36.28979741310587</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.692649432659968</v>
+        <v>4.699922494426534</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.65681422468714</v>
+        <v>30.66186785150267</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.40183647311463</v>
+        <v>43.36775487783004</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.9000466737719675</v>
+        <v>-1.138881207049383</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2446808510638298</v>
+        <v>0.1263157894736842</v>
       </c>
       <c r="AM7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.8248379811028</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>314.64074202557</v>
       </c>
       <c r="AO7" t="n">
-        <v>238.5401393401742</v>
+        <v>238.5363460188314</v>
       </c>
       <c r="AP7" t="n">
-        <v>207.8971385449045</v>
+        <v>207.7988529052818</v>
       </c>
       <c r="AQ7" t="n">
-        <v>269.1831401354438</v>
+        <v>269.2738391323809</v>
       </c>
       <c r="AR7" t="n">
-        <v>200.188996887207</v>
+        <v>200.5286157488275</v>
       </c>
       <c r="AS7" t="n">
-        <v>283.4139921694386</v>
+        <v>283.6251169010084</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -36586,13 +37913,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>557.89</v>
+        <v>534.39</v>
       </c>
       <c r="I8" t="n">
         <v>3.01</v>
       </c>
       <c r="J8" t="n">
-        <v>185.34552</v>
+        <v>177.53821</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -36601,55 +37928,55 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>93.14339691737914</v>
+        <v>96.25283295253539</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>150.0592088166947</v>
+        <v>151.3828611384844</v>
       </c>
       <c r="P8" t="n">
-        <v>153.0967237128586</v>
+        <v>154.5934458247951</v>
       </c>
       <c r="Q8" t="n">
-        <v>25.44735448575645</v>
+        <v>24.5571117805376</v>
       </c>
       <c r="R8" t="n">
-        <v>108.0705623986586</v>
+        <v>114.5837701761498</v>
       </c>
       <c r="S8" t="n">
         <v>177.8216452676742</v>
       </c>
       <c r="T8" t="n">
-        <v>1.386639668302494</v>
+        <v>1.065082453313776</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="V8" t="n">
-        <v>280.3616247213112</v>
+        <v>289.7210271871315</v>
       </c>
       <c r="W8" t="n">
         <v>573.2914816934554</v>
       </c>
       <c r="X8" t="n">
-        <v>451.678218538251</v>
+        <v>455.662412026838</v>
       </c>
       <c r="Y8" t="n">
-        <v>375.0816815361241</v>
+        <v>381.7455055674197</v>
       </c>
       <c r="Z8" t="n">
-        <v>528.2747555403779</v>
+        <v>529.5793184862562</v>
       </c>
       <c r="AA8" t="n">
-        <v>325.2923928199624</v>
+        <v>344.8971482302108</v>
       </c>
       <c r="AB8" t="n">
         <v>535.2431522556993</v>
       </c>
       <c r="AC8" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD8" t="n">
         <v>72.05660262197819</v>
@@ -36658,25 +37985,25 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>119.1675643373071</v>
+        <v>119.844107766781</v>
       </c>
       <c r="AG8" t="n">
-        <v>117.94088579751</v>
+        <v>121.3152730406211</v>
       </c>
       <c r="AH8" t="n">
-        <v>38.12887330765528</v>
+        <v>38.57211859517521</v>
       </c>
       <c r="AI8" t="n">
-        <v>75.52037537772701</v>
+        <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>171.0059034003586</v>
+        <v>171.4347584208504</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.735638898341277</v>
+        <v>1.495746262701672</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9919354838709677</v>
+        <v>0.943089430894309</v>
       </c>
       <c r="AM8" t="n">
         <v>216.8903738921543</v>
@@ -36685,30 +38012,30 @@
         <v>573.2914816934554</v>
       </c>
       <c r="AO8" t="n">
-        <v>358.6943686552942</v>
+        <v>360.7307643780109</v>
       </c>
       <c r="AP8" t="n">
-        <v>243.9264599992518</v>
+        <v>244.6286874065335</v>
       </c>
       <c r="AQ8" t="n">
-        <v>473.4622773113366</v>
+        <v>476.8328413494882</v>
       </c>
       <c r="AR8" t="n">
-        <v>227.3163298869583</v>
+        <v>227.3129224784419</v>
       </c>
       <c r="AS8" t="n">
-        <v>514.7277692350794</v>
+        <v>516.0186228467597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -36737,13 +38064,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>399.97</v>
+        <v>384.05</v>
       </c>
       <c r="I9" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>66.4402</v>
+        <v>64.00833</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -36758,13 +38085,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.25986237576616</v>
+        <v>75.09657990997806</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.365689884193202</v>
+        <v>9.475172797189035</v>
       </c>
       <c r="R9" t="n">
         <v>62.25973272085587</v>
@@ -36773,34 +38100,34 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9416991684351417</v>
+        <v>-1.170242500829913</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="V9" t="n">
-        <v>361.0497626433158</v>
+        <v>359.8502617707467</v>
       </c>
       <c r="W9" t="n">
-        <v>565.1172405637031</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="X9" t="n">
-        <v>453.0643715021122</v>
+        <v>450.5794794598684</v>
       </c>
       <c r="Y9" t="n">
-        <v>396.6829183992692</v>
+        <v>393.7284426767342</v>
       </c>
       <c r="Z9" t="n">
-        <v>509.4458246049553</v>
+        <v>507.4305162430026</v>
       </c>
       <c r="AA9" t="n">
-        <v>374.8035909795523</v>
+        <v>373.5583963251352</v>
       </c>
       <c r="AB9" t="n">
-        <v>502.6324388886986</v>
+        <v>500.9625636764438</v>
       </c>
       <c r="AC9" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AD9" t="n">
         <v>57.19493248774063</v>
@@ -36809,57 +38136,57 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.2242627536224</v>
+        <v>71.11813106554642</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.44129991831269</v>
+        <v>69.41509126867139</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.271965198433307</v>
+        <v>8.323384333990594</v>
       </c>
       <c r="AI9" t="n">
-        <v>61.75973393952787</v>
+        <v>61.7377704233179</v>
       </c>
       <c r="AJ9" t="n">
-        <v>82.35048706768551</v>
+        <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.5783465765219231</v>
+        <v>-0.8541959352413649</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.2439024390243902</v>
       </c>
       <c r="AM9" t="n">
-        <v>344.3134935761985</v>
+        <v>343.1695949264438</v>
       </c>
       <c r="AN9" t="n">
-        <v>565.1172405637031</v>
+        <v>563.2397746482092</v>
       </c>
       <c r="AO9" t="n">
-        <v>428.7700617768068</v>
+        <v>426.7087863932785</v>
       </c>
       <c r="AP9" t="n">
-        <v>378.9728312822383</v>
+        <v>376.768480389335</v>
       </c>
       <c r="AQ9" t="n">
-        <v>478.5672922713753</v>
+        <v>476.649092397222</v>
       </c>
       <c r="AR9" t="n">
-        <v>371.7935983159578</v>
+        <v>370.4266225399074</v>
       </c>
       <c r="AS9" t="n">
-        <v>495.7499321474667</v>
+        <v>494.1777743512428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-10 16:26:16</t>
+          <t>2026-07-13 16:23:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -36888,19 +38215,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.37</v>
+        <v>73.83</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.667744</v>
+        <v>23.81613</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -36919,7 +38246,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -36928,25 +38255,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>31.89578623712688</v>
+        <v>32.77522457364311</v>
       </c>
       <c r="AG10" t="n">
-        <v>36.09881344520055</v>
+        <v>36.27667935940586</v>
       </c>
       <c r="AH10" t="n">
-        <v>11.08574236888346</v>
+        <v>10.04327385547198</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.753759468607635</v>
+        <v>30.00316182615256</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.24110623687622</v>
+        <v>39.25849763772231</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.7422184246516635</v>
+        <v>-0.8920492164775371</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.09375</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -36955,19 +38282,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>98.87693733509334</v>
+        <v>101.6031961782937</v>
       </c>
       <c r="AP10" t="n">
-        <v>64.5111359915546</v>
+        <v>70.46904722633052</v>
       </c>
       <c r="AQ10" t="n">
-        <v>133.2427386786321</v>
+        <v>132.7373451302568</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.63665435268367</v>
+        <v>93.00980166107296</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.6474293343163</v>
+        <v>121.7013426769392</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS244"/>
+  <dimension ref="A1:AS253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34522,7 +34522,7 @@
         <v>260.9202453441735</v>
       </c>
       <c r="AR229" t="n">
-        <v>222.4373937104878</v>
+        <v>222.4373937104877</v>
       </c>
       <c r="AS229" t="n">
         <v>270.2816597189562</v>
@@ -35478,13 +35478,13 @@
         <v>1.755640081803493</v>
       </c>
       <c r="U236" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V236" t="n">
         <v>270.6247707704955</v>
       </c>
       <c r="W236" t="n">
-        <v>317.3099975585938</v>
+        <v>317.3099975585937</v>
       </c>
       <c r="X236" t="n">
         <v>295.4695746275784</v>
@@ -35535,7 +35535,7 @@
         <v>257.8688405483584</v>
       </c>
       <c r="AN236" t="n">
-        <v>317.3099975585938</v>
+        <v>317.3099975585937</v>
       </c>
       <c r="AO236" t="n">
         <v>284.9649592900641</v>
@@ -35605,7 +35605,7 @@
         <v>62</v>
       </c>
       <c r="M237" t="n">
-        <v>96.25283295253539</v>
+        <v>96.2528329525354</v>
       </c>
       <c r="N237" t="n">
         <v>190.4622862768955</v>
@@ -35692,7 +35692,7 @@
         <v>360.7307643780109</v>
       </c>
       <c r="AP237" t="n">
-        <v>244.6286874065335</v>
+        <v>244.6286874065334</v>
       </c>
       <c r="AQ237" t="n">
         <v>476.8328413494882</v>
@@ -35792,7 +35792,7 @@
         <v>262.3646428875588</v>
       </c>
       <c r="Y238" t="n">
-        <v>240.8121870181178</v>
+        <v>240.8121870181177</v>
       </c>
       <c r="Z238" t="n">
         <v>283.9170987569998</v>
@@ -35816,7 +35816,7 @@
         <v>30.91993347538324</v>
       </c>
       <c r="AG238" t="n">
-        <v>29.81450547733067</v>
+        <v>29.81450547733068</v>
       </c>
       <c r="AH238" t="n">
         <v>2.388523702572737</v>
@@ -35849,7 +35849,7 @@
         <v>278.7917865794915</v>
       </c>
       <c r="AR238" t="n">
-        <v>238.3527696016303</v>
+        <v>238.3527696016302</v>
       </c>
       <c r="AS238" t="n">
         <v>288.866661265745</v>
@@ -35910,7 +35910,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N239" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O239" t="n">
         <v>75.09657990997806</v>
@@ -35961,7 +35961,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE239" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF239" t="n">
         <v>71.11813106554642</v>
@@ -35973,7 +35973,7 @@
         <v>8.323384333990594</v>
       </c>
       <c r="AI239" t="n">
-        <v>61.7377704233179</v>
+        <v>61.73777042331791</v>
       </c>
       <c r="AJ239" t="n">
         <v>82.36296239187379</v>
@@ -36064,7 +36064,7 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O240" t="n">
-        <v>28.82457073369382</v>
+        <v>28.82457073369381</v>
       </c>
       <c r="P240" t="n">
         <v>28.94813194245805</v>
@@ -36088,7 +36088,7 @@
         <v>334.434708770589</v>
       </c>
       <c r="W240" t="n">
-        <v>422.3507729952915</v>
+        <v>422.3507729952916</v>
       </c>
       <c r="X240" t="n">
         <v>377.601876611389</v>
@@ -36133,7 +36133,7 @@
         <v>-1.14122015320935</v>
       </c>
       <c r="AL240" t="n">
-        <v>0.08943089430894309</v>
+        <v>0.08943089430894299</v>
       </c>
       <c r="AM240" t="n">
         <v>331.002237918088</v>
@@ -36417,7 +36417,7 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF242" t="n">
-        <v>25.15200029139151</v>
+        <v>25.15200029139152</v>
       </c>
       <c r="AG242" t="n">
         <v>24.81926112267433</v>
@@ -36530,7 +36530,7 @@
         <v>64</v>
       </c>
       <c r="AD243" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE243" t="n">
         <v>42.60474344487245</v>
@@ -36548,7 +36548,7 @@
         <v>30.00316182615256</v>
       </c>
       <c r="AJ243" t="n">
-        <v>39.25849763772231</v>
+        <v>39.25849763772232</v>
       </c>
       <c r="AK243" t="n">
         <v>-0.8920492164775371</v>
@@ -36651,7 +36651,7 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T244" t="n">
-        <v>-0.9059784111605109</v>
+        <v>-0.9059784111605108</v>
       </c>
       <c r="U244" t="n">
         <v>0.1935483870967742</v>
@@ -36696,7 +36696,7 @@
         <v>4.699922494426534</v>
       </c>
       <c r="AI244" t="n">
-        <v>30.66186785150267</v>
+        <v>30.66186785150268</v>
       </c>
       <c r="AJ244" t="n">
         <v>43.36775487783004</v>
@@ -36727,6 +36727,1333 @@
       </c>
       <c r="AS244" t="n">
         <v>283.6251169010084</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>314.86</v>
+      </c>
+      <c r="I245" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J245" t="n">
+        <v>38.16485</v>
+      </c>
+      <c r="K245" t="n">
+        <v>67</v>
+      </c>
+      <c r="L245" t="n">
+        <v>62</v>
+      </c>
+      <c r="M245" t="n">
+        <v>33.31113727560344</v>
+      </c>
+      <c r="N245" t="n">
+        <v>38.41525394171838</v>
+      </c>
+      <c r="O245" t="n">
+        <v>35.8575116017553</v>
+      </c>
+      <c r="P245" t="n">
+        <v>35.80992839526899</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>1.484147167761942</v>
+      </c>
+      <c r="R245" t="n">
+        <v>33.93462617518539</v>
+      </c>
+      <c r="S245" t="n">
+        <v>37.8504847787483</v>
+      </c>
+      <c r="T245" t="n">
+        <v>1.554656066705375</v>
+      </c>
+      <c r="U245" t="n">
+        <v>0.9516129032258065</v>
+      </c>
+      <c r="V245" t="n">
+        <v>274.8168825237283</v>
+      </c>
+      <c r="W245" t="n">
+        <v>316.9258450191766</v>
+      </c>
+      <c r="X245" t="n">
+        <v>295.8244707144812</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>283.5802565804452</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>308.0686848485172</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>279.9606659452795</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>312.2664994246734</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>38.41525394171838</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>34.5259869677567</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>1.865897474633354</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>37.5268776364823</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>1.950194521249529</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>0.975609756097561</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>316.9258450191766</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>284.8393924839928</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>269.4457383182676</v>
+      </c>
+      <c r="AQ245" t="n">
+        <v>300.233046649718</v>
+      </c>
+      <c r="AR245" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS245" t="n">
+        <v>309.596740500979</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>548.13</v>
+      </c>
+      <c r="I246" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J246" t="n">
+        <v>183.32108</v>
+      </c>
+      <c r="K246" t="n">
+        <v>63</v>
+      </c>
+      <c r="L246" t="n">
+        <v>62</v>
+      </c>
+      <c r="M246" t="n">
+        <v>97.40377174233491</v>
+      </c>
+      <c r="N246" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O246" t="n">
+        <v>152.7290211827868</v>
+      </c>
+      <c r="P246" t="n">
+        <v>158.0262331102715</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>23.76013302907137</v>
+      </c>
+      <c r="R246" t="n">
+        <v>115.8935800228479</v>
+      </c>
+      <c r="S246" t="n">
+        <v>179.11474609375</v>
+      </c>
+      <c r="T246" t="n">
+        <v>1.287537354264084</v>
+      </c>
+      <c r="U246" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="V246" t="n">
+        <v>291.2372775095814</v>
+      </c>
+      <c r="W246" t="n">
+        <v>569.4822359679176</v>
+      </c>
+      <c r="X246" t="n">
+        <v>456.6597733365325</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>385.6169755796091</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>527.7025710934558</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>346.5218042683152</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>535.5530908203125</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>120.4096928841907</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>121.9660345113502</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>38.93708106705625</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>173.9986912461578</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>1.615719139487246</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>0.9918699186991869</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>215.4492418397148</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>569.4822359679176</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>360.0249817237303</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>243.6031093332321</v>
+      </c>
+      <c r="AQ246" t="n">
+        <v>476.4468541142285</v>
+      </c>
+      <c r="AR246" t="n">
+        <v>225.8025376114755</v>
+      </c>
+      <c r="AS246" t="n">
+        <v>520.2560868260118</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>247.49</v>
+      </c>
+      <c r="I247" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="J247" t="n">
+        <v>29.604069</v>
+      </c>
+      <c r="K247" t="n">
+        <v>67</v>
+      </c>
+      <c r="L247" t="n">
+        <v>62</v>
+      </c>
+      <c r="M247" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N247" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O247" t="n">
+        <v>31.2631458603365</v>
+      </c>
+      <c r="P247" t="n">
+        <v>31.42344643624776</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>2.546642815746941</v>
+      </c>
+      <c r="R247" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S247" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T247" t="n">
+        <v>-0.6514760727644043</v>
+      </c>
+      <c r="U247" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="V247" t="n">
+        <v>227.0099945068359</v>
+      </c>
+      <c r="W247" t="n">
+        <v>307.8042285020049</v>
+      </c>
+      <c r="X247" t="n">
+        <v>261.3598993924131</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>240.0699654527687</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>282.6498333320575</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>238.0339996337891</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>292.0694818259948</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>30.88886784336587</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>29.775454043677</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>2.380508771726309</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>34.5121459098859</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>-0.539716071885822</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>0.4715447154471545</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>227.0099945068359</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>307.8042285020049</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>258.2309351705386</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>238.3298818389067</v>
+      </c>
+      <c r="AQ247" t="n">
+        <v>278.1319885021706</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>238.0679992675781</v>
+      </c>
+      <c r="AS247" t="n">
+        <v>288.5215398066461</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="I248" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="J248" t="n">
+        <v>64.95993</v>
+      </c>
+      <c r="K248" t="n">
+        <v>34</v>
+      </c>
+      <c r="L248" t="n">
+        <v>62</v>
+      </c>
+      <c r="M248" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N248" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O248" t="n">
+        <v>74.94363857678844</v>
+      </c>
+      <c r="P248" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>9.56555110926034</v>
+      </c>
+      <c r="R248" t="n">
+        <v>62.25973272085587</v>
+      </c>
+      <c r="S248" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T248" t="n">
+        <v>-1.043714937357168</v>
+      </c>
+      <c r="U248" t="n">
+        <v>0.2741935483870968</v>
+      </c>
+      <c r="V248" t="n">
+        <v>359.2505113344621</v>
+      </c>
+      <c r="W248" t="n">
+        <v>562.3010416904622</v>
+      </c>
+      <c r="X248" t="n">
+        <v>448.9123950749628</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>391.6147439304934</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>506.2100462194322</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>372.9357989979267</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>500.1276260703164</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>71.06518789230968</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>69.33543207260549</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>8.343188832949277</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>61.7377704233179</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>-0.7317655173041914</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>0.2764227642276423</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>342.5976456015664</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>562.3010416904622</v>
+      </c>
+      <c r="AO248" t="n">
+        <v>425.680475474935</v>
+      </c>
+      <c r="AP248" t="n">
+        <v>375.7047743655688</v>
+      </c>
+      <c r="AQ248" t="n">
+        <v>475.6561765843012</v>
+      </c>
+      <c r="AR248" t="n">
+        <v>369.8092448356742</v>
+      </c>
+      <c r="AS248" t="n">
+        <v>493.354144727324</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>357.33</v>
+      </c>
+      <c r="I249" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J249" t="n">
+        <v>27.235518</v>
+      </c>
+      <c r="K249" t="n">
+        <v>37</v>
+      </c>
+      <c r="L249" t="n">
+        <v>62</v>
+      </c>
+      <c r="M249" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N249" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O249" t="n">
+        <v>28.77094733939274</v>
+      </c>
+      <c r="P249" t="n">
+        <v>28.82570547515613</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>1.708404785024138</v>
+      </c>
+      <c r="R249" t="n">
+        <v>26.81037373255447</v>
+      </c>
+      <c r="S249" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T249" t="n">
+        <v>-0.898750315412545</v>
+      </c>
+      <c r="U249" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="V249" t="n">
+        <v>334.9452961122235</v>
+      </c>
+      <c r="W249" t="n">
+        <v>422.9955833357424</v>
+      </c>
+      <c r="X249" t="n">
+        <v>377.4748290928328</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>355.0605583133161</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>399.8890998723495</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>351.7521033711146</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>409.6170917408649</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>29.04395076764544</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>28.62257203164749</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>2.0080968523495</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>26.82593443846539</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>32.38137131233157</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>-0.9005704906760622</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>0.1626016260162602</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>331.5075848462072</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>446.7016702785662</v>
+      </c>
+      <c r="AO249" t="n">
+        <v>381.0566340715082</v>
+      </c>
+      <c r="AP249" t="n">
+        <v>354.7104033686828</v>
+      </c>
+      <c r="AQ249" t="n">
+        <v>407.4028647743336</v>
+      </c>
+      <c r="AR249" t="n">
+        <v>351.9562598326659</v>
+      </c>
+      <c r="AS249" t="n">
+        <v>424.8435916177901</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>661.04</v>
+      </c>
+      <c r="I250" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="J250" t="n">
+        <v>24.020348</v>
+      </c>
+      <c r="K250" t="n">
+        <v>55</v>
+      </c>
+      <c r="L250" t="n">
+        <v>62</v>
+      </c>
+      <c r="M250" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N250" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O250" t="n">
+        <v>23.07314854736387</v>
+      </c>
+      <c r="P250" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>2.772055640108698</v>
+      </c>
+      <c r="R250" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S250" t="n">
+        <v>28.57799154893039</v>
+      </c>
+      <c r="T250" t="n">
+        <v>0.3416956856605454</v>
+      </c>
+      <c r="U250" t="n">
+        <v>0.7903225806451613</v>
+      </c>
+      <c r="V250" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="W250" t="n">
+        <v>806.6792534722222</v>
+      </c>
+      <c r="X250" t="n">
+        <v>634.9730480234538</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>558.6860768076625</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>711.2600192392451</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>564.5732764204546</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>786.4663274265644</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>25.12473923321306</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>25.32524540861803</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>3.129521483260999</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>28.73427065040975</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>-0.3528946003790572</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>0.4227642276422764</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>864.9762082934226</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>691.4328236980235</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>605.3083924786808</v>
+      </c>
+      <c r="AQ250" t="n">
+        <v>777.5572549173661</v>
+      </c>
+      <c r="AR250" t="n">
+        <v>583.6621980113637</v>
+      </c>
+      <c r="AS250" t="n">
+        <v>790.7671282992762</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="I251" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="J251" t="n">
+        <v>22.953487</v>
+      </c>
+      <c r="K251" t="n">
+        <v>67</v>
+      </c>
+      <c r="L251" t="n">
+        <v>62</v>
+      </c>
+      <c r="M251" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N251" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O251" t="n">
+        <v>24.38031540827067</v>
+      </c>
+      <c r="P251" t="n">
+        <v>24.56339336576916</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>1.526715353570546</v>
+      </c>
+      <c r="R251" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S251" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T251" t="n">
+        <v>-0.9345739563918927</v>
+      </c>
+      <c r="U251" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="V251" t="n">
+        <v>352.1999330248152</v>
+      </c>
+      <c r="W251" t="n">
+        <v>459.6976318904332</v>
+      </c>
+      <c r="X251" t="n">
+        <v>408.8578893966991</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>383.2548729173211</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>434.4609058760773</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>373.7683650588989</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>444.7070531333365</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>25.0726480027028</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>24.80178651355562</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>2.471604230144712</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>22.87476167224703</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>26.89693601225375</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>-0.8574030489415061</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>0.1382113821138211</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>352.1999330248152</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>573.2095572415998</v>
+      </c>
+      <c r="AO251" t="n">
+        <v>420.4683070053259</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>379.0195040657991</v>
+      </c>
+      <c r="AQ251" t="n">
+        <v>461.9171099448528</v>
+      </c>
+      <c r="AR251" t="n">
+        <v>383.6097532435826</v>
+      </c>
+      <c r="AS251" t="n">
+        <v>451.0616169254954</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="I252" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J252" t="n">
+        <v>23.719355</v>
+      </c>
+      <c r="K252" t="n">
+        <v>67</v>
+      </c>
+      <c r="L252" t="n">
+        <v>2</v>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr"/>
+      <c r="T252" t="inlineStr"/>
+      <c r="U252" t="inlineStr"/>
+      <c r="V252" t="inlineStr"/>
+      <c r="W252" t="inlineStr"/>
+      <c r="X252" t="inlineStr"/>
+      <c r="Y252" t="inlineStr"/>
+      <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr"/>
+      <c r="AB252" t="inlineStr"/>
+      <c r="AC252" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>33.23675463771948</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>36.29248999795422</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>9.414973243740455</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>30.11462366156897</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>39.26719333814537</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>-1.010879095598824</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>0.07936507936507936</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO252" t="n">
+        <v>103.0339393769304</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>73.84752232133498</v>
+      </c>
+      <c r="AQ252" t="n">
+        <v>132.2203564325258</v>
+      </c>
+      <c r="AR252" t="n">
+        <v>93.35533335086382</v>
+      </c>
+      <c r="AS252" t="n">
+        <v>121.7282993482506</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:22:36</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="I253" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J253" t="n">
+        <v>32.434914</v>
+      </c>
+      <c r="K253" t="n">
+        <v>65</v>
+      </c>
+      <c r="L253" t="n">
+        <v>62</v>
+      </c>
+      <c r="M253" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N253" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O253" t="n">
+        <v>36.21504570105553</v>
+      </c>
+      <c r="P253" t="n">
+        <v>32.93951014099588</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>5.759623065888312</v>
+      </c>
+      <c r="R253" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S253" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T253" t="n">
+        <v>-0.6563158140406047</v>
+      </c>
+      <c r="U253" t="n">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="V253" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W253" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X253" t="n">
+        <v>236.4842484278926</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>198.8739098076419</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>274.0945870481433</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>197.7220016479492</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>96</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>36.43137937054528</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>36.27142925651706</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>4.693255359422203</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>30.66692147831822</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>43.33367328254543</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>-0.8515337573784381</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>237.8969072896607</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>207.2499497926337</v>
+      </c>
+      <c r="AQ253" t="n">
+        <v>268.5438647866877</v>
+      </c>
+      <c r="AR253" t="n">
+        <v>200.254997253418</v>
+      </c>
+      <c r="AS253" t="n">
+        <v>282.9688865350217</v>
       </c>
     </row>
   </sheetData>
@@ -36973,12 +38300,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -37007,13 +38334,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>350.67</v>
+        <v>357.33</v>
       </c>
       <c r="I2" t="n">
-        <v>13.1</v>
+        <v>13.12</v>
       </c>
       <c r="J2" t="n">
-        <v>26.768703</v>
+        <v>27.235518</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -37028,13 +38355,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.82457073369382</v>
+        <v>28.77094733939274</v>
       </c>
       <c r="P2" t="n">
-        <v>28.94813194245805</v>
+        <v>28.82570547515613</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.712256124281385</v>
+        <v>1.708404785024138</v>
       </c>
       <c r="R2" t="n">
         <v>26.81037373255447</v>
@@ -37043,31 +38370,31 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.200677693330864</v>
+        <v>-0.898750315412545</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="V2" t="n">
-        <v>334.434708770589</v>
+        <v>334.9452961122235</v>
       </c>
       <c r="W2" t="n">
-        <v>422.3507729952915</v>
+        <v>422.9955833357424</v>
       </c>
       <c r="X2" t="n">
-        <v>377.601876611389</v>
+        <v>377.4748290928328</v>
       </c>
       <c r="Y2" t="n">
-        <v>355.1713213833029</v>
+        <v>355.0605583133161</v>
       </c>
       <c r="Z2" t="n">
-        <v>400.0324318394752</v>
+        <v>399.8890998723495</v>
       </c>
       <c r="AA2" t="n">
-        <v>351.2158958964635</v>
+        <v>351.7521033711146</v>
       </c>
       <c r="AB2" t="n">
-        <v>408.9926754424794</v>
+        <v>409.6170917408649</v>
       </c>
       <c r="AC2" t="n">
         <v>123</v>
@@ -37079,57 +38406,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.09226878046618</v>
+        <v>29.04395076764544</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.71319547488797</v>
+        <v>28.62257203164749</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.036036407113766</v>
+        <v>2.0080968523495</v>
       </c>
       <c r="AI2" t="n">
         <v>26.82593443846539</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.42053258807379</v>
+        <v>32.38137131233157</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1.14122015320935</v>
+        <v>-0.9005704906760622</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.08943089430894309</v>
+        <v>0.1626016260162602</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.002237918088</v>
+        <v>331.5075848462072</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.0207226104586</v>
+        <v>446.7016702785662</v>
       </c>
       <c r="AO2" t="n">
-        <v>381.108721024107</v>
+        <v>381.0566340715082</v>
       </c>
       <c r="AP2" t="n">
-        <v>354.4366440909167</v>
+        <v>354.7104033686828</v>
       </c>
       <c r="AQ2" t="n">
-        <v>407.7807979572974</v>
+        <v>407.4028647743336</v>
       </c>
       <c r="AR2" t="n">
-        <v>351.4197411438966</v>
+        <v>351.9562598326659</v>
       </c>
       <c r="AS2" t="n">
-        <v>424.7089769037667</v>
+        <v>424.8435916177901</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -37158,13 +38485,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>390.99</v>
+        <v>384.93</v>
       </c>
       <c r="I3" t="n">
-        <v>16.79</v>
+        <v>16.77</v>
       </c>
       <c r="J3" t="n">
-        <v>23.287073</v>
+        <v>22.953487</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -37179,13 +38506,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.40728702089413</v>
+        <v>24.38031540827067</v>
       </c>
       <c r="P3" t="n">
-        <v>24.57421541107486</v>
+        <v>24.56339336576916</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.515086151785492</v>
+        <v>1.526715353570546</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -37194,31 +38521,31 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.739373150215907</v>
+        <v>-0.9345739563918927</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="V3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.1999330248152</v>
       </c>
       <c r="W3" t="n">
-        <v>460.2458699725923</v>
+        <v>459.6976318904332</v>
       </c>
       <c r="X3" t="n">
-        <v>409.7983490808125</v>
+        <v>408.8578893966991</v>
       </c>
       <c r="Y3" t="n">
-        <v>384.3600525923341</v>
+        <v>383.2548729173211</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.2366455692909</v>
+        <v>434.4609058760773</v>
       </c>
       <c r="AA3" t="n">
-        <v>374.2141233952839</v>
+        <v>373.7683650588989</v>
       </c>
       <c r="AB3" t="n">
-        <v>445.2374133636685</v>
+        <v>444.7070531333365</v>
       </c>
       <c r="AC3" t="n">
         <v>123</v>
@@ -37230,57 +38557,57 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.15200029139151</v>
+        <v>25.0726480027028</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.81926112267433</v>
+        <v>24.80178651355562</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.556891985278869</v>
+        <v>2.471604230144712</v>
       </c>
       <c r="AI3" t="n">
         <v>22.87476167224703</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27.04152673240599</v>
+        <v>26.89693601225375</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.7293727314758328</v>
+        <v>-0.8574030489415061</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2195121951219512</v>
+        <v>0.1382113821138211</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.6199687231154</v>
+        <v>352.1999330248152</v>
       </c>
       <c r="AN3" t="n">
-        <v>573.8931703092702</v>
+        <v>573.2095572415998</v>
       </c>
       <c r="AO3" t="n">
-        <v>422.3020848924635</v>
+        <v>420.4683070053259</v>
       </c>
       <c r="AP3" t="n">
-        <v>379.3718684596312</v>
+        <v>379.0195040657991</v>
       </c>
       <c r="AQ3" t="n">
-        <v>465.2323013252957</v>
+        <v>461.9171099448528</v>
       </c>
       <c r="AR3" t="n">
-        <v>384.0672484770275</v>
+        <v>383.6097532435826</v>
       </c>
       <c r="AS3" t="n">
-        <v>454.0272338370966</v>
+        <v>451.0616169254954</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -37309,13 +38636,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>656.73</v>
+        <v>661.04</v>
       </c>
       <c r="I4" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="J4" t="n">
-        <v>23.88109</v>
+        <v>24.020348</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -37330,13 +38657,13 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.1403299560018</v>
+        <v>23.07314854736387</v>
       </c>
       <c r="P4" t="n">
         <v>22.19399968927557</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.845322499107136</v>
+        <v>2.772055640108698</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
@@ -37345,31 +38672,31 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2603430873760875</v>
+        <v>0.3416956856605454</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7903225806451613</v>
       </c>
       <c r="V4" t="n">
-        <v>542.8699951171875</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="W4" t="n">
-        <v>806.0930040147568</v>
+        <v>806.6792534722222</v>
       </c>
       <c r="X4" t="n">
-        <v>636.3590737900496</v>
+        <v>634.9730480234538</v>
       </c>
       <c r="Y4" t="n">
-        <v>558.1127050646033</v>
+        <v>558.6860768076625</v>
       </c>
       <c r="Z4" t="n">
-        <v>714.6054425154958</v>
+        <v>711.2600192392451</v>
       </c>
       <c r="AA4" t="n">
-        <v>564.1629760742187</v>
+        <v>564.5732764204546</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.8947675955858</v>
+        <v>786.4663274265644</v>
       </c>
       <c r="AC4" t="n">
         <v>123</v>
@@ -37381,13 +38708,13 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.15093195827638</v>
+        <v>25.12473923321306</v>
       </c>
       <c r="AG4" t="n">
-        <v>25.7156235657128</v>
+        <v>25.32524540861803</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.133829023683002</v>
+        <v>3.129521483260999</v>
       </c>
       <c r="AI4" t="n">
         <v>21.20865545099432</v>
@@ -37396,42 +38723,42 @@
         <v>28.73427065040975</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.4052046071052107</v>
+        <v>-0.3528946003790572</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4227642276422764</v>
       </c>
       <c r="AM4" t="n">
-        <v>542.8699951171875</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.3475918629769</v>
+        <v>864.9762082934226</v>
       </c>
       <c r="AO4" t="n">
-        <v>691.6506288526003</v>
+        <v>691.4328236980235</v>
       </c>
       <c r="AP4" t="n">
-        <v>605.4703307013178</v>
+        <v>605.3083924786808</v>
       </c>
       <c r="AQ4" t="n">
-        <v>777.8309270038829</v>
+        <v>777.5572549173661</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.2380249023437</v>
+        <v>583.6621980113637</v>
       </c>
       <c r="AS4" t="n">
-        <v>790.1924428862681</v>
+        <v>790.7671282992762</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -37460,13 +38787,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>247.31</v>
+        <v>247.49</v>
       </c>
       <c r="I5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>29.547192</v>
+        <v>29.604069</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -37481,13 +38808,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.34583547043713</v>
+        <v>31.2631458603365</v>
       </c>
       <c r="P5" t="n">
-        <v>31.63875598086125</v>
+        <v>31.42344643624776</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.574964858953528</v>
+        <v>2.546642815746941</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -37496,31 +38823,31 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6985118512134212</v>
+        <v>-0.6514760727644043</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="V5" t="n">
-        <v>227.2815375624661</v>
+        <v>227.0099945068359</v>
       </c>
       <c r="W5" t="n">
-        <v>308.1724153782034</v>
+        <v>307.8042285020049</v>
       </c>
       <c r="X5" t="n">
-        <v>262.3646428875588</v>
+        <v>261.3598993924131</v>
       </c>
       <c r="Y5" t="n">
-        <v>240.8121870181178</v>
+        <v>240.0699654527687</v>
       </c>
       <c r="Z5" t="n">
-        <v>283.9170987569998</v>
+        <v>282.6498333320575</v>
       </c>
       <c r="AA5" t="n">
-        <v>238.3187292984228</v>
+        <v>238.0339996337891</v>
       </c>
       <c r="AB5" t="n">
-        <v>292.4188472348776</v>
+        <v>292.0694818259948</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -37532,13 +38859,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>30.91993347538324</v>
+        <v>30.88886784336587</v>
       </c>
       <c r="AG5" t="n">
-        <v>29.81450547733067</v>
+        <v>29.775454043677</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.388523702572737</v>
+        <v>2.380508771726309</v>
       </c>
       <c r="AI5" t="n">
         <v>28.4770334052127</v>
@@ -37547,42 +38874,42 @@
         <v>34.5121459098859</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.5747238237178148</v>
+        <v>-0.539716071885822</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4471544715447154</v>
+        <v>0.4715447154471545</v>
       </c>
       <c r="AM5" t="n">
-        <v>227.2815375624661</v>
+        <v>227.0099945068359</v>
       </c>
       <c r="AN5" t="n">
-        <v>308.1724153782034</v>
+        <v>307.8042285020049</v>
       </c>
       <c r="AO5" t="n">
-        <v>258.7998431889577</v>
+        <v>258.2309351705386</v>
       </c>
       <c r="AP5" t="n">
-        <v>238.8078997984238</v>
+        <v>238.3298818389067</v>
       </c>
       <c r="AQ5" t="n">
-        <v>278.7917865794915</v>
+        <v>278.1319885021706</v>
       </c>
       <c r="AR5" t="n">
-        <v>238.3527696016303</v>
+        <v>238.0679992675781</v>
       </c>
       <c r="AS5" t="n">
-        <v>288.866661265745</v>
+        <v>288.5215398066461</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -37611,13 +38938,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>317.31</v>
+        <v>314.86</v>
       </c>
       <c r="I6" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>38.415253</v>
+        <v>38.16485</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -37626,52 +38953,52 @@
         <v>62</v>
       </c>
       <c r="M6" t="n">
-        <v>32.7632894395273</v>
+        <v>33.31113727560344</v>
       </c>
       <c r="N6" t="n">
         <v>38.41525394171838</v>
       </c>
       <c r="O6" t="n">
-        <v>35.7711349428061</v>
+        <v>35.8575116017553</v>
       </c>
       <c r="P6" t="n">
-        <v>35.74031432662115</v>
+        <v>35.80992839526899</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.506070683051228</v>
+        <v>1.484147167761942</v>
       </c>
       <c r="R6" t="n">
-        <v>33.87873912213476</v>
+        <v>33.93462617518539</v>
       </c>
       <c r="S6" t="n">
-        <v>37.82869352844091</v>
+        <v>37.8504847787483</v>
       </c>
       <c r="T6" t="n">
-        <v>1.755640081803493</v>
+        <v>1.554656066705375</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9516129032258065</v>
       </c>
       <c r="V6" t="n">
-        <v>270.6247707704955</v>
+        <v>274.8168825237283</v>
       </c>
       <c r="W6" t="n">
-        <v>317.3099975585938</v>
+        <v>316.9258450191766</v>
       </c>
       <c r="X6" t="n">
-        <v>295.4695746275784</v>
+        <v>295.8244707144812</v>
       </c>
       <c r="Y6" t="n">
-        <v>283.0294307855752</v>
+        <v>283.5802565804452</v>
       </c>
       <c r="Z6" t="n">
-        <v>307.9097184695815</v>
+        <v>308.0686848485172</v>
       </c>
       <c r="AA6" t="n">
-        <v>279.8383851488331</v>
+        <v>279.9606659452795</v>
       </c>
       <c r="AB6" t="n">
-        <v>312.4650085449219</v>
+        <v>312.2664994246734</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -37683,57 +39010,57 @@
         <v>38.41525394171838</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.49938974455982</v>
+        <v>34.5259869677567</v>
       </c>
       <c r="AG6" t="n">
         <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.837364774767286</v>
+        <v>1.865897474633354</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.38280954430236</v>
+        <v>37.5268776364823</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.131238885831012</v>
+        <v>1.950194521249529</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.9918699186991869</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="AM6" t="n">
-        <v>257.8688405483584</v>
+        <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>317.3099975585938</v>
+        <v>316.9258450191766</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.9649592900641</v>
+        <v>284.8393924839928</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.7883262504863</v>
+        <v>269.4457383182676</v>
       </c>
       <c r="AQ6" t="n">
-        <v>300.1415923296419</v>
+        <v>300.233046649718</v>
       </c>
       <c r="AR6" t="n">
-        <v>265.4471175413494</v>
+        <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>308.7820068359375</v>
+        <v>309.596740500979</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -37762,13 +39089,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>203.53</v>
+        <v>211.8</v>
       </c>
       <c r="I7" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="J7" t="n">
-        <v>31.120794</v>
+        <v>32.434914</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -37783,13 +39110,13 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.33874189897329</v>
+        <v>36.21504570105553</v>
       </c>
       <c r="P7" t="n">
-        <v>33.23047515261592</v>
+        <v>32.93951014099588</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.759461632523198</v>
+        <v>5.759623065888312</v>
       </c>
       <c r="R7" t="n">
         <v>30.27902016048226</v>
@@ -37798,34 +39125,34 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9059784111605109</v>
+        <v>-0.6563158140406047</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="V7" t="n">
-        <v>192.8248379811028</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="W7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="X7" t="n">
-        <v>237.6553720192853</v>
+        <v>236.4842484278926</v>
       </c>
       <c r="Y7" t="n">
-        <v>199.9884929425836</v>
+        <v>198.8739098076419</v>
       </c>
       <c r="Z7" t="n">
-        <v>275.322251095987</v>
+        <v>274.0945870481433</v>
       </c>
       <c r="AA7" t="n">
-        <v>198.024791849554</v>
+        <v>197.7220016479492</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.5075091365892</v>
+        <v>292.0602499483069</v>
       </c>
       <c r="AC7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -37834,57 +39161,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.47344740349104</v>
+        <v>36.43137937054528</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.28979741310587</v>
+        <v>36.27142925651706</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.699922494426534</v>
+        <v>4.693255359422203</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.66186785150267</v>
+        <v>30.66692147831822</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.36775487783004</v>
+        <v>43.33367328254543</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.138881207049383</v>
+        <v>-0.8515337573784381</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1263157894736842</v>
+        <v>0.2604166666666667</v>
       </c>
       <c r="AM7" t="n">
-        <v>192.8248379811028</v>
+        <v>192.5299987792968</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.64074202557</v>
+        <v>314.1596399735431</v>
       </c>
       <c r="AO7" t="n">
-        <v>238.5363460188314</v>
+        <v>237.8969072896607</v>
       </c>
       <c r="AP7" t="n">
-        <v>207.7988529052818</v>
+        <v>207.2499497926337</v>
       </c>
       <c r="AQ7" t="n">
-        <v>269.2738391323809</v>
+        <v>268.5438647866877</v>
       </c>
       <c r="AR7" t="n">
-        <v>200.5286157488275</v>
+        <v>200.254997253418</v>
       </c>
       <c r="AS7" t="n">
-        <v>283.6251169010084</v>
+        <v>282.9688865350217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -37913,13 +39240,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>534.39</v>
+        <v>548.13</v>
       </c>
       <c r="I8" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="J8" t="n">
-        <v>177.53821</v>
+        <v>183.32108</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -37928,52 +39255,52 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>96.25283295253539</v>
+        <v>97.40377174233491</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>151.3828611384844</v>
+        <v>152.7290211827868</v>
       </c>
       <c r="P8" t="n">
-        <v>154.5934458247951</v>
+        <v>158.0262331102715</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.5571117805376</v>
+        <v>23.76013302907137</v>
       </c>
       <c r="R8" t="n">
-        <v>114.5837701761498</v>
+        <v>115.8935800228479</v>
       </c>
       <c r="S8" t="n">
-        <v>177.8216452676742</v>
+        <v>179.11474609375</v>
       </c>
       <c r="T8" t="n">
-        <v>1.065082453313776</v>
+        <v>1.287537354264084</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8870967741935484</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="V8" t="n">
-        <v>289.7210271871315</v>
+        <v>291.2372775095814</v>
       </c>
       <c r="W8" t="n">
-        <v>573.2914816934554</v>
+        <v>569.4822359679176</v>
       </c>
       <c r="X8" t="n">
-        <v>455.662412026838</v>
+        <v>456.6597733365325</v>
       </c>
       <c r="Y8" t="n">
-        <v>381.7455055674197</v>
+        <v>385.6169755796091</v>
       </c>
       <c r="Z8" t="n">
-        <v>529.5793184862562</v>
+        <v>527.7025710934558</v>
       </c>
       <c r="AA8" t="n">
-        <v>344.8971482302108</v>
+        <v>346.5218042683152</v>
       </c>
       <c r="AB8" t="n">
-        <v>535.2431522556993</v>
+        <v>535.5530908203125</v>
       </c>
       <c r="AC8" t="n">
         <v>123</v>
@@ -37985,57 +39312,57 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>119.844107766781</v>
+        <v>120.4096928841907</v>
       </c>
       <c r="AG8" t="n">
-        <v>121.3152730406211</v>
+        <v>121.9660345113502</v>
       </c>
       <c r="AH8" t="n">
-        <v>38.57211859517521</v>
+        <v>38.93708106705625</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>171.4347584208504</v>
+        <v>173.9986912461578</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.495746262701672</v>
+        <v>1.615719139487246</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.943089430894309</v>
+        <v>0.9918699186991869</v>
       </c>
       <c r="AM8" t="n">
-        <v>216.8903738921543</v>
+        <v>215.4492418397148</v>
       </c>
       <c r="AN8" t="n">
-        <v>573.2914816934554</v>
+        <v>569.4822359679176</v>
       </c>
       <c r="AO8" t="n">
-        <v>360.7307643780109</v>
+        <v>360.0249817237303</v>
       </c>
       <c r="AP8" t="n">
-        <v>244.6286874065335</v>
+        <v>243.6031093332321</v>
       </c>
       <c r="AQ8" t="n">
-        <v>476.8328413494882</v>
+        <v>476.4468541142285</v>
       </c>
       <c r="AR8" t="n">
-        <v>227.3129224784419</v>
+        <v>225.8025376114755</v>
       </c>
       <c r="AS8" t="n">
-        <v>516.0186228467597</v>
+        <v>520.2560868260118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38064,13 +39391,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>384.05</v>
+        <v>389.11</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="J9" t="n">
-        <v>64.00833</v>
+        <v>64.95993</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -38085,13 +39412,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>75.09657990997806</v>
+        <v>74.94363857678844</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.475172797189035</v>
+        <v>9.56555110926034</v>
       </c>
       <c r="R9" t="n">
         <v>62.25973272085587</v>
@@ -38100,31 +39427,31 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.170242500829913</v>
+        <v>-1.043714937357168</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="V9" t="n">
-        <v>359.8502617707467</v>
+        <v>359.2505113344621</v>
       </c>
       <c r="W9" t="n">
-        <v>563.2397746482092</v>
+        <v>562.3010416904622</v>
       </c>
       <c r="X9" t="n">
-        <v>450.5794794598684</v>
+        <v>448.9123950749628</v>
       </c>
       <c r="Y9" t="n">
-        <v>393.7284426767342</v>
+        <v>391.6147439304934</v>
       </c>
       <c r="Z9" t="n">
-        <v>507.4305162430026</v>
+        <v>506.2100462194322</v>
       </c>
       <c r="AA9" t="n">
-        <v>373.5583963251352</v>
+        <v>372.9357989979267</v>
       </c>
       <c r="AB9" t="n">
-        <v>500.9625636764438</v>
+        <v>500.1276260703164</v>
       </c>
       <c r="AC9" t="n">
         <v>123</v>
@@ -38136,13 +39463,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.11813106554642</v>
+        <v>71.06518789230968</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.41509126867139</v>
+        <v>69.33543207260549</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.323384333990594</v>
+        <v>8.343188832949277</v>
       </c>
       <c r="AI9" t="n">
         <v>61.7377704233179</v>
@@ -38151,42 +39478,42 @@
         <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.8541959352413649</v>
+        <v>-0.7317655173041914</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.2764227642276423</v>
       </c>
       <c r="AM9" t="n">
-        <v>343.1695949264438</v>
+        <v>342.5976456015664</v>
       </c>
       <c r="AN9" t="n">
-        <v>563.2397746482092</v>
+        <v>562.3010416904622</v>
       </c>
       <c r="AO9" t="n">
-        <v>426.7087863932785</v>
+        <v>425.680475474935</v>
       </c>
       <c r="AP9" t="n">
-        <v>376.768480389335</v>
+        <v>375.7047743655688</v>
       </c>
       <c r="AQ9" t="n">
-        <v>476.649092397222</v>
+        <v>475.6561765843012</v>
       </c>
       <c r="AR9" t="n">
-        <v>370.4266225399074</v>
+        <v>369.8092448356742</v>
       </c>
       <c r="AS9" t="n">
-        <v>494.1777743512428</v>
+        <v>493.354144727324</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-13 16:23:50</t>
+          <t>2026-07-14 16:22:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38215,19 +39542,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.83</v>
+        <v>73.53</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.81613</v>
+        <v>23.719355</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -38246,7 +39573,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -38255,25 +39582,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>32.77522457364311</v>
+        <v>33.23675463771948</v>
       </c>
       <c r="AG10" t="n">
-        <v>36.27667935940586</v>
+        <v>36.29248999795422</v>
       </c>
       <c r="AH10" t="n">
-        <v>10.04327385547198</v>
+        <v>9.414973243740455</v>
       </c>
       <c r="AI10" t="n">
-        <v>30.00316182615256</v>
+        <v>30.11462366156897</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.25849763772231</v>
+        <v>39.26719333814537</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.8920492164775371</v>
+        <v>-1.010879095598824</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.09375</v>
+        <v>0.07936507936507936</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -38282,19 +39609,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>101.6031961782937</v>
+        <v>103.0339393769304</v>
       </c>
       <c r="AP10" t="n">
-        <v>70.46904722633052</v>
+        <v>73.84752232133498</v>
       </c>
       <c r="AQ10" t="n">
-        <v>132.7373451302568</v>
+        <v>132.2203564325258</v>
       </c>
       <c r="AR10" t="n">
-        <v>93.00980166107296</v>
+        <v>93.35533335086382</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.7013426769392</v>
+        <v>121.7282993482506</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS253"/>
+  <dimension ref="A1:AS262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36714,7 +36714,7 @@
         <v>314.64074202557</v>
       </c>
       <c r="AO244" t="n">
-        <v>238.5363460188314</v>
+        <v>238.5363460188313</v>
       </c>
       <c r="AP244" t="n">
         <v>207.7988529052818</v>
@@ -36805,7 +36805,7 @@
         <v>1.554656066705375</v>
       </c>
       <c r="U245" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9516129032258064</v>
       </c>
       <c r="V245" t="n">
         <v>274.8168825237283</v>
@@ -36932,7 +36932,7 @@
         <v>62</v>
       </c>
       <c r="M246" t="n">
-        <v>97.40377174233491</v>
+        <v>97.40377174233492</v>
       </c>
       <c r="N246" t="n">
         <v>190.4622862768955</v>
@@ -36956,7 +36956,7 @@
         <v>1.287537354264084</v>
       </c>
       <c r="U246" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9838709677419356</v>
       </c>
       <c r="V246" t="n">
         <v>291.2372775095814</v>
@@ -37025,7 +37025,7 @@
         <v>476.4468541142285</v>
       </c>
       <c r="AR246" t="n">
-        <v>225.8025376114755</v>
+        <v>225.8025376114756</v>
       </c>
       <c r="AS246" t="n">
         <v>520.2560868260118</v>
@@ -37237,7 +37237,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N248" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O248" t="n">
         <v>74.94363857678844</v>
@@ -37258,7 +37258,7 @@
         <v>-1.043714937357168</v>
       </c>
       <c r="U248" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.2741935483870967</v>
       </c>
       <c r="V248" t="n">
         <v>359.2505113344621</v>
@@ -37288,7 +37288,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE248" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF248" t="n">
         <v>71.06518789230968</v>
@@ -37300,7 +37300,7 @@
         <v>8.343188832949277</v>
       </c>
       <c r="AI248" t="n">
-        <v>61.7377704233179</v>
+        <v>61.73777042331791</v>
       </c>
       <c r="AJ248" t="n">
         <v>82.36296239187379</v>
@@ -37460,7 +37460,7 @@
         <v>-0.9005704906760622</v>
       </c>
       <c r="AL249" t="n">
-        <v>0.1626016260162602</v>
+        <v>0.1626016260162601</v>
       </c>
       <c r="AM249" t="n">
         <v>331.5075848462072</v>
@@ -37557,7 +37557,7 @@
         <v>28.57799154893039</v>
       </c>
       <c r="T250" t="n">
-        <v>0.3416956856605454</v>
+        <v>0.3416956856605453</v>
       </c>
       <c r="U250" t="n">
         <v>0.7903225806451613</v>
@@ -37708,7 +37708,7 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T251" t="n">
-        <v>-0.9345739563918927</v>
+        <v>-0.9345739563918928</v>
       </c>
       <c r="U251" t="n">
         <v>0.2258064516129032</v>
@@ -37720,7 +37720,7 @@
         <v>459.6976318904332</v>
       </c>
       <c r="X251" t="n">
-        <v>408.8578893966991</v>
+        <v>408.8578893966992</v>
       </c>
       <c r="Y251" t="n">
         <v>383.2548729173211</v>
@@ -37857,7 +37857,7 @@
         <v>63</v>
       </c>
       <c r="AD252" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE252" t="n">
         <v>42.60474344487245</v>
@@ -37881,7 +37881,7 @@
         <v>-1.010879095598824</v>
       </c>
       <c r="AL252" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.07936507936507931</v>
       </c>
       <c r="AM252" t="n">
         <v>10.81762752038992</v>
@@ -37990,7 +37990,7 @@
         <v>314.1596399735431</v>
       </c>
       <c r="X253" t="n">
-        <v>236.4842484278926</v>
+        <v>236.4842484278927</v>
       </c>
       <c r="Y253" t="n">
         <v>198.8739098076419</v>
@@ -38054,6 +38054,1333 @@
       </c>
       <c r="AS253" t="n">
         <v>282.9688865350217</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="I254" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J254" t="n">
+        <v>39.696968</v>
+      </c>
+      <c r="K254" t="n">
+        <v>67</v>
+      </c>
+      <c r="L254" t="n">
+        <v>62</v>
+      </c>
+      <c r="M254" t="n">
+        <v>33.31113727560344</v>
+      </c>
+      <c r="N254" t="n">
+        <v>39.64891041162227</v>
+      </c>
+      <c r="O254" t="n">
+        <v>35.95305345470759</v>
+      </c>
+      <c r="P254" t="n">
+        <v>35.85774973576063</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>1.534450055593982</v>
+      </c>
+      <c r="R254" t="n">
+        <v>34.11793547763685</v>
+      </c>
+      <c r="S254" t="n">
+        <v>37.93184183411679</v>
+      </c>
+      <c r="T254" t="n">
+        <v>2.439906422267456</v>
+      </c>
+      <c r="U254" t="n">
+        <v>1</v>
+      </c>
+      <c r="V254" t="n">
+        <v>274.8168825237283</v>
+      </c>
+      <c r="W254" t="n">
+        <v>327.1035108958837</v>
+      </c>
+      <c r="X254" t="n">
+        <v>296.6126910013376</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>283.9534780426873</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>309.2719039599879</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>281.472967690504</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>312.9376951314635</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>39.64891041162227</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>34.56693258581248</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>34.35593205560495</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>1.922222460951787</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>37.60048485264074</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>2.668804219282395</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>327.1035108958837</v>
+      </c>
+      <c r="AO254" t="n">
+        <v>285.177193832953</v>
+      </c>
+      <c r="AP254" t="n">
+        <v>269.3188585301007</v>
+      </c>
+      <c r="AQ254" t="n">
+        <v>301.0355291358052</v>
+      </c>
+      <c r="AR254" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS254" t="n">
+        <v>310.2040000342861</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>529.14</v>
+      </c>
+      <c r="I255" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J255" t="n">
+        <v>175.79402</v>
+      </c>
+      <c r="K255" t="n">
+        <v>63</v>
+      </c>
+      <c r="L255" t="n">
+        <v>62</v>
+      </c>
+      <c r="M255" t="n">
+        <v>103.754721587559</v>
+      </c>
+      <c r="N255" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O255" t="n">
+        <v>153.9561946932803</v>
+      </c>
+      <c r="P255" t="n">
+        <v>160.4557375048028</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>22.80130998949041</v>
+      </c>
+      <c r="R255" t="n">
+        <v>122.3969784142836</v>
+      </c>
+      <c r="S255" t="n">
+        <v>179.11474609375</v>
+      </c>
+      <c r="T255" t="n">
+        <v>0.9577443277068394</v>
+      </c>
+      <c r="U255" t="n">
+        <v>0.8225806451612904</v>
+      </c>
+      <c r="V255" t="n">
+        <v>312.3017119785525</v>
+      </c>
+      <c r="W255" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="X255" t="n">
+        <v>463.4081460267735</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>394.7762029584074</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>532.0400890951397</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>368.4149050269937</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>539.1353857421875</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>120.9073568535075</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>123.0541886954472</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>39.22240982201477</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>174.3881996029713</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>1.399369987605547</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>0.9105691056910569</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>216.8903738921543</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="AO255" t="n">
+        <v>363.9311441290575</v>
+      </c>
+      <c r="AP255" t="n">
+        <v>245.8716905647931</v>
+      </c>
+      <c r="AQ255" t="n">
+        <v>481.990597693322</v>
+      </c>
+      <c r="AR255" t="n">
+        <v>227.3129224784419</v>
+      </c>
+      <c r="AS255" t="n">
+        <v>524.9084808049437</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>254.96</v>
+      </c>
+      <c r="I256" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="J256" t="n">
+        <v>30.461172</v>
+      </c>
+      <c r="K256" t="n">
+        <v>67</v>
+      </c>
+      <c r="L256" t="n">
+        <v>62</v>
+      </c>
+      <c r="M256" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N256" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O256" t="n">
+        <v>31.19603795699403</v>
+      </c>
+      <c r="P256" t="n">
+        <v>31.13636400140644</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>2.510269199223419</v>
+      </c>
+      <c r="R256" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S256" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T256" t="n">
+        <v>-0.2927438846882892</v>
+      </c>
+      <c r="U256" t="n">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="V256" t="n">
+        <v>227.2815375624661</v>
+      </c>
+      <c r="W256" t="n">
+        <v>308.1724153782034</v>
+      </c>
+      <c r="X256" t="n">
+        <v>261.11083770004</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>240.09988450254</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>282.12179089754</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>238.3187292984228</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>292.4188472348776</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>30.86330984787999</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>29.775454043677</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>2.36755643114337</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>34.5121459098859</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>-0.1698535429146186</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>0.5528455284552846</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>227.2815375624661</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>308.1724153782034</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>258.3259034267555</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>238.5094560980855</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>278.1423507554255</v>
+      </c>
+      <c r="AR256" t="n">
+        <v>238.3527696016303</v>
+      </c>
+      <c r="AS256" t="n">
+        <v>288.866661265745</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>394.28</v>
+      </c>
+      <c r="I257" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="J257" t="n">
+        <v>65.823044</v>
+      </c>
+      <c r="K257" t="n">
+        <v>34</v>
+      </c>
+      <c r="L257" t="n">
+        <v>62</v>
+      </c>
+      <c r="M257" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N257" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O257" t="n">
+        <v>74.75445566662759</v>
+      </c>
+      <c r="P257" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>9.633263064441762</v>
+      </c>
+      <c r="R257" t="n">
+        <v>62.25973272085587</v>
+      </c>
+      <c r="S257" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T257" t="n">
+        <v>-0.9271429220691757</v>
+      </c>
+      <c r="U257" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="V257" t="n">
+        <v>359.2505113344621</v>
+      </c>
+      <c r="W257" t="n">
+        <v>562.3010416904622</v>
+      </c>
+      <c r="X257" t="n">
+        <v>447.7791894430993</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>390.0759436870931</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>505.4824351991055</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>372.9357989979267</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>500.1276260703164</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>71.01390371148848</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>69.28302117113797</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>8.357316288336976</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>61.7377704233179</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>-0.6211156228145358</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>0.3495934959349594</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>342.5976456015664</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>562.3010416904622</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>425.373283231816</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>375.3129586646775</v>
+      </c>
+      <c r="AQ257" t="n">
+        <v>475.4336077989545</v>
+      </c>
+      <c r="AR257" t="n">
+        <v>369.8092448356742</v>
+      </c>
+      <c r="AS257" t="n">
+        <v>493.354144727324</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="I258" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J258" t="n">
+        <v>28.238749</v>
+      </c>
+      <c r="K258" t="n">
+        <v>37</v>
+      </c>
+      <c r="L258" t="n">
+        <v>62</v>
+      </c>
+      <c r="M258" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N258" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O258" t="n">
+        <v>28.72736593168552</v>
+      </c>
+      <c r="P258" t="n">
+        <v>28.56636076460896</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>1.686468307005828</v>
+      </c>
+      <c r="R258" t="n">
+        <v>26.81037373255447</v>
+      </c>
+      <c r="S258" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T258" t="n">
+        <v>-0.2897279063328614</v>
+      </c>
+      <c r="U258" t="n">
+        <v>0.4677419354838709</v>
+      </c>
+      <c r="V258" t="n">
+        <v>334.6900024414062</v>
+      </c>
+      <c r="W258" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X258" t="n">
+        <v>376.6157673643972</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>354.5061678595508</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>398.7253668692436</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>351.483999633789</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>29.0061483114272</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>28.61887096366212</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>1.97868076721291</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>26.82593443846539</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>32.22164581044751</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>-0.3878338154103216</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>0.4146341463414634</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO258" t="n">
+        <v>380.2706043628106</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>354.3300995046494</v>
+      </c>
+      <c r="AQ258" t="n">
+        <v>406.2111092209719</v>
+      </c>
+      <c r="AR258" t="n">
+        <v>351.6880004882812</v>
+      </c>
+      <c r="AS258" t="n">
+        <v>422.4257765749668</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>681.3099999999999</v>
+      </c>
+      <c r="I259" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J259" t="n">
+        <v>24.774908</v>
+      </c>
+      <c r="K259" t="n">
+        <v>55</v>
+      </c>
+      <c r="L259" t="n">
+        <v>62</v>
+      </c>
+      <c r="M259" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N259" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O259" t="n">
+        <v>23.01161419188674</v>
+      </c>
+      <c r="P259" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>2.688673837079926</v>
+      </c>
+      <c r="R259" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S259" t="n">
+        <v>28.55389422485299</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0.655822875871144</v>
+      </c>
+      <c r="U259" t="n">
+        <v>0.8225806451612904</v>
+      </c>
+      <c r="V259" t="n">
+        <v>542.8699951171875</v>
+      </c>
+      <c r="W259" t="n">
+        <v>806.0930040147568</v>
+      </c>
+      <c r="X259" t="n">
+        <v>632.8193902768853</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>558.8808597571874</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>706.7579207965832</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>564.1629760742187</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>785.2320911834573</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>25.10263803475524</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>25.27288093420737</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>3.122247414654399</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>28.73427065040975</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>-0.104966068101145</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>0.4796747967479675</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>542.8699951171875</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>864.3475918629769</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>690.322545955769</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>604.4607420527731</v>
+      </c>
+      <c r="AQ259" t="n">
+        <v>776.184349858765</v>
+      </c>
+      <c r="AR259" t="n">
+        <v>583.2380249023437</v>
+      </c>
+      <c r="AS259" t="n">
+        <v>790.1924428862681</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>395.63</v>
+      </c>
+      <c r="I260" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="J260" t="n">
+        <v>23.577473</v>
+      </c>
+      <c r="K260" t="n">
+        <v>67</v>
+      </c>
+      <c r="L260" t="n">
+        <v>62</v>
+      </c>
+      <c r="M260" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N260" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O260" t="n">
+        <v>24.3453489832566</v>
+      </c>
+      <c r="P260" t="n">
+        <v>24.53571410406203</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>1.520404730985607</v>
+      </c>
+      <c r="R260" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S260" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T260" t="n">
+        <v>-0.5050470888490437</v>
+      </c>
+      <c r="U260" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="V260" t="n">
+        <v>352.4099508739653</v>
+      </c>
+      <c r="W260" t="n">
+        <v>459.9717509315128</v>
+      </c>
+      <c r="X260" t="n">
+        <v>408.5149559390457</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>383.0025645531072</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>434.0273473249842</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>373.9912442270914</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>444.9722332485025</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>25.00004662612664</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>24.76369040352958</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>2.381777296364286</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>22.87476167224703</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>26.83592233527477</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>-0.5972739887554372</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>0.2845528455284553</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>352.4099508739653</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>573.551363775435</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>419.500782386405</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>379.5345593534123</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>459.4670054193978</v>
+      </c>
+      <c r="AR260" t="n">
+        <v>383.8385008603051</v>
+      </c>
+      <c r="AS260" t="n">
+        <v>450.3067767859106</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="I261" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J261" t="n">
+        <v>23.767742</v>
+      </c>
+      <c r="K261" t="n">
+        <v>67</v>
+      </c>
+      <c r="L261" t="n">
+        <v>1</v>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr"/>
+      <c r="U261" t="inlineStr"/>
+      <c r="V261" t="inlineStr"/>
+      <c r="W261" t="inlineStr"/>
+      <c r="X261" t="inlineStr"/>
+      <c r="Y261" t="inlineStr"/>
+      <c r="Z261" t="inlineStr"/>
+      <c r="AA261" t="inlineStr"/>
+      <c r="AB261" t="inlineStr"/>
+      <c r="AC261" t="n">
+        <v>62</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>33.71350963204349</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>36.38339890792905</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>8.691404435968238</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>30.38853852645209</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>39.27588903856842</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>-1.144322267513434</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>104.5118798593348</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>77.56852610783328</v>
+      </c>
+      <c r="AQ261" t="n">
+        <v>131.4552336108364</v>
+      </c>
+      <c r="AR261" t="n">
+        <v>94.20446943200149</v>
+      </c>
+      <c r="AS261" t="n">
+        <v>121.7552560195621</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-07-15 16:26:00</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="I262" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J262" t="n">
+        <v>32.592026</v>
+      </c>
+      <c r="K262" t="n">
+        <v>65</v>
+      </c>
+      <c r="L262" t="n">
+        <v>62</v>
+      </c>
+      <c r="M262" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N262" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O262" t="n">
+        <v>36.08531021773137</v>
+      </c>
+      <c r="P262" t="n">
+        <v>32.89509958731634</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>5.750143100550352</v>
+      </c>
+      <c r="R262" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S262" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T262" t="n">
+        <v>-0.6075125708431545</v>
+      </c>
+      <c r="U262" t="n">
+        <v>0.4677419354838709</v>
+      </c>
+      <c r="V262" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="W262" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="X262" t="n">
+        <v>235.2762226196085</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>197.7852896040202</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>272.7671556351968</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>197.4192114463443</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>291.6129907600247</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>97</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>36.39128384428321</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>36.25306109992825</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>4.685418210778027</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>30.67197510513375</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>43.29959168726084</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>-0.8108684589870012</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>0.2989690721649484</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>237.2711706647265</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>206.7222439304538</v>
+      </c>
+      <c r="AQ262" t="n">
+        <v>267.8200973989992</v>
+      </c>
+      <c r="AR262" t="n">
+        <v>199.9812776854721</v>
+      </c>
+      <c r="AS262" t="n">
+        <v>282.3133378009407</v>
       </c>
     </row>
   </sheetData>
@@ -38300,12 +39627,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -38334,13 +39661,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>357.33</v>
+        <v>370.21</v>
       </c>
       <c r="I2" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>27.235518</v>
+        <v>28.238749</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -38355,13 +39682,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.77094733939274</v>
+        <v>28.72736593168552</v>
       </c>
       <c r="P2" t="n">
-        <v>28.82570547515613</v>
+        <v>28.56636076460896</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.708404785024138</v>
+        <v>1.686468307005828</v>
       </c>
       <c r="R2" t="n">
         <v>26.81037373255447</v>
@@ -38370,31 +39697,31 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.898750315412545</v>
+        <v>-0.2897279063328614</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="V2" t="n">
-        <v>334.9452961122235</v>
+        <v>334.6900024414062</v>
       </c>
       <c r="W2" t="n">
-        <v>422.9955833357424</v>
+        <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>377.4748290928328</v>
+        <v>376.6157673643972</v>
       </c>
       <c r="Y2" t="n">
-        <v>355.0605583133161</v>
+        <v>354.5061678595508</v>
       </c>
       <c r="Z2" t="n">
-        <v>399.8890998723495</v>
+        <v>398.7253668692436</v>
       </c>
       <c r="AA2" t="n">
-        <v>351.7521033711146</v>
+        <v>351.483999633789</v>
       </c>
       <c r="AB2" t="n">
-        <v>409.6170917408649</v>
+        <v>409.3048835916722</v>
       </c>
       <c r="AC2" t="n">
         <v>123</v>
@@ -38406,57 +39733,57 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.04395076764544</v>
+        <v>29.0061483114272</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.62257203164749</v>
+        <v>28.61887096366212</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.0080968523495</v>
+        <v>1.97868076721291</v>
       </c>
       <c r="AI2" t="n">
         <v>26.82593443846539</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.38137131233157</v>
+        <v>32.22164581044751</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.9005704906760622</v>
+        <v>-0.3878338154103216</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1626016260162602</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="AM2" t="n">
-        <v>331.5075848462072</v>
+        <v>331.2549113821476</v>
       </c>
       <c r="AN2" t="n">
-        <v>446.7016702785662</v>
+        <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>381.0566340715082</v>
+        <v>380.2706043628106</v>
       </c>
       <c r="AP2" t="n">
-        <v>354.7104033686828</v>
+        <v>354.3300995046494</v>
       </c>
       <c r="AQ2" t="n">
-        <v>407.4028647743336</v>
+        <v>406.2111092209719</v>
       </c>
       <c r="AR2" t="n">
-        <v>351.9562598326659</v>
+        <v>351.6880004882812</v>
       </c>
       <c r="AS2" t="n">
-        <v>424.8435916177901</v>
+        <v>422.4257765749668</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -38485,13 +39812,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>384.93</v>
+        <v>395.63</v>
       </c>
       <c r="I3" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
       <c r="J3" t="n">
-        <v>22.953487</v>
+        <v>23.577473</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -38506,13 +39833,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.38031540827067</v>
+        <v>24.3453489832566</v>
       </c>
       <c r="P3" t="n">
-        <v>24.56339336576916</v>
+        <v>24.53571410406203</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.526715353570546</v>
+        <v>1.520404730985607</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -38521,31 +39848,31 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9345739563918927</v>
+        <v>-0.5050470888490437</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="V3" t="n">
-        <v>352.1999330248152</v>
+        <v>352.4099508739653</v>
       </c>
       <c r="W3" t="n">
-        <v>459.6976318904332</v>
+        <v>459.9717509315128</v>
       </c>
       <c r="X3" t="n">
-        <v>408.8578893966991</v>
+        <v>408.5149559390457</v>
       </c>
       <c r="Y3" t="n">
-        <v>383.2548729173211</v>
+        <v>383.0025645531072</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.4609058760773</v>
+        <v>434.0273473249842</v>
       </c>
       <c r="AA3" t="n">
-        <v>373.7683650588989</v>
+        <v>373.9912442270914</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.7070531333365</v>
+        <v>444.9722332485025</v>
       </c>
       <c r="AC3" t="n">
         <v>123</v>
@@ -38557,57 +39884,57 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.0726480027028</v>
+        <v>25.00004662612664</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.80178651355562</v>
+        <v>24.76369040352958</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.471604230144712</v>
+        <v>2.381777296364286</v>
       </c>
       <c r="AI3" t="n">
         <v>22.87476167224703</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26.89693601225375</v>
+        <v>26.83592233527477</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.8574030489415061</v>
+        <v>-0.5972739887554372</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1382113821138211</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.1999330248152</v>
+        <v>352.4099508739653</v>
       </c>
       <c r="AN3" t="n">
-        <v>573.2095572415998</v>
+        <v>573.551363775435</v>
       </c>
       <c r="AO3" t="n">
-        <v>420.4683070053259</v>
+        <v>419.500782386405</v>
       </c>
       <c r="AP3" t="n">
-        <v>379.0195040657991</v>
+        <v>379.5345593534123</v>
       </c>
       <c r="AQ3" t="n">
-        <v>461.9171099448528</v>
+        <v>459.4670054193978</v>
       </c>
       <c r="AR3" t="n">
-        <v>383.6097532435826</v>
+        <v>383.8385008603051</v>
       </c>
       <c r="AS3" t="n">
-        <v>451.0616169254954</v>
+        <v>450.3067767859106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38636,13 +39963,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>661.04</v>
+        <v>681.3099999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>27.52</v>
+        <v>27.5</v>
       </c>
       <c r="J4" t="n">
-        <v>24.020348</v>
+        <v>24.774908</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -38657,46 +39984,46 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.07314854736387</v>
+        <v>23.01161419188674</v>
       </c>
       <c r="P4" t="n">
         <v>22.19399968927557</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.772055640108698</v>
+        <v>2.688673837079926</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
       </c>
       <c r="S4" t="n">
-        <v>28.57799154893039</v>
+        <v>28.55389422485299</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3416956856605454</v>
+        <v>0.655822875871144</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="V4" t="n">
-        <v>543.2648096590909</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="W4" t="n">
-        <v>806.6792534722222</v>
+        <v>806.0930040147568</v>
       </c>
       <c r="X4" t="n">
-        <v>634.9730480234538</v>
+        <v>632.8193902768853</v>
       </c>
       <c r="Y4" t="n">
-        <v>558.6860768076625</v>
+        <v>558.8808597571874</v>
       </c>
       <c r="Z4" t="n">
-        <v>711.2600192392451</v>
+        <v>706.7579207965832</v>
       </c>
       <c r="AA4" t="n">
-        <v>564.5732764204546</v>
+        <v>564.1629760742187</v>
       </c>
       <c r="AB4" t="n">
-        <v>786.4663274265644</v>
+        <v>785.2320911834573</v>
       </c>
       <c r="AC4" t="n">
         <v>123</v>
@@ -38708,13 +40035,13 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.12473923321306</v>
+        <v>25.10263803475524</v>
       </c>
       <c r="AG4" t="n">
-        <v>25.32524540861803</v>
+        <v>25.27288093420737</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.129521483260999</v>
+        <v>3.122247414654399</v>
       </c>
       <c r="AI4" t="n">
         <v>21.20865545099432</v>
@@ -38723,42 +40050,42 @@
         <v>28.73427065040975</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.3528946003790572</v>
+        <v>-0.104966068101145</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.4227642276422764</v>
+        <v>0.4796747967479675</v>
       </c>
       <c r="AM4" t="n">
-        <v>543.2648096590909</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.9762082934226</v>
+        <v>864.3475918629769</v>
       </c>
       <c r="AO4" t="n">
-        <v>691.4328236980235</v>
+        <v>690.322545955769</v>
       </c>
       <c r="AP4" t="n">
-        <v>605.3083924786808</v>
+        <v>604.4607420527731</v>
       </c>
       <c r="AQ4" t="n">
-        <v>777.5572549173661</v>
+        <v>776.184349858765</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.6621980113637</v>
+        <v>583.2380249023437</v>
       </c>
       <c r="AS4" t="n">
-        <v>790.7671282992762</v>
+        <v>790.1924428862681</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38787,13 +40114,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>247.49</v>
+        <v>254.96</v>
       </c>
       <c r="I5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>29.604069</v>
+        <v>30.461172</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -38808,13 +40135,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.2631458603365</v>
+        <v>31.19603795699403</v>
       </c>
       <c r="P5" t="n">
-        <v>31.42344643624776</v>
+        <v>31.13636400140644</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.546642815746941</v>
+        <v>2.510269199223419</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -38823,31 +40150,31 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6514760727644043</v>
+        <v>-0.2927438846882892</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="V5" t="n">
-        <v>227.0099945068359</v>
+        <v>227.2815375624661</v>
       </c>
       <c r="W5" t="n">
-        <v>307.8042285020049</v>
+        <v>308.1724153782034</v>
       </c>
       <c r="X5" t="n">
-        <v>261.3598993924131</v>
+        <v>261.11083770004</v>
       </c>
       <c r="Y5" t="n">
-        <v>240.0699654527687</v>
+        <v>240.09988450254</v>
       </c>
       <c r="Z5" t="n">
-        <v>282.6498333320575</v>
+        <v>282.12179089754</v>
       </c>
       <c r="AA5" t="n">
-        <v>238.0339996337891</v>
+        <v>238.3187292984228</v>
       </c>
       <c r="AB5" t="n">
-        <v>292.0694818259948</v>
+        <v>292.4188472348776</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -38859,13 +40186,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>30.88886784336587</v>
+        <v>30.86330984787999</v>
       </c>
       <c r="AG5" t="n">
         <v>29.775454043677</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.380508771726309</v>
+        <v>2.36755643114337</v>
       </c>
       <c r="AI5" t="n">
         <v>28.4770334052127</v>
@@ -38874,42 +40201,42 @@
         <v>34.5121459098859</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.539716071885822</v>
+        <v>-0.1698535429146186</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.4715447154471545</v>
+        <v>0.5528455284552846</v>
       </c>
       <c r="AM5" t="n">
-        <v>227.0099945068359</v>
+        <v>227.2815375624661</v>
       </c>
       <c r="AN5" t="n">
-        <v>307.8042285020049</v>
+        <v>308.1724153782034</v>
       </c>
       <c r="AO5" t="n">
-        <v>258.2309351705386</v>
+        <v>258.3259034267555</v>
       </c>
       <c r="AP5" t="n">
-        <v>238.3298818389067</v>
+        <v>238.5094560980855</v>
       </c>
       <c r="AQ5" t="n">
-        <v>278.1319885021706</v>
+        <v>278.1423507554255</v>
       </c>
       <c r="AR5" t="n">
-        <v>238.0679992675781</v>
+        <v>238.3527696016303</v>
       </c>
       <c r="AS5" t="n">
-        <v>288.5215398066461</v>
+        <v>288.866661265745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38938,13 +40265,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>314.86</v>
+        <v>327.5</v>
       </c>
       <c r="I6" t="n">
         <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>38.16485</v>
+        <v>39.696968</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -38956,49 +40283,49 @@
         <v>33.31113727560344</v>
       </c>
       <c r="N6" t="n">
-        <v>38.41525394171838</v>
+        <v>39.64891041162227</v>
       </c>
       <c r="O6" t="n">
-        <v>35.8575116017553</v>
+        <v>35.95305345470759</v>
       </c>
       <c r="P6" t="n">
-        <v>35.80992839526899</v>
+        <v>35.85774973576063</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.484147167761942</v>
+        <v>1.534450055593982</v>
       </c>
       <c r="R6" t="n">
-        <v>33.93462617518539</v>
+        <v>34.11793547763685</v>
       </c>
       <c r="S6" t="n">
-        <v>37.8504847787483</v>
+        <v>37.93184183411679</v>
       </c>
       <c r="T6" t="n">
-        <v>1.554656066705375</v>
+        <v>2.439906422267456</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9516129032258065</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>274.8168825237283</v>
       </c>
       <c r="W6" t="n">
-        <v>316.9258450191766</v>
+        <v>327.1035108958837</v>
       </c>
       <c r="X6" t="n">
-        <v>295.8244707144812</v>
+        <v>296.6126910013376</v>
       </c>
       <c r="Y6" t="n">
-        <v>283.5802565804452</v>
+        <v>283.9534780426873</v>
       </c>
       <c r="Z6" t="n">
-        <v>308.0686848485172</v>
+        <v>309.2719039599879</v>
       </c>
       <c r="AA6" t="n">
-        <v>279.9606659452795</v>
+        <v>281.472967690504</v>
       </c>
       <c r="AB6" t="n">
-        <v>312.2664994246734</v>
+        <v>312.9376951314635</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -39007,60 +40334,60 @@
         <v>31.21898795984968</v>
       </c>
       <c r="AE6" t="n">
-        <v>38.41525394171838</v>
+        <v>39.64891041162227</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.5259869677567</v>
+        <v>34.56693258581248</v>
       </c>
       <c r="AG6" t="n">
         <v>34.35593205560495</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.865897474633354</v>
+        <v>1.922222460951787</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.5268776364823</v>
+        <v>37.60048485264074</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.950194521249529</v>
+        <v>2.668804219282395</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.975609756097561</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
         <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>316.9258450191766</v>
+        <v>327.1035108958837</v>
       </c>
       <c r="AO6" t="n">
-        <v>284.8393924839928</v>
+        <v>285.177193832953</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.4457383182676</v>
+        <v>269.3188585301007</v>
       </c>
       <c r="AQ6" t="n">
-        <v>300.233046649718</v>
+        <v>301.0355291358052</v>
       </c>
       <c r="AR6" t="n">
         <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>309.596740500979</v>
+        <v>310.2040000342861</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -39089,13 +40416,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>211.8</v>
+        <v>212.5</v>
       </c>
       <c r="I7" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="J7" t="n">
-        <v>32.434914</v>
+        <v>32.592026</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -39110,13 +40437,13 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.21504570105553</v>
+        <v>36.08531021773137</v>
       </c>
       <c r="P7" t="n">
-        <v>32.93951014099588</v>
+        <v>32.89509958731634</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.759623065888312</v>
+        <v>5.750143100550352</v>
       </c>
       <c r="R7" t="n">
         <v>30.27902016048226</v>
@@ -39125,34 +40452,34 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6563158140406047</v>
+        <v>-0.6075125708431545</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="V7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.2351595774909</v>
       </c>
       <c r="W7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="X7" t="n">
-        <v>236.4842484278926</v>
+        <v>235.2762226196085</v>
       </c>
       <c r="Y7" t="n">
-        <v>198.8739098076419</v>
+        <v>197.7852896040202</v>
       </c>
       <c r="Z7" t="n">
-        <v>274.0945870481433</v>
+        <v>272.7671556351968</v>
       </c>
       <c r="AA7" t="n">
-        <v>197.7220016479492</v>
+        <v>197.4192114463443</v>
       </c>
       <c r="AB7" t="n">
-        <v>292.0602499483069</v>
+        <v>291.6129907600247</v>
       </c>
       <c r="AC7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -39161,57 +40488,57 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.43137937054528</v>
+        <v>36.39128384428321</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.27142925651706</v>
+        <v>36.25306109992825</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.693255359422203</v>
+        <v>4.685418210778027</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.66692147831822</v>
+        <v>30.67197510513375</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.33367328254543</v>
+        <v>43.29959168726084</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.8515337573784381</v>
+        <v>-0.8108684589870012</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2604166666666667</v>
+        <v>0.2989690721649484</v>
       </c>
       <c r="AM7" t="n">
-        <v>192.5299987792968</v>
+        <v>192.2351595774909</v>
       </c>
       <c r="AN7" t="n">
-        <v>314.1596399735431</v>
+        <v>313.6785379215162</v>
       </c>
       <c r="AO7" t="n">
-        <v>237.8969072896607</v>
+        <v>237.2711706647265</v>
       </c>
       <c r="AP7" t="n">
-        <v>207.2499497926337</v>
+        <v>206.7222439304538</v>
       </c>
       <c r="AQ7" t="n">
-        <v>268.5438647866877</v>
+        <v>267.8200973989992</v>
       </c>
       <c r="AR7" t="n">
-        <v>200.254997253418</v>
+        <v>199.9812776854721</v>
       </c>
       <c r="AS7" t="n">
-        <v>282.9688865350217</v>
+        <v>282.3133378009407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -39240,13 +40567,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>548.13</v>
+        <v>529.14</v>
       </c>
       <c r="I8" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="J8" t="n">
-        <v>183.32108</v>
+        <v>175.79402</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -39255,52 +40582,52 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>97.40377174233491</v>
+        <v>103.754721587559</v>
       </c>
       <c r="N8" t="n">
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>152.7290211827868</v>
+        <v>153.9561946932803</v>
       </c>
       <c r="P8" t="n">
-        <v>158.0262331102715</v>
+        <v>160.4557375048028</v>
       </c>
       <c r="Q8" t="n">
-        <v>23.76013302907137</v>
+        <v>22.80130998949041</v>
       </c>
       <c r="R8" t="n">
-        <v>115.8935800228479</v>
+        <v>122.3969784142836</v>
       </c>
       <c r="S8" t="n">
         <v>179.11474609375</v>
       </c>
       <c r="T8" t="n">
-        <v>1.287537354264084</v>
+        <v>0.9577443277068394</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="V8" t="n">
-        <v>291.2372775095814</v>
+        <v>312.3017119785525</v>
       </c>
       <c r="W8" t="n">
-        <v>569.4822359679176</v>
+        <v>573.2914816934554</v>
       </c>
       <c r="X8" t="n">
-        <v>456.6597733365325</v>
+        <v>463.4081460267735</v>
       </c>
       <c r="Y8" t="n">
-        <v>385.6169755796091</v>
+        <v>394.7762029584074</v>
       </c>
       <c r="Z8" t="n">
-        <v>527.7025710934558</v>
+        <v>532.0400890951397</v>
       </c>
       <c r="AA8" t="n">
-        <v>346.5218042683152</v>
+        <v>368.4149050269937</v>
       </c>
       <c r="AB8" t="n">
-        <v>535.5530908203125</v>
+        <v>539.1353857421875</v>
       </c>
       <c r="AC8" t="n">
         <v>123</v>
@@ -39312,57 +40639,57 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>120.4096928841907</v>
+        <v>120.9073568535075</v>
       </c>
       <c r="AG8" t="n">
-        <v>121.9660345113502</v>
+        <v>123.0541886954472</v>
       </c>
       <c r="AH8" t="n">
-        <v>38.93708106705625</v>
+        <v>39.22240982201477</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51924334831958</v>
       </c>
       <c r="AJ8" t="n">
-        <v>173.9986912461578</v>
+        <v>174.3881996029713</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.615719139487246</v>
+        <v>1.399369987605547</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9918699186991869</v>
+        <v>0.9105691056910569</v>
       </c>
       <c r="AM8" t="n">
-        <v>215.4492418397148</v>
+        <v>216.8903738921543</v>
       </c>
       <c r="AN8" t="n">
-        <v>569.4822359679176</v>
+        <v>573.2914816934554</v>
       </c>
       <c r="AO8" t="n">
-        <v>360.0249817237303</v>
+        <v>363.9311441290575</v>
       </c>
       <c r="AP8" t="n">
-        <v>243.6031093332321</v>
+        <v>245.8716905647931</v>
       </c>
       <c r="AQ8" t="n">
-        <v>476.4468541142285</v>
+        <v>481.990597693322</v>
       </c>
       <c r="AR8" t="n">
-        <v>225.8025376114755</v>
+        <v>227.3129224784419</v>
       </c>
       <c r="AS8" t="n">
-        <v>520.2560868260118</v>
+        <v>524.9084808049437</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -39391,13 +40718,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>389.11</v>
+        <v>394.28</v>
       </c>
       <c r="I9" t="n">
         <v>5.99</v>
       </c>
       <c r="J9" t="n">
-        <v>64.95993</v>
+        <v>65.823044</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -39412,13 +40739,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>74.94363857678844</v>
+        <v>74.75445566662759</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.56555110926034</v>
+        <v>9.633263064441762</v>
       </c>
       <c r="R9" t="n">
         <v>62.25973272085587</v>
@@ -39427,10 +40754,10 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.043714937357168</v>
+        <v>-0.9271429220691757</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="V9" t="n">
         <v>359.2505113344621</v>
@@ -39439,13 +40766,13 @@
         <v>562.3010416904622</v>
       </c>
       <c r="X9" t="n">
-        <v>448.9123950749628</v>
+        <v>447.7791894430993</v>
       </c>
       <c r="Y9" t="n">
-        <v>391.6147439304934</v>
+        <v>390.0759436870931</v>
       </c>
       <c r="Z9" t="n">
-        <v>506.2100462194322</v>
+        <v>505.4824351991055</v>
       </c>
       <c r="AA9" t="n">
         <v>372.9357989979267</v>
@@ -39463,13 +40790,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.06518789230968</v>
+        <v>71.01390371148848</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.33543207260549</v>
+        <v>69.28302117113797</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.343188832949277</v>
+        <v>8.357316288336976</v>
       </c>
       <c r="AI9" t="n">
         <v>61.7377704233179</v>
@@ -39478,10 +40805,10 @@
         <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.7317655173041914</v>
+        <v>-0.6211156228145358</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.2764227642276423</v>
+        <v>0.3495934959349594</v>
       </c>
       <c r="AM9" t="n">
         <v>342.5976456015664</v>
@@ -39490,13 +40817,13 @@
         <v>562.3010416904622</v>
       </c>
       <c r="AO9" t="n">
-        <v>425.680475474935</v>
+        <v>425.373283231816</v>
       </c>
       <c r="AP9" t="n">
-        <v>375.7047743655688</v>
+        <v>375.3129586646775</v>
       </c>
       <c r="AQ9" t="n">
-        <v>475.6561765843012</v>
+        <v>475.4336077989545</v>
       </c>
       <c r="AR9" t="n">
         <v>369.8092448356742</v>
@@ -39508,12 +40835,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-14 16:22:36</t>
+          <t>2026-07-15 16:26:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -39542,19 +40869,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.53</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.719355</v>
+        <v>23.767742</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -39573,7 +40900,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -39582,25 +40909,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>33.23675463771948</v>
+        <v>33.71350963204349</v>
       </c>
       <c r="AG10" t="n">
-        <v>36.29248999795422</v>
+        <v>36.38339890792905</v>
       </c>
       <c r="AH10" t="n">
-        <v>9.414973243740455</v>
+        <v>8.691404435968238</v>
       </c>
       <c r="AI10" t="n">
-        <v>30.11462366156897</v>
+        <v>30.38853852645209</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.26719333814537</v>
+        <v>39.27588903856842</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.010879095598824</v>
+        <v>-1.144322267513434</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.07936507936507936</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -39609,19 +40936,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>103.0339393769304</v>
+        <v>104.5118798593348</v>
       </c>
       <c r="AP10" t="n">
-        <v>73.84752232133498</v>
+        <v>77.56852610783328</v>
       </c>
       <c r="AQ10" t="n">
-        <v>132.2203564325258</v>
+        <v>131.4552336108364</v>
       </c>
       <c r="AR10" t="n">
-        <v>93.35533335086382</v>
+        <v>94.20446943200149</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.7282993482506</v>
+        <v>121.7552560195621</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS262"/>
+  <dimension ref="A1:AS271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38111,7 +38111,7 @@
         <v>33.31113727560344</v>
       </c>
       <c r="N254" t="n">
-        <v>39.64891041162227</v>
+        <v>39.64891041162228</v>
       </c>
       <c r="O254" t="n">
         <v>35.95305345470759</v>
@@ -38162,7 +38162,7 @@
         <v>31.21898795984968</v>
       </c>
       <c r="AE254" t="n">
-        <v>39.64891041162227</v>
+        <v>39.64891041162228</v>
       </c>
       <c r="AF254" t="n">
         <v>34.56693258581248</v>
@@ -38334,7 +38334,7 @@
         <v>1.399369987605547</v>
       </c>
       <c r="AL255" t="n">
-        <v>0.9105691056910569</v>
+        <v>0.9105691056910568</v>
       </c>
       <c r="AM255" t="n">
         <v>216.8903738921543</v>
@@ -38343,7 +38343,7 @@
         <v>573.2914816934554</v>
       </c>
       <c r="AO255" t="n">
-        <v>363.9311441290575</v>
+        <v>363.9311441290576</v>
       </c>
       <c r="AP255" t="n">
         <v>245.8716905647931</v>
@@ -38416,7 +38416,7 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O256" t="n">
-        <v>31.19603795699403</v>
+        <v>31.19603795699402</v>
       </c>
       <c r="P256" t="n">
         <v>31.13636400140644</v>
@@ -38431,7 +38431,7 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T256" t="n">
-        <v>-0.2927438846882892</v>
+        <v>-0.2927438846882891</v>
       </c>
       <c r="U256" t="n">
         <v>0.4516129032258064</v>
@@ -38467,7 +38467,7 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF256" t="n">
-        <v>30.86330984787999</v>
+        <v>30.86330984788</v>
       </c>
       <c r="AG256" t="n">
         <v>29.775454043677</v>
@@ -38494,7 +38494,7 @@
         <v>308.1724153782034</v>
       </c>
       <c r="AO256" t="n">
-        <v>258.3259034267555</v>
+        <v>258.3259034267556</v>
       </c>
       <c r="AP256" t="n">
         <v>238.5094560980855</v>
@@ -38503,7 +38503,7 @@
         <v>278.1423507554255</v>
       </c>
       <c r="AR256" t="n">
-        <v>238.3527696016303</v>
+        <v>238.3527696016302</v>
       </c>
       <c r="AS256" t="n">
         <v>288.866661265745</v>
@@ -38564,7 +38564,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N257" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O257" t="n">
         <v>74.75445566662759</v>
@@ -38582,7 +38582,7 @@
         <v>83.49376061274063</v>
       </c>
       <c r="T257" t="n">
-        <v>-0.9271429220691757</v>
+        <v>-0.9271429220691756</v>
       </c>
       <c r="U257" t="n">
         <v>0.3548387096774194</v>
@@ -38615,7 +38615,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE257" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF257" t="n">
         <v>71.01390371148848</v>
@@ -38627,7 +38627,7 @@
         <v>8.357316288336976</v>
       </c>
       <c r="AI257" t="n">
-        <v>61.7377704233179</v>
+        <v>61.73777042331791</v>
       </c>
       <c r="AJ257" t="n">
         <v>82.36296239187379</v>
@@ -38636,7 +38636,7 @@
         <v>-0.6211156228145358</v>
       </c>
       <c r="AL257" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.3495934959349593</v>
       </c>
       <c r="AM257" t="n">
         <v>342.5976456015664</v>
@@ -38799,7 +38799,7 @@
         <v>380.2706043628106</v>
       </c>
       <c r="AP258" t="n">
-        <v>354.3300995046494</v>
+        <v>354.3300995046493</v>
       </c>
       <c r="AQ258" t="n">
         <v>406.2111092209719</v>
@@ -38881,7 +38881,7 @@
         <v>20.51501731178977</v>
       </c>
       <c r="S259" t="n">
-        <v>28.55389422485299</v>
+        <v>28.553894224853</v>
       </c>
       <c r="T259" t="n">
         <v>0.655822875871144</v>
@@ -39023,7 +39023,7 @@
         <v>24.3453489832566</v>
       </c>
       <c r="P260" t="n">
-        <v>24.53571410406203</v>
+        <v>24.53571410406204</v>
       </c>
       <c r="Q260" t="n">
         <v>1.520404730985607</v>
@@ -39184,7 +39184,7 @@
         <v>62</v>
       </c>
       <c r="AD261" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE261" t="n">
         <v>42.60474344487245</v>
@@ -39208,7 +39208,7 @@
         <v>-1.144322267513434</v>
       </c>
       <c r="AL261" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.06451612903225799</v>
       </c>
       <c r="AM261" t="n">
         <v>10.81762752038992</v>
@@ -39226,7 +39226,7 @@
         <v>131.4552336108364</v>
       </c>
       <c r="AR261" t="n">
-        <v>94.20446943200149</v>
+        <v>94.20446943200147</v>
       </c>
       <c r="AS261" t="n">
         <v>121.7552560195621</v>
@@ -39350,7 +39350,7 @@
         <v>4.685418210778027</v>
       </c>
       <c r="AI262" t="n">
-        <v>30.67197510513375</v>
+        <v>30.67197510513376</v>
       </c>
       <c r="AJ262" t="n">
         <v>43.29959168726084</v>
@@ -39381,6 +39381,1333 @@
       </c>
       <c r="AS262" t="n">
         <v>282.3133378009407</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="I263" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="J263" t="n">
+        <v>40.395153</v>
+      </c>
+      <c r="K263" t="n">
+        <v>67</v>
+      </c>
+      <c r="L263" t="n">
+        <v>62</v>
+      </c>
+      <c r="M263" t="n">
+        <v>33.31113727560344</v>
+      </c>
+      <c r="N263" t="n">
+        <v>40.34624815564467</v>
+      </c>
+      <c r="O263" t="n">
+        <v>36.06602888658409</v>
+      </c>
+      <c r="P263" t="n">
+        <v>35.92191423688617</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>1.595674415072756</v>
+      </c>
+      <c r="R263" t="n">
+        <v>34.19949533969541</v>
+      </c>
+      <c r="S263" t="n">
+        <v>38.10084603889225</v>
+      </c>
+      <c r="T263" t="n">
+        <v>2.71303724150927</v>
+      </c>
+      <c r="U263" t="n">
+        <v>1</v>
+      </c>
+      <c r="V263" t="n">
+        <v>274.8168825237283</v>
+      </c>
+      <c r="W263" t="n">
+        <v>332.8565472840685</v>
+      </c>
+      <c r="X263" t="n">
+        <v>297.5447383143187</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>284.3804243899685</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>310.709052238669</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>282.1458365524871</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>314.3319798208611</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>40.34624815564467</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>34.61646833469738</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>34.37533544790968</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>1.991339692299404</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>32.13645490815368</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>37.62857210838189</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>2.901908040927945</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>257.5566506687599</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>332.8565472840685</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>285.5858637612534</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>269.1573112997833</v>
+      </c>
+      <c r="AQ263" t="n">
+        <v>302.0144162227235</v>
+      </c>
+      <c r="AR263" t="n">
+        <v>265.1257529922678</v>
+      </c>
+      <c r="AS263" t="n">
+        <v>310.4357198941506</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>500.94</v>
+      </c>
+      <c r="I264" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="J264" t="n">
+        <v>165.87418</v>
+      </c>
+      <c r="K264" t="n">
+        <v>63</v>
+      </c>
+      <c r="L264" t="n">
+        <v>62</v>
+      </c>
+      <c r="M264" t="n">
+        <v>103.754721587559</v>
+      </c>
+      <c r="N264" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O264" t="n">
+        <v>154.9116599591066</v>
+      </c>
+      <c r="P264" t="n">
+        <v>161.6180319864242</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>21.94133562981567</v>
+      </c>
+      <c r="R264" t="n">
+        <v>126.369057709316</v>
+      </c>
+      <c r="S264" t="n">
+        <v>179.11474609375</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0.4996286564249353</v>
+      </c>
+      <c r="U264" t="n">
+        <v>0.5483870967741935</v>
+      </c>
+      <c r="V264" t="n">
+        <v>313.3392591944281</v>
+      </c>
+      <c r="W264" t="n">
+        <v>575.1961045562244</v>
+      </c>
+      <c r="X264" t="n">
+        <v>467.833213076502</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>401.5703794744587</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>534.0960466785453</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>381.6345542821344</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>540.926533203125</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>121.3141914259135</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>123.798028353987</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>39.41135640080815</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>75.51924334831958</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>174.3881996029713</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>1.130638289149896</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>0.7723577235772358</v>
+      </c>
+      <c r="AM264" t="n">
+        <v>217.6109399183741</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>575.1961045562244</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>366.3688581062586</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>247.346561775818</v>
+      </c>
+      <c r="AQ264" t="n">
+        <v>485.3911544366993</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>228.0681149119251</v>
+      </c>
+      <c r="AS264" t="n">
+        <v>526.6523628009734</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>249.89</v>
+      </c>
+      <c r="I265" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="J265" t="n">
+        <v>29.89115</v>
+      </c>
+      <c r="K265" t="n">
+        <v>67</v>
+      </c>
+      <c r="L265" t="n">
+        <v>62</v>
+      </c>
+      <c r="M265" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N265" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O265" t="n">
+        <v>31.11644902466197</v>
+      </c>
+      <c r="P265" t="n">
+        <v>30.85286993729441</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>2.471225792457922</v>
+      </c>
+      <c r="R265" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S265" t="n">
+        <v>34.93654088827689</v>
+      </c>
+      <c r="T265" t="n">
+        <v>-0.4958264147297008</v>
+      </c>
+      <c r="U265" t="n">
+        <v>0.4354838709677419</v>
+      </c>
+      <c r="V265" t="n">
+        <v>227.0099945068359</v>
+      </c>
+      <c r="W265" t="n">
+        <v>307.8042285020049</v>
+      </c>
+      <c r="X265" t="n">
+        <v>260.1335138461741</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>239.4740662212259</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>280.7929614711223</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>238.0339996337891</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>292.0694818259948</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>30.83174186123428</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>29.775454043677</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>2.354277249022969</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>28.4770334052127</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>34.5121459098859</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>-0.3995246785928164</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>0.5203252032520326</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>227.0099945068359</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>307.8042285020049</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>257.7533619599185</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>238.0716041580866</v>
+      </c>
+      <c r="AQ265" t="n">
+        <v>277.4351197617506</v>
+      </c>
+      <c r="AR265" t="n">
+        <v>238.0679992675781</v>
+      </c>
+      <c r="AS265" t="n">
+        <v>288.5215398066461</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>374.45</v>
+      </c>
+      <c r="I266" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="J266" t="n">
+        <v>62.512524</v>
+      </c>
+      <c r="K266" t="n">
+        <v>34</v>
+      </c>
+      <c r="L266" t="n">
+        <v>62</v>
+      </c>
+      <c r="M266" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N266" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O266" t="n">
+        <v>74.50655293062798</v>
+      </c>
+      <c r="P266" t="n">
+        <v>78.71540210865163</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>9.753897933009513</v>
+      </c>
+      <c r="R266" t="n">
+        <v>62.22212907280184</v>
+      </c>
+      <c r="S266" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T266" t="n">
+        <v>-1.229665208002364</v>
+      </c>
+      <c r="U266" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="V266" t="n">
+        <v>359.2505113344621</v>
+      </c>
+      <c r="W266" t="n">
+        <v>562.3010416904622</v>
+      </c>
+      <c r="X266" t="n">
+        <v>446.2942520544616</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>387.8684034357346</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>504.7201006731885</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>372.710553146083</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>500.1276260703164</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>70.92098292867908</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>69.25366799536492</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>8.390300782310522</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>61.7377704233179</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>82.36296239187379</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>-1.00216418300603</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>0.1626016260162602</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>342.5976456015664</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>562.3010416904622</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>424.8166877427877</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>374.5587860567477</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>475.0745894288277</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>369.8092448356742</v>
+      </c>
+      <c r="AS266" t="n">
+        <v>493.354144727324</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="I267" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J267" t="n">
+        <v>26.987797</v>
+      </c>
+      <c r="K267" t="n">
+        <v>37</v>
+      </c>
+      <c r="L267" t="n">
+        <v>62</v>
+      </c>
+      <c r="M267" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N267" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O267" t="n">
+        <v>28.66614436137828</v>
+      </c>
+      <c r="P267" t="n">
+        <v>28.36308133774909</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>1.679483717861193</v>
+      </c>
+      <c r="R267" t="n">
+        <v>26.81037373255447</v>
+      </c>
+      <c r="S267" t="n">
+        <v>31.22081491927324</v>
+      </c>
+      <c r="T267" t="n">
+        <v>-0.9993233894018544</v>
+      </c>
+      <c r="U267" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="V267" t="n">
+        <v>334.6900024414062</v>
+      </c>
+      <c r="W267" t="n">
+        <v>422.673178165517</v>
+      </c>
+      <c r="X267" t="n">
+        <v>375.8131525776692</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>353.7951210365089</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>397.8311841188294</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>351.483999633789</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>409.3048835916722</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>28.96043877199228</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>28.53099106639541</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>1.959592168836796</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>26.82593443846539</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>32.14264565325797</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>-1.006659346451272</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>0.1300813008130081</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>331.2549113821476</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>446.3611964445124</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>379.6713523008188</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>353.9810989673684</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>405.3616056342692</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>351.6880004882812</v>
+      </c>
+      <c r="AS267" t="n">
+        <v>421.390084514212</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>664.54</v>
+      </c>
+      <c r="I268" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="J268" t="n">
+        <v>24.147528</v>
+      </c>
+      <c r="K268" t="n">
+        <v>55</v>
+      </c>
+      <c r="L268" t="n">
+        <v>62</v>
+      </c>
+      <c r="M268" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N268" t="n">
+        <v>29.31247287326389</v>
+      </c>
+      <c r="O268" t="n">
+        <v>22.93661176914591</v>
+      </c>
+      <c r="P268" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>2.587063165187867</v>
+      </c>
+      <c r="R268" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S268" t="n">
+        <v>28.48412082975801</v>
+      </c>
+      <c r="T268" t="n">
+        <v>0.4680659703823513</v>
+      </c>
+      <c r="U268" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="V268" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="W268" t="n">
+        <v>806.6792534722222</v>
+      </c>
+      <c r="X268" t="n">
+        <v>631.2155558868953</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>560.0195775809252</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>702.4115341928654</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>564.5732764204546</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>783.8830052349404</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>25.0757769859408</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>25.24137858280784</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>3.115928029175227</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>21.20865545099432</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>28.73427065040975</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>-0.2979045014035528</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>0.4308943089430894</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>543.2648096590909</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>864.9762082934226</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>690.0853826530908</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>604.3350432901887</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>775.835722015993</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>583.6621980113637</v>
+      </c>
+      <c r="AS268" t="n">
+        <v>790.7671282992762</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>401.1</v>
+      </c>
+      <c r="I269" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="J269" t="n">
+        <v>23.91771</v>
+      </c>
+      <c r="K269" t="n">
+        <v>67</v>
+      </c>
+      <c r="L269" t="n">
+        <v>62</v>
+      </c>
+      <c r="M269" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N269" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O269" t="n">
+        <v>24.30651548454128</v>
+      </c>
+      <c r="P269" t="n">
+        <v>24.49761890229725</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>1.500731797820628</v>
+      </c>
+      <c r="R269" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S269" t="n">
+        <v>26.51801151659729</v>
+      </c>
+      <c r="T269" t="n">
+        <v>-0.2590772615772579</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="V269" t="n">
+        <v>352.1999330248152</v>
+      </c>
+      <c r="W269" t="n">
+        <v>459.6976318904332</v>
+      </c>
+      <c r="X269" t="n">
+        <v>407.6202646757573</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>382.4529924263054</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>432.7875369252092</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>373.7683650588989</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>444.7070531333365</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>123</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>24.92824200236349</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>24.73733507148022</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>2.278416541050988</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>22.87476167224703</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>26.75357060844389</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>-0.4435238175971789</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>352.1999330248152</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>573.2095572415998</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>418.0466183796358</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>379.8375729862107</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>456.2556637730608</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>383.6097532435826</v>
+      </c>
+      <c r="AS269" t="n">
+        <v>448.6573791036041</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="I270" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J270" t="n">
+        <v>23.983871</v>
+      </c>
+      <c r="K270" t="n">
+        <v>67</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr"/>
+      <c r="T270" t="inlineStr"/>
+      <c r="U270" t="inlineStr"/>
+      <c r="V270" t="inlineStr"/>
+      <c r="W270" t="inlineStr"/>
+      <c r="X270" t="inlineStr"/>
+      <c r="Y270" t="inlineStr"/>
+      <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="inlineStr"/>
+      <c r="AB270" t="inlineStr"/>
+      <c r="AC270" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>34.20593017834855</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>36.47430781790388</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>7.843170490235964</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>30.43478260869564</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>39.28458473899146</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>-1.303307022469304</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>10.81762752038992</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>132.0747046791046</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>106.0383835528805</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>81.724555033149</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>130.352212072612</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>94.34782608695649</v>
+      </c>
+      <c r="AS270" t="n">
+        <v>121.7822126908735</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:22:58</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>207.4</v>
+      </c>
+      <c r="I271" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J271" t="n">
+        <v>31.809814</v>
+      </c>
+      <c r="K271" t="n">
+        <v>65</v>
+      </c>
+      <c r="L271" t="n">
+        <v>62</v>
+      </c>
+      <c r="M271" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N271" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O271" t="n">
+        <v>35.94468938847864</v>
+      </c>
+      <c r="P271" t="n">
+        <v>32.84839203675344</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>5.747523975055628</v>
+      </c>
+      <c r="R271" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S271" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T271" t="n">
+        <v>-0.7194185542198833</v>
+      </c>
+      <c r="U271" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="V271" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="W271" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="X271" t="n">
+        <v>234.3593748128807</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>196.885518495518</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>271.8332311302434</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>197.4192114463443</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>291.6129907600247</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>98</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>36.3440370873893</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>36.22755089584662</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>4.684611385303</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>30.67702873194929</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>43.26551009197624</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>-0.9678973802639192</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>0.2040816326530612</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>192.2351595774909</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>313.6785379215162</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>236.9631218097782</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>206.4194555776027</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>267.5067880419538</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>200.0142273323094</v>
+      </c>
+      <c r="AS271" t="n">
+        <v>282.0911257996851</v>
       </c>
     </row>
   </sheetData>
@@ -39627,12 +40954,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -39661,13 +40988,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>370.21</v>
+        <v>353.81</v>
       </c>
       <c r="I2" t="n">
         <v>13.11</v>
       </c>
       <c r="J2" t="n">
-        <v>28.238749</v>
+        <v>26.987797</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -39682,13 +41009,13 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.72736593168552</v>
+        <v>28.66614436137828</v>
       </c>
       <c r="P2" t="n">
-        <v>28.56636076460896</v>
+        <v>28.36308133774909</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.686468307005828</v>
+        <v>1.679483717861193</v>
       </c>
       <c r="R2" t="n">
         <v>26.81037373255447</v>
@@ -39697,10 +41024,10 @@
         <v>31.22081491927324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2897279063328614</v>
+        <v>-0.9993233894018544</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="V2" t="n">
         <v>334.6900024414062</v>
@@ -39709,13 +41036,13 @@
         <v>422.673178165517</v>
       </c>
       <c r="X2" t="n">
-        <v>376.6157673643972</v>
+        <v>375.8131525776692</v>
       </c>
       <c r="Y2" t="n">
-        <v>354.5061678595508</v>
+        <v>353.7951210365089</v>
       </c>
       <c r="Z2" t="n">
-        <v>398.7253668692436</v>
+        <v>397.8311841188294</v>
       </c>
       <c r="AA2" t="n">
         <v>351.483999633789</v>
@@ -39733,25 +41060,25 @@
         <v>34.04738340537852</v>
       </c>
       <c r="AF2" t="n">
-        <v>29.0061483114272</v>
+        <v>28.96043877199228</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.61887096366212</v>
+        <v>28.53099106639541</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.97868076721291</v>
+        <v>1.959592168836796</v>
       </c>
       <c r="AI2" t="n">
         <v>26.82593443846539</v>
       </c>
       <c r="AJ2" t="n">
-        <v>32.22164581044751</v>
+        <v>32.14264565325797</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.3878338154103216</v>
+        <v>-1.006659346451272</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.1300813008130081</v>
       </c>
       <c r="AM2" t="n">
         <v>331.2549113821476</v>
@@ -39760,30 +41087,30 @@
         <v>446.3611964445124</v>
       </c>
       <c r="AO2" t="n">
-        <v>380.2706043628106</v>
+        <v>379.6713523008188</v>
       </c>
       <c r="AP2" t="n">
-        <v>354.3300995046494</v>
+        <v>353.9810989673684</v>
       </c>
       <c r="AQ2" t="n">
-        <v>406.2111092209719</v>
+        <v>405.3616056342692</v>
       </c>
       <c r="AR2" t="n">
         <v>351.6880004882812</v>
       </c>
       <c r="AS2" t="n">
-        <v>422.4257765749668</v>
+        <v>421.390084514212</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -39812,13 +41139,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>395.63</v>
+        <v>401.1</v>
       </c>
       <c r="I3" t="n">
-        <v>16.78</v>
+        <v>16.77</v>
       </c>
       <c r="J3" t="n">
-        <v>23.577473</v>
+        <v>23.91771</v>
       </c>
       <c r="K3" t="n">
         <v>67</v>
@@ -39833,13 +41160,13 @@
         <v>27.41190410795666</v>
       </c>
       <c r="O3" t="n">
-        <v>24.3453489832566</v>
+        <v>24.30651548454128</v>
       </c>
       <c r="P3" t="n">
-        <v>24.53571410406203</v>
+        <v>24.49761890229725</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.520404730985607</v>
+        <v>1.500731797820628</v>
       </c>
       <c r="R3" t="n">
         <v>22.28791681925455</v>
@@ -39848,31 +41175,31 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5050470888490437</v>
+        <v>-0.2590772615772579</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="V3" t="n">
-        <v>352.4099508739653</v>
+        <v>352.1999330248152</v>
       </c>
       <c r="W3" t="n">
-        <v>459.9717509315128</v>
+        <v>459.6976318904332</v>
       </c>
       <c r="X3" t="n">
-        <v>408.5149559390457</v>
+        <v>407.6202646757573</v>
       </c>
       <c r="Y3" t="n">
-        <v>383.0025645531072</v>
+        <v>382.4529924263054</v>
       </c>
       <c r="Z3" t="n">
-        <v>434.0273473249842</v>
+        <v>432.7875369252092</v>
       </c>
       <c r="AA3" t="n">
-        <v>373.9912442270914</v>
+        <v>373.7683650588989</v>
       </c>
       <c r="AB3" t="n">
-        <v>444.9722332485025</v>
+        <v>444.7070531333365</v>
       </c>
       <c r="AC3" t="n">
         <v>123</v>
@@ -39884,57 +41211,57 @@
         <v>34.18065338351818</v>
       </c>
       <c r="AF3" t="n">
-        <v>25.00004662612664</v>
+        <v>24.92824200236349</v>
       </c>
       <c r="AG3" t="n">
-        <v>24.76369040352958</v>
+        <v>24.73733507148022</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.381777296364286</v>
+        <v>2.278416541050988</v>
       </c>
       <c r="AI3" t="n">
         <v>22.87476167224703</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26.83592233527477</v>
+        <v>26.75357060844389</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.5972739887554372</v>
+        <v>-0.4435238175971789</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2845528455284553</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="AM3" t="n">
-        <v>352.4099508739653</v>
+        <v>352.1999330248152</v>
       </c>
       <c r="AN3" t="n">
-        <v>573.551363775435</v>
+        <v>573.2095572415998</v>
       </c>
       <c r="AO3" t="n">
-        <v>419.500782386405</v>
+        <v>418.0466183796358</v>
       </c>
       <c r="AP3" t="n">
-        <v>379.5345593534123</v>
+        <v>379.8375729862107</v>
       </c>
       <c r="AQ3" t="n">
-        <v>459.4670054193978</v>
+        <v>456.2556637730608</v>
       </c>
       <c r="AR3" t="n">
-        <v>383.8385008603051</v>
+        <v>383.6097532435826</v>
       </c>
       <c r="AS3" t="n">
-        <v>450.3067767859106</v>
+        <v>448.6573791036041</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -39963,13 +41290,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>681.3099999999999</v>
+        <v>664.54</v>
       </c>
       <c r="I4" t="n">
-        <v>27.5</v>
+        <v>27.52</v>
       </c>
       <c r="J4" t="n">
-        <v>24.774908</v>
+        <v>24.147528</v>
       </c>
       <c r="K4" t="n">
         <v>55</v>
@@ -39984,46 +41311,46 @@
         <v>29.31247287326389</v>
       </c>
       <c r="O4" t="n">
-        <v>23.01161419188674</v>
+        <v>22.93661176914591</v>
       </c>
       <c r="P4" t="n">
         <v>22.19399968927557</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.688673837079926</v>
+        <v>2.587063165187867</v>
       </c>
       <c r="R4" t="n">
         <v>20.51501731178977</v>
       </c>
       <c r="S4" t="n">
-        <v>28.55389422485299</v>
+        <v>28.48412082975801</v>
       </c>
       <c r="T4" t="n">
-        <v>0.655822875871144</v>
+        <v>0.4680659703823513</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="V4" t="n">
-        <v>542.8699951171875</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="W4" t="n">
-        <v>806.0930040147568</v>
+        <v>806.6792534722222</v>
       </c>
       <c r="X4" t="n">
-        <v>632.8193902768853</v>
+        <v>631.2155558868953</v>
       </c>
       <c r="Y4" t="n">
-        <v>558.8808597571874</v>
+        <v>560.0195775809252</v>
       </c>
       <c r="Z4" t="n">
-        <v>706.7579207965832</v>
+        <v>702.4115341928654</v>
       </c>
       <c r="AA4" t="n">
-        <v>564.1629760742187</v>
+        <v>564.5732764204546</v>
       </c>
       <c r="AB4" t="n">
-        <v>785.2320911834573</v>
+        <v>783.8830052349404</v>
       </c>
       <c r="AC4" t="n">
         <v>123</v>
@@ -40035,13 +41362,13 @@
         <v>31.43082152229007</v>
       </c>
       <c r="AF4" t="n">
-        <v>25.10263803475524</v>
+        <v>25.0757769859408</v>
       </c>
       <c r="AG4" t="n">
-        <v>25.27288093420737</v>
+        <v>25.24137858280784</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.122247414654399</v>
+        <v>3.115928029175227</v>
       </c>
       <c r="AI4" t="n">
         <v>21.20865545099432</v>
@@ -40050,42 +41377,42 @@
         <v>28.73427065040975</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.104966068101145</v>
+        <v>-0.2979045014035528</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.4796747967479675</v>
+        <v>0.4308943089430894</v>
       </c>
       <c r="AM4" t="n">
-        <v>542.8699951171875</v>
+        <v>543.2648096590909</v>
       </c>
       <c r="AN4" t="n">
-        <v>864.3475918629769</v>
+        <v>864.9762082934226</v>
       </c>
       <c r="AO4" t="n">
-        <v>690.322545955769</v>
+        <v>690.0853826530908</v>
       </c>
       <c r="AP4" t="n">
-        <v>604.4607420527731</v>
+        <v>604.3350432901887</v>
       </c>
       <c r="AQ4" t="n">
-        <v>776.184349858765</v>
+        <v>775.835722015993</v>
       </c>
       <c r="AR4" t="n">
-        <v>583.2380249023437</v>
+        <v>583.6621980113637</v>
       </c>
       <c r="AS4" t="n">
-        <v>790.1924428862681</v>
+        <v>790.7671282992762</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -40114,13 +41441,13 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>254.96</v>
+        <v>249.89</v>
       </c>
       <c r="I5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>30.461172</v>
+        <v>29.89115</v>
       </c>
       <c r="K5" t="n">
         <v>67</v>
@@ -40135,13 +41462,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="O5" t="n">
-        <v>31.19603795699403</v>
+        <v>31.11644902466197</v>
       </c>
       <c r="P5" t="n">
-        <v>31.13636400140644</v>
+        <v>30.85286993729441</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.510269199223419</v>
+        <v>2.471225792457922</v>
       </c>
       <c r="R5" t="n">
         <v>28.4729664633719</v>
@@ -40150,31 +41477,31 @@
         <v>34.93654088827689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2927438846882892</v>
+        <v>-0.4958264147297008</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="V5" t="n">
-        <v>227.2815375624661</v>
+        <v>227.0099945068359</v>
       </c>
       <c r="W5" t="n">
-        <v>308.1724153782034</v>
+        <v>307.8042285020049</v>
       </c>
       <c r="X5" t="n">
-        <v>261.11083770004</v>
+        <v>260.1335138461741</v>
       </c>
       <c r="Y5" t="n">
-        <v>240.09988450254</v>
+        <v>239.4740662212259</v>
       </c>
       <c r="Z5" t="n">
-        <v>282.12179089754</v>
+        <v>280.7929614711223</v>
       </c>
       <c r="AA5" t="n">
-        <v>238.3187292984228</v>
+        <v>238.0339996337891</v>
       </c>
       <c r="AB5" t="n">
-        <v>292.4188472348776</v>
+        <v>292.0694818259948</v>
       </c>
       <c r="AC5" t="n">
         <v>123</v>
@@ -40186,13 +41513,13 @@
         <v>36.81868761985704</v>
       </c>
       <c r="AF5" t="n">
-        <v>30.86330984787999</v>
+        <v>30.83174186123428</v>
       </c>
       <c r="AG5" t="n">
         <v>29.775454043677</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.36755643114337</v>
+        <v>2.354277249022969</v>
       </c>
       <c r="AI5" t="n">
         <v>28.4770334052127</v>
@@ -40201,42 +41528,42 @@
         <v>34.5121459098859</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.1698535429146186</v>
+        <v>-0.3995246785928164</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5528455284552846</v>
+        <v>0.5203252032520326</v>
       </c>
       <c r="AM5" t="n">
-        <v>227.2815375624661</v>
+        <v>227.0099945068359</v>
       </c>
       <c r="AN5" t="n">
-        <v>308.1724153782034</v>
+        <v>307.8042285020049</v>
       </c>
       <c r="AO5" t="n">
-        <v>258.3259034267555</v>
+        <v>257.7533619599185</v>
       </c>
       <c r="AP5" t="n">
-        <v>238.5094560980855</v>
+        <v>238.0716041580866</v>
       </c>
       <c r="AQ5" t="n">
-        <v>278.1423507554255</v>
+        <v>277.4351197617506</v>
       </c>
       <c r="AR5" t="n">
-        <v>238.3527696016303</v>
+        <v>238.0679992675781</v>
       </c>
       <c r="AS5" t="n">
-        <v>288.866661265745</v>
+        <v>288.5215398066461</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -40265,13 +41592,13 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>327.5</v>
+        <v>333.26</v>
       </c>
       <c r="I6" t="n">
         <v>8.25</v>
       </c>
       <c r="J6" t="n">
-        <v>39.696968</v>
+        <v>40.395153</v>
       </c>
       <c r="K6" t="n">
         <v>67</v>
@@ -40283,25 +41610,25 @@
         <v>33.31113727560344</v>
       </c>
       <c r="N6" t="n">
-        <v>39.64891041162227</v>
+        <v>40.34624815564467</v>
       </c>
       <c r="O6" t="n">
-        <v>35.95305345470759</v>
+        <v>36.06602888658409</v>
       </c>
       <c r="P6" t="n">
-        <v>35.85774973576063</v>
+        <v>35.92191423688617</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.534450055593982</v>
+        <v>1.595674415072756</v>
       </c>
       <c r="R6" t="n">
-        <v>34.11793547763685</v>
+        <v>34.19949533969541</v>
       </c>
       <c r="S6" t="n">
-        <v>37.93184183411679</v>
+        <v>38.10084603889225</v>
       </c>
       <c r="T6" t="n">
-        <v>2.439906422267456</v>
+        <v>2.71303724150927</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -40310,22 +41637,22 @@
         <v>274.8168825237283</v>
       </c>
       <c r="W6" t="n">
-        <v>327.1035108958837</v>
+        <v>332.8565472840685</v>
       </c>
       <c r="X6" t="n">
-        <v>296.6126910013376</v>
+        <v>297.5447383143187</v>
       </c>
       <c r="Y6" t="n">
-        <v>283.9534780426873</v>
+        <v>284.3804243899685</v>
       </c>
       <c r="Z6" t="n">
-        <v>309.2719039599879</v>
+        <v>310.709052238669</v>
       </c>
       <c r="AA6" t="n">
-        <v>281.472967690504</v>
+        <v>282.1458365524871</v>
       </c>
       <c r="AB6" t="n">
-        <v>312.9376951314635</v>
+        <v>314.3319798208611</v>
       </c>
       <c r="AC6" t="n">
         <v>123</v>
@@ -40334,25 +41661,25 @@
         <v>31.21898795984968</v>
       </c>
       <c r="AE6" t="n">
-        <v>39.64891041162227</v>
+        <v>40.34624815564467</v>
       </c>
       <c r="AF6" t="n">
-        <v>34.56693258581248</v>
+        <v>34.61646833469738</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.35593205560495</v>
+        <v>34.37533544790968</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.922222460951787</v>
+        <v>1.991339692299404</v>
       </c>
       <c r="AI6" t="n">
         <v>32.13645490815368</v>
       </c>
       <c r="AJ6" t="n">
-        <v>37.60048485264074</v>
+        <v>37.62857210838189</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.668804219282395</v>
+        <v>2.901908040927945</v>
       </c>
       <c r="AL6" t="n">
         <v>1</v>
@@ -40361,33 +41688,33 @@
         <v>257.5566506687599</v>
       </c>
       <c r="AN6" t="n">
-        <v>327.1035108958837</v>
+        <v>332.8565472840685</v>
       </c>
       <c r="AO6" t="n">
-        <v>285.177193832953</v>
+        <v>285.5858637612534</v>
       </c>
       <c r="AP6" t="n">
-        <v>269.3188585301007</v>
+        <v>269.1573112997833</v>
       </c>
       <c r="AQ6" t="n">
-        <v>301.0355291358052</v>
+        <v>302.0144162227235</v>
       </c>
       <c r="AR6" t="n">
         <v>265.1257529922678</v>
       </c>
       <c r="AS6" t="n">
-        <v>310.2040000342861</v>
+        <v>310.4357198941506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -40416,13 +41743,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>212.5</v>
+        <v>207.4</v>
       </c>
       <c r="I7" t="n">
         <v>6.52</v>
       </c>
       <c r="J7" t="n">
-        <v>32.592026</v>
+        <v>31.809814</v>
       </c>
       <c r="K7" t="n">
         <v>65</v>
@@ -40437,13 +41764,13 @@
         <v>48.11020520268654</v>
       </c>
       <c r="O7" t="n">
-        <v>36.08531021773137</v>
+        <v>35.94468938847864</v>
       </c>
       <c r="P7" t="n">
-        <v>32.89509958731634</v>
+        <v>32.84839203675344</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.750143100550352</v>
+        <v>5.747523975055628</v>
       </c>
       <c r="R7" t="n">
         <v>30.27902016048226</v>
@@ -40452,10 +41779,10 @@
         <v>44.72591882822464</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6075125708431545</v>
+        <v>-0.7194185542198833</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="V7" t="n">
         <v>192.2351595774909</v>
@@ -40464,13 +41791,13 @@
         <v>313.6785379215162</v>
       </c>
       <c r="X7" t="n">
-        <v>235.2762226196085</v>
+        <v>234.3593748128807</v>
       </c>
       <c r="Y7" t="n">
-        <v>197.7852896040202</v>
+        <v>196.885518495518</v>
       </c>
       <c r="Z7" t="n">
-        <v>272.7671556351968</v>
+        <v>271.8332311302434</v>
       </c>
       <c r="AA7" t="n">
         <v>197.4192114463443</v>
@@ -40479,7 +41806,7 @@
         <v>291.6129907600247</v>
       </c>
       <c r="AC7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AD7" t="n">
         <v>29.48392018059676</v>
@@ -40488,25 +41815,25 @@
         <v>48.11020520268654</v>
       </c>
       <c r="AF7" t="n">
-        <v>36.39128384428321</v>
+        <v>36.3440370873893</v>
       </c>
       <c r="AG7" t="n">
-        <v>36.25306109992825</v>
+        <v>36.22755089584662</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.685418210778027</v>
+        <v>4.684611385303</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.67197510513375</v>
+        <v>30.67702873194929</v>
       </c>
       <c r="AJ7" t="n">
-        <v>43.29959168726084</v>
+        <v>43.26551009197624</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.8108684589870012</v>
+        <v>-0.9678973802639192</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2989690721649484</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="AM7" t="n">
         <v>192.2351595774909</v>
@@ -40515,30 +41842,30 @@
         <v>313.6785379215162</v>
       </c>
       <c r="AO7" t="n">
-        <v>237.2711706647265</v>
+        <v>236.9631218097782</v>
       </c>
       <c r="AP7" t="n">
-        <v>206.7222439304538</v>
+        <v>206.4194555776027</v>
       </c>
       <c r="AQ7" t="n">
-        <v>267.8200973989992</v>
+        <v>267.5067880419538</v>
       </c>
       <c r="AR7" t="n">
-        <v>199.9812776854721</v>
+        <v>200.0142273323094</v>
       </c>
       <c r="AS7" t="n">
-        <v>282.3133378009407</v>
+        <v>282.0911257996851</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -40567,13 +41894,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>529.14</v>
+        <v>500.94</v>
       </c>
       <c r="I8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="J8" t="n">
-        <v>175.79402</v>
+        <v>165.87418</v>
       </c>
       <c r="K8" t="n">
         <v>63</v>
@@ -40588,46 +41915,46 @@
         <v>190.4622862768955</v>
       </c>
       <c r="O8" t="n">
-        <v>153.9561946932803</v>
+        <v>154.9116599591066</v>
       </c>
       <c r="P8" t="n">
-        <v>160.4557375048028</v>
+        <v>161.6180319864242</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.80130998949041</v>
+        <v>21.94133562981567</v>
       </c>
       <c r="R8" t="n">
-        <v>122.3969784142836</v>
+        <v>126.369057709316</v>
       </c>
       <c r="S8" t="n">
         <v>179.11474609375</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9577443277068394</v>
+        <v>0.4996286564249353</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="V8" t="n">
-        <v>312.3017119785525</v>
+        <v>313.3392591944281</v>
       </c>
       <c r="W8" t="n">
-        <v>573.2914816934554</v>
+        <v>575.1961045562244</v>
       </c>
       <c r="X8" t="n">
-        <v>463.4081460267735</v>
+        <v>467.833213076502</v>
       </c>
       <c r="Y8" t="n">
-        <v>394.7762029584074</v>
+        <v>401.5703794744587</v>
       </c>
       <c r="Z8" t="n">
-        <v>532.0400890951397</v>
+        <v>534.0960466785453</v>
       </c>
       <c r="AA8" t="n">
-        <v>368.4149050269937</v>
+        <v>381.6345542821344</v>
       </c>
       <c r="AB8" t="n">
-        <v>539.1353857421875</v>
+        <v>540.926533203125</v>
       </c>
       <c r="AC8" t="n">
         <v>123</v>
@@ -40639,13 +41966,13 @@
         <v>190.4622862768955</v>
       </c>
       <c r="AF8" t="n">
-        <v>120.9073568535075</v>
+        <v>121.3141914259135</v>
       </c>
       <c r="AG8" t="n">
-        <v>123.0541886954472</v>
+        <v>123.798028353987</v>
       </c>
       <c r="AH8" t="n">
-        <v>39.22240982201477</v>
+        <v>39.41135640080815</v>
       </c>
       <c r="AI8" t="n">
         <v>75.51924334831958</v>
@@ -40654,42 +41981,42 @@
         <v>174.3881996029713</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.399369987605547</v>
+        <v>1.130638289149896</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.9105691056910569</v>
+        <v>0.7723577235772358</v>
       </c>
       <c r="AM8" t="n">
-        <v>216.8903738921543</v>
+        <v>217.6109399183741</v>
       </c>
       <c r="AN8" t="n">
-        <v>573.2914816934554</v>
+        <v>575.1961045562244</v>
       </c>
       <c r="AO8" t="n">
-        <v>363.9311441290575</v>
+        <v>366.3688581062586</v>
       </c>
       <c r="AP8" t="n">
-        <v>245.8716905647931</v>
+        <v>247.346561775818</v>
       </c>
       <c r="AQ8" t="n">
-        <v>481.990597693322</v>
+        <v>485.3911544366993</v>
       </c>
       <c r="AR8" t="n">
-        <v>227.3129224784419</v>
+        <v>228.0681149119251</v>
       </c>
       <c r="AS8" t="n">
-        <v>524.9084808049437</v>
+        <v>526.6523628009734</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -40718,13 +42045,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>394.28</v>
+        <v>374.45</v>
       </c>
       <c r="I9" t="n">
         <v>5.99</v>
       </c>
       <c r="J9" t="n">
-        <v>65.823044</v>
+        <v>62.512524</v>
       </c>
       <c r="K9" t="n">
         <v>34</v>
@@ -40739,25 +42066,25 @@
         <v>93.87329577470153</v>
       </c>
       <c r="O9" t="n">
-        <v>74.75445566662759</v>
+        <v>74.50655293062798</v>
       </c>
       <c r="P9" t="n">
         <v>78.71540210865163</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.633263064441762</v>
+        <v>9.753897933009513</v>
       </c>
       <c r="R9" t="n">
-        <v>62.25973272085587</v>
+        <v>62.22212907280184</v>
       </c>
       <c r="S9" t="n">
         <v>83.49376061274063</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9271429220691757</v>
+        <v>-1.229665208002364</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="V9" t="n">
         <v>359.2505113344621</v>
@@ -40766,16 +42093,16 @@
         <v>562.3010416904622</v>
       </c>
       <c r="X9" t="n">
-        <v>447.7791894430993</v>
+        <v>446.2942520544616</v>
       </c>
       <c r="Y9" t="n">
-        <v>390.0759436870931</v>
+        <v>387.8684034357346</v>
       </c>
       <c r="Z9" t="n">
-        <v>505.4824351991055</v>
+        <v>504.7201006731885</v>
       </c>
       <c r="AA9" t="n">
-        <v>372.9357989979267</v>
+        <v>372.710553146083</v>
       </c>
       <c r="AB9" t="n">
         <v>500.1276260703164</v>
@@ -40790,13 +42117,13 @@
         <v>93.87329577470153</v>
       </c>
       <c r="AF9" t="n">
-        <v>71.01390371148848</v>
+        <v>70.92098292867908</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.28302117113797</v>
+        <v>69.25366799536492</v>
       </c>
       <c r="AH9" t="n">
-        <v>8.357316288336976</v>
+        <v>8.390300782310522</v>
       </c>
       <c r="AI9" t="n">
         <v>61.7377704233179</v>
@@ -40805,10 +42132,10 @@
         <v>82.36296239187379</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.6211156228145358</v>
+        <v>-1.00216418300603</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.3495934959349594</v>
+        <v>0.1626016260162602</v>
       </c>
       <c r="AM9" t="n">
         <v>342.5976456015664</v>
@@ -40817,13 +42144,13 @@
         <v>562.3010416904622</v>
       </c>
       <c r="AO9" t="n">
-        <v>425.373283231816</v>
+        <v>424.8166877427877</v>
       </c>
       <c r="AP9" t="n">
-        <v>375.3129586646775</v>
+        <v>374.5587860567477</v>
       </c>
       <c r="AQ9" t="n">
-        <v>475.4336077989545</v>
+        <v>475.0745894288277</v>
       </c>
       <c r="AR9" t="n">
         <v>369.8092448356742</v>
@@ -40835,12 +42162,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-15 16:26:00</t>
+          <t>2026-07-16 16:22:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -40869,19 +42196,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.68000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>23.767742</v>
+        <v>23.983871</v>
       </c>
       <c r="K10" t="n">
         <v>67</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -40900,7 +42227,7 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AD10" t="n">
         <v>3.489557264641911</v>
@@ -40909,25 +42236,25 @@
         <v>42.60474344487245</v>
       </c>
       <c r="AF10" t="n">
-        <v>33.71350963204349</v>
+        <v>34.20593017834855</v>
       </c>
       <c r="AG10" t="n">
-        <v>36.38339890792905</v>
+        <v>36.47430781790388</v>
       </c>
       <c r="AH10" t="n">
-        <v>8.691404435968238</v>
+        <v>7.843170490235964</v>
       </c>
       <c r="AI10" t="n">
-        <v>30.38853852645209</v>
+        <v>30.43478260869564</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.27588903856842</v>
+        <v>39.28458473899146</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.144322267513434</v>
+        <v>-1.303307022469304</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.04918032786885246</v>
       </c>
       <c r="AM10" t="n">
         <v>10.81762752038992</v>
@@ -40936,19 +42263,19 @@
         <v>132.0747046791046</v>
       </c>
       <c r="AO10" t="n">
-        <v>104.5118798593348</v>
+        <v>106.0383835528805</v>
       </c>
       <c r="AP10" t="n">
-        <v>77.56852610783328</v>
+        <v>81.724555033149</v>
       </c>
       <c r="AQ10" t="n">
-        <v>131.4552336108364</v>
+        <v>130.352212072612</v>
       </c>
       <c r="AR10" t="n">
-        <v>94.20446943200149</v>
+        <v>94.34782608695649</v>
       </c>
       <c r="AS10" t="n">
-        <v>121.7552560195621</v>
+        <v>121.7822126908735</v>
       </c>
     </row>
   </sheetData>

--- a/data/pe_valuation_history.xlsx
+++ b/data/pe_valuation_history.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS271"/>
+  <dimension ref="A1:AS280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39628,7 +39628,7 @@
         <v>534.0960466785453</v>
       </c>
       <c r="AA264" t="n">
-        <v>381.6345542821344</v>
+        <v>381.6345542821345</v>
       </c>
       <c r="AB264" t="n">
         <v>540.926533203125</v>
@@ -39679,7 +39679,7 @@
         <v>485.3911544366993</v>
       </c>
       <c r="AR264" t="n">
-        <v>228.0681149119251</v>
+        <v>228.0681149119252</v>
       </c>
       <c r="AS264" t="n">
         <v>526.6523628009734</v>
@@ -39891,7 +39891,7 @@
         <v>59.97504362845778</v>
       </c>
       <c r="N266" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="O266" t="n">
         <v>74.50655293062798</v>
@@ -39900,7 +39900,7 @@
         <v>78.71540210865163</v>
       </c>
       <c r="Q266" t="n">
-        <v>9.753897933009513</v>
+        <v>9.753897933009512</v>
       </c>
       <c r="R266" t="n">
         <v>62.22212907280184</v>
@@ -39942,7 +39942,7 @@
         <v>57.19493248774063</v>
       </c>
       <c r="AE266" t="n">
-        <v>93.87329577470153</v>
+        <v>93.87329577470152</v>
       </c>
       <c r="AF266" t="n">
         <v>70.92098292867908</v>
@@ -39954,7 +39954,7 @@
         <v>8.390300782310522</v>
       </c>
       <c r="AI266" t="n">
-        <v>61.7377704233179</v>
+        <v>61.73777042331791</v>
       </c>
       <c r="AJ266" t="n">
         <v>82.36296239187379</v>
@@ -39963,7 +39963,7 @@
         <v>-1.00216418300603</v>
       </c>
       <c r="AL266" t="n">
-        <v>0.1626016260162602</v>
+        <v>0.1626016260162601</v>
       </c>
       <c r="AM266" t="n">
         <v>342.5976456015664</v>
@@ -40063,7 +40063,7 @@
         <v>-0.9993233894018544</v>
       </c>
       <c r="U267" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1612903225806451</v>
       </c>
       <c r="V267" t="n">
         <v>334.6900024414062</v>
@@ -40211,7 +40211,7 @@
         <v>28.48412082975801</v>
       </c>
       <c r="T268" t="n">
-        <v>0.4680659703823513</v>
+        <v>0.4680659703823512</v>
       </c>
       <c r="U268" t="n">
         <v>0.8064516129032258</v>
@@ -40253,7 +40253,7 @@
         <v>25.24137858280784</v>
       </c>
       <c r="AH268" t="n">
-        <v>3.115928029175227</v>
+        <v>3.115928029175228</v>
       </c>
       <c r="AI268" t="n">
         <v>21.20865545099432</v>
@@ -40362,7 +40362,7 @@
         <v>26.51801151659729</v>
       </c>
       <c r="T269" t="n">
-        <v>-0.2590772615772579</v>
+        <v>-0.2590772615772578</v>
       </c>
       <c r="U269" t="n">
         <v>0.4032258064516129</v>
@@ -40511,7 +40511,7 @@
         <v>61</v>
       </c>
       <c r="AD270" t="n">
-        <v>3.489557264641911</v>
+        <v>3.48955726464191</v>
       </c>
       <c r="AE270" t="n">
         <v>42.60474344487245</v>
@@ -40535,7 +40535,7 @@
         <v>-1.303307022469304</v>
       </c>
       <c r="AL270" t="n">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="AM270" t="n">
         <v>10.81762752038992</v>
@@ -40553,7 +40553,7 @@
         <v>130.352212072612</v>
       </c>
       <c r="AR270" t="n">
-        <v>94.34782608695649</v>
+        <v>94.34782608695647</v>
       </c>
       <c r="AS270" t="n">
         <v>121.7822126908735</v>
@@ -40708,6 +40708,1333 @@
       </c>
       <c r="AS271" t="n">
         <v>282.0911257996851</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="I272" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J272" t="n">
+        <v>40.404358</v>
+      </c>
+      <c r="K272" t="n">
+        <v>67</v>
+      </c>
+      <c r="L272" t="n">
+        <v>62</v>
+      </c>
+      <c r="M272" t="n">
+        <v>33.31113727560344</v>
+      </c>
+      <c r="N272" t="n">
+        <v>40.40435717123184</v>
+      </c>
+      <c r="O272" t="n">
+        <v>36.16599705862657</v>
+      </c>
+      <c r="P272" t="n">
+        <v>36.00786961885688</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>1.669690243243161</v>
+      </c>
+      <c r="R272" t="n">
+        <v>34.20557104183149</v>
+      </c>
+      <c r="S272" t="n">
+        <v>38.15569122536131</v>
+      </c>
+      <c r="T272" t="n">
+        <v>2.538411515863537</v>
+      </c>
+      <c r="U272" t="n">
+        <v>1</v>
+      </c>
+      <c r="V272" t="n">
+        <v>275.1499938964844</v>
+      </c>
+      <c r="W272" t="n">
+        <v>333.739990234375</v>
+      </c>
+      <c r="X272" t="n">
+        <v>298.7311357042555</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>284.939494295067</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>312.522777113444</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>282.5380168055281</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>315.1660095214844</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>31.21898795984968</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>40.40435717123184</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>34.66314485757266</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>34.38984645735565</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>2.050208037458889</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>32.14202455931072</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>37.66537645538552</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>2.800307596854041</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>257.8688405483584</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>333.739990234375</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>286.3175765235501</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>269.3828581341398</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>303.2522949129606</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>265.4931228599065</v>
+      </c>
+      <c r="AS272" t="n">
+        <v>311.1160095214844</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>495.76</v>
+      </c>
+      <c r="I273" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J273" t="n">
+        <v>164.70432</v>
+      </c>
+      <c r="K273" t="n">
+        <v>63</v>
+      </c>
+      <c r="L273" t="n">
+        <v>62</v>
+      </c>
+      <c r="M273" t="n">
+        <v>103.754721587559</v>
+      </c>
+      <c r="N273" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="O273" t="n">
+        <v>155.8389410845991</v>
+      </c>
+      <c r="P273" t="n">
+        <v>162.5081997230405</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>20.9940656553267</v>
+      </c>
+      <c r="R273" t="n">
+        <v>127.3784859135466</v>
+      </c>
+      <c r="S273" t="n">
+        <v>179.11474609375</v>
+      </c>
+      <c r="T273" t="n">
+        <v>0.4222802319926778</v>
+      </c>
+      <c r="U273" t="n">
+        <v>0.532258064516129</v>
+      </c>
+      <c r="V273" t="n">
+        <v>312.3017119785525</v>
+      </c>
+      <c r="W273" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="X273" t="n">
+        <v>469.0752126646433</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>405.88307504211</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>532.2673502871767</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>383.4092425997752</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>539.1353857421875</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>72.05660262197819</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>190.4622862768955</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>121.6466920232603</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>123.9753685561307</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>39.42506750874811</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>75.52037537772701</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>174.2757408267162</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>1.092138344904178</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>0.7661290322580645</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>216.8903738921543</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>573.2914816934554</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>366.1565429900136</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>247.4870897886818</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>484.8259961913454</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>227.3163298869583</v>
+      </c>
+      <c r="AS273" t="n">
+        <v>524.5699798884158</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>247.23</v>
+      </c>
+      <c r="I274" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="J274" t="n">
+        <v>29.537634</v>
+      </c>
+      <c r="K274" t="n">
+        <v>67</v>
+      </c>
+      <c r="L274" t="n">
+        <v>62</v>
+      </c>
+      <c r="M274" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="N274" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="O274" t="n">
+        <v>31.02979353501777</v>
+      </c>
+      <c r="P274" t="n">
+        <v>30.59090883537913</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>2.428582184979229</v>
+      </c>
+      <c r="R274" t="n">
+        <v>28.4729664633719</v>
+      </c>
+      <c r="S274" t="n">
+        <v>34.83221801587561</v>
+      </c>
+      <c r="T274" t="n">
+        <v>-0.6144159107510424</v>
+      </c>
+      <c r="U274" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="V274" t="n">
+        <v>227.2815375624661</v>
+      </c>
+      <c r="W274" t="n">
+        <v>308.1724153782034</v>
+      </c>
+      <c r="X274" t="n">
+        <v>259.7193718880987</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>239.3921389998225</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>280.0466047763749</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>238.3187292984228</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>291.5456647928788</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>27.15430556301865</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>36.81868761985704</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>30.82159044296721</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>29.75592832685016</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>2.347410863751638</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>28.48110034705349</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>34.48855836512679</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>-0.5469670703130286</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>0.4435483870967742</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>227.2815375624661</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>308.1724153782034</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>257.9767120076355</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>238.3288830780343</v>
+      </c>
+      <c r="AQ274" t="n">
+        <v>277.6245409372367</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>238.3868099048377</v>
+      </c>
+      <c r="AS274" t="n">
+        <v>288.6692335161111</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>370.825</v>
+      </c>
+      <c r="I275" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J275" t="n">
+        <v>61.496685</v>
+      </c>
+      <c r="K275" t="n">
+        <v>34</v>
+      </c>
+      <c r="L275" t="n">
+        <v>62</v>
+      </c>
+      <c r="M275" t="n">
+        <v>59.97504362845778</v>
+      </c>
+      <c r="N275" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="O275" t="n">
+        <v>74.22354919074773</v>
+      </c>
+      <c r="P275" t="n">
+        <v>78.16764132553608</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>9.867965082485165</v>
+      </c>
+      <c r="R275" t="n">
+        <v>61.99584199267497</v>
+      </c>
+      <c r="S275" t="n">
+        <v>83.49376061274063</v>
+      </c>
+      <c r="T275" t="n">
+        <v>-1.289715162585737</v>
+      </c>
+      <c r="U275" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="V275" t="n">
+        <v>361.6495130796005</v>
+      </c>
+      <c r="W275" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="X275" t="n">
+        <v>447.5680016202089</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>388.0641721728232</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>507.0718310675944</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>373.8349272158301</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>503.467376494826</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>57.19493248774063</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>93.87329577470153</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>70.84663091430205</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>69.21845228833641</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>8.397041873220235</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>61.69609031740719</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>82.35048706768551</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>-1.113480920479962</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>0.08870967741935484</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>344.885442901076</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>566.0559735214503</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>427.2051844132414</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>376.5710219177234</v>
+      </c>
+      <c r="AQ275" t="n">
+        <v>477.8393469087594</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>372.0274246139654</v>
+      </c>
+      <c r="AS275" t="n">
+        <v>496.5734370181436</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="I276" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J276" t="n">
+        <v>26.361004</v>
+      </c>
+      <c r="K276" t="n">
+        <v>37</v>
+      </c>
+      <c r="L276" t="n">
+        <v>62</v>
+      </c>
+      <c r="M276" t="n">
+        <v>25.52936708172435</v>
+      </c>
+      <c r="N276" t="n">
+        <v>32.24051702254134</v>
+      </c>
+      <c r="O276" t="n">
+        <v>28.58556961735361</v>
+      </c>
+      <c r="P276" t="n">
+        <v>28.27269250795552</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>1.666109549843578</v>
+      </c>
+      <c r="R276" t="n">
+        <v>26.75293760205115</v>
+      </c>
+      <c r="S276" t="n">
+        <v>30.98122059471843</v>
+      </c>
+      <c r="T276" t="n">
+        <v>-1.335185683055754</v>
+      </c>
+      <c r="U276" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="V276" t="n">
+        <v>335.2005897830408</v>
+      </c>
+      <c r="W276" t="n">
+        <v>423.3179885059678</v>
+      </c>
+      <c r="X276" t="n">
+        <v>375.3285290758529</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>353.4525106864068</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>397.2045474652992</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>351.2660707149317</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>406.783426408653</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>25.26734640596091</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>34.04738340537852</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>28.93979991149203</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>28.47525856036268</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>1.96509574876542</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>26.79080259777322</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>32.14088799885089</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>-1.312300386946624</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>331.7602583102668</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>447.04214411262</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>379.9795728378903</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>354.1778656566004</v>
+      </c>
+      <c r="AQ276" t="n">
+        <v>405.7812800191803</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>351.7632381087623</v>
+      </c>
+      <c r="AS276" t="n">
+        <v>422.0098594249122</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>646.01</v>
+      </c>
+      <c r="I277" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="J277" t="n">
+        <v>23.482733</v>
+      </c>
+      <c r="K277" t="n">
+        <v>55</v>
+      </c>
+      <c r="L277" t="n">
+        <v>62</v>
+      </c>
+      <c r="M277" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="N277" t="n">
+        <v>28.88974010715996</v>
+      </c>
+      <c r="O277" t="n">
+        <v>22.84272144993821</v>
+      </c>
+      <c r="P277" t="n">
+        <v>22.19399968927557</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>2.4540903797399</v>
+      </c>
+      <c r="R277" t="n">
+        <v>20.51501731178977</v>
+      </c>
+      <c r="S277" t="n">
+        <v>28.43214246961805</v>
+      </c>
+      <c r="T277" t="n">
+        <v>0.2607937977123802</v>
+      </c>
+      <c r="U277" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="V277" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="W277" t="n">
+        <v>794.7567503479705</v>
+      </c>
+      <c r="X277" t="n">
+        <v>628.4032670878003</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>560.8912407411557</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>695.9152934344449</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>564.3681262473367</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>782.1682393391926</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>19.74072709517046</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>31.43082152229007</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>25.06299872865407</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>25.00814379246926</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>3.106496364292782</v>
+      </c>
+      <c r="AI277" t="n">
+        <v>21.21480091441762</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>28.73295069045338</v>
+      </c>
+      <c r="AK277" t="n">
+        <v>-0.508697111903375</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>0.4112903225806452</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>543.0674023881393</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>864.6619000781998</v>
+      </c>
+      <c r="AO277" t="n">
+        <v>689.4830950252735</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>604.0233800435792</v>
+      </c>
+      <c r="AQ277" t="n">
+        <v>774.942810006968</v>
+      </c>
+      <c r="AR277" t="n">
+        <v>583.6191731556287</v>
+      </c>
+      <c r="AS277" t="n">
+        <v>790.4434734943726</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="I278" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="J278" t="n">
+        <v>23.427723</v>
+      </c>
+      <c r="K278" t="n">
+        <v>67</v>
+      </c>
+      <c r="L278" t="n">
+        <v>62</v>
+      </c>
+      <c r="M278" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="N278" t="n">
+        <v>27.41190410795666</v>
+      </c>
+      <c r="O278" t="n">
+        <v>24.25814074269271</v>
+      </c>
+      <c r="P278" t="n">
+        <v>24.42886897495815</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>1.478985170888174</v>
+      </c>
+      <c r="R278" t="n">
+        <v>22.28791681925455</v>
+      </c>
+      <c r="S278" t="n">
+        <v>26.500766630436</v>
+      </c>
+      <c r="T278" t="n">
+        <v>-0.5614780722879187</v>
+      </c>
+      <c r="U278" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="V278" t="n">
+        <v>353.0400044214157</v>
+      </c>
+      <c r="W278" t="n">
+        <v>460.7941080547514</v>
+      </c>
+      <c r="X278" t="n">
+        <v>407.7793458846645</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>382.9176051620342</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>432.6410866072946</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>374.659881731669</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>445.4778870576292</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>124</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>21.00178491501581</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>34.18065338351818</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>24.9162534951076</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>24.72342929518021</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>2.273059395909297</v>
+      </c>
+      <c r="AI278" t="n">
+        <v>22.87523778279622</v>
+      </c>
+      <c r="AJ278" t="n">
+        <v>26.73035620330944</v>
+      </c>
+      <c r="AK278" t="n">
+        <v>-0.6548577207381492</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>0.2661290322580645</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>353.0400044214157</v>
+      </c>
+      <c r="AN278" t="n">
+        <v>574.5767833769405</v>
+      </c>
+      <c r="AO278" t="n">
+        <v>418.8422212527587</v>
+      </c>
+      <c r="AP278" t="n">
+        <v>380.6320928075234</v>
+      </c>
+      <c r="AQ278" t="n">
+        <v>457.0523496979939</v>
+      </c>
+      <c r="AR278" t="n">
+        <v>384.5327471288045</v>
+      </c>
+      <c r="AS278" t="n">
+        <v>449.3372877776317</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>68.95</v>
+      </c>
+      <c r="I279" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="J279" t="n">
+        <v>21.682388</v>
+      </c>
+      <c r="K279" t="n">
+        <v>68</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="inlineStr"/>
+      <c r="T279" t="inlineStr"/>
+      <c r="U279" t="inlineStr"/>
+      <c r="V279" t="inlineStr"/>
+      <c r="W279" t="inlineStr"/>
+      <c r="X279" t="inlineStr"/>
+      <c r="Y279" t="inlineStr"/>
+      <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
+      <c r="AB279" t="inlineStr"/>
+      <c r="AC279" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>3.489557264641911</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>42.60474344487245</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>34.20593017834855</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>36.47430781790388</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>7.843170490235964</v>
+      </c>
+      <c r="AI279" t="n">
+        <v>30.43478260869564</v>
+      </c>
+      <c r="AJ279" t="n">
+        <v>39.28458473899146</v>
+      </c>
+      <c r="AK279" t="n">
+        <v>-1.596744861524969</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>11.09679210156128</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>135.4830841546944</v>
+      </c>
+      <c r="AO279" t="n">
+        <v>108.7748579671484</v>
+      </c>
+      <c r="AP279" t="n">
+        <v>83.83357580819802</v>
+      </c>
+      <c r="AQ279" t="n">
+        <v>133.7161401260987</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>96.78260869565213</v>
+      </c>
+      <c r="AS279" t="n">
+        <v>124.9249794699929</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-07-17 16:13:03</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>SEC point-in-time</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="I280" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="J280" t="n">
+        <v>31.058191</v>
+      </c>
+      <c r="K280" t="n">
+        <v>65</v>
+      </c>
+      <c r="L280" t="n">
+        <v>62</v>
+      </c>
+      <c r="M280" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="N280" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="O280" t="n">
+        <v>35.78177020142998</v>
+      </c>
+      <c r="P280" t="n">
+        <v>32.68376769552187</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>5.740447822600014</v>
+      </c>
+      <c r="R280" t="n">
+        <v>30.27902016048226</v>
+      </c>
+      <c r="S280" t="n">
+        <v>44.72591882822464</v>
+      </c>
+      <c r="T280" t="n">
+        <v>-0.8228590081131566</v>
+      </c>
+      <c r="U280" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="V280" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="W280" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="X280" t="n">
+        <v>233.6549594153378</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>196.1698351337597</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>271.1400836969159</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>197.7220016479492</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>292.0602499483069</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>99</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>29.48392018059676</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>48.11020520268654</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>36.2906447186451</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>36.20204069176499</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>4.690828611385312</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>30.68208235876483</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>43.23142849669164</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>-1.115464697632566</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>192.5299987792968</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>314.1596399735431</v>
+      </c>
+      <c r="AO280" t="n">
+        <v>236.9779100127525</v>
+      </c>
+      <c r="AP280" t="n">
+        <v>206.3467991804064</v>
+      </c>
+      <c r="AQ280" t="n">
+        <v>267.6090208450987</v>
+      </c>
+      <c r="AR280" t="n">
+        <v>200.3539978027343</v>
+      </c>
+      <c r="AS280" t="n">
+        <v>282.3012280833964</v>
       </c>
     </row>
   </sheetData>
@@ -40954,12 +42281,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-16 16:22:58</t>
+          <t>2026-07-17 16:13:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -40988,13 +42315,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>353.81</v>
+        <v>346.12</v>
       </c>
       <c r="I2" t="n">
-        <v>13.11</v>
+        <v>13.13</v>
       </c>
       <c r="J2" t="n">
-        <v>26.987797</v>
+        <v>26.361004</v>
       </c>
       <c r="K2" t="n">
         <v>37</v>
@@ -41009,49 +42336,49 @@
         <v>32.24051702254134</v>
       </c>
       <c r="O2" t="n">
-        <v>28.66614436137828</v>
+        <v>28.58556961735361</v>
       </c>
       <c r="P2" t="n">
-        <v>28.36308133774909</v>
+        <v>28.27269250795552</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.679483717861193</v>
+        <v>1.666109549843578</v>
       </c>
       <c r="R2" t="n">
-        <v>26.81037373255447</v>
+        <v>26.75293760205115</v>
       </c>
       <c r="S2" t="n">
-        <v>31.22081491927324</v>
+        <v>30.98122059471843</v>
       </c>
       <c r="T2" t="n">
-